--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="1219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="1220">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,67 +44,67 @@
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.957332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3883285522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.889612197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8527965545654</t>
+    <t xml:space="preserve">14.057746887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9573335647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3883295059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896131515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8527956008911</t>
   </si>
   <si>
     <t xml:space="preserve">12.9532089233398</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6185007095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3842039108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8821401596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7348699569702</t>
+    <t xml:space="preserve">12.6184997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846181869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.384204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8821420669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7348709106445</t>
   </si>
   <si>
     <t xml:space="preserve">11.2127256393433</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7307453155518</t>
+    <t xml:space="preserve">10.7307472229004</t>
   </si>
   <si>
     <t xml:space="preserve">11.2294607162476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2194204330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2461967468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.914834022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1323947906494</t>
+    <t xml:space="preserve">11.2194194793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2461948394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9148349761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1323938369751</t>
   </si>
   <si>
     <t xml:space="preserve">11.6143751144409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6813182830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5474338531494</t>
+    <t xml:space="preserve">11.6813163757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5474328994751</t>
   </si>
   <si>
     <t xml:space="preserve">11.3466091156006</t>
@@ -113,31 +113,31 @@
     <t xml:space="preserve">11.3131370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">11.329873085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8947525024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8780164718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0453720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4261608123779</t>
+    <t xml:space="preserve">11.3298721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8947534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8780174255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.045371055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4261617660522</t>
   </si>
   <si>
     <t xml:space="preserve">10.4094266891479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7080945968628</t>
+    <t xml:space="preserve">11.7080936431885</t>
   </si>
   <si>
     <t xml:space="preserve">11.7147874832153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0494966506958</t>
+    <t xml:space="preserve">12.0494956970215</t>
   </si>
   <si>
     <t xml:space="preserve">11.7482576370239</t>
@@ -146,52 +146,52 @@
     <t xml:space="preserve">11.744912147522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2135019302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3674697875977</t>
+    <t xml:space="preserve">12.2135028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168483734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3674688339233</t>
   </si>
   <si>
     <t xml:space="preserve">12.7189111709595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8293676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0201501846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2209758758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3849840164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870895385742</t>
+    <t xml:space="preserve">12.8293685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0201511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2209749221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3849830627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870923995972</t>
   </si>
   <si>
     <t xml:space="preserve">13.0536212921143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3347749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3146924972534</t>
+    <t xml:space="preserve">13.3347759246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3146944046021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0569677352905</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2109327316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661832809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306047439575</t>
+    <t xml:space="preserve">13.2109336853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306028366089</t>
   </si>
   <si>
     <t xml:space="preserve">13.2879161834717</t>
@@ -200,28 +200,28 @@
     <t xml:space="preserve">12.8260183334351</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9833335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9030017852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2377090454102</t>
+    <t xml:space="preserve">12.9833326339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.903003692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2377099990845</t>
   </si>
   <si>
     <t xml:space="preserve">13.1674222946167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1138677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5046977996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8092832565308</t>
+    <t xml:space="preserve">13.1138668060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971345901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5046997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8092842102051</t>
   </si>
   <si>
     <t xml:space="preserve">12.886266708374</t>
@@ -230,43 +230,43 @@
     <t xml:space="preserve">12.7055234909058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7222595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9163904190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0301923751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327150344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6318883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7021751403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8695316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5582513809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5682945251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8360586166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494482040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958946228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5348224639893</t>
+    <t xml:space="preserve">12.7222576141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9163885116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0301904678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.631890296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7021780014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8695287704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.558253288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5682916641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8360595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494501113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5348234176636</t>
   </si>
   <si>
     <t xml:space="preserve">12.7791614532471</t>
@@ -284,31 +284,31 @@
     <t xml:space="preserve">12.6512584686279</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7527379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5836067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4990377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5700740814209</t>
+    <t xml:space="preserve">12.7527389526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5836038589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4990367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5700721740723</t>
   </si>
   <si>
     <t xml:space="preserve">12.5159521102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2791604995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0660524368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1641492843628</t>
+    <t xml:space="preserve">12.2791624069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0660514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776809692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1641511917114</t>
   </si>
   <si>
     <t xml:space="preserve">12.1709156036377</t>
@@ -320,22 +320,22 @@
     <t xml:space="preserve">12.1269407272339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9814853668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7459754943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231382369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6973419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.778525352478</t>
+    <t xml:space="preserve">11.9814863204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7459726333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580219268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231372833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6973400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7785234451294</t>
   </si>
   <si>
     <t xml:space="preserve">11.2406768798828</t>
@@ -344,25 +344,25 @@
     <t xml:space="preserve">10.8212242126465</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6554708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0613956451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1967010498047</t>
+    <t xml:space="preserve">10.6554718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.061393737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.196702003479</t>
   </si>
   <si>
     <t xml:space="preserve">11.4064283370972</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6656179428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1886606216431</t>
+    <t xml:space="preserve">11.5248222351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6656198501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1886596679688</t>
   </si>
   <si>
     <t xml:space="preserve">10.5878171920776</t>
@@ -371,58 +371,58 @@
     <t xml:space="preserve">10.6825332641602</t>
   </si>
   <si>
-    <t xml:space="preserve">11.839412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0199728012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3616218566895</t>
+    <t xml:space="preserve">11.8394117355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0199747085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3616237640381</t>
   </si>
   <si>
     <t xml:space="preserve">13.0233564376831</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1924905776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4969320297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4698696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307569503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4800176620483</t>
+    <t xml:space="preserve">13.1924886703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4969301223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4698686599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307588577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.480016708374</t>
   </si>
   <si>
     <t xml:space="preserve">13.2939691543579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3108835220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548564910889</t>
+    <t xml:space="preserve">13.3108825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548574447632</t>
   </si>
   <si>
     <t xml:space="preserve">13.0740957260132</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0368843078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9489336013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0910081863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0707120895386</t>
+    <t xml:space="preserve">13.0368852615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9489345550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.091007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0707130432129</t>
   </si>
   <si>
     <t xml:space="preserve">12.9962930679321</t>
@@ -431,43 +431,43 @@
     <t xml:space="preserve">12.8576011657715</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1113014221191</t>
+    <t xml:space="preserve">13.1113033294678</t>
   </si>
   <si>
     <t xml:space="preserve">13.1248350143433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1823415756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.060564994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857242584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4123630523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5679693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4157476425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.513843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.706657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8352003097534</t>
+    <t xml:space="preserve">13.1823425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0605640411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857233047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4123649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.567967414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4157466888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5138425827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7066583633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8352012634277</t>
   </si>
   <si>
     <t xml:space="preserve">14.2106781005859</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4576148986816</t>
+    <t xml:space="preserve">14.4576168060303</t>
   </si>
   <si>
     <t xml:space="preserve">14.7552909851074</t>
@@ -479,58 +479,58 @@
     <t xml:space="preserve">15.0157585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9853115081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303470611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6652364730835</t>
+    <t xml:space="preserve">14.9853143692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303451538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6652336120605</t>
   </si>
   <si>
     <t xml:space="preserve">15.2897577285767</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8297100067139</t>
+    <t xml:space="preserve">14.8297109603882</t>
   </si>
   <si>
     <t xml:space="preserve">14.6842555999756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7722053527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9514875411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7485246658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7180805206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8770685195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7992639541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751663208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.90074634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2018051147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939819335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988460540771</t>
+    <t xml:space="preserve">14.7722072601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.951488494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7485275268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7180824279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8770694732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7992687225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751672744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9007472991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2018060684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988470077515</t>
   </si>
   <si>
     <t xml:space="preserve">14.9142789840698</t>
@@ -539,49 +539,49 @@
     <t xml:space="preserve">14.9278078079224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7383785247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7248449325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5421838760376</t>
+    <t xml:space="preserve">14.7383766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7248468399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.542181968689</t>
   </si>
   <si>
     <t xml:space="preserve">14.4440841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0529689788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1442995071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1104726791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.954870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0901775360107</t>
+    <t xml:space="preserve">15.0529708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1104736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9548721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0901765823364</t>
   </si>
   <si>
     <t xml:space="preserve">15.2187204360962</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7823514938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707258224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6166000366211</t>
+    <t xml:space="preserve">14.7823524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707239151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6166019439697</t>
   </si>
   <si>
     <t xml:space="preserve">14.3764314651489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1599397659302</t>
+    <t xml:space="preserve">14.1599388122559</t>
   </si>
   <si>
     <t xml:space="preserve">14.2546548843384</t>
@@ -590,58 +590,58 @@
     <t xml:space="preserve">14.0415420532227</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1125802993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.038161277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1430253982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903810501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527507781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2072944641113</t>
+    <t xml:space="preserve">14.1125831604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0381622314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1430244445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903820037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2072973251343</t>
   </si>
   <si>
     <t xml:space="preserve">14.3561334609985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4373188018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730497360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3087759017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2411212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3392200469971</t>
+    <t xml:space="preserve">14.4373178482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3087778091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2411222457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3392210006714</t>
   </si>
   <si>
     <t xml:space="preserve">14.2512712478638</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1464080810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058149337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.119345664978</t>
+    <t xml:space="preserve">14.1464071273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058158874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1193466186523</t>
   </si>
   <si>
     <t xml:space="preserve">14.2275915145874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2715644836426</t>
+    <t xml:space="preserve">14.2715673446655</t>
   </si>
   <si>
     <t xml:space="preserve">14.149790763855</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">14.0753707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0719861984253</t>
+    <t xml:space="preserve">14.0719881057739</t>
   </si>
   <si>
     <t xml:space="preserve">14.2749500274658</t>
@@ -659,37 +659,37 @@
     <t xml:space="preserve">14.1667051315308</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4779100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267499923706</t>
+    <t xml:space="preserve">14.4779109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267490386963</t>
   </si>
   <si>
     <t xml:space="preserve">14.7519092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8161773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1037063598633</t>
+    <t xml:space="preserve">14.8161811828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1037101745605</t>
   </si>
   <si>
     <t xml:space="preserve">15.0834121704102</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1882753372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172380447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1544494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999029159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758033752441</t>
+    <t xml:space="preserve">15.1882734298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172409057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1544504165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758043289185</t>
   </si>
   <si>
     <t xml:space="preserve">15.3574113845825</t>
@@ -698,109 +698,109 @@
     <t xml:space="preserve">15.3912372589111</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4893360137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1713600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1003227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946199417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3168144226074</t>
+    <t xml:space="preserve">15.4893350601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1713619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1003265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3168163299561</t>
   </si>
   <si>
     <t xml:space="preserve">15.3134346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4182977676392</t>
+    <t xml:space="preserve">15.4182996749878</t>
   </si>
   <si>
     <t xml:space="preserve">15.4250602722168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5366916656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6753807067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6449375152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7295074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6618509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6517028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6821489334106</t>
+    <t xml:space="preserve">15.536693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6753816604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6449403762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7295036315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6618528366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6517019271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6821479797363</t>
   </si>
   <si>
     <t xml:space="preserve">15.5637521743774</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4081516265869</t>
+    <t xml:space="preserve">15.4081497192383</t>
   </si>
   <si>
     <t xml:space="preserve">15.6415557861328</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7024402618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584672927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588899612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5874347686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6550855636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227420806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3350048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0339469909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4060459136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4026622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4195747375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6935691833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0994968414307</t>
+    <t xml:space="preserve">15.7024431228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584701538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588918685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5874338150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.655086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227401733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3350067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0339488983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4060440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4026584625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4195728302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6935710906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.099494934082</t>
   </si>
   <si>
     <t xml:space="preserve">16.9980144500732</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1671504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4208488464355</t>
+    <t xml:space="preserve">17.1671466827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4208526611328</t>
   </si>
   <si>
     <t xml:space="preserve">17.5392436981201</t>
@@ -812,49 +812,49 @@
     <t xml:space="preserve">17.403938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4885025024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3531970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3870258331299</t>
+    <t xml:space="preserve">17.4885063171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3531951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3870277404785</t>
   </si>
   <si>
     <t xml:space="preserve">17.522331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4546756744385</t>
+    <t xml:space="preserve">17.4546775817871</t>
   </si>
   <si>
     <t xml:space="preserve">17.877513885498</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8098602294922</t>
+    <t xml:space="preserve">17.8098621368408</t>
   </si>
   <si>
     <t xml:space="preserve">17.7083778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7591209411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6745529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.573070526123</t>
+    <t xml:space="preserve">17.7591171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6745510101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730724334717</t>
   </si>
   <si>
     <t xml:space="preserve">17.3362827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2009735107422</t>
+    <t xml:space="preserve">17.2009754180908</t>
   </si>
   <si>
     <t xml:space="preserve">17.2348041534424</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2517166137695</t>
+    <t xml:space="preserve">17.2517147064209</t>
   </si>
   <si>
     <t xml:space="preserve">17.2178897857666</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">17.3701095581055</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4560203552246</t>
+    <t xml:space="preserve">17.456018447876</t>
   </si>
   <si>
     <t xml:space="preserve">17.7147541046143</t>
@@ -872,70 +872,70 @@
     <t xml:space="preserve">17.5767631530762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.559513092041</t>
+    <t xml:space="preserve">17.5595149993896</t>
   </si>
   <si>
     <t xml:space="preserve">17.6975059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4698162078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.614709854126</t>
+    <t xml:space="preserve">17.469820022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6147117614746</t>
   </si>
   <si>
     <t xml:space="preserve">16.7729568481445</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0075435638428</t>
+    <t xml:space="preserve">17.0075454711914</t>
   </si>
   <si>
     <t xml:space="preserve">17.1662349700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1317386627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.993745803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9868469238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9661483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8350563049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8488540649414</t>
+    <t xml:space="preserve">17.1317367553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9937477111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9868450164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9661464691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.835054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.84885597229</t>
   </si>
   <si>
     <t xml:space="preserve">16.8281555175781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7591609954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8695545196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9178524017334</t>
+    <t xml:space="preserve">16.7591590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8695526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9178504943848</t>
   </si>
   <si>
     <t xml:space="preserve">16.9730491638184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9385509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1524353027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6625633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5935668945312</t>
+    <t xml:space="preserve">16.9385471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1524391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6625652313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5935649871826</t>
   </si>
   <si>
     <t xml:space="preserve">16.5659713745117</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">16.5038738250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9040508270264</t>
+    <t xml:space="preserve">16.8626518249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9040470123291</t>
   </si>
   <si>
     <t xml:space="preserve">16.80055809021</t>
@@ -956,40 +956,40 @@
     <t xml:space="preserve">16.8971519470215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5383701324463</t>
+    <t xml:space="preserve">16.5383739471436</t>
   </si>
   <si>
     <t xml:space="preserve">16.5590705871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4900741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2416877746582</t>
+    <t xml:space="preserve">16.4900722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2416858673096</t>
   </si>
   <si>
     <t xml:space="preserve">16.303783416748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2485866546631</t>
+    <t xml:space="preserve">16.2485885620117</t>
   </si>
   <si>
     <t xml:space="preserve">16.1243953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1864910125732</t>
+    <t xml:space="preserve">16.1864929199219</t>
   </si>
   <si>
     <t xml:space="preserve">16.1588916778564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.53147315979</t>
+    <t xml:space="preserve">16.5314693450928</t>
   </si>
   <si>
     <t xml:space="preserve">16.2899875640869</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3175830841064</t>
+    <t xml:space="preserve">16.3175849914551</t>
   </si>
   <si>
     <t xml:space="preserve">16.5452709197998</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">16.3658809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.462474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3313827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3520832061768</t>
+    <t xml:space="preserve">16.4624767303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3313846588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3520812988281</t>
   </si>
   <si>
     <t xml:space="preserve">16.6970615386963</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">16.3865776062012</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4486789703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5107746124268</t>
+    <t xml:space="preserve">16.4486770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5107727050781</t>
   </si>
   <si>
     <t xml:space="preserve">16.4210777282715</t>
@@ -1025,16 +1025,16 @@
     <t xml:space="preserve">16.4348773956299</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3934803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4969730377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5245704650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4003810882568</t>
+    <t xml:space="preserve">16.393482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4969749450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5245723724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4003772735596</t>
   </si>
   <si>
     <t xml:space="preserve">16.4555759429932</t>
@@ -1043,160 +1043,160 @@
     <t xml:space="preserve">16.358980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2830867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5521697998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.179594039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2071933746338</t>
+    <t xml:space="preserve">16.2830848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5521678924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1795902252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2071876525879</t>
   </si>
   <si>
     <t xml:space="preserve">16.1933898925781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1519927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9036073684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5586261749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4965305328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9381046295166</t>
+    <t xml:space="preserve">16.1519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9036064147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5586252212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4965295791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9381065368652</t>
   </si>
   <si>
     <t xml:space="preserve">15.7794151306152</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7656145095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7863111495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9795036315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9312047958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.703516960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6483192443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8415098190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7518148422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691082000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8622102737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0278015136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8967094421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6276206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7173194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310306549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034284591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413328170776</t>
+    <t xml:space="preserve">15.7656154632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7863130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9795026779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.931206703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7035188674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.648323059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8415107727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7518167495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691091537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8622093200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0277996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8967084884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6276216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7173175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310277938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034294128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413318634033</t>
   </si>
   <si>
     <t xml:space="preserve">15.248143196106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3171415328979</t>
+    <t xml:space="preserve">15.3171377182007</t>
   </si>
   <si>
     <t xml:space="preserve">15.3309392929077</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2826404571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792390823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.26194190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.600025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896306991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9519033432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.972601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.986400604248</t>
+    <t xml:space="preserve">15.282639503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792371749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.261944770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6000232696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.489631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.951904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9726028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9864025115967</t>
   </si>
   <si>
     <t xml:space="preserve">16.0416011810303</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8553113937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932138442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758291244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2895412445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1791467666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2067489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3999328613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2343435287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3033409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137363433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.386137008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6345224380493</t>
+    <t xml:space="preserve">15.8553104400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932147979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.475830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2895431518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1791477203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2067461013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3999347686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2343454360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033418655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137334823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3861360549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.634521484375</t>
   </si>
   <si>
     <t xml:space="preserve">16.1450939178467</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">16.6073684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">16.37278175354</t>
+    <t xml:space="preserve">16.3727798461914</t>
   </si>
   <si>
     <t xml:space="preserve">16.6349658966064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.414176940918</t>
+    <t xml:space="preserve">16.4141788482666</t>
   </si>
   <si>
     <t xml:space="preserve">16.0898952484131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2002906799316</t>
+    <t xml:space="preserve">16.200288772583</t>
   </si>
   <si>
     <t xml:space="preserve">16.7315616607666</t>
@@ -1232,34 +1232,34 @@
     <t xml:space="preserve">16.4762744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7522621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6487655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6280670166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0420417785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0765419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1110382080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2145347595215</t>
+    <t xml:space="preserve">16.7522602081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6487636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6280651092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0420436859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0765399932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1110363006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2145328521729</t>
   </si>
   <si>
     <t xml:space="preserve">17.1455364227295</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1800346374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0070991516113</t>
+    <t xml:space="preserve">17.1800365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0071029663086</t>
   </si>
   <si>
     <t xml:space="preserve">16.21409034729</t>
@@ -1268,127 +1268,127 @@
     <t xml:space="preserve">16.110595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5931253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621217727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0066566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7306728363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9031658172607</t>
+    <t xml:space="preserve">15.5931234359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0066585540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.730673789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9031639099121</t>
   </si>
   <si>
     <t xml:space="preserve">14.9721603393555</t>
   </si>
   <si>
-    <t xml:space="preserve">15.455132484436</t>
+    <t xml:space="preserve">15.4551296234131</t>
   </si>
   <si>
     <t xml:space="preserve">15.1101493835449</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0411539077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0756521224976</t>
+    <t xml:space="preserve">15.0411548614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0756530761719</t>
   </si>
   <si>
     <t xml:space="preserve">15.3516397476196</t>
   </si>
   <si>
-    <t xml:space="preserve">15.42063331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5241298675537</t>
+    <t xml:space="preserve">15.4206342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5241289138794</t>
   </si>
   <si>
     <t xml:space="preserve">15.6966190338135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0156631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8742475509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5560550689697</t>
+    <t xml:space="preserve">16.0156669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8742485046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.556056022644</t>
   </si>
   <si>
     <t xml:space="preserve">15.7328300476074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5914125442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3439292907715</t>
+    <t xml:space="preserve">15.5914087295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3439273834229</t>
   </si>
   <si>
     <t xml:space="preserve">15.3792839050293</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7782535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4247074127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5307703018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600610733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.495415687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8873147964478</t>
+    <t xml:space="preserve">14.7782545089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4247064590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5307683944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600620269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4954147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8873157501221</t>
   </si>
   <si>
     <t xml:space="preserve">14.1135854721069</t>
   </si>
   <si>
-    <t xml:space="preserve">14.318642616272</t>
+    <t xml:space="preserve">14.3186407089233</t>
   </si>
   <si>
     <t xml:space="preserve">14.6014785766602</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0257349014282</t>
+    <t xml:space="preserve">15.0257339477539</t>
   </si>
   <si>
     <t xml:space="preserve">15.061089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9550256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8489618301392</t>
+    <t xml:space="preserve">14.9550266265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8489627838135</t>
   </si>
   <si>
     <t xml:space="preserve">14.884316444397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7075424194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2025089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5661268234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.636833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2832889556885</t>
+    <t xml:space="preserve">14.7075443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2025108337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.566125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6368350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2832870483398</t>
   </si>
   <si>
     <t xml:space="preserve">14.0853004455566</t>
@@ -1397,28 +1397,28 @@
     <t xml:space="preserve">14.8136081695557</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3539962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3893518447876</t>
+    <t xml:space="preserve">14.3539981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3893527984619</t>
   </si>
   <si>
     <t xml:space="preserve">14.74289894104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1418685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1772232055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.247932434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2125806808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0711612701416</t>
+    <t xml:space="preserve">14.1418695449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1772241592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2479333877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2125778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0711603164673</t>
   </si>
   <si>
     <t xml:space="preserve">13.9438829421997</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">13.8731746673584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8166093826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8590335845947</t>
+    <t xml:space="preserve">13.8166055679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8590316772461</t>
   </si>
   <si>
     <t xml:space="preserve">14.0145921707153</t>
@@ -1439,13 +1439,13 @@
     <t xml:space="preserve">13.929741859436</t>
   </si>
   <si>
-    <t xml:space="preserve">14.000449180603</t>
+    <t xml:space="preserve">14.0004482269287</t>
   </si>
   <si>
     <t xml:space="preserve">14.0994443893433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9721660614014</t>
+    <t xml:space="preserve">13.97216796875</t>
   </si>
   <si>
     <t xml:space="preserve">14.0287351608276</t>
@@ -1454,34 +1454,34 @@
     <t xml:space="preserve">14.057017326355</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1277284622192</t>
+    <t xml:space="preserve">14.1277256011963</t>
   </si>
   <si>
     <t xml:space="preserve">14.9196739196777</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6721887588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4347763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5054845809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4913444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3782072067261</t>
+    <t xml:space="preserve">14.6721897125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.434775352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.505485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4913425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3782081604004</t>
   </si>
   <si>
     <t xml:space="preserve">13.4630603790283</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5620517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5337677001953</t>
+    <t xml:space="preserve">13.5620536804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.533766746521</t>
   </si>
   <si>
     <t xml:space="preserve">13.1660814285278</t>
@@ -1490,37 +1490,37 @@
     <t xml:space="preserve">12.7842493057251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6852560043335</t>
+    <t xml:space="preserve">12.6852569580078</t>
   </si>
   <si>
     <t xml:space="preserve">12.1620082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6569728851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4064922332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5479106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7883224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7741813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5903358459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.448917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3074989318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3923501968384</t>
+    <t xml:space="preserve">12.6569719314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4064912796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5479116439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7883234024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7741794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5903377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4489154815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3074998855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3923511505127</t>
   </si>
   <si>
     <t xml:space="preserve">13.0105199813843</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">13.0388031005859</t>
   </si>
   <si>
-    <t xml:space="preserve">12.996376991272</t>
+    <t xml:space="preserve">12.9963779449463</t>
   </si>
   <si>
     <t xml:space="preserve">13.2367887496948</t>
@@ -1547,19 +1547,19 @@
     <t xml:space="preserve">13.0953712463379</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6469020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6751871109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0670871734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2509307861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2085046768188</t>
+    <t xml:space="preserve">13.6469030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6751899719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0670862197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2509298324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2085075378418</t>
   </si>
   <si>
     <t xml:space="preserve">13.0812292098999</t>
@@ -1580,118 +1580,118 @@
     <t xml:space="preserve">12.6004047393799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7317543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5761957168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.519627571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7176132202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8307466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7600383758545</t>
+    <t xml:space="preserve">13.7317533493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5761947631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5196285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7176141738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8307476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7600402832031</t>
   </si>
   <si>
     <t xml:space="preserve">13.915599822998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7458972930908</t>
+    <t xml:space="preserve">13.7458963394165</t>
   </si>
   <si>
     <t xml:space="preserve">14.0428771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8448905944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.541766166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2218475341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9455537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1782245635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9891805648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2073078155518</t>
+    <t xml:space="preserve">13.8448896408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5417680740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.221848487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9455556869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1782236099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9891815185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2073068618774</t>
   </si>
   <si>
     <t xml:space="preserve">14.4399757385254</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2654752731323</t>
+    <t xml:space="preserve">14.2654733657837</t>
   </si>
   <si>
     <t xml:space="preserve">14.4108905792236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4981412887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690580368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527250289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3381814956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5126838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3963489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871852874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4254322052002</t>
+    <t xml:space="preserve">14.498143196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690561294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527240753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3381834030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5126819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3963508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871862411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4254331588745</t>
   </si>
   <si>
     <t xml:space="preserve">14.4835996627808</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6144771575928</t>
+    <t xml:space="preserve">14.6144762039185</t>
   </si>
   <si>
     <t xml:space="preserve">14.8326034545898</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9780187606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1234378814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1961469650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4142742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.450629234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3415660858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2325029373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3052110671997</t>
+    <t xml:space="preserve">14.9780206680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1234369277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1961479187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4142732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.450626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3415651321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2325000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3052101135254</t>
   </si>
   <si>
     <t xml:space="preserve">15.268856048584</t>
@@ -1700,43 +1700,43 @@
     <t xml:space="preserve">15.6687545776367</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0507278442383</t>
+    <t xml:space="preserve">15.0507307052612</t>
   </si>
   <si>
     <t xml:space="preserve">15.0870847702026</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9416637420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7235374450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0143756866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5781211853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7598924636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6508302688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3672647476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3236408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5272264480591</t>
+    <t xml:space="preserve">14.9416666030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7235383987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0143747329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5781221389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7598943710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6508321762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3672666549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3236427307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5272254943848</t>
   </si>
   <si>
     <t xml:space="preserve">14.4545154571533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7962484359741</t>
+    <t xml:space="preserve">14.7962474822998</t>
   </si>
   <si>
     <t xml:space="preserve">14.9053106307983</t>
@@ -1745,31 +1745,31 @@
     <t xml:space="preserve">16.032299041748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.359489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5049057006836</t>
+    <t xml:space="preserve">16.3594875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5049076080322</t>
   </si>
   <si>
     <t xml:space="preserve">16.6139698028564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5412616729736</t>
+    <t xml:space="preserve">16.541259765625</t>
   </si>
   <si>
     <t xml:space="preserve">16.8320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6503238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.577615737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8684520721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7593860626221</t>
+    <t xml:space="preserve">16.6503257751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5776138305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8684501647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7593879699707</t>
   </si>
   <si>
     <t xml:space="preserve">17.0502223968506</t>
@@ -1778,25 +1778,25 @@
     <t xml:space="preserve">17.086576461792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4864768981934</t>
+    <t xml:space="preserve">17.4864730834961</t>
   </si>
   <si>
     <t xml:space="preserve">17.4137668609619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.268346786499</t>
+    <t xml:space="preserve">17.2683486938477</t>
   </si>
   <si>
     <t xml:space="preserve">17.5228309631348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.813663482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7409572601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6318950653076</t>
+    <t xml:space="preserve">17.8136672973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7409553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.631893157959</t>
   </si>
   <si>
     <t xml:space="preserve">17.7046031951904</t>
@@ -1808,25 +1808,25 @@
     <t xml:space="preserve">18.0681476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9227275848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1044998168945</t>
+    <t xml:space="preserve">17.9227256774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1045017242432</t>
   </si>
   <si>
     <t xml:space="preserve">17.8500194549561</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9590816497803</t>
+    <t xml:space="preserve">17.9590835571289</t>
   </si>
   <si>
     <t xml:space="preserve">18.1772079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0317916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2862720489502</t>
+    <t xml:space="preserve">18.0317897796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2862701416016</t>
   </si>
   <si>
     <t xml:space="preserve">18.358980178833</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">17.5591831207275</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5955390930176</t>
+    <t xml:space="preserve">17.5955371856689</t>
   </si>
   <si>
     <t xml:space="preserve">17.4501209259033</t>
@@ -1865,16 +1865,16 @@
     <t xml:space="preserve">18.6134624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8315868377686</t>
+    <t xml:space="preserve">18.6861724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8315887451172</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9770069122314</t>
+    <t xml:space="preserve">18.9770050048828</t>
   </si>
   <si>
     <t xml:space="preserve">19.0860691070557</t>
@@ -1883,19 +1883,19 @@
     <t xml:space="preserve">19.26784324646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1224212646484</t>
+    <t xml:space="preserve">19.1224250793457</t>
   </si>
   <si>
     <t xml:space="preserve">19.3041954040527</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4132614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4496116638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9048023223877</t>
+    <t xml:space="preserve">19.4132595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4496154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9048042297363</t>
   </si>
   <si>
     <t xml:space="preserve">16.7230319976807</t>
@@ -1904,61 +1904,61 @@
     <t xml:space="preserve">16.4321975708008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7957420349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2314872741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9775161743164</t>
+    <t xml:space="preserve">16.7957401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2314891815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9775123596191</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047027587891</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3774147033691</t>
+    <t xml:space="preserve">17.3774127960205</t>
   </si>
   <si>
     <t xml:space="preserve">18.7952346801758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5407562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8679447174072</t>
+    <t xml:space="preserve">18.5407543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8679428100586</t>
   </si>
   <si>
     <t xml:space="preserve">18.904296875</t>
   </si>
   <si>
+    <t xml:space="preserve">19.8495101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.42138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7327499389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3943996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8105926513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3554821014404</t>
+  </si>
+  <si>
     <t xml:space="preserve">19.8495121002197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4213848114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7327518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.394401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8105945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3554801940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8495140075684</t>
-  </si>
-  <si>
     <t xml:space="preserve">20.1219577789307</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9273548126221</t>
+    <t xml:space="preserve">19.9273529052734</t>
   </si>
   <si>
     <t xml:space="preserve">19.4603061676025</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">19.966272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2657032012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7716693878174</t>
+    <t xml:space="preserve">19.2657012939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.771671295166</t>
   </si>
   <si>
     <t xml:space="preserve">18.7597370147705</t>
@@ -1985,37 +1985,37 @@
     <t xml:space="preserve">20.1608772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.044116973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1728134155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0560512542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9392890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2895755767822</t>
+    <t xml:space="preserve">20.0441150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.172815322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0560531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9392910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2895774841309</t>
   </si>
   <si>
     <t xml:space="preserve">21.0171318054199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7836093902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7057647705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0949726104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4452590942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7566223144531</t>
+    <t xml:space="preserve">20.7836055755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7057666778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.094970703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4452571868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7566242218018</t>
   </si>
   <si>
     <t xml:space="preserve">21.9512252807617</t>
@@ -2027,22 +2027,22 @@
     <t xml:space="preserve">21.7955436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0290641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0679874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5350360870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5739555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.651798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7685585021973</t>
+    <t xml:space="preserve">22.0290679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.067985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5350341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5739574432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6517944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7685565948486</t>
   </si>
   <si>
     <t xml:space="preserve">22.8074779510498</t>
@@ -2054,31 +2054,31 @@
     <t xml:space="preserve">22.3404312133789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2625923156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5080528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9750957489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4032230377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9091930389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7145900726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5199871063232</t>
+    <t xml:space="preserve">22.2625904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5080509185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.97509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4032249450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9091911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7145881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5199851989746</t>
   </si>
   <si>
     <t xml:space="preserve">25.298397064209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7924327850342</t>
+    <t xml:space="preserve">24.7924308776855</t>
   </si>
   <si>
     <t xml:space="preserve">25.1427154541016</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">24.7535095214844</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6367492675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1697006225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0140171051025</t>
+    <t xml:space="preserve">24.6367473602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.16969871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0140190124512</t>
   </si>
   <si>
     <t xml:space="preserve">23.0799236297607</t>
@@ -2102,49 +2102,49 @@
     <t xml:space="preserve">23.7026538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0529403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4691295623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5858917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1577644348145</t>
+    <t xml:space="preserve">24.0529384613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4691276550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5858898162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1577663421631</t>
   </si>
   <si>
     <t xml:space="preserve">23.8583354949951</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7415733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8194160461426</t>
+    <t xml:space="preserve">23.7415714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8194141387939</t>
   </si>
   <si>
     <t xml:space="preserve">23.6637325286865</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4302082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0918579101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3912887573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3523693084717</t>
+    <t xml:space="preserve">23.4302101135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0918598175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3912868499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3523654937744</t>
   </si>
   <si>
     <t xml:space="preserve">23.0410022735596</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0020809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1188449859619</t>
+    <t xml:space="preserve">23.0020790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1188430786133</t>
   </si>
   <si>
     <t xml:space="preserve">23.624813079834</t>
@@ -2153,19 +2153,19 @@
     <t xml:space="preserve">22.6128749847412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1069068908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1847515106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4961128234863</t>
+    <t xml:space="preserve">22.1069087982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1847476959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.496114730835</t>
   </si>
   <si>
     <t xml:space="preserve">22.3015098571777</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6907157897949</t>
+    <t xml:space="preserve">22.6907176971436</t>
   </si>
   <si>
     <t xml:space="preserve">22.3793525695801</t>
@@ -2174,37 +2174,37 @@
     <t xml:space="preserve">22.9631614685059</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2356033325195</t>
+    <t xml:space="preserve">23.2356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">22.9242420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2236709594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4182739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9123058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4841785430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1338939666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.523099899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7177028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6398582458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2506561279297</t>
+    <t xml:space="preserve">22.223669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4182720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9123039245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4841766357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1338901519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5230979919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.717700958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6398601531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2506523132324</t>
   </si>
   <si>
     <t xml:space="preserve">21.5620193481445</t>
@@ -2213,13 +2213,13 @@
     <t xml:space="preserve">21.8344612121582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.678783416748</t>
+    <t xml:space="preserve">21.6787815093994</t>
   </si>
   <si>
     <t xml:space="preserve">21.9901466369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1458282470703</t>
+    <t xml:space="preserve">22.1458301544189</t>
   </si>
   <si>
     <t xml:space="preserve">22.8464012145996</t>
@@ -2228,40 +2228,40 @@
     <t xml:space="preserve">22.8853187561035</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4571933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3284969329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2117347717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3674144744873</t>
+    <t xml:space="preserve">22.4571952819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2117328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3674163818359</t>
   </si>
   <si>
     <t xml:space="preserve">20.9782104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6279239654541</t>
+    <t xml:space="preserve">20.6279258728027</t>
   </si>
   <si>
     <t xml:space="preserve">21.873384475708</t>
   </si>
   <si>
-    <t xml:space="preserve">23.440731048584</t>
+    <t xml:space="preserve">23.4407329559326</t>
   </si>
   <si>
     <t xml:space="preserve">22.88356590271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7243766784668</t>
+    <t xml:space="preserve">22.7243747711182</t>
   </si>
   <si>
     <t xml:space="preserve">22.8039703369141</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7641754150391</t>
+    <t xml:space="preserve">22.7641735076904</t>
   </si>
   <si>
     <t xml:space="preserve">23.0427570343018</t>
@@ -2270,52 +2270,52 @@
     <t xml:space="preserve">23.2417449951172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0029582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2019462585449</t>
+    <t xml:space="preserve">23.0029563903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2019443511963</t>
   </si>
   <si>
     <t xml:space="preserve">23.122350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1621494293213</t>
+    <t xml:space="preserve">23.1621475219727</t>
   </si>
   <si>
     <t xml:space="preserve">23.5203247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9580993652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0774898529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4356708526611</t>
+    <t xml:space="preserve">23.9580974578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0774917602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4356689453125</t>
   </si>
   <si>
     <t xml:space="preserve">24.3162746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3560752868652</t>
+    <t xml:space="preserve">24.3560733795166</t>
   </si>
   <si>
     <t xml:space="preserve">24.7938442230225</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1570873260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6744518280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.913236618042</t>
+    <t xml:space="preserve">24.1570854187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6744537353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9132385253906</t>
   </si>
   <si>
     <t xml:space="preserve">24.555061340332</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7540473937988</t>
+    <t xml:space="preserve">24.7540493011475</t>
   </si>
   <si>
     <t xml:space="preserve">24.2764778137207</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">24.1172885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5152626037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4754657745361</t>
+    <t xml:space="preserve">24.5152645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4754638671875</t>
   </si>
   <si>
     <t xml:space="preserve">24.2366828918457</t>
@@ -2336,22 +2336,22 @@
     <t xml:space="preserve">24.3958721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7142486572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6346549987793</t>
+    <t xml:space="preserve">24.7142505645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6346569061279</t>
   </si>
   <si>
     <t xml:space="preserve">24.1968841552734</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6295948028564</t>
+    <t xml:space="preserve">25.6295928955078</t>
   </si>
   <si>
     <t xml:space="preserve">25.5102005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1520252227783</t>
+    <t xml:space="preserve">25.1520233154297</t>
   </si>
   <si>
     <t xml:space="preserve">25.3510131835938</t>
@@ -2363,13 +2363,13 @@
     <t xml:space="preserve">25.6693916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3908081054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.191822052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0326290130615</t>
+    <t xml:space="preserve">25.3908100128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1918201446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0326328277588</t>
   </si>
   <si>
     <t xml:space="preserve">25.2714157104492</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">24.8336429595947</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9530353546143</t>
+    <t xml:space="preserve">24.9530372619629</t>
   </si>
   <si>
     <t xml:space="preserve">25.8683795928955</t>
@@ -2387,19 +2387,19 @@
     <t xml:space="preserve">25.0724296569824</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7591094970703</t>
+    <t xml:space="preserve">23.7591133117676</t>
   </si>
   <si>
     <t xml:space="preserve">23.4805278778076</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8785057067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6397190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7989063262939</t>
+    <t xml:space="preserve">23.8785037994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6397171020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7989082336426</t>
   </si>
   <si>
     <t xml:space="preserve">24.5948581695557</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">25.430606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3112144470215</t>
+    <t xml:space="preserve">25.3112106323242</t>
   </si>
   <si>
     <t xml:space="preserve">25.2316188812256</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">25.9479732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1071624755859</t>
+    <t xml:space="preserve">26.1071643829346</t>
   </si>
   <si>
     <t xml:space="preserve">25.7489852905273</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">24.8734397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0376949310303</t>
+    <t xml:space="preserve">24.0376930236816</t>
   </si>
   <si>
     <t xml:space="preserve">22.3263988494873</t>
@@ -2468,28 +2468,28 @@
     <t xml:space="preserve">23.5999202728271</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3611354827881</t>
+    <t xml:space="preserve">23.3611373901367</t>
   </si>
   <si>
     <t xml:space="preserve">23.4009323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5601215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4855899810791</t>
+    <t xml:space="preserve">23.5601234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4855918884277</t>
   </si>
   <si>
     <t xml:space="preserve">23.8387050628662</t>
   </si>
   <si>
-    <t xml:space="preserve">23.997896194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.719310760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8264102935791</t>
+    <t xml:space="preserve">23.9978942871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7193126678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8264083862305</t>
   </si>
   <si>
     <t xml:space="preserve">23.5692901611328</t>
@@ -2522,25 +2522,25 @@
     <t xml:space="preserve">24.2549419403076</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977981567383</t>
+    <t xml:space="preserve">24.2977962493896</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264377593994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.99782371521</t>
+    <t xml:space="preserve">23.9978218078613</t>
   </si>
   <si>
     <t xml:space="preserve">23.9121170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8692646026611</t>
+    <t xml:space="preserve">23.8692626953125</t>
   </si>
   <si>
     <t xml:space="preserve">23.7407035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6549968719482</t>
+    <t xml:space="preserve">23.6549987792969</t>
   </si>
   <si>
     <t xml:space="preserve">22.9693431854248</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">22.5836658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">22.92649269104</t>
+    <t xml:space="preserve">22.9264907836914</t>
   </si>
   <si>
     <t xml:space="preserve">23.1407585144043</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">22.7550773620605</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6693744659424</t>
+    <t xml:space="preserve">22.6693725585938</t>
   </si>
   <si>
     <t xml:space="preserve">23.0550518035889</t>
@@ -2573,13 +2573,13 @@
     <t xml:space="preserve">23.2264652252197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7122249603271</t>
+    <t xml:space="preserve">22.7122268676758</t>
   </si>
   <si>
     <t xml:space="preserve">22.4122524261475</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1836090087891</t>
+    <t xml:space="preserve">23.1836109161377</t>
   </si>
   <si>
     <t xml:space="preserve">23.0979061126709</t>
@@ -2591,10 +2591,10 @@
     <t xml:space="preserve">23.3550243377686</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0121974945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3121719360352</t>
+    <t xml:space="preserve">23.0121994018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3121738433838</t>
   </si>
   <si>
     <t xml:space="preserve">23.397876739502</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">22.7979316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4551086425781</t>
+    <t xml:space="preserve">22.4551067352295</t>
   </si>
   <si>
     <t xml:space="preserve">22.4979591369629</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">21.426628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4694805145264</t>
+    <t xml:space="preserve">21.469482421875</t>
   </si>
   <si>
     <t xml:space="preserve">21.2552146911621</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">20.1410293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9980964660645</t>
+    <t xml:space="preserve">20.9980945587158</t>
   </si>
   <si>
     <t xml:space="preserve">21.1266536712646</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5267105102539</t>
+    <t xml:space="preserve">20.5267086029053</t>
   </si>
   <si>
     <t xml:space="preserve">20.6552696228027</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">21.512336730957</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3409194946289</t>
+    <t xml:space="preserve">21.3409214019775</t>
   </si>
   <si>
     <t xml:space="preserve">22.0265731811523</t>
@@ -2684,19 +2684,19 @@
     <t xml:space="preserve">21.8123073577881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1551342010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2408390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6837482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7266006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8980140686035</t>
+    <t xml:space="preserve">22.1551322937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2408409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6837463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.726598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8980121612549</t>
   </si>
   <si>
     <t xml:space="preserve">21.7694530487061</t>
@@ -2705,28 +2705,28 @@
     <t xml:space="preserve">21.6408939361572</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1979866027832</t>
+    <t xml:space="preserve">22.1979846954346</t>
   </si>
   <si>
     <t xml:space="preserve">22.0694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9837207794189</t>
+    <t xml:space="preserve">21.9837188720703</t>
   </si>
   <si>
     <t xml:space="preserve">21.8551597595215</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1695079803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0838012695312</t>
+    <t xml:space="preserve">21.1695098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0838031768799</t>
   </si>
   <si>
     <t xml:space="preserve">21.9408664703369</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5551853179932</t>
+    <t xml:space="preserve">21.5551872253418</t>
   </si>
   <si>
     <t xml:space="preserve">21.0409488677979</t>
@@ -3669,6 +3669,9 @@
   </si>
   <si>
     <t xml:space="preserve">33.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4500007629395</t>
   </si>
 </sst>
 </file>
@@ -68721,7 +68724,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6497106481</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>54341</v>
@@ -68742,6 +68745,32 @@
         <v>1218</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6494328704</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>61976</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>33.4000015258789</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>32.9500007629395</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>33.4500007629395</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1219</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="1220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="1221">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8067150115967</t>
+    <t xml:space="preserve">13.806715965271</t>
   </si>
   <si>
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.057746887207</t>
+    <t xml:space="preserve">14.0577459335327</t>
   </si>
   <si>
     <t xml:space="preserve">13.9573335647583</t>
@@ -53,55 +53,55 @@
     <t xml:space="preserve">13.3883295059204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8896131515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8527956008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9532089233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6184997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846181869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.384204864502</t>
+    <t xml:space="preserve">12.889612197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8527975082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9532079696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.618501663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846162796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3842029571533</t>
   </si>
   <si>
     <t xml:space="preserve">11.8821420669556</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7348709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2127256393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7307472229004</t>
+    <t xml:space="preserve">11.7348718643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2127246856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7307462692261</t>
   </si>
   <si>
     <t xml:space="preserve">11.2294607162476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2194194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2461948394775</t>
+    <t xml:space="preserve">11.2194204330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2461967468262</t>
   </si>
   <si>
     <t xml:space="preserve">10.9148349761963</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1323938369751</t>
+    <t xml:space="preserve">11.1323957443237</t>
   </si>
   <si>
     <t xml:space="preserve">11.6143751144409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6813163757324</t>
+    <t xml:space="preserve">11.6813182830811</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474328994751</t>
@@ -116,145 +116,145 @@
     <t xml:space="preserve">11.3298721313477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8947534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8780174255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.045371055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4261617660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094266891479</t>
+    <t xml:space="preserve">10.8947525024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8780164718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0453701019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4261608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094257354736</t>
   </si>
   <si>
     <t xml:space="preserve">11.7080936431885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7147874832153</t>
+    <t xml:space="preserve">11.714786529541</t>
   </si>
   <si>
     <t xml:space="preserve">12.0494956970215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7482576370239</t>
+    <t xml:space="preserve">11.7482585906982</t>
   </si>
   <si>
     <t xml:space="preserve">11.744912147522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2135028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168483734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3674688339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7189111709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8293685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0201511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2209749221802</t>
+    <t xml:space="preserve">12.2135038375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.367467880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7189140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8293657302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0201501846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2209739685059</t>
   </si>
   <si>
     <t xml:space="preserve">13.3849830627441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0870923995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3347759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3146944046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569677352905</t>
+    <t xml:space="preserve">13.0870904922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3347749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3146953582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569667816162</t>
   </si>
   <si>
     <t xml:space="preserve">13.2109336853027</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8661842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306028366089</t>
+    <t xml:space="preserve">12.8661832809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306037902832</t>
   </si>
   <si>
     <t xml:space="preserve">13.2879161834717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8260183334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9833326339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.903003692627</t>
+    <t xml:space="preserve">12.8260192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9833316802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9029998779297</t>
   </si>
   <si>
     <t xml:space="preserve">13.2377099990845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1674222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1138668060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971345901489</t>
+    <t xml:space="preserve">13.1674213409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1138677597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971307754517</t>
   </si>
   <si>
     <t xml:space="preserve">12.5046997070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.886266708374</t>
+    <t xml:space="preserve">12.8092851638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8862676620483</t>
   </si>
   <si>
     <t xml:space="preserve">12.7055234909058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7222576141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9163885116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0301904678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.631890296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7021780014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8695287704468</t>
+    <t xml:space="preserve">12.7222604751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9163904190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0301895141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6318883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7021770477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8695316314697</t>
   </si>
   <si>
     <t xml:space="preserve">12.558253288269</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5682916641235</t>
+    <t xml:space="preserve">12.5682926177979</t>
   </si>
   <si>
     <t xml:space="preserve">12.8360595703125</t>
@@ -266,70 +266,70 @@
     <t xml:space="preserve">12.7958965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5348234176636</t>
+    <t xml:space="preserve">12.5348224639893</t>
   </si>
   <si>
     <t xml:space="preserve">12.7791614532471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7691173553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7865648269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.502420425415</t>
+    <t xml:space="preserve">12.769118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7865629196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5024185180664</t>
   </si>
   <si>
     <t xml:space="preserve">12.6512584686279</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7527389526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5836038589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4990367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5700721740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159521102905</t>
+    <t xml:space="preserve">12.752739906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5836048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4990377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5700731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159511566162</t>
   </si>
   <si>
     <t xml:space="preserve">12.2791624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0660514831543</t>
+    <t xml:space="preserve">12.06605052948</t>
   </si>
   <si>
     <t xml:space="preserve">12.1776809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1641511917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1709156036377</t>
+    <t xml:space="preserve">12.1641492843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.170916557312</t>
   </si>
   <si>
     <t xml:space="preserve">12.1100282669067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1269407272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9814863204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7459726333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580219268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231372833252</t>
+    <t xml:space="preserve">12.1269416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.981484413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7459754943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580238342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231391906738</t>
   </si>
   <si>
     <t xml:space="preserve">11.6973400115967</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">11.2406768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8212242126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.061393737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.196702003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4064283370972</t>
+    <t xml:space="preserve">10.8212232589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554708480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0613946914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1967010498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4064292907715</t>
   </si>
   <si>
     <t xml:space="preserve">11.5248222351074</t>
@@ -371,43 +371,43 @@
     <t xml:space="preserve">10.6825332641602</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8394117355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0199747085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3616237640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0233564376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1924886703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4969301223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4698686599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307588577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.480016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2939691543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548574447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0740957260132</t>
+    <t xml:space="preserve">11.839412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0199728012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3616228103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0233554840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1924877166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4969310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4698696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307569503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4800148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2939682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.310884475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548603057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0740938186646</t>
   </si>
   <si>
     <t xml:space="preserve">13.0368852615356</t>
@@ -416,208 +416,208 @@
     <t xml:space="preserve">12.9489345550537</t>
   </si>
   <si>
-    <t xml:space="preserve">12.982762336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.091007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0707130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9962930679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8576011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113033294678</t>
+    <t xml:space="preserve">12.9827613830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0910081863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0707120895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9962911605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8576030731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113023757935</t>
   </si>
   <si>
     <t xml:space="preserve">13.1248350143433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1823425292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0605640411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857233047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4123649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.567967414856</t>
+    <t xml:space="preserve">13.1823406219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0605630874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4123659133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5679664611816</t>
   </si>
   <si>
     <t xml:space="preserve">13.4157466888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5138425827026</t>
+    <t xml:space="preserve">13.5138444900513</t>
   </si>
   <si>
     <t xml:space="preserve">13.7066583633423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8352012634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2106781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4576168060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7552909851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838329315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0157585144043</t>
+    <t xml:space="preserve">13.8352022171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2106771469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4576139450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7552900314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838338851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.01575756073</t>
   </si>
   <si>
     <t xml:space="preserve">14.9853143692017</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3303451538086</t>
+    <t xml:space="preserve">15.3303489685059</t>
   </si>
   <si>
     <t xml:space="preserve">15.6652336120605</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2897577285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8297109603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7722072601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.951488494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7485275268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7180824279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8770694732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7992687225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751672744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9007472991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2018060684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988470077515</t>
+    <t xml:space="preserve">15.2897567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8297090530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.684253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7722043991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9514875411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7485237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7180814743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8770666122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7992639541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751653671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.90074634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2018022537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939828872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330936431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988451004028</t>
   </si>
   <si>
     <t xml:space="preserve">14.9142789840698</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9278078079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7383766174316</t>
+    <t xml:space="preserve">14.9278087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7383785247803</t>
   </si>
   <si>
     <t xml:space="preserve">14.7248468399048</t>
   </si>
   <si>
-    <t xml:space="preserve">14.542181968689</t>
+    <t xml:space="preserve">14.5421838760376</t>
   </si>
   <si>
     <t xml:space="preserve">14.4440841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0529708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1104736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9548721313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0901765823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2187204360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7823524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707239151001</t>
+    <t xml:space="preserve">15.0529699325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1442995071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1104726791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.954870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0901803970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2187213897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7823534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707220077515</t>
   </si>
   <si>
     <t xml:space="preserve">14.6166019439697</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3764314651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1599388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2546548843384</t>
+    <t xml:space="preserve">14.376428604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1599369049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2546529769897</t>
   </si>
   <si>
     <t xml:space="preserve">14.0415420532227</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1125831604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0381622314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1430244445801</t>
+    <t xml:space="preserve">14.1125812530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.038161277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1430253982544</t>
   </si>
   <si>
     <t xml:space="preserve">14.1903820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3527526855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2072973251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3561334609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373178482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3087778091431</t>
+    <t xml:space="preserve">14.3527498245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.20729637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3561344146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373197555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3087759017944</t>
   </si>
   <si>
     <t xml:space="preserve">14.2411222457886</t>
@@ -626,16 +626,16 @@
     <t xml:space="preserve">14.3392210006714</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2512712478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464071273804</t>
+    <t xml:space="preserve">14.2512702941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1464099884033</t>
   </si>
   <si>
     <t xml:space="preserve">14.1058158874512</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1193466186523</t>
+    <t xml:space="preserve">14.119348526001</t>
   </si>
   <si>
     <t xml:space="preserve">14.2275915145874</t>
@@ -644,22 +644,22 @@
     <t xml:space="preserve">14.2715673446655</t>
   </si>
   <si>
-    <t xml:space="preserve">14.149790763855</t>
+    <t xml:space="preserve">14.1497898101807</t>
   </si>
   <si>
     <t xml:space="preserve">14.0753707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0719881057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749500274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667051315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4779109954834</t>
+    <t xml:space="preserve">14.0719861984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749490737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4779100418091</t>
   </si>
   <si>
     <t xml:space="preserve">14.6267490386963</t>
@@ -668,121 +668,121 @@
     <t xml:space="preserve">14.7519092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8161811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1037101745605</t>
+    <t xml:space="preserve">14.8161792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1037082672119</t>
   </si>
   <si>
     <t xml:space="preserve">15.0834121704102</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1882734298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172409057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1544504165649</t>
+    <t xml:space="preserve">15.1882762908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1544485092163</t>
   </si>
   <si>
     <t xml:space="preserve">15.2999038696289</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4758043289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3574113845825</t>
+    <t xml:space="preserve">15.4758033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3574104309082</t>
   </si>
   <si>
     <t xml:space="preserve">15.3912372589111</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4893350601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1713619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1003265380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3168163299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3134346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4182996749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4250602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.536693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6753816604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6449403762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7295036315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6618528366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6517019271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6821479797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637521743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081497192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415557861328</t>
+    <t xml:space="preserve">15.4893360137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1713571548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.100323677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946180343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3168182373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3134355545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4182977676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4250631332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366926193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6753835678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6449394226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7295055389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6618518829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6517038345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6821460723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637540817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.408148765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415548324585</t>
   </si>
   <si>
     <t xml:space="preserve">15.7024431228638</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5333080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584701538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588918685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5874338150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.655086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227401733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3350067138672</t>
+    <t xml:space="preserve">15.5333099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584711074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.458890914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5874347686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6550884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227392196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3350105285645</t>
   </si>
   <si>
     <t xml:space="preserve">16.0339488983154</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4060440063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4026584625244</t>
+    <t xml:space="preserve">16.4060459136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4026622772217</t>
   </si>
   <si>
     <t xml:space="preserve">16.4195728302002</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">16.9980144500732</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1671466827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4208526611328</t>
+    <t xml:space="preserve">17.1671485900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4208507537842</t>
   </si>
   <si>
     <t xml:space="preserve">17.5392436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6407260894775</t>
+    <t xml:space="preserve">17.6407241821289</t>
   </si>
   <si>
     <t xml:space="preserve">17.403938293457</t>
@@ -815,10 +815,10 @@
     <t xml:space="preserve">17.4885063171387</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3531951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3870277404785</t>
+    <t xml:space="preserve">17.3531970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3870220184326</t>
   </si>
   <si>
     <t xml:space="preserve">17.522331237793</t>
@@ -827,34 +827,34 @@
     <t xml:space="preserve">17.4546775817871</t>
   </si>
   <si>
-    <t xml:space="preserve">17.877513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8098621368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7083778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7591171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6745510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5730724334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3362827301025</t>
+    <t xml:space="preserve">17.8775119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8098602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7083797454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7591209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6745529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.573070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3362846374512</t>
   </si>
   <si>
     <t xml:space="preserve">17.2009754180908</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2348041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2517147064209</t>
+    <t xml:space="preserve">17.2348003387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2517166137695</t>
   </si>
   <si>
     <t xml:space="preserve">17.2178897857666</t>
@@ -863,46 +863,46 @@
     <t xml:space="preserve">17.3701095581055</t>
   </si>
   <si>
-    <t xml:space="preserve">17.456018447876</t>
+    <t xml:space="preserve">17.4560203552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.7147541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5767631530762</t>
+    <t xml:space="preserve">17.5767612457275</t>
   </si>
   <si>
     <t xml:space="preserve">17.5595149993896</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6975059509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.469820022583</t>
+    <t xml:space="preserve">17.6975078582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4698181152344</t>
   </si>
   <si>
     <t xml:space="preserve">17.6147117614746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7729568481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0075454711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1662349700928</t>
+    <t xml:space="preserve">16.7729606628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0075435638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1662368774414</t>
   </si>
   <si>
     <t xml:space="preserve">17.1317367553711</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9937477111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9868450164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9661464691162</t>
+    <t xml:space="preserve">16.993745803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9868488311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9661483764648</t>
   </si>
   <si>
     <t xml:space="preserve">16.835054397583</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">16.84885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8281555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7591590881348</t>
+    <t xml:space="preserve">16.8281517028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7591609954834</t>
   </si>
   <si>
     <t xml:space="preserve">16.8695526123047</t>
@@ -923,97 +923,97 @@
     <t xml:space="preserve">16.9178504943848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9730491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9385471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1524391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6625652313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5935649871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5659713745117</t>
+    <t xml:space="preserve">16.9730472564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.938549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.152437210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6625633239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5935688018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5659694671631</t>
   </si>
   <si>
     <t xml:space="preserve">16.5038738250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626518249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9040470123291</t>
+    <t xml:space="preserve">16.8626537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9040508270264</t>
   </si>
   <si>
     <t xml:space="preserve">16.80055809021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8971519470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5383739471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5590705871582</t>
+    <t xml:space="preserve">16.8971500396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5383701324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5590724945068</t>
   </si>
   <si>
     <t xml:space="preserve">16.4900722503662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2416858673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.303783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2485885620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1243953704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1864929199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1588916778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5314693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2899875640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3175849914551</t>
+    <t xml:space="preserve">16.2416877746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3037853240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2485866546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.124397277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1864891052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1588935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5314712524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2899837493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3175830841064</t>
   </si>
   <si>
     <t xml:space="preserve">16.5452709197998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3658809661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4624767303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3313846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3520812988281</t>
+    <t xml:space="preserve">16.3658790588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.462474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3313827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3520832061768</t>
   </si>
   <si>
     <t xml:space="preserve">16.6970615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3865776062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4486770629883</t>
+    <t xml:space="preserve">16.3865795135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4486751556396</t>
   </si>
   <si>
     <t xml:space="preserve">16.5107727050781</t>
@@ -1022,88 +1022,88 @@
     <t xml:space="preserve">16.4210777282715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4348773956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.393482208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4969749450684</t>
+    <t xml:space="preserve">16.4348793029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3934783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4969730377197</t>
   </si>
   <si>
     <t xml:space="preserve">16.5245723724365</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4003772735596</t>
+    <t xml:space="preserve">16.4003791809082</t>
   </si>
   <si>
     <t xml:space="preserve">16.4555759429932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.358980178833</t>
+    <t xml:space="preserve">16.3589820861816</t>
   </si>
   <si>
     <t xml:space="preserve">16.2830848693848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5521678924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1795902252197</t>
+    <t xml:space="preserve">16.5521697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1795921325684</t>
   </si>
   <si>
     <t xml:space="preserve">16.2071876525879</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1933898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9036064147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5586252212524</t>
+    <t xml:space="preserve">16.1933860778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.903603553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5586261749268</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965295791626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9381065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7794151306152</t>
+    <t xml:space="preserve">15.9381055831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7794132232666</t>
   </si>
   <si>
     <t xml:space="preserve">15.7656154632568</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7863130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9795026779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.931206703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7035188674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.648323059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8415107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7518167495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691091537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8622093200684</t>
+    <t xml:space="preserve">15.7863121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9795017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9312047958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.703516960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6483240127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8415117263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7518177032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691072463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8622102737427</t>
   </si>
   <si>
     <t xml:space="preserve">16.0277996063232</t>
@@ -1112,34 +1112,34 @@
     <t xml:space="preserve">15.8967084884644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6276216506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7173175811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310277938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413318634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.248143196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3171377182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3309392929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.282639503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792371749878</t>
+    <t xml:space="preserve">15.6276226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7173166275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310287475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034275054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413328170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2481451034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3171405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3309383392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2826414108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792343139648</t>
   </si>
   <si>
     <t xml:space="preserve">15.261944770813</t>
@@ -1148,34 +1148,34 @@
     <t xml:space="preserve">15.6000232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">15.489631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.951904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9726028442383</t>
+    <t xml:space="preserve">15.4896287918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9519062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9726009368896</t>
   </si>
   <si>
     <t xml:space="preserve">15.9864025115967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0416011810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8553104400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932147979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.475830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2895431518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1791477203369</t>
+    <t xml:space="preserve">16.0415992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8553094863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932109832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2895421981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1791458129883</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067461013794</t>
@@ -1187,46 +1187,46 @@
     <t xml:space="preserve">15.2343454360962</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3033418655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137334823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3861360549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.634521484375</t>
+    <t xml:space="preserve">15.3033399581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137344360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3861351013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6345224380493</t>
   </si>
   <si>
     <t xml:space="preserve">16.1450939178467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4831733703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6073684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3727798461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6349658966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141788482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0898952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.200288772583</t>
+    <t xml:space="preserve">16.4831714630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6073665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.37278175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6349678039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141807556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0898971557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2002906799316</t>
   </si>
   <si>
     <t xml:space="preserve">16.7315616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6901626586914</t>
+    <t xml:space="preserve">16.69016456604</t>
   </si>
   <si>
     <t xml:space="preserve">16.4762744903564</t>
@@ -1235,19 +1235,19 @@
     <t xml:space="preserve">16.7522602081299</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6487636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6280651092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0420436859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0765399932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1110363006592</t>
+    <t xml:space="preserve">16.6487655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6280670166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0420417785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0765419006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1110382080078</t>
   </si>
   <si>
     <t xml:space="preserve">17.2145328521729</t>
@@ -1259,103 +1259,103 @@
     <t xml:space="preserve">17.1800365447998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0071029663086</t>
+    <t xml:space="preserve">16.00710105896</t>
   </si>
   <si>
     <t xml:space="preserve">16.21409034729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.110595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5931234359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621208190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0066585540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.730673789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9031639099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9721603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551296234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1101493835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0411548614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0756530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3516397476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4206342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5241289138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6966190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8742485046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.556056022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7328300476074</t>
+    <t xml:space="preserve">16.1105976104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5931224822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0066576004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7306728363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9031648635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9721622467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551343917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1101512908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0411539077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0756540298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3516407012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4206352233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5241279602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6966180801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156650543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8742475509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5560550689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7328310012817</t>
   </si>
   <si>
     <t xml:space="preserve">15.5914087295532</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3439273834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7782545089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4247064590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5307683944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600620269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4954147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8873157501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1135854721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3186407089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6014785766602</t>
+    <t xml:space="preserve">15.3439292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792819976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7782535552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4247045516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5307693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600610733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.495415687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8873138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1135845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.318642616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6014776229858</t>
   </si>
   <si>
     <t xml:space="preserve">15.0257339477539</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">15.061089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9550266265869</t>
+    <t xml:space="preserve">14.955023765564</t>
   </si>
   <si>
     <t xml:space="preserve">14.8489627838135</t>
@@ -1373,97 +1373,97 @@
     <t xml:space="preserve">14.884316444397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7075443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671524047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2025108337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.566125869751</t>
+    <t xml:space="preserve">14.707540512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2025098800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5661249160767</t>
   </si>
   <si>
     <t xml:space="preserve">14.6368350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2832870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0853004455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8136081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3539981842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3893527984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.74289894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1418695449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1772241592407</t>
+    <t xml:space="preserve">14.2832880020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.085301399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.81360912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3539972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.389349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428998947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1418685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.177225112915</t>
   </si>
   <si>
     <t xml:space="preserve">14.2479333877563</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2125778198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0711603164673</t>
+    <t xml:space="preserve">14.2125797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0711584091187</t>
   </si>
   <si>
     <t xml:space="preserve">13.9438829421997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8731746673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8166055679321</t>
+    <t xml:space="preserve">13.8731737136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8166074752808</t>
   </si>
   <si>
     <t xml:space="preserve">13.8590316772461</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0145921707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.929741859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0004482269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0994443893433</t>
+    <t xml:space="preserve">14.0145931243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9297428131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0004510879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0994434356689</t>
   </si>
   <si>
     <t xml:space="preserve">13.97216796875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0287351608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.057017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1277256011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9196739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6721897125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.434775352478</t>
+    <t xml:space="preserve">14.0287342071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1277265548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9196720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6721887588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4347772598267</t>
   </si>
   <si>
     <t xml:space="preserve">13.505485534668</t>
@@ -1472,55 +1472,55 @@
     <t xml:space="preserve">13.4913425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3782081604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4630603790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5620536804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.533766746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1660814285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7842493057251</t>
+    <t xml:space="preserve">13.3782062530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.463059425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5620527267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5337696075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1660804748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7842483520508</t>
   </si>
   <si>
     <t xml:space="preserve">12.6852569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1620082855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6569719314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4064912796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5479116439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7883234024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7741794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5903377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4489154815674</t>
+    <t xml:space="preserve">12.1620073318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6569728851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4064922332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5479106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7883224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7741785049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5903358459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.448917388916</t>
   </si>
   <si>
     <t xml:space="preserve">13.3074998855591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3923511505127</t>
+    <t xml:space="preserve">13.3923492431641</t>
   </si>
   <si>
     <t xml:space="preserve">13.0105199813843</t>
@@ -1529,205 +1529,205 @@
     <t xml:space="preserve">13.1519384384155</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2933559417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.925669670105</t>
+    <t xml:space="preserve">13.2933578491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9256687164307</t>
   </si>
   <si>
     <t xml:space="preserve">13.0388031005859</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9963779449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2367887496948</t>
+    <t xml:space="preserve">12.9963788986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2367877960205</t>
   </si>
   <si>
     <t xml:space="preserve">13.0953712463379</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6469030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6751899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0670862197876</t>
+    <t xml:space="preserve">13.6469049453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6751871109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0670852661133</t>
   </si>
   <si>
     <t xml:space="preserve">13.2509298324585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2085075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812292098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3499240875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8408174514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5296964645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8973836898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6004047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7317533493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5761947631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5196285247803</t>
+    <t xml:space="preserve">13.2085065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812282562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3499212265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8408164978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5296955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.897385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6004056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7317543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5761957168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.519627571106</t>
   </si>
   <si>
     <t xml:space="preserve">13.7176141738892</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8307476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7600402832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.915599822998</t>
+    <t xml:space="preserve">13.8307495117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7600364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9156007766724</t>
   </si>
   <si>
     <t xml:space="preserve">13.7458963394165</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0428771972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8448896408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5417680740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.221848487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9455556869507</t>
+    <t xml:space="preserve">14.042875289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8448915481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5417671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2218494415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9455547332764</t>
   </si>
   <si>
     <t xml:space="preserve">14.1782236099243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9891815185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2073068618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4399757385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2654733657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4108905792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.498143196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690561294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3381834030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5126819610596</t>
+    <t xml:space="preserve">13.9891796112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2073078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4399747848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.265474319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4108924865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4981422424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690570831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.352725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3381824493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5126838684082</t>
   </si>
   <si>
     <t xml:space="preserve">14.3963508605957</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6871862411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4254331588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4835996627808</t>
+    <t xml:space="preserve">14.6871852874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4254322052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4836006164551</t>
   </si>
   <si>
     <t xml:space="preserve">14.6144762039185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8326034545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9780206680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1234369277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1961479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4142732620239</t>
+    <t xml:space="preserve">14.8326005935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9780216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1234350204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1961469650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4142751693726</t>
   </si>
   <si>
     <t xml:space="preserve">15.450626373291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3415651321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2325000762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3052101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.268856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687545776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0507307052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0870847702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9416666030884</t>
+    <t xml:space="preserve">15.3415641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2325010299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3052091598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2688541412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687507629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0507297515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0870838165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9416646957397</t>
   </si>
   <si>
     <t xml:space="preserve">14.7235383987427</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0143747329712</t>
+    <t xml:space="preserve">15.0143728256226</t>
   </si>
   <si>
     <t xml:space="preserve">14.5781221389771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598943710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6508321762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3672666549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3236427307129</t>
+    <t xml:space="preserve">14.7598934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6508302688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3672676086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3236417770386</t>
   </si>
   <si>
     <t xml:space="preserve">14.5272254943848</t>
@@ -1742,37 +1742,37 @@
     <t xml:space="preserve">14.9053106307983</t>
   </si>
   <si>
-    <t xml:space="preserve">16.032299041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3594875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5049076080322</t>
+    <t xml:space="preserve">16.0322971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.359489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5049057006836</t>
   </si>
   <si>
     <t xml:space="preserve">16.6139698028564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.541259765625</t>
+    <t xml:space="preserve">16.5412616729736</t>
   </si>
   <si>
     <t xml:space="preserve">16.8320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6503257751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5776138305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8684501647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7593879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0502223968506</t>
+    <t xml:space="preserve">16.6503238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5776119232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8684482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7593841552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.050220489502</t>
   </si>
   <si>
     <t xml:space="preserve">17.086576461792</t>
@@ -1787,31 +1787,31 @@
     <t xml:space="preserve">17.2683486938477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5228309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8136672973633</t>
+    <t xml:space="preserve">17.5228290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.813663482666</t>
   </si>
   <si>
     <t xml:space="preserve">17.7409553527832</t>
   </si>
   <si>
-    <t xml:space="preserve">17.631893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7046031951904</t>
+    <t xml:space="preserve">17.6318912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7046012878418</t>
   </si>
   <si>
     <t xml:space="preserve">17.6682472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0681476593018</t>
+    <t xml:space="preserve">18.0681457519531</t>
   </si>
   <si>
     <t xml:space="preserve">17.9227256774902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1045017242432</t>
+    <t xml:space="preserve">18.1044998168945</t>
   </si>
   <si>
     <t xml:space="preserve">17.8500194549561</t>
@@ -1820,43 +1820,43 @@
     <t xml:space="preserve">17.9590835571289</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1772079467773</t>
+    <t xml:space="preserve">18.177209854126</t>
   </si>
   <si>
     <t xml:space="preserve">18.0317897796631</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2862701416016</t>
+    <t xml:space="preserve">18.2862720489502</t>
   </si>
   <si>
     <t xml:space="preserve">18.358980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4680442810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5771083831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9954357147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5591831207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5955371856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4501209259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2499179840088</t>
+    <t xml:space="preserve">18.4680461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5771064758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9954376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5591850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5955390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.450122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2499160766602</t>
   </si>
   <si>
     <t xml:space="preserve">18.3953342437744</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2135639190674</t>
+    <t xml:space="preserve">18.2135620117188</t>
   </si>
   <si>
     <t xml:space="preserve">18.3226280212402</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">18.6134624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6861724853516</t>
+    <t xml:space="preserve">18.6861705780029</t>
   </si>
   <si>
     <t xml:space="preserve">18.8315887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1951332092285</t>
+    <t xml:space="preserve">19.1951351165771</t>
   </si>
   <si>
     <t xml:space="preserve">18.9770050048828</t>
@@ -1880,19 +1880,19 @@
     <t xml:space="preserve">19.0860691070557</t>
   </si>
   <si>
-    <t xml:space="preserve">19.26784324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1224250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3041954040527</t>
+    <t xml:space="preserve">19.2678413391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1224231719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3041973114014</t>
   </si>
   <si>
     <t xml:space="preserve">19.4132595062256</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4496154785156</t>
+    <t xml:space="preserve">19.4496116638184</t>
   </si>
   <si>
     <t xml:space="preserve">16.9048042297363</t>
@@ -1904,19 +1904,19 @@
     <t xml:space="preserve">16.4321975708008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7957401275635</t>
+    <t xml:space="preserve">16.7957420349121</t>
   </si>
   <si>
     <t xml:space="preserve">19.2314891815186</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9775123596191</t>
+    <t xml:space="preserve">16.9775142669678</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047027587891</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3774127960205</t>
+    <t xml:space="preserve">17.3774108886719</t>
   </si>
   <si>
     <t xml:space="preserve">18.7952346801758</t>
@@ -1928,10 +1928,10 @@
     <t xml:space="preserve">18.8679428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">18.904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8495101928711</t>
+    <t xml:space="preserve">18.9042987823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8495121002197</t>
   </si>
   <si>
     <t xml:space="preserve">19.42138671875</t>
@@ -1940,22 +1940,22 @@
     <t xml:space="preserve">19.7327499389648</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3943996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8105926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3554821014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8495121002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1219577789307</t>
+    <t xml:space="preserve">20.394401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8105907440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549110412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3554801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8495140075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.121955871582</t>
   </si>
   <si>
     <t xml:space="preserve">19.9273529052734</t>
@@ -1964,49 +1964,49 @@
     <t xml:space="preserve">19.4603061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3435459136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3046226501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.966272354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2657012939453</t>
+    <t xml:space="preserve">19.3435440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3046245574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9662742614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2657051086426</t>
   </si>
   <si>
     <t xml:space="preserve">19.771671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7597370147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1608772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0441150665283</t>
+    <t xml:space="preserve">18.7597389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1608791351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.044116973877</t>
   </si>
   <si>
     <t xml:space="preserve">21.172815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0560531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9392910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2895774841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0171318054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7836055755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7057666778564</t>
+    <t xml:space="preserve">21.0560512542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9392890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2895755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0171298980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7836074829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7057647705078</t>
   </si>
   <si>
     <t xml:space="preserve">21.094970703125</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">21.4452571868896</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7566242218018</t>
+    <t xml:space="preserve">21.7566223144531</t>
   </si>
   <si>
     <t xml:space="preserve">21.9512252807617</t>
@@ -2030,19 +2030,19 @@
     <t xml:space="preserve">22.0290679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.067985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5350341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5739574432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6517944335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7685565948486</t>
+    <t xml:space="preserve">22.0679874420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5350360870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.57395362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6517963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7685585021973</t>
   </si>
   <si>
     <t xml:space="preserve">22.8074779510498</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">22.7296390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3404312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2625904083252</t>
+    <t xml:space="preserve">22.3404331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2625923156738</t>
   </si>
   <si>
     <t xml:space="preserve">23.5080509185791</t>
@@ -2075,19 +2075,19 @@
     <t xml:space="preserve">24.5199851989746</t>
   </si>
   <si>
-    <t xml:space="preserve">25.298397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7924308776855</t>
+    <t xml:space="preserve">25.2983989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7924327850342</t>
   </si>
   <si>
     <t xml:space="preserve">25.1427154541016</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7535095214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6367473602295</t>
+    <t xml:space="preserve">24.7535076141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6367492675781</t>
   </si>
   <si>
     <t xml:space="preserve">24.16969871521</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">23.0799236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7026538848877</t>
+    <t xml:space="preserve">23.7026519775391</t>
   </si>
   <si>
     <t xml:space="preserve">24.0529384613037</t>
@@ -2108,25 +2108,25 @@
     <t xml:space="preserve">23.4691276550293</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5858898162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1577663421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8583354949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7415714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8194141387939</t>
+    <t xml:space="preserve">23.5858917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1577644348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8583335876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7415733337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8194160461426</t>
   </si>
   <si>
     <t xml:space="preserve">23.6637325286865</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4302101135254</t>
+    <t xml:space="preserve">23.4302082061768</t>
   </si>
   <si>
     <t xml:space="preserve">24.0918598175049</t>
@@ -2135,22 +2135,22 @@
     <t xml:space="preserve">23.3912868499756</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3523654937744</t>
+    <t xml:space="preserve">23.352367401123</t>
   </si>
   <si>
     <t xml:space="preserve">23.0410022735596</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0020790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1188430786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.624813079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6128749847412</t>
+    <t xml:space="preserve">23.002082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1188449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6248111724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6128768920898</t>
   </si>
   <si>
     <t xml:space="preserve">22.1069087982178</t>
@@ -2159,22 +2159,22 @@
     <t xml:space="preserve">22.1847476959229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.496114730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3015098571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6907176971436</t>
+    <t xml:space="preserve">22.4961128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3015117645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6907157897949</t>
   </si>
   <si>
     <t xml:space="preserve">22.3793525695801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9631614685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2356052398682</t>
+    <t xml:space="preserve">22.9631595611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2356071472168</t>
   </si>
   <si>
     <t xml:space="preserve">22.9242420196533</t>
@@ -2183,28 +2183,28 @@
     <t xml:space="preserve">22.223669052124</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4182720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9123039245605</t>
+    <t xml:space="preserve">22.4182739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9123058319092</t>
   </si>
   <si>
     <t xml:space="preserve">21.4841766357422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1338901519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5230979919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.717700958252</t>
+    <t xml:space="preserve">21.1338920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5231018066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7177028656006</t>
   </si>
   <si>
     <t xml:space="preserve">21.6398601531982</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2506523132324</t>
+    <t xml:space="preserve">21.2506542205811</t>
   </si>
   <si>
     <t xml:space="preserve">21.5620193481445</t>
@@ -2216,19 +2216,19 @@
     <t xml:space="preserve">21.6787815093994</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9901466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1458301544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8464012145996</t>
+    <t xml:space="preserve">21.9901447296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1458282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.846399307251</t>
   </si>
   <si>
     <t xml:space="preserve">22.8853187561035</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4571952819824</t>
+    <t xml:space="preserve">22.4571933746338</t>
   </si>
   <si>
     <t xml:space="preserve">21.3284950256348</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">21.2117328643799</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3674163818359</t>
+    <t xml:space="preserve">21.3674182891846</t>
   </si>
   <si>
     <t xml:space="preserve">20.9782104492188</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">21.873384475708</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4407329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.88356590271</t>
+    <t xml:space="preserve">23.440731048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8835639953613</t>
   </si>
   <si>
     <t xml:space="preserve">22.7243747711182</t>
@@ -2264,28 +2264,28 @@
     <t xml:space="preserve">22.7641735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0427570343018</t>
+    <t xml:space="preserve">23.0427551269531</t>
   </si>
   <si>
     <t xml:space="preserve">23.2417449951172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0029563903809</t>
+    <t xml:space="preserve">23.0029582977295</t>
   </si>
   <si>
     <t xml:space="preserve">23.2019443511963</t>
   </si>
   <si>
-    <t xml:space="preserve">23.122350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1621475219727</t>
+    <t xml:space="preserve">23.1223487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1621494293213</t>
   </si>
   <si>
     <t xml:space="preserve">23.5203247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9580974578857</t>
+    <t xml:space="preserve">23.9580993652344</t>
   </si>
   <si>
     <t xml:space="preserve">24.0774917602539</t>
@@ -2306,13 +2306,13 @@
     <t xml:space="preserve">24.1570854187012</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6744537353516</t>
+    <t xml:space="preserve">24.6744518280029</t>
   </si>
   <si>
     <t xml:space="preserve">24.9132385253906</t>
   </si>
   <si>
-    <t xml:space="preserve">24.555061340332</t>
+    <t xml:space="preserve">24.5550632476807</t>
   </si>
   <si>
     <t xml:space="preserve">24.7540493011475</t>
@@ -2324,37 +2324,37 @@
     <t xml:space="preserve">24.1172885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5152645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4754638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2366828918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3958721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7142505645752</t>
+    <t xml:space="preserve">24.5152626037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4754676818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2366809844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3958702087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7142486572266</t>
   </si>
   <si>
     <t xml:space="preserve">24.6346569061279</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1968841552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6295928955078</t>
+    <t xml:space="preserve">24.1968822479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6295948028564</t>
   </si>
   <si>
     <t xml:space="preserve">25.5102005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1520233154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3510131835938</t>
+    <t xml:space="preserve">25.1520252227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3510112762451</t>
   </si>
   <si>
     <t xml:space="preserve">25.4704036712646</t>
@@ -2375,19 +2375,19 @@
     <t xml:space="preserve">25.2714157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8336429595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9530372619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8683795928955</t>
+    <t xml:space="preserve">24.8336448669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9530353546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8683776855469</t>
   </si>
   <si>
     <t xml:space="preserve">25.0724296569824</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7591133117676</t>
+    <t xml:space="preserve">23.7591114044189</t>
   </si>
   <si>
     <t xml:space="preserve">23.4805278778076</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">23.8785037994385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6397171020508</t>
+    <t xml:space="preserve">23.6397190093994</t>
   </si>
   <si>
     <t xml:space="preserve">23.7989082336426</t>
@@ -2405,13 +2405,13 @@
     <t xml:space="preserve">24.5948581695557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9928321838379</t>
+    <t xml:space="preserve">24.9928340911865</t>
   </si>
   <si>
     <t xml:space="preserve">25.430606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3112106323242</t>
+    <t xml:space="preserve">25.3112144470215</t>
   </si>
   <si>
     <t xml:space="preserve">25.2316188812256</t>
@@ -2420,25 +2420,25 @@
     <t xml:space="preserve">26.0673656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2663536071777</t>
+    <t xml:space="preserve">26.2663516998291</t>
   </si>
   <si>
     <t xml:space="preserve">26.0275688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7887859344482</t>
+    <t xml:space="preserve">25.788782119751</t>
   </si>
   <si>
     <t xml:space="preserve">25.5499992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5897979736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9479732513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1071643829346</t>
+    <t xml:space="preserve">25.5897960662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9479713439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1071624755859</t>
   </si>
   <si>
     <t xml:space="preserve">25.7489852905273</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">24.0376930236816</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3263988494873</t>
+    <t xml:space="preserve">22.3264007568359</t>
   </si>
   <si>
     <t xml:space="preserve">22.3661975860596</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">23.0825538635254</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9233646392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3213367462158</t>
+    <t xml:space="preserve">22.923360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3213386535645</t>
   </si>
   <si>
     <t xml:space="preserve">23.5999202728271</t>
@@ -2471,25 +2471,25 @@
     <t xml:space="preserve">23.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4009323120117</t>
+    <t xml:space="preserve">23.4009342193604</t>
   </si>
   <si>
     <t xml:space="preserve">23.5601234436035</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4855918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8387050628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9978942871094</t>
+    <t xml:space="preserve">22.4855899810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8387069702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.997896194458</t>
   </si>
   <si>
     <t xml:space="preserve">23.7193126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8264083862305</t>
+    <t xml:space="preserve">23.8264102935791</t>
   </si>
   <si>
     <t xml:space="preserve">23.5692901611328</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">24.1263828277588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9549694061279</t>
+    <t xml:space="preserve">23.9549713134766</t>
   </si>
   <si>
     <t xml:space="preserve">24.4692077636719</t>
@@ -2507,13 +2507,13 @@
     <t xml:space="preserve">24.4263553619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1692352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2120895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7835559844971</t>
+    <t xml:space="preserve">24.1692371368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2120876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7835578918457</t>
   </si>
   <si>
     <t xml:space="preserve">24.340648651123</t>
@@ -2528,19 +2528,19 @@
     <t xml:space="preserve">23.5264377593994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9978218078613</t>
+    <t xml:space="preserve">23.99782371521</t>
   </si>
   <si>
     <t xml:space="preserve">23.9121170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8692626953125</t>
+    <t xml:space="preserve">23.8692646026611</t>
   </si>
   <si>
     <t xml:space="preserve">23.7407035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6549987792969</t>
+    <t xml:space="preserve">23.6549968719482</t>
   </si>
   <si>
     <t xml:space="preserve">22.9693431854248</t>
@@ -2558,16 +2558,16 @@
     <t xml:space="preserve">23.1407585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8407859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7550773620605</t>
+    <t xml:space="preserve">22.840784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7550792694092</t>
   </si>
   <si>
     <t xml:space="preserve">22.6693725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0550518035889</t>
+    <t xml:space="preserve">23.0550498962402</t>
   </si>
   <si>
     <t xml:space="preserve">23.2264652252197</t>
@@ -2588,16 +2588,16 @@
     <t xml:space="preserve">22.3694000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3550243377686</t>
+    <t xml:space="preserve">23.3550262451172</t>
   </si>
   <si>
     <t xml:space="preserve">23.0121994018555</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3121738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.397876739502</t>
+    <t xml:space="preserve">23.3121719360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3978748321533</t>
   </si>
   <si>
     <t xml:space="preserve">22.7979316711426</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">22.4979591369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6265182495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6978492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5408115386963</t>
+    <t xml:space="preserve">22.6265201568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6978511810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5408134460449</t>
   </si>
   <si>
     <t xml:space="preserve">23.2693176269531</t>
@@ -2636,25 +2636,25 @@
     <t xml:space="preserve">20.826681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9267616271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1410293579102</t>
+    <t xml:space="preserve">19.9267635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1410312652588</t>
   </si>
   <si>
     <t xml:space="preserve">20.9980945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1266536712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5267086029053</t>
+    <t xml:space="preserve">21.1266555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5267105102539</t>
   </si>
   <si>
     <t xml:space="preserve">20.6552696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">20.312442779541</t>
+    <t xml:space="preserve">20.3124446868896</t>
   </si>
   <si>
     <t xml:space="preserve">20.4410037994385</t>
@@ -2669,13 +2669,13 @@
     <t xml:space="preserve">21.3837757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">21.512336730957</t>
+    <t xml:space="preserve">21.5123329162598</t>
   </si>
   <si>
     <t xml:space="preserve">21.3409214019775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0265731811523</t>
+    <t xml:space="preserve">22.026575088501</t>
   </si>
   <si>
     <t xml:space="preserve">22.1122798919678</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">22.1551322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2408409118652</t>
+    <t xml:space="preserve">22.2408390045166</t>
   </si>
   <si>
     <t xml:space="preserve">21.6837463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.726598739624</t>
+    <t xml:space="preserve">21.7266006469727</t>
   </si>
   <si>
     <t xml:space="preserve">21.8980121612549</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">21.6408939361572</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1979846954346</t>
+    <t xml:space="preserve">22.1979866027832</t>
   </si>
   <si>
     <t xml:space="preserve">22.0694274902344</t>
@@ -2717,22 +2717,22 @@
     <t xml:space="preserve">21.8551597595215</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1695098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0838031768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9408664703369</t>
+    <t xml:space="preserve">21.1695079803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0838012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9408683776855</t>
   </si>
   <si>
     <t xml:space="preserve">21.5551872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0409488677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.912389755249</t>
+    <t xml:space="preserve">21.0409469604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9123878479004</t>
   </si>
   <si>
     <t xml:space="preserve">21.2980690002441</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">20.7409763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1838817596436</t>
+    <t xml:space="preserve">20.1838836669922</t>
   </si>
   <si>
     <t xml:space="preserve">20.3552951812744</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">22.0611591339111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1051959991455</t>
+    <t xml:space="preserve">22.1051940917969</t>
   </si>
   <si>
     <t xml:space="preserve">22.017126083374</t>
@@ -2783,10 +2783,10 @@
     <t xml:space="preserve">21.664852142334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5767841339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4887161254883</t>
+    <t xml:space="preserve">21.5767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4887142181396</t>
   </si>
   <si>
     <t xml:space="preserve">21.9290561676025</t>
@@ -2795,22 +2795,22 @@
     <t xml:space="preserve">21.8409881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7088851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4006462097168</t>
+    <t xml:space="preserve">21.7088871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4006443023682</t>
   </si>
   <si>
     <t xml:space="preserve">21.7969551086426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9730930328369</t>
+    <t xml:space="preserve">21.9730911254883</t>
   </si>
   <si>
     <t xml:space="preserve">21.7529201507568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5015029907227</t>
+    <t xml:space="preserve">22.501501083374</t>
   </si>
   <si>
     <t xml:space="preserve">22.2372970581055</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">22.3253650665283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5455360412598</t>
+    <t xml:space="preserve">22.5455379486084</t>
   </si>
   <si>
     <t xml:space="preserve">22.149227142334</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">21.0483722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3566112518311</t>
+    <t xml:space="preserve">21.3566131591797</t>
   </si>
   <si>
     <t xml:space="preserve">21.6208171844482</t>
@@ -2852,13 +2852,13 @@
     <t xml:space="preserve">21.4446811676025</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5327491760254</t>
+    <t xml:space="preserve">21.532751083374</t>
   </si>
   <si>
     <t xml:space="preserve">21.0043392181396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8722343444824</t>
+    <t xml:space="preserve">20.8722362518311</t>
   </si>
   <si>
     <t xml:space="preserve">20.6960983276367</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">20.2557563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3878593444824</t>
+    <t xml:space="preserve">20.3878574371338</t>
   </si>
   <si>
     <t xml:space="preserve">20.2997894287109</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">20.7841682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9603023529053</t>
+    <t xml:space="preserve">20.9603042602539</t>
   </si>
   <si>
     <t xml:space="preserve">20.7401313781738</t>
@@ -2900,10 +2900,10 @@
     <t xml:space="preserve">21.1804752349854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6336059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4574680328369</t>
+    <t xml:space="preserve">22.6336078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4574699401855</t>
   </si>
   <si>
     <t xml:space="preserve">22.5895709991455</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">24.3949756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3069076538086</t>
+    <t xml:space="preserve">24.30690574646</t>
   </si>
   <si>
     <t xml:space="preserve">24.1307697296143</t>
@@ -2936,13 +2936,13 @@
     <t xml:space="preserve">24.3509407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4390087127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5711135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6591815948486</t>
+    <t xml:space="preserve">24.4390106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5711116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6591796875</t>
   </si>
   <si>
     <t xml:space="preserve">24.7032146453857</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">24.0867366790771</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2188377380371</t>
+    <t xml:space="preserve">24.2188396453857</t>
   </si>
   <si>
     <t xml:space="preserve">24.1748046875</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">23.9546337127686</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7600383758545</t>
+    <t xml:space="preserve">25.7600364685059</t>
   </si>
   <si>
     <t xml:space="preserve">25.4077625274658</t>
@@ -2990,19 +2990,19 @@
     <t xml:space="preserve">26.1123104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1563472747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4645843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5910148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3708438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8992576599121</t>
+    <t xml:space="preserve">26.1563453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4645862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5910167694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3708457946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8992595672607</t>
   </si>
   <si>
     <t xml:space="preserve">30.0313587188721</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">29.5029487609863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7671527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2827777862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0753955841064</t>
+    <t xml:space="preserve">29.7671546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2827758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0753974914551</t>
   </si>
   <si>
     <t xml:space="preserve">29.7231216430664</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">30.471700668335</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8111877441406</t>
+    <t xml:space="preserve">29.811185836792</t>
   </si>
   <si>
     <t xml:space="preserve">29.2387447357178</t>
@@ -3047,28 +3047,28 @@
     <t xml:space="preserve">28.7103309631348</t>
   </si>
   <si>
-    <t xml:space="preserve">28.842435836792</t>
+    <t xml:space="preserve">28.8424339294434</t>
   </si>
   <si>
     <t xml:space="preserve">28.8864688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5469818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2955665588379</t>
+    <t xml:space="preserve">29.5469837188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2955646514893</t>
   </si>
   <si>
     <t xml:space="preserve">30.7359104156494</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3836326599121</t>
+    <t xml:space="preserve">30.3836345672607</t>
   </si>
   <si>
     <t xml:space="preserve">29.9873237609863</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4276676177979</t>
+    <t xml:space="preserve">30.4276695251465</t>
   </si>
   <si>
     <t xml:space="preserve">29.4632396697998</t>
@@ -3672,6 +3672,9 @@
   </si>
   <si>
     <t xml:space="preserve">33.4500007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5</t>
   </si>
 </sst>
 </file>
@@ -68750,13 +68753,13 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6494328704</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>61976</v>
       </c>
       <c r="C2491" t="n">
-        <v>33.4000015258789</v>
+        <v>33.4500007629395</v>
       </c>
       <c r="D2491" t="n">
         <v>32.9500007629395</v>
@@ -68771,6 +68774,32 @@
         <v>1219</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6494212963</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>18334</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>33.0999984741211</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="1221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="1222">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.806715965271</t>
+    <t xml:space="preserve">13.8067150115967</t>
   </si>
   <si>
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577459335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9573335647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3883295059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.889612197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8527975082397</t>
+    <t xml:space="preserve">14.0577478408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.957332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3883275985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896141052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8527946472168</t>
   </si>
   <si>
     <t xml:space="preserve">12.9532079696655</t>
   </si>
   <si>
-    <t xml:space="preserve">12.618501663208</t>
+    <t xml:space="preserve">12.6184997558594</t>
   </si>
   <si>
     <t xml:space="preserve">12.4846162796021</t>
@@ -71,94 +71,94 @@
     <t xml:space="preserve">12.3842029571533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8821420669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7348718643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2127246856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7307462692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2294607162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2194204330444</t>
+    <t xml:space="preserve">11.8821430206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7348709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2127265930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7307453155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2294597625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2194194793701</t>
   </si>
   <si>
     <t xml:space="preserve">11.2461967468262</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9148349761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1323957443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6143751144409</t>
+    <t xml:space="preserve">10.914834022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1323947906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6143770217896</t>
   </si>
   <si>
     <t xml:space="preserve">11.6813182830811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474328994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3466091156006</t>
+    <t xml:space="preserve">11.5474338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3466100692749</t>
   </si>
   <si>
     <t xml:space="preserve">11.3131370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3298721313477</t>
+    <t xml:space="preserve">11.329873085022</t>
   </si>
   <si>
     <t xml:space="preserve">10.8947525024414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8780164718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0453701019287</t>
+    <t xml:space="preserve">10.8780174255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.045371055603</t>
   </si>
   <si>
     <t xml:space="preserve">10.4261608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4094257354736</t>
+    <t xml:space="preserve">10.4094266891479</t>
   </si>
   <si>
     <t xml:space="preserve">11.7080936431885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.714786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0494956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7482585906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.744912147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2135038375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.367467880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7189140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8293657302856</t>
+    <t xml:space="preserve">11.714789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0494966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7482576370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7449111938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2135028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.216851234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3674697875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7189111709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8293676376343</t>
   </si>
   <si>
     <t xml:space="preserve">13.0201501846313</t>
@@ -167,70 +167,70 @@
     <t xml:space="preserve">13.2209739685059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3849830627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870904922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3347749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3146953582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569667816162</t>
+    <t xml:space="preserve">13.3849821090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870885848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3347759246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3146934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569677352905</t>
   </si>
   <si>
     <t xml:space="preserve">13.2109336853027</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8661832809448</t>
+    <t xml:space="preserve">12.8661842346191</t>
   </si>
   <si>
     <t xml:space="preserve">13.1306037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2879161834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8260192871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9833316802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9029998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2377099990845</t>
+    <t xml:space="preserve">13.2879152297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8260202407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9833307266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9030027389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2377109527588</t>
   </si>
   <si>
     <t xml:space="preserve">13.1674213409424</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1138677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971307754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5046997070312</t>
+    <t xml:space="preserve">13.1138696670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.097131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5046987533569</t>
   </si>
   <si>
     <t xml:space="preserve">12.8092851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8862676620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7055234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7222604751587</t>
+    <t xml:space="preserve">12.886266708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7055244445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7222595214844</t>
   </si>
   <si>
     <t xml:space="preserve">12.9163904190063</t>
@@ -239,58 +239,58 @@
     <t xml:space="preserve">13.0301895141602</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8327112197876</t>
+    <t xml:space="preserve">12.8327121734619</t>
   </si>
   <si>
     <t xml:space="preserve">12.6318883895874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7021770477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8695316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.558253288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5682926177979</t>
+    <t xml:space="preserve">12.7021789550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.869532585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5582542419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5682935714722</t>
   </si>
   <si>
     <t xml:space="preserve">12.8360595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8494501113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5348224639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7791614532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.769118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7865629196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5024185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6512584686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.752739906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5836048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4990377426147</t>
+    <t xml:space="preserve">12.8494482040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958946228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5348234176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7791604995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7691211700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.786563873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5024194717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6512594223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7527379989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5836057662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4990386962891</t>
   </si>
   <si>
     <t xml:space="preserve">12.5700731277466</t>
@@ -302,43 +302,43 @@
     <t xml:space="preserve">12.2791624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">12.06605052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776809692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1641492843628</t>
+    <t xml:space="preserve">12.0660533905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776819229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1641511917114</t>
   </si>
   <si>
     <t xml:space="preserve">12.170916557312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1100282669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1269416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.981484413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7459754943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580238342285</t>
+    <t xml:space="preserve">12.1100263595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1269407272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9814863204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7459716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580219268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.3231391906738</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6973400115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7785234451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2406768798828</t>
+    <t xml:space="preserve">11.697340965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7785243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2406778335571</t>
   </si>
   <si>
     <t xml:space="preserve">10.8212232589722</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">10.6554708480835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0613946914673</t>
+    <t xml:space="preserve">11.061393737793</t>
   </si>
   <si>
     <t xml:space="preserve">11.1967010498047</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4064292907715</t>
+    <t xml:space="preserve">11.4064283370972</t>
   </si>
   <si>
     <t xml:space="preserve">11.5248222351074</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">10.6656198501587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1886596679688</t>
+    <t xml:space="preserve">10.1886606216431</t>
   </si>
   <si>
     <t xml:space="preserve">10.5878171920776</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">10.6825332641602</t>
   </si>
   <si>
-    <t xml:space="preserve">11.839412689209</t>
+    <t xml:space="preserve">11.8394136428833</t>
   </si>
   <si>
     <t xml:space="preserve">13.0199728012085</t>
@@ -380,13 +380,13 @@
     <t xml:space="preserve">13.3616228103638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0233554840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1924877166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4969310760498</t>
+    <t xml:space="preserve">13.0233564376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1924886703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4969320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.4698696136475</t>
@@ -395,22 +395,22 @@
     <t xml:space="preserve">13.5307569503784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4800148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2939682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.310884475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548603057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0740938186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368852615356</t>
+    <t xml:space="preserve">13.4800176620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2939691543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548564910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0740976333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368871688843</t>
   </si>
   <si>
     <t xml:space="preserve">12.9489345550537</t>
@@ -419,64 +419,64 @@
     <t xml:space="preserve">12.9827613830566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910081863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0707120895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9962911605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8576030731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1248350143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1823406219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0605630874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857242584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4123659133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5679664611816</t>
+    <t xml:space="preserve">13.091010093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0707111358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9962921142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8576021194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113042831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1248369216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1823425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0605640411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857233047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4123640060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5679683685303</t>
   </si>
   <si>
     <t xml:space="preserve">13.4157466888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5138444900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7066583633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8352022171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2106771469116</t>
+    <t xml:space="preserve">13.5138463973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.706657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8352012634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2106781005859</t>
   </si>
   <si>
     <t xml:space="preserve">14.4576139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7552900314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838338851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.01575756073</t>
+    <t xml:space="preserve">14.7552919387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838319778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0157556533813</t>
   </si>
   <si>
     <t xml:space="preserve">14.9853143692017</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">15.3303489685059</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6652336120605</t>
+    <t xml:space="preserve">15.6652374267578</t>
   </si>
   <si>
     <t xml:space="preserve">15.2897567749023</t>
@@ -503,91 +503,91 @@
     <t xml:space="preserve">14.9514875411987</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7485237121582</t>
+    <t xml:space="preserve">14.7485256195068</t>
   </si>
   <si>
     <t xml:space="preserve">14.7180814743042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8770666122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7992639541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751653671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.90074634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2018022537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939828872681</t>
+    <t xml:space="preserve">14.8770685195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7992658615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9007425308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.201807975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939809799194</t>
   </si>
   <si>
     <t xml:space="preserve">14.8330936431885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9988451004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9142789840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9278087615967</t>
+    <t xml:space="preserve">14.9988422393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9142770767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.927806854248</t>
   </si>
   <si>
     <t xml:space="preserve">14.7383785247803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7248468399048</t>
+    <t xml:space="preserve">14.7248449325562</t>
   </si>
   <si>
     <t xml:space="preserve">14.5421838760376</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4440841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0529699325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1442995071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1104726791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.954870223999</t>
+    <t xml:space="preserve">14.4440851211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0529680252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1443014144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1104745864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9548683166504</t>
   </si>
   <si>
     <t xml:space="preserve">15.0901803970337</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2187213897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7823534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707220077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6166019439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.376428604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1599369049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2546529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0415420532227</t>
+    <t xml:space="preserve">15.2187204360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7823514938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707239151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.616602897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764305114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1599397659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2546520233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0415439605713</t>
   </si>
   <si>
     <t xml:space="preserve">14.1125812530518</t>
@@ -596,67 +596,67 @@
     <t xml:space="preserve">14.038161277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1430253982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903820037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527498245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.20729637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3561344146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373197555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730459213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3087759017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2411222457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3392210006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2512702941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464099884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058158874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.119348526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2275915145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2715673446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1497898101807</t>
+    <t xml:space="preserve">14.1430244445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527507781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2072973251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3561334609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730478286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3087778091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2411212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3392181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2512693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1464071273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058168411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.119345664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2275943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2715635299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1497917175293</t>
   </si>
   <si>
     <t xml:space="preserve">14.0753707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0719861984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749490737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667022705078</t>
+    <t xml:space="preserve">14.0719900131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667032241821</t>
   </si>
   <si>
     <t xml:space="preserve">14.4779100418091</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">14.7519092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8161792755127</t>
+    <t xml:space="preserve">14.8161783218384</t>
   </si>
   <si>
     <t xml:space="preserve">15.1037082672119</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0834121704102</t>
+    <t xml:space="preserve">15.0834131240845</t>
   </si>
   <si>
     <t xml:space="preserve">15.1882762908936</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">15.1172399520874</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1544485092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999038696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3574104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3912372589111</t>
+    <t xml:space="preserve">15.1544466018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758014678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3574085235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3912382125854</t>
   </si>
   <si>
     <t xml:space="preserve">15.4893360137939</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1713571548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.100323677063</t>
+    <t xml:space="preserve">15.1713609695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1003255844116</t>
   </si>
   <si>
     <t xml:space="preserve">15.3946180343628</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">15.3134355545044</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4182977676392</t>
+    <t xml:space="preserve">15.4182996749878</t>
   </si>
   <si>
     <t xml:space="preserve">15.4250631332397</t>
@@ -728,31 +728,31 @@
     <t xml:space="preserve">15.6753835678101</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6449394226074</t>
+    <t xml:space="preserve">15.6449375152588</t>
   </si>
   <si>
     <t xml:space="preserve">15.7295055389404</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6618518829346</t>
+    <t xml:space="preserve">15.6618537902832</t>
   </si>
   <si>
     <t xml:space="preserve">15.6517038345337</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6821460723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637540817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.408148765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415548324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7024431228638</t>
+    <t xml:space="preserve">15.6821479797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637521743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081506729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415567398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7024440765381</t>
   </si>
   <si>
     <t xml:space="preserve">15.5333099365234</t>
@@ -761,34 +761,34 @@
     <t xml:space="preserve">15.6584711074829</t>
   </si>
   <si>
-    <t xml:space="preserve">15.458890914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5874347686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6550884246826</t>
+    <t xml:space="preserve">15.4588871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5874357223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.655086517334</t>
   </si>
   <si>
     <t xml:space="preserve">15.7227392196655</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3350105285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0339488983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4060459136963</t>
+    <t xml:space="preserve">16.3350086212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0339469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.406042098999</t>
   </si>
   <si>
     <t xml:space="preserve">16.4026622772217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4195728302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6935710906982</t>
+    <t xml:space="preserve">16.4195766448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6935729980469</t>
   </si>
   <si>
     <t xml:space="preserve">17.099494934082</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">16.9980144500732</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1671485900879</t>
+    <t xml:space="preserve">17.1671466827393</t>
   </si>
   <si>
     <t xml:space="preserve">17.4208507537842</t>
@@ -806,100 +806,100 @@
     <t xml:space="preserve">17.5392436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6407241821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.403938293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4885063171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3531970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3870220184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.522331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4546775817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8775119781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8098602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7083797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7591209411621</t>
+    <t xml:space="preserve">17.6407260894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4039363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.48850440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3531951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3870258331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5223293304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4546756744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.877513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8098621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7083759307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7591190338135</t>
   </si>
   <si>
     <t xml:space="preserve">17.6745529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.573070526123</t>
+    <t xml:space="preserve">17.5730724334717</t>
   </si>
   <si>
     <t xml:space="preserve">17.3362846374512</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2009754180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2348003387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2517166137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2178897857666</t>
+    <t xml:space="preserve">17.2009735107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2348022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2517185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2178916931152</t>
   </si>
   <si>
     <t xml:space="preserve">17.3701095581055</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4560203552246</t>
+    <t xml:space="preserve">17.456018447876</t>
   </si>
   <si>
     <t xml:space="preserve">17.7147541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5767612457275</t>
+    <t xml:space="preserve">17.5767631530762</t>
   </si>
   <si>
     <t xml:space="preserve">17.5595149993896</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6975078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4698181152344</t>
+    <t xml:space="preserve">17.6975040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.469820022583</t>
   </si>
   <si>
     <t xml:space="preserve">17.6147117614746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7729606628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0075435638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1662368774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1317367553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.993745803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9868488311768</t>
+    <t xml:space="preserve">16.7729568481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0075454711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1662349700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1317386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9937438964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9868469238281</t>
   </si>
   <si>
     <t xml:space="preserve">16.9661483764648</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">16.835054397583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.84885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8281517028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7591609954834</t>
+    <t xml:space="preserve">16.8488521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8281555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7591590881348</t>
   </si>
   <si>
     <t xml:space="preserve">16.8695526123047</t>
@@ -926,19 +926,19 @@
     <t xml:space="preserve">16.9730472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.938549041748</t>
+    <t xml:space="preserve">16.9385471343994</t>
   </si>
   <si>
     <t xml:space="preserve">17.152437210083</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6625633239746</t>
+    <t xml:space="preserve">16.6625652313232</t>
   </si>
   <si>
     <t xml:space="preserve">16.5935688018799</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5659694671631</t>
+    <t xml:space="preserve">16.5659713745117</t>
   </si>
   <si>
     <t xml:space="preserve">16.5038738250732</t>
@@ -947,19 +947,19 @@
     <t xml:space="preserve">16.8626537322998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9040508270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.80055809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8971500396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5383701324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5590724945068</t>
+    <t xml:space="preserve">16.9040489196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8005561828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8971519470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5383720397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5590705871582</t>
   </si>
   <si>
     <t xml:space="preserve">16.4900722503662</t>
@@ -974,43 +974,43 @@
     <t xml:space="preserve">16.2485866546631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.124397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1864891052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1588935852051</t>
+    <t xml:space="preserve">16.1243953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1864910125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1588954925537</t>
   </si>
   <si>
     <t xml:space="preserve">16.5314712524414</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2899837493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3175830841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5452709197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3658790588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.462474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3313827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3520832061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6970615386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3865795135498</t>
+    <t xml:space="preserve">16.2899856567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3175849914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5452728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3658809661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4624729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3313846588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3520812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6970634460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3865776062012</t>
   </si>
   <si>
     <t xml:space="preserve">16.4486751556396</t>
@@ -1019,13 +1019,13 @@
     <t xml:space="preserve">16.5107727050781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4210777282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4348793029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3934783935547</t>
+    <t xml:space="preserve">16.4210758209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4348754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3934803009033</t>
   </si>
   <si>
     <t xml:space="preserve">16.4969730377197</t>
@@ -1037,124 +1037,124 @@
     <t xml:space="preserve">16.4003791809082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4555759429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3589820861816</t>
+    <t xml:space="preserve">16.4555740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.358980178833</t>
   </si>
   <si>
     <t xml:space="preserve">16.2830848693848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5521697998047</t>
+    <t xml:space="preserve">16.5521717071533</t>
   </si>
   <si>
     <t xml:space="preserve">16.1795921325684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2071876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1933860778809</t>
+    <t xml:space="preserve">16.2071914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1933898925781</t>
   </si>
   <si>
     <t xml:space="preserve">16.1519927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.903603553772</t>
+    <t xml:space="preserve">15.9036054611206</t>
   </si>
   <si>
     <t xml:space="preserve">15.5586261749268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965295791626</t>
+    <t xml:space="preserve">15.4965314865112</t>
   </si>
   <si>
     <t xml:space="preserve">15.9381055831909</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7794132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7656154632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7863121032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9795017242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9312047958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.703516960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6483240127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8415117263794</t>
+    <t xml:space="preserve">15.7794151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7656116485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7863140106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9795036315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.931206703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7035188674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6483221054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8415098190308</t>
   </si>
   <si>
     <t xml:space="preserve">15.7518177032471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8691072463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8622102737427</t>
+    <t xml:space="preserve">15.8691091537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.862208366394</t>
   </si>
   <si>
     <t xml:space="preserve">16.0277996063232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8967084884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6276226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7173166275024</t>
+    <t xml:space="preserve">15.896710395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6276216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7173185348511</t>
   </si>
   <si>
     <t xml:space="preserve">15.5310287475586</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5034275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413328170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2481451034546</t>
+    <t xml:space="preserve">15.5034303665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413347244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.248143196106</t>
   </si>
   <si>
     <t xml:space="preserve">15.3171405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3309383392334</t>
+    <t xml:space="preserve">15.3309364318848</t>
   </si>
   <si>
     <t xml:space="preserve">15.2826414108276</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3792343139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.261944770813</t>
+    <t xml:space="preserve">15.3792381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619428634644</t>
   </si>
   <si>
     <t xml:space="preserve">15.6000232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4896287918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9519062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9726009368896</t>
+    <t xml:space="preserve">15.4896326065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.951904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9726028442383</t>
   </si>
   <si>
     <t xml:space="preserve">15.9864025115967</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">15.7932109832764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4758310317993</t>
+    <t xml:space="preserve">15.4758329391479</t>
   </si>
   <si>
     <t xml:space="preserve">15.2895421981812</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">15.2343454360962</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3033399581909</t>
+    <t xml:space="preserve">15.3033390045166</t>
   </si>
   <si>
     <t xml:space="preserve">15.4137344360352</t>
@@ -1199,22 +1199,22 @@
     <t xml:space="preserve">15.6345224380493</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1450939178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4831714630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6073665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.37278175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6349678039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141807556152</t>
+    <t xml:space="preserve">16.145092010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4831733703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6073684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3727779388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6349697113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.414176940918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0898971557617</t>
@@ -1223,25 +1223,25 @@
     <t xml:space="preserve">16.2002906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7315616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.69016456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4762744903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7522602081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6487655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6280670166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0420417785645</t>
+    <t xml:space="preserve">16.731559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6901626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4762725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7522583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6487636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6280689239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0420436859131</t>
   </si>
   <si>
     <t xml:space="preserve">17.0765419006348</t>
@@ -1250,82 +1250,82 @@
     <t xml:space="preserve">17.1110382080078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2145328521729</t>
+    <t xml:space="preserve">17.2145347595215</t>
   </si>
   <si>
     <t xml:space="preserve">17.1455364227295</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1800365447998</t>
+    <t xml:space="preserve">17.1800346374512</t>
   </si>
   <si>
     <t xml:space="preserve">16.00710105896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.21409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1105976104736</t>
+    <t xml:space="preserve">16.2140884399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.110595703125</t>
   </si>
   <si>
     <t xml:space="preserve">15.5931224822998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6621217727661</t>
+    <t xml:space="preserve">15.6621198654175</t>
   </si>
   <si>
     <t xml:space="preserve">15.0066576004028</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7306728363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9031648635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9721622467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551343917847</t>
+    <t xml:space="preserve">14.7306747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9031639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9721603393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551305770874</t>
   </si>
   <si>
     <t xml:space="preserve">15.1101512908936</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0411539077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0756540298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3516407012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4206352233887</t>
+    <t xml:space="preserve">15.0411558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0756521224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3516387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4206342697144</t>
   </si>
   <si>
     <t xml:space="preserve">15.5241279602051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6966180801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8742475509644</t>
+    <t xml:space="preserve">15.6966199874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8742485046387</t>
   </si>
   <si>
     <t xml:space="preserve">15.5560550689697</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7328310012817</t>
+    <t xml:space="preserve">15.7328290939331</t>
   </si>
   <si>
     <t xml:space="preserve">15.5914087295532</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3439292907715</t>
+    <t xml:space="preserve">15.3439283370972</t>
   </si>
   <si>
     <t xml:space="preserve">15.3792819976807</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">14.7782535552979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4247045516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5307693481445</t>
+    <t xml:space="preserve">14.4247074127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5307703018188</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600610733032</t>
@@ -1346,34 +1346,34 @@
     <t xml:space="preserve">14.495415687561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8873138427734</t>
+    <t xml:space="preserve">13.8873167037964</t>
   </si>
   <si>
     <t xml:space="preserve">14.1135845184326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.318642616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6014776229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0257339477539</t>
+    <t xml:space="preserve">14.3186435699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6014795303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0257358551025</t>
   </si>
   <si>
     <t xml:space="preserve">15.061089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">14.955023765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8489627838135</t>
+    <t xml:space="preserve">14.9550256729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8489608764648</t>
   </si>
   <si>
     <t xml:space="preserve">14.884316444397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.707540512085</t>
+    <t xml:space="preserve">14.7075443267822</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671562194824</t>
@@ -1382,16 +1382,16 @@
     <t xml:space="preserve">15.2025098800659</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5661249160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6368350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2832880020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.085301399231</t>
+    <t xml:space="preserve">14.5661239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.636833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2832899093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0853033065796</t>
   </si>
   <si>
     <t xml:space="preserve">14.81360912323</t>
@@ -1400,46 +1400,46 @@
     <t xml:space="preserve">14.3539972305298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.389349937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428998947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1418685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.177225112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2479333877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2125797271729</t>
+    <t xml:space="preserve">14.3893527984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428979873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1418704986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1772222518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.247932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2125787734985</t>
   </si>
   <si>
     <t xml:space="preserve">14.0711584091187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9438829421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8731737136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8166074752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8590316772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0145931243896</t>
+    <t xml:space="preserve">13.9438810348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8731746673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8166055679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8590326309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0145950317383</t>
   </si>
   <si>
     <t xml:space="preserve">13.9297428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0004510879517</t>
+    <t xml:space="preserve">14.0004501342773</t>
   </si>
   <si>
     <t xml:space="preserve">14.0994434356689</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">14.0287342071533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0570163726807</t>
+    <t xml:space="preserve">14.057017326355</t>
   </si>
   <si>
     <t xml:space="preserve">14.1277265548706</t>
@@ -1466,28 +1466,28 @@
     <t xml:space="preserve">13.4347772598267</t>
   </si>
   <si>
-    <t xml:space="preserve">13.505485534668</t>
+    <t xml:space="preserve">13.5054864883423</t>
   </si>
   <si>
     <t xml:space="preserve">13.4913425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3782062530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.463059425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5620527267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5337696075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1660804748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7842483520508</t>
+    <t xml:space="preserve">13.3782072067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4630603790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5620517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5337677001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1660814285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7842502593994</t>
   </si>
   <si>
     <t xml:space="preserve">12.6852569580078</t>
@@ -1499,16 +1499,16 @@
     <t xml:space="preserve">12.6569728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4064922332764</t>
+    <t xml:space="preserve">13.4064903259277</t>
   </si>
   <si>
     <t xml:space="preserve">13.5479106903076</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7883224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7741785049438</t>
+    <t xml:space="preserve">13.7883205413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7741804122925</t>
   </si>
   <si>
     <t xml:space="preserve">13.5903358459473</t>
@@ -1517,55 +1517,55 @@
     <t xml:space="preserve">13.448917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074998855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3923492431641</t>
+    <t xml:space="preserve">13.3075008392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.392352104187</t>
   </si>
   <si>
     <t xml:space="preserve">13.0105199813843</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1519384384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2933578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9256687164307</t>
+    <t xml:space="preserve">13.1519374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2933568954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9256706237793</t>
   </si>
   <si>
     <t xml:space="preserve">13.0388031005859</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9963788986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2367877960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0953712463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6469049453735</t>
+    <t xml:space="preserve">12.996376991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2367897033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0953722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6469030380249</t>
   </si>
   <si>
     <t xml:space="preserve">13.6751871109009</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0670852661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2509298324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2085065841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812282562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3499212265015</t>
+    <t xml:space="preserve">13.0670871734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2509288787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2085056304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812292098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3499231338501</t>
   </si>
   <si>
     <t xml:space="preserve">12.8408164978027</t>
@@ -1577,64 +1577,64 @@
     <t xml:space="preserve">12.897385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6004056930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7317543029785</t>
+    <t xml:space="preserve">12.6004037857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7317552566528</t>
   </si>
   <si>
     <t xml:space="preserve">13.5761957168579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.519627571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7176141738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8307495117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7600364685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9156007766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7458963394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.042875289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8448915481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5417671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2218494415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9455547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1782236099243</t>
+    <t xml:space="preserve">13.5196266174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7176113128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8307466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7600383758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.915599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7458982467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0428771972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8448905944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.54176902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2218475341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9455537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1782217025757</t>
   </si>
   <si>
     <t xml:space="preserve">13.9891796112061</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2073078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4399747848511</t>
+    <t xml:space="preserve">14.2073059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4399766921997</t>
   </si>
   <si>
     <t xml:space="preserve">14.265474319458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4108924865723</t>
+    <t xml:space="preserve">14.4108943939209</t>
   </si>
   <si>
     <t xml:space="preserve">14.4981422424316</t>
@@ -1643,37 +1643,37 @@
     <t xml:space="preserve">14.4690570831299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.352725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3381824493408</t>
+    <t xml:space="preserve">14.3527240753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3381805419922</t>
   </si>
   <si>
     <t xml:space="preserve">14.5126838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3963508605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871852874756</t>
+    <t xml:space="preserve">14.3963489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871871948242</t>
   </si>
   <si>
     <t xml:space="preserve">14.4254322052002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4836006164551</t>
+    <t xml:space="preserve">14.4836015701294</t>
   </si>
   <si>
     <t xml:space="preserve">14.6144762039185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8326005935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9780216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1234350204468</t>
+    <t xml:space="preserve">14.8326044082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9780197143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.123438835144</t>
   </si>
   <si>
     <t xml:space="preserve">15.1961469650269</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">15.4142751693726</t>
   </si>
   <si>
-    <t xml:space="preserve">15.450626373291</t>
+    <t xml:space="preserve">15.4506282806396</t>
   </si>
   <si>
     <t xml:space="preserve">15.3415641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2325010299683</t>
+    <t xml:space="preserve">15.2325019836426</t>
   </si>
   <si>
     <t xml:space="preserve">15.3052091598511</t>
@@ -1697,25 +1697,25 @@
     <t xml:space="preserve">15.2688541412354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6687507629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0507297515869</t>
+    <t xml:space="preserve">15.6687536239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0507278442383</t>
   </si>
   <si>
     <t xml:space="preserve">15.0870838165283</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9416646957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7235383987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0143728256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5781221389771</t>
+    <t xml:space="preserve">14.9416666030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7235403060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0143747329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5781202316284</t>
   </si>
   <si>
     <t xml:space="preserve">14.7598934173584</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">14.4545154571533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7962474822998</t>
+    <t xml:space="preserve">14.7962493896484</t>
   </si>
   <si>
     <t xml:space="preserve">14.9053106307983</t>
@@ -1748,10 +1748,10 @@
     <t xml:space="preserve">16.359489440918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5049057006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6139698028564</t>
+    <t xml:space="preserve">16.5049076080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6139678955078</t>
   </si>
   <si>
     <t xml:space="preserve">16.5412616729736</t>
@@ -1763,19 +1763,19 @@
     <t xml:space="preserve">16.6503238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5776119232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8684482574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7593841552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.050220489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.086576461792</t>
+    <t xml:space="preserve">16.577615737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8684501647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7593860626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0502223968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0865783691406</t>
   </si>
   <si>
     <t xml:space="preserve">17.4864730834961</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">17.4137668609619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2683486938477</t>
+    <t xml:space="preserve">17.2683506011963</t>
   </si>
   <si>
     <t xml:space="preserve">17.5228290557861</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">17.6682472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0681457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9227256774902</t>
+    <t xml:space="preserve">18.0681476593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9227275848389</t>
   </si>
   <si>
     <t xml:space="preserve">18.1044998168945</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">17.8500194549561</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9590835571289</t>
+    <t xml:space="preserve">17.9590854644775</t>
   </si>
   <si>
     <t xml:space="preserve">18.177209854126</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0317897796631</t>
+    <t xml:space="preserve">18.0317916870117</t>
   </si>
   <si>
     <t xml:space="preserve">18.2862720489502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.358980178833</t>
+    <t xml:space="preserve">18.3589820861816</t>
   </si>
   <si>
     <t xml:space="preserve">18.4680461883545</t>
@@ -1838,28 +1838,28 @@
     <t xml:space="preserve">18.5771064758301</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9954376220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5591850280762</t>
+    <t xml:space="preserve">17.9954357147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5591831207275</t>
   </si>
   <si>
     <t xml:space="preserve">17.5955390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.450122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2499160766602</t>
+    <t xml:space="preserve">17.4501209259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2499198913574</t>
   </si>
   <si>
     <t xml:space="preserve">18.3953342437744</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2135620117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3226280212402</t>
+    <t xml:space="preserve">18.2135639190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3226261138916</t>
   </si>
   <si>
     <t xml:space="preserve">18.6134624481201</t>
@@ -1871,25 +1871,25 @@
     <t xml:space="preserve">18.8315887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1951351165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9770050048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0860691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2678413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1224231719971</t>
+    <t xml:space="preserve">19.1951332092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9770069122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0860710144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2678394317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1224250793457</t>
   </si>
   <si>
     <t xml:space="preserve">19.3041973114014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4132595062256</t>
+    <t xml:space="preserve">19.4132614135742</t>
   </si>
   <si>
     <t xml:space="preserve">19.4496116638184</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">17.3047027587891</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3774108886719</t>
+    <t xml:space="preserve">17.3774127960205</t>
   </si>
   <si>
     <t xml:space="preserve">18.7952346801758</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">19.8495121002197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.42138671875</t>
+    <t xml:space="preserve">19.4213848114014</t>
   </si>
   <si>
     <t xml:space="preserve">19.7327499389648</t>
@@ -1952,19 +1952,16 @@
     <t xml:space="preserve">20.3554801940918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8495140075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.121955871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9273529052734</t>
+    <t xml:space="preserve">20.1219577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9273548126221</t>
   </si>
   <si>
     <t xml:space="preserve">19.4603061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3435440063477</t>
+    <t xml:space="preserve">19.3435459136963</t>
   </si>
   <si>
     <t xml:space="preserve">19.3046245574951</t>
@@ -1979,10 +1976,10 @@
     <t xml:space="preserve">19.771671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7597389221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1608791351318</t>
+    <t xml:space="preserve">18.7597351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1608772277832</t>
   </si>
   <si>
     <t xml:space="preserve">20.044116973877</t>
@@ -2000,19 +1997,19 @@
     <t xml:space="preserve">21.2895755767822</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0171298980713</t>
+    <t xml:space="preserve">21.0171318054199</t>
   </si>
   <si>
     <t xml:space="preserve">20.7836074829102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7057647705078</t>
+    <t xml:space="preserve">20.7057666778564</t>
   </si>
   <si>
     <t xml:space="preserve">21.094970703125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4452571868896</t>
+    <t xml:space="preserve">21.445255279541</t>
   </si>
   <si>
     <t xml:space="preserve">21.7566223144531</t>
@@ -2021,25 +2018,25 @@
     <t xml:space="preserve">21.9512252807617</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6009387969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7955436706543</t>
+    <t xml:space="preserve">21.6009407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7955417633057</t>
   </si>
   <si>
     <t xml:space="preserve">22.0290679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0679874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5350360870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.57395362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6517963409424</t>
+    <t xml:space="preserve">22.0679893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5350341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.651798248291</t>
   </si>
   <si>
     <t xml:space="preserve">22.7685585021973</t>
@@ -2048,10 +2045,10 @@
     <t xml:space="preserve">22.8074779510498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7296390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3404331207275</t>
+    <t xml:space="preserve">22.7296409606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3404312133789</t>
   </si>
   <si>
     <t xml:space="preserve">22.2625923156738</t>
@@ -2063,13 +2060,13 @@
     <t xml:space="preserve">23.97509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4032249450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9091911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7145881652832</t>
+    <t xml:space="preserve">24.4032230377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9091930389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7145900726318</t>
   </si>
   <si>
     <t xml:space="preserve">24.5199851989746</t>
@@ -2090,13 +2087,13 @@
     <t xml:space="preserve">24.6367492675781</t>
   </si>
   <si>
-    <t xml:space="preserve">24.16969871521</t>
+    <t xml:space="preserve">24.1697006225586</t>
   </si>
   <si>
     <t xml:space="preserve">24.0140190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0799236297607</t>
+    <t xml:space="preserve">23.0799217224121</t>
   </si>
   <si>
     <t xml:space="preserve">23.7026519775391</t>
@@ -2105,7 +2102,7 @@
     <t xml:space="preserve">24.0529384613037</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4691276550293</t>
+    <t xml:space="preserve">23.4691295623779</t>
   </si>
   <si>
     <t xml:space="preserve">23.5858917236328</t>
@@ -2120,7 +2117,7 @@
     <t xml:space="preserve">23.7415733337402</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8194160461426</t>
+    <t xml:space="preserve">23.8194141387939</t>
   </si>
   <si>
     <t xml:space="preserve">23.6637325286865</t>
@@ -2132,7 +2129,7 @@
     <t xml:space="preserve">24.0918598175049</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3912868499756</t>
+    <t xml:space="preserve">23.3912887573242</t>
   </si>
   <si>
     <t xml:space="preserve">23.352367401123</t>
@@ -2141,19 +2138,19 @@
     <t xml:space="preserve">23.0410022735596</t>
   </si>
   <si>
-    <t xml:space="preserve">23.002082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1188449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6248111724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6128768920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1069087982178</t>
+    <t xml:space="preserve">23.0020809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1188430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.624813079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6128749847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1069068908691</t>
   </si>
   <si>
     <t xml:space="preserve">22.1847476959229</t>
@@ -2171,102 +2168,105 @@
     <t xml:space="preserve">22.3793525695801</t>
   </si>
   <si>
+    <t xml:space="preserve">22.9631614685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2356071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9242420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.223669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4182720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9123058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4841766357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1338901519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.523099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.717700958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6398601531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2506542205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5620193481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8344612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6787815093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9901466369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1458282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.846399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8853206634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4571914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2117328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3674182891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9782104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6279239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.873384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4407329559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8835639953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7243747711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8039703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7641735076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0427551269531</t>
+  </si>
+  <si>
     <t xml:space="preserve">22.9631595611572</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2356071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9242420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.223669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4182739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9123058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4841766357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1338920593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5231018066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7177028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6398601531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2506542205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5620193481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8344612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6787815093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9901447296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1458282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.846399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8853187561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4571933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3284950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2117328643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3674182891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9782104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6279258728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.873384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.440731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8835639953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7243747711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8039703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7641735076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0427551269531</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.2417449951172</t>
   </si>
   <si>
@@ -2294,25 +2294,25 @@
     <t xml:space="preserve">24.4356689453125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3162746429443</t>
+    <t xml:space="preserve">24.3162727355957</t>
   </si>
   <si>
     <t xml:space="preserve">24.3560733795166</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7938442230225</t>
+    <t xml:space="preserve">24.7938461303711</t>
   </si>
   <si>
     <t xml:space="preserve">24.1570854187012</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6744518280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9132385253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5550632476807</t>
+    <t xml:space="preserve">24.6744537353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.913236618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.555061340332</t>
   </si>
   <si>
     <t xml:space="preserve">24.7540493011475</t>
@@ -2327,16 +2327,16 @@
     <t xml:space="preserve">24.5152626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4754676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2366809844971</t>
+    <t xml:space="preserve">24.4754657745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2366790771484</t>
   </si>
   <si>
     <t xml:space="preserve">24.3958702087402</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7142486572266</t>
+    <t xml:space="preserve">24.7142505645752</t>
   </si>
   <si>
     <t xml:space="preserve">24.6346569061279</t>
@@ -2345,34 +2345,34 @@
     <t xml:space="preserve">24.1968822479248</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6295948028564</t>
+    <t xml:space="preserve">25.6295928955078</t>
   </si>
   <si>
     <t xml:space="preserve">25.5102005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1520252227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3510112762451</t>
+    <t xml:space="preserve">25.1520233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3510131835938</t>
   </si>
   <si>
     <t xml:space="preserve">25.4704036712646</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6693916320801</t>
+    <t xml:space="preserve">25.6693897247314</t>
   </si>
   <si>
     <t xml:space="preserve">25.3908100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1918201446533</t>
+    <t xml:space="preserve">25.191822052002</t>
   </si>
   <si>
     <t xml:space="preserve">25.0326328277588</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2714157104492</t>
+    <t xml:space="preserve">25.2714176177979</t>
   </si>
   <si>
     <t xml:space="preserve">24.8336448669434</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">25.8683776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0724296569824</t>
+    <t xml:space="preserve">25.0724277496338</t>
   </si>
   <si>
     <t xml:space="preserve">23.7591114044189</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">24.5948581695557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9928340911865</t>
+    <t xml:space="preserve">24.9928321838379</t>
   </si>
   <si>
     <t xml:space="preserve">25.430606842041</t>
@@ -2423,10 +2423,10 @@
     <t xml:space="preserve">26.2663516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0275688171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.788782119751</t>
+    <t xml:space="preserve">26.0275707244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7887840270996</t>
   </si>
   <si>
     <t xml:space="preserve">25.5499992370605</t>
@@ -2435,19 +2435,19 @@
     <t xml:space="preserve">25.5897960662842</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9479713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1071624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7489852905273</t>
+    <t xml:space="preserve">25.9479732513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1071643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7489833831787</t>
   </si>
   <si>
     <t xml:space="preserve">24.8734397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0376930236816</t>
+    <t xml:space="preserve">24.0376949310303</t>
   </si>
   <si>
     <t xml:space="preserve">22.3264007568359</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">23.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4009342193604</t>
+    <t xml:space="preserve">23.4009323120117</t>
   </si>
   <si>
     <t xml:space="preserve">23.5601234436035</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4855899810791</t>
+    <t xml:space="preserve">22.4855918884277</t>
   </si>
   <si>
     <t xml:space="preserve">23.8387069702148</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">23.8264102935791</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5692901611328</t>
+    <t xml:space="preserve">23.5692920684814</t>
   </si>
   <si>
     <t xml:space="preserve">24.1263828277588</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">24.1692371368408</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2120876312256</t>
+    <t xml:space="preserve">24.2120895385742</t>
   </si>
   <si>
     <t xml:space="preserve">23.7835578918457</t>
@@ -2522,19 +2522,19 @@
     <t xml:space="preserve">24.2549419403076</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977962493896</t>
+    <t xml:space="preserve">24.2977981567383</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264377593994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.99782371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9121170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8692646026611</t>
+    <t xml:space="preserve">23.9978218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9121150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8692626953125</t>
   </si>
   <si>
     <t xml:space="preserve">23.7407035827637</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">23.6549968719482</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9693431854248</t>
+    <t xml:space="preserve">22.9693450927734</t>
   </si>
   <si>
     <t xml:space="preserve">22.8836402893066</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">23.1407585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">22.840784072876</t>
+    <t xml:space="preserve">22.8407859802246</t>
   </si>
   <si>
     <t xml:space="preserve">22.7550792694092</t>
@@ -2567,19 +2567,19 @@
     <t xml:space="preserve">22.6693725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0550498962402</t>
+    <t xml:space="preserve">23.0550518035889</t>
   </si>
   <si>
     <t xml:space="preserve">23.2264652252197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7122268676758</t>
+    <t xml:space="preserve">22.7122249603271</t>
   </si>
   <si>
     <t xml:space="preserve">22.4122524261475</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1836109161377</t>
+    <t xml:space="preserve">23.1836090087891</t>
   </si>
   <si>
     <t xml:space="preserve">23.0979061126709</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">22.3694000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3550262451172</t>
+    <t xml:space="preserve">23.3550243377686</t>
   </si>
   <si>
     <t xml:space="preserve">23.0121994018555</t>
@@ -2597,28 +2597,28 @@
     <t xml:space="preserve">23.3121719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3978748321533</t>
+    <t xml:space="preserve">23.397876739502</t>
   </si>
   <si>
     <t xml:space="preserve">22.7979316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4551067352295</t>
+    <t xml:space="preserve">22.4551048278809</t>
   </si>
   <si>
     <t xml:space="preserve">22.4979591369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6265201568604</t>
+    <t xml:space="preserve">22.6265182495117</t>
   </si>
   <si>
     <t xml:space="preserve">23.6978511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5408134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2693176269531</t>
+    <t xml:space="preserve">22.5408115386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2693157196045</t>
   </si>
   <si>
     <t xml:space="preserve">22.2836933135986</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">21.426628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.469482421875</t>
+    <t xml:space="preserve">21.4694805145264</t>
   </si>
   <si>
     <t xml:space="preserve">21.2552146911621</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">20.6981220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5980415344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3837757110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5123329162598</t>
+    <t xml:space="preserve">21.5980434417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3837738037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5123348236084</t>
   </si>
   <si>
     <t xml:space="preserve">21.3409214019775</t>
@@ -2684,10 +2684,10 @@
     <t xml:space="preserve">21.8123073577881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1551322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2408390045166</t>
+    <t xml:space="preserve">22.1551342010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2408409118652</t>
   </si>
   <si>
     <t xml:space="preserve">21.6837463378906</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">21.0409469604492</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9123878479004</t>
+    <t xml:space="preserve">20.912389755249</t>
   </si>
   <si>
     <t xml:space="preserve">21.2980690002441</t>
@@ -3675,6 +3675,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7000007629395</t>
   </si>
 </sst>
 </file>
@@ -32761,7 +32764,7 @@
         <v>25.5</v>
       </c>
       <c r="G1106" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32813,7 +32816,7 @@
         <v>25.5</v>
       </c>
       <c r="G1108" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32839,7 +32842,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G1109" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32865,7 +32868,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1110" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32891,7 +32894,7 @@
         <v>25</v>
       </c>
       <c r="G1111" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32917,7 +32920,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1112" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32943,7 +32946,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1113" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32969,7 +32972,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1114" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -33021,7 +33024,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1116" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -33047,7 +33050,7 @@
         <v>24.75</v>
       </c>
       <c r="G1117" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -33073,7 +33076,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1118" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33099,7 +33102,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1119" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33177,7 +33180,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1122" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33203,7 +33206,7 @@
         <v>25.75</v>
       </c>
       <c r="G1123" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33229,7 +33232,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1124" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33255,7 +33258,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1125" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33281,7 +33284,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1126" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33307,7 +33310,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G1127" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33333,7 +33336,7 @@
         <v>27</v>
       </c>
       <c r="G1128" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33359,7 +33362,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1129" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33385,7 +33388,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1130" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33411,7 +33414,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1131" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33437,7 +33440,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1132" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33463,7 +33466,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1133" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33489,7 +33492,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1134" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33515,7 +33518,7 @@
         <v>27.75</v>
       </c>
       <c r="G1135" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33541,7 +33544,7 @@
         <v>28</v>
       </c>
       <c r="G1136" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33567,7 +33570,7 @@
         <v>28</v>
       </c>
       <c r="G1137" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33593,7 +33596,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33619,7 +33622,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1139" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33645,7 +33648,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1140" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33671,7 +33674,7 @@
         <v>29</v>
       </c>
       <c r="G1141" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33697,7 +33700,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33723,7 +33726,7 @@
         <v>29.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33749,7 +33752,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1144" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33775,7 +33778,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1145" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33801,7 +33804,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1146" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33827,7 +33830,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1147" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33853,7 +33856,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1148" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33879,7 +33882,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1149" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33905,7 +33908,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1150" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33931,7 +33934,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1151" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33957,7 +33960,7 @@
         <v>32</v>
       </c>
       <c r="G1152" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33983,7 +33986,7 @@
         <v>31.75</v>
       </c>
       <c r="G1153" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -34009,7 +34012,7 @@
         <v>31.5</v>
       </c>
       <c r="G1154" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -34035,7 +34038,7 @@
         <v>32.5</v>
       </c>
       <c r="G1155" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34061,7 +34064,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1156" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34087,7 +34090,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1157" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34113,7 +34116,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1158" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34139,7 +34142,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1159" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34165,7 +34168,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G1160" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34191,7 +34194,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1161" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34217,7 +34220,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G1162" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34243,7 +34246,7 @@
         <v>29.25</v>
       </c>
       <c r="G1163" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34269,7 +34272,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1164" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34295,7 +34298,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G1165" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34321,7 +34324,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34347,7 +34350,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G1167" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34373,7 +34376,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34399,7 +34402,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1169" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34425,7 +34428,7 @@
         <v>29.75</v>
       </c>
       <c r="G1170" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34451,7 +34454,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1171" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34477,7 +34480,7 @@
         <v>30.5</v>
       </c>
       <c r="G1172" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34503,7 +34506,7 @@
         <v>30.5</v>
       </c>
       <c r="G1173" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34529,7 +34532,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1174" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34555,7 +34558,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34581,7 +34584,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34607,7 +34610,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1177" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34633,7 +34636,7 @@
         <v>30.5</v>
       </c>
       <c r="G1178" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34659,7 +34662,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1179" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34685,7 +34688,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1180" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34711,7 +34714,7 @@
         <v>30.5</v>
       </c>
       <c r="G1181" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34737,7 +34740,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1182" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34763,7 +34766,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1183" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34789,7 +34792,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1184" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34815,7 +34818,7 @@
         <v>30.5</v>
       </c>
       <c r="G1185" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34841,7 +34844,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34867,7 +34870,7 @@
         <v>30</v>
       </c>
       <c r="G1187" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34893,7 +34896,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1188" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34919,7 +34922,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1189" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34945,7 +34948,7 @@
         <v>30</v>
       </c>
       <c r="G1190" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34971,7 +34974,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1191" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34997,7 +35000,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1192" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -35023,7 +35026,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1193" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -35049,7 +35052,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1194" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -35075,7 +35078,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1195" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35101,7 +35104,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1196" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35127,7 +35130,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1197" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35153,7 +35156,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35179,7 +35182,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35205,7 +35208,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1200" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35231,7 +35234,7 @@
         <v>28.5</v>
       </c>
       <c r="G1201" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35257,7 +35260,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1202" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35283,7 +35286,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1203" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35309,7 +35312,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1204" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35335,7 +35338,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1205" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35361,7 +35364,7 @@
         <v>28.75</v>
       </c>
       <c r="G1206" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35387,7 +35390,7 @@
         <v>29.5</v>
       </c>
       <c r="G1207" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35413,7 +35416,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1208" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35439,7 +35442,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1209" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35465,7 +35468,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1210" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35491,7 +35494,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1211" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35517,7 +35520,7 @@
         <v>29</v>
       </c>
       <c r="G1212" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35543,7 +35546,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35569,7 +35572,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1214" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35595,7 +35598,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1215" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35621,7 +35624,7 @@
         <v>29</v>
       </c>
       <c r="G1216" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35647,7 +35650,7 @@
         <v>29</v>
       </c>
       <c r="G1217" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35673,7 +35676,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1218" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35699,7 +35702,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1219" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35725,7 +35728,7 @@
         <v>29</v>
       </c>
       <c r="G1220" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35751,7 +35754,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1221" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35777,7 +35780,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35803,7 +35806,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1223" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35829,7 +35832,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35855,7 +35858,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1225" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35881,7 +35884,7 @@
         <v>28</v>
       </c>
       <c r="G1226" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35907,7 +35910,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1227" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35933,7 +35936,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1228" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35959,7 +35962,7 @@
         <v>27.75</v>
       </c>
       <c r="G1229" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35985,7 +35988,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -36011,7 +36014,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -36037,7 +36040,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -36063,7 +36066,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1233" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -36089,7 +36092,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1234" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36115,7 +36118,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1235" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36141,7 +36144,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1236" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36167,7 +36170,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1237" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36193,7 +36196,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1238" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36219,7 +36222,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36245,7 +36248,7 @@
         <v>27.75</v>
       </c>
       <c r="G1240" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36271,7 +36274,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G1241" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36297,7 +36300,7 @@
         <v>27.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36323,7 +36326,7 @@
         <v>28</v>
       </c>
       <c r="G1243" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36349,7 +36352,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1244" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36375,7 +36378,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36401,7 +36404,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1246" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36427,7 +36430,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1247" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36453,7 +36456,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1248" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36479,7 +36482,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1249" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36505,7 +36508,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36531,7 +36534,7 @@
         <v>28.75</v>
       </c>
       <c r="G1251" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36557,7 +36560,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1252" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36583,7 +36586,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36609,7 +36612,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1254" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36635,7 +36638,7 @@
         <v>28.25</v>
       </c>
       <c r="G1255" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36661,7 +36664,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G1256" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36687,7 +36690,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36713,7 +36716,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1258" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36739,7 +36742,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1259" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36765,7 +36768,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1260" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36791,7 +36794,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1261" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36817,7 +36820,7 @@
         <v>29.25</v>
       </c>
       <c r="G1262" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36843,7 +36846,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1263" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36869,7 +36872,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1264" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36895,7 +36898,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1265" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36921,7 +36924,7 @@
         <v>30</v>
       </c>
       <c r="G1266" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36947,7 +36950,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1267" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36973,7 +36976,7 @@
         <v>29.25</v>
       </c>
       <c r="G1268" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36999,7 +37002,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -37025,7 +37028,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1270" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -37051,7 +37054,7 @@
         <v>29.5</v>
       </c>
       <c r="G1271" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -37077,7 +37080,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1272" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37103,7 +37106,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1273" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37129,7 +37132,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1274" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37155,7 +37158,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37181,7 +37184,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1276" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37207,7 +37210,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1277" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37233,7 +37236,7 @@
         <v>29.25</v>
       </c>
       <c r="G1278" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37259,7 +37262,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37285,7 +37288,7 @@
         <v>28.75</v>
       </c>
       <c r="G1280" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37311,7 +37314,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1281" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37337,7 +37340,7 @@
         <v>29.25</v>
       </c>
       <c r="G1282" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37363,7 +37366,7 @@
         <v>29.25</v>
       </c>
       <c r="G1283" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37389,7 +37392,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1284" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37415,7 +37418,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1285" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37441,7 +37444,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1286" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37467,7 +37470,7 @@
         <v>27.75</v>
       </c>
       <c r="G1287" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37493,7 +37496,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1288" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37519,7 +37522,7 @@
         <v>27.25</v>
       </c>
       <c r="G1289" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37545,7 +37548,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1290" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37571,7 +37574,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1291" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37597,7 +37600,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1292" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37623,7 +37626,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1293" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37649,7 +37652,7 @@
         <v>28.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37675,7 +37678,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G1295" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37701,7 +37704,7 @@
         <v>28.75</v>
       </c>
       <c r="G1296" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37727,7 +37730,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37753,7 +37756,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1298" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37779,7 +37782,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1299" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37805,7 +37808,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1300" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37831,7 +37834,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1301" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37857,7 +37860,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1302" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37883,7 +37886,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1303" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37909,7 +37912,7 @@
         <v>27</v>
       </c>
       <c r="G1304" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37935,7 +37938,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1305" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37961,7 +37964,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1306" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37987,7 +37990,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1307" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -38013,7 +38016,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1308" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -38039,7 +38042,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -38065,7 +38068,7 @@
         <v>26.5</v>
       </c>
       <c r="G1310" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -38091,7 +38094,7 @@
         <v>27.25</v>
       </c>
       <c r="G1311" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38117,7 +38120,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1312" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38143,7 +38146,7 @@
         <v>27.25</v>
       </c>
       <c r="G1313" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38169,7 +38172,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1314" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38195,7 +38198,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38221,7 +38224,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38247,7 +38250,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1317" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38273,7 +38276,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1318" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38299,7 +38302,7 @@
         <v>29.75</v>
       </c>
       <c r="G1319" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38325,7 +38328,7 @@
         <v>29.5</v>
       </c>
       <c r="G1320" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38351,7 +38354,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38377,7 +38380,7 @@
         <v>29.5</v>
       </c>
       <c r="G1322" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38403,7 +38406,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38429,7 +38432,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38455,7 +38458,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38481,7 +38484,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1326" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38507,7 +38510,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1327" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38533,7 +38536,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1328" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38559,7 +38562,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1329" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38585,7 +38588,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1330" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38611,7 +38614,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1331" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38637,7 +38640,7 @@
         <v>29</v>
       </c>
       <c r="G1332" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38663,7 +38666,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1333" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38689,7 +38692,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1334" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38715,7 +38718,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1335" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38741,7 +38744,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1336" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38767,7 +38770,7 @@
         <v>29</v>
       </c>
       <c r="G1337" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38793,7 +38796,7 @@
         <v>29.25</v>
       </c>
       <c r="G1338" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38819,7 +38822,7 @@
         <v>29</v>
       </c>
       <c r="G1339" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38845,7 +38848,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1340" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38871,7 +38874,7 @@
         <v>29</v>
       </c>
       <c r="G1341" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38897,7 +38900,7 @@
         <v>29</v>
       </c>
       <c r="G1342" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38923,7 +38926,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38949,7 +38952,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1344" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38975,7 +38978,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1345" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -39001,7 +39004,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -39027,7 +39030,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -39053,7 +39056,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1348" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39079,7 +39082,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1349" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39105,7 +39108,7 @@
         <v>28.75</v>
       </c>
       <c r="G1350" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39131,7 +39134,7 @@
         <v>29</v>
       </c>
       <c r="G1351" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39157,7 +39160,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1352" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39183,7 +39186,7 @@
         <v>29.5</v>
       </c>
       <c r="G1353" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39209,7 +39212,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1354" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39235,7 +39238,7 @@
         <v>28.75</v>
       </c>
       <c r="G1355" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39261,7 +39264,7 @@
         <v>28.75</v>
       </c>
       <c r="G1356" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39287,7 +39290,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1357" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39313,7 +39316,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39339,7 +39342,7 @@
         <v>28.75</v>
       </c>
       <c r="G1359" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39365,7 +39368,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39391,7 +39394,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1361" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39417,7 +39420,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1362" t="s">
-        <v>719</v>
+        <v>750</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39443,7 +39446,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1363" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39521,7 +39524,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1366" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -39573,7 +39576,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -39677,7 +39680,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1372" t="s">
-        <v>719</v>
+        <v>750</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -44825,7 +44828,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1570" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44851,7 +44854,7 @@
         <v>28.75</v>
       </c>
       <c r="G1571" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44981,7 +44984,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1576" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45423,7 +45426,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1593" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45475,7 +45478,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1595" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45605,7 +45608,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1600" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45631,7 +45634,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1601" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45969,7 +45972,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1614" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -68779,7 +68782,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6494212963</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>18334</v>
@@ -68800,6 +68803,32 @@
         <v>1220</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6493981481</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>13027</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>33.0999984741211</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>32.5999984741211</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>32.7000007629395</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>32.7000007629395</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="1222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="1223">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577478408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.957332611084</t>
+    <t xml:space="preserve">14.0577449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9573316574097</t>
   </si>
   <si>
     <t xml:space="preserve">13.3883275985718</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">12.8896141052246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8527946472168</t>
+    <t xml:space="preserve">12.8527975082397</t>
   </si>
   <si>
     <t xml:space="preserve">12.9532079696655</t>
@@ -65,49 +65,49 @@
     <t xml:space="preserve">12.6184997558594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4846162796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3842029571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8821430206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7348709106445</t>
+    <t xml:space="preserve">12.4846172332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3842039108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8821420669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7348699569702</t>
   </si>
   <si>
     <t xml:space="preserve">11.2127265930176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7307453155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2294597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2194194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2461967468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.914834022522</t>
+    <t xml:space="preserve">10.7307462692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2294607162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2194185256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2461957931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9148349761963</t>
   </si>
   <si>
     <t xml:space="preserve">11.1323947906494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6143770217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6813182830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5474338531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3466100692749</t>
+    <t xml:space="preserve">11.6143760681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6813173294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5474328994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3466091156006</t>
   </si>
   <si>
     <t xml:space="preserve">11.3131370544434</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">11.329873085022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8947525024414</t>
+    <t xml:space="preserve">10.8947515487671</t>
   </si>
   <si>
     <t xml:space="preserve">10.8780174255371</t>
@@ -128,34 +128,34 @@
     <t xml:space="preserve">10.4261608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4094266891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7080936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.714789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0494966506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7482576370239</t>
+    <t xml:space="preserve">10.4094257354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7080926895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7147874832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0494956970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7482585906982</t>
   </si>
   <si>
     <t xml:space="preserve">11.7449111938477</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2135028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.216851234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3674697875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7189111709595</t>
+    <t xml:space="preserve">12.2135038375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.367467880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7189140319824</t>
   </si>
   <si>
     <t xml:space="preserve">12.8293676376343</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">13.3849821090698</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0870885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536212921143</t>
+    <t xml:space="preserve">13.0870895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536222457886</t>
   </si>
   <si>
     <t xml:space="preserve">13.3347759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3146934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569677352905</t>
+    <t xml:space="preserve">13.3146924972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569686889648</t>
   </si>
   <si>
     <t xml:space="preserve">13.2109336853027</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8661842346191</t>
+    <t xml:space="preserve">12.8661813735962</t>
   </si>
   <si>
     <t xml:space="preserve">13.1306037902832</t>
@@ -197,25 +197,25 @@
     <t xml:space="preserve">13.2879152297974</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8260202407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9833307266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9030027389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2377109527588</t>
+    <t xml:space="preserve">12.8260192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9833316802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.903000831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2377099990845</t>
   </si>
   <si>
     <t xml:space="preserve">13.1674213409424</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1138696670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.097131729126</t>
+    <t xml:space="preserve">13.1138687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971326828003</t>
   </si>
   <si>
     <t xml:space="preserve">12.5046987533569</t>
@@ -227,73 +227,73 @@
     <t xml:space="preserve">12.886266708374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7055244445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7222595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9163904190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0301895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6318883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7021789550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.869532585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5582542419434</t>
+    <t xml:space="preserve">12.7055225372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7222585678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.916389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0301923751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6318893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7021770477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8695344924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5582523345947</t>
   </si>
   <si>
     <t xml:space="preserve">12.5682935714722</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8360595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494482040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958946228027</t>
+    <t xml:space="preserve">12.8360605239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958955764771</t>
   </si>
   <si>
     <t xml:space="preserve">12.5348234176636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7791604995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7691211700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.786563873291</t>
+    <t xml:space="preserve">12.7791585922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7691192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.786566734314</t>
   </si>
   <si>
     <t xml:space="preserve">12.5024194717407</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6512594223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7527379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5836057662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4990386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5700731277466</t>
+    <t xml:space="preserve">12.6512603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7527389526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5836048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4990367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5700740814209</t>
   </si>
   <si>
     <t xml:space="preserve">12.5159511566162</t>
@@ -302,46 +302,46 @@
     <t xml:space="preserve">12.2791624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0660533905029</t>
+    <t xml:space="preserve">12.0660524368286</t>
   </si>
   <si>
     <t xml:space="preserve">12.1776819229126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1641511917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.170916557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1100263595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1269407272339</t>
+    <t xml:space="preserve">12.1641502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1709146499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1100273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1269397735596</t>
   </si>
   <si>
     <t xml:space="preserve">11.9814863204956</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7459716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580219268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231391906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.697340965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7785243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2406778335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8212232589722</t>
+    <t xml:space="preserve">12.7459745407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580238342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231382369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6973400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.778525352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2406759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8212242126465</t>
   </si>
   <si>
     <t xml:space="preserve">10.6554708480835</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">11.5248222351074</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6656198501587</t>
+    <t xml:space="preserve">10.665620803833</t>
   </si>
   <si>
     <t xml:space="preserve">10.1886606216431</t>
@@ -368,25 +368,25 @@
     <t xml:space="preserve">10.5878171920776</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6825332641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8394136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0199728012085</t>
+    <t xml:space="preserve">10.6825323104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.839412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0199718475342</t>
   </si>
   <si>
     <t xml:space="preserve">13.3616228103638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0233564376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1924886703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4969320297241</t>
+    <t xml:space="preserve">13.0233554840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1924896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4969329833984</t>
   </si>
   <si>
     <t xml:space="preserve">13.4698696136475</t>
@@ -398,262 +398,262 @@
     <t xml:space="preserve">13.4800176620483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2939691543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548564910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0740976333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368871688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9489345550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827613830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.091010093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0707111358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9962921142578</t>
+    <t xml:space="preserve">13.2939701080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108806610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548574447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0740947723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368843078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9489336013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0910081863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0707120895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9962930679321</t>
   </si>
   <si>
     <t xml:space="preserve">12.8576021194458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1113042831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1248369216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1823425292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0605640411377</t>
+    <t xml:space="preserve">13.1113033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1248331069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1823406219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.060564994812</t>
   </si>
   <si>
     <t xml:space="preserve">13.1857233047485</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4123640060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5679683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4157466888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5138463973999</t>
+    <t xml:space="preserve">13.4123630523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.567967414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4157485961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.513843536377</t>
   </si>
   <si>
     <t xml:space="preserve">13.706657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8352012634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2106781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4576139450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7552919387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838319778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0157556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9853143692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6652374267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2897567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8297090530396</t>
+    <t xml:space="preserve">13.8351984024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2106771469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4576168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7552909851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838348388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0157604217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9853162765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303499221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6652345657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2897548675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8297100067139</t>
   </si>
   <si>
     <t xml:space="preserve">14.684253692627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7722043991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9514875411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7485256195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7180814743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8770685195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7992658615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751663208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9007425308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.201807975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939809799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988422393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9142770767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.927806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7383785247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7248449325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5421838760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4440851211548</t>
+    <t xml:space="preserve">14.7722053527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.951488494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7485246658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7180795669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.877067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7992639541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751653671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9007453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2018041610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939819335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330907821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988441467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9142780303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9278116226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.738377571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7248468399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5421829223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4440841674805</t>
   </si>
   <si>
     <t xml:space="preserve">15.0529680252075</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1443014144897</t>
+    <t xml:space="preserve">15.1442995071411</t>
   </si>
   <si>
     <t xml:space="preserve">15.1104745864868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9548683166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0901803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2187204360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7823514938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707239151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.616602897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764305114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1599397659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2546520233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0415439605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1125812530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.038161277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1430244445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903839111328</t>
+    <t xml:space="preserve">14.9548673629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0901775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2187194824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7823534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6166019439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764295578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1599378585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2546510696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.041543006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1125793457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0381593704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1430225372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903829574585</t>
   </si>
   <si>
     <t xml:space="preserve">14.3527507781982</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2072973251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3561334609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373168945312</t>
+    <t xml:space="preserve">14.2072954177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3561344146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373188018799</t>
   </si>
   <si>
     <t xml:space="preserve">14.3730478286743</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3087778091431</t>
+    <t xml:space="preserve">14.3087739944458</t>
   </si>
   <si>
     <t xml:space="preserve">14.2411212921143</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3392181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2512693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464071273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058168411255</t>
+    <t xml:space="preserve">14.3392210006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2512731552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1464061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058139801025</t>
   </si>
   <si>
     <t xml:space="preserve">14.119345664978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2275943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2715635299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1497917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0753707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0719900131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749509811401</t>
+    <t xml:space="preserve">14.2275905609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2715663909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.149790763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0753698348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0719881057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749500274658</t>
   </si>
   <si>
     <t xml:space="preserve">14.1667032241821</t>
@@ -665,139 +665,139 @@
     <t xml:space="preserve">14.6267490386963</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7519092559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8161783218384</t>
+    <t xml:space="preserve">14.7519083023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8161792755127</t>
   </si>
   <si>
     <t xml:space="preserve">15.1037082672119</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0834131240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882762908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172399520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1544466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758014678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3574085235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3912382125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893360137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1713609695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1003255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946180343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3168182373047</t>
+    <t xml:space="preserve">15.0834121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172370910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.154447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758043289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3912353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1713619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1003246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946199417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3168172836304</t>
   </si>
   <si>
     <t xml:space="preserve">15.3134355545044</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4182996749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4250631332397</t>
+    <t xml:space="preserve">15.4183006286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4250602722168</t>
   </si>
   <si>
     <t xml:space="preserve">15.5366926193237</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6753835678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6449375152588</t>
+    <t xml:space="preserve">15.6753807067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6449394226074</t>
   </si>
   <si>
     <t xml:space="preserve">15.7295055389404</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6618537902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6517038345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6821479797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637521743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081506729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415567398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7024440765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584711074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5874357223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.655086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227392196655</t>
+    <t xml:space="preserve">15.6618509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.651704788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6821489334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637531280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081516265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415596008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7024421691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333089828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584692001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588899612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5874328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6550874710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227420806885</t>
   </si>
   <si>
     <t xml:space="preserve">16.3350086212158</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0339469909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.406042098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4026622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4195766448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6935729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.099494934082</t>
+    <t xml:space="preserve">16.0339488983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4060440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4026641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4195728302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6935691833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0994930267334</t>
   </si>
   <si>
     <t xml:space="preserve">16.9980144500732</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1671466827393</t>
+    <t xml:space="preserve">17.1671524047852</t>
   </si>
   <si>
     <t xml:space="preserve">17.4208507537842</t>
@@ -815,28 +815,28 @@
     <t xml:space="preserve">17.48850440979</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3531951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3870258331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5223293304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4546756744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.877513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8098621368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7083759307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7591190338135</t>
+    <t xml:space="preserve">17.3531970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3870239257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.522331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4546794891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8775119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8098602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7083797454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7591209411621</t>
   </si>
   <si>
     <t xml:space="preserve">17.6745529174805</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">17.2009735107422</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2348022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2517185211182</t>
+    <t xml:space="preserve">17.2348041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2517166137695</t>
   </si>
   <si>
     <t xml:space="preserve">17.2178916931152</t>
@@ -863,28 +863,28 @@
     <t xml:space="preserve">17.3701095581055</t>
   </si>
   <si>
-    <t xml:space="preserve">17.456018447876</t>
+    <t xml:space="preserve">17.4560203552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.7147541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5767631530762</t>
+    <t xml:space="preserve">17.5767650604248</t>
   </si>
   <si>
     <t xml:space="preserve">17.5595149993896</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6975040435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.469820022583</t>
+    <t xml:space="preserve">17.6975059509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4698181152344</t>
   </si>
   <si>
     <t xml:space="preserve">17.6147117614746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7729568481445</t>
+    <t xml:space="preserve">16.7729587554932</t>
   </si>
   <si>
     <t xml:space="preserve">17.0075454711914</t>
@@ -893,16 +893,16 @@
     <t xml:space="preserve">17.1662349700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1317386627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9937438964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9868469238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9661483764648</t>
+    <t xml:space="preserve">17.1317367553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.993745803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9868450164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9661464691162</t>
   </si>
   <si>
     <t xml:space="preserve">16.835054397583</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">16.7591590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8695526123047</t>
+    <t xml:space="preserve">16.8695545196533</t>
   </si>
   <si>
     <t xml:space="preserve">16.9178504943848</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">16.9730472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9385471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.152437210083</t>
+    <t xml:space="preserve">16.938549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1524353027344</t>
   </si>
   <si>
     <t xml:space="preserve">16.6625652313232</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">16.5935688018799</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5659713745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5038738250732</t>
+    <t xml:space="preserve">16.5659694671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5038719177246</t>
   </si>
   <si>
     <t xml:space="preserve">16.8626537322998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9040489196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8005561828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8971519470215</t>
+    <t xml:space="preserve">16.9040508270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.80055809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8971500396729</t>
   </si>
   <si>
     <t xml:space="preserve">16.5383720397949</t>
@@ -962,43 +962,43 @@
     <t xml:space="preserve">16.5590705871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4900722503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2416877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3037853240967</t>
+    <t xml:space="preserve">16.4900741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2416896820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3037815093994</t>
   </si>
   <si>
     <t xml:space="preserve">16.2485866546631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1243953704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1864910125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1588954925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5314712524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2899856567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3175849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5452728271484</t>
+    <t xml:space="preserve">16.124397277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.186487197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1588935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.53147315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2899875640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3175830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5452709197998</t>
   </si>
   <si>
     <t xml:space="preserve">16.3658809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4624729156494</t>
+    <t xml:space="preserve">16.4624767303467</t>
   </si>
   <si>
     <t xml:space="preserve">16.3313846588135</t>
@@ -1007,25 +1007,25 @@
     <t xml:space="preserve">16.3520812988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6970634460449</t>
+    <t xml:space="preserve">16.6970653533936</t>
   </si>
   <si>
     <t xml:space="preserve">16.3865776062012</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4486751556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5107727050781</t>
+    <t xml:space="preserve">16.4486789703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5107746124268</t>
   </si>
   <si>
     <t xml:space="preserve">16.4210758209229</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4348754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3934803009033</t>
+    <t xml:space="preserve">16.4348773956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3934783935547</t>
   </si>
   <si>
     <t xml:space="preserve">16.4969730377197</t>
@@ -1037,19 +1037,19 @@
     <t xml:space="preserve">16.4003791809082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4555740356445</t>
+    <t xml:space="preserve">16.4555759429932</t>
   </si>
   <si>
     <t xml:space="preserve">16.358980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2830848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5521717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1795921325684</t>
+    <t xml:space="preserve">16.2830867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5521697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.179594039917</t>
   </si>
   <si>
     <t xml:space="preserve">16.2071914672852</t>
@@ -1064,25 +1064,25 @@
     <t xml:space="preserve">15.9036054611206</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5586261749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4965314865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9381055831909</t>
+    <t xml:space="preserve">15.5586223602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4965305328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9381046295166</t>
   </si>
   <si>
     <t xml:space="preserve">15.7794151306152</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7656116485596</t>
+    <t xml:space="preserve">15.7656164169312</t>
   </si>
   <si>
     <t xml:space="preserve">15.7863140106201</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9795036315918</t>
+    <t xml:space="preserve">15.9795017242432</t>
   </si>
   <si>
     <t xml:space="preserve">15.931206703186</t>
@@ -1091,70 +1091,70 @@
     <t xml:space="preserve">15.7035188674927</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6483221054077</t>
+    <t xml:space="preserve">15.6483211517334</t>
   </si>
   <si>
     <t xml:space="preserve">15.8415098190308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7518177032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691091537476</t>
+    <t xml:space="preserve">15.7518167495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691120147705</t>
   </si>
   <si>
     <t xml:space="preserve">15.862208366394</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0277996063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.896710395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6276216506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7173185348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310287475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034303665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413347244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.248143196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3171405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3309364318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2826414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792381286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619428634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6000232696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896326065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.951904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9726028442383</t>
+    <t xml:space="preserve">16.0277976989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.89670753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6276206970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7173175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310297012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034275054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.441333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2481451034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3171415328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3309392929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2826433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792352676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.261944770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6000270843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896278381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9519071578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.972601890564</t>
   </si>
   <si>
     <t xml:space="preserve">15.9864025115967</t>
@@ -1166,61 +1166,61 @@
     <t xml:space="preserve">15.8553094863892</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7932109832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758329391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2895421981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1791458129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2067461013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3999347686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2343454360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3033390045166</t>
+    <t xml:space="preserve">15.7932119369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2895412445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1791486740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2067470550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3999338150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2343435287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033418655396</t>
   </si>
   <si>
     <t xml:space="preserve">15.4137344360352</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3861351013184</t>
+    <t xml:space="preserve">15.3861360549927</t>
   </si>
   <si>
     <t xml:space="preserve">15.6345224380493</t>
   </si>
   <si>
-    <t xml:space="preserve">16.145092010498</t>
+    <t xml:space="preserve">16.1450939178467</t>
   </si>
   <si>
     <t xml:space="preserve">16.4831733703613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6073684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3727779388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6349697113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.414176940918</t>
+    <t xml:space="preserve">16.6073665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3727798461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6349658966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141788482666</t>
   </si>
   <si>
     <t xml:space="preserve">16.0898971557617</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2002906799316</t>
+    <t xml:space="preserve">16.2002925872803</t>
   </si>
   <si>
     <t xml:space="preserve">16.731559753418</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">16.7522583007812</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6487636566162</t>
+    <t xml:space="preserve">16.6487655639648</t>
   </si>
   <si>
     <t xml:space="preserve">16.6280689239502</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">17.1110382080078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2145347595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1455364227295</t>
+    <t xml:space="preserve">17.2145328521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1455383300781</t>
   </si>
   <si>
     <t xml:space="preserve">17.1800346374512</t>
@@ -1265,70 +1265,70 @@
     <t xml:space="preserve">16.2140884399414</t>
   </si>
   <si>
-    <t xml:space="preserve">16.110595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5931224822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621198654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0066576004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7306747436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9031639099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9721603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551305770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1101512908936</t>
+    <t xml:space="preserve">16.1105976104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5931215286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0066585540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7306728363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9031648635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9721612930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.455132484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1101503372192</t>
   </si>
   <si>
     <t xml:space="preserve">15.0411558151245</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0756521224976</t>
+    <t xml:space="preserve">15.0756530761719</t>
   </si>
   <si>
     <t xml:space="preserve">15.3516387939453</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4206342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5241279602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6966199874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8742485046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5560550689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7328290939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914087295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3439283370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792819976807</t>
+    <t xml:space="preserve">15.42063331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5241270065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6966190338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8742456436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5560579299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7328300476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914106369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3439292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792839050293</t>
   </si>
   <si>
     <t xml:space="preserve">14.7782535552979</t>
@@ -1337,46 +1337,46 @@
     <t xml:space="preserve">14.4247074127197</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5307703018188</t>
+    <t xml:space="preserve">14.5307722091675</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600610733032</t>
   </si>
   <si>
-    <t xml:space="preserve">14.495415687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8873167037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1135845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3186435699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6014795303345</t>
+    <t xml:space="preserve">14.4954166412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8873138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1135854721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3186416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6014804840088</t>
   </si>
   <si>
     <t xml:space="preserve">15.0257358551025</t>
   </si>
   <si>
-    <t xml:space="preserve">15.061089515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9550256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8489608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.884316444397</t>
+    <t xml:space="preserve">15.0610904693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9550266265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8489618301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8843173980713</t>
   </si>
   <si>
     <t xml:space="preserve">14.7075443267822</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1671562194824</t>
+    <t xml:space="preserve">15.1671543121338</t>
   </si>
   <si>
     <t xml:space="preserve">15.2025098800659</t>
@@ -1385,91 +1385,91 @@
     <t xml:space="preserve">14.5661239624023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.636833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2832899093628</t>
+    <t xml:space="preserve">14.6368322372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2832880020142</t>
   </si>
   <si>
     <t xml:space="preserve">14.0853033065796</t>
   </si>
   <si>
-    <t xml:space="preserve">14.81360912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3539972305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3893527984619</t>
+    <t xml:space="preserve">14.8136081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3539953231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3893518447876</t>
   </si>
   <si>
     <t xml:space="preserve">14.7428979873657</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1418704986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1772222518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.247932434082</t>
+    <t xml:space="preserve">14.1418676376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1772232055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2479314804077</t>
   </si>
   <si>
     <t xml:space="preserve">14.2125787734985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0711584091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9438810348511</t>
+    <t xml:space="preserve">14.0711603164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.943883895874</t>
   </si>
   <si>
     <t xml:space="preserve">13.8731746673584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8166055679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8590326309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0145950317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9297428131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0004501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0994434356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.97216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0287342071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.057017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1277265548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9196720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6721887588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4347772598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5054864883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4913425445557</t>
+    <t xml:space="preserve">13.8166074752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8590307235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0145931243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.929741859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0004510879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0994443893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9721660614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0287351608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570154190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1277275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9196729660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6721878051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5054845809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.49134349823</t>
   </si>
   <si>
     <t xml:space="preserve">13.3782072067261</t>
@@ -1478,121 +1478,121 @@
     <t xml:space="preserve">13.4630603790283</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5620517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5337677001953</t>
+    <t xml:space="preserve">13.5620527267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5337686538696</t>
   </si>
   <si>
     <t xml:space="preserve">13.1660814285278</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7842502593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6852569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1620073318481</t>
+    <t xml:space="preserve">12.7842493057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6852560043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1620082855225</t>
   </si>
   <si>
     <t xml:space="preserve">12.6569728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4064903259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5479106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7883205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7741804122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5903358459473</t>
+    <t xml:space="preserve">13.4064912796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5479097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7883224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7741794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5903339385986</t>
   </si>
   <si>
     <t xml:space="preserve">13.448917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3075008392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.392352104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0105199813843</t>
+    <t xml:space="preserve">13.3074989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3923501968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.01051902771</t>
   </si>
   <si>
     <t xml:space="preserve">13.1519374847412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2933568954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9256706237793</t>
+    <t xml:space="preserve">13.2933559417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9256687164307</t>
   </si>
   <si>
     <t xml:space="preserve">13.0388031005859</t>
   </si>
   <si>
-    <t xml:space="preserve">12.996376991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2367897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0953722000122</t>
+    <t xml:space="preserve">12.9963779449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2367877960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0953712463379</t>
   </si>
   <si>
     <t xml:space="preserve">13.6469030380249</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6751871109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0670871734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2509288787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2085056304932</t>
+    <t xml:space="preserve">13.6751861572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0670862197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2509307861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2085046768188</t>
   </si>
   <si>
     <t xml:space="preserve">13.0812292098999</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3499231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8408164978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5296955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.897385597229</t>
+    <t xml:space="preserve">13.3499240875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8408174514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5296964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8973836898804</t>
   </si>
   <si>
     <t xml:space="preserve">12.6004037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7317552566528</t>
+    <t xml:space="preserve">13.7317543029785</t>
   </si>
   <si>
     <t xml:space="preserve">13.5761957168579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5196266174316</t>
+    <t xml:space="preserve">13.5196285247803</t>
   </si>
   <si>
     <t xml:space="preserve">13.7176113128662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8307466506958</t>
+    <t xml:space="preserve">13.8307485580444</t>
   </si>
   <si>
     <t xml:space="preserve">13.7600383758545</t>
@@ -1604,49 +1604,49 @@
     <t xml:space="preserve">13.7458982467651</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0428771972656</t>
+    <t xml:space="preserve">14.0428781509399</t>
   </si>
   <si>
     <t xml:space="preserve">13.8448905944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.54176902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2218475341797</t>
+    <t xml:space="preserve">14.541766166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.221848487854</t>
   </si>
   <si>
     <t xml:space="preserve">13.9455537796021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1782217025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9891796112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2073059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4399766921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.265474319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4108943939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4981422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3381805419922</t>
+    <t xml:space="preserve">14.1782245635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9891805648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2073078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4399757385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2654752731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4108915328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.498143196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690580368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3381824493408</t>
   </si>
   <si>
     <t xml:space="preserve">14.5126838684082</t>
@@ -1655,49 +1655,49 @@
     <t xml:space="preserve">14.3963489532471</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6871871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4254322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4836015701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6144762039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8326044082642</t>
+    <t xml:space="preserve">14.6871852874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4254341125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4836006164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6144781112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8326053619385</t>
   </si>
   <si>
     <t xml:space="preserve">14.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">15.123438835144</t>
+    <t xml:space="preserve">15.1234378814697</t>
   </si>
   <si>
     <t xml:space="preserve">15.1961469650269</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4142751693726</t>
+    <t xml:space="preserve">15.4142732620239</t>
   </si>
   <si>
     <t xml:space="preserve">15.4506282806396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3415641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2325019836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3052091598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2688541412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687536239624</t>
+    <t xml:space="preserve">15.3415670394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2325010299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3052101135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2688550949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687545776367</t>
   </si>
   <si>
     <t xml:space="preserve">15.0507278442383</t>
@@ -1709,22 +1709,22 @@
     <t xml:space="preserve">14.9416666030884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7235403060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0143747329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5781202316284</t>
+    <t xml:space="preserve">14.723539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0143756866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5781221389771</t>
   </si>
   <si>
     <t xml:space="preserve">14.7598934173584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6508302688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3672676086426</t>
+    <t xml:space="preserve">14.6508293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3672657012939</t>
   </si>
   <si>
     <t xml:space="preserve">14.3236417770386</t>
@@ -1733,10 +1733,10 @@
     <t xml:space="preserve">14.5272254943848</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4545154571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7962493896484</t>
+    <t xml:space="preserve">14.454514503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7962484359741</t>
   </si>
   <si>
     <t xml:space="preserve">14.9053106307983</t>
@@ -1745,13 +1745,13 @@
     <t xml:space="preserve">16.0322971343994</t>
   </si>
   <si>
-    <t xml:space="preserve">16.359489440918</t>
+    <t xml:space="preserve">16.3594875335693</t>
   </si>
   <si>
     <t xml:space="preserve">16.5049076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6139678955078</t>
+    <t xml:space="preserve">16.6139698028564</t>
   </si>
   <si>
     <t xml:space="preserve">16.5412616729736</t>
@@ -1760,52 +1760,52 @@
     <t xml:space="preserve">16.8320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6503238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.577615737915</t>
+    <t xml:space="preserve">16.6503200531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5776138305664</t>
   </si>
   <si>
     <t xml:space="preserve">16.8684501647949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7593860626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0502223968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0865783691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4864730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4137668609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2683506011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5228290557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.813663482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7409553527832</t>
+    <t xml:space="preserve">16.7593841552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0502243041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.086576461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4864768981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4137649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.268346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5228309631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8136653900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7409572601318</t>
   </si>
   <si>
     <t xml:space="preserve">17.6318912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7046012878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6682472229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0681476593018</t>
+    <t xml:space="preserve">17.7046031951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6682453155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0681438446045</t>
   </si>
   <si>
     <t xml:space="preserve">17.9227275848389</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">18.1044998168945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8500194549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9590854644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.177209854126</t>
+    <t xml:space="preserve">17.8500175476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9590835571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1772079467773</t>
   </si>
   <si>
     <t xml:space="preserve">18.0317916870117</t>
@@ -1829,85 +1829,85 @@
     <t xml:space="preserve">18.2862720489502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3589820861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4680461883545</t>
+    <t xml:space="preserve">18.358980178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4680423736572</t>
   </si>
   <si>
     <t xml:space="preserve">18.5771064758301</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9954357147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5591831207275</t>
+    <t xml:space="preserve">17.9954376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5591850280762</t>
   </si>
   <si>
     <t xml:space="preserve">17.5955390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4501209259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2499198913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3953342437744</t>
+    <t xml:space="preserve">17.4501190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2499179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.395336151123</t>
   </si>
   <si>
     <t xml:space="preserve">18.2135639190674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3226261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6134624481201</t>
+    <t xml:space="preserve">18.3226280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6134605407715</t>
   </si>
   <si>
     <t xml:space="preserve">18.6861705780029</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8315887451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1951332092285</t>
+    <t xml:space="preserve">18.8315868377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1951351165771</t>
   </si>
   <si>
     <t xml:space="preserve">18.9770069122314</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0860710144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2678394317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1224250793457</t>
+    <t xml:space="preserve">19.0860691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.26784324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1224231719971</t>
   </si>
   <si>
     <t xml:space="preserve">19.3041973114014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4132614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4496116638184</t>
+    <t xml:space="preserve">19.4132595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.449613571167</t>
   </si>
   <si>
     <t xml:space="preserve">16.9048042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7230319976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321975708008</t>
+    <t xml:space="preserve">16.7230358123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321956634521</t>
   </si>
   <si>
     <t xml:space="preserve">16.7957420349121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2314891815186</t>
+    <t xml:space="preserve">19.2314872741699</t>
   </si>
   <si>
     <t xml:space="preserve">16.9775142669678</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">18.7952346801758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5407543182373</t>
+    <t xml:space="preserve">18.5407562255859</t>
   </si>
   <si>
     <t xml:space="preserve">18.8679428100586</t>
@@ -1931,31 +1931,34 @@
     <t xml:space="preserve">18.9042987823486</t>
   </si>
   <si>
+    <t xml:space="preserve">19.8495101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.42138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7327499389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3944034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8105926513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3554801940918</t>
+  </si>
+  <si>
     <t xml:space="preserve">19.8495121002197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4213848114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7327499389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.394401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8105907440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549110412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3554801940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1219577789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9273548126221</t>
+    <t xml:space="preserve">20.121955871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9273529052734</t>
   </si>
   <si>
     <t xml:space="preserve">19.4603061676025</t>
@@ -1967,7 +1970,7 @@
     <t xml:space="preserve">19.3046245574951</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9662742614746</t>
+    <t xml:space="preserve">19.966272354126</t>
   </si>
   <si>
     <t xml:space="preserve">19.2657051086426</t>
@@ -1985,10 +1988,10 @@
     <t xml:space="preserve">20.044116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.172815322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0560512542725</t>
+    <t xml:space="preserve">21.1728134155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0560493469238</t>
   </si>
   <si>
     <t xml:space="preserve">20.9392890930176</t>
@@ -2000,52 +2003,52 @@
     <t xml:space="preserve">21.0171318054199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7836074829102</t>
+    <t xml:space="preserve">20.7836093902588</t>
   </si>
   <si>
     <t xml:space="preserve">20.7057666778564</t>
   </si>
   <si>
-    <t xml:space="preserve">21.094970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.445255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7566223144531</t>
+    <t xml:space="preserve">21.0949726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4452571868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7566242218018</t>
   </si>
   <si>
     <t xml:space="preserve">21.9512252807617</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6009407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7955417633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0290679931641</t>
+    <t xml:space="preserve">21.6009387969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7955436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0290660858154</t>
   </si>
   <si>
     <t xml:space="preserve">22.0679893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5350341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5739555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.651798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7685585021973</t>
+    <t xml:space="preserve">22.5350360870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.57395362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6517963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7685604095459</t>
   </si>
   <si>
     <t xml:space="preserve">22.8074779510498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7296409606934</t>
+    <t xml:space="preserve">22.7296371459961</t>
   </si>
   <si>
     <t xml:space="preserve">22.3404312133789</t>
@@ -2054,10 +2057,10 @@
     <t xml:space="preserve">22.2625923156738</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5080509185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.97509765625</t>
+    <t xml:space="preserve">23.5080528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9750938415527</t>
   </si>
   <si>
     <t xml:space="preserve">24.4032230377197</t>
@@ -2069,7 +2072,7 @@
     <t xml:space="preserve">24.7145900726318</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5199851989746</t>
+    <t xml:space="preserve">24.5199871063232</t>
   </si>
   <si>
     <t xml:space="preserve">25.2983989715576</t>
@@ -2078,10 +2081,10 @@
     <t xml:space="preserve">24.7924327850342</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1427154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7535076141357</t>
+    <t xml:space="preserve">25.1427173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7535095214844</t>
   </si>
   <si>
     <t xml:space="preserve">24.6367492675781</t>
@@ -2093,10 +2096,10 @@
     <t xml:space="preserve">24.0140190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0799217224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7026519775391</t>
+    <t xml:space="preserve">23.0799236297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7026538848877</t>
   </si>
   <si>
     <t xml:space="preserve">24.0529384613037</t>
@@ -2105,10 +2108,10 @@
     <t xml:space="preserve">23.4691295623779</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5858917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1577644348145</t>
+    <t xml:space="preserve">23.5858898162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1577663421631</t>
   </si>
   <si>
     <t xml:space="preserve">23.8583335876465</t>
@@ -2117,7 +2120,7 @@
     <t xml:space="preserve">23.7415733337402</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8194141387939</t>
+    <t xml:space="preserve">23.8194160461426</t>
   </si>
   <si>
     <t xml:space="preserve">23.6637325286865</t>
@@ -2126,7 +2129,7 @@
     <t xml:space="preserve">23.4302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0918598175049</t>
+    <t xml:space="preserve">24.0918579101562</t>
   </si>
   <si>
     <t xml:space="preserve">23.3912887573242</t>
@@ -2141,7 +2144,7 @@
     <t xml:space="preserve">23.0020809173584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1188430786133</t>
+    <t xml:space="preserve">23.1188449859619</t>
   </si>
   <si>
     <t xml:space="preserve">23.624813079834</t>
@@ -2153,13 +2156,13 @@
     <t xml:space="preserve">22.1069068908691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1847476959229</t>
+    <t xml:space="preserve">22.1847496032715</t>
   </si>
   <si>
     <t xml:space="preserve">22.4961128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3015117645264</t>
+    <t xml:space="preserve">22.3015098571777</t>
   </si>
   <si>
     <t xml:space="preserve">22.6907157897949</t>
@@ -2171,16 +2174,16 @@
     <t xml:space="preserve">22.9631614685059</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2356071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9242420196533</t>
+    <t xml:space="preserve">23.2356052398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9242401123047</t>
   </si>
   <si>
     <t xml:space="preserve">22.223669052124</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4182720184326</t>
+    <t xml:space="preserve">22.4182739257812</t>
   </si>
   <si>
     <t xml:space="preserve">21.9123058319092</t>
@@ -2189,40 +2192,40 @@
     <t xml:space="preserve">21.4841766357422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1338901519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.523099899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.717700958252</t>
+    <t xml:space="preserve">21.1338939666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5230979919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7177028656006</t>
   </si>
   <si>
     <t xml:space="preserve">21.6398601531982</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2506542205811</t>
+    <t xml:space="preserve">21.2506523132324</t>
   </si>
   <si>
     <t xml:space="preserve">21.5620193481445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8344612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6787815093994</t>
+    <t xml:space="preserve">21.8344631195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.678783416748</t>
   </si>
   <si>
     <t xml:space="preserve">21.9901466369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1458282470703</t>
+    <t xml:space="preserve">22.1458301544189</t>
   </si>
   <si>
     <t xml:space="preserve">22.846399307251</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8853206634521</t>
+    <t xml:space="preserve">22.8853187561035</t>
   </si>
   <si>
     <t xml:space="preserve">22.4571914672852</t>
@@ -2234,7 +2237,7 @@
     <t xml:space="preserve">21.2117328643799</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3674182891846</t>
+    <t xml:space="preserve">21.3674144744873</t>
   </si>
   <si>
     <t xml:space="preserve">20.9782104492188</t>
@@ -2246,10 +2249,10 @@
     <t xml:space="preserve">21.873384475708</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4407329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8835639953613</t>
+    <t xml:space="preserve">23.440731048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.88356590271</t>
   </si>
   <si>
     <t xml:space="preserve">22.7243747711182</t>
@@ -2258,13 +2261,10 @@
     <t xml:space="preserve">22.8039703369141</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7641735076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0427551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9631595611572</t>
+    <t xml:space="preserve">22.7641754150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0427570343018</t>
   </si>
   <si>
     <t xml:space="preserve">23.2417449951172</t>
@@ -2273,31 +2273,31 @@
     <t xml:space="preserve">23.0029582977295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2019443511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1223487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1621494293213</t>
+    <t xml:space="preserve">23.2019462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.122350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1621475219727</t>
   </si>
   <si>
     <t xml:space="preserve">23.5203247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9580993652344</t>
+    <t xml:space="preserve">23.9580974578857</t>
   </si>
   <si>
     <t xml:space="preserve">24.0774917602539</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4356689453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3162727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3560733795166</t>
+    <t xml:space="preserve">24.4356708526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3162746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3560752868652</t>
   </si>
   <si>
     <t xml:space="preserve">24.7938461303711</t>
@@ -2306,22 +2306,22 @@
     <t xml:space="preserve">24.1570854187012</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6744537353516</t>
+    <t xml:space="preserve">24.6744518280029</t>
   </si>
   <si>
     <t xml:space="preserve">24.913236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">24.555061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7540493011475</t>
+    <t xml:space="preserve">24.5550632476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7540473937988</t>
   </si>
   <si>
     <t xml:space="preserve">24.2764778137207</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1172885894775</t>
+    <t xml:space="preserve">24.1172866821289</t>
   </si>
   <si>
     <t xml:space="preserve">24.5152626037598</t>
@@ -2330,28 +2330,28 @@
     <t xml:space="preserve">24.4754657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2366790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3958702087402</t>
+    <t xml:space="preserve">24.2366828918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3958721160889</t>
   </si>
   <si>
     <t xml:space="preserve">24.7142505645752</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6346569061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1968822479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6295928955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5102005004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1520233154297</t>
+    <t xml:space="preserve">24.6346549987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1968841552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6295948028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5102024078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1520252227783</t>
   </si>
   <si>
     <t xml:space="preserve">25.3510131835938</t>
@@ -2360,28 +2360,28 @@
     <t xml:space="preserve">25.4704036712646</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6693897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3908100128174</t>
+    <t xml:space="preserve">25.6693916320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3908081054688</t>
   </si>
   <si>
     <t xml:space="preserve">25.191822052002</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0326328277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2714176177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8336448669434</t>
+    <t xml:space="preserve">25.0326309204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2714157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8336429595947</t>
   </si>
   <si>
     <t xml:space="preserve">24.9530353546143</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8683776855469</t>
+    <t xml:space="preserve">25.8683815002441</t>
   </si>
   <si>
     <t xml:space="preserve">25.0724277496338</t>
@@ -2399,19 +2399,19 @@
     <t xml:space="preserve">23.6397190093994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7989082336426</t>
+    <t xml:space="preserve">23.7989063262939</t>
   </si>
   <si>
     <t xml:space="preserve">24.5948581695557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9928321838379</t>
+    <t xml:space="preserve">24.9928340911865</t>
   </si>
   <si>
     <t xml:space="preserve">25.430606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3112144470215</t>
+    <t xml:space="preserve">25.3112125396729</t>
   </si>
   <si>
     <t xml:space="preserve">25.2316188812256</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">26.0673656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2663516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0275707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7887840270996</t>
+    <t xml:space="preserve">26.2663536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0275688171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7887859344482</t>
   </si>
   <si>
     <t xml:space="preserve">25.5499992370605</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">25.9479732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1071643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7489833831787</t>
+    <t xml:space="preserve">26.1071624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7489852905273</t>
   </si>
   <si>
     <t xml:space="preserve">24.8734397888184</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">24.0376949310303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3264007568359</t>
+    <t xml:space="preserve">22.3263988494873</t>
   </si>
   <si>
     <t xml:space="preserve">22.3661975860596</t>
@@ -2459,16 +2459,16 @@
     <t xml:space="preserve">23.0825538635254</t>
   </si>
   <si>
-    <t xml:space="preserve">22.923360824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3213386535645</t>
+    <t xml:space="preserve">22.9233646392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3213367462158</t>
   </si>
   <si>
     <t xml:space="preserve">23.5999202728271</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3611373901367</t>
+    <t xml:space="preserve">23.3611354827881</t>
   </si>
   <si>
     <t xml:space="preserve">23.4009323120117</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">23.5601234436035</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4855918884277</t>
+    <t xml:space="preserve">22.4855899810791</t>
   </si>
   <si>
     <t xml:space="preserve">23.8387069702148</t>
@@ -2492,13 +2492,13 @@
     <t xml:space="preserve">23.8264102935791</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5692920684814</t>
+    <t xml:space="preserve">23.5692901611328</t>
   </si>
   <si>
     <t xml:space="preserve">24.1263828277588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9549713134766</t>
+    <t xml:space="preserve">23.9549694061279</t>
   </si>
   <si>
     <t xml:space="preserve">24.4692077636719</t>
@@ -2507,13 +2507,13 @@
     <t xml:space="preserve">24.4263553619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1692371368408</t>
+    <t xml:space="preserve">24.1692352294922</t>
   </si>
   <si>
     <t xml:space="preserve">24.2120895385742</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7835578918457</t>
+    <t xml:space="preserve">23.7835559844971</t>
   </si>
   <si>
     <t xml:space="preserve">24.340648651123</t>
@@ -2528,13 +2528,13 @@
     <t xml:space="preserve">23.5264377593994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9978218078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9121150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8692626953125</t>
+    <t xml:space="preserve">23.99782371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9121170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8692646026611</t>
   </si>
   <si>
     <t xml:space="preserve">23.7407035827637</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">23.6549968719482</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9693450927734</t>
+    <t xml:space="preserve">22.9693431854248</t>
   </si>
   <si>
     <t xml:space="preserve">22.8836402893066</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">22.5836658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9264907836914</t>
+    <t xml:space="preserve">22.92649269104</t>
   </si>
   <si>
     <t xml:space="preserve">23.1407585144043</t>
@@ -2561,10 +2561,10 @@
     <t xml:space="preserve">22.8407859802246</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7550792694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6693725585938</t>
+    <t xml:space="preserve">22.7550773620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6693744659424</t>
   </si>
   <si>
     <t xml:space="preserve">23.0550518035889</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">23.3550243377686</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0121994018555</t>
+    <t xml:space="preserve">23.0121974945068</t>
   </si>
   <si>
     <t xml:space="preserve">23.3121719360352</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">22.7979316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4551048278809</t>
+    <t xml:space="preserve">22.4551086425781</t>
   </si>
   <si>
     <t xml:space="preserve">22.4979591369629</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">22.6265182495117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6978511810303</t>
+    <t xml:space="preserve">23.6978492736816</t>
   </si>
   <si>
     <t xml:space="preserve">22.5408115386963</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2693157196045</t>
+    <t xml:space="preserve">23.2693176269531</t>
   </si>
   <si>
     <t xml:space="preserve">22.2836933135986</t>
@@ -2636,16 +2636,16 @@
     <t xml:space="preserve">20.826681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9267635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1410312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9980945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1266555786133</t>
+    <t xml:space="preserve">19.9267616271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1410293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9980964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1266536712646</t>
   </si>
   <si>
     <t xml:space="preserve">20.5267105102539</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">20.6552696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3124446868896</t>
+    <t xml:space="preserve">20.312442779541</t>
   </si>
   <si>
     <t xml:space="preserve">20.4410037994385</t>
@@ -2663,19 +2663,19 @@
     <t xml:space="preserve">20.6981220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5980434417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3837738037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5123348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3409214019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.026575088501</t>
+    <t xml:space="preserve">21.5980415344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3837757110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.512336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3409194946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0265731811523</t>
   </si>
   <si>
     <t xml:space="preserve">22.1122798919678</t>
@@ -2687,16 +2687,16 @@
     <t xml:space="preserve">22.1551342010498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2408409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6837463378906</t>
+    <t xml:space="preserve">22.2408390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6837482452393</t>
   </si>
   <si>
     <t xml:space="preserve">21.7266006469727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8980121612549</t>
+    <t xml:space="preserve">21.8980140686035</t>
   </si>
   <si>
     <t xml:space="preserve">21.7694530487061</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">22.0694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9837188720703</t>
+    <t xml:space="preserve">21.9837207794189</t>
   </si>
   <si>
     <t xml:space="preserve">21.8551597595215</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">21.0838012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9408683776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5551872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0409469604492</t>
+    <t xml:space="preserve">21.9408664703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5551853179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0409488677979</t>
   </si>
   <si>
     <t xml:space="preserve">20.912389755249</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">20.7409763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1838836669922</t>
+    <t xml:space="preserve">20.1838817596436</t>
   </si>
   <si>
     <t xml:space="preserve">20.3552951812744</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">22.0611591339111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1051940917969</t>
+    <t xml:space="preserve">22.1051959991455</t>
   </si>
   <si>
     <t xml:space="preserve">22.017126083374</t>
@@ -2783,10 +2783,10 @@
     <t xml:space="preserve">21.664852142334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5767822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4887142181396</t>
+    <t xml:space="preserve">21.5767841339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4887161254883</t>
   </si>
   <si>
     <t xml:space="preserve">21.9290561676025</t>
@@ -2795,22 +2795,22 @@
     <t xml:space="preserve">21.8409881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7088871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4006443023682</t>
+    <t xml:space="preserve">21.7088851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4006462097168</t>
   </si>
   <si>
     <t xml:space="preserve">21.7969551086426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9730911254883</t>
+    <t xml:space="preserve">21.9730930328369</t>
   </si>
   <si>
     <t xml:space="preserve">21.7529201507568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.501501083374</t>
+    <t xml:space="preserve">22.5015029907227</t>
   </si>
   <si>
     <t xml:space="preserve">22.2372970581055</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">22.3253650665283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5455379486084</t>
+    <t xml:space="preserve">22.5455360412598</t>
   </si>
   <si>
     <t xml:space="preserve">22.149227142334</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">21.0483722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3566131591797</t>
+    <t xml:space="preserve">21.3566112518311</t>
   </si>
   <si>
     <t xml:space="preserve">21.6208171844482</t>
@@ -2852,13 +2852,13 @@
     <t xml:space="preserve">21.4446811676025</t>
   </si>
   <si>
-    <t xml:space="preserve">21.532751083374</t>
+    <t xml:space="preserve">21.5327491760254</t>
   </si>
   <si>
     <t xml:space="preserve">21.0043392181396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8722362518311</t>
+    <t xml:space="preserve">20.8722343444824</t>
   </si>
   <si>
     <t xml:space="preserve">20.6960983276367</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">20.2557563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3878574371338</t>
+    <t xml:space="preserve">20.3878593444824</t>
   </si>
   <si>
     <t xml:space="preserve">20.2997894287109</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">20.7841682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9603042602539</t>
+    <t xml:space="preserve">20.9603023529053</t>
   </si>
   <si>
     <t xml:space="preserve">20.7401313781738</t>
@@ -2900,10 +2900,10 @@
     <t xml:space="preserve">21.1804752349854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6336078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4574699401855</t>
+    <t xml:space="preserve">22.6336059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4574680328369</t>
   </si>
   <si>
     <t xml:space="preserve">22.5895709991455</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">24.3949756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">24.30690574646</t>
+    <t xml:space="preserve">24.3069076538086</t>
   </si>
   <si>
     <t xml:space="preserve">24.1307697296143</t>
@@ -2936,13 +2936,13 @@
     <t xml:space="preserve">24.3509407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4390106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5711116790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6591796875</t>
+    <t xml:space="preserve">24.4390087127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5711135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6591815948486</t>
   </si>
   <si>
     <t xml:space="preserve">24.7032146453857</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">24.0867366790771</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2188396453857</t>
+    <t xml:space="preserve">24.2188377380371</t>
   </si>
   <si>
     <t xml:space="preserve">24.1748046875</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">23.9546337127686</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7600364685059</t>
+    <t xml:space="preserve">25.7600383758545</t>
   </si>
   <si>
     <t xml:space="preserve">25.4077625274658</t>
@@ -2990,19 +2990,19 @@
     <t xml:space="preserve">26.1123104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1563453674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4645862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5910167694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3708457946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8992595672607</t>
+    <t xml:space="preserve">26.1563472747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4645843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5910148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3708438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8992576599121</t>
   </si>
   <si>
     <t xml:space="preserve">30.0313587188721</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">29.5029487609863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7671546936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2827758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0753974914551</t>
+    <t xml:space="preserve">29.7671527862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2827777862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0753955841064</t>
   </si>
   <si>
     <t xml:space="preserve">29.7231216430664</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">30.471700668335</t>
   </si>
   <si>
-    <t xml:space="preserve">29.811185836792</t>
+    <t xml:space="preserve">29.8111877441406</t>
   </si>
   <si>
     <t xml:space="preserve">29.2387447357178</t>
@@ -3047,28 +3047,28 @@
     <t xml:space="preserve">28.7103309631348</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8424339294434</t>
+    <t xml:space="preserve">28.842435836792</t>
   </si>
   <si>
     <t xml:space="preserve">28.8864688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5469837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2955646514893</t>
+    <t xml:space="preserve">29.5469818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2955665588379</t>
   </si>
   <si>
     <t xml:space="preserve">30.7359104156494</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3836345672607</t>
+    <t xml:space="preserve">30.3836326599121</t>
   </si>
   <si>
     <t xml:space="preserve">29.9873237609863</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4276695251465</t>
+    <t xml:space="preserve">30.4276676177979</t>
   </si>
   <si>
     <t xml:space="preserve">29.4632396697998</t>
@@ -3678,6 +3678,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
   </si>
 </sst>
 </file>
@@ -32764,7 +32767,7 @@
         <v>25.5</v>
       </c>
       <c r="G1106" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32816,7 +32819,7 @@
         <v>25.5</v>
       </c>
       <c r="G1108" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32842,7 +32845,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G1109" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32868,7 +32871,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1110" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32894,7 +32897,7 @@
         <v>25</v>
       </c>
       <c r="G1111" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32920,7 +32923,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1112" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32946,7 +32949,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1113" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32972,7 +32975,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1114" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -33024,7 +33027,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1116" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -33050,7 +33053,7 @@
         <v>24.75</v>
       </c>
       <c r="G1117" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -33076,7 +33079,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1118" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33102,7 +33105,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1119" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33180,7 +33183,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1122" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33206,7 +33209,7 @@
         <v>25.75</v>
       </c>
       <c r="G1123" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33232,7 +33235,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1124" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33258,7 +33261,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1125" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33284,7 +33287,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1126" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33310,7 +33313,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G1127" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33336,7 +33339,7 @@
         <v>27</v>
       </c>
       <c r="G1128" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33362,7 +33365,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1129" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33388,7 +33391,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1130" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33414,7 +33417,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1131" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33440,7 +33443,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1132" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33466,7 +33469,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1133" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33492,7 +33495,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1134" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33518,7 +33521,7 @@
         <v>27.75</v>
       </c>
       <c r="G1135" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33544,7 +33547,7 @@
         <v>28</v>
       </c>
       <c r="G1136" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33570,7 +33573,7 @@
         <v>28</v>
       </c>
       <c r="G1137" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33596,7 +33599,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33622,7 +33625,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1139" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33648,7 +33651,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1140" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33674,7 +33677,7 @@
         <v>29</v>
       </c>
       <c r="G1141" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33700,7 +33703,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33726,7 +33729,7 @@
         <v>29.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33752,7 +33755,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1144" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33778,7 +33781,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1145" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33804,7 +33807,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1146" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33830,7 +33833,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1147" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33856,7 +33859,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1148" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33882,7 +33885,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1149" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33908,7 +33911,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1150" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33934,7 +33937,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1151" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33960,7 +33963,7 @@
         <v>32</v>
       </c>
       <c r="G1152" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33986,7 +33989,7 @@
         <v>31.75</v>
       </c>
       <c r="G1153" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -34012,7 +34015,7 @@
         <v>31.5</v>
       </c>
       <c r="G1154" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -34038,7 +34041,7 @@
         <v>32.5</v>
       </c>
       <c r="G1155" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34064,7 +34067,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1156" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34090,7 +34093,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1157" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34116,7 +34119,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1158" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34142,7 +34145,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1159" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34168,7 +34171,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G1160" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34194,7 +34197,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1161" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34220,7 +34223,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G1162" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34246,7 +34249,7 @@
         <v>29.25</v>
       </c>
       <c r="G1163" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34272,7 +34275,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1164" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34298,7 +34301,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G1165" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34324,7 +34327,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34350,7 +34353,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G1167" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34376,7 +34379,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34402,7 +34405,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1169" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34428,7 +34431,7 @@
         <v>29.75</v>
       </c>
       <c r="G1170" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34454,7 +34457,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1171" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34480,7 +34483,7 @@
         <v>30.5</v>
       </c>
       <c r="G1172" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34506,7 +34509,7 @@
         <v>30.5</v>
       </c>
       <c r="G1173" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34532,7 +34535,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1174" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34558,7 +34561,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34584,7 +34587,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34610,7 +34613,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1177" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34636,7 +34639,7 @@
         <v>30.5</v>
       </c>
       <c r="G1178" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34662,7 +34665,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1179" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34688,7 +34691,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1180" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34714,7 +34717,7 @@
         <v>30.5</v>
       </c>
       <c r="G1181" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34740,7 +34743,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1182" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34766,7 +34769,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1183" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34792,7 +34795,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1184" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34818,7 +34821,7 @@
         <v>30.5</v>
       </c>
       <c r="G1185" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34844,7 +34847,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34870,7 +34873,7 @@
         <v>30</v>
       </c>
       <c r="G1187" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34896,7 +34899,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1188" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34922,7 +34925,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1189" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34948,7 +34951,7 @@
         <v>30</v>
       </c>
       <c r="G1190" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34974,7 +34977,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1191" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -35000,7 +35003,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1192" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -35026,7 +35029,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1193" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -35052,7 +35055,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1194" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -35078,7 +35081,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1195" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35104,7 +35107,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1196" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35130,7 +35133,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1197" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35156,7 +35159,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35182,7 +35185,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35208,7 +35211,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1200" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35234,7 +35237,7 @@
         <v>28.5</v>
       </c>
       <c r="G1201" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35260,7 +35263,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1202" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35286,7 +35289,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1203" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35312,7 +35315,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1204" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35338,7 +35341,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1205" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35364,7 +35367,7 @@
         <v>28.75</v>
       </c>
       <c r="G1206" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35390,7 +35393,7 @@
         <v>29.5</v>
       </c>
       <c r="G1207" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35416,7 +35419,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1208" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35442,7 +35445,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1209" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35468,7 +35471,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1210" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35494,7 +35497,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1211" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35520,7 +35523,7 @@
         <v>29</v>
       </c>
       <c r="G1212" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35546,7 +35549,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35572,7 +35575,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1214" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35598,7 +35601,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1215" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35624,7 +35627,7 @@
         <v>29</v>
       </c>
       <c r="G1216" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35650,7 +35653,7 @@
         <v>29</v>
       </c>
       <c r="G1217" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35676,7 +35679,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1218" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35702,7 +35705,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1219" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35728,7 +35731,7 @@
         <v>29</v>
       </c>
       <c r="G1220" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35754,7 +35757,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1221" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35780,7 +35783,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35806,7 +35809,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1223" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35832,7 +35835,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35858,7 +35861,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1225" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35884,7 +35887,7 @@
         <v>28</v>
       </c>
       <c r="G1226" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35910,7 +35913,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1227" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35936,7 +35939,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1228" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35962,7 +35965,7 @@
         <v>27.75</v>
       </c>
       <c r="G1229" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35988,7 +35991,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -36014,7 +36017,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -36040,7 +36043,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -36066,7 +36069,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1233" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -36092,7 +36095,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1234" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36118,7 +36121,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1235" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36144,7 +36147,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1236" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36170,7 +36173,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1237" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36196,7 +36199,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1238" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36222,7 +36225,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36248,7 +36251,7 @@
         <v>27.75</v>
       </c>
       <c r="G1240" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36274,7 +36277,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G1241" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36300,7 +36303,7 @@
         <v>27.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36326,7 +36329,7 @@
         <v>28</v>
       </c>
       <c r="G1243" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36352,7 +36355,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1244" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36378,7 +36381,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36404,7 +36407,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1246" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36430,7 +36433,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1247" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36456,7 +36459,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1248" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36482,7 +36485,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1249" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36508,7 +36511,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36534,7 +36537,7 @@
         <v>28.75</v>
       </c>
       <c r="G1251" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36560,7 +36563,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1252" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36586,7 +36589,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36612,7 +36615,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1254" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36638,7 +36641,7 @@
         <v>28.25</v>
       </c>
       <c r="G1255" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36664,7 +36667,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G1256" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36690,7 +36693,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36716,7 +36719,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1258" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36742,7 +36745,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1259" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36768,7 +36771,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1260" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36794,7 +36797,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1261" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36820,7 +36823,7 @@
         <v>29.25</v>
       </c>
       <c r="G1262" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36846,7 +36849,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1263" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36872,7 +36875,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1264" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36898,7 +36901,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1265" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36924,7 +36927,7 @@
         <v>30</v>
       </c>
       <c r="G1266" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36950,7 +36953,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1267" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36976,7 +36979,7 @@
         <v>29.25</v>
       </c>
       <c r="G1268" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -37002,7 +37005,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -37028,7 +37031,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1270" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -37054,7 +37057,7 @@
         <v>29.5</v>
       </c>
       <c r="G1271" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -37080,7 +37083,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1272" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37106,7 +37109,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1273" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37132,7 +37135,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1274" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37158,7 +37161,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37184,7 +37187,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1276" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37210,7 +37213,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1277" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37236,7 +37239,7 @@
         <v>29.25</v>
       </c>
       <c r="G1278" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37262,7 +37265,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37288,7 +37291,7 @@
         <v>28.75</v>
       </c>
       <c r="G1280" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37314,7 +37317,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1281" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37340,7 +37343,7 @@
         <v>29.25</v>
       </c>
       <c r="G1282" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37366,7 +37369,7 @@
         <v>29.25</v>
       </c>
       <c r="G1283" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37392,7 +37395,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1284" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37418,7 +37421,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1285" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37444,7 +37447,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1286" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37470,7 +37473,7 @@
         <v>27.75</v>
       </c>
       <c r="G1287" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37496,7 +37499,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1288" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37522,7 +37525,7 @@
         <v>27.25</v>
       </c>
       <c r="G1289" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37548,7 +37551,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1290" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37574,7 +37577,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1291" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37600,7 +37603,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1292" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37626,7 +37629,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1293" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37652,7 +37655,7 @@
         <v>28.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37678,7 +37681,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G1295" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37704,7 +37707,7 @@
         <v>28.75</v>
       </c>
       <c r="G1296" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37730,7 +37733,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37756,7 +37759,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1298" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37782,7 +37785,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1299" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37808,7 +37811,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1300" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37834,7 +37837,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1301" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37860,7 +37863,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1302" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37886,7 +37889,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1303" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37912,7 +37915,7 @@
         <v>27</v>
       </c>
       <c r="G1304" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37938,7 +37941,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1305" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37964,7 +37967,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1306" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37990,7 +37993,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1307" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -38016,7 +38019,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1308" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -38042,7 +38045,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -38068,7 +38071,7 @@
         <v>26.5</v>
       </c>
       <c r="G1310" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -38094,7 +38097,7 @@
         <v>27.25</v>
       </c>
       <c r="G1311" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38120,7 +38123,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1312" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38146,7 +38149,7 @@
         <v>27.25</v>
       </c>
       <c r="G1313" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38172,7 +38175,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1314" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38198,7 +38201,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38224,7 +38227,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38250,7 +38253,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1317" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38276,7 +38279,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1318" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38302,7 +38305,7 @@
         <v>29.75</v>
       </c>
       <c r="G1319" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38328,7 +38331,7 @@
         <v>29.5</v>
       </c>
       <c r="G1320" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38354,7 +38357,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38380,7 +38383,7 @@
         <v>29.5</v>
       </c>
       <c r="G1322" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38406,7 +38409,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38432,7 +38435,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38458,7 +38461,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38484,7 +38487,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1326" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38510,7 +38513,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1327" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38536,7 +38539,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1328" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38562,7 +38565,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1329" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38588,7 +38591,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1330" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38614,7 +38617,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1331" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38640,7 +38643,7 @@
         <v>29</v>
       </c>
       <c r="G1332" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38666,7 +38669,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1333" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38692,7 +38695,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1334" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38718,7 +38721,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1335" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38744,7 +38747,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1336" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38770,7 +38773,7 @@
         <v>29</v>
       </c>
       <c r="G1337" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38796,7 +38799,7 @@
         <v>29.25</v>
       </c>
       <c r="G1338" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38822,7 +38825,7 @@
         <v>29</v>
       </c>
       <c r="G1339" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38848,7 +38851,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1340" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38874,7 +38877,7 @@
         <v>29</v>
       </c>
       <c r="G1341" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38900,7 +38903,7 @@
         <v>29</v>
       </c>
       <c r="G1342" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38926,7 +38929,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38952,7 +38955,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1344" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38978,7 +38981,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1345" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -39004,7 +39007,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -39030,7 +39033,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -39056,7 +39059,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1348" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39082,7 +39085,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1349" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39108,7 +39111,7 @@
         <v>28.75</v>
       </c>
       <c r="G1350" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39134,7 +39137,7 @@
         <v>29</v>
       </c>
       <c r="G1351" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39160,7 +39163,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1352" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39186,7 +39189,7 @@
         <v>29.5</v>
       </c>
       <c r="G1353" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39212,7 +39215,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1354" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39238,7 +39241,7 @@
         <v>28.75</v>
       </c>
       <c r="G1355" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39264,7 +39267,7 @@
         <v>28.75</v>
       </c>
       <c r="G1356" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39290,7 +39293,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1357" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39316,7 +39319,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39342,7 +39345,7 @@
         <v>28.75</v>
       </c>
       <c r="G1359" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39368,7 +39371,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39394,7 +39397,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1361" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39420,7 +39423,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1362" t="s">
-        <v>750</v>
+        <v>719</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39446,7 +39449,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1363" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39524,7 +39527,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1366" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -39576,7 +39579,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -39680,7 +39683,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1372" t="s">
-        <v>750</v>
+        <v>719</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -44828,7 +44831,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1570" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44854,7 +44857,7 @@
         <v>28.75</v>
       </c>
       <c r="G1571" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44984,7 +44987,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1576" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45426,7 +45429,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1593" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45478,7 +45481,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1595" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45608,7 +45611,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1600" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45634,7 +45637,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1601" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45972,7 +45975,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1614" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -68808,7 +68811,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6493981481</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>13027</v>
@@ -68829,6 +68832,32 @@
         <v>1221</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6495949074</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>13277</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>33.1500015258789</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>33</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8067140579224</t>
+    <t xml:space="preserve">13.8067150115967</t>
   </si>
   <si>
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577449798584</t>
+    <t xml:space="preserve">14.057746887207</t>
   </si>
   <si>
     <t xml:space="preserve">13.9573335647583</t>
@@ -53,154 +53,154 @@
     <t xml:space="preserve">13.3883295059204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8896102905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8527946472168</t>
+    <t xml:space="preserve">12.8896141052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8527975082397</t>
   </si>
   <si>
     <t xml:space="preserve">12.9532079696655</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6184988021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846162796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.384204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8821420669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7348709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2127256393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7307453155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2294607162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2194204330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2461967468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9148359298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1323947906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6143770217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6813163757324</t>
+    <t xml:space="preserve">12.6184997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846143722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3842039108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8821411132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7348699569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2127265930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7307462692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2294597625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2194194793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2461948394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9148349761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1323957443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6143751144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6813182830811</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474338531494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3466081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3131380081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3298711776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8947515487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8780164718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.045371055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4261617660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094266891479</t>
+    <t xml:space="preserve">11.3466091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.313136100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3298721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8947525024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8780174255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0453729629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4261608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094257354736</t>
   </si>
   <si>
     <t xml:space="preserve">11.7080936431885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7147874832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0494956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7482585906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7449111938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2135038375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168502807617</t>
+    <t xml:space="preserve">11.7147884368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0494966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7482576370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.744912147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2135019302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168483734131</t>
   </si>
   <si>
     <t xml:space="preserve">12.3674697875977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7189130783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8293685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0201501846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2209739685059</t>
+    <t xml:space="preserve">12.7189121246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8293676376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0201511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2209730148315</t>
   </si>
   <si>
     <t xml:space="preserve">13.3849840164185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0870923995972</t>
+    <t xml:space="preserve">13.0870904922485</t>
   </si>
   <si>
     <t xml:space="preserve">13.0536203384399</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3347759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3146934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569667816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661832809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306028366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.287917137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8260202407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9833335876465</t>
+    <t xml:space="preserve">13.3347749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3146915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569677352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109327316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306047439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2879190444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8260183334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9833316802979</t>
   </si>
   <si>
     <t xml:space="preserve">12.9030017852783</t>
@@ -209,148 +209,148 @@
     <t xml:space="preserve">13.2377090454102</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1674213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1138677597046</t>
+    <t xml:space="preserve">13.167423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1138668060303</t>
   </si>
   <si>
     <t xml:space="preserve">13.0971336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5046997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8092851638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8862676620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7055234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7222585678101</t>
+    <t xml:space="preserve">12.5047006607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8092823028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.886266708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7055225372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7222595214844</t>
   </si>
   <si>
     <t xml:space="preserve">12.916389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0301914215088</t>
+    <t xml:space="preserve">13.0301904678345</t>
   </si>
   <si>
     <t xml:space="preserve">12.8327131271362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6318883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7021770477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8695306777954</t>
+    <t xml:space="preserve">12.6318893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7021760940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8695316314697</t>
   </si>
   <si>
     <t xml:space="preserve">12.5582523345947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5682926177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8360614776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494501113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5348224639893</t>
+    <t xml:space="preserve">12.5682935714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8360605239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958955764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5348243713379</t>
   </si>
   <si>
     <t xml:space="preserve">12.7791595458984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7691211700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.786566734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5024194717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6512584686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.752739906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5836057662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4990386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5700740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159502029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2791614532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0660524368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1641521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1709156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1100292205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1269407272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.981484413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7459745407104</t>
+    <t xml:space="preserve">12.7691173553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7865657806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5024213790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6512575149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7527389526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5836048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4990377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5700721740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159511566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2791633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0660533905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776828765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1641511917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.170916557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1100282669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1269416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9814853668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7459735870361</t>
   </si>
   <si>
     <t xml:space="preserve">12.6580247879028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3231372833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6973419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.778525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2406768798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8212242126465</t>
+    <t xml:space="preserve">12.3231391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6973400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7785243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2406759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8212232589722</t>
   </si>
   <si>
     <t xml:space="preserve">10.6554708480835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0613946914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1967010498047</t>
+    <t xml:space="preserve">11.061393737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.196702003479</t>
   </si>
   <si>
     <t xml:space="preserve">11.4064283370972</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">10.6656198501587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1886615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5878171920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6825332641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.839412689209</t>
+    <t xml:space="preserve">10.1886596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.587818145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6825323104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8394136428833</t>
   </si>
   <si>
     <t xml:space="preserve">13.0199737548828</t>
@@ -380,13 +380,13 @@
     <t xml:space="preserve">13.3616228103638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0233564376831</t>
+    <t xml:space="preserve">13.0233545303345</t>
   </si>
   <si>
     <t xml:space="preserve">13.1924886703491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4969320297241</t>
+    <t xml:space="preserve">13.4969310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.4698686599731</t>
@@ -395,58 +395,58 @@
     <t xml:space="preserve">13.5307588577271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.480016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2939672470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108816146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548564910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0740966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368852615356</t>
+    <t xml:space="preserve">13.4800186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2939691543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108835220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0740957260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.03688621521</t>
   </si>
   <si>
     <t xml:space="preserve">12.9489326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9827632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0910091400146</t>
+    <t xml:space="preserve">12.982762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0910081863403</t>
   </si>
   <si>
     <t xml:space="preserve">13.0707120895386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9962902069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8576030731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113033294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1248321533203</t>
+    <t xml:space="preserve">12.9962921142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8576021194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1248340606689</t>
   </si>
   <si>
     <t xml:space="preserve">13.1823415756226</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0605621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857233047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4123640060425</t>
+    <t xml:space="preserve">13.0605630874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4123620986938</t>
   </si>
   <si>
     <t xml:space="preserve">13.5679683685303</t>
@@ -461,160 +461,160 @@
     <t xml:space="preserve">13.7066564559937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8352003097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2106781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4576139450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7552909851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838338851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.01575756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.985312461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303470611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6652345657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2897577285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8297119140625</t>
+    <t xml:space="preserve">13.8352012634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2106800079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.457615852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7552919387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838329315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0157594680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9853134155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303499221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6652326583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.289755821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8297090530396</t>
   </si>
   <si>
     <t xml:space="preserve">14.6842546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7722034454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9514865875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7485227584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7180814743042</t>
+    <t xml:space="preserve">14.7722043991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9514856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7485256195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7180805206299</t>
   </si>
   <si>
     <t xml:space="preserve">14.8770666122437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992639541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751672744751</t>
+    <t xml:space="preserve">14.7992649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751691818237</t>
   </si>
   <si>
     <t xml:space="preserve">14.9007472991943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2018051147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939828872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988470077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9142761230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.927806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7383785247803</t>
+    <t xml:space="preserve">15.2018041610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939809799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330907821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988441467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9142780303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9278106689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.738377571106</t>
   </si>
   <si>
     <t xml:space="preserve">14.7248468399048</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5421829223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4440832138062</t>
+    <t xml:space="preserve">14.5421810150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4440841674805</t>
   </si>
   <si>
     <t xml:space="preserve">15.0529680252075</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1443014144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1104736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9548711776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0901765823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2187194824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7823524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707220077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6166009902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764314651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1599388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2546539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0415439605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1125783920288</t>
+    <t xml:space="preserve">15.1442975997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1104726791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9548692703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0901775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2187185287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7823534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6166000366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764276504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1599369049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2546529769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.041543006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1125812530518</t>
   </si>
   <si>
     <t xml:space="preserve">14.0381622314453</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1430244445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527517318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2072944641113</t>
+    <t xml:space="preserve">14.1430263519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903800964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527488708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2072973251343</t>
   </si>
   <si>
     <t xml:space="preserve">14.3561344146729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4373188018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730497360229</t>
+    <t xml:space="preserve">14.4373178482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730487823486</t>
   </si>
   <si>
     <t xml:space="preserve">14.3087768554688</t>
@@ -626,82 +626,82 @@
     <t xml:space="preserve">14.3392200469971</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2512693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464071273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058139801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1193475723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2275915145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2715673446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.149790763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0753707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0719871520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749490737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667041778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4779090881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.626748085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7519092559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8161783218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1037092208862</t>
+    <t xml:space="preserve">14.2512722015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1464061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058158874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1193447113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2275896072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2715644836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1497917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0753698348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0719881057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667032241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4779100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267499923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7519102096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8161792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1037073135376</t>
   </si>
   <si>
     <t xml:space="preserve">15.0834131240845</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1882781982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172370910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1544494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758043289185</t>
+    <t xml:space="preserve">15.1882743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172389984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.154447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999048233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758024215698</t>
   </si>
   <si>
     <t xml:space="preserve">15.3574113845825</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3912391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.489333152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1713638305664</t>
+    <t xml:space="preserve">15.3912401199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893350601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1713609695435</t>
   </si>
   <si>
     <t xml:space="preserve">15.1003246307373</t>
@@ -710,139 +710,139 @@
     <t xml:space="preserve">15.3946180343628</t>
   </si>
   <si>
-    <t xml:space="preserve">15.316819190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3134355545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4182996749878</t>
+    <t xml:space="preserve">15.3168172836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3134346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4182977676392</t>
   </si>
   <si>
     <t xml:space="preserve">15.4250631332397</t>
   </si>
   <si>
-    <t xml:space="preserve">15.536693572998</t>
+    <t xml:space="preserve">15.5366945266724</t>
   </si>
   <si>
     <t xml:space="preserve">15.6753826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6449394226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7295064926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6618528366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.651704788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6821508407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637550354004</t>
+    <t xml:space="preserve">15.6449375152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7295074462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6618509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6517028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6821489334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637531280518</t>
   </si>
   <si>
     <t xml:space="preserve">15.4081506729126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6415567398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7024431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333108901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584692001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588890075684</t>
+    <t xml:space="preserve">15.6415576934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7024440765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333089828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584711074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588899612427</t>
   </si>
   <si>
     <t xml:space="preserve">15.5874328613281</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6550846099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227420806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3350067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0339488983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4060401916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.402660369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4195747375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6935710906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0994968414307</t>
+    <t xml:space="preserve">15.6550855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227401733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3350086212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0339469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4060459136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4026622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4195728302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6935691833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0994930267334</t>
   </si>
   <si>
     <t xml:space="preserve">16.9980144500732</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1671504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4208488464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5392436981201</t>
+    <t xml:space="preserve">17.1671485900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4208507537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5392456054688</t>
   </si>
   <si>
     <t xml:space="preserve">17.6407241821289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4039363861084</t>
+    <t xml:space="preserve">17.4039344787598</t>
   </si>
   <si>
     <t xml:space="preserve">17.48850440979</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3531970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3870239257812</t>
+    <t xml:space="preserve">17.3531951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3870258331299</t>
   </si>
   <si>
     <t xml:space="preserve">17.522331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4546775817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8775157928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8098621368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7083778381348</t>
+    <t xml:space="preserve">17.4546756744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.877513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8098583221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7083797454834</t>
   </si>
   <si>
     <t xml:space="preserve">17.7591209411621</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6745529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.573070526123</t>
+    <t xml:space="preserve">17.6745491027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730724334717</t>
   </si>
   <si>
     <t xml:space="preserve">17.3362846374512</t>
@@ -851,13 +851,13 @@
     <t xml:space="preserve">17.2009773254395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2348022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2517147064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2178897857666</t>
+    <t xml:space="preserve">17.2348041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2517166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2178916931152</t>
   </si>
   <si>
     <t xml:space="preserve">17.3701095581055</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">17.7147541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5767650604248</t>
+    <t xml:space="preserve">17.5767631530762</t>
   </si>
   <si>
     <t xml:space="preserve">17.559513092041</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">17.6147117614746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7729587554932</t>
+    <t xml:space="preserve">16.7729568481445</t>
   </si>
   <si>
     <t xml:space="preserve">17.0075454711914</t>
@@ -893,82 +893,82 @@
     <t xml:space="preserve">17.1662349700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1317386627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9937419891357</t>
+    <t xml:space="preserve">17.1317367553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9937438964844</t>
   </si>
   <si>
     <t xml:space="preserve">16.9868469238281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9661464691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.835054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8488540649414</t>
+    <t xml:space="preserve">16.9661483764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8350524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.84885597229</t>
   </si>
   <si>
     <t xml:space="preserve">16.8281555175781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7591571807861</t>
+    <t xml:space="preserve">16.7591590881348</t>
   </si>
   <si>
     <t xml:space="preserve">16.8695545196533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9178524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9730453491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.938549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1524391174316</t>
+    <t xml:space="preserve">16.9178504943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9730472564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9385471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1524353027344</t>
   </si>
   <si>
     <t xml:space="preserve">16.6625633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5935688018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5659694671631</t>
+    <t xml:space="preserve">16.5935668945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5659675598145</t>
   </si>
   <si>
     <t xml:space="preserve">16.5038738250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626537322998</t>
+    <t xml:space="preserve">16.8626518249512</t>
   </si>
   <si>
     <t xml:space="preserve">16.9040489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">16.80055809021</t>
+    <t xml:space="preserve">16.8005599975586</t>
   </si>
   <si>
     <t xml:space="preserve">16.8971500396729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5383739471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5590705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4900760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2416858673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.303783416748</t>
+    <t xml:space="preserve">16.5383720397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5590686798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4900722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2416877746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3037815093994</t>
   </si>
   <si>
     <t xml:space="preserve">16.2485866546631</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">16.1864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1588935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5314693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2899856567383</t>
+    <t xml:space="preserve">16.1588916778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5314712524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">16.3175830841064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5452690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3658809661865</t>
+    <t xml:space="preserve">16.5452709197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3658790588379</t>
   </si>
   <si>
     <t xml:space="preserve">16.462474822998</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">16.3313827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3520812988281</t>
+    <t xml:space="preserve">16.3520832061768</t>
   </si>
   <si>
     <t xml:space="preserve">16.6970615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3865795135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4486751556396</t>
+    <t xml:space="preserve">16.3865814208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4486770629883</t>
   </si>
   <si>
     <t xml:space="preserve">16.5107746124268</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">16.4210777282715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4348773956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3934803009033</t>
+    <t xml:space="preserve">16.4348735809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3934783935547</t>
   </si>
   <si>
     <t xml:space="preserve">16.4969730377197</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">16.4003791809082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4555759429932</t>
+    <t xml:space="preserve">16.4555778503418</t>
   </si>
   <si>
     <t xml:space="preserve">16.358980178833</t>
@@ -1055,79 +1055,79 @@
     <t xml:space="preserve">16.2071895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1933917999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9036073684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5586271286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4965295791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9381046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7794141769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7656135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7863149642944</t>
+    <t xml:space="preserve">16.1933879852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9036054611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5586252212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4965305328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9381065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7794151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7656145095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7863130569458</t>
   </si>
   <si>
     <t xml:space="preserve">15.9795017242432</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9312038421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7035179138184</t>
+    <t xml:space="preserve">15.9312047958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.703516960144</t>
   </si>
   <si>
     <t xml:space="preserve">15.6483211517334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8415088653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7518167495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691101074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.862211227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0277996063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8967084884644</t>
+    <t xml:space="preserve">15.8415098190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7518148422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691082000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.862208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0277976989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8967056274414</t>
   </si>
   <si>
     <t xml:space="preserve">15.6276226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7173175811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310277938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034255981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.441330909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2481451034546</t>
+    <t xml:space="preserve">15.7173156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310287475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034275054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413328170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.248143196106</t>
   </si>
   <si>
     <t xml:space="preserve">15.3171405792236</t>
@@ -1136,43 +1136,43 @@
     <t xml:space="preserve">15.3309383392334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.282642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792362213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619457244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6000213623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896326065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9519052505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9726037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9864044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0415992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8553094863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.793212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758329391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2895402908325</t>
+    <t xml:space="preserve">15.2826414108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792371749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619438171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.600025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896306991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9519033432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.972601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9864025115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0416011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8553113937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932138442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2895393371582</t>
   </si>
   <si>
     <t xml:space="preserve">15.1791486740112</t>
@@ -1181,34 +1181,34 @@
     <t xml:space="preserve">15.2067461013794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3999347686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2343454360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3033390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137344360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3861351013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6345224380493</t>
+    <t xml:space="preserve">15.3999366760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2343444824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137372970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.386137008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6345205307007</t>
   </si>
   <si>
     <t xml:space="preserve">16.1450939178467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4831771850586</t>
+    <t xml:space="preserve">16.4831733703613</t>
   </si>
   <si>
     <t xml:space="preserve">16.6073684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">16.37278175354</t>
+    <t xml:space="preserve">16.3727798461914</t>
   </si>
   <si>
     <t xml:space="preserve">16.6349658966064</t>
@@ -1217,37 +1217,37 @@
     <t xml:space="preserve">16.4141807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0898952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2002906799316</t>
+    <t xml:space="preserve">16.0898971557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2002925872803</t>
   </si>
   <si>
     <t xml:space="preserve">16.731559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6901626586914</t>
+    <t xml:space="preserve">16.6901607513428</t>
   </si>
   <si>
     <t xml:space="preserve">16.4762725830078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7522621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6487636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6280670166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0420436859131</t>
+    <t xml:space="preserve">16.7522602081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6487655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6280651092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0420455932617</t>
   </si>
   <si>
     <t xml:space="preserve">17.0765399932861</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1110401153564</t>
+    <t xml:space="preserve">17.1110382080078</t>
   </si>
   <si>
     <t xml:space="preserve">17.2145328521729</t>
@@ -1256,25 +1256,25 @@
     <t xml:space="preserve">17.1455364227295</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1800365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.00710105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.21409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1105976104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5931253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621198654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0066547393799</t>
+    <t xml:space="preserve">17.1800346374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0071029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2140922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.110595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5931215286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0066576004028</t>
   </si>
   <si>
     <t xml:space="preserve">14.730673789978</t>
@@ -1283,64 +1283,64 @@
     <t xml:space="preserve">14.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9721584320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551315307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1101522445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0411529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0756521224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3516387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.42063331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5241289138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6966209411621</t>
+    <t xml:space="preserve">14.9721603393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.455132484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1101541519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0411558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0756540298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3516368865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4206342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5241270065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6966190338135</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8742513656616</t>
+    <t xml:space="preserve">15.874249458313</t>
   </si>
   <si>
     <t xml:space="preserve">15.556056022644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7328281402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914096832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3439264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792819976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7782535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4247064590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5307693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600620269775</t>
+    <t xml:space="preserve">15.7328300476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914106369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3439292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7782526016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.424708366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5307683944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600601196289</t>
   </si>
   <si>
     <t xml:space="preserve">14.4954147338867</t>
@@ -1349,67 +1349,67 @@
     <t xml:space="preserve">13.8873138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1135854721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3186435699463</t>
+    <t xml:space="preserve">14.1135864257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.318642616272</t>
   </si>
   <si>
     <t xml:space="preserve">14.6014776229858</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0257368087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.061089515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9550256729126</t>
+    <t xml:space="preserve">15.0257349014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0610914230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9550266265869</t>
   </si>
   <si>
     <t xml:space="preserve">14.8489627838135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.884316444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7075424194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2025117874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5661268234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.636833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2832899093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0853033065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8136072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3539962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3893527984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428979873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1418704986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1772222518921</t>
+    <t xml:space="preserve">14.8843145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7075452804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671543121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2025098800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5661239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6368350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2832889556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0853004455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8136081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3539981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3893537521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.74289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1418695449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.177225112915</t>
   </si>
   <si>
     <t xml:space="preserve">14.247932434082</t>
@@ -1418,28 +1418,28 @@
     <t xml:space="preserve">14.2125787734985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0711584091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9438810348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8731737136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8166074752808</t>
+    <t xml:space="preserve">14.0711603164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9438848495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8731756210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8166065216064</t>
   </si>
   <si>
     <t xml:space="preserve">13.8590326309204</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0145931243896</t>
+    <t xml:space="preserve">14.0145921707153</t>
   </si>
   <si>
     <t xml:space="preserve">13.929741859436</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0004501342773</t>
+    <t xml:space="preserve">14.000449180603</t>
   </si>
   <si>
     <t xml:space="preserve">14.0994434356689</t>
@@ -1451,43 +1451,43 @@
     <t xml:space="preserve">14.0287351608276</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0570154190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1277275085449</t>
+    <t xml:space="preserve">14.057017326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1277265548706</t>
   </si>
   <si>
     <t xml:space="preserve">14.9196720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6721906661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4347763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5054874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4913425445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3782091140747</t>
+    <t xml:space="preserve">14.6721887588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.434775352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5054836273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.49134349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3782072067261</t>
   </si>
   <si>
     <t xml:space="preserve">13.4630603790283</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5620527267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5337677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1660833358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7842502593994</t>
+    <t xml:space="preserve">13.5620546340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5337686538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1660804748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7842483520508</t>
   </si>
   <si>
     <t xml:space="preserve">12.6852569580078</t>
@@ -1499,310 +1499,310 @@
     <t xml:space="preserve">12.6569728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4064903259277</t>
+    <t xml:space="preserve">13.4064922332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.5479097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7883224487305</t>
+    <t xml:space="preserve">13.7883243560791</t>
   </si>
   <si>
     <t xml:space="preserve">13.7741804122925</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5903358459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4489164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3074979782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.392352104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.01051902771</t>
+    <t xml:space="preserve">13.5903367996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.448917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3074998855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3923511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0105199813843</t>
   </si>
   <si>
     <t xml:space="preserve">13.1519384384155</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2933568954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.925669670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0388031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.996376991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2367897033691</t>
+    <t xml:space="preserve">13.2933559417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9256706237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0388021469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9963760375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2367887496948</t>
   </si>
   <si>
     <t xml:space="preserve">13.0953712463379</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6469039916992</t>
+    <t xml:space="preserve">13.6469020843506</t>
   </si>
   <si>
     <t xml:space="preserve">13.6751880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0670881271362</t>
+    <t xml:space="preserve">13.0670862197876</t>
   </si>
   <si>
     <t xml:space="preserve">13.2509298324585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2085065841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812292098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3499231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8408164978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5296945571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.897385597229</t>
+    <t xml:space="preserve">13.2085075378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812282562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3499240875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8408184051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5296964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8973846435547</t>
   </si>
   <si>
     <t xml:space="preserve">12.6004047393799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7317552566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5761957168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5196266174316</t>
+    <t xml:space="preserve">13.7317543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5761947631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5196285247803</t>
   </si>
   <si>
     <t xml:space="preserve">13.7176113128662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8307466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7600364685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.915599822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7458982467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0428781509399</t>
+    <t xml:space="preserve">13.8307485580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7600374221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9155988693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7458963394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0428771972656</t>
   </si>
   <si>
     <t xml:space="preserve">13.8448886871338</t>
   </si>
   <si>
-    <t xml:space="preserve">14.54176902771</t>
+    <t xml:space="preserve">14.5417671203613</t>
   </si>
   <si>
     <t xml:space="preserve">14.2218475341797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9455547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1782236099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9891796112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2073078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4399766921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.265474319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4108924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4981422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527221679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3381805419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5126838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3963489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4254341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4836015701294</t>
+    <t xml:space="preserve">13.9455556869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1782245635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9891815185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2073068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4399757385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2654733657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4108915328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.498143196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690561294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3381814956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5126829147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3963499069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871862411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4254331588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4836006164551</t>
   </si>
   <si>
     <t xml:space="preserve">14.6144762039185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8326025009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9780216217041</t>
+    <t xml:space="preserve">14.8326034545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9780206680298</t>
   </si>
   <si>
     <t xml:space="preserve">15.1234369277954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1961469650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4142751693726</t>
+    <t xml:space="preserve">15.1961460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4142742156982</t>
   </si>
   <si>
     <t xml:space="preserve">15.4506282806396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3415641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2325010299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3052091598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.268856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687526702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0507278442383</t>
+    <t xml:space="preserve">15.3415651321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2325000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3052082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2688541412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687545776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0507297515869</t>
   </si>
   <si>
     <t xml:space="preserve">15.0870847702026</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9416646957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7235403060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0143728256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5781202316284</t>
+    <t xml:space="preserve">14.9416666030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7235383987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0143747329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5781221389771</t>
   </si>
   <si>
     <t xml:space="preserve">14.7598934173584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6508302688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3672676086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3236417770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5272254943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.454514503479</t>
+    <t xml:space="preserve">14.6508293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3672657012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3236408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5272245407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4545154571533</t>
   </si>
   <si>
     <t xml:space="preserve">14.7962493896484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9053106307983</t>
+    <t xml:space="preserve">14.9053115844727</t>
   </si>
   <si>
     <t xml:space="preserve">16.0322971343994</t>
   </si>
   <si>
-    <t xml:space="preserve">16.359489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5049057006836</t>
+    <t xml:space="preserve">16.3594875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5049076080322</t>
   </si>
   <si>
     <t xml:space="preserve">16.6139698028564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5412635803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8320980072021</t>
+    <t xml:space="preserve">16.541259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8320941925049</t>
   </si>
   <si>
     <t xml:space="preserve">16.6503238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5776138305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8684501647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7593860626221</t>
+    <t xml:space="preserve">16.577615737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8684520721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7593841552734</t>
   </si>
   <si>
     <t xml:space="preserve">17.0502223968506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0865783691406</t>
+    <t xml:space="preserve">17.086576461792</t>
   </si>
   <si>
     <t xml:space="preserve">17.4864749908447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4137668609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2683506011963</t>
+    <t xml:space="preserve">17.4137649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2683486938477</t>
   </si>
   <si>
     <t xml:space="preserve">17.5228290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">17.813663482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7409553527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7046012878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6682472229004</t>
+    <t xml:space="preserve">17.8136653900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7409572601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.631893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7046031951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6682453155518</t>
   </si>
   <si>
     <t xml:space="preserve">18.0681476593018</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">17.9227275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1044998168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8500194549561</t>
+    <t xml:space="preserve">18.1045017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8500175476074</t>
   </si>
   <si>
     <t xml:space="preserve">17.9590854644775</t>
@@ -1829,25 +1829,25 @@
     <t xml:space="preserve">18.2862720489502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.358980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4680461883545</t>
+    <t xml:space="preserve">18.3589820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4680442810059</t>
   </si>
   <si>
     <t xml:space="preserve">18.5771064758301</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9954357147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5591831207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5955390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4501209259033</t>
+    <t xml:space="preserve">17.9954376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5591850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5955371856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4501190185547</t>
   </si>
   <si>
     <t xml:space="preserve">18.2499179840088</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">18.395336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2135639190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.322624206543</t>
+    <t xml:space="preserve">18.2135620117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3226280212402</t>
   </si>
   <si>
     <t xml:space="preserve">18.6134624481201</t>
@@ -1874,73 +1874,73 @@
     <t xml:space="preserve">19.1951332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9770069122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0860710144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2678394317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1224250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3041973114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4132614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4496116638184</t>
+    <t xml:space="preserve">18.9770050048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.086067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2678413391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1224231719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3041954040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4132595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4496154785156</t>
   </si>
   <si>
     <t xml:space="preserve">16.9048042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7230339050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321994781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7957401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2314872741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9775142669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3047027587891</t>
+    <t xml:space="preserve">16.7230319976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321975708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7957382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2314891815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9775123596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3047046661377</t>
   </si>
   <si>
     <t xml:space="preserve">17.3774127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7952346801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5407543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8679428100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9042987823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8495140075684</t>
+    <t xml:space="preserve">18.7952365875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5407524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8679447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9042949676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8495121002197</t>
   </si>
   <si>
     <t xml:space="preserve">19.4213848114014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7327499389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.394401550293</t>
+    <t xml:space="preserve">19.7327518463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3943996429443</t>
   </si>
   <si>
     <t xml:space="preserve">19.8105926513672</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">19.6549091339111</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3554801940918</t>
+    <t xml:space="preserve">20.3554821014404</t>
   </si>
   <si>
     <t xml:space="preserve">20.1219577789307</t>
@@ -1961,22 +1961,22 @@
     <t xml:space="preserve">19.4603061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3435440063477</t>
+    <t xml:space="preserve">19.3435459136963</t>
   </si>
   <si>
     <t xml:space="preserve">19.3046226501465</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9662742614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2657051086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.771671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7597351074219</t>
+    <t xml:space="preserve">19.966272354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2657032012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7716693878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7597370147705</t>
   </si>
   <si>
     <t xml:space="preserve">20.1608772277832</t>
@@ -2003,16 +2003,16 @@
     <t xml:space="preserve">20.7836074829102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7057647705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0949726104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.445255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7566242218018</t>
+    <t xml:space="preserve">20.7057685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.094970703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4452571868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7566223144531</t>
   </si>
   <si>
     <t xml:space="preserve">21.9512252807617</t>
@@ -2024,25 +2024,25 @@
     <t xml:space="preserve">21.7955436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0290660858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0679874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5350360870361</t>
+    <t xml:space="preserve">22.0290679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.067985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5350341796875</t>
   </si>
   <si>
     <t xml:space="preserve">22.5739555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">22.651798248291</t>
+    <t xml:space="preserve">22.6517963409424</t>
   </si>
   <si>
     <t xml:space="preserve">22.7685585021973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8074779510498</t>
+    <t xml:space="preserve">22.8074760437012</t>
   </si>
   <si>
     <t xml:space="preserve">22.7296390533447</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">23.5080509185791</t>
   </si>
   <si>
-    <t xml:space="preserve">23.97509765625</t>
+    <t xml:space="preserve">23.9750957489014</t>
   </si>
   <si>
     <t xml:space="preserve">24.4032249450684</t>
@@ -2069,22 +2069,22 @@
     <t xml:space="preserve">24.7145881652832</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5199871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2983989715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7924327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1427173614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7535076141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6367492675781</t>
+    <t xml:space="preserve">24.5199851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.298397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7924308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1427154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7535095214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6367473602295</t>
   </si>
   <si>
     <t xml:space="preserve">24.1697006225586</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">24.0140190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0799236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7026519775391</t>
+    <t xml:space="preserve">23.0799255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7026538848877</t>
   </si>
   <si>
     <t xml:space="preserve">24.0529384613037</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">23.1577663421631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8583354949951</t>
+    <t xml:space="preserve">23.8583335876465</t>
   </si>
   <si>
     <t xml:space="preserve">23.7415733337402</t>
@@ -2120,10 +2120,10 @@
     <t xml:space="preserve">23.8194160461426</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6637325286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4302082061768</t>
+    <t xml:space="preserve">23.6637306213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4302101135254</t>
   </si>
   <si>
     <t xml:space="preserve">24.0918598175049</t>
@@ -2138,19 +2138,19 @@
     <t xml:space="preserve">23.0410022735596</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0020809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1188449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6248111724854</t>
+    <t xml:space="preserve">23.0020790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1188430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.624813079834</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128749847412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1069068908691</t>
+    <t xml:space="preserve">22.1069087982178</t>
   </si>
   <si>
     <t xml:space="preserve">22.1847476959229</t>
@@ -2159,31 +2159,31 @@
     <t xml:space="preserve">22.496114730835</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3015098571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6907157897949</t>
+    <t xml:space="preserve">22.3015117645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6907176971436</t>
   </si>
   <si>
     <t xml:space="preserve">22.3793525695801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9631595611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2356071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9242420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.223669052124</t>
+    <t xml:space="preserve">22.9631633758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2356052398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9242401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2236709594727</t>
   </si>
   <si>
     <t xml:space="preserve">22.4182739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9123058319092</t>
+    <t xml:space="preserve">21.9123039245605</t>
   </si>
   <si>
     <t xml:space="preserve">21.4841766357422</t>
@@ -2192,19 +2192,19 @@
     <t xml:space="preserve">21.1338920593262</t>
   </si>
   <si>
-    <t xml:space="preserve">21.523099899292</t>
+    <t xml:space="preserve">21.5230979919434</t>
   </si>
   <si>
     <t xml:space="preserve">21.717700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6398582458496</t>
+    <t xml:space="preserve">21.6398601531982</t>
   </si>
   <si>
     <t xml:space="preserve">21.2506542205811</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5620193481445</t>
+    <t xml:space="preserve">21.5620212554932</t>
   </si>
   <si>
     <t xml:space="preserve">21.8344631195068</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">22.1458282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">22.846399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8853206634521</t>
+    <t xml:space="preserve">22.8464012145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8853187561035</t>
   </si>
   <si>
     <t xml:space="preserve">22.4571933746338</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">21.3284950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2117347717285</t>
+    <t xml:space="preserve">21.2117328643799</t>
   </si>
   <si>
     <t xml:space="preserve">21.3674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9782085418701</t>
+    <t xml:space="preserve">20.9782104492188</t>
   </si>
   <si>
     <t xml:space="preserve">20.6279239654541</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8733863830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4407329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8835639953613</t>
+    <t xml:space="preserve">21.873384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.440731048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.88356590271</t>
   </si>
   <si>
     <t xml:space="preserve">22.7243747711182</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">22.7641735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0427551269531</t>
+    <t xml:space="preserve">23.0427570343018</t>
   </si>
   <si>
     <t xml:space="preserve">23.2417449951172</t>
@@ -2270,10 +2270,10 @@
     <t xml:space="preserve">23.0029582977295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2019443511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1223487854004</t>
+    <t xml:space="preserve">23.2019462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.122350692749</t>
   </si>
   <si>
     <t xml:space="preserve">23.1621494293213</t>
@@ -2285,34 +2285,34 @@
     <t xml:space="preserve">23.9580993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0774917602539</t>
+    <t xml:space="preserve">24.0774898529053</t>
   </si>
   <si>
     <t xml:space="preserve">24.4356689453125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3162727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3560733795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7938461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1570854187012</t>
+    <t xml:space="preserve">24.3162746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3560752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7938442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1570873260498</t>
   </si>
   <si>
     <t xml:space="preserve">24.6744537353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.913236618042</t>
+    <t xml:space="preserve">24.9132385253906</t>
   </si>
   <si>
     <t xml:space="preserve">24.555061340332</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7540493011475</t>
+    <t xml:space="preserve">24.7540473937988</t>
   </si>
   <si>
     <t xml:space="preserve">24.2764778137207</t>
@@ -2321,28 +2321,28 @@
     <t xml:space="preserve">24.1172885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5152626037598</t>
+    <t xml:space="preserve">24.5152645111084</t>
   </si>
   <si>
     <t xml:space="preserve">24.4754657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2366790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3958702087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7142505645752</t>
+    <t xml:space="preserve">24.2366828918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3958721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7142486572266</t>
   </si>
   <si>
     <t xml:space="preserve">24.6346569061279</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1968822479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6295928955078</t>
+    <t xml:space="preserve">24.1968841552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6295948028564</t>
   </si>
   <si>
     <t xml:space="preserve">25.5102005004883</t>
@@ -2357,31 +2357,31 @@
     <t xml:space="preserve">25.4704036712646</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6693897247314</t>
+    <t xml:space="preserve">25.6693916320801</t>
   </si>
   <si>
     <t xml:space="preserve">25.3908100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">25.191822052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0326328277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2714176177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8336448669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9530353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8683776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0724277496338</t>
+    <t xml:space="preserve">25.1918201446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0326309204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2714138031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8336429595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9530372619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8683795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0724296569824</t>
   </si>
   <si>
     <t xml:space="preserve">23.7591114044189</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">25.430606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3112144470215</t>
+    <t xml:space="preserve">25.3112125396729</t>
   </si>
   <si>
     <t xml:space="preserve">25.2316188812256</t>
@@ -2417,37 +2417,37 @@
     <t xml:space="preserve">26.0673656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2663516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0275707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7887840270996</t>
+    <t xml:space="preserve">26.2663536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0275688171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7887878417969</t>
   </si>
   <si>
     <t xml:space="preserve">25.5499992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5897960662842</t>
+    <t xml:space="preserve">25.5897979736328</t>
   </si>
   <si>
     <t xml:space="preserve">25.9479732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1071643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7489833831787</t>
+    <t xml:space="preserve">26.1071624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7489852905273</t>
   </si>
   <si>
     <t xml:space="preserve">24.8734397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0376949310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3264007568359</t>
+    <t xml:space="preserve">24.0376930236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3263988494873</t>
   </si>
   <si>
     <t xml:space="preserve">22.3661975860596</t>
@@ -2456,31 +2456,31 @@
     <t xml:space="preserve">23.0825538635254</t>
   </si>
   <si>
-    <t xml:space="preserve">22.923360824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3213386535645</t>
+    <t xml:space="preserve">22.9233646392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3213367462158</t>
   </si>
   <si>
     <t xml:space="preserve">23.5999202728271</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3611373901367</t>
+    <t xml:space="preserve">23.3611354827881</t>
   </si>
   <si>
     <t xml:space="preserve">23.4009323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5601234436035</t>
+    <t xml:space="preserve">23.5601215362549</t>
   </si>
   <si>
     <t xml:space="preserve">22.4855918884277</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8387069702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.997896194458</t>
+    <t xml:space="preserve">23.8387050628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9978942871094</t>
   </si>
   <si>
     <t xml:space="preserve">23.7193126678467</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">23.8264102935791</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5692920684814</t>
+    <t xml:space="preserve">23.5692901611328</t>
   </si>
   <si>
     <t xml:space="preserve">24.1263828277588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9549713134766</t>
+    <t xml:space="preserve">23.9549694061279</t>
   </si>
   <si>
     <t xml:space="preserve">24.4692077636719</t>
@@ -2504,13 +2504,13 @@
     <t xml:space="preserve">24.4263553619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1692371368408</t>
+    <t xml:space="preserve">24.1692352294922</t>
   </si>
   <si>
     <t xml:space="preserve">24.2120895385742</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7835578918457</t>
+    <t xml:space="preserve">23.7835559844971</t>
   </si>
   <si>
     <t xml:space="preserve">24.340648651123</t>
@@ -2525,13 +2525,13 @@
     <t xml:space="preserve">23.5264377593994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9978218078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9121150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8692626953125</t>
+    <t xml:space="preserve">23.99782371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9121170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8692646026611</t>
   </si>
   <si>
     <t xml:space="preserve">23.7407035827637</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">23.6549968719482</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9693450927734</t>
+    <t xml:space="preserve">22.9693431854248</t>
   </si>
   <si>
     <t xml:space="preserve">22.8836402893066</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">22.5836658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9264907836914</t>
+    <t xml:space="preserve">22.92649269104</t>
   </si>
   <si>
     <t xml:space="preserve">23.1407585144043</t>
@@ -2558,10 +2558,10 @@
     <t xml:space="preserve">22.8407859802246</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7550792694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6693725585938</t>
+    <t xml:space="preserve">22.7550773620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6693744659424</t>
   </si>
   <si>
     <t xml:space="preserve">23.0550518035889</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">23.3550243377686</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0121994018555</t>
+    <t xml:space="preserve">23.0121974945068</t>
   </si>
   <si>
     <t xml:space="preserve">23.3121719360352</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">22.7979316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4551048278809</t>
+    <t xml:space="preserve">22.4551086425781</t>
   </si>
   <si>
     <t xml:space="preserve">22.4979591369629</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">22.6265182495117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6978511810303</t>
+    <t xml:space="preserve">23.6978492736816</t>
   </si>
   <si>
     <t xml:space="preserve">22.5408115386963</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2693157196045</t>
+    <t xml:space="preserve">23.2693176269531</t>
   </si>
   <si>
     <t xml:space="preserve">22.2836933135986</t>
@@ -2633,16 +2633,16 @@
     <t xml:space="preserve">20.826681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9267635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1410312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9980945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1266555786133</t>
+    <t xml:space="preserve">19.9267616271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1410293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9980964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1266536712646</t>
   </si>
   <si>
     <t xml:space="preserve">20.5267105102539</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">20.6552696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3124446868896</t>
+    <t xml:space="preserve">20.312442779541</t>
   </si>
   <si>
     <t xml:space="preserve">20.4410037994385</t>
@@ -2660,19 +2660,19 @@
     <t xml:space="preserve">20.6981220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5980434417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3837738037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5123348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3409214019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.026575088501</t>
+    <t xml:space="preserve">21.5980415344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3837757110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.512336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3409194946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0265731811523</t>
   </si>
   <si>
     <t xml:space="preserve">22.1122798919678</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">22.1551342010498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2408409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6837463378906</t>
+    <t xml:space="preserve">22.2408390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6837482452393</t>
   </si>
   <si>
     <t xml:space="preserve">21.7266006469727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8980121612549</t>
+    <t xml:space="preserve">21.8980140686035</t>
   </si>
   <si>
     <t xml:space="preserve">21.7694530487061</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.0694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9837188720703</t>
+    <t xml:space="preserve">21.9837207794189</t>
   </si>
   <si>
     <t xml:space="preserve">21.8551597595215</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">21.0838012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9408683776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5551872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0409469604492</t>
+    <t xml:space="preserve">21.9408664703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5551853179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0409488677979</t>
   </si>
   <si>
     <t xml:space="preserve">20.912389755249</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">20.7409763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1838836669922</t>
+    <t xml:space="preserve">20.1838817596436</t>
   </si>
   <si>
     <t xml:space="preserve">20.3552951812744</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">22.0611591339111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1051940917969</t>
+    <t xml:space="preserve">22.1051959991455</t>
   </si>
   <si>
     <t xml:space="preserve">22.017126083374</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">21.664852142334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5767822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4887142181396</t>
+    <t xml:space="preserve">21.5767841339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4887161254883</t>
   </si>
   <si>
     <t xml:space="preserve">21.9290561676025</t>
@@ -2792,22 +2792,22 @@
     <t xml:space="preserve">21.8409881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7088871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4006443023682</t>
+    <t xml:space="preserve">21.7088851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4006462097168</t>
   </si>
   <si>
     <t xml:space="preserve">21.7969551086426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9730911254883</t>
+    <t xml:space="preserve">21.9730930328369</t>
   </si>
   <si>
     <t xml:space="preserve">21.7529201507568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.501501083374</t>
+    <t xml:space="preserve">22.5015029907227</t>
   </si>
   <si>
     <t xml:space="preserve">22.2372970581055</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">22.3253650665283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5455379486084</t>
+    <t xml:space="preserve">22.5455360412598</t>
   </si>
   <si>
     <t xml:space="preserve">22.149227142334</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">21.0483722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3566131591797</t>
+    <t xml:space="preserve">21.3566112518311</t>
   </si>
   <si>
     <t xml:space="preserve">21.6208171844482</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">21.4446811676025</t>
   </si>
   <si>
-    <t xml:space="preserve">21.532751083374</t>
+    <t xml:space="preserve">21.5327491760254</t>
   </si>
   <si>
     <t xml:space="preserve">21.0043392181396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8722362518311</t>
+    <t xml:space="preserve">20.8722343444824</t>
   </si>
   <si>
     <t xml:space="preserve">20.6960983276367</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">20.2557563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3878574371338</t>
+    <t xml:space="preserve">20.3878593444824</t>
   </si>
   <si>
     <t xml:space="preserve">20.2997894287109</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">20.7841682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9603042602539</t>
+    <t xml:space="preserve">20.9603023529053</t>
   </si>
   <si>
     <t xml:space="preserve">20.7401313781738</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">21.1804752349854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6336078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4574699401855</t>
+    <t xml:space="preserve">22.6336059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4574680328369</t>
   </si>
   <si>
     <t xml:space="preserve">22.5895709991455</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">24.3949756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">24.30690574646</t>
+    <t xml:space="preserve">24.3069076538086</t>
   </si>
   <si>
     <t xml:space="preserve">24.1307697296143</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">24.3509407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4390106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5711116790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6591796875</t>
+    <t xml:space="preserve">24.4390087127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5711135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6591815948486</t>
   </si>
   <si>
     <t xml:space="preserve">24.7032146453857</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">24.0867366790771</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2188396453857</t>
+    <t xml:space="preserve">24.2188377380371</t>
   </si>
   <si>
     <t xml:space="preserve">24.1748046875</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">23.9546337127686</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7600364685059</t>
+    <t xml:space="preserve">25.7600383758545</t>
   </si>
   <si>
     <t xml:space="preserve">25.4077625274658</t>
@@ -2987,19 +2987,19 @@
     <t xml:space="preserve">26.1123104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1563453674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4645862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5910167694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3708457946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8992595672607</t>
+    <t xml:space="preserve">26.1563472747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4645843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5910148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3708438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8992576599121</t>
   </si>
   <si>
     <t xml:space="preserve">30.0313587188721</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">29.5029487609863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7671546936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2827758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0753974914551</t>
+    <t xml:space="preserve">29.7671527862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2827777862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0753955841064</t>
   </si>
   <si>
     <t xml:space="preserve">29.7231216430664</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">30.471700668335</t>
   </si>
   <si>
-    <t xml:space="preserve">29.811185836792</t>
+    <t xml:space="preserve">29.8111877441406</t>
   </si>
   <si>
     <t xml:space="preserve">29.2387447357178</t>
@@ -3044,28 +3044,28 @@
     <t xml:space="preserve">28.7103309631348</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8424339294434</t>
+    <t xml:space="preserve">28.842435836792</t>
   </si>
   <si>
     <t xml:space="preserve">28.8864688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5469837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2955646514893</t>
+    <t xml:space="preserve">29.5469818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2955665588379</t>
   </si>
   <si>
     <t xml:space="preserve">30.7359104156494</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3836345672607</t>
+    <t xml:space="preserve">30.3836326599121</t>
   </si>
   <si>
     <t xml:space="preserve">29.9873237609863</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4276695251465</t>
+    <t xml:space="preserve">30.4276676177979</t>
   </si>
   <si>
     <t xml:space="preserve">29.4632396697998</t>
@@ -68863,7 +68863,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6495949074</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>14148</v>
@@ -68884,6 +68884,32 @@
         <v>1222</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6494791667</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>22662</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>32.9000015258789</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>32.9500007629395</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>33</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="1223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="1224">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,91 +38,91 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8067150115967</t>
+    <t xml:space="preserve">13.8067121505737</t>
   </si>
   <si>
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.057746887207</t>
+    <t xml:space="preserve">14.0577459335327</t>
   </si>
   <si>
     <t xml:space="preserve">13.9573335647583</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3883295059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8896141052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8527975082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9532079696655</t>
+    <t xml:space="preserve">13.3883285522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896131515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8527946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9532070159912</t>
   </si>
   <si>
     <t xml:space="preserve">12.6184997558594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4846143722534</t>
+    <t xml:space="preserve">12.4846162796021</t>
   </si>
   <si>
     <t xml:space="preserve">12.3842039108276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8821411132812</t>
+    <t xml:space="preserve">11.8821420669556</t>
   </si>
   <si>
     <t xml:space="preserve">11.7348699569702</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2127265930176</t>
+    <t xml:space="preserve">11.2127256393433</t>
   </si>
   <si>
     <t xml:space="preserve">10.7307462692261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2294597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2194194793701</t>
+    <t xml:space="preserve">11.2294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2194204330444</t>
   </si>
   <si>
     <t xml:space="preserve">11.2461948394775</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9148349761963</t>
+    <t xml:space="preserve">10.9148359298706</t>
   </si>
   <si>
     <t xml:space="preserve">11.1323957443237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6143751144409</t>
+    <t xml:space="preserve">11.6143760681152</t>
   </si>
   <si>
     <t xml:space="preserve">11.6813182830811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474338531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3466091156006</t>
+    <t xml:space="preserve">11.5474328994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.346607208252</t>
   </si>
   <si>
     <t xml:space="preserve">11.313136100769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3298721313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8947525024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8780174255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0453729629517</t>
+    <t xml:space="preserve">11.329873085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8947515487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8780155181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.045371055603</t>
   </si>
   <si>
     <t xml:space="preserve">10.4261608123779</t>
@@ -131,25 +131,25 @@
     <t xml:space="preserve">10.4094257354736</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7080936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7147884368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0494966506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7482576370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.744912147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2135019302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168483734131</t>
+    <t xml:space="preserve">11.7080926895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7147874832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0494956970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7482595443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7449111938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2135028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168493270874</t>
   </si>
   <si>
     <t xml:space="preserve">12.3674697875977</t>
@@ -158,136 +158,136 @@
     <t xml:space="preserve">12.7189121246338</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8293676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0201511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2209730148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3849840164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870904922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536203384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3347749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3146915435791</t>
+    <t xml:space="preserve">12.82936668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0201482772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2209739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3849821090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870923995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536222457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3347759246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3146924972534</t>
   </si>
   <si>
     <t xml:space="preserve">13.0569677352905</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2109327316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306047439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2879190444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8260183334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9833316802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9030017852783</t>
+    <t xml:space="preserve">13.2109336853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661832809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.287917137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.826021194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9833326339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.903000831604</t>
   </si>
   <si>
     <t xml:space="preserve">13.2377090454102</t>
   </si>
   <si>
-    <t xml:space="preserve">13.167423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1138668060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5047006607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8092823028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.886266708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7055225372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7222595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.916389465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0301904678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327131271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6318893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7021760940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8695316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5582523345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5682935714722</t>
+    <t xml:space="preserve">13.1674222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.113865852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971326828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5047016143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8092851638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8862648010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7055234909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7222585678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.916392326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0301895141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6318883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7021770477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8695306777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5582504272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5682916641235</t>
   </si>
   <si>
     <t xml:space="preserve">12.8360605239868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8494491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958955764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5348243713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7791595458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7691173553467</t>
+    <t xml:space="preserve">12.8494482040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958936691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5348224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7791614532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7691192626953</t>
   </si>
   <si>
     <t xml:space="preserve">12.7865657806396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5024213790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6512575149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7527389526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5836048126221</t>
+    <t xml:space="preserve">12.502420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6512584686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7527408599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5836057662964</t>
   </si>
   <si>
     <t xml:space="preserve">12.4990377426147</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">12.5159511566162</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2791633605957</t>
+    <t xml:space="preserve">12.2791614532471</t>
   </si>
   <si>
     <t xml:space="preserve">12.0660533905029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1776828765869</t>
+    <t xml:space="preserve">12.1776819229126</t>
   </si>
   <si>
     <t xml:space="preserve">12.1641511917114</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">12.170916557312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1100282669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1269416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9814853668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7459735870361</t>
+    <t xml:space="preserve">12.1100263595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1269397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9814863204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7459726333618</t>
   </si>
   <si>
     <t xml:space="preserve">12.6580247879028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3231391906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6973400115967</t>
+    <t xml:space="preserve">12.3231372833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.697340965271</t>
   </si>
   <si>
     <t xml:space="preserve">11.7785243988037</t>
@@ -344,43 +344,43 @@
     <t xml:space="preserve">10.8212232589722</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6554708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.061393737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.196702003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4064283370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5248222351074</t>
+    <t xml:space="preserve">10.6554718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0613946914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1967010498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4064273834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5248231887817</t>
   </si>
   <si>
     <t xml:space="preserve">10.6656198501587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1886596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.587818145752</t>
+    <t xml:space="preserve">10.1886606216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5878171920776</t>
   </si>
   <si>
     <t xml:space="preserve">10.6825323104858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8394136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0199737548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3616228103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0233545303345</t>
+    <t xml:space="preserve">11.839412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0199718475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3616218566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0233535766602</t>
   </si>
   <si>
     <t xml:space="preserve">13.1924886703491</t>
@@ -389,19 +389,19 @@
     <t xml:space="preserve">13.4969310760498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4698686599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307588577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4800186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2939691543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108835220337</t>
+    <t xml:space="preserve">13.4698696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307569503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4800157546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2939710617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108825683594</t>
   </si>
   <si>
     <t xml:space="preserve">13.3548583984375</t>
@@ -413,64 +413,64 @@
     <t xml:space="preserve">13.03688621521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9489326477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.982762336731</t>
+    <t xml:space="preserve">12.948935508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9827632904053</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910081863403</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0707120895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9962921142578</t>
+    <t xml:space="preserve">13.0707101821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9962930679321</t>
   </si>
   <si>
     <t xml:space="preserve">12.8576021194458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1113023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1248340606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1823415756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0605630874634</t>
+    <t xml:space="preserve">13.1113033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1248350143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1823396682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0605659484863</t>
   </si>
   <si>
     <t xml:space="preserve">13.1857242584229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4123620986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5679683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4157466888428</t>
+    <t xml:space="preserve">13.4123640060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5679693222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4157457351685</t>
   </si>
   <si>
     <t xml:space="preserve">13.513843536377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7066564559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8352012634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2106800079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.457615852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7552919387817</t>
+    <t xml:space="preserve">13.706657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8352022171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2106790542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4576168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7552900314331</t>
   </si>
   <si>
     <t xml:space="preserve">14.8838329315186</t>
@@ -479,58 +479,58 @@
     <t xml:space="preserve">15.0157594680786</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9853134155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303499221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6652326583862</t>
+    <t xml:space="preserve">14.985315322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6652345657349</t>
   </si>
   <si>
     <t xml:space="preserve">15.289755821228</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8297090530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7722043991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9514856338501</t>
+    <t xml:space="preserve">14.8297119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.684253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7722072601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.951491355896</t>
   </si>
   <si>
     <t xml:space="preserve">14.7485256195068</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7180805206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8770666122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7992649078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9007472991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2018041610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939809799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330907821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988441467285</t>
+    <t xml:space="preserve">14.7180824279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.877067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7992677688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751653671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9007482528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2018032073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939828872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330936431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988460540771</t>
   </si>
   <si>
     <t xml:space="preserve">14.9142780303955</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">14.9278106689453</t>
   </si>
   <si>
-    <t xml:space="preserve">14.738377571106</t>
+    <t xml:space="preserve">14.7383813858032</t>
   </si>
   <si>
     <t xml:space="preserve">14.7248468399048</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5421810150146</t>
+    <t xml:space="preserve">14.5421838760376</t>
   </si>
   <si>
     <t xml:space="preserve">14.4440841674805</t>
@@ -554,58 +554,58 @@
     <t xml:space="preserve">15.0529680252075</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1442975997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1104726791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9548692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0901775360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2187185287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7823534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6166000366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764276504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1599369049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2546529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.041543006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1125812530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0381622314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1430263519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903800964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527488708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2072973251343</t>
+    <t xml:space="preserve">15.1443014144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1104736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9548683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0901784896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2187194824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7823553085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6166009902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764305114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1599378585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2546520233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0415439605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1125802993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.038161277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1430253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903810501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527498245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2072954177856</t>
   </si>
   <si>
     <t xml:space="preserve">14.3561344146729</t>
@@ -614,49 +614,49 @@
     <t xml:space="preserve">14.4373178482056</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3730487823486</t>
+    <t xml:space="preserve">14.3730506896973</t>
   </si>
   <si>
     <t xml:space="preserve">14.3087768554688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2411212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3392200469971</t>
+    <t xml:space="preserve">14.2411231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3392210006714</t>
   </si>
   <si>
     <t xml:space="preserve">14.2512722015381</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1464061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058158874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1193447113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2275896072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2715644836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1497917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0753698348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0719881057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749500274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667032241821</t>
+    <t xml:space="preserve">14.1464080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058149337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1193475723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.227593421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2715673446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1497898101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0753726959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0719871520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749490737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667022705078</t>
   </si>
   <si>
     <t xml:space="preserve">14.4779100418091</t>
@@ -665,133 +665,133 @@
     <t xml:space="preserve">14.6267499923706</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7519102096558</t>
+    <t xml:space="preserve">14.7519092559814</t>
   </si>
   <si>
     <t xml:space="preserve">14.8161792755127</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1037073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0834131240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172389984131</t>
+    <t xml:space="preserve">15.1037082672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0834121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882734298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172409057617</t>
   </si>
   <si>
     <t xml:space="preserve">15.154447555542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2999048233032</t>
+    <t xml:space="preserve">15.2999029159546</t>
   </si>
   <si>
     <t xml:space="preserve">15.4758024215698</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3574113845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3912401199341</t>
+    <t xml:space="preserve">15.3574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3912343978882</t>
   </si>
   <si>
     <t xml:space="preserve">15.4893350601196</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1713609695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1003246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946180343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3168172836304</t>
+    <t xml:space="preserve">15.1713619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1003255844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3168153762817</t>
   </si>
   <si>
     <t xml:space="preserve">15.3134346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4182977676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4250631332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366945266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6753826141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6449375152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7295074462891</t>
+    <t xml:space="preserve">15.4182968139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4250650405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366926193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6753835678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6449365615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7295064926147</t>
   </si>
   <si>
     <t xml:space="preserve">15.6618509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6517028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6821489334106</t>
+    <t xml:space="preserve">15.6517038345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.682147026062</t>
   </si>
   <si>
     <t xml:space="preserve">15.5637531280518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4081506729126</t>
+    <t xml:space="preserve">15.4081497192383</t>
   </si>
   <si>
     <t xml:space="preserve">15.6415576934814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7024440765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584711074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588899612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5874328613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6550855636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227401733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3350086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0339469909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4060459136963</t>
+    <t xml:space="preserve">15.7024421691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333070755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584672927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5874338150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6550874710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227392196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3350048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0339508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4060440063477</t>
   </si>
   <si>
     <t xml:space="preserve">16.4026622772217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4195728302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6935691833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0994930267334</t>
+    <t xml:space="preserve">16.4195747375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6935729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.099494934082</t>
   </si>
   <si>
     <t xml:space="preserve">16.9980144500732</t>
@@ -803,28 +803,28 @@
     <t xml:space="preserve">17.4208507537842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5392456054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6407241821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4039344787598</t>
+    <t xml:space="preserve">17.5392436981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6407260894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4039363861084</t>
   </si>
   <si>
     <t xml:space="preserve">17.48850440979</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3531951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3870258331299</t>
+    <t xml:space="preserve">17.3531970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3870239257812</t>
   </si>
   <si>
     <t xml:space="preserve">17.522331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4546756744385</t>
+    <t xml:space="preserve">17.4546775817871</t>
   </si>
   <si>
     <t xml:space="preserve">17.877513885498</t>
@@ -833,22 +833,22 @@
     <t xml:space="preserve">17.8098583221436</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7083797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7591209411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6745491027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5730724334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3362846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2009773254395</t>
+    <t xml:space="preserve">17.7083778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7591228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6745548248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.573070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3362827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2009754180908</t>
   </si>
   <si>
     <t xml:space="preserve">17.2348041534424</t>
@@ -857,31 +857,31 @@
     <t xml:space="preserve">17.2517166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2178916931152</t>
+    <t xml:space="preserve">17.2178897857666</t>
   </si>
   <si>
     <t xml:space="preserve">17.3701095581055</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4560203552246</t>
+    <t xml:space="preserve">17.456018447876</t>
   </si>
   <si>
     <t xml:space="preserve">17.7147541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5767631530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.559513092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4698181152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6147117614746</t>
+    <t xml:space="preserve">17.5767650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5595149993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975059509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.469820022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6147136688232</t>
   </si>
   <si>
     <t xml:space="preserve">16.7729568481445</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">17.1662349700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1317367553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9937438964844</t>
+    <t xml:space="preserve">17.1317386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.993745803833</t>
   </si>
   <si>
     <t xml:space="preserve">16.9868469238281</t>
@@ -908,25 +908,25 @@
     <t xml:space="preserve">16.8350524902344</t>
   </si>
   <si>
-    <t xml:space="preserve">16.84885597229</t>
+    <t xml:space="preserve">16.8488540649414</t>
   </si>
   <si>
     <t xml:space="preserve">16.8281555175781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7591590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8695545196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9178504943848</t>
+    <t xml:space="preserve">16.7591609954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.869556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9178466796875</t>
   </si>
   <si>
     <t xml:space="preserve">16.9730472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9385471343994</t>
+    <t xml:space="preserve">16.9385509490967</t>
   </si>
   <si>
     <t xml:space="preserve">17.1524353027344</t>
@@ -935,22 +935,22 @@
     <t xml:space="preserve">16.6625633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5935668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5659675598145</t>
+    <t xml:space="preserve">16.5935688018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5659713745117</t>
   </si>
   <si>
     <t xml:space="preserve">16.5038738250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626518249512</t>
+    <t xml:space="preserve">16.8626537322998</t>
   </si>
   <si>
     <t xml:space="preserve">16.9040489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8005599975586</t>
+    <t xml:space="preserve">16.80055809021</t>
   </si>
   <si>
     <t xml:space="preserve">16.8971500396729</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">16.5383720397949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5590686798096</t>
+    <t xml:space="preserve">16.5590705871582</t>
   </si>
   <si>
     <t xml:space="preserve">16.4900722503662</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">16.2416877746582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3037815093994</t>
+    <t xml:space="preserve">16.3037853240967</t>
   </si>
   <si>
     <t xml:space="preserve">16.2485866546631</t>
@@ -983,10 +983,10 @@
     <t xml:space="preserve">16.1588916778564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5314712524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2899837493896</t>
+    <t xml:space="preserve">16.5314693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2899875640869</t>
   </si>
   <si>
     <t xml:space="preserve">16.3175830841064</t>
@@ -995,73 +995,73 @@
     <t xml:space="preserve">16.5452709197998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3658790588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.462474822998</t>
+    <t xml:space="preserve">16.3658809661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4624767303467</t>
   </si>
   <si>
     <t xml:space="preserve">16.3313827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3520832061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6970615386963</t>
+    <t xml:space="preserve">16.3520812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6970653533936</t>
   </si>
   <si>
     <t xml:space="preserve">16.3865814208984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4486770629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5107746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4210777282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4348735809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3934783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4969730377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5245723724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4003791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4555778503418</t>
+    <t xml:space="preserve">16.448673248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5107727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4210758209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4348773956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3934803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.496976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5245742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4003829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4555759429932</t>
   </si>
   <si>
     <t xml:space="preserve">16.358980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2830867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5521697998047</t>
+    <t xml:space="preserve">16.2830848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5521717071533</t>
   </si>
   <si>
     <t xml:space="preserve">16.1795921325684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2071895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1933879852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9036054611206</t>
+    <t xml:space="preserve">16.2071914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1933917999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9036092758179</t>
   </si>
   <si>
     <t xml:space="preserve">15.5586252212524</t>
@@ -1070,181 +1070,181 @@
     <t xml:space="preserve">15.4965305328369</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9381065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7794151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7656145095825</t>
+    <t xml:space="preserve">15.9381055831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7794170379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7656154632568</t>
   </si>
   <si>
     <t xml:space="preserve">15.7863130569458</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9795017242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9312047958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.703516960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6483211517334</t>
+    <t xml:space="preserve">15.9795007705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9312076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7035188674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6483221054077</t>
   </si>
   <si>
     <t xml:space="preserve">15.8415098190308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7518148422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691082000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.862208366394</t>
+    <t xml:space="preserve">15.7518177032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691091537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.862211227417</t>
   </si>
   <si>
     <t xml:space="preserve">16.0277976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8967056274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6276226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7173156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310287475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413328170776</t>
+    <t xml:space="preserve">15.8967084884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6276235580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7173185348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310258865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034313201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413290023804</t>
   </si>
   <si>
     <t xml:space="preserve">15.248143196106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3171405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3309383392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2826414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792371749878</t>
+    <t xml:space="preserve">15.3171415328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3309392929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.282642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792343139648</t>
   </si>
   <si>
     <t xml:space="preserve">15.2619438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">15.600025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896306991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9519033432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.972601890564</t>
+    <t xml:space="preserve">15.6000270843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896335601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9519062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9726047515869</t>
   </si>
   <si>
     <t xml:space="preserve">15.9864025115967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0416011810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8553113937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932138442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2895393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1791486740112</t>
+    <t xml:space="preserve">16.041597366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8553075790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.793212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2895412445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1791477203369</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067461013794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3999366760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2343444824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3033409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137372970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.386137008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6345205307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1450939178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4831733703613</t>
+    <t xml:space="preserve">15.3999347686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2343435287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033428192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137353897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3861351013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6345224380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.145092010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.48317527771</t>
   </si>
   <si>
     <t xml:space="preserve">16.6073684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3727798461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6349658966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141807556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0898971557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2002925872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.731559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6901607513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4762725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7522602081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6487655639648</t>
+    <t xml:space="preserve">16.37278175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6349678039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141788482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0898952484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7315616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6901626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4762744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7522583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6487636566162</t>
   </si>
   <si>
     <t xml:space="preserve">16.6280651092529</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0420455932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0765399932861</t>
+    <t xml:space="preserve">17.0420436859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0765419006348</t>
   </si>
   <si>
     <t xml:space="preserve">17.1110382080078</t>
@@ -1253,61 +1253,61 @@
     <t xml:space="preserve">17.2145328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1455364227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1800346374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0071029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2140922546387</t>
+    <t xml:space="preserve">17.1455402374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1800365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.00710105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2140865325928</t>
   </si>
   <si>
     <t xml:space="preserve">16.110595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5931215286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621217727661</t>
+    <t xml:space="preserve">15.5931243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621198654175</t>
   </si>
   <si>
     <t xml:space="preserve">15.0066576004028</t>
   </si>
   <si>
-    <t xml:space="preserve">14.730673789978</t>
+    <t xml:space="preserve">14.7306756973267</t>
   </si>
   <si>
     <t xml:space="preserve">14.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9721603393555</t>
+    <t xml:space="preserve">14.9721584320068</t>
   </si>
   <si>
     <t xml:space="preserve">15.455132484436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1101541519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0411558151245</t>
+    <t xml:space="preserve">15.1101522445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0411548614502</t>
   </si>
   <si>
     <t xml:space="preserve">15.0756540298462</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3516368865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4206342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5241270065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6966190338135</t>
+    <t xml:space="preserve">15.351637840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4206323623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5241289138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6966209411621</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156669616699</t>
@@ -1322,43 +1322,43 @@
     <t xml:space="preserve">15.7328300476074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5914106369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3439292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7782526016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.424708366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5307683944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4954147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8873138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1135864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.318642616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6014776229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0257349014282</t>
+    <t xml:space="preserve">15.5914096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3439273834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.379282951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7782554626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4247064590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5307693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600610733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.495415687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8873157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1135835647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3186416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6014795303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0257368087769</t>
   </si>
   <si>
     <t xml:space="preserve">15.0610914230347</t>
@@ -1370,190 +1370,190 @@
     <t xml:space="preserve">14.8489627838135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8843145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7075452804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671543121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2025098800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5661239624023</t>
+    <t xml:space="preserve">14.8843173980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7075433731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671552658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2025089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.566125869751</t>
   </si>
   <si>
     <t xml:space="preserve">14.6368350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2832889556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0853004455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8136081695557</t>
+    <t xml:space="preserve">14.2832880020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0853023529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8136072158813</t>
   </si>
   <si>
     <t xml:space="preserve">14.3539981842041</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3893537521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.74289894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1418695449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.177225112915</t>
+    <t xml:space="preserve">14.389349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428998947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1418676376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1772222518921</t>
   </si>
   <si>
     <t xml:space="preserve">14.247932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2125787734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0711603164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9438848495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8731756210327</t>
+    <t xml:space="preserve">14.2125778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.071159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9438819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8731727600098</t>
   </si>
   <si>
     <t xml:space="preserve">13.8166065216064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8590326309204</t>
+    <t xml:space="preserve">13.859034538269</t>
   </si>
   <si>
     <t xml:space="preserve">14.0145921707153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.929741859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.000449180603</t>
+    <t xml:space="preserve">13.9297437667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0004501342773</t>
   </si>
   <si>
     <t xml:space="preserve">14.0994434356689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.97216796875</t>
+    <t xml:space="preserve">13.9721660614014</t>
   </si>
   <si>
     <t xml:space="preserve">14.0287351608276</t>
   </si>
   <si>
-    <t xml:space="preserve">14.057017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1277265548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9196720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6721887588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.434775352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5054836273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.49134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3782072067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4630603790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5620546340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5337686538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1660804748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7842483520508</t>
+    <t xml:space="preserve">14.0570182800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1277284622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9196729660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6721897125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.505485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4913425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3782081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.463059425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5620527267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5337677001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1660823822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7842502593994</t>
   </si>
   <si>
     <t xml:space="preserve">12.6852569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1620082855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6569728851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4064922332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5479097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7883243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7741804122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5903367996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.448917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3074998855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3923511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0105199813843</t>
+    <t xml:space="preserve">12.1620092391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6569719314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4064903259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5479116439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7883224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7741794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5903358459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4489192962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3074989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3923501968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0105209350586</t>
   </si>
   <si>
     <t xml:space="preserve">13.1519384384155</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2933559417725</t>
+    <t xml:space="preserve">13.2933549880981</t>
   </si>
   <si>
     <t xml:space="preserve">12.9256706237793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0388021469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9963760375977</t>
+    <t xml:space="preserve">13.0388031005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.996376991272</t>
   </si>
   <si>
     <t xml:space="preserve">13.2367887496948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0953712463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6469020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6751880645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0670862197876</t>
+    <t xml:space="preserve">13.0953722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6469049453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6751852035522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0670871734619</t>
   </si>
   <si>
     <t xml:space="preserve">13.2509298324585</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">13.3499240875244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8408184051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5296964645386</t>
+    <t xml:space="preserve">12.8408164978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5296945571899</t>
   </si>
   <si>
     <t xml:space="preserve">12.8973846435547</t>
@@ -1580,34 +1580,34 @@
     <t xml:space="preserve">12.6004047393799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7317543029785</t>
+    <t xml:space="preserve">13.7317552566528</t>
   </si>
   <si>
     <t xml:space="preserve">13.5761947631836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5196285247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7176113128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8307485580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7600374221802</t>
+    <t xml:space="preserve">13.5196266174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7176122665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8307466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7600393295288</t>
   </si>
   <si>
     <t xml:space="preserve">13.9155988693237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7458963394165</t>
+    <t xml:space="preserve">13.7458982467651</t>
   </si>
   <si>
     <t xml:space="preserve">14.0428771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8448886871338</t>
+    <t xml:space="preserve">13.8448896408081</t>
   </si>
   <si>
     <t xml:space="preserve">14.5417671203613</t>
@@ -1616,19 +1616,19 @@
     <t xml:space="preserve">14.2218475341797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9455556869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1782245635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9891815185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2073068618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4399757385254</t>
+    <t xml:space="preserve">13.9455537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.17822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9891796112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2073078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4399747848511</t>
   </si>
   <si>
     <t xml:space="preserve">14.2654733657837</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">14.498143196106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4690561294556</t>
+    <t xml:space="preserve">14.4690570831299</t>
   </si>
   <si>
     <t xml:space="preserve">14.3527250289917</t>
@@ -1664,16 +1664,16 @@
     <t xml:space="preserve">14.4836006164551</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6144762039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8326034545898</t>
+    <t xml:space="preserve">14.6144752502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8326025009155</t>
   </si>
   <si>
     <t xml:space="preserve">14.9780206680298</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1234369277954</t>
+    <t xml:space="preserve">15.123438835144</t>
   </si>
   <si>
     <t xml:space="preserve">15.1961460113525</t>
@@ -1682,16 +1682,16 @@
     <t xml:space="preserve">15.4142742156982</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4506282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3415651321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2325000762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3052082061768</t>
+    <t xml:space="preserve">15.450629234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3415660858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2325010299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3052110671997</t>
   </si>
   <si>
     <t xml:space="preserve">15.2688541412354</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">15.6687545776367</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0507297515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0870847702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9416666030884</t>
+    <t xml:space="preserve">15.0507307052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0870838165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9416656494141</t>
   </si>
   <si>
     <t xml:space="preserve">14.7235383987427</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">15.0143747329712</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5781221389771</t>
+    <t xml:space="preserve">14.5781211853027</t>
   </si>
   <si>
     <t xml:space="preserve">14.7598934173584</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">14.3672657012939</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3236408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5272245407104</t>
+    <t xml:space="preserve">14.3236427307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5272264480591</t>
   </si>
   <si>
     <t xml:space="preserve">14.4545154571533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7962493896484</t>
+    <t xml:space="preserve">14.7962474822998</t>
   </si>
   <si>
     <t xml:space="preserve">14.9053115844727</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">16.0322971343994</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3594875335693</t>
+    <t xml:space="preserve">16.359489440918</t>
   </si>
   <si>
     <t xml:space="preserve">16.5049076080322</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">16.6139698028564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.541259765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8320941925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6503238677979</t>
+    <t xml:space="preserve">16.5412616729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8320980072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6503219604492</t>
   </si>
   <si>
     <t xml:space="preserve">16.577615737915</t>
@@ -1769,31 +1769,31 @@
     <t xml:space="preserve">16.8684520721436</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7593841552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0502223968506</t>
+    <t xml:space="preserve">16.7593879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0502243041992</t>
   </si>
   <si>
     <t xml:space="preserve">17.086576461792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4864749908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4137649536133</t>
+    <t xml:space="preserve">17.4864730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4137668609619</t>
   </si>
   <si>
     <t xml:space="preserve">17.2683486938477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5228290557861</t>
+    <t xml:space="preserve">17.5228309631348</t>
   </si>
   <si>
     <t xml:space="preserve">17.8136653900146</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7409572601318</t>
+    <t xml:space="preserve">17.7409553527832</t>
   </si>
   <si>
     <t xml:space="preserve">17.631893157959</t>
@@ -1802,28 +1802,28 @@
     <t xml:space="preserve">17.7046031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6682453155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0681476593018</t>
+    <t xml:space="preserve">17.6682472229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0681457519531</t>
   </si>
   <si>
     <t xml:space="preserve">17.9227275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1045017242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8500175476074</t>
+    <t xml:space="preserve">18.1044998168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8500194549561</t>
   </si>
   <si>
     <t xml:space="preserve">17.9590854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">18.177209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0317916870117</t>
+    <t xml:space="preserve">18.1772060394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0317935943604</t>
   </si>
   <si>
     <t xml:space="preserve">18.2862720489502</t>
@@ -1841,16 +1841,16 @@
     <t xml:space="preserve">17.9954376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5591850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5955371856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4501190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2499179840088</t>
+    <t xml:space="preserve">17.5591831207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5955390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.450122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2499160766602</t>
   </si>
   <si>
     <t xml:space="preserve">18.395336151123</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">18.2135620117188</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3226280212402</t>
+    <t xml:space="preserve">18.3226261138916</t>
   </si>
   <si>
     <t xml:space="preserve">18.6134624481201</t>
@@ -1868,16 +1868,16 @@
     <t xml:space="preserve">18.6861705780029</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8315887451172</t>
+    <t xml:space="preserve">18.8315868377686</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9770050048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.086067199707</t>
+    <t xml:space="preserve">18.9770088195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0860691070557</t>
   </si>
   <si>
     <t xml:space="preserve">19.2678413391113</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">19.4132595062256</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4496154785156</t>
+    <t xml:space="preserve">19.449613571167</t>
   </si>
   <si>
     <t xml:space="preserve">16.9048042297363</t>
@@ -1901,10 +1901,10 @@
     <t xml:space="preserve">16.7230319976807</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4321975708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7957382202148</t>
+    <t xml:space="preserve">16.4321994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7957420349121</t>
   </si>
   <si>
     <t xml:space="preserve">19.2314891815186</t>
@@ -1913,22 +1913,22 @@
     <t xml:space="preserve">16.9775123596191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3047046661377</t>
+    <t xml:space="preserve">17.3047027587891</t>
   </si>
   <si>
     <t xml:space="preserve">17.3774127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7952365875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5407524108887</t>
+    <t xml:space="preserve">18.7952327728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5407543182373</t>
   </si>
   <si>
     <t xml:space="preserve">18.8679447174072</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9042949676514</t>
+    <t xml:space="preserve">18.9042987823486</t>
   </si>
   <si>
     <t xml:space="preserve">19.8495121002197</t>
@@ -1940,19 +1940,19 @@
     <t xml:space="preserve">19.7327518463135</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3943996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8105926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549091339111</t>
+    <t xml:space="preserve">20.394401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8105907440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549110412598</t>
   </si>
   <si>
     <t xml:space="preserve">20.3554821014404</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1219577789307</t>
+    <t xml:space="preserve">20.121955871582</t>
   </si>
   <si>
     <t xml:space="preserve">19.9273548126221</t>
@@ -1964,25 +1964,25 @@
     <t xml:space="preserve">19.3435459136963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3046226501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.966272354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2657032012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7716693878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7597370147705</t>
+    <t xml:space="preserve">19.3046245574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9662742614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2657012939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.771671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7597351074219</t>
   </si>
   <si>
     <t xml:space="preserve">20.1608772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0441150665283</t>
+    <t xml:space="preserve">20.044116973877</t>
   </si>
   <si>
     <t xml:space="preserve">21.172815322876</t>
@@ -1991,19 +1991,19 @@
     <t xml:space="preserve">21.0560512542725</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9392890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2895755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0171318054199</t>
+    <t xml:space="preserve">20.9392871856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2895774841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0171298980713</t>
   </si>
   <si>
     <t xml:space="preserve">20.7836074829102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7057685852051</t>
+    <t xml:space="preserve">20.7057647705078</t>
   </si>
   <si>
     <t xml:space="preserve">21.094970703125</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">21.9512252807617</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6009387969971</t>
+    <t xml:space="preserve">21.6009426116943</t>
   </si>
   <si>
     <t xml:space="preserve">21.7955436706543</t>
@@ -2027,10 +2027,10 @@
     <t xml:space="preserve">22.0290679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.067985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5350341796875</t>
+    <t xml:space="preserve">22.0679874420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5350360870361</t>
   </si>
   <si>
     <t xml:space="preserve">22.5739555358887</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">22.7685585021973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8074760437012</t>
+    <t xml:space="preserve">22.8074779510498</t>
   </si>
   <si>
     <t xml:space="preserve">22.7296390533447</t>
@@ -2054,34 +2054,34 @@
     <t xml:space="preserve">22.2625904083252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5080509185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9750957489014</t>
+    <t xml:space="preserve">23.5080490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.97509765625</t>
   </si>
   <si>
     <t xml:space="preserve">24.4032249450684</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9091911315918</t>
+    <t xml:space="preserve">24.9091930389404</t>
   </si>
   <si>
     <t xml:space="preserve">24.7145881652832</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5199851989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.298397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7924308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1427154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7535095214844</t>
+    <t xml:space="preserve">24.5199871063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2983989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7924327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1427135467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7535076141357</t>
   </si>
   <si>
     <t xml:space="preserve">24.6367473602295</t>
@@ -2093,43 +2093,43 @@
     <t xml:space="preserve">24.0140190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0799255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7026538848877</t>
+    <t xml:space="preserve">23.0799236297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7026557922363</t>
   </si>
   <si>
     <t xml:space="preserve">24.0529384613037</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4691295623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5858898162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1577663421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8583335876465</t>
+    <t xml:space="preserve">23.4691276550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5858917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1577644348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8583374023438</t>
   </si>
   <si>
     <t xml:space="preserve">23.7415733337402</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8194160461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6637306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4302101135254</t>
+    <t xml:space="preserve">23.8194141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6637325286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4302082061768</t>
   </si>
   <si>
     <t xml:space="preserve">24.0918598175049</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3912868499756</t>
+    <t xml:space="preserve">23.3912887573242</t>
   </si>
   <si>
     <t xml:space="preserve">23.352367401123</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">23.0410022735596</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0020790100098</t>
+    <t xml:space="preserve">23.0020809173584</t>
   </si>
   <si>
     <t xml:space="preserve">23.1188430786133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.624813079834</t>
+    <t xml:space="preserve">23.6248111724854</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128749847412</t>
@@ -2156,28 +2156,28 @@
     <t xml:space="preserve">22.1847476959229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.496114730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3015117645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6907176971436</t>
+    <t xml:space="preserve">22.4961128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3015098571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6907157897949</t>
   </si>
   <si>
     <t xml:space="preserve">22.3793525695801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9631633758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2356052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9242401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2236709594727</t>
+    <t xml:space="preserve">22.9631614685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2356071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9242420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.223669052124</t>
   </si>
   <si>
     <t xml:space="preserve">22.4182739257812</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">21.9123039245605</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4841766357422</t>
+    <t xml:space="preserve">21.4841785430908</t>
   </si>
   <si>
     <t xml:space="preserve">21.1338920593262</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5230979919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.717700958252</t>
+    <t xml:space="preserve">21.5230960845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7177028656006</t>
   </si>
   <si>
     <t xml:space="preserve">21.6398601531982</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">21.2506542205811</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5620212554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8344631195068</t>
+    <t xml:space="preserve">21.5620193481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8344612121582</t>
   </si>
   <si>
     <t xml:space="preserve">21.6787815093994</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">21.3674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9782104492188</t>
+    <t xml:space="preserve">20.9782123565674</t>
   </si>
   <si>
     <t xml:space="preserve">20.6279239654541</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">21.873384475708</t>
   </si>
   <si>
-    <t xml:space="preserve">23.440731048584</t>
+    <t xml:space="preserve">23.4407329559326</t>
   </si>
   <si>
     <t xml:space="preserve">22.88356590271</t>
@@ -2267,25 +2267,25 @@
     <t xml:space="preserve">23.2417449951172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0029582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2019462585449</t>
+    <t xml:space="preserve">23.0029563903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2019443511963</t>
   </si>
   <si>
     <t xml:space="preserve">23.122350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1621494293213</t>
+    <t xml:space="preserve">23.1621475219727</t>
   </si>
   <si>
     <t xml:space="preserve">23.5203247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9580993652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0774898529053</t>
+    <t xml:space="preserve">23.9580974578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0774917602539</t>
   </si>
   <si>
     <t xml:space="preserve">24.4356689453125</t>
@@ -2294,13 +2294,13 @@
     <t xml:space="preserve">24.3162746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3560752868652</t>
+    <t xml:space="preserve">24.3560733795166</t>
   </si>
   <si>
     <t xml:space="preserve">24.7938442230225</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1570873260498</t>
+    <t xml:space="preserve">24.1570854187012</t>
   </si>
   <si>
     <t xml:space="preserve">24.6744537353516</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">24.555061340332</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7540473937988</t>
+    <t xml:space="preserve">24.7540493011475</t>
   </si>
   <si>
     <t xml:space="preserve">24.2764778137207</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">24.5152645111084</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4754657745361</t>
+    <t xml:space="preserve">24.4754638671875</t>
   </si>
   <si>
     <t xml:space="preserve">24.2366828918457</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">24.3958721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7142486572266</t>
+    <t xml:space="preserve">24.7142505645752</t>
   </si>
   <si>
     <t xml:space="preserve">24.6346569061279</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">24.1968841552734</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6295948028564</t>
+    <t xml:space="preserve">25.6295928955078</t>
   </si>
   <si>
     <t xml:space="preserve">25.5102005004883</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">25.1918201446533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0326309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2714138031006</t>
+    <t xml:space="preserve">25.0326328277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2714157104492</t>
   </si>
   <si>
     <t xml:space="preserve">24.8336429595947</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">25.0724296569824</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7591114044189</t>
+    <t xml:space="preserve">23.7591133117676</t>
   </si>
   <si>
     <t xml:space="preserve">23.4805278778076</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">23.8785037994385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6397190093994</t>
+    <t xml:space="preserve">23.6397171020508</t>
   </si>
   <si>
     <t xml:space="preserve">23.7989082336426</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">25.430606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3112125396729</t>
+    <t xml:space="preserve">25.3112106323242</t>
   </si>
   <si>
     <t xml:space="preserve">25.2316188812256</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">26.0275688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7887878417969</t>
+    <t xml:space="preserve">25.7887859344482</t>
   </si>
   <si>
     <t xml:space="preserve">25.5499992370605</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">25.9479732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1071624755859</t>
+    <t xml:space="preserve">26.1071643829346</t>
   </si>
   <si>
     <t xml:space="preserve">25.7489852905273</t>
@@ -2465,13 +2465,13 @@
     <t xml:space="preserve">23.5999202728271</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3611354827881</t>
+    <t xml:space="preserve">23.3611373901367</t>
   </si>
   <si>
     <t xml:space="preserve">23.4009323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5601215362549</t>
+    <t xml:space="preserve">23.5601234436035</t>
   </si>
   <si>
     <t xml:space="preserve">22.4855918884277</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">23.7193126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8264102935791</t>
+    <t xml:space="preserve">23.8264083862305</t>
   </si>
   <si>
     <t xml:space="preserve">23.5692901611328</t>
@@ -2519,25 +2519,25 @@
     <t xml:space="preserve">24.2549419403076</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977981567383</t>
+    <t xml:space="preserve">24.2977962493896</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264377593994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.99782371521</t>
+    <t xml:space="preserve">23.9978218078613</t>
   </si>
   <si>
     <t xml:space="preserve">23.9121170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8692646026611</t>
+    <t xml:space="preserve">23.8692626953125</t>
   </si>
   <si>
     <t xml:space="preserve">23.7407035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6549968719482</t>
+    <t xml:space="preserve">23.6549987792969</t>
   </si>
   <si>
     <t xml:space="preserve">22.9693431854248</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">22.5836658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">22.92649269104</t>
+    <t xml:space="preserve">22.9264907836914</t>
   </si>
   <si>
     <t xml:space="preserve">23.1407585144043</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">22.7550773620605</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6693744659424</t>
+    <t xml:space="preserve">22.6693725585938</t>
   </si>
   <si>
     <t xml:space="preserve">23.0550518035889</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">23.2264652252197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7122249603271</t>
+    <t xml:space="preserve">22.7122268676758</t>
   </si>
   <si>
     <t xml:space="preserve">22.4122524261475</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1836090087891</t>
+    <t xml:space="preserve">23.1836109161377</t>
   </si>
   <si>
     <t xml:space="preserve">23.0979061126709</t>
@@ -2588,10 +2588,10 @@
     <t xml:space="preserve">23.3550243377686</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0121974945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3121719360352</t>
+    <t xml:space="preserve">23.0121994018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3121738433838</t>
   </si>
   <si>
     <t xml:space="preserve">23.397876739502</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">22.7979316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4551086425781</t>
+    <t xml:space="preserve">22.4551067352295</t>
   </si>
   <si>
     <t xml:space="preserve">22.4979591369629</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">21.426628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4694805145264</t>
+    <t xml:space="preserve">21.469482421875</t>
   </si>
   <si>
     <t xml:space="preserve">21.2552146911621</t>
@@ -2639,13 +2639,13 @@
     <t xml:space="preserve">20.1410293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9980964660645</t>
+    <t xml:space="preserve">20.9980945587158</t>
   </si>
   <si>
     <t xml:space="preserve">21.1266536712646</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5267105102539</t>
+    <t xml:space="preserve">20.5267086029053</t>
   </si>
   <si>
     <t xml:space="preserve">20.6552696228027</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">21.512336730957</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3409194946289</t>
+    <t xml:space="preserve">21.3409214019775</t>
   </si>
   <si>
     <t xml:space="preserve">22.0265731811523</t>
@@ -2681,19 +2681,19 @@
     <t xml:space="preserve">21.8123073577881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1551342010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2408390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6837482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7266006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8980140686035</t>
+    <t xml:space="preserve">22.1551322937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2408409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6837463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.726598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8980121612549</t>
   </si>
   <si>
     <t xml:space="preserve">21.7694530487061</t>
@@ -2702,28 +2702,28 @@
     <t xml:space="preserve">21.6408939361572</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1979866027832</t>
+    <t xml:space="preserve">22.1979846954346</t>
   </si>
   <si>
     <t xml:space="preserve">22.0694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9837207794189</t>
+    <t xml:space="preserve">21.9837188720703</t>
   </si>
   <si>
     <t xml:space="preserve">21.8551597595215</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1695079803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0838012695312</t>
+    <t xml:space="preserve">21.1695098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0838031768799</t>
   </si>
   <si>
     <t xml:space="preserve">21.9408664703369</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5551853179932</t>
+    <t xml:space="preserve">21.5551872253418</t>
   </si>
   <si>
     <t xml:space="preserve">21.0409488677979</t>
@@ -3681,6 +3681,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.8499984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0999984741211</t>
   </si>
 </sst>
 </file>
@@ -68889,7 +68892,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6494791667</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>22662</v>
@@ -68910,6 +68913,32 @@
         <v>1221</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6493055556</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>37707</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>33.3499984741211</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>32.9000015258789</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>33.2000007629395</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>33.0999984741211</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1223</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="1224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="1226">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,85 +44,85 @@
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577459335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9573335647583</t>
+    <t xml:space="preserve">14.0577449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9573364257812</t>
   </si>
   <si>
     <t xml:space="preserve">13.3883285522461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8896131515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8527946472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9532070159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6184997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846162796021</t>
+    <t xml:space="preserve">12.889612197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8527975082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9532089233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6184988021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846172332764</t>
   </si>
   <si>
     <t xml:space="preserve">12.3842039108276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8821420669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7348699569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2127256393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7307462692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2294616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2194204330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2461948394775</t>
+    <t xml:space="preserve">11.8821411132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7348709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2127246856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7307453155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2294607162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2194185256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2461977005005</t>
   </si>
   <si>
     <t xml:space="preserve">10.9148359298706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1323957443237</t>
+    <t xml:space="preserve">11.1323947906494</t>
   </si>
   <si>
     <t xml:space="preserve">11.6143760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6813182830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5474328994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.346607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.313136100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.329873085022</t>
+    <t xml:space="preserve">11.6813173294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5474338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3466081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3131370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3298740386963</t>
   </si>
   <si>
     <t xml:space="preserve">10.8947515487671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8780155181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.045371055603</t>
+    <t xml:space="preserve">10.8780164718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0453720092773</t>
   </si>
   <si>
     <t xml:space="preserve">10.4261608123779</t>
@@ -137,46 +137,46 @@
     <t xml:space="preserve">11.7147874832153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0494956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7482595443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7449111938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2135028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168493270874</t>
+    <t xml:space="preserve">12.0494966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7482576370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7449102401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2135038375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.216851234436</t>
   </si>
   <si>
     <t xml:space="preserve">12.3674697875977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7189121246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.82936668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0201482772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2209739685059</t>
+    <t xml:space="preserve">12.7189140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8293685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0201501846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2209749221802</t>
   </si>
   <si>
     <t xml:space="preserve">13.3849821090698</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0870923995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536222457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3347759246826</t>
+    <t xml:space="preserve">13.0870895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.334774017334</t>
   </si>
   <si>
     <t xml:space="preserve">13.3146924972534</t>
@@ -191,61 +191,61 @@
     <t xml:space="preserve">12.8661832809448</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1306037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.287917137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.826021194458</t>
+    <t xml:space="preserve">13.1306028366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2879161834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8260192871094</t>
   </si>
   <si>
     <t xml:space="preserve">12.9833326339722</t>
   </si>
   <si>
-    <t xml:space="preserve">12.903000831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2377090454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1674222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.113865852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971326828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5047016143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8092851638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8862648010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7055234909058</t>
+    <t xml:space="preserve">12.9030017852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2377109527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1674213409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1138687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5047006607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8092842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8862676620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7055253982544</t>
   </si>
   <si>
     <t xml:space="preserve">12.7222585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.916392326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0301895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6318883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7021770477295</t>
+    <t xml:space="preserve">12.9163904190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0301885604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6318893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7021780014038</t>
   </si>
   <si>
     <t xml:space="preserve">12.8695306777954</t>
@@ -257,34 +257,34 @@
     <t xml:space="preserve">12.5682916641235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8360605239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494482040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5348224639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7791614532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7691192626953</t>
+    <t xml:space="preserve">12.8360595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958946228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5348215103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7791585922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7691202163696</t>
   </si>
   <si>
     <t xml:space="preserve">12.7865657806396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.502420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6512584686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7527408599854</t>
+    <t xml:space="preserve">12.5024194717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6512594223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7527389526367</t>
   </si>
   <si>
     <t xml:space="preserve">12.5836057662964</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">12.4990377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5700721740723</t>
+    <t xml:space="preserve">12.5700731277466</t>
   </si>
   <si>
     <t xml:space="preserve">12.5159511566162</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">12.2791614532471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0660533905029</t>
+    <t xml:space="preserve">12.0660524368286</t>
   </si>
   <si>
     <t xml:space="preserve">12.1776819229126</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">12.170916557312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1100263595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1269397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9814863204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7459726333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580247879028</t>
+    <t xml:space="preserve">12.1100292205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1269416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.981484413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7459735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580238342285</t>
   </si>
   <si>
     <t xml:space="preserve">12.3231372833252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.697340965271</t>
+    <t xml:space="preserve">11.6973419189453</t>
   </si>
   <si>
     <t xml:space="preserve">11.7785243988037</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">11.2406759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8212232589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0613946914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1967010498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4064273834229</t>
+    <t xml:space="preserve">10.8212242126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554708480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0613956451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.196702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4064283370972</t>
   </si>
   <si>
     <t xml:space="preserve">11.5248231887817</t>
@@ -362,34 +362,34 @@
     <t xml:space="preserve">10.6656198501587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1886606216431</t>
+    <t xml:space="preserve">10.1886615753174</t>
   </si>
   <si>
     <t xml:space="preserve">10.5878171920776</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6825323104858</t>
+    <t xml:space="preserve">10.6825332641602</t>
   </si>
   <si>
     <t xml:space="preserve">11.839412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0199718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3616218566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0233535766602</t>
+    <t xml:space="preserve">13.0199708938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3616247177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0233564376831</t>
   </si>
   <si>
     <t xml:space="preserve">13.1924886703491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4969310760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4698696136475</t>
+    <t xml:space="preserve">13.4969329833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4698686599731</t>
   </si>
   <si>
     <t xml:space="preserve">13.5307569503784</t>
@@ -398,193 +398,193 @@
     <t xml:space="preserve">13.4800157546997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2939710617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0740957260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.03688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.948935508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827632904053</t>
+    <t xml:space="preserve">13.2939691543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108806610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548564910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0740947723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368843078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9489336013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982762336731</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910081863403</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0707101821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9962930679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8576021194458</t>
+    <t xml:space="preserve">13.0707130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9962921142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8576030731201</t>
   </si>
   <si>
     <t xml:space="preserve">13.1113033294678</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1248350143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1823396682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0605659484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857242584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4123640060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5679693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4157457351685</t>
+    <t xml:space="preserve">13.1248340606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1823415756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0605640411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857233047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4123649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5679683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4157438278198</t>
   </si>
   <si>
     <t xml:space="preserve">13.513843536377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.706657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8352022171021</t>
+    <t xml:space="preserve">13.7066564559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8352003097534</t>
   </si>
   <si>
     <t xml:space="preserve">14.2106790542603</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4576168060303</t>
+    <t xml:space="preserve">14.4576139450073</t>
   </si>
   <si>
     <t xml:space="preserve">14.7552900314331</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8838329315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0157594680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.985315322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6652345657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.289755821228</t>
+    <t xml:space="preserve">14.8838319778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0157585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9853143692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303480148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6652364730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2897567749023</t>
   </si>
   <si>
     <t xml:space="preserve">14.8297119140625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.684253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7722072601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.951491355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7485256195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7180824279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.877067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7992677688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751653671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9007482528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2018032073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939828872681</t>
+    <t xml:space="preserve">14.6842546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7722034454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.951488494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7485246658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7180805206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8770694732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7992658615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9007472991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2018060684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939781188965</t>
   </si>
   <si>
     <t xml:space="preserve">14.8330936431885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9988460540771</t>
+    <t xml:space="preserve">14.9988451004028</t>
   </si>
   <si>
     <t xml:space="preserve">14.9142780303955</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9278106689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7383813858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7248468399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5421838760376</t>
+    <t xml:space="preserve">14.9278078079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.738377571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7248487472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5421829223633</t>
   </si>
   <si>
     <t xml:space="preserve">14.4440841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0529680252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1443014144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1104736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9548683166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0901784896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2187194824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7823553085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6166009902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764305114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1599378585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2546520233154</t>
+    <t xml:space="preserve">15.0529670715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1443004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1104698181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.954870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0901775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2187204360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7823524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707239151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6166000366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764295578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1599359512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2546548843384</t>
   </si>
   <si>
     <t xml:space="preserve">14.0415439605713</t>
@@ -596,169 +596,169 @@
     <t xml:space="preserve">14.038161277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1430253982544</t>
+    <t xml:space="preserve">14.1430244445801</t>
   </si>
   <si>
     <t xml:space="preserve">14.1903810501099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3527498245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2072954177856</t>
+    <t xml:space="preserve">14.3527517318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2072944641113</t>
   </si>
   <si>
     <t xml:space="preserve">14.3561344146729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4373178482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3087768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2411231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3392210006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2512722015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464080810547</t>
+    <t xml:space="preserve">14.4373216629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730497360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3087759017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2411212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3392200469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2512693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1464071273804</t>
   </si>
   <si>
     <t xml:space="preserve">14.1058149337769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1193475723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.227593421936</t>
+    <t xml:space="preserve">14.119348526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2275943756104</t>
   </si>
   <si>
     <t xml:space="preserve">14.2715673446655</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1497898101807</t>
+    <t xml:space="preserve">14.149790763855</t>
   </si>
   <si>
     <t xml:space="preserve">14.0753726959229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0719871520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749490737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4779100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267499923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7519092559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8161792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1037082672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0834121704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882734298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172409057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.154447555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999029159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758024215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3574104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3912343978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893350601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1713619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1003255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3168153762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3134346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4182968139648</t>
+    <t xml:space="preserve">14.0719881057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667060852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4779090881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267490386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7519083023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8161811828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1037101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0834150314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882762908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172380447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1544485092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3574075698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3912382125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893369674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1713638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1003217697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946180343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3168172836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3134336471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4182987213135</t>
   </si>
   <si>
     <t xml:space="preserve">15.4250650405884</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5366926193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6753835678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6449365615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7295064926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6618509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6517038345337</t>
+    <t xml:space="preserve">15.5366897583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6753845214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6449384689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7295074462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6618490219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.651704788208</t>
   </si>
   <si>
     <t xml:space="preserve">15.682147026062</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5637531280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081497192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415576934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7024421691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333070755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584672927856</t>
+    <t xml:space="preserve">15.5637521743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081506729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415567398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7024450302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.65846824646</t>
   </si>
   <si>
     <t xml:space="preserve">15.4588928222656</t>
@@ -767,22 +767,22 @@
     <t xml:space="preserve">15.5874338150024</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6550874710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227392196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3350048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0339508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4060440063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4026622772217</t>
+    <t xml:space="preserve">15.655086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227411270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3350086212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0339488983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.406042098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.402660369873</t>
   </si>
   <si>
     <t xml:space="preserve">16.4195747375488</t>
@@ -794,16 +794,16 @@
     <t xml:space="preserve">17.099494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9980144500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1671485900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4208507537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5392436981201</t>
+    <t xml:space="preserve">16.9980163574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1671466827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4208488464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5392417907715</t>
   </si>
   <si>
     <t xml:space="preserve">17.6407260894775</t>
@@ -824,28 +824,28 @@
     <t xml:space="preserve">17.522331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4546775817871</t>
+    <t xml:space="preserve">17.4546756744385</t>
   </si>
   <si>
     <t xml:space="preserve">17.877513885498</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8098583221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7083778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7591228485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6745548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.573070526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3362827301025</t>
+    <t xml:space="preserve">17.8098602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7083759307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7591190338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6745529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730724334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3362846374512</t>
   </si>
   <si>
     <t xml:space="preserve">17.2009754180908</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">17.2517166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2178897857666</t>
+    <t xml:space="preserve">17.2178916931152</t>
   </si>
   <si>
     <t xml:space="preserve">17.3701095581055</t>
@@ -878,19 +878,19 @@
     <t xml:space="preserve">17.6975059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.469820022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6147136688232</t>
+    <t xml:space="preserve">17.4698181152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6147117614746</t>
   </si>
   <si>
     <t xml:space="preserve">16.7729568481445</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0075454711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1662349700928</t>
+    <t xml:space="preserve">17.0075435638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1662368774414</t>
   </si>
   <si>
     <t xml:space="preserve">17.1317386627197</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">16.9868469238281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9661483764648</t>
+    <t xml:space="preserve">16.9661464691162</t>
   </si>
   <si>
     <t xml:space="preserve">16.8350524902344</t>
@@ -911,31 +911,31 @@
     <t xml:space="preserve">16.8488540649414</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8281555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7591609954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.869556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9178466796875</t>
+    <t xml:space="preserve">16.8281574249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7591590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8695526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9178524017334</t>
   </si>
   <si>
     <t xml:space="preserve">16.9730472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9385509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1524353027344</t>
+    <t xml:space="preserve">16.938549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.152437210083</t>
   </si>
   <si>
     <t xml:space="preserve">16.6625633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5935688018799</t>
+    <t xml:space="preserve">16.5935668945312</t>
   </si>
   <si>
     <t xml:space="preserve">16.5659713745117</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">16.5038738250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9040489196777</t>
+    <t xml:space="preserve">16.8626556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9040508270264</t>
   </si>
   <si>
     <t xml:space="preserve">16.80055809021</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">16.8971500396729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5383720397949</t>
+    <t xml:space="preserve">16.5383701324463</t>
   </si>
   <si>
     <t xml:space="preserve">16.5590705871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4900722503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2416877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3037853240967</t>
+    <t xml:space="preserve">16.4900741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2416896820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.303783416748</t>
   </si>
   <si>
     <t xml:space="preserve">16.2485866546631</t>
@@ -977,25 +977,25 @@
     <t xml:space="preserve">16.1243953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1864891052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1588916778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5314693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2899875640869</t>
+    <t xml:space="preserve">16.1864910125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1588897705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5314712524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2899856567383</t>
   </si>
   <si>
     <t xml:space="preserve">16.3175830841064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5452709197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3658809661865</t>
+    <t xml:space="preserve">16.5452690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3658828735352</t>
   </si>
   <si>
     <t xml:space="preserve">16.4624767303467</t>
@@ -1004,88 +1004,88 @@
     <t xml:space="preserve">16.3313827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3520812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6970653533936</t>
+    <t xml:space="preserve">16.3520832061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6970634460449</t>
   </si>
   <si>
     <t xml:space="preserve">16.3865814208984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.448673248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5107727050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4210758209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4348773956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3934803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.496976852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5245742797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4003829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4555759429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.358980178833</t>
+    <t xml:space="preserve">16.4486751556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5107707977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4210777282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4348754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3934783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4969730377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5245723724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4003791809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4555778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3589782714844</t>
   </si>
   <si>
     <t xml:space="preserve">16.2830848693848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5521717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1795921325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2071914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1933917999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9036092758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5586252212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4965305328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9381055831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7794170379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7656154632568</t>
+    <t xml:space="preserve">16.5521697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1795902252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2071895599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1933898925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9036073684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5586261749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4965286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.938102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7794151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7656164169312</t>
   </si>
   <si>
     <t xml:space="preserve">15.7863130569458</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9795007705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9312076568604</t>
+    <t xml:space="preserve">15.9795026779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.931206703186</t>
   </si>
   <si>
     <t xml:space="preserve">15.7035188674927</t>
@@ -1094,220 +1094,220 @@
     <t xml:space="preserve">15.6483221054077</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8415098190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7518177032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691091537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.862211227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0277976989746</t>
+    <t xml:space="preserve">15.8415117263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7518157958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691101074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8622093200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0277996063232</t>
   </si>
   <si>
     <t xml:space="preserve">15.8967084884644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6276235580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7173185348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310258865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034313201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413290023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.248143196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3171415328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3309392929077</t>
+    <t xml:space="preserve">15.6276216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7173175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310287475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034294128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413318634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2481460571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3171396255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3309383392334</t>
   </si>
   <si>
     <t xml:space="preserve">15.282642364502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3792343139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619438171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6000270843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896335601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9519062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9726047515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9864025115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.041597366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8553075790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.793212890625</t>
+    <t xml:space="preserve">15.3792352676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619428634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6000242233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896306991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.951904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9726009368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.986403465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0415992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8553085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932119369507</t>
   </si>
   <si>
     <t xml:space="preserve">15.4758319854736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2895412445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1791477203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2067461013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3999347686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2343435287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3033428192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137353897095</t>
+    <t xml:space="preserve">15.2895402908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1791467666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.206748008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3999319076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2343454360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137344360352</t>
   </si>
   <si>
     <t xml:space="preserve">15.3861351013184</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6345224380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.145092010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.48317527771</t>
+    <t xml:space="preserve">15.634521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1450958251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4831714630127</t>
   </si>
   <si>
     <t xml:space="preserve">16.6073684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">16.37278175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6349678039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141788482666</t>
+    <t xml:space="preserve">16.3727798461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6349639892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.414176940918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0898952484131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2002906799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7315616607666</t>
+    <t xml:space="preserve">16.200288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.731559753418</t>
   </si>
   <si>
     <t xml:space="preserve">16.6901626586914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4762744903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7522583007812</t>
+    <t xml:space="preserve">16.4762763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7522602081299</t>
   </si>
   <si>
     <t xml:space="preserve">16.6487636566162</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6280651092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0420436859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0765419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1110382080078</t>
+    <t xml:space="preserve">16.6280670166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0420455932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0765399932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1110401153564</t>
   </si>
   <si>
     <t xml:space="preserve">17.2145328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1455402374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1800365447998</t>
+    <t xml:space="preserve">17.1455364227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1800346374512</t>
   </si>
   <si>
     <t xml:space="preserve">16.00710105896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2140865325928</t>
+    <t xml:space="preserve">16.2140884399414</t>
   </si>
   <si>
     <t xml:space="preserve">16.110595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5931243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621198654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0066576004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7306756973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9031639099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9721584320068</t>
+    <t xml:space="preserve">15.5931253433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0066566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.730673789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9031629562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9721622467041</t>
   </si>
   <si>
     <t xml:space="preserve">15.455132484436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1101522445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0411548614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0756540298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.351637840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4206323623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5241289138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6966209411621</t>
+    <t xml:space="preserve">15.1101531982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0411539077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0756530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3516359329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4206352233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5241279602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6966190338135</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156669616699</t>
@@ -1316,103 +1316,103 @@
     <t xml:space="preserve">15.874249458313</t>
   </si>
   <si>
-    <t xml:space="preserve">15.556056022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7328300476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914096832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3439273834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.379282951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7782554626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4247064590454</t>
+    <t xml:space="preserve">15.5560541152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7328290939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914106369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3439292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792819976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7782535552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.424708366394</t>
   </si>
   <si>
     <t xml:space="preserve">14.5307693481445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4600610733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.495415687561</t>
+    <t xml:space="preserve">14.4600620269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4954147338867</t>
   </si>
   <si>
     <t xml:space="preserve">13.8873157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1135835647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3186416625977</t>
+    <t xml:space="preserve">14.1135845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.318642616272</t>
   </si>
   <si>
     <t xml:space="preserve">14.6014795303345</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0257368087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0610914230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9550266265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8489627838135</t>
+    <t xml:space="preserve">15.0257358551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0610904693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9550275802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8489646911621</t>
   </si>
   <si>
     <t xml:space="preserve">14.8843173980713</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7075433731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671552658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2025089263916</t>
+    <t xml:space="preserve">14.7075452804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2025127410889</t>
   </si>
   <si>
     <t xml:space="preserve">14.566125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6368350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2832880020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0853023529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8136072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3539981842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.389349937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428998947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1418676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1772222518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.247932434082</t>
+    <t xml:space="preserve">14.6368341445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2832889556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0853042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.81360912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3539972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3893508911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.74289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1418695449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1772232055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2479314804077</t>
   </si>
   <si>
     <t xml:space="preserve">14.2125778198242</t>
@@ -1421,22 +1421,22 @@
     <t xml:space="preserve">14.071159362793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9438819885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8731727600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8166065216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.859034538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0145921707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9297437667847</t>
+    <t xml:space="preserve">13.9438810348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8731737136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8166084289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8590316772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0145931243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.929741859436</t>
   </si>
   <si>
     <t xml:space="preserve">14.0004501342773</t>
@@ -1445,46 +1445,46 @@
     <t xml:space="preserve">14.0994434356689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9721660614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0287351608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0570182800293</t>
+    <t xml:space="preserve">13.9721670150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.028733253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.057017326355</t>
   </si>
   <si>
     <t xml:space="preserve">14.1277284622192</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9196729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6721897125244</t>
+    <t xml:space="preserve">14.9196720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6721887588501</t>
   </si>
   <si>
     <t xml:space="preserve">13.4347763061523</t>
   </si>
   <si>
-    <t xml:space="preserve">13.505485534668</t>
+    <t xml:space="preserve">13.5054864883423</t>
   </si>
   <si>
     <t xml:space="preserve">13.4913425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3782081604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.463059425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5620527267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5337677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1660823822021</t>
+    <t xml:space="preserve">13.3782072067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4630603790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5620536804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.533766746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1660804748535</t>
   </si>
   <si>
     <t xml:space="preserve">12.7842502593994</t>
@@ -1493,64 +1493,64 @@
     <t xml:space="preserve">12.6852569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1620092391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6569719314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4064903259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5479116439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7883224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7741794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5903358459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4489192962646</t>
+    <t xml:space="preserve">12.1620082855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6569728851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4064893722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5479097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7883205413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7741804122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5903367996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4489164352417</t>
   </si>
   <si>
     <t xml:space="preserve">13.3074989318848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3923501968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0105209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1519384384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2933549880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9256706237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0388031005859</t>
+    <t xml:space="preserve">13.392352104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.01051902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1519393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2933559417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9256687164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0388040542603</t>
   </si>
   <si>
     <t xml:space="preserve">12.996376991272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2367887496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0953722000122</t>
+    <t xml:space="preserve">13.2367897033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0953712463379</t>
   </si>
   <si>
     <t xml:space="preserve">13.6469049453735</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6751852035522</t>
+    <t xml:space="preserve">13.6751871109009</t>
   </si>
   <si>
     <t xml:space="preserve">13.0670871734619</t>
@@ -1562,118 +1562,118 @@
     <t xml:space="preserve">13.2085075378418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0812282562256</t>
+    <t xml:space="preserve">13.0812292098999</t>
   </si>
   <si>
     <t xml:space="preserve">13.3499240875244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8408164978027</t>
+    <t xml:space="preserve">12.8408174514771</t>
   </si>
   <si>
     <t xml:space="preserve">12.5296945571899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8973846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6004047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7317552566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5761947631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5196266174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7176122665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8307466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7600393295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9155988693237</t>
+    <t xml:space="preserve">12.897385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6004037857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7317562103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5761957168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.519627571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7176103591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8307476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7600374221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.915599822998</t>
   </si>
   <si>
     <t xml:space="preserve">13.7458982467651</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0428771972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8448896408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5417671203613</t>
+    <t xml:space="preserve">14.0428781509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8448915481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.54176902771</t>
   </si>
   <si>
     <t xml:space="preserve">14.2218475341797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9455537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.17822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9891796112061</t>
+    <t xml:space="preserve">13.9455547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1782236099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9891805648804</t>
   </si>
   <si>
     <t xml:space="preserve">14.2073078155518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4399747848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2654733657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4108915328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.498143196106</t>
+    <t xml:space="preserve">14.4399766921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.265474319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4108924865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4981422424316</t>
   </si>
   <si>
     <t xml:space="preserve">14.4690570831299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3527250289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3381814956665</t>
+    <t xml:space="preserve">14.3527221679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3381805419922</t>
   </si>
   <si>
     <t xml:space="preserve">14.5126829147339</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3963499069214</t>
+    <t xml:space="preserve">14.3963489532471</t>
   </si>
   <si>
     <t xml:space="preserve">14.6871862411499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4254331588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4836006164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6144752502441</t>
+    <t xml:space="preserve">14.4254341125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4836025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6144771575928</t>
   </si>
   <si>
     <t xml:space="preserve">14.8326025009155</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9780206680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.123438835144</t>
+    <t xml:space="preserve">14.9780197143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1234359741211</t>
   </si>
   <si>
     <t xml:space="preserve">15.1961460113525</t>
@@ -1682,61 +1682,61 @@
     <t xml:space="preserve">15.4142742156982</t>
   </si>
   <si>
-    <t xml:space="preserve">15.450629234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3415660858154</t>
+    <t xml:space="preserve">15.4506273269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3415641784668</t>
   </si>
   <si>
     <t xml:space="preserve">15.2325010299683</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3052110671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2688541412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687545776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0507307052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0870838165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9416656494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7235383987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0143747329712</t>
+    <t xml:space="preserve">15.3052091598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.268856048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687526702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0507278442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0870847702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9416646957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7235403060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0143728256226</t>
   </si>
   <si>
     <t xml:space="preserve">14.5781211853027</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598934173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6508293151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3672657012939</t>
+    <t xml:space="preserve">14.7598943710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6508312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3672666549683</t>
   </si>
   <si>
     <t xml:space="preserve">14.3236427307129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5272264480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4545154571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7962474822998</t>
+    <t xml:space="preserve">14.5272254943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.454514503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7962484359741</t>
   </si>
   <si>
     <t xml:space="preserve">14.9053115844727</t>
@@ -1751,31 +1751,31 @@
     <t xml:space="preserve">16.5049076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6139698028564</t>
+    <t xml:space="preserve">16.6139678955078</t>
   </si>
   <si>
     <t xml:space="preserve">16.5412616729736</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8320980072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6503219604492</t>
+    <t xml:space="preserve">16.8320960998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6503257751465</t>
   </si>
   <si>
     <t xml:space="preserve">16.577615737915</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8684520721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7593879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0502243041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.086576461792</t>
+    <t xml:space="preserve">16.8684501647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7593860626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0502223968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0865783691406</t>
   </si>
   <si>
     <t xml:space="preserve">17.4864730834961</t>
@@ -1793,22 +1793,22 @@
     <t xml:space="preserve">17.8136653900146</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7409553527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.631893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7046031951904</t>
+    <t xml:space="preserve">17.7409572601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6318912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7046012878418</t>
   </si>
   <si>
     <t xml:space="preserve">17.6682472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0681457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9227275848389</t>
+    <t xml:space="preserve">18.0681476593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9227294921875</t>
   </si>
   <si>
     <t xml:space="preserve">18.1044998168945</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">17.8500194549561</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9590854644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1772060394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0317935943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2862720489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3589820861816</t>
+    <t xml:space="preserve">17.9590835571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.177209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0317916870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2862739562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.358980178833</t>
   </si>
   <si>
     <t xml:space="preserve">18.4680442810059</t>
@@ -1841,25 +1841,25 @@
     <t xml:space="preserve">17.9954376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5591831207275</t>
+    <t xml:space="preserve">17.5591812133789</t>
   </si>
   <si>
     <t xml:space="preserve">17.5955390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.450122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2499160766602</t>
+    <t xml:space="preserve">17.4501209259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2499179840088</t>
   </si>
   <si>
     <t xml:space="preserve">18.395336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2135620117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3226261138916</t>
+    <t xml:space="preserve">18.213565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.322624206543</t>
   </si>
   <si>
     <t xml:space="preserve">18.6134624481201</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">18.8315868377686</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1951332092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9770088195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0860691070557</t>
+    <t xml:space="preserve">19.1951313018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9770069122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0860729217529</t>
   </si>
   <si>
     <t xml:space="preserve">19.2678413391113</t>
@@ -1889,28 +1889,28 @@
     <t xml:space="preserve">19.3041954040527</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4132595062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.449613571167</t>
+    <t xml:space="preserve">19.4132614135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4496116638184</t>
   </si>
   <si>
     <t xml:space="preserve">16.9048042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7230319976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321994781494</t>
+    <t xml:space="preserve">16.7230339050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321975708008</t>
   </si>
   <si>
     <t xml:space="preserve">16.7957420349121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2314891815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9775123596191</t>
+    <t xml:space="preserve">19.2314872741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9775142669678</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047027587891</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">17.3774127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7952327728271</t>
+    <t xml:space="preserve">18.7952346801758</t>
   </si>
   <si>
     <t xml:space="preserve">18.5407543182373</t>
@@ -1928,28 +1928,28 @@
     <t xml:space="preserve">18.8679447174072</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9042987823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8495121002197</t>
+    <t xml:space="preserve">18.904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8495140075684</t>
   </si>
   <si>
     <t xml:space="preserve">19.4213848114014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7327518463135</t>
+    <t xml:space="preserve">19.7327499389648</t>
   </si>
   <si>
     <t xml:space="preserve">20.394401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8105907440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549110412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3554821014404</t>
+    <t xml:space="preserve">19.8105926513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3554801940918</t>
   </si>
   <si>
     <t xml:space="preserve">20.121955871582</t>
@@ -1961,16 +1961,16 @@
     <t xml:space="preserve">19.4603061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3435459136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3046245574951</t>
+    <t xml:space="preserve">19.3435440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3046226501465</t>
   </si>
   <si>
     <t xml:space="preserve">19.9662742614746</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2657012939453</t>
+    <t xml:space="preserve">19.2657051086426</t>
   </si>
   <si>
     <t xml:space="preserve">19.771671295166</t>
@@ -1979,25 +1979,25 @@
     <t xml:space="preserve">18.7597351074219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1608772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.044116973877</t>
+    <t xml:space="preserve">20.1608753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0441150665283</t>
   </si>
   <si>
     <t xml:space="preserve">21.172815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0560512542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9392871856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2895774841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0171298980713</t>
+    <t xml:space="preserve">21.0560493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9392890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2895755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0171318054199</t>
   </si>
   <si>
     <t xml:space="preserve">20.7836074829102</t>
@@ -2006,25 +2006,25 @@
     <t xml:space="preserve">20.7057647705078</t>
   </si>
   <si>
-    <t xml:space="preserve">21.094970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4452571868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7566223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9512252807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6009426116943</t>
+    <t xml:space="preserve">21.0949726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.445255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7566242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9512271881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6009387969971</t>
   </si>
   <si>
     <t xml:space="preserve">21.7955436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0290679931641</t>
+    <t xml:space="preserve">22.0290641784668</t>
   </si>
   <si>
     <t xml:space="preserve">22.0679874420166</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">22.5739555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6517963409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7685585021973</t>
+    <t xml:space="preserve">22.651798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7685565948486</t>
   </si>
   <si>
     <t xml:space="preserve">22.8074779510498</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">22.7296390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3404312133789</t>
+    <t xml:space="preserve">22.3404331207275</t>
   </si>
   <si>
     <t xml:space="preserve">22.2625904083252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5080490112305</t>
+    <t xml:space="preserve">23.5080509185791</t>
   </si>
   <si>
     <t xml:space="preserve">23.97509765625</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">24.4032249450684</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9091930389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7145881652832</t>
+    <t xml:space="preserve">24.9091911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7145900726318</t>
   </si>
   <si>
     <t xml:space="preserve">24.5199871063232</t>
@@ -2075,13 +2075,13 @@
     <t xml:space="preserve">25.2983989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7924327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1427135467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7535076141357</t>
+    <t xml:space="preserve">24.7924308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1427154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7535095214844</t>
   </si>
   <si>
     <t xml:space="preserve">24.6367473602295</t>
@@ -2096,28 +2096,28 @@
     <t xml:space="preserve">23.0799236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7026557922363</t>
+    <t xml:space="preserve">23.7026519775391</t>
   </si>
   <si>
     <t xml:space="preserve">24.0529384613037</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4691276550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5858917236328</t>
+    <t xml:space="preserve">23.4691295623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5858898162842</t>
   </si>
   <si>
     <t xml:space="preserve">23.1577644348145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8583374023438</t>
+    <t xml:space="preserve">23.8583354949951</t>
   </si>
   <si>
     <t xml:space="preserve">23.7415733337402</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8194141387939</t>
+    <t xml:space="preserve">23.8194160461426</t>
   </si>
   <si>
     <t xml:space="preserve">23.6637325286865</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">23.4302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0918598175049</t>
+    <t xml:space="preserve">24.0918579101562</t>
   </si>
   <si>
     <t xml:space="preserve">23.3912887573242</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">23.0020809173584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1188430786133</t>
+    <t xml:space="preserve">23.1188449859619</t>
   </si>
   <si>
     <t xml:space="preserve">23.6248111724854</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">22.6128749847412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1069087982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1847476959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4961128234863</t>
+    <t xml:space="preserve">22.1069068908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1847496032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.496114730835</t>
   </si>
   <si>
     <t xml:space="preserve">22.3015098571777</t>
@@ -2165,40 +2165,40 @@
     <t xml:space="preserve">22.6907157897949</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3793525695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9631614685059</t>
+    <t xml:space="preserve">22.3793506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9631595611572</t>
   </si>
   <si>
     <t xml:space="preserve">23.2356071472168</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9242420196533</t>
+    <t xml:space="preserve">22.9242401123047</t>
   </si>
   <si>
     <t xml:space="preserve">22.223669052124</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4182739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9123039245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4841785430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1338920593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5230960845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7177028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6398601531982</t>
+    <t xml:space="preserve">22.4182720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9123058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4841766357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1338939666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.523099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.717700958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6398582458496</t>
   </si>
   <si>
     <t xml:space="preserve">21.2506542205811</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">21.5620193481445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8344612121582</t>
+    <t xml:space="preserve">21.8344631195068</t>
   </si>
   <si>
     <t xml:space="preserve">21.6787815093994</t>
@@ -2222,25 +2222,25 @@
     <t xml:space="preserve">22.8464012145996</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8853187561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4571933746338</t>
+    <t xml:space="preserve">22.8853206634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4571952819824</t>
   </si>
   <si>
     <t xml:space="preserve">21.3284950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2117328643799</t>
+    <t xml:space="preserve">21.2117347717285</t>
   </si>
   <si>
     <t xml:space="preserve">21.3674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9782123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6279239654541</t>
+    <t xml:space="preserve">20.9782104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6279258728027</t>
   </si>
   <si>
     <t xml:space="preserve">21.873384475708</t>
@@ -2258,31 +2258,31 @@
     <t xml:space="preserve">22.8039703369141</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7641735076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0427570343018</t>
+    <t xml:space="preserve">22.7641754150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0427551269531</t>
   </si>
   <si>
     <t xml:space="preserve">23.2417449951172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0029563903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2019443511963</t>
+    <t xml:space="preserve">23.0029582977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2019462585449</t>
   </si>
   <si>
     <t xml:space="preserve">23.122350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1621475219727</t>
+    <t xml:space="preserve">23.1621494293213</t>
   </si>
   <si>
     <t xml:space="preserve">23.5203247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9580974578857</t>
+    <t xml:space="preserve">23.9580993652344</t>
   </si>
   <si>
     <t xml:space="preserve">24.0774917602539</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">24.3560733795166</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7938442230225</t>
+    <t xml:space="preserve">24.7938461303711</t>
   </si>
   <si>
     <t xml:space="preserve">24.1570854187012</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">24.6744537353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9132385253906</t>
+    <t xml:space="preserve">24.913236618042</t>
   </si>
   <si>
     <t xml:space="preserve">24.555061340332</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">24.5152645111084</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4754638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2366828918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3958721160889</t>
+    <t xml:space="preserve">24.4754657745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2366790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3958702087402</t>
   </si>
   <si>
     <t xml:space="preserve">24.7142505645752</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">24.6346569061279</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1968841552734</t>
+    <t xml:space="preserve">24.1968822479248</t>
   </si>
   <si>
     <t xml:space="preserve">25.6295928955078</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">25.4704036712646</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6693916320801</t>
+    <t xml:space="preserve">25.6693897247314</t>
   </si>
   <si>
     <t xml:space="preserve">25.3908100128174</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">25.1918201446533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0326328277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2714157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8336429595947</t>
+    <t xml:space="preserve">25.0326309204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2714176177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8336448669434</t>
   </si>
   <si>
     <t xml:space="preserve">24.9530372619629</t>
@@ -2381,10 +2381,10 @@
     <t xml:space="preserve">25.8683795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0724296569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7591133117676</t>
+    <t xml:space="preserve">25.0724277496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7591114044189</t>
   </si>
   <si>
     <t xml:space="preserve">23.4805278778076</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">23.8785037994385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6397171020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7989082336426</t>
+    <t xml:space="preserve">23.6397190093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7989063262939</t>
   </si>
   <si>
     <t xml:space="preserve">24.5948581695557</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">25.430606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3112106323242</t>
+    <t xml:space="preserve">25.3112125396729</t>
   </si>
   <si>
     <t xml:space="preserve">25.2316188812256</t>
@@ -2420,1047 +2420,1050 @@
     <t xml:space="preserve">26.2663536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0275688171387</t>
+    <t xml:space="preserve">26.0275707244873</t>
   </si>
   <si>
     <t xml:space="preserve">25.7887859344482</t>
   </si>
   <si>
+    <t xml:space="preserve">25.5499973297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5897960662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9479732513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1071643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7489833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8734397888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0376949310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3264007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3661975860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0825538635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.923360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3213386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5999202728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3611354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4009323120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5601234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4855899810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8387069702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.997896194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7193126678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8264102935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5692920684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1263828277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9549713134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4692077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4263553619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1692371368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2120895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7835578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.340648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2549419403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2977981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5264377593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9978218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9121150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8692626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7407035827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6549968719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9693450927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8836402893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5836658477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9264907836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1407585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8407859802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7550792694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6693725585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0550518035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2264652252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7122249603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4122524261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1836090087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0979061126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3694000244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3550243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0121994018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3121719360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.397876739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7979316711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4551048278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4979591369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6265182495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6978511810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5408115386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2693157196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2836933135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.426628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4694805145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2552146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.826681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9267635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1410312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9980945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1266555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5267105102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6552696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3124446868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4410037994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6981220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5980434417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3837738037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5123348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3409214019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.026575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1122798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8123073577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1551342010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2408409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6837463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7266006469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8980121612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7694530487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6408939361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1979866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0694274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9837188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8551597595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1695079803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0838012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9408683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5551872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0409469604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.912389755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2980690002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2123622894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4838562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6124153137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7409763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1838836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3552951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.809741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7657089233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7216739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2813320159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0611591339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1051940917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.017126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8850250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.664852142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4887142181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9290561676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8409881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7088871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4006443023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7969551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9730911254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7529201507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.501501083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2372970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1932640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4134349822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3253650665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5455379486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.149227142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3125782012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1364402770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0483722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3566131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6208171844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2685432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4446811676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.532751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0043392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8722362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6960983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3438243865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6080303192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9162693023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8282012939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2557563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3878574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2997894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7841682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9603042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7401313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0924072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1804752349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6336078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4574699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5895709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8537769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0299129486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4702568054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5142917633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8665657043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3949756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.30690574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1307697296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3509407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4390106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5711116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7032146453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.319694519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8353176116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7472496032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8793525695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0867366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2188396453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.52707862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2628726959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9546337127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7600364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4077625274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8481063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1123104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1563453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4645862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5910167694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3708457946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8992595672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0313587188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5029487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7671546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2827758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0753974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7231216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.471700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.811185836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2387447357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4148826599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1506729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9745388031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7103309631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8424339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8864688873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5469837188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2955646514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7359104156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3836345672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9873237609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4276695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4632396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8007907867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8972339630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8490123748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7525691986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0418968200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6079063415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2703552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0292491912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9328060150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2221336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6916999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4023723602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5470352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7399196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0774707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5952568054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5596828460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2094860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7272720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1003952026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1486167907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4861660003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5826091766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4379444122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.052173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9075088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5343856811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9201583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8237152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1612663269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0165996551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7754936218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9683799743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3541488647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1130428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4988136291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6434783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8363628387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8845863342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6790523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.473518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2324123382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3770751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7146244049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6181812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6664028167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0039520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.245059967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8110656738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8592891693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3415031433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1968383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9557323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5699596405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2577075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3897228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2932796478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1841888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.280632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1359691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7501983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0877456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.991304397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8466396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.701976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5090923309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6055335998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7984180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5573120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6537551879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4252967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0395259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3644256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0750980377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6893291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7857723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9786548614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9304351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.219762802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8822135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1715412139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5928859710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3517780303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0268783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4126491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2679843902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1233196258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4608688354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8948612213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9430828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5446643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1462440490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8569183349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5675888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3391304016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8213443756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.255334854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9177856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1106719970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0142288208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8695659637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6766796112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2426872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6640319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6158103942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0371551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1209487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4940719604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2173919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8798408508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9407119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0853748321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.422924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.194465637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2909088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6284580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7731227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0499992370605</t>
+  </si>
+  <si>
     <t xml:space="preserve">25.5499992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5897979736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9479732513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1071643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7489852905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8734397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0376930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3263988494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3661975860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0825538635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9233646392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3213367462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5999202728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3611373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4009323120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5601234436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4855918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8387050628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9978942871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7193126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8264083862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5692901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1263828277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9549694061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4692077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4263553619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1692352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2120895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7835559844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.340648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2549419403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2977962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5264377593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9978218078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9121170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8692626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7407035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6549987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9693431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8836402893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5836658477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9264907836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1407585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8407859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7550773620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6693725585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0550518035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2264652252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7122268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4122524261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1836109161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0979061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3694000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3550243377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0121994018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3121738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.397876739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7979316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4551067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4979591369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6265182495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6978492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5408115386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2693176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2836933135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.426628112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.469482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2552146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.826681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9267616271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1410293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9980945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1266536712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5267086029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6552696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.312442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4410037994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6981220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5980415344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3837757110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.512336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3409214019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0265731811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1122798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8123073577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1551322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2408409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6837463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.726598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8980121612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7694530487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6408939361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1979846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0694274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9837188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8551597595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1695098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0838031768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9408664703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5551872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0409488677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.912389755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2980690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2123622894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4838562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6124153137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7409763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1838817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3552951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.809741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7657089233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7216739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2813320159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0611591339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1051959991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.017126083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8850250244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.664852142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5767841339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4887161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9290561676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8409881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7088851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4006462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7969551086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9730930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7529201507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5015029907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2372970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1932640075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4134349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3253650665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5455360412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.149227142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3125782012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1364402770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0483722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3566112518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6208171844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2685432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4446811676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5327491760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0043392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8722343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6960983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3438243865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6080303192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9162693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8282012939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2557563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3878593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2997894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7841682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9603023529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7401313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0924072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1804752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6336059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4574680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5895709991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8537769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0299129486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4702568054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5142917633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8665657043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3949756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3069076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1307697296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3509407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4390087127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5711135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6591815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7032146453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.319694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8353176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7472496032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8793525695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0867366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2188377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.52707862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2628726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9546337127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7600383758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4077625274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8481063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1123104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1563472747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4645843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5910148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3708438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8992576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0313587188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5029487609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7671527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2827777862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0753955841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7231216430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.471700668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8111877441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2387447357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4148826599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1506729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9745388031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7103309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.842435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8864688873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5469818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2955665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7359104156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3836326599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9873237609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4276676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4632396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8007907867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8972339630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8490123748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7525691986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0418968200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6079063415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2703552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0292491912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9328060150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2221336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6916999816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4023723602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5470352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7399196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0774707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5952568054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5596828460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2094860076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7272720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1003952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1486167907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4861660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5826091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4379444122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.052173614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9075088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5343856811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9201583862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8237152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1612663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0165996551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7754936218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9683799743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3541488647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1130428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4988136291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6434783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8363628387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8845863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6790523529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.473518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2324123382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3770751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7146244049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6181812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6664028167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0039520263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.245059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8110656738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8592891693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3415031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1968383789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9557323455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5699596405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2577075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3897228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2932796478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1841888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.280632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1359691619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7501983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0877456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.991304397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8466396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.701976776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5090923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6055335998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7984180450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5573120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6537551879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4252967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0395259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3644256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0750980377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6893291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7857723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9786548614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9304351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.219762802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8822135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1715412139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5928859710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3517780303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0268783569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4126491546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2679843902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1233196258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4608688354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8948612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9430828094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5446643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1462440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8569183349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5675888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3391304016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8213443756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.255334854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3999996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9177856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1106719970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0142288208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8695659637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6766796112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2426872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6640319824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6158103942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0371551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1209487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4940719604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2173919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8798408508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9407119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0853748321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.422924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.194465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2909088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6284580230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7731227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3500003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2000007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8500003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7000007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8999996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2000007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6000003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8500003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7000007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8999996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0499992370605</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.1499996185303</t>
   </si>
   <si>
@@ -3684,6 +3687,9 @@
   </si>
   <si>
     <t xml:space="preserve">33.0999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5</t>
   </si>
 </sst>
 </file>
@@ -66102,7 +66108,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G2388" t="s">
-        <v>804</v>
+        <v>1149</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66128,7 +66134,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66154,7 +66160,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66180,7 +66186,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G2391" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66206,7 +66212,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66232,7 +66238,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66258,7 +66264,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66284,7 +66290,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66310,7 +66316,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G2396" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66336,7 +66342,7 @@
         <v>26.75</v>
       </c>
       <c r="G2397" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66362,7 +66368,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2398" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66388,7 +66394,7 @@
         <v>27</v>
       </c>
       <c r="G2399" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66414,7 +66420,7 @@
         <v>27</v>
       </c>
       <c r="G2400" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66440,7 +66446,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66466,7 +66472,7 @@
         <v>26.25</v>
       </c>
       <c r="G2402" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66492,7 +66498,7 @@
         <v>25.5</v>
       </c>
       <c r="G2403" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66518,7 +66524,7 @@
         <v>25.25</v>
       </c>
       <c r="G2404" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66570,7 +66576,7 @@
         <v>25.25</v>
       </c>
       <c r="G2406" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66622,7 +66628,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G2408" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66648,7 +66654,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G2409" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66674,7 +66680,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G2410" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66700,7 +66706,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2411" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66726,7 +66732,7 @@
         <v>25.5</v>
       </c>
       <c r="G2412" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66778,7 +66784,7 @@
         <v>26</v>
       </c>
       <c r="G2414" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66804,7 +66810,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2415" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66830,7 +66836,7 @@
         <v>27</v>
       </c>
       <c r="G2416" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66856,7 +66862,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66882,7 +66888,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G2418" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66908,7 +66914,7 @@
         <v>27.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66934,7 +66940,7 @@
         <v>27.5</v>
       </c>
       <c r="G2420" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66960,7 +66966,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66986,7 +66992,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2422" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67012,7 +67018,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G2423" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67038,7 +67044,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2424" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67064,7 +67070,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G2425" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67090,7 +67096,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2426" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67116,7 +67122,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2427" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67142,7 +67148,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2428" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67168,7 +67174,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2429" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67194,7 +67200,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67220,7 +67226,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67246,7 +67252,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2432" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67272,7 +67278,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67298,7 +67304,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G2434" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67324,7 +67330,7 @@
         <v>29</v>
       </c>
       <c r="G2435" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67350,7 +67356,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G2436" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67376,7 +67382,7 @@
         <v>28.25</v>
       </c>
       <c r="G2437" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67402,7 +67408,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G2438" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67428,7 +67434,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67454,7 +67460,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2440" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67480,7 +67486,7 @@
         <v>27</v>
       </c>
       <c r="G2441" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67506,7 +67512,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2442" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67532,7 +67538,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G2443" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67558,7 +67564,7 @@
         <v>27.25</v>
       </c>
       <c r="G2444" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67584,7 +67590,7 @@
         <v>27.25</v>
       </c>
       <c r="G2445" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67610,7 +67616,7 @@
         <v>27.25</v>
       </c>
       <c r="G2446" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67636,7 +67642,7 @@
         <v>27.25</v>
       </c>
       <c r="G2447" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67662,7 +67668,7 @@
         <v>27.5</v>
       </c>
       <c r="G2448" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67688,7 +67694,7 @@
         <v>27.75</v>
       </c>
       <c r="G2449" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67714,7 +67720,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G2450" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67740,7 +67746,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G2451" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67766,7 +67772,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G2452" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67792,7 +67798,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G2453" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67818,7 +67824,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G2454" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67844,7 +67850,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G2455" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67870,7 +67876,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67896,7 +67902,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67922,7 +67928,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G2458" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67948,7 +67954,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G2459" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67974,7 +67980,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G2460" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68000,7 +68006,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2461" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68026,7 +68032,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68052,7 +68058,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68078,7 +68084,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68104,7 +68110,7 @@
         <v>28.75</v>
       </c>
       <c r="G2465" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68130,7 +68136,7 @@
         <v>29</v>
       </c>
       <c r="G2466" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68156,7 +68162,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68182,7 +68188,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G2468" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68208,7 +68214,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68234,7 +68240,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68260,7 +68266,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68286,7 +68292,7 @@
         <v>29.9500007629395</v>
       </c>
       <c r="G2472" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68312,7 +68318,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68338,7 +68344,7 @@
         <v>30</v>
       </c>
       <c r="G2474" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68364,7 +68370,7 @@
         <v>29.75</v>
       </c>
       <c r="G2475" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68390,7 +68396,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G2476" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68416,7 +68422,7 @@
         <v>30</v>
       </c>
       <c r="G2477" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68442,7 +68448,7 @@
         <v>30.5</v>
       </c>
       <c r="G2478" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68468,7 +68474,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G2479" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68494,7 +68500,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68520,7 +68526,7 @@
         <v>31.25</v>
       </c>
       <c r="G2481" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68546,7 +68552,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G2482" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68572,7 +68578,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68598,7 +68604,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68624,7 +68630,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G2485" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68650,7 +68656,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G2486" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68676,7 +68682,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G2487" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68702,7 +68708,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2488" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68728,7 +68734,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2489" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68754,7 +68760,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G2490" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68780,7 +68786,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G2491" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68806,7 +68812,7 @@
         <v>32.5</v>
       </c>
       <c r="G2492" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68832,7 +68838,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G2493" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68858,7 +68864,7 @@
         <v>33</v>
       </c>
       <c r="G2494" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68884,7 +68890,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G2495" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68910,7 +68916,7 @@
         <v>33</v>
       </c>
       <c r="G2496" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68918,7 +68924,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6493055556</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>37707</v>
@@ -68936,9 +68942,35 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G2497" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6910416667</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>96452</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>33.9000015258789</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>32.9500007629395</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8067121505737</t>
+    <t xml:space="preserve">13.8067140579224</t>
   </si>
   <si>
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9573364257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3883285522461</t>
+    <t xml:space="preserve">14.0577440261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.957332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3883275985718</t>
   </si>
   <si>
     <t xml:space="preserve">12.889612197876</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8527975082397</t>
+    <t xml:space="preserve">12.8527965545654</t>
   </si>
   <si>
     <t xml:space="preserve">12.9532089233398</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">12.6184988021851</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4846172332764</t>
+    <t xml:space="preserve">12.4846153259277</t>
   </si>
   <si>
     <t xml:space="preserve">12.3842039108276</t>
@@ -83,163 +83,163 @@
     <t xml:space="preserve">10.7307453155518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2294607162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2194185256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2461977005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9148359298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1323947906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6143760681152</t>
+    <t xml:space="preserve">11.2294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2194204330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2461957931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9148349761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1323957443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6143751144409</t>
   </si>
   <si>
     <t xml:space="preserve">11.6813173294067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474338531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3466081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3131370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3298740386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8947515487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8780164718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0453720092773</t>
+    <t xml:space="preserve">11.5474328994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3466091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.313138961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.329873085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8947525024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8780183792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0453701019287</t>
   </si>
   <si>
     <t xml:space="preserve">10.4261608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4094257354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7080926895142</t>
+    <t xml:space="preserve">10.4094247817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7080955505371</t>
   </si>
   <si>
     <t xml:space="preserve">11.7147874832153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0494966506958</t>
+    <t xml:space="preserve">12.0494947433472</t>
   </si>
   <si>
     <t xml:space="preserve">11.7482576370239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7449102401733</t>
+    <t xml:space="preserve">11.744912147522</t>
   </si>
   <si>
     <t xml:space="preserve">12.2135038375854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.216851234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3674697875977</t>
+    <t xml:space="preserve">12.2168493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3674688339233</t>
   </si>
   <si>
     <t xml:space="preserve">12.7189140319824</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8293685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0201501846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2209749221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3849821090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536193847656</t>
+    <t xml:space="preserve">12.8293676376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.02015209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2209739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3849811553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870914459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536212921143</t>
   </si>
   <si>
     <t xml:space="preserve">13.334774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3146924972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569677352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661832809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306028366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2879161834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8260192871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9833326339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9030017852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2377109527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1674213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1138687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5047006607056</t>
+    <t xml:space="preserve">13.3146934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569667816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661823272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2879180908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8260183334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9833345413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.903000831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2377099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1674203872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1138668060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.097131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5046997070312</t>
   </si>
   <si>
     <t xml:space="preserve">12.8092842102051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8862676620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7055253982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7222585678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9163904190063</t>
+    <t xml:space="preserve">12.8862657546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7055234909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7222576141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.916389465332</t>
   </si>
   <si>
     <t xml:space="preserve">13.0301885604858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8327140808105</t>
+    <t xml:space="preserve">12.8327121734619</t>
   </si>
   <si>
     <t xml:space="preserve">12.6318893432617</t>
@@ -248,103 +248,103 @@
     <t xml:space="preserve">12.7021780014038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8695306777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5582504272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5682916641235</t>
+    <t xml:space="preserve">12.8695316314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5582523345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5682935714722</t>
   </si>
   <si>
     <t xml:space="preserve">12.8360595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958946228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5348215103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7791585922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7691202163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7865657806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5024194717407</t>
+    <t xml:space="preserve">12.8494510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958936691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5348224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7791604995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.769118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.786566734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5024213790894</t>
   </si>
   <si>
     <t xml:space="preserve">12.6512594223022</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7527389526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5836057662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4990377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5700731277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159511566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2791614532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0660524368286</t>
+    <t xml:space="preserve">12.7527370452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5836048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4990367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5700740814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2791624069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0660514831543</t>
   </si>
   <si>
     <t xml:space="preserve">12.1776819229126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1641511917114</t>
+    <t xml:space="preserve">12.1641502380371</t>
   </si>
   <si>
     <t xml:space="preserve">12.170916557312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1100292205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1269416809082</t>
+    <t xml:space="preserve">12.1100282669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1269407272339</t>
   </si>
   <si>
     <t xml:space="preserve">11.981484413147</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7459735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580238342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231372833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6973419189453</t>
+    <t xml:space="preserve">12.7459726333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231382369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6973400115967</t>
   </si>
   <si>
     <t xml:space="preserve">11.7785243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2406759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8212242126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554708480835</t>
+    <t xml:space="preserve">11.2406768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8212232589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554718017578</t>
   </si>
   <si>
     <t xml:space="preserve">11.0613956451416</t>
@@ -353,16 +353,16 @@
     <t xml:space="preserve">11.196702003479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4064283370972</t>
+    <t xml:space="preserve">11.4064302444458</t>
   </si>
   <si>
     <t xml:space="preserve">11.5248231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6656198501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1886615753174</t>
+    <t xml:space="preserve">10.665620803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1886596679688</t>
   </si>
   <si>
     <t xml:space="preserve">10.5878171920776</t>
@@ -374,46 +374,46 @@
     <t xml:space="preserve">11.839412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0199708938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3616247177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0233564376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1924886703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4969329833984</t>
+    <t xml:space="preserve">13.0199737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3616218566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0233554840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1924896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4969320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.4698686599731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5307569503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4800157546997</t>
+    <t xml:space="preserve">13.5307588577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4800176620483</t>
   </si>
   <si>
     <t xml:space="preserve">13.2939691543579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3108806610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548564910889</t>
+    <t xml:space="preserve">13.3108825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548583984375</t>
   </si>
   <si>
     <t xml:space="preserve">13.0740947723389</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0368843078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9489336013794</t>
+    <t xml:space="preserve">13.03688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.948935508728</t>
   </si>
   <si>
     <t xml:space="preserve">12.982762336731</t>
@@ -428,124 +428,124 @@
     <t xml:space="preserve">12.9962921142578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8576030731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113033294678</t>
+    <t xml:space="preserve">12.8576021194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113023757935</t>
   </si>
   <si>
     <t xml:space="preserve">13.1248340606689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1823415756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0605640411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857233047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4123649597168</t>
+    <t xml:space="preserve">13.1823396682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0605630874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4123640060425</t>
   </si>
   <si>
     <t xml:space="preserve">13.5679683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4157438278198</t>
+    <t xml:space="preserve">13.4157457351685</t>
   </si>
   <si>
     <t xml:space="preserve">13.513843536377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7066564559937</t>
+    <t xml:space="preserve">13.7066583633423</t>
   </si>
   <si>
     <t xml:space="preserve">13.8352003097534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2106790542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4576139450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7552900314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838319778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0157585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9853143692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303480148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6652364730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2897567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8297119140625</t>
+    <t xml:space="preserve">14.2106771469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.457615852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7552919387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838329315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.01575756073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9853134155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303470611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6652326583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.289755821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8297109603882</t>
   </si>
   <si>
     <t xml:space="preserve">14.6842546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7722034454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.951488494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7485246658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7180805206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8770694732666</t>
+    <t xml:space="preserve">14.7722053527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9514875411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7485265731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7180814743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8770666122437</t>
   </si>
   <si>
     <t xml:space="preserve">14.7992658615112</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9751663208008</t>
+    <t xml:space="preserve">14.9751653671265</t>
   </si>
   <si>
     <t xml:space="preserve">14.9007472991943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2018060684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939781188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988451004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9142780303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9278078079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.738377571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7248487472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5421829223633</t>
+    <t xml:space="preserve">15.2018032073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939828872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988470077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9142761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.927809715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7383766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7248449325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5421838760376</t>
   </si>
   <si>
     <t xml:space="preserve">14.4440841674805</t>
@@ -554,13 +554,13 @@
     <t xml:space="preserve">15.0529670715332</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1443004608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1104698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.954870223999</t>
+    <t xml:space="preserve">15.1443014144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1104736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9548692703247</t>
   </si>
   <si>
     <t xml:space="preserve">15.0901775360107</t>
@@ -569,121 +569,121 @@
     <t xml:space="preserve">15.2187204360962</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7823524475098</t>
+    <t xml:space="preserve">14.7823534011841</t>
   </si>
   <si>
     <t xml:space="preserve">14.6707239151001</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6166000366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764295578003</t>
+    <t xml:space="preserve">14.6165981292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764276504517</t>
   </si>
   <si>
     <t xml:space="preserve">14.1599359512329</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2546548843384</t>
+    <t xml:space="preserve">14.2546539306641</t>
   </si>
   <si>
     <t xml:space="preserve">14.0415439605713</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1125802993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.038161277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1430244445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903810501099</t>
+    <t xml:space="preserve">14.1125822067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0381593704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1430225372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903820037842</t>
   </si>
   <si>
     <t xml:space="preserve">14.3527517318726</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2072944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3561344146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373216629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730497360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3087759017944</t>
+    <t xml:space="preserve">14.2072954177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3561334609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373188018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3087778091431</t>
   </si>
   <si>
     <t xml:space="preserve">14.2411212921143</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3392200469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2512693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464071273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058149337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.119348526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2275943756104</t>
+    <t xml:space="preserve">14.3392181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2512712478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1464061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058158874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1193466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2275905609131</t>
   </si>
   <si>
     <t xml:space="preserve">14.2715673446655</t>
   </si>
   <si>
-    <t xml:space="preserve">14.149790763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0753726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0719881057739</t>
+    <t xml:space="preserve">14.1497926712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0753698348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0719871520996</t>
   </si>
   <si>
     <t xml:space="preserve">14.2749500274658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1667060852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4779090881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267490386963</t>
+    <t xml:space="preserve">14.1667041778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4779100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267528533936</t>
   </si>
   <si>
     <t xml:space="preserve">14.7519083023071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8161811828613</t>
+    <t xml:space="preserve">14.8161773681641</t>
   </si>
   <si>
     <t xml:space="preserve">15.1037101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0834150314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882762908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172380447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1544485092163</t>
+    <t xml:space="preserve">15.0834121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882734298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1544456481934</t>
   </si>
   <si>
     <t xml:space="preserve">15.2999057769775</t>
@@ -692,94 +692,94 @@
     <t xml:space="preserve">15.4758033752441</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3574075698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3912382125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893369674683</t>
+    <t xml:space="preserve">15.3574085235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3912363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893360137939</t>
   </si>
   <si>
     <t xml:space="preserve">15.1713638305664</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1003217697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946180343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3168172836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3134336471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4182987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4250650405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366897583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6753845214844</t>
+    <t xml:space="preserve">15.1003255844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946170806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.316819190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3134346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4182977676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4250640869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366926193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6753826141357</t>
   </si>
   <si>
     <t xml:space="preserve">15.6449384689331</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7295074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6618490219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.651704788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.682147026062</t>
+    <t xml:space="preserve">15.7295083999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6618528366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6517019271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6821479797363</t>
   </si>
   <si>
     <t xml:space="preserve">15.5637521743774</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4081506729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415567398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7024450302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.65846824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588928222656</t>
+    <t xml:space="preserve">15.4081497192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415586471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7024421691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333108901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584692001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.458890914917</t>
   </si>
   <si>
     <t xml:space="preserve">15.5874338150024</t>
   </si>
   <si>
-    <t xml:space="preserve">15.655086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227411270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3350086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0339488983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.406042098999</t>
+    <t xml:space="preserve">15.6550893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227373123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3350105285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0339469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4060459136963</t>
   </si>
   <si>
     <t xml:space="preserve">16.402660369873</t>
@@ -788,25 +788,25 @@
     <t xml:space="preserve">16.4195747375488</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6935729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.099494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9980163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1671466827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4208488464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5392417907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6407260894775</t>
+    <t xml:space="preserve">16.6935691833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0994968414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9980144500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1671504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4208507537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5392456054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6407279968262</t>
   </si>
   <si>
     <t xml:space="preserve">17.4039363861084</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">17.3870239257812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.522331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4546756744385</t>
+    <t xml:space="preserve">17.5223331451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4546775817871</t>
   </si>
   <si>
     <t xml:space="preserve">17.877513885498</t>
@@ -833,22 +833,22 @@
     <t xml:space="preserve">17.8098602294922</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7083759307861</t>
+    <t xml:space="preserve">17.7083778381348</t>
   </si>
   <si>
     <t xml:space="preserve">17.7591190338135</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6745529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5730724334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3362846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2009754180908</t>
+    <t xml:space="preserve">17.6745510101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.573070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3362827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2009735107422</t>
   </si>
   <si>
     <t xml:space="preserve">17.2348041534424</t>
@@ -857,16 +857,16 @@
     <t xml:space="preserve">17.2517166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2178916931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3701095581055</t>
+    <t xml:space="preserve">17.2178897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3701114654541</t>
   </si>
   <si>
     <t xml:space="preserve">17.456018447876</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7147541046143</t>
+    <t xml:space="preserve">17.7147560119629</t>
   </si>
   <si>
     <t xml:space="preserve">17.5767650604248</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">17.5595149993896</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6975059509277</t>
+    <t xml:space="preserve">17.6975040435791</t>
   </si>
   <si>
     <t xml:space="preserve">17.4698181152344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6147117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7729568481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0075435638428</t>
+    <t xml:space="preserve">17.614709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7729587554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0075454711914</t>
   </si>
   <si>
     <t xml:space="preserve">17.1662368774414</t>
@@ -905,28 +905,28 @@
     <t xml:space="preserve">16.9661464691162</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8350524902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8488540649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8281574249268</t>
+    <t xml:space="preserve">16.835054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8488521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8281536102295</t>
   </si>
   <si>
     <t xml:space="preserve">16.7591590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8695526123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9178524017334</t>
+    <t xml:space="preserve">16.8695545196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9178485870361</t>
   </si>
   <si>
     <t xml:space="preserve">16.9730472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.938549041748</t>
+    <t xml:space="preserve">16.9385509490967</t>
   </si>
   <si>
     <t xml:space="preserve">17.152437210083</t>
@@ -935,16 +935,16 @@
     <t xml:space="preserve">16.6625633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5935668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5659713745117</t>
+    <t xml:space="preserve">16.5935688018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5659694671631</t>
   </si>
   <si>
     <t xml:space="preserve">16.5038738250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626556396484</t>
+    <t xml:space="preserve">16.8626537322998</t>
   </si>
   <si>
     <t xml:space="preserve">16.9040508270264</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">16.80055809021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8971500396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5383701324463</t>
+    <t xml:space="preserve">16.8971519470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5383682250977</t>
   </si>
   <si>
     <t xml:space="preserve">16.5590705871582</t>
@@ -965,37 +965,37 @@
     <t xml:space="preserve">16.4900741577148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2416896820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.303783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2485866546631</t>
+    <t xml:space="preserve">16.2416915893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3037815093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2485847473145</t>
   </si>
   <si>
     <t xml:space="preserve">16.1243953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1864910125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1588897705078</t>
+    <t xml:space="preserve">16.1864891052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1588916778564</t>
   </si>
   <si>
     <t xml:space="preserve">16.5314712524414</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2899856567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3175830841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5452690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3658828735352</t>
+    <t xml:space="preserve">16.2899837493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3175849914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5452728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3658809661865</t>
   </si>
   <si>
     <t xml:space="preserve">16.4624767303467</t>
@@ -1004,25 +1004,25 @@
     <t xml:space="preserve">16.3313827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3520832061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6970634460449</t>
+    <t xml:space="preserve">16.3520851135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6970615386963</t>
   </si>
   <si>
     <t xml:space="preserve">16.3865814208984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4486751556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5107707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4210777282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4348754882812</t>
+    <t xml:space="preserve">16.4486770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5107727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4210758209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4348773956299</t>
   </si>
   <si>
     <t xml:space="preserve">16.3934783935547</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">16.4969730377197</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5245723724365</t>
+    <t xml:space="preserve">16.5245742797852</t>
   </si>
   <si>
     <t xml:space="preserve">16.4003791809082</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">16.3589782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2830848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5521697998047</t>
+    <t xml:space="preserve">16.2830867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5521678924561</t>
   </si>
   <si>
     <t xml:space="preserve">16.1795902252197</t>
@@ -1061,46 +1061,46 @@
     <t xml:space="preserve">16.1519927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9036073684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5586261749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4965286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.938102722168</t>
+    <t xml:space="preserve">15.9036064147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5586242675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.496527671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9381046295166</t>
   </si>
   <si>
     <t xml:space="preserve">15.7794151306152</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7656164169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7863130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9795026779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.931206703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7035188674927</t>
+    <t xml:space="preserve">15.7656145095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7863121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9795017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9312076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7035179138184</t>
   </si>
   <si>
     <t xml:space="preserve">15.6483221054077</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8415117263794</t>
+    <t xml:space="preserve">15.8415098190308</t>
   </si>
   <si>
     <t xml:space="preserve">15.7518157958984</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8691101074219</t>
+    <t xml:space="preserve">15.8691082000732</t>
   </si>
   <si>
     <t xml:space="preserve">15.8622093200684</t>
@@ -1109,88 +1109,88 @@
     <t xml:space="preserve">16.0277996063232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8967084884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6276216506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7173175811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310287475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413318634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2481460571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3171396255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3309383392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.282642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792352676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619428634644</t>
+    <t xml:space="preserve">15.89670753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6276206970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7173166275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310277938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034284591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413328170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2481441497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3171424865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3309392929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2826414108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.261944770813</t>
   </si>
   <si>
     <t xml:space="preserve">15.6000242233276</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4896306991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.951904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9726009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.986403465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0415992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8553085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932119369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2895402908325</t>
+    <t xml:space="preserve">15.4896297454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9519071578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9726047515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9864025115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0416011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8553104400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932147979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2895421981812</t>
   </si>
   <si>
     <t xml:space="preserve">15.1791467666626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.206748008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3999319076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2343454360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3033409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137344360352</t>
+    <t xml:space="preserve">15.2067470550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3999347686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2343444824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033418655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137353897095</t>
   </si>
   <si>
     <t xml:space="preserve">15.3861351013184</t>
@@ -1199,31 +1199,31 @@
     <t xml:space="preserve">15.634521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1450958251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4831714630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6073684692383</t>
+    <t xml:space="preserve">16.1450939178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4831733703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6073665618896</t>
   </si>
   <si>
     <t xml:space="preserve">16.3727798461914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6349639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.414176940918</t>
+    <t xml:space="preserve">16.6349678039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141788482666</t>
   </si>
   <si>
     <t xml:space="preserve">16.0898952484131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.200288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.731559753418</t>
+    <t xml:space="preserve">16.2002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7315616607666</t>
   </si>
   <si>
     <t xml:space="preserve">16.6901626586914</t>
@@ -1232,22 +1232,22 @@
     <t xml:space="preserve">16.4762763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7522602081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6487636566162</t>
+    <t xml:space="preserve">16.7522583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6487617492676</t>
   </si>
   <si>
     <t xml:space="preserve">16.6280670166016</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0420455932617</t>
+    <t xml:space="preserve">17.0420417785645</t>
   </si>
   <si>
     <t xml:space="preserve">17.0765399932861</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1110401153564</t>
+    <t xml:space="preserve">17.1110382080078</t>
   </si>
   <si>
     <t xml:space="preserve">17.2145328521729</t>
@@ -1256,52 +1256,52 @@
     <t xml:space="preserve">17.1455364227295</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1800346374512</t>
+    <t xml:space="preserve">17.1800365447998</t>
   </si>
   <si>
     <t xml:space="preserve">16.00710105896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2140884399414</t>
+    <t xml:space="preserve">16.21409034729</t>
   </si>
   <si>
     <t xml:space="preserve">16.110595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5931253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0066566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.730673789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9031629562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9721622467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.455132484436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1101531982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0411539077759</t>
+    <t xml:space="preserve">15.5931234359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0066576004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7306728363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9031639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9721593856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551305770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1101493835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0411548614502</t>
   </si>
   <si>
     <t xml:space="preserve">15.0756530761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3516359329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4206352233887</t>
+    <t xml:space="preserve">15.351637840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.42063331604</t>
   </si>
   <si>
     <t xml:space="preserve">15.5241279602051</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">15.6966190338135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0156669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.874249458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5560541152954</t>
+    <t xml:space="preserve">16.0156650543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8742475509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5560550689697</t>
   </si>
   <si>
     <t xml:space="preserve">15.7328290939331</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5914106369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3439292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792819976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7782535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.424708366394</t>
+    <t xml:space="preserve">15.5914087295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3439283370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.379282951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7782516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4247064590454</t>
   </si>
   <si>
     <t xml:space="preserve">14.5307693481445</t>
@@ -1343,10 +1343,10 @@
     <t xml:space="preserve">14.4600620269775</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4954147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8873157501221</t>
+    <t xml:space="preserve">14.495415687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8873167037964</t>
   </si>
   <si>
     <t xml:space="preserve">14.1135845184326</t>
@@ -1358,40 +1358,40 @@
     <t xml:space="preserve">14.6014795303345</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0257358551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0610904693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9550275802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8489646911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8843173980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7075452804565</t>
+    <t xml:space="preserve">15.0257339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0610876083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9550285339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8489627838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.884316444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7075443267822</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671562194824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2025127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.566125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6368341445923</t>
+    <t xml:space="preserve">15.2025098800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5661277770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6368350982666</t>
   </si>
   <si>
     <t xml:space="preserve">14.2832889556885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0853042602539</t>
+    <t xml:space="preserve">14.0853004455566</t>
   </si>
   <si>
     <t xml:space="preserve">14.81360912323</t>
@@ -1400,46 +1400,46 @@
     <t xml:space="preserve">14.3539972305298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3893508911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.74289894104</t>
+    <t xml:space="preserve">14.3893527984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428998947144</t>
   </si>
   <si>
     <t xml:space="preserve">14.1418695449829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1772232055664</t>
+    <t xml:space="preserve">14.177225112915</t>
   </si>
   <si>
     <t xml:space="preserve">14.2479314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2125778198242</t>
+    <t xml:space="preserve">14.2125797271729</t>
   </si>
   <si>
     <t xml:space="preserve">14.071159362793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9438810348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8731737136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8166084289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8590316772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0145931243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.929741859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0004501342773</t>
+    <t xml:space="preserve">13.9438819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8731756210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8166065216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8590307235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0145921707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9297428131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0004510879517</t>
   </si>
   <si>
     <t xml:space="preserve">14.0994434356689</t>
@@ -1448,19 +1448,19 @@
     <t xml:space="preserve">13.9721670150757</t>
   </si>
   <si>
-    <t xml:space="preserve">14.028733253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.057017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1277284622192</t>
+    <t xml:space="preserve">14.0287351608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.127724647522</t>
   </si>
   <si>
     <t xml:space="preserve">14.9196720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6721887588501</t>
+    <t xml:space="preserve">14.6721868515015</t>
   </si>
   <si>
     <t xml:space="preserve">13.4347763061523</t>
@@ -1469,28 +1469,28 @@
     <t xml:space="preserve">13.5054864883423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4913425445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3782072067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4630603790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5620536804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.533766746521</t>
+    <t xml:space="preserve">13.4913444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3782091140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.463059425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5620527267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5337696075439</t>
   </si>
   <si>
     <t xml:space="preserve">13.1660804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7842502593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6852569580078</t>
+    <t xml:space="preserve">12.7842483520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6852560043335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1620082855225</t>
@@ -1499,19 +1499,19 @@
     <t xml:space="preserve">12.6569728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4064893722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5479097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7883205413818</t>
+    <t xml:space="preserve">13.4064903259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5479106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7883234024048</t>
   </si>
   <si>
     <t xml:space="preserve">13.7741804122925</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5903367996216</t>
+    <t xml:space="preserve">13.5903358459473</t>
   </si>
   <si>
     <t xml:space="preserve">13.4489164352417</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">13.3074989318848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.392352104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.01051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1519393920898</t>
+    <t xml:space="preserve">13.3923501968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0105199813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1519374847412</t>
   </si>
   <si>
     <t xml:space="preserve">13.2933559417725</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">12.9256687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0388040542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.996376991272</t>
+    <t xml:space="preserve">13.0388021469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9963788986206</t>
   </si>
   <si>
     <t xml:space="preserve">13.2367897033691</t>
@@ -1547,52 +1547,52 @@
     <t xml:space="preserve">13.0953712463379</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6469049453735</t>
+    <t xml:space="preserve">13.6469039916992</t>
   </si>
   <si>
     <t xml:space="preserve">13.6751871109009</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0670871734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2509298324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2085075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812292098999</t>
+    <t xml:space="preserve">13.0670881271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2509326934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2085065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812282562256</t>
   </si>
   <si>
     <t xml:space="preserve">13.3499240875244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8408174514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5296945571899</t>
+    <t xml:space="preserve">12.8408164978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5296964645386</t>
   </si>
   <si>
     <t xml:space="preserve">12.897385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6004037857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7317562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5761957168579</t>
+    <t xml:space="preserve">12.6004056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7317543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5761947631836</t>
   </si>
   <si>
     <t xml:space="preserve">13.519627571106</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7176103591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8307476043701</t>
+    <t xml:space="preserve">13.7176113128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8307456970215</t>
   </si>
   <si>
     <t xml:space="preserve">13.7600374221802</t>
@@ -1601,34 +1601,34 @@
     <t xml:space="preserve">13.915599822998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7458982467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0428781509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8448915481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.54176902771</t>
+    <t xml:space="preserve">13.7458972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0428762435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8448905944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5417680740356</t>
   </si>
   <si>
     <t xml:space="preserve">14.2218475341797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9455547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1782236099243</t>
+    <t xml:space="preserve">13.9455556869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.17822265625</t>
   </si>
   <si>
     <t xml:space="preserve">13.9891805648804</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2073078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4399766921997</t>
+    <t xml:space="preserve">14.2073068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4399747848511</t>
   </si>
   <si>
     <t xml:space="preserve">14.265474319458</t>
@@ -1637,58 +1637,58 @@
     <t xml:space="preserve">14.4108924865723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4981422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527221679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3381805419922</t>
+    <t xml:space="preserve">14.4981412887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690580368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3381834030151</t>
   </si>
   <si>
     <t xml:space="preserve">14.5126829147339</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3963489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871862411499</t>
+    <t xml:space="preserve">14.3963499069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871871948242</t>
   </si>
   <si>
     <t xml:space="preserve">14.4254341125488</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4836025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6144771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8326025009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9780197143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1234359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1961460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4142742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4506273269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3415641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2325010299683</t>
+    <t xml:space="preserve">14.4836006164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6144781112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8326005935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9780216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1234350204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1961469650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4142732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.450626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3415660858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2325019836426</t>
   </si>
   <si>
     <t xml:space="preserve">15.3052091598511</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">15.268856048584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6687526702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0507278442383</t>
+    <t xml:space="preserve">15.6687536239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0507297515869</t>
   </si>
   <si>
     <t xml:space="preserve">15.0870847702026</t>
@@ -1709,25 +1709,25 @@
     <t xml:space="preserve">14.9416646957397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7235403060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0143728256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5781211853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7598943710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6508312225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3672666549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3236427307129</t>
+    <t xml:space="preserve">14.7235383987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0143747329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5781221389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7598934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6508283615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3672676086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3236408233643</t>
   </si>
   <si>
     <t xml:space="preserve">14.5272254943848</t>
@@ -1736,22 +1736,22 @@
     <t xml:space="preserve">14.454514503479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7962484359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9053115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0322971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.359489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5049076080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6139678955078</t>
+    <t xml:space="preserve">14.7962493896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9053106307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0322952270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3594875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5049057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6139717102051</t>
   </si>
   <si>
     <t xml:space="preserve">16.5412616729736</t>
@@ -1760,22 +1760,22 @@
     <t xml:space="preserve">16.8320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6503257751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.577615737915</t>
+    <t xml:space="preserve">16.6503219604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5776138305664</t>
   </si>
   <si>
     <t xml:space="preserve">16.8684501647949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7593860626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0502223968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0865783691406</t>
+    <t xml:space="preserve">16.7593841552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.050220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.086576461792</t>
   </si>
   <si>
     <t xml:space="preserve">17.4864730834961</t>
@@ -1796,19 +1796,19 @@
     <t xml:space="preserve">17.7409572601318</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7046012878418</t>
+    <t xml:space="preserve">17.631893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7046031951904</t>
   </si>
   <si>
     <t xml:space="preserve">17.6682472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0681476593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9227294921875</t>
+    <t xml:space="preserve">18.0681457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9227275848389</t>
   </si>
   <si>
     <t xml:space="preserve">18.1044998168945</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">17.8500194549561</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9590835571289</t>
+    <t xml:space="preserve">17.9590816497803</t>
   </si>
   <si>
     <t xml:space="preserve">18.177209854126</t>
@@ -1826,13 +1826,13 @@
     <t xml:space="preserve">18.0317916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2862739562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.358980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4680442810059</t>
+    <t xml:space="preserve">18.2862720489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3589820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4680461883545</t>
   </si>
   <si>
     <t xml:space="preserve">18.5771064758301</t>
@@ -1841,46 +1841,46 @@
     <t xml:space="preserve">17.9954376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5591812133789</t>
+    <t xml:space="preserve">17.5591831207275</t>
   </si>
   <si>
     <t xml:space="preserve">17.5955390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4501209259033</t>
+    <t xml:space="preserve">17.4501190185547</t>
   </si>
   <si>
     <t xml:space="preserve">18.2499179840088</t>
   </si>
   <si>
-    <t xml:space="preserve">18.395336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.213565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.322624206543</t>
+    <t xml:space="preserve">18.3953342437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2135620117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3226280212402</t>
   </si>
   <si>
     <t xml:space="preserve">18.6134624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8315868377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1951313018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9770069122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0860729217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2678413391113</t>
+    <t xml:space="preserve">18.6861686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8315887451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1951332092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9770050048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0860691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.26784324646</t>
   </si>
   <si>
     <t xml:space="preserve">19.1224231719971</t>
@@ -1892,10 +1892,10 @@
     <t xml:space="preserve">19.4132614135742</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4496116638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9048042297363</t>
+    <t xml:space="preserve">19.449613571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.904806137085</t>
   </si>
   <si>
     <t xml:space="preserve">16.7230339050293</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">16.7957420349121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2314872741699</t>
+    <t xml:space="preserve">19.2314891815186</t>
   </si>
   <si>
     <t xml:space="preserve">16.9775142669678</t>
@@ -1925,16 +1925,16 @@
     <t xml:space="preserve">18.5407543182373</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8679447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8495140075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4213848114014</t>
+    <t xml:space="preserve">18.8679428100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9042987823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8495121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.42138671875</t>
   </si>
   <si>
     <t xml:space="preserve">19.7327499389648</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">20.394401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8105926513672</t>
+    <t xml:space="preserve">19.8105907440186</t>
   </si>
   <si>
     <t xml:space="preserve">19.6549091339111</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">20.3554801940918</t>
   </si>
   <si>
-    <t xml:space="preserve">20.121955871582</t>
+    <t xml:space="preserve">20.1219577789307</t>
   </si>
   <si>
     <t xml:space="preserve">19.9273548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4603061676025</t>
+    <t xml:space="preserve">19.4603080749512</t>
   </si>
   <si>
     <t xml:space="preserve">19.3435440063477</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3046226501465</t>
+    <t xml:space="preserve">19.3046245574951</t>
   </si>
   <si>
     <t xml:space="preserve">19.9662742614746</t>
@@ -1973,22 +1973,22 @@
     <t xml:space="preserve">19.2657051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">19.771671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7597351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1608753204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0441150665283</t>
+    <t xml:space="preserve">19.7716732025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7597370147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1608772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.044116973877</t>
   </si>
   <si>
     <t xml:space="preserve">21.172815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0560493469238</t>
+    <t xml:space="preserve">21.0560512542725</t>
   </si>
   <si>
     <t xml:space="preserve">20.9392890930176</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">21.2895755767822</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0171318054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7836074829102</t>
+    <t xml:space="preserve">21.0171298980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7836093902588</t>
   </si>
   <si>
     <t xml:space="preserve">20.7057647705078</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">21.0949726104736</t>
   </si>
   <si>
-    <t xml:space="preserve">21.445255279541</t>
+    <t xml:space="preserve">21.4452571868896</t>
   </si>
   <si>
     <t xml:space="preserve">21.7566242218018</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">21.9512271881104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6009387969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7955436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0290641784668</t>
+    <t xml:space="preserve">21.6009407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7955417633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0290679931641</t>
   </si>
   <si>
     <t xml:space="preserve">22.0679874420166</t>
@@ -2033,13 +2033,13 @@
     <t xml:space="preserve">22.5350360870361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5739555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.651798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7685565948486</t>
+    <t xml:space="preserve">22.57395362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6517963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7685585021973</t>
   </si>
   <si>
     <t xml:space="preserve">22.8074779510498</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">22.7296390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3404331207275</t>
+    <t xml:space="preserve">22.3404312133789</t>
   </si>
   <si>
     <t xml:space="preserve">22.2625904083252</t>
@@ -2057,16 +2057,16 @@
     <t xml:space="preserve">23.5080509185791</t>
   </si>
   <si>
-    <t xml:space="preserve">23.97509765625</t>
+    <t xml:space="preserve">23.9750957489014</t>
   </si>
   <si>
     <t xml:space="preserve">24.4032249450684</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9091911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7145900726318</t>
+    <t xml:space="preserve">24.9091930389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7145881652832</t>
   </si>
   <si>
     <t xml:space="preserve">24.5199871063232</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">24.7924308776855</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1427154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7535095214844</t>
+    <t xml:space="preserve">25.1427135467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7535076141357</t>
   </si>
   <si>
     <t xml:space="preserve">24.6367473602295</t>
@@ -2093,31 +2093,31 @@
     <t xml:space="preserve">24.0140190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0799236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7026519775391</t>
+    <t xml:space="preserve">23.0799217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7026538848877</t>
   </si>
   <si>
     <t xml:space="preserve">24.0529384613037</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4691295623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5858898162842</t>
+    <t xml:space="preserve">23.4691257476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5858917236328</t>
   </si>
   <si>
     <t xml:space="preserve">23.1577644348145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8583354949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7415733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8194160461426</t>
+    <t xml:space="preserve">23.8583335876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7415752410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8194141387939</t>
   </si>
   <si>
     <t xml:space="preserve">23.6637325286865</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">23.4302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0918579101562</t>
+    <t xml:space="preserve">24.0918617248535</t>
   </si>
   <si>
     <t xml:space="preserve">23.3912887573242</t>
@@ -2135,52 +2135,52 @@
     <t xml:space="preserve">23.352367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0410022735596</t>
+    <t xml:space="preserve">23.0410041809082</t>
   </si>
   <si>
     <t xml:space="preserve">23.0020809173584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1188449859619</t>
+    <t xml:space="preserve">23.1188430786133</t>
   </si>
   <si>
     <t xml:space="preserve">23.6248111724854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6128749847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1069068908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1847496032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.496114730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3015098571777</t>
+    <t xml:space="preserve">22.6128768920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1069087982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1847476959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4961128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3015117645264</t>
   </si>
   <si>
     <t xml:space="preserve">22.6907157897949</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3793506622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9631595611572</t>
+    <t xml:space="preserve">22.3793525695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9631614685059</t>
   </si>
   <si>
     <t xml:space="preserve">23.2356071472168</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9242401123047</t>
+    <t xml:space="preserve">22.9242420196533</t>
   </si>
   <si>
     <t xml:space="preserve">22.223669052124</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4182720184326</t>
+    <t xml:space="preserve">22.4182739257812</t>
   </si>
   <si>
     <t xml:space="preserve">21.9123058319092</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">21.4841766357422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1338939666748</t>
+    <t xml:space="preserve">21.1338920593262</t>
   </si>
   <si>
     <t xml:space="preserve">21.523099899292</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">21.717700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6398582458496</t>
+    <t xml:space="preserve">21.6398601531982</t>
   </si>
   <si>
     <t xml:space="preserve">21.2506542205811</t>
@@ -2213,25 +2213,25 @@
     <t xml:space="preserve">21.6787815093994</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9901466369629</t>
+    <t xml:space="preserve">21.9901447296143</t>
   </si>
   <si>
     <t xml:space="preserve">22.1458282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8464012145996</t>
+    <t xml:space="preserve">22.846399307251</t>
   </si>
   <si>
     <t xml:space="preserve">22.8853206634521</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4571952819824</t>
+    <t xml:space="preserve">22.4571933746338</t>
   </si>
   <si>
     <t xml:space="preserve">21.3284950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2117347717285</t>
+    <t xml:space="preserve">21.2117328643799</t>
   </si>
   <si>
     <t xml:space="preserve">21.3674163818359</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">21.873384475708</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4407329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.88356590271</t>
+    <t xml:space="preserve">23.440731048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8835639953613</t>
   </si>
   <si>
     <t xml:space="preserve">22.7243747711182</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">22.8039703369141</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7641754150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0427551269531</t>
+    <t xml:space="preserve">22.7641716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0427570343018</t>
   </si>
   <si>
     <t xml:space="preserve">23.2417449951172</t>
@@ -2273,13 +2273,13 @@
     <t xml:space="preserve">23.2019462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">23.122350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1621494293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5203247070312</t>
+    <t xml:space="preserve">23.1223487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1621475219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5203266143799</t>
   </si>
   <si>
     <t xml:space="preserve">23.9580993652344</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">24.6744537353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.913236618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.555061340332</t>
+    <t xml:space="preserve">24.9132385253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5550594329834</t>
   </si>
   <si>
     <t xml:space="preserve">24.7540493011475</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">24.1172885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5152645111084</t>
+    <t xml:space="preserve">24.5152626037598</t>
   </si>
   <si>
     <t xml:space="preserve">24.4754657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2366790771484</t>
+    <t xml:space="preserve">24.2366828918457</t>
   </si>
   <si>
     <t xml:space="preserve">24.3958702087402</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7142505645752</t>
+    <t xml:space="preserve">24.7142486572266</t>
   </si>
   <si>
     <t xml:space="preserve">24.6346569061279</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">25.6295928955078</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5102005004883</t>
+    <t xml:space="preserve">25.5102024078369</t>
   </si>
   <si>
     <t xml:space="preserve">25.1520233154297</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">25.4704036712646</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6693897247314</t>
+    <t xml:space="preserve">25.6693916320801</t>
   </si>
   <si>
     <t xml:space="preserve">25.3908100128174</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">25.1918201446533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0326309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2714176177979</t>
+    <t xml:space="preserve">25.0326328277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2714157104492</t>
   </si>
   <si>
     <t xml:space="preserve">24.8336448669434</t>
@@ -2378,10 +2378,10 @@
     <t xml:space="preserve">24.9530372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8683795928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0724277496338</t>
+    <t xml:space="preserve">25.8683776855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0724296569824</t>
   </si>
   <si>
     <t xml:space="preserve">23.7591114044189</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">23.8785037994385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6397190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7989063262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5948581695557</t>
+    <t xml:space="preserve">23.639720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7989101409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.594856262207</t>
   </si>
   <si>
     <t xml:space="preserve">24.9928321838379</t>
@@ -2411,22 +2411,22 @@
     <t xml:space="preserve">25.3112125396729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2316188812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0673656463623</t>
+    <t xml:space="preserve">25.2316207885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0673675537109</t>
   </si>
   <si>
     <t xml:space="preserve">26.2663536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0275707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7887859344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5499973297119</t>
+    <t xml:space="preserve">26.0275688171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7887840270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5499992370605</t>
   </si>
   <si>
     <t xml:space="preserve">25.5897960662842</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">25.7489833831787</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8734397888184</t>
+    <t xml:space="preserve">24.873441696167</t>
   </si>
   <si>
     <t xml:space="preserve">24.0376949310303</t>
@@ -2450,19 +2450,19 @@
     <t xml:space="preserve">22.3264007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3661975860596</t>
+    <t xml:space="preserve">22.3661994934082</t>
   </si>
   <si>
     <t xml:space="preserve">23.0825538635254</t>
   </si>
   <si>
-    <t xml:space="preserve">22.923360824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3213386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5999202728271</t>
+    <t xml:space="preserve">22.9233627319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3213367462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5999221801758</t>
   </si>
   <si>
     <t xml:space="preserve">23.3611354827881</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">23.5601234436035</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4855899810791</t>
+    <t xml:space="preserve">22.4855918884277</t>
   </si>
   <si>
     <t xml:space="preserve">23.8387069702148</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">23.8264102935791</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5692920684814</t>
+    <t xml:space="preserve">23.5692901611328</t>
   </si>
   <si>
     <t xml:space="preserve">24.1263828277588</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">24.1692371368408</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2120895385742</t>
+    <t xml:space="preserve">24.2120876312256</t>
   </si>
   <si>
     <t xml:space="preserve">23.7835578918457</t>
@@ -2519,19 +2519,19 @@
     <t xml:space="preserve">24.2549419403076</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977981567383</t>
+    <t xml:space="preserve">24.2977962493896</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264377593994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9978218078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9121150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8692626953125</t>
+    <t xml:space="preserve">23.99782371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9121170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8692646026611</t>
   </si>
   <si>
     <t xml:space="preserve">23.7407035827637</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">23.6549968719482</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9693450927734</t>
+    <t xml:space="preserve">22.9693431854248</t>
   </si>
   <si>
     <t xml:space="preserve">22.8836402893066</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">23.1407585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8407859802246</t>
+    <t xml:space="preserve">22.840784072876</t>
   </si>
   <si>
     <t xml:space="preserve">22.7550792694092</t>
@@ -2564,19 +2564,19 @@
     <t xml:space="preserve">22.6693725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0550518035889</t>
+    <t xml:space="preserve">23.0550498962402</t>
   </si>
   <si>
     <t xml:space="preserve">23.2264652252197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7122249603271</t>
+    <t xml:space="preserve">22.7122268676758</t>
   </si>
   <si>
     <t xml:space="preserve">22.4122524261475</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1836090087891</t>
+    <t xml:space="preserve">23.1836109161377</t>
   </si>
   <si>
     <t xml:space="preserve">23.0979061126709</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">22.3694000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3550243377686</t>
+    <t xml:space="preserve">23.3550262451172</t>
   </si>
   <si>
     <t xml:space="preserve">23.0121994018555</t>
@@ -2594,28 +2594,28 @@
     <t xml:space="preserve">23.3121719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">23.397876739502</t>
+    <t xml:space="preserve">23.3978748321533</t>
   </si>
   <si>
     <t xml:space="preserve">22.7979316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4551048278809</t>
+    <t xml:space="preserve">22.4551067352295</t>
   </si>
   <si>
     <t xml:space="preserve">22.4979591369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6265182495117</t>
+    <t xml:space="preserve">22.6265201568604</t>
   </si>
   <si>
     <t xml:space="preserve">23.6978511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5408115386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2693157196045</t>
+    <t xml:space="preserve">22.5408134460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2693176269531</t>
   </si>
   <si>
     <t xml:space="preserve">22.2836933135986</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">21.426628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4694805145264</t>
+    <t xml:space="preserve">21.469482421875</t>
   </si>
   <si>
     <t xml:space="preserve">21.2552146911621</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">20.6981220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5980434417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3837738037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5123348236084</t>
+    <t xml:space="preserve">21.5980415344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3837757110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5123329162598</t>
   </si>
   <si>
     <t xml:space="preserve">21.3409214019775</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">21.8123073577881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1551342010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2408409118652</t>
+    <t xml:space="preserve">22.1551322937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2408390045166</t>
   </si>
   <si>
     <t xml:space="preserve">21.6837463378906</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">21.0409469604492</t>
   </si>
   <si>
-    <t xml:space="preserve">20.912389755249</t>
+    <t xml:space="preserve">20.9123878479004</t>
   </si>
   <si>
     <t xml:space="preserve">21.2980690002441</t>
@@ -3461,9 +3461,6 @@
     <t xml:space="preserve">26.0499992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5499992370605</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.1499996185303</t>
   </si>
   <si>
@@ -3690,6 +3687,9 @@
   </si>
   <si>
     <t xml:space="preserve">33.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4000015258789</t>
   </si>
 </sst>
 </file>
@@ -66108,7 +66108,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G2388" t="s">
-        <v>1149</v>
+        <v>804</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66134,7 +66134,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66160,7 +66160,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66186,7 +66186,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G2391" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66212,7 +66212,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66238,7 +66238,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66264,7 +66264,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66290,7 +66290,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66316,7 +66316,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G2396" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66342,7 +66342,7 @@
         <v>26.75</v>
       </c>
       <c r="G2397" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66368,7 +66368,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2398" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66394,7 +66394,7 @@
         <v>27</v>
       </c>
       <c r="G2399" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66420,7 +66420,7 @@
         <v>27</v>
       </c>
       <c r="G2400" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66446,7 +66446,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66472,7 +66472,7 @@
         <v>26.25</v>
       </c>
       <c r="G2402" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66498,7 +66498,7 @@
         <v>25.5</v>
       </c>
       <c r="G2403" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66524,7 +66524,7 @@
         <v>25.25</v>
       </c>
       <c r="G2404" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66576,7 +66576,7 @@
         <v>25.25</v>
       </c>
       <c r="G2406" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66628,7 +66628,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G2408" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66654,7 +66654,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G2409" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66680,7 +66680,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G2410" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66706,7 +66706,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2411" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66732,7 +66732,7 @@
         <v>25.5</v>
       </c>
       <c r="G2412" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66784,7 +66784,7 @@
         <v>26</v>
       </c>
       <c r="G2414" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66810,7 +66810,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2415" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66836,7 +66836,7 @@
         <v>27</v>
       </c>
       <c r="G2416" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66862,7 +66862,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66888,7 +66888,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G2418" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66914,7 +66914,7 @@
         <v>27.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66940,7 +66940,7 @@
         <v>27.5</v>
       </c>
       <c r="G2420" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66966,7 +66966,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66992,7 +66992,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2422" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67018,7 +67018,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G2423" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67044,7 +67044,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2424" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67070,7 +67070,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G2425" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67096,7 +67096,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2426" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67122,7 +67122,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2427" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67148,7 +67148,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2428" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67174,7 +67174,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2429" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67200,7 +67200,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67226,7 +67226,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67252,7 +67252,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2432" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67278,7 +67278,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67304,7 +67304,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G2434" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67330,7 +67330,7 @@
         <v>29</v>
       </c>
       <c r="G2435" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67356,7 +67356,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G2436" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67382,7 +67382,7 @@
         <v>28.25</v>
       </c>
       <c r="G2437" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67408,7 +67408,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G2438" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67434,7 +67434,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67460,7 +67460,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2440" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67486,7 +67486,7 @@
         <v>27</v>
       </c>
       <c r="G2441" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67512,7 +67512,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2442" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67538,7 +67538,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G2443" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67564,7 +67564,7 @@
         <v>27.25</v>
       </c>
       <c r="G2444" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67590,7 +67590,7 @@
         <v>27.25</v>
       </c>
       <c r="G2445" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67616,7 +67616,7 @@
         <v>27.25</v>
       </c>
       <c r="G2446" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67642,7 +67642,7 @@
         <v>27.25</v>
       </c>
       <c r="G2447" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67668,7 +67668,7 @@
         <v>27.5</v>
       </c>
       <c r="G2448" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67694,7 +67694,7 @@
         <v>27.75</v>
       </c>
       <c r="G2449" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67720,7 +67720,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G2450" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67746,7 +67746,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G2451" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67772,7 +67772,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G2452" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67798,7 +67798,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G2453" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67824,7 +67824,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G2454" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67850,7 +67850,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G2455" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67876,7 +67876,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67902,7 +67902,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67928,7 +67928,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G2458" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67954,7 +67954,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G2459" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67980,7 +67980,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G2460" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68006,7 +68006,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2461" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68032,7 +68032,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68058,7 +68058,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68084,7 +68084,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68110,7 +68110,7 @@
         <v>28.75</v>
       </c>
       <c r="G2465" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68136,7 +68136,7 @@
         <v>29</v>
       </c>
       <c r="G2466" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68162,7 +68162,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68188,7 +68188,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G2468" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68214,7 +68214,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68240,7 +68240,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68266,7 +68266,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68292,7 +68292,7 @@
         <v>29.9500007629395</v>
       </c>
       <c r="G2472" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68318,7 +68318,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68344,7 +68344,7 @@
         <v>30</v>
       </c>
       <c r="G2474" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68370,7 +68370,7 @@
         <v>29.75</v>
       </c>
       <c r="G2475" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68396,7 +68396,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G2476" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68422,7 +68422,7 @@
         <v>30</v>
       </c>
       <c r="G2477" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68448,7 +68448,7 @@
         <v>30.5</v>
       </c>
       <c r="G2478" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68474,7 +68474,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G2479" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68500,7 +68500,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68526,7 +68526,7 @@
         <v>31.25</v>
       </c>
       <c r="G2481" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68552,7 +68552,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G2482" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68578,7 +68578,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68604,7 +68604,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68630,7 +68630,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G2485" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68656,7 +68656,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G2486" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68682,7 +68682,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G2487" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68708,7 +68708,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2488" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68734,7 +68734,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2489" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68760,7 +68760,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G2490" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68786,7 +68786,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G2491" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68812,7 +68812,7 @@
         <v>32.5</v>
       </c>
       <c r="G2492" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68838,7 +68838,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G2493" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68864,7 +68864,7 @@
         <v>33</v>
       </c>
       <c r="G2494" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68890,7 +68890,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G2495" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68916,7 +68916,7 @@
         <v>33</v>
       </c>
       <c r="G2496" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68942,7 +68942,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G2497" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68950,7 +68950,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6910416667</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>96452</v>
@@ -68968,9 +68968,35 @@
         <v>33.5</v>
       </c>
       <c r="G2498" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.691099537</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>21761</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>33.5999984741211</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>33.2999992370605</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>33.4500007629395</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>33.4000015258789</v>
+      </c>
+      <c r="G2499" t="s">
         <v>1225</v>
       </c>
-      <c r="H2498" t="s">
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="1227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="1228">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,73 +38,73 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8067150115967</t>
+    <t xml:space="preserve">13.806715965271</t>
   </si>
   <si>
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.057746887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9573316574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3883275985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.889612197876</t>
+    <t xml:space="preserve">14.0577459335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9573354721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3883295059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896141052246</t>
   </si>
   <si>
     <t xml:space="preserve">12.8527956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9532079696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.618501663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846181869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3842039108276</t>
+    <t xml:space="preserve">12.9532098770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6185007095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846162796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.384204864502</t>
   </si>
   <si>
     <t xml:space="preserve">11.8821420669556</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7348709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2127256393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7307462692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2294607162476</t>
+    <t xml:space="preserve">11.7348699569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2127246856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7307453155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2294616699219</t>
   </si>
   <si>
     <t xml:space="preserve">11.2194204330444</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2461957931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9148359298706</t>
+    <t xml:space="preserve">11.2461967468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9148349761963</t>
   </si>
   <si>
     <t xml:space="preserve">11.1323957443237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6143741607666</t>
+    <t xml:space="preserve">11.6143760681152</t>
   </si>
   <si>
     <t xml:space="preserve">11.6813173294067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474319458008</t>
+    <t xml:space="preserve">11.5474338531494</t>
   </si>
   <si>
     <t xml:space="preserve">11.3466091156006</t>
@@ -113,28 +113,28 @@
     <t xml:space="preserve">11.3131380081177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.329873085022</t>
+    <t xml:space="preserve">11.3298711776733</t>
   </si>
   <si>
     <t xml:space="preserve">10.8947525024414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8780174255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0453701019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4261608123779</t>
+    <t xml:space="preserve">10.8780164718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.045371055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4261617660522</t>
   </si>
   <si>
     <t xml:space="preserve">10.4094257354736</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7080936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.714786529541</t>
+    <t xml:space="preserve">11.7080945968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7147874832153</t>
   </si>
   <si>
     <t xml:space="preserve">12.0494956970215</t>
@@ -146,85 +146,85 @@
     <t xml:space="preserve">11.744912147522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2135047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168502807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3674688339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7189111709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8293657302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.020149230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2209749221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3849840164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536212921143</t>
+    <t xml:space="preserve">12.2135057449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.367467880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7189130783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.82936668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0201511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2209720611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3849830627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870923995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536203384399</t>
   </si>
   <si>
     <t xml:space="preserve">13.3347759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3146915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569667816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109346389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661813735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306028366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2879180908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8260192871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9833326339722</t>
+    <t xml:space="preserve">13.3146953582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569677352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306018829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2879161834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.826021194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9833307266235</t>
   </si>
   <si>
     <t xml:space="preserve">12.9029998779297</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2377109527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1674213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1138677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.097131729126</t>
+    <t xml:space="preserve">13.2377099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1674222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1138696670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971336364746</t>
   </si>
   <si>
     <t xml:space="preserve">12.5046997070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092832565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8862676620483</t>
+    <t xml:space="preserve">12.8092842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8862648010254</t>
   </si>
   <si>
     <t xml:space="preserve">12.7055234909058</t>
@@ -236,43 +236,43 @@
     <t xml:space="preserve">12.916389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0301904678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6318874359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7021780014038</t>
+    <t xml:space="preserve">13.0301923751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6318893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7021770477295</t>
   </si>
   <si>
     <t xml:space="preserve">12.8695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.558253288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5682935714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8360586166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494501113892</t>
+    <t xml:space="preserve">12.5582523345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5682954788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8360595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494482040405</t>
   </si>
   <si>
     <t xml:space="preserve">12.7958946228027</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5348234176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7791585922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.769118309021</t>
+    <t xml:space="preserve">12.5348224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7791604995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7691192626953</t>
   </si>
   <si>
     <t xml:space="preserve">12.7865657806396</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">12.5024194717407</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6512594223022</t>
+    <t xml:space="preserve">12.6512584686279</t>
   </si>
   <si>
     <t xml:space="preserve">12.752739906311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5836038589478</t>
+    <t xml:space="preserve">12.5836048126221</t>
   </si>
   <si>
     <t xml:space="preserve">12.4990367889404</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">12.5700731277466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5159511566162</t>
+    <t xml:space="preserve">12.5159502029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.2791614532471</t>
@@ -305,64 +305,64 @@
     <t xml:space="preserve">12.0660524368286</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1776819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1641492843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.170916557312</t>
+    <t xml:space="preserve">12.177680015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1641511917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1709156036377</t>
   </si>
   <si>
     <t xml:space="preserve">12.1100282669067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1269407272339</t>
+    <t xml:space="preserve">12.1269426345825</t>
   </si>
   <si>
     <t xml:space="preserve">11.9814853668213</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7459735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580219268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231372833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6973390579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7785234451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2406749725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8212232589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0613946914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1967000961304</t>
+    <t xml:space="preserve">12.7459764480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6973419189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.778525352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2406759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8212242126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.061393737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.196702003479</t>
   </si>
   <si>
     <t xml:space="preserve">11.4064283370972</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248241424561</t>
+    <t xml:space="preserve">11.5248231887817</t>
   </si>
   <si>
     <t xml:space="preserve">10.6656198501587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1886596679688</t>
+    <t xml:space="preserve">10.1886615753174</t>
   </si>
   <si>
     <t xml:space="preserve">10.587818145752</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">11.8394117355347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0199718475342</t>
+    <t xml:space="preserve">13.0199708938599</t>
   </si>
   <si>
     <t xml:space="preserve">13.3616237640381</t>
@@ -383,163 +383,163 @@
     <t xml:space="preserve">13.0233554840088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1924886703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4969301223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4698705673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307569503784</t>
+    <t xml:space="preserve">13.1924896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4969320297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4698686599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307579040527</t>
   </si>
   <si>
     <t xml:space="preserve">13.4800176620483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2939710617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108816146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548593521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0740947723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368852615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.948935508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.982762336731</t>
+    <t xml:space="preserve">13.2939672470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548564910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0740957260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368843078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9489336013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9827613830566</t>
   </si>
   <si>
     <t xml:space="preserve">13.091007232666</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0707130432129</t>
+    <t xml:space="preserve">13.0707111358643</t>
   </si>
   <si>
     <t xml:space="preserve">12.9962921142578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8576021194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113033294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1248350143433</t>
+    <t xml:space="preserve">12.8576011657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113061904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1248331069946</t>
   </si>
   <si>
     <t xml:space="preserve">13.1823415756226</t>
   </si>
   <si>
-    <t xml:space="preserve">13.060564994812</t>
+    <t xml:space="preserve">13.0605640411377</t>
   </si>
   <si>
     <t xml:space="preserve">13.1857223510742</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4123640060425</t>
+    <t xml:space="preserve">13.4123649597168</t>
   </si>
   <si>
     <t xml:space="preserve">13.567967414856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4157457351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5138444900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7066583633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8352003097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2106781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.457615852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7552928924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838338851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0157585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9853143692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303461074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6652345657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2897548675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8297119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7722053527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9514904022217</t>
+    <t xml:space="preserve">13.4157476425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5138416290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7066564559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8351993560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2106761932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4576148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7552900314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838329315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0157594680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9853115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303470611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6652326583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.289758682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8297090530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.684253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7722034454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.951488494873</t>
   </si>
   <si>
     <t xml:space="preserve">14.7485246658325</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7180833816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8770704269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7992687225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751663208008</t>
+    <t xml:space="preserve">14.7180805206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8770685195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7992668151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751644134521</t>
   </si>
   <si>
     <t xml:space="preserve">14.9007472991943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2018051147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939828872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330926895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9142789840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9278087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7383794784546</t>
+    <t xml:space="preserve">15.2018041610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939819335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988441467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9142770767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.927806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.738377571106</t>
   </si>
   <si>
     <t xml:space="preserve">14.7248477935791</t>
@@ -551,64 +551,64 @@
     <t xml:space="preserve">14.4440860748291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0529689788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1104745864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9548673629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0901775360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2187194824219</t>
+    <t xml:space="preserve">15.0529680252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1443014144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1104736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.954873085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0901784896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2187213897705</t>
   </si>
   <si>
     <t xml:space="preserve">14.7823534011841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6707277297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6166019439697</t>
+    <t xml:space="preserve">14.6707239151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6166009902954</t>
   </si>
   <si>
     <t xml:space="preserve">14.3764305114746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1599369049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2546539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0415439605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1125793457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.038161277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1430234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527488708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.20729637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3561344146729</t>
+    <t xml:space="preserve">14.1599388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2546548843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0415420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1125812530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0381631851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1430244445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903820037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527507781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.207293510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3561315536499</t>
   </si>
   <si>
     <t xml:space="preserve">14.4373178482056</t>
@@ -617,91 +617,91 @@
     <t xml:space="preserve">14.3730487823486</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3087768554688</t>
+    <t xml:space="preserve">14.3087759017944</t>
   </si>
   <si>
     <t xml:space="preserve">14.2411222457886</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3392210006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2512722015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464052200317</t>
+    <t xml:space="preserve">14.3392200469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2512712478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1464071273804</t>
   </si>
   <si>
     <t xml:space="preserve">14.1058139801025</t>
   </si>
   <si>
-    <t xml:space="preserve">14.119345664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2275924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2715682983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1497917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0753717422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0719861984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749481201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667051315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4779119491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267509460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7519111633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8161811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1037082672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0834131240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882762908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172380447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1544485092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999029159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3574085235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3912372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893350601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1713638305664</t>
+    <t xml:space="preserve">14.1193466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2275943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2715654373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1497898101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0753707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0719881057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667041778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4779100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267490386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7519102096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8161792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1037092208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0834112167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172370910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.154447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999048233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758043289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3574075698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3912343978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.489333152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1713609695435</t>
   </si>
   <si>
     <t xml:space="preserve">15.1003265380859</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">15.3946199417114</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3168172836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3134355545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4182996749878</t>
+    <t xml:space="preserve">15.3168182373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3134365081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4182977676392</t>
   </si>
   <si>
     <t xml:space="preserve">15.4250631332397</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5366926193237</t>
+    <t xml:space="preserve">15.5366916656494</t>
   </si>
   <si>
     <t xml:space="preserve">15.6753807067871</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6449384689331</t>
+    <t xml:space="preserve">15.6449394226074</t>
   </si>
   <si>
     <t xml:space="preserve">15.7295064926147</t>
@@ -737,73 +737,73 @@
     <t xml:space="preserve">15.6618509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6517038345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6821460723877</t>
+    <t xml:space="preserve">15.6517028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6821489334106</t>
   </si>
   <si>
     <t xml:space="preserve">15.5637531280518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4081506729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415567398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7024421691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584692001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.458890914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5874319076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6550855636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227392196655</t>
+    <t xml:space="preserve">15.4081497192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415586471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7024412155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333089828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584711074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588937759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5874347686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.655086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227420806885</t>
   </si>
   <si>
     <t xml:space="preserve">16.3350067138672</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0339488983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4060440063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.402660369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4195728302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6935729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.099494934082</t>
+    <t xml:space="preserve">16.0339469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.406042098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4026622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4195747375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6935710906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0994968414307</t>
   </si>
   <si>
     <t xml:space="preserve">16.9980144500732</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1671485900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4208507537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5392436981201</t>
+    <t xml:space="preserve">17.1671504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4208488464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5392417907715</t>
   </si>
   <si>
     <t xml:space="preserve">17.6407260894775</t>
@@ -812,40 +812,40 @@
     <t xml:space="preserve">17.4039363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.48850440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3531970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3870239257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.522331237793</t>
+    <t xml:space="preserve">17.4885063171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3531951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3870258331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5223293304443</t>
   </si>
   <si>
     <t xml:space="preserve">17.4546775817871</t>
   </si>
   <si>
-    <t xml:space="preserve">17.877513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8098621368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7083797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7591171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6745510101318</t>
+    <t xml:space="preserve">17.8775100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8098602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7083778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7591190338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6745529174805</t>
   </si>
   <si>
     <t xml:space="preserve">17.573070526123</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3362865447998</t>
+    <t xml:space="preserve">17.3362846374512</t>
   </si>
   <si>
     <t xml:space="preserve">17.2009754180908</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">17.217887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3701114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.456018447876</t>
+    <t xml:space="preserve">17.3701076507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4560203552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.7147541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5767612457275</t>
+    <t xml:space="preserve">17.5767650604248</t>
   </si>
   <si>
     <t xml:space="preserve">17.559513092041</t>
@@ -878,34 +878,34 @@
     <t xml:space="preserve">17.6975059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4698181152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6147117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7729587554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.00754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1662368774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1317386627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.993745803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9868469238281</t>
+    <t xml:space="preserve">17.469820022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6147136688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7729568481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0075454711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1662349700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1317405700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9937438964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9868488311768</t>
   </si>
   <si>
     <t xml:space="preserve">16.9661483764648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8350563049316</t>
+    <t xml:space="preserve">16.835054397583</t>
   </si>
   <si>
     <t xml:space="preserve">16.8488540649414</t>
@@ -914,85 +914,85 @@
     <t xml:space="preserve">16.8281536102295</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7591609954834</t>
+    <t xml:space="preserve">16.7591590881348</t>
   </si>
   <si>
     <t xml:space="preserve">16.8695526123047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9178524017334</t>
+    <t xml:space="preserve">16.9178504943848</t>
   </si>
   <si>
     <t xml:space="preserve">16.9730472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.938549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.152437210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6625633239746</t>
+    <t xml:space="preserve">16.9385509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1524391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.662561416626</t>
   </si>
   <si>
     <t xml:space="preserve">16.5935668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5659694671631</t>
+    <t xml:space="preserve">16.5659713745117</t>
   </si>
   <si>
     <t xml:space="preserve">16.5038738250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626518249512</t>
+    <t xml:space="preserve">16.8626537322998</t>
   </si>
   <si>
     <t xml:space="preserve">16.9040508270264</t>
   </si>
   <si>
-    <t xml:space="preserve">16.80055809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8971519470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5383682250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5590705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4900722503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2416915893555</t>
+    <t xml:space="preserve">16.8005561828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8971500396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5383739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5590724945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4900741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2416896820068</t>
   </si>
   <si>
     <t xml:space="preserve">16.303783416748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2485866546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1243953704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1864910125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1588916778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.53147315979</t>
+    <t xml:space="preserve">16.2485885620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.124397277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1864891052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1588935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5314712524414</t>
   </si>
   <si>
     <t xml:space="preserve">16.2899856567383</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3175849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5452709197998</t>
+    <t xml:space="preserve">16.3175830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5452690124512</t>
   </si>
   <si>
     <t xml:space="preserve">16.3658790588379</t>
@@ -1001,10 +1001,10 @@
     <t xml:space="preserve">16.4624767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3313808441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3520812988281</t>
+    <t xml:space="preserve">16.3313827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3520793914795</t>
   </si>
   <si>
     <t xml:space="preserve">16.6970634460449</t>
@@ -1016,40 +1016,40 @@
     <t xml:space="preserve">16.4486751556396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5107746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4210739135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4348773956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3934803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4969711303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5245704650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4003791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4555759429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3589820861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2830867767334</t>
+    <t xml:space="preserve">16.5107727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4210777282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4348754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.393482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4969730377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5245723724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4003772735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4555778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.358980178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2830848693848</t>
   </si>
   <si>
     <t xml:space="preserve">16.5521717071533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1795902252197</t>
+    <t xml:space="preserve">16.1795921325684</t>
   </si>
   <si>
     <t xml:space="preserve">16.2071895599365</t>
@@ -1058,46 +1058,46 @@
     <t xml:space="preserve">16.1933898925781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1519927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9036045074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5586252212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4965295791626</t>
+    <t xml:space="preserve">16.1519908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9036092758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5586261749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4965286254883</t>
   </si>
   <si>
     <t xml:space="preserve">15.9381065368652</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7794170379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7656145095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7863121032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9795036315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9312038421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7035160064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6483201980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8415079116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7518157958984</t>
+    <t xml:space="preserve">15.7794160842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7656173706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7863130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9795017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9312057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7035179138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6483192443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8415088653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7518167495728</t>
   </si>
   <si>
     <t xml:space="preserve">15.8691082000732</t>
@@ -1106,40 +1106,40 @@
     <t xml:space="preserve">15.8622093200684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0277996063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8967094421387</t>
+    <t xml:space="preserve">16.0277976989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8967065811157</t>
   </si>
   <si>
     <t xml:space="preserve">15.6276226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7173166275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.53102684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034313201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.441330909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2481412887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3171415328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3309383392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2826414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792371749878</t>
+    <t xml:space="preserve">15.7173156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310287475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034275054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.441333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2481460571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.317138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3309392929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2826404571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792362213135</t>
   </si>
   <si>
     <t xml:space="preserve">15.261944770813</t>
@@ -1154,67 +1154,67 @@
     <t xml:space="preserve">15.9519071578979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.972599029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9864044189453</t>
+    <t xml:space="preserve">15.972601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.986400604248</t>
   </si>
   <si>
     <t xml:space="preserve">16.0415992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8553104400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932138442993</t>
+    <t xml:space="preserve">15.8553094863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.793212890625</t>
   </si>
   <si>
     <t xml:space="preserve">15.4758310317993</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2895412445068</t>
+    <t xml:space="preserve">15.2895383834839</t>
   </si>
   <si>
     <t xml:space="preserve">15.1791458129883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.206748008728</t>
+    <t xml:space="preserve">15.2067461013794</t>
   </si>
   <si>
     <t xml:space="preserve">15.3999357223511</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2343473434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3033437728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137325286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3861351013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6345195770264</t>
+    <t xml:space="preserve">15.2343454360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033399581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137344360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.386137008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6345205307007</t>
   </si>
   <si>
     <t xml:space="preserve">16.1450939178467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4831733703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6073665618896</t>
+    <t xml:space="preserve">16.48317527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6073684692383</t>
   </si>
   <si>
     <t xml:space="preserve">16.3727798461914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6349678039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141788482666</t>
+    <t xml:space="preserve">16.6349639892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141807556152</t>
   </si>
   <si>
     <t xml:space="preserve">16.0898952484131</t>
@@ -1223,61 +1223,61 @@
     <t xml:space="preserve">16.2002906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.731559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6901626586914</t>
+    <t xml:space="preserve">16.7315578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6901607513428</t>
   </si>
   <si>
     <t xml:space="preserve">16.4762744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7522602081299</t>
+    <t xml:space="preserve">16.7522621154785</t>
   </si>
   <si>
     <t xml:space="preserve">16.6487655639648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6280670166016</t>
+    <t xml:space="preserve">16.6280689239502</t>
   </si>
   <si>
     <t xml:space="preserve">17.0420436859131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0765399932861</t>
+    <t xml:space="preserve">17.0765419006348</t>
   </si>
   <si>
     <t xml:space="preserve">17.1110382080078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2145347595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1455364227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1800365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.00710105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2140884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.110595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5931262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621227264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0066576004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.730673789978</t>
+    <t xml:space="preserve">17.2145328521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1455383300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1800346374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0070991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.21409034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1105976104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5931272506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621179580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0066556930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7306756973267</t>
   </si>
   <si>
     <t xml:space="preserve">14.9031639099121</t>
@@ -1286,10 +1286,10 @@
     <t xml:space="preserve">14.9721612930298</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4551315307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1101522445679</t>
+    <t xml:space="preserve">15.4551334381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1101512908936</t>
   </si>
   <si>
     <t xml:space="preserve">15.0411548614502</t>
@@ -1298,16 +1298,16 @@
     <t xml:space="preserve">15.0756549835205</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3516387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4206342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5241298675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6966199874878</t>
+    <t xml:space="preserve">15.3516368865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4206352233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5241279602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6966171264648</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156669616699</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">15.8742475509644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5560541152954</t>
+    <t xml:space="preserve">15.556056022644</t>
   </si>
   <si>
     <t xml:space="preserve">15.7328300476074</t>
@@ -1325,112 +1325,112 @@
     <t xml:space="preserve">15.5914096832275</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3439302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.379282951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7782526016235</t>
+    <t xml:space="preserve">15.3439292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792810440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7782545089722</t>
   </si>
   <si>
     <t xml:space="preserve">14.4247064590454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5307693481445</t>
+    <t xml:space="preserve">14.5307712554932</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600610733032</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4954137802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8873157501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1135854721069</t>
+    <t xml:space="preserve">14.4954147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8873138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1135845184326</t>
   </si>
   <si>
     <t xml:space="preserve">14.318642616272</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6014776229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0257358551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0610876083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9550266265869</t>
+    <t xml:space="preserve">14.6014804840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0257377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.061089515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9550275802612</t>
   </si>
   <si>
     <t xml:space="preserve">14.8489627838135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.884316444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7075414657593</t>
+    <t xml:space="preserve">14.8843154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7075424194336</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671562194824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2025089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5661249160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6368350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2832908630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0853033065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8136072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3539991378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3893508911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1418676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1772232055664</t>
+    <t xml:space="preserve">15.2025098800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.566125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6368341445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2832889556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0853023529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8136081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3539972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3893518447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428998947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1418685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1772241592407</t>
   </si>
   <si>
     <t xml:space="preserve">14.2479314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2125806808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0711584091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.943883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8731737136841</t>
+    <t xml:space="preserve">14.2125797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0711603164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9438819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8731727600098</t>
   </si>
   <si>
     <t xml:space="preserve">13.8166074752808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8590335845947</t>
+    <t xml:space="preserve">13.859034538269</t>
   </si>
   <si>
     <t xml:space="preserve">14.014594078064</t>
@@ -1439,94 +1439,94 @@
     <t xml:space="preserve">13.929741859436</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0004501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.97216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.028733253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0570182800293</t>
+    <t xml:space="preserve">14.0004510879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0994434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9721670150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0287342071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570163726807</t>
   </si>
   <si>
     <t xml:space="preserve">14.1277275085449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9196729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6721887588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.434775352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5054845809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4913415908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3782081604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4630603790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5620527267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5337686538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1660804748535</t>
+    <t xml:space="preserve">14.9196720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6721897125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.505485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4913425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3782072067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4630584716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5620517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5337677001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1660814285278</t>
   </si>
   <si>
     <t xml:space="preserve">12.7842502593994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6852579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1620073318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6569738388062</t>
+    <t xml:space="preserve">12.6852569580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1620092391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6569728851318</t>
   </si>
   <si>
     <t xml:space="preserve">13.4064903259277</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5479116439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7883224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7741794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5903358459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4489183425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3074989318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3923492431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0105180740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1519393920898</t>
+    <t xml:space="preserve">13.5479125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7883214950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7741804122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5903367996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4489164352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3074979782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3923501968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.01051902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1519384384155</t>
   </si>
   <si>
     <t xml:space="preserve">13.2933559417725</t>
@@ -1535,163 +1535,163 @@
     <t xml:space="preserve">12.9256687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0388031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9963779449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2367897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0953693389893</t>
+    <t xml:space="preserve">13.0388059616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.996376991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2367887496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0953722000122</t>
   </si>
   <si>
     <t xml:space="preserve">13.6469039916992</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0670862197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2509326934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2085065841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812301635742</t>
+    <t xml:space="preserve">13.6751861572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0670852661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2509317398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2085075378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812292098999</t>
   </si>
   <si>
     <t xml:space="preserve">13.3499231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8408174514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5296964645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8973846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6004066467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7317533493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5761947631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5196285247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7176132202148</t>
+    <t xml:space="preserve">12.8408164978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5296955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.897385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6004056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7317552566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5761938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5196266174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7176122665405</t>
   </si>
   <si>
     <t xml:space="preserve">13.8307456970215</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7600374221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.915599822998</t>
+    <t xml:space="preserve">13.7600364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9156007766724</t>
   </si>
   <si>
     <t xml:space="preserve">13.7458972930908</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0428771972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8448896408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.541766166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2218465805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9455547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1782236099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9891805648804</t>
+    <t xml:space="preserve">14.0428762435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8448905944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5417671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2218456268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9455537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.17822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9891796112061</t>
   </si>
   <si>
     <t xml:space="preserve">14.2073078155518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4399757385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.265474319458</t>
+    <t xml:space="preserve">14.4399747848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2654733657837</t>
   </si>
   <si>
     <t xml:space="preserve">14.4108934402466</t>
   </si>
   <si>
-    <t xml:space="preserve">14.498140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3381834030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5126838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3963489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871881484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4254322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4836015701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6144781112671</t>
+    <t xml:space="preserve">14.4981422424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3381814956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5126829147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3963499069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871862411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4254331588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4836006164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6144771575928</t>
   </si>
   <si>
     <t xml:space="preserve">14.8326025009155</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9780197143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1234359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1961460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4142723083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4506273269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3415660858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2325010299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3052091598511</t>
+    <t xml:space="preserve">14.9780206680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1234369277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1961479187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4142732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.450629234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3415641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2325019836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3052082061768</t>
   </si>
   <si>
     <t xml:space="preserve">15.268856048584</t>
@@ -1700,31 +1700,31 @@
     <t xml:space="preserve">15.6687545776367</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0507297515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.087082862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9416646957397</t>
+    <t xml:space="preserve">15.0507287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0870838165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9416666030884</t>
   </si>
   <si>
     <t xml:space="preserve">14.723539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0143728256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5781211853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7598962783813</t>
+    <t xml:space="preserve">15.0143756866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5781221389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7598943710327</t>
   </si>
   <si>
     <t xml:space="preserve">14.6508293151855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3672676086426</t>
+    <t xml:space="preserve">14.3672666549683</t>
   </si>
   <si>
     <t xml:space="preserve">14.3236417770386</t>
@@ -1733,43 +1733,43 @@
     <t xml:space="preserve">14.5272254943848</t>
   </si>
   <si>
-    <t xml:space="preserve">14.454517364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7962474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.905309677124</t>
+    <t xml:space="preserve">14.4545154571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7962484359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9053106307983</t>
   </si>
   <si>
     <t xml:space="preserve">16.0322971343994</t>
   </si>
   <si>
-    <t xml:space="preserve">16.359489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5049076080322</t>
+    <t xml:space="preserve">16.3594875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5049057006836</t>
   </si>
   <si>
     <t xml:space="preserve">16.6139698028564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5412616729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8320922851562</t>
+    <t xml:space="preserve">16.541259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8320960998535</t>
   </si>
   <si>
     <t xml:space="preserve">16.6503238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">16.577615737915</t>
+    <t xml:space="preserve">16.5776138305664</t>
   </si>
   <si>
     <t xml:space="preserve">16.8684501647949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7593841552734</t>
+    <t xml:space="preserve">16.7593879699707</t>
   </si>
   <si>
     <t xml:space="preserve">17.0502223968506</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">17.4864730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4137649536133</t>
+    <t xml:space="preserve">17.4137668609619</t>
   </si>
   <si>
     <t xml:space="preserve">17.2683486938477</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">17.5228309631348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8136653900146</t>
+    <t xml:space="preserve">17.813663482666</t>
   </si>
   <si>
     <t xml:space="preserve">17.7409572601318</t>
@@ -1802,13 +1802,13 @@
     <t xml:space="preserve">17.7046031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6682472229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0681457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9227294921875</t>
+    <t xml:space="preserve">17.6682453155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0681438446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9227275848389</t>
   </si>
   <si>
     <t xml:space="preserve">18.1045017242432</t>
@@ -1817,10 +1817,10 @@
     <t xml:space="preserve">17.8500194549561</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9590835571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1772117614746</t>
+    <t xml:space="preserve">17.9590854644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.177209854126</t>
   </si>
   <si>
     <t xml:space="preserve">18.0317916870117</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">17.9954376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5591831207275</t>
+    <t xml:space="preserve">17.5591812133789</t>
   </si>
   <si>
     <t xml:space="preserve">17.5955390930176</t>
@@ -1853,16 +1853,16 @@
     <t xml:space="preserve">18.2499179840088</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3953342437744</t>
+    <t xml:space="preserve">18.395336151123</t>
   </si>
   <si>
     <t xml:space="preserve">18.2135639190674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3226280212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6134605407715</t>
+    <t xml:space="preserve">18.3226261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6134624481201</t>
   </si>
   <si>
     <t xml:space="preserve">18.6861705780029</t>
@@ -1874,19 +1874,19 @@
     <t xml:space="preserve">19.1951332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9770050048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0860691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.26784324646</t>
+    <t xml:space="preserve">18.9770069122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0860729217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2678413391113</t>
   </si>
   <si>
     <t xml:space="preserve">19.1224231719971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3041954040527</t>
+    <t xml:space="preserve">19.3041973114014</t>
   </si>
   <si>
     <t xml:space="preserve">19.4132614135742</t>
@@ -1898,58 +1898,58 @@
     <t xml:space="preserve">16.9048042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7230319976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321994781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7957420349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2314872741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9775142669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3047008514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3774108886719</t>
+    <t xml:space="preserve">16.7230339050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321975708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7957401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2314853668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9775161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3047027587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3774127960205</t>
   </si>
   <si>
     <t xml:space="preserve">18.7952346801758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5407524108887</t>
+    <t xml:space="preserve">18.5407543182373</t>
   </si>
   <si>
     <t xml:space="preserve">18.8679447174072</t>
   </si>
   <si>
-    <t xml:space="preserve">18.904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8495140075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.42138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7327499389648</t>
+    <t xml:space="preserve">18.9042987823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8495121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4213848114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7327518463135</t>
   </si>
   <si>
     <t xml:space="preserve">20.394401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8105907440186</t>
+    <t xml:space="preserve">19.8105945587158</t>
   </si>
   <si>
     <t xml:space="preserve">19.6549110412598</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3554801940918</t>
+    <t xml:space="preserve">20.3554821014404</t>
   </si>
   <si>
     <t xml:space="preserve">20.121955871582</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">19.4603080749512</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3435440063477</t>
+    <t xml:space="preserve">19.343542098999</t>
   </si>
   <si>
     <t xml:space="preserve">19.3046226501465</t>
@@ -1970,58 +1970,58 @@
     <t xml:space="preserve">19.966272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2657051086426</t>
+    <t xml:space="preserve">19.2657032012939</t>
   </si>
   <si>
     <t xml:space="preserve">19.771671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7597351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1608772277832</t>
+    <t xml:space="preserve">18.7597370147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1608791351318</t>
   </si>
   <si>
     <t xml:space="preserve">20.044116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1728134155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0560493469238</t>
+    <t xml:space="preserve">21.1728115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0560512542725</t>
   </si>
   <si>
     <t xml:space="preserve">20.9392890930176</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2895755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0171318054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7836093902588</t>
+    <t xml:space="preserve">21.2895736694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0171298980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7836074829102</t>
   </si>
   <si>
     <t xml:space="preserve">20.7057666778564</t>
   </si>
   <si>
-    <t xml:space="preserve">21.094970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4452571868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7566223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9512271881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6009407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7955417633057</t>
+    <t xml:space="preserve">21.0949726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4452590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7566242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9512252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6009387969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7955436706543</t>
   </si>
   <si>
     <t xml:space="preserve">22.0290660858154</t>
@@ -2033,13 +2033,13 @@
     <t xml:space="preserve">22.5350360870361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5739555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.651798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7685565948486</t>
+    <t xml:space="preserve">22.57395362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6517963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7685585021973</t>
   </si>
   <si>
     <t xml:space="preserve">22.8074779510498</t>
@@ -2048,10 +2048,10 @@
     <t xml:space="preserve">22.7296390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3404312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2625923156738</t>
+    <t xml:space="preserve">22.3404331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2625904083252</t>
   </si>
   <si>
     <t xml:space="preserve">23.5080528259277</t>
@@ -2060,28 +2060,28 @@
     <t xml:space="preserve">23.97509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4032249450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9091911315918</t>
+    <t xml:space="preserve">24.4032230377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9091930389404</t>
   </si>
   <si>
     <t xml:space="preserve">24.7145900726318</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5199871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2983989715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7924327850342</t>
+    <t xml:space="preserve">24.5199851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.298397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7924308776855</t>
   </si>
   <si>
     <t xml:space="preserve">25.1427135467529</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7535095214844</t>
+    <t xml:space="preserve">24.7535076141357</t>
   </si>
   <si>
     <t xml:space="preserve">24.6367454528809</t>
@@ -2093,13 +2093,13 @@
     <t xml:space="preserve">24.0140190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0799217224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7026519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0529365539551</t>
+    <t xml:space="preserve">23.0799236297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7026557922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0529384613037</t>
   </si>
   <si>
     <t xml:space="preserve">23.4691295623779</t>
@@ -2108,28 +2108,28 @@
     <t xml:space="preserve">23.5858917236328</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1577644348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8583354949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7415714263916</t>
+    <t xml:space="preserve">23.1577625274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8583335876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7415752410889</t>
   </si>
   <si>
     <t xml:space="preserve">23.8194160461426</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6637306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4302101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0918617248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3912887573242</t>
+    <t xml:space="preserve">23.6637325286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4302082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0918598175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3912868499756</t>
   </si>
   <si>
     <t xml:space="preserve">23.3523654937744</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">23.1188430786133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6248111724854</t>
+    <t xml:space="preserve">23.6248149871826</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128749847412</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">22.1069087982178</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1847476959229</t>
+    <t xml:space="preserve">22.1847496032715</t>
   </si>
   <si>
     <t xml:space="preserve">22.4961128234863</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">22.6907157897949</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3793506622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9631595611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2356071472168</t>
+    <t xml:space="preserve">22.3793525695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9631614685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">22.9242420196533</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">22.2236709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9123058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4841766357422</t>
+    <t xml:space="preserve">22.4182739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9123039245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4841785430908</t>
   </si>
   <si>
     <t xml:space="preserve">21.1338939666748</t>
@@ -2201,46 +2201,46 @@
     <t xml:space="preserve">21.6398620605469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2506523132324</t>
+    <t xml:space="preserve">21.2506542205811</t>
   </si>
   <si>
     <t xml:space="preserve">21.5620212554932</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8344612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6787796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9901447296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1458301544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8464012145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8853206634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4571933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3284969329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2117328643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3674182891846</t>
+    <t xml:space="preserve">21.8344631195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.678783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9901466369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1458282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.846399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8853187561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4571914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2117309570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3674144744873</t>
   </si>
   <si>
     <t xml:space="preserve">20.9782104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6279258728027</t>
+    <t xml:space="preserve">20.6279239654541</t>
   </si>
   <si>
     <t xml:space="preserve">21.873384475708</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">23.2417449951172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0029563903809</t>
+    <t xml:space="preserve">23.0029582977295</t>
   </si>
   <si>
     <t xml:space="preserve">23.2019462585449</t>
@@ -2276,10 +2276,10 @@
     <t xml:space="preserve">23.122350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1621475219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5203266143799</t>
+    <t xml:space="preserve">23.1621494293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5203247070312</t>
   </si>
   <si>
     <t xml:space="preserve">23.9580974578857</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">24.0774898529053</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4356689453125</t>
+    <t xml:space="preserve">24.4356708526611</t>
   </si>
   <si>
     <t xml:space="preserve">24.3162746429443</t>
@@ -2303,25 +2303,25 @@
     <t xml:space="preserve">24.1570854187012</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6744518280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9132385253906</t>
+    <t xml:space="preserve">24.6744537353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.913236618042</t>
   </si>
   <si>
     <t xml:space="preserve">24.555061340332</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7540493011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2764759063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1172866821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5152626037598</t>
+    <t xml:space="preserve">24.7540473937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2764797210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1172885894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5152645111084</t>
   </si>
   <si>
     <t xml:space="preserve">24.4754657745361</t>
@@ -2330,16 +2330,16 @@
     <t xml:space="preserve">24.2366809844971</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3958702087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7142505645752</t>
+    <t xml:space="preserve">24.3958721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7142486572266</t>
   </si>
   <si>
     <t xml:space="preserve">24.6346549987793</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1968822479248</t>
+    <t xml:space="preserve">24.1968841552734</t>
   </si>
   <si>
     <t xml:space="preserve">25.6295948028564</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">25.5102005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1520252227783</t>
+    <t xml:space="preserve">25.1520233154297</t>
   </si>
   <si>
     <t xml:space="preserve">25.3510131835938</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">24.9530372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8683795928955</t>
+    <t xml:space="preserve">25.8683815002441</t>
   </si>
   <si>
     <t xml:space="preserve">25.0724277496338</t>
@@ -2387,28 +2387,28 @@
     <t xml:space="preserve">23.7591114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4805297851562</t>
+    <t xml:space="preserve">23.4805278778076</t>
   </si>
   <si>
     <t xml:space="preserve">23.8785037994385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.639720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7989082336426</t>
+    <t xml:space="preserve">23.6397171020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7989063262939</t>
   </si>
   <si>
     <t xml:space="preserve">24.5948581695557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9928340911865</t>
+    <t xml:space="preserve">24.9928321838379</t>
   </si>
   <si>
     <t xml:space="preserve">25.430606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3112144470215</t>
+    <t xml:space="preserve">25.3112125396729</t>
   </si>
   <si>
     <t xml:space="preserve">25.2316188812256</t>
@@ -2417,13 +2417,13 @@
     <t xml:space="preserve">26.0673656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2663555145264</t>
+    <t xml:space="preserve">26.2663536071777</t>
   </si>
   <si>
     <t xml:space="preserve">26.0275688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7887840270996</t>
+    <t xml:space="preserve">25.7887859344482</t>
   </si>
   <si>
     <t xml:space="preserve">25.5499973297119</t>
@@ -2432,70 +2432,70 @@
     <t xml:space="preserve">25.5897979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9479713439941</t>
+    <t xml:space="preserve">25.9479732513428</t>
   </si>
   <si>
     <t xml:space="preserve">26.1071624755859</t>
   </si>
   <si>
-    <t xml:space="preserve">25.748987197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.873441696167</t>
+    <t xml:space="preserve">25.7489852905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8734397888184</t>
   </si>
   <si>
     <t xml:space="preserve">24.0376949310303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3264007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3661994934082</t>
+    <t xml:space="preserve">22.3263988494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3661975860596</t>
   </si>
   <si>
     <t xml:space="preserve">23.0825538635254</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9233627319336</t>
+    <t xml:space="preserve">22.9233646392822</t>
   </si>
   <si>
     <t xml:space="preserve">23.3213386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5999221801758</t>
+    <t xml:space="preserve">23.5999202728271</t>
   </si>
   <si>
     <t xml:space="preserve">23.3611354827881</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4009323120117</t>
+    <t xml:space="preserve">23.4009304046631</t>
   </si>
   <si>
     <t xml:space="preserve">23.5601234436035</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4855899810791</t>
+    <t xml:space="preserve">22.4855918884277</t>
   </si>
   <si>
     <t xml:space="preserve">23.8387069702148</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9978942871094</t>
+    <t xml:space="preserve">23.997896194458</t>
   </si>
   <si>
     <t xml:space="preserve">23.7193126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8264083862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5692901611328</t>
+    <t xml:space="preserve">23.8264102935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5692920684814</t>
   </si>
   <si>
     <t xml:space="preserve">24.1263828277588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9549694061279</t>
+    <t xml:space="preserve">23.9549713134766</t>
   </si>
   <si>
     <t xml:space="preserve">24.4692077636719</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">24.2120895385742</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7835559844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.340648651123</t>
+    <t xml:space="preserve">23.7835578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3406505584717</t>
   </si>
   <si>
     <t xml:space="preserve">24.2549419403076</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977962493896</t>
+    <t xml:space="preserve">24.2977981567383</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264377593994</t>
@@ -2528,16 +2528,16 @@
     <t xml:space="preserve">23.9978218078613</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9121170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8692626953125</t>
+    <t xml:space="preserve">23.9121150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8692646026611</t>
   </si>
   <si>
     <t xml:space="preserve">23.7407035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6549987792969</t>
+    <t xml:space="preserve">23.6549949645996</t>
   </si>
   <si>
     <t xml:space="preserve">22.9693431854248</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">22.5836658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9264907836914</t>
+    <t xml:space="preserve">22.92649269104</t>
   </si>
   <si>
     <t xml:space="preserve">23.1407585144043</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">22.7550773620605</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6693725585938</t>
+    <t xml:space="preserve">22.6693744659424</t>
   </si>
   <si>
     <t xml:space="preserve">23.0550518035889</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">23.2264652252197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7122268676758</t>
+    <t xml:space="preserve">22.7122249603271</t>
   </si>
   <si>
     <t xml:space="preserve">22.4122524261475</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1836109161377</t>
+    <t xml:space="preserve">23.1836090087891</t>
   </si>
   <si>
     <t xml:space="preserve">23.0979061126709</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">23.3550243377686</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0121994018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3121738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.397876739502</t>
+    <t xml:space="preserve">23.0121974945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3121719360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3978786468506</t>
   </si>
   <si>
     <t xml:space="preserve">22.7979316711426</t>
@@ -2618,13 +2618,13 @@
     <t xml:space="preserve">23.2693176269531</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2836933135986</t>
+    <t xml:space="preserve">22.28369140625</t>
   </si>
   <si>
     <t xml:space="preserve">21.426628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.469482421875</t>
+    <t xml:space="preserve">21.4694805145264</t>
   </si>
   <si>
     <t xml:space="preserve">21.2552146911621</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">20.9980945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1266536712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5267086029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6552696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.312442779541</t>
+    <t xml:space="preserve">21.1266555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5267105102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6552677154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3124446868896</t>
   </si>
   <si>
     <t xml:space="preserve">20.4410037994385</t>
@@ -2663,16 +2663,16 @@
     <t xml:space="preserve">21.5980415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3837757110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.512336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3409214019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0265731811523</t>
+    <t xml:space="preserve">21.3837738037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5123348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3409194946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.026575088501</t>
   </si>
   <si>
     <t xml:space="preserve">22.1122798919678</t>
@@ -2681,16 +2681,16 @@
     <t xml:space="preserve">21.8123073577881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1551322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2408409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6837463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.726598739624</t>
+    <t xml:space="preserve">22.1551342010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2408390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6837482452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7266006469727</t>
   </si>
   <si>
     <t xml:space="preserve">21.8980121612549</t>
@@ -2702,34 +2702,34 @@
     <t xml:space="preserve">21.6408939361572</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1979846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0694274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9837188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8551597595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1695098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0838031768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9408664703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5551872253418</t>
+    <t xml:space="preserve">22.1979866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0694255828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9837207794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8551616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1695079803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0838012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9408683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5551853179932</t>
   </si>
   <si>
     <t xml:space="preserve">21.0409488677979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.912389755249</t>
+    <t xml:space="preserve">20.9123878479004</t>
   </si>
   <si>
     <t xml:space="preserve">21.2980690002441</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">22.0611591339111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1051959991455</t>
+    <t xml:space="preserve">22.1051940917969</t>
   </si>
   <si>
     <t xml:space="preserve">22.017126083374</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">21.664852142334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5767841339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4887161254883</t>
+    <t xml:space="preserve">21.5767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4887142181396</t>
   </si>
   <si>
     <t xml:space="preserve">21.9290561676025</t>
@@ -2792,22 +2792,22 @@
     <t xml:space="preserve">21.8409881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7088851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4006462097168</t>
+    <t xml:space="preserve">21.7088871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4006443023682</t>
   </si>
   <si>
     <t xml:space="preserve">21.7969551086426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9730930328369</t>
+    <t xml:space="preserve">21.9730911254883</t>
   </si>
   <si>
     <t xml:space="preserve">21.7529201507568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5015029907227</t>
+    <t xml:space="preserve">22.501501083374</t>
   </si>
   <si>
     <t xml:space="preserve">22.2372970581055</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">22.3253650665283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5455360412598</t>
+    <t xml:space="preserve">22.5455379486084</t>
   </si>
   <si>
     <t xml:space="preserve">22.149227142334</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">21.0483722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3566112518311</t>
+    <t xml:space="preserve">21.3566131591797</t>
   </si>
   <si>
     <t xml:space="preserve">21.6208171844482</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">21.4446811676025</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5327491760254</t>
+    <t xml:space="preserve">21.532751083374</t>
   </si>
   <si>
     <t xml:space="preserve">21.0043392181396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8722343444824</t>
+    <t xml:space="preserve">20.8722362518311</t>
   </si>
   <si>
     <t xml:space="preserve">20.6960983276367</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">20.2557563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3878593444824</t>
+    <t xml:space="preserve">20.3878574371338</t>
   </si>
   <si>
     <t xml:space="preserve">20.2997894287109</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">20.7841682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9603023529053</t>
+    <t xml:space="preserve">20.9603042602539</t>
   </si>
   <si>
     <t xml:space="preserve">20.7401313781738</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">21.1804752349854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6336059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4574680328369</t>
+    <t xml:space="preserve">22.6336078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4574699401855</t>
   </si>
   <si>
     <t xml:space="preserve">22.5895709991455</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">24.3949756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3069076538086</t>
+    <t xml:space="preserve">24.30690574646</t>
   </si>
   <si>
     <t xml:space="preserve">24.1307697296143</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">24.3509407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4390087127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5711135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6591815948486</t>
+    <t xml:space="preserve">24.4390106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5711116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6591796875</t>
   </si>
   <si>
     <t xml:space="preserve">24.7032146453857</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">24.0867366790771</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2188377380371</t>
+    <t xml:space="preserve">24.2188396453857</t>
   </si>
   <si>
     <t xml:space="preserve">24.1748046875</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">23.9546337127686</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7600383758545</t>
+    <t xml:space="preserve">25.7600364685059</t>
   </si>
   <si>
     <t xml:space="preserve">25.4077625274658</t>
@@ -2987,19 +2987,19 @@
     <t xml:space="preserve">26.1123104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1563472747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4645843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5910148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3708438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8992576599121</t>
+    <t xml:space="preserve">26.1563453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4645862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5910167694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3708457946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8992595672607</t>
   </si>
   <si>
     <t xml:space="preserve">30.0313587188721</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">29.5029487609863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7671527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2827777862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0753955841064</t>
+    <t xml:space="preserve">29.7671546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2827758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0753974914551</t>
   </si>
   <si>
     <t xml:space="preserve">29.7231216430664</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">30.471700668335</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8111877441406</t>
+    <t xml:space="preserve">29.811185836792</t>
   </si>
   <si>
     <t xml:space="preserve">29.2387447357178</t>
@@ -3044,28 +3044,28 @@
     <t xml:space="preserve">28.7103309631348</t>
   </si>
   <si>
-    <t xml:space="preserve">28.842435836792</t>
+    <t xml:space="preserve">28.8424339294434</t>
   </si>
   <si>
     <t xml:space="preserve">28.8864688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5469818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2955665588379</t>
+    <t xml:space="preserve">29.5469837188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2955646514893</t>
   </si>
   <si>
     <t xml:space="preserve">30.7359104156494</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3836326599121</t>
+    <t xml:space="preserve">30.3836345672607</t>
   </si>
   <si>
     <t xml:space="preserve">29.9873237609863</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4276676177979</t>
+    <t xml:space="preserve">30.4276695251465</t>
   </si>
   <si>
     <t xml:space="preserve">29.4632396697998</t>
@@ -3693,6 +3693,9 @@
   </si>
   <si>
     <t xml:space="preserve">33.4000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5999984741211</t>
   </si>
 </sst>
 </file>
@@ -69031,7 +69034,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6910648148</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>15450</v>
@@ -69052,6 +69055,32 @@
         <v>1223</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6911111111</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>16254</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>32.9500007629395</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>32.4500007629395</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>32.9500007629395</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>32.5999984741211</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1227</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="1228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="1229">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,31 +44,31 @@
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577459335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9573354721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3883295059204</t>
+    <t xml:space="preserve">14.0577440261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9573316574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3883266448975</t>
   </si>
   <si>
     <t xml:space="preserve">12.8896141052246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8527956008911</t>
+    <t xml:space="preserve">12.8527975082397</t>
   </si>
   <si>
     <t xml:space="preserve">12.9532098770142</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6185007095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846162796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.384204864502</t>
+    <t xml:space="preserve">12.618501663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3842039108276</t>
   </si>
   <si>
     <t xml:space="preserve">11.8821420669556</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">10.7307453155518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2294616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2194204330444</t>
+    <t xml:space="preserve">11.2294607162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2194194793701</t>
   </si>
   <si>
     <t xml:space="preserve">11.2461967468262</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">10.9148349761963</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1323957443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6143760681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6813173294067</t>
+    <t xml:space="preserve">11.1323947906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6143751144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6813182830811</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474338531494</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">11.3131380081177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3298711776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8947525024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8780164718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.045371055603</t>
+    <t xml:space="preserve">11.329873085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8947515487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8780174255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0453729629517</t>
   </si>
   <si>
     <t xml:space="preserve">10.4261617660522</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">10.4094257354736</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7080945968628</t>
+    <t xml:space="preserve">11.7080936431885</t>
   </si>
   <si>
     <t xml:space="preserve">11.7147874832153</t>
@@ -140,79 +140,79 @@
     <t xml:space="preserve">12.0494956970215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7482576370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.744912147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2135057449341</t>
+    <t xml:space="preserve">11.7482566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7449111938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2135038375854</t>
   </si>
   <si>
     <t xml:space="preserve">12.2168493270874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.367467880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7189130783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.82936668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0201511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2209720611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3849830627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870923995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536203384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3347759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3146953582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569677352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109355926514</t>
+    <t xml:space="preserve">12.3674688339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7189140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8293657302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0201501846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2209749221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3849849700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870914459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3347768783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3146924972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109327316284</t>
   </si>
   <si>
     <t xml:space="preserve">12.8661842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1306018829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2879161834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.826021194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9833307266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9029998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2377099990845</t>
+    <t xml:space="preserve">13.1306056976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2879190444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8260183334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9833335876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9030027389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2377090454102</t>
   </si>
   <si>
     <t xml:space="preserve">13.1674222946167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1138696670532</t>
+    <t xml:space="preserve">13.113865852356</t>
   </si>
   <si>
     <t xml:space="preserve">13.0971336364746</t>
@@ -221,79 +221,79 @@
     <t xml:space="preserve">12.5046997070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8862648010254</t>
+    <t xml:space="preserve">12.8092832565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8862686157227</t>
   </si>
   <si>
     <t xml:space="preserve">12.7055234909058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7222585678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.916389465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0301923751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327131271362</t>
+    <t xml:space="preserve">12.7222595214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9163913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0301885604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327121734619</t>
   </si>
   <si>
     <t xml:space="preserve">12.6318893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7021770477295</t>
+    <t xml:space="preserve">12.7021780014038</t>
   </si>
   <si>
     <t xml:space="preserve">12.8695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5582523345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5682954788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8360595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494482040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958946228027</t>
+    <t xml:space="preserve">12.558253288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5682926177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8360586166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494501113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958936691284</t>
   </si>
   <si>
     <t xml:space="preserve">12.5348224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7791604995728</t>
+    <t xml:space="preserve">12.7791614532471</t>
   </si>
   <si>
     <t xml:space="preserve">12.7691192626953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7865657806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5024194717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6512584686279</t>
+    <t xml:space="preserve">12.786566734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.502420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6512594223022</t>
   </si>
   <si>
     <t xml:space="preserve">12.752739906311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5836048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4990367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5700731277466</t>
+    <t xml:space="preserve">12.5836057662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4990377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5700740814209</t>
   </si>
   <si>
     <t xml:space="preserve">12.5159502029419</t>
@@ -302,91 +302,91 @@
     <t xml:space="preserve">12.2791614532471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0660524368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.177680015564</t>
+    <t xml:space="preserve">12.0660533905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776828765869</t>
   </si>
   <si>
     <t xml:space="preserve">12.1641511917114</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1709156036377</t>
+    <t xml:space="preserve">12.170916557312</t>
   </si>
   <si>
     <t xml:space="preserve">12.1100282669067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1269426345825</t>
+    <t xml:space="preserve">12.1269416809082</t>
   </si>
   <si>
     <t xml:space="preserve">11.9814853668213</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7459764480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231391906738</t>
+    <t xml:space="preserve">12.7459726333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580247879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231372833252</t>
   </si>
   <si>
     <t xml:space="preserve">11.6973419189453</t>
   </si>
   <si>
-    <t xml:space="preserve">11.778525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2406759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8212242126465</t>
+    <t xml:space="preserve">11.7785243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2406768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8212251663208</t>
   </si>
   <si>
     <t xml:space="preserve">10.6554718017578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.061393737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.196702003479</t>
+    <t xml:space="preserve">11.0613946914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1967029571533</t>
   </si>
   <si>
     <t xml:space="preserve">11.4064283370972</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248231887817</t>
+    <t xml:space="preserve">11.5248222351074</t>
   </si>
   <si>
     <t xml:space="preserve">10.6656198501587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1886615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.587818145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6825332641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8394117355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0199708938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3616237640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0233554840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1924896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4969320297241</t>
+    <t xml:space="preserve">10.1886606216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5878171920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6825323104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.839412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0199718475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3616228103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0233564376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1924877166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4969329833984</t>
   </si>
   <si>
     <t xml:space="preserve">13.4698686599731</t>
@@ -395,55 +395,55 @@
     <t xml:space="preserve">13.5307579040527</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4800176620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2939672470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108825683594</t>
+    <t xml:space="preserve">13.4800138473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2939691543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108835220337</t>
   </si>
   <si>
     <t xml:space="preserve">13.3548564910889</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0740957260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368843078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9489336013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827613830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.091007232666</t>
+    <t xml:space="preserve">13.0740947723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.036883354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9489345550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0910081863403</t>
   </si>
   <si>
     <t xml:space="preserve">13.0707111358643</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9962921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8576011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113061904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1248331069946</t>
+    <t xml:space="preserve">12.9962911605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8576030731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113042831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1248340606689</t>
   </si>
   <si>
     <t xml:space="preserve">13.1823415756226</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0605640411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857223510742</t>
+    <t xml:space="preserve">13.0605621337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857233047485</t>
   </si>
   <si>
     <t xml:space="preserve">13.4123649597168</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">13.567967414856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4157476425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5138416290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7066564559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8351993560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2106761932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4576148986816</t>
+    <t xml:space="preserve">13.4157466888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.513843536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.706657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8352012634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2106771469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4576139450073</t>
   </si>
   <si>
     <t xml:space="preserve">14.7552900314331</t>
@@ -476,70 +476,70 @@
     <t xml:space="preserve">14.8838329315186</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0157594680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9853115081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303470611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6652326583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.289758682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8297090530396</t>
+    <t xml:space="preserve">15.01575756073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.985315322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303480148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6652345657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2897567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8297109603882</t>
   </si>
   <si>
     <t xml:space="preserve">14.684253692627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7722034454346</t>
+    <t xml:space="preserve">14.7722053527832</t>
   </si>
   <si>
     <t xml:space="preserve">14.951488494873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7485246658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7180805206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8770685195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7992668151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751644134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9007472991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2018041610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939819335938</t>
+    <t xml:space="preserve">14.7485237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7180833816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8770694732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7992658615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751682281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.90074634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2018022537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939800262451</t>
   </si>
   <si>
     <t xml:space="preserve">14.8330917358398</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9988441467285</t>
+    <t xml:space="preserve">14.9988460540771</t>
   </si>
   <si>
     <t xml:space="preserve">14.9142770767212</t>
   </si>
   <si>
-    <t xml:space="preserve">14.927806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.738377571106</t>
+    <t xml:space="preserve">14.9278078079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7383785247803</t>
   </si>
   <si>
     <t xml:space="preserve">14.7248477935791</t>
@@ -551,133 +551,133 @@
     <t xml:space="preserve">14.4440860748291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0529680252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1443014144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1104736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.954873085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0901784896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2187213897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7823534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707239151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6166009902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764305114746</t>
+    <t xml:space="preserve">15.0529670715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1443004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1104726791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9548683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0901765823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2187204360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7823524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6166019439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764295578003</t>
   </si>
   <si>
     <t xml:space="preserve">14.1599388122559</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2546548843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0415420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1125812530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0381631851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1430244445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903820037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527507781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.207293510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3561315536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373178482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730487823486</t>
+    <t xml:space="preserve">14.2546539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0415439605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1125793457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.038161277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1430263519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903810501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527536392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2072954177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3561334609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373188018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730497360229</t>
   </si>
   <si>
     <t xml:space="preserve">14.3087759017944</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2411222457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3392200469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2512712478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464071273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058139801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1193466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2275943756104</t>
+    <t xml:space="preserve">14.2411212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3392210006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2512722015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1464080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058130264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.119345664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2275915145874</t>
   </si>
   <si>
     <t xml:space="preserve">14.2715654373169</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1497898101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0753707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0719881057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667041778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4779100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267490386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7519102096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8161792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1037092208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0834112167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882743835449</t>
+    <t xml:space="preserve">14.1497917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0753726959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0719871520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4779090881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267499923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7519083023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.816180229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.103705406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0834140777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882762908936</t>
   </si>
   <si>
     <t xml:space="preserve">15.1172370910645</t>
@@ -686,103 +686,103 @@
     <t xml:space="preserve">15.154447555542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2999048233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758043289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3574075698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3912343978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.489333152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1713609695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1003265380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946199417114</t>
+    <t xml:space="preserve">15.299901008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3574132919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3912372589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893350601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1713619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.100323677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946189880371</t>
   </si>
   <si>
     <t xml:space="preserve">15.3168182373047</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3134365081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4182977676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4250631332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366916656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6753807067871</t>
+    <t xml:space="preserve">15.3134346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4182987213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4250640869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366926193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6753826141357</t>
   </si>
   <si>
     <t xml:space="preserve">15.6449394226074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7295064926147</t>
+    <t xml:space="preserve">15.7295055389404</t>
   </si>
   <si>
     <t xml:space="preserve">15.6618509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6517028808594</t>
+    <t xml:space="preserve">15.651704788208</t>
   </si>
   <si>
     <t xml:space="preserve">15.6821489334106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5637531280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081497192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415586471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7024412155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584711074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588937759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5874347686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.655086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227420806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3350067138672</t>
+    <t xml:space="preserve">15.5637521743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081506729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415576934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7024459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584692001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588899612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5874328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6550855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227401733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3350048065186</t>
   </si>
   <si>
     <t xml:space="preserve">16.0339469909668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.406042098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4026622772217</t>
+    <t xml:space="preserve">16.4060440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.402660369873</t>
   </si>
   <si>
     <t xml:space="preserve">16.4195747375488</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">16.6935710906982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0994968414307</t>
+    <t xml:space="preserve">17.099494934082</t>
   </si>
   <si>
     <t xml:space="preserve">16.9980144500732</t>
@@ -800,55 +800,55 @@
     <t xml:space="preserve">17.1671504974365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4208488464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5392417907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6407260894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4039363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4885063171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3531951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3870258331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5223293304443</t>
+    <t xml:space="preserve">17.4208507537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5392436981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6407241821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4039344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.48850440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3531970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3870239257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.522331237793</t>
   </si>
   <si>
     <t xml:space="preserve">17.4546775817871</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8775100708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8098602294922</t>
+    <t xml:space="preserve">17.8775119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8098621368408</t>
   </si>
   <si>
     <t xml:space="preserve">17.7083778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7591190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6745529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.573070526123</t>
+    <t xml:space="preserve">17.7591209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6745510101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730724334717</t>
   </si>
   <si>
     <t xml:space="preserve">17.3362846374512</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2009754180908</t>
+    <t xml:space="preserve">17.2009773254395</t>
   </si>
   <si>
     <t xml:space="preserve">17.2348041534424</t>
@@ -857,31 +857,31 @@
     <t xml:space="preserve">17.2517166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">17.217887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3701076507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4560203552246</t>
+    <t xml:space="preserve">17.2178897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3701095581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.456018447876</t>
   </si>
   <si>
     <t xml:space="preserve">17.7147541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5767650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.559513092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975059509277</t>
+    <t xml:space="preserve">17.5767631530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5595149993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975078582764</t>
   </si>
   <si>
     <t xml:space="preserve">17.469820022583</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6147136688232</t>
+    <t xml:space="preserve">17.614709854126</t>
   </si>
   <si>
     <t xml:space="preserve">16.7729568481445</t>
@@ -893,22 +893,22 @@
     <t xml:space="preserve">17.1662349700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1317405700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9937438964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9868488311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9661483764648</t>
+    <t xml:space="preserve">17.1317386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9937419891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9868469238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9661445617676</t>
   </si>
   <si>
     <t xml:space="preserve">16.835054397583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8488540649414</t>
+    <t xml:space="preserve">16.84885597229</t>
   </si>
   <si>
     <t xml:space="preserve">16.8281536102295</t>
@@ -917,40 +917,40 @@
     <t xml:space="preserve">16.7591590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8695526123047</t>
+    <t xml:space="preserve">16.8695545196533</t>
   </si>
   <si>
     <t xml:space="preserve">16.9178504943848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9730472564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9385509490967</t>
+    <t xml:space="preserve">16.9730453491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.938549041748</t>
   </si>
   <si>
     <t xml:space="preserve">17.1524391174316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.662561416626</t>
+    <t xml:space="preserve">16.6625633239746</t>
   </si>
   <si>
     <t xml:space="preserve">16.5935668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5659713745117</t>
+    <t xml:space="preserve">16.5659694671631</t>
   </si>
   <si>
     <t xml:space="preserve">16.5038738250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9040508270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8005561828613</t>
+    <t xml:space="preserve">16.8626518249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9040489196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.80055809021</t>
   </si>
   <si>
     <t xml:space="preserve">16.8971500396729</t>
@@ -959,25 +959,25 @@
     <t xml:space="preserve">16.5383739471436</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5590724945068</t>
+    <t xml:space="preserve">16.5590686798096</t>
   </si>
   <si>
     <t xml:space="preserve">16.4900741577148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2416896820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.303783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2485885620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.124397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1864891052246</t>
+    <t xml:space="preserve">16.2416877746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3037815093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2485847473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1243953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1864910125732</t>
   </si>
   <si>
     <t xml:space="preserve">16.1588935852051</t>
@@ -986,25 +986,25 @@
     <t xml:space="preserve">16.5314712524414</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2899856567383</t>
+    <t xml:space="preserve">16.2899875640869</t>
   </si>
   <si>
     <t xml:space="preserve">16.3175830841064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5452690124512</t>
+    <t xml:space="preserve">16.5452709197998</t>
   </si>
   <si>
     <t xml:space="preserve">16.3658790588379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4624767303467</t>
+    <t xml:space="preserve">16.4624729156494</t>
   </si>
   <si>
     <t xml:space="preserve">16.3313827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3520793914795</t>
+    <t xml:space="preserve">16.3520832061768</t>
   </si>
   <si>
     <t xml:space="preserve">16.6970634460449</t>
@@ -1013,40 +1013,40 @@
     <t xml:space="preserve">16.3865814208984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4486751556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5107727050781</t>
+    <t xml:space="preserve">16.4486770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5107746124268</t>
   </si>
   <si>
     <t xml:space="preserve">16.4210777282715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4348754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.393482208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4969730377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5245723724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4003772735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4555778503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.358980178833</t>
+    <t xml:space="preserve">16.4348773956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3934764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4969749450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5245742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4003791809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4555759429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3589820861816</t>
   </si>
   <si>
     <t xml:space="preserve">16.2830848693848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5521717071533</t>
+    <t xml:space="preserve">16.5521678924561</t>
   </si>
   <si>
     <t xml:space="preserve">16.1795921325684</t>
@@ -1055,109 +1055,109 @@
     <t xml:space="preserve">16.2071895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1933898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9036092758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5586261749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4965286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9381065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7794160842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7656173706055</t>
+    <t xml:space="preserve">16.1933917999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9036054611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5586242675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4965295791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9381046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7794170379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7656145095825</t>
   </si>
   <si>
     <t xml:space="preserve">15.7863130569458</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9795017242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9312057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7035179138184</t>
+    <t xml:space="preserve">15.9795036315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9312028884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7035188674927</t>
   </si>
   <si>
     <t xml:space="preserve">15.6483192443848</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8415088653564</t>
+    <t xml:space="preserve">15.8415098190308</t>
   </si>
   <si>
     <t xml:space="preserve">15.7518167495728</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8691082000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8622093200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0277976989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8967065811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6276226043701</t>
+    <t xml:space="preserve">15.8691101074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8622102737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0277996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8967056274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6276206970215</t>
   </si>
   <si>
     <t xml:space="preserve">15.7173156738281</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5310287475586</t>
+    <t xml:space="preserve">15.5310277938843</t>
   </si>
   <si>
     <t xml:space="preserve">15.5034275054932</t>
   </si>
   <si>
-    <t xml:space="preserve">15.441333770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2481460571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.317138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3309392929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2826404571533</t>
+    <t xml:space="preserve">15.4413318634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.248143196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3171405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.330940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2826414108276</t>
   </si>
   <si>
     <t xml:space="preserve">15.3792362213135</t>
   </si>
   <si>
-    <t xml:space="preserve">15.261944770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.600025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9519071578979</t>
+    <t xml:space="preserve">15.2619457244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6000232696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.489631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9519052505493</t>
   </si>
   <si>
     <t xml:space="preserve">15.972601890564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.986400604248</t>
+    <t xml:space="preserve">15.9864025115967</t>
   </si>
   <si>
     <t xml:space="preserve">16.0415992736816</t>
@@ -1166,22 +1166,22 @@
     <t xml:space="preserve">15.8553094863892</t>
   </si>
   <si>
-    <t xml:space="preserve">15.793212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2895383834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1791458129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2067461013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3999357223511</t>
+    <t xml:space="preserve">15.7932138442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2895393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1791477203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2067470550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3999328613281</t>
   </si>
   <si>
     <t xml:space="preserve">15.2343454360962</t>
@@ -1199,58 +1199,58 @@
     <t xml:space="preserve">15.6345205307007</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1450939178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.48317527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6073684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3727798461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6349639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141807556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0898952484131</t>
+    <t xml:space="preserve">16.145092010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4831733703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6073665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3727779388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6349678039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141788482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0898971557617</t>
   </si>
   <si>
     <t xml:space="preserve">16.2002906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7315578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6901607513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4762744903564</t>
+    <t xml:space="preserve">16.731559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6901626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4762763977051</t>
   </si>
   <si>
     <t xml:space="preserve">16.7522621154785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6487655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6280689239502</t>
+    <t xml:space="preserve">16.6487636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6280670166016</t>
   </si>
   <si>
     <t xml:space="preserve">17.0420436859131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0765419006348</t>
+    <t xml:space="preserve">17.0765399932861</t>
   </si>
   <si>
     <t xml:space="preserve">17.1110382080078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2145328521729</t>
+    <t xml:space="preserve">17.2145347595215</t>
   </si>
   <si>
     <t xml:space="preserve">17.1455383300781</t>
@@ -1259,46 +1259,46 @@
     <t xml:space="preserve">17.1800346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0070991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.21409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1105976104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5931272506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621179580688</t>
+    <t xml:space="preserve">16.0071029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2140884399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.110595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5931253433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621217727661</t>
   </si>
   <si>
     <t xml:space="preserve">15.0066556930542</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7306756973267</t>
+    <t xml:space="preserve">14.7306747436523</t>
   </si>
   <si>
     <t xml:space="preserve">14.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9721612930298</t>
+    <t xml:space="preserve">14.9721584320068</t>
   </si>
   <si>
     <t xml:space="preserve">15.4551334381104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1101512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0411548614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0756549835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3516368865967</t>
+    <t xml:space="preserve">15.1101503372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0411539077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0756540298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3516387939453</t>
   </si>
   <si>
     <t xml:space="preserve">15.4206352233887</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">15.5241279602051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6966171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8742475509644</t>
+    <t xml:space="preserve">15.6966190338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156650543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.874249458313</t>
   </si>
   <si>
     <t xml:space="preserve">15.556056022644</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">15.7328300476074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5914096832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3439292907715</t>
+    <t xml:space="preserve">15.5914087295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3439264297485</t>
   </si>
   <si>
     <t xml:space="preserve">15.3792810440063</t>
@@ -1334,55 +1334,55 @@
     <t xml:space="preserve">14.7782545089722</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4247064590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5307712554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600610733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4954147338867</t>
+    <t xml:space="preserve">14.4247074127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5307703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600620269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.495415687561</t>
   </si>
   <si>
     <t xml:space="preserve">13.8873138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1135845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.318642616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6014804840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0257377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.061089515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9550275802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8489627838135</t>
+    <t xml:space="preserve">14.1135864257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3186435699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6014795303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0257349014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0610904693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9550266265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8489637374878</t>
   </si>
   <si>
     <t xml:space="preserve">14.8843154907227</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7075424194336</t>
+    <t xml:space="preserve">14.7075443267822</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671562194824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2025098800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.566125869751</t>
+    <t xml:space="preserve">15.2025108337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5661239624023</t>
   </si>
   <si>
     <t xml:space="preserve">14.6368341445923</t>
@@ -1391,31 +1391,31 @@
     <t xml:space="preserve">14.2832889556885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0853023529053</t>
+    <t xml:space="preserve">14.0853033065796</t>
   </si>
   <si>
     <t xml:space="preserve">14.8136081695557</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3539972305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3893518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428998947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1418685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1772241592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2479314804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2125797271729</t>
+    <t xml:space="preserve">14.3539981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3893527984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428979873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1418704986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1772232055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2479333877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2125787734985</t>
   </si>
   <si>
     <t xml:space="preserve">14.0711603164673</t>
@@ -1424,22 +1424,22 @@
     <t xml:space="preserve">13.9438819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8731727600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8166074752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.859034538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.014594078064</t>
+    <t xml:space="preserve">13.8731737136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8166065216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8590316772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0145931243896</t>
   </si>
   <si>
     <t xml:space="preserve">13.929741859436</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0004510879517</t>
+    <t xml:space="preserve">14.0004501342773</t>
   </si>
   <si>
     <t xml:space="preserve">14.0994434356689</t>
@@ -1451,19 +1451,19 @@
     <t xml:space="preserve">14.0287342071533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0570163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1277275085449</t>
+    <t xml:space="preserve">14.0570154190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1277284622192</t>
   </si>
   <si>
     <t xml:space="preserve">14.9196720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6721897125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4347763061523</t>
+    <t xml:space="preserve">14.6721887588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4347772598267</t>
   </si>
   <si>
     <t xml:space="preserve">13.505485534668</t>
@@ -1472,25 +1472,25 @@
     <t xml:space="preserve">13.4913425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3782072067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4630584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5620517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5337677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1660814285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7842502593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6852569580078</t>
+    <t xml:space="preserve">13.3782081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.463059425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5620527267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.533766746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1660823822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7842493057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6852560043335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1620092391968</t>
@@ -1502,25 +1502,25 @@
     <t xml:space="preserve">13.4064903259277</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5479125976562</t>
+    <t xml:space="preserve">13.5479097366333</t>
   </si>
   <si>
     <t xml:space="preserve">13.7883214950562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7741804122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5903367996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4489164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3074979782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3923501968384</t>
+    <t xml:space="preserve">13.7741813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5903358459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.448917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3074998855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.392352104187</t>
   </si>
   <si>
     <t xml:space="preserve">13.01051902771</t>
@@ -1532,40 +1532,40 @@
     <t xml:space="preserve">13.2933559417725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9256687164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0388059616089</t>
+    <t xml:space="preserve">12.925669670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0388031005859</t>
   </si>
   <si>
     <t xml:space="preserve">12.996376991272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2367887496948</t>
+    <t xml:space="preserve">13.2367897033691</t>
   </si>
   <si>
     <t xml:space="preserve">13.0953722000122</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6469039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6751861572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0670852661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2509317398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2085075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812292098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3499231338501</t>
+    <t xml:space="preserve">13.6469030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6751871109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0670871734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2509298324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2085046768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812273025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3499240875244</t>
   </si>
   <si>
     <t xml:space="preserve">12.8408164978027</t>
@@ -1574,46 +1574,46 @@
     <t xml:space="preserve">12.5296955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">12.897385597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6004056930542</t>
+    <t xml:space="preserve">12.8973846435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6004037857056</t>
   </si>
   <si>
     <t xml:space="preserve">13.7317552566528</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5761938095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5196266174316</t>
+    <t xml:space="preserve">13.5761957168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.519624710083</t>
   </si>
   <si>
     <t xml:space="preserve">13.7176122665405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8307456970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7600364685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9156007766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7458972930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0428762435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8448905944824</t>
+    <t xml:space="preserve">13.8307476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7600374221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.915599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7458992004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0428781509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8448886871338</t>
   </si>
   <si>
     <t xml:space="preserve">14.5417671203613</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2218456268311</t>
+    <t xml:space="preserve">14.2218475341797</t>
   </si>
   <si>
     <t xml:space="preserve">13.9455537796021</t>
@@ -1622,13 +1622,13 @@
     <t xml:space="preserve">14.17822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9891796112061</t>
+    <t xml:space="preserve">13.9891815185547</t>
   </si>
   <si>
     <t xml:space="preserve">14.2073078155518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4399747848511</t>
+    <t xml:space="preserve">14.4399766921997</t>
   </si>
   <si>
     <t xml:space="preserve">14.2654733657837</t>
@@ -1640,16 +1640,16 @@
     <t xml:space="preserve">14.4981422424316</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4690589904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527250289917</t>
+    <t xml:space="preserve">14.4690570831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527231216431</t>
   </si>
   <si>
     <t xml:space="preserve">14.3381814956665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5126829147339</t>
+    <t xml:space="preserve">14.5126848220825</t>
   </si>
   <si>
     <t xml:space="preserve">14.3963499069214</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">14.6144771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8326025009155</t>
+    <t xml:space="preserve">14.8326044082642</t>
   </si>
   <si>
     <t xml:space="preserve">14.9780206680298</t>
@@ -1679,16 +1679,16 @@
     <t xml:space="preserve">15.1961479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4142732620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.450629234314</t>
+    <t xml:space="preserve">15.4142751693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4506282806396</t>
   </si>
   <si>
     <t xml:space="preserve">15.3415641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2325019836426</t>
+    <t xml:space="preserve">15.2325010299683</t>
   </si>
   <si>
     <t xml:space="preserve">15.3052082061768</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">15.268856048584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6687545776367</t>
+    <t xml:space="preserve">15.6687526702881</t>
   </si>
   <si>
     <t xml:space="preserve">15.0507287979126</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">15.0870838165283</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9416666030884</t>
+    <t xml:space="preserve">14.9416646957397</t>
   </si>
   <si>
     <t xml:space="preserve">14.723539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0143756866455</t>
+    <t xml:space="preserve">15.0143747329712</t>
   </si>
   <si>
     <t xml:space="preserve">14.5781221389771</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">14.7598943710327</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6508293151855</t>
+    <t xml:space="preserve">14.6508312225342</t>
   </si>
   <si>
     <t xml:space="preserve">14.3672666549683</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">14.5272254943848</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4545154571533</t>
+    <t xml:space="preserve">14.454514503479</t>
   </si>
   <si>
     <t xml:space="preserve">14.7962484359741</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">16.6139698028564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.541259765625</t>
+    <t xml:space="preserve">16.5412616729736</t>
   </si>
   <si>
     <t xml:space="preserve">16.8320960998535</t>
@@ -1763,10 +1763,10 @@
     <t xml:space="preserve">16.6503238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5776138305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8684501647949</t>
+    <t xml:space="preserve">16.577615737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8684520721436</t>
   </si>
   <si>
     <t xml:space="preserve">16.7593879699707</t>
@@ -1775,13 +1775,13 @@
     <t xml:space="preserve">17.0502223968506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.086576461792</t>
+    <t xml:space="preserve">17.0865783691406</t>
   </si>
   <si>
     <t xml:space="preserve">17.4864730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4137668609619</t>
+    <t xml:space="preserve">17.4137687683105</t>
   </si>
   <si>
     <t xml:space="preserve">17.2683486938477</t>
@@ -1805,13 +1805,13 @@
     <t xml:space="preserve">17.6682453155518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0681438446045</t>
+    <t xml:space="preserve">18.0681457519531</t>
   </si>
   <si>
     <t xml:space="preserve">17.9227275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1045017242432</t>
+    <t xml:space="preserve">18.1044998168945</t>
   </si>
   <si>
     <t xml:space="preserve">17.8500194549561</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">18.2862739562988</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3589820861816</t>
+    <t xml:space="preserve">18.358980178833</t>
   </si>
   <si>
     <t xml:space="preserve">18.4680423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5771064758301</t>
+    <t xml:space="preserve">18.5771045684814</t>
   </si>
   <si>
     <t xml:space="preserve">17.9954376220703</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">17.5955390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4501209259033</t>
+    <t xml:space="preserve">17.4501190185547</t>
   </si>
   <si>
     <t xml:space="preserve">18.2499179840088</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">19.1951332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9770069122314</t>
+    <t xml:space="preserve">18.9770088195801</t>
   </si>
   <si>
     <t xml:space="preserve">19.0860729217529</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">19.449613571167</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9048042297363</t>
+    <t xml:space="preserve">16.9048023223877</t>
   </si>
   <si>
     <t xml:space="preserve">16.7230339050293</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">18.7952346801758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5407543182373</t>
+    <t xml:space="preserve">18.5407562255859</t>
   </si>
   <si>
     <t xml:space="preserve">18.8679447174072</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">19.8495121002197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4213848114014</t>
+    <t xml:space="preserve">19.4213829040527</t>
   </si>
   <si>
     <t xml:space="preserve">19.7327518463135</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">19.8105945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6549110412598</t>
+    <t xml:space="preserve">19.6549091339111</t>
   </si>
   <si>
     <t xml:space="preserve">20.3554821014404</t>
@@ -1955,13 +1955,13 @@
     <t xml:space="preserve">20.121955871582</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9273529052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4603080749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.343542098999</t>
+    <t xml:space="preserve">19.9273548126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4603061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3435440063477</t>
   </si>
   <si>
     <t xml:space="preserve">19.3046226501465</t>
@@ -1970,22 +1970,22 @@
     <t xml:space="preserve">19.966272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2657032012939</t>
+    <t xml:space="preserve">19.2657051086426</t>
   </si>
   <si>
     <t xml:space="preserve">19.771671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7597370147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1608791351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.044116973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1728115081787</t>
+    <t xml:space="preserve">18.7597351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1608772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0441150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1728134155273</t>
   </si>
   <si>
     <t xml:space="preserve">21.0560512542725</t>
@@ -1994,10 +1994,10 @@
     <t xml:space="preserve">20.9392890930176</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2895736694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0171298980713</t>
+    <t xml:space="preserve">21.2895755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0171318054199</t>
   </si>
   <si>
     <t xml:space="preserve">20.7836074829102</t>
@@ -2006,10 +2006,10 @@
     <t xml:space="preserve">20.7057666778564</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0949726104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4452590942383</t>
+    <t xml:space="preserve">21.0949745178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4452571868896</t>
   </si>
   <si>
     <t xml:space="preserve">21.7566242218018</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">21.7955436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0290660858154</t>
+    <t xml:space="preserve">22.0290641784668</t>
   </si>
   <si>
     <t xml:space="preserve">22.0679874420166</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">22.5350360870361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.57395362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6517963409424</t>
+    <t xml:space="preserve">22.5739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.651798248291</t>
   </si>
   <si>
     <t xml:space="preserve">22.7685585021973</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">22.2625904083252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5080528259277</t>
+    <t xml:space="preserve">23.5080509185791</t>
   </si>
   <si>
     <t xml:space="preserve">23.97509765625</t>
@@ -2072,19 +2072,19 @@
     <t xml:space="preserve">24.5199851989746</t>
   </si>
   <si>
-    <t xml:space="preserve">25.298397064209</t>
+    <t xml:space="preserve">25.2983989715576</t>
   </si>
   <si>
     <t xml:space="preserve">24.7924308776855</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1427135467529</t>
+    <t xml:space="preserve">25.1427154541016</t>
   </si>
   <si>
     <t xml:space="preserve">24.7535076141357</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6367454528809</t>
+    <t xml:space="preserve">24.6367473602295</t>
   </si>
   <si>
     <t xml:space="preserve">24.1697006225586</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">24.0140190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0799236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7026557922363</t>
+    <t xml:space="preserve">23.0799255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7026538848877</t>
   </si>
   <si>
     <t xml:space="preserve">24.0529384613037</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">23.5858917236328</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1577625274658</t>
+    <t xml:space="preserve">23.1577644348145</t>
   </si>
   <si>
     <t xml:space="preserve">23.8583335876465</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">23.4302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0918598175049</t>
+    <t xml:space="preserve">24.0918579101562</t>
   </si>
   <si>
     <t xml:space="preserve">23.3912868499756</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3523654937744</t>
+    <t xml:space="preserve">23.352367401123</t>
   </si>
   <si>
     <t xml:space="preserve">23.0410022735596</t>
@@ -2144,13 +2144,13 @@
     <t xml:space="preserve">23.1188430786133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6248149871826</t>
+    <t xml:space="preserve">23.624813079834</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128749847412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1069087982178</t>
+    <t xml:space="preserve">22.1069068908691</t>
   </si>
   <si>
     <t xml:space="preserve">22.1847496032715</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">22.4961128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3015117645264</t>
+    <t xml:space="preserve">22.3015098571777</t>
   </si>
   <si>
     <t xml:space="preserve">22.6907157897949</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">22.9631614685059</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2356052398682</t>
+    <t xml:space="preserve">23.2356071472168</t>
   </si>
   <si>
     <t xml:space="preserve">22.9242420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2236709594727</t>
+    <t xml:space="preserve">22.223669052124</t>
   </si>
   <si>
     <t xml:space="preserve">22.4182739257812</t>
@@ -2186,25 +2186,25 @@
     <t xml:space="preserve">21.9123039245605</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4841785430908</t>
+    <t xml:space="preserve">21.4841766357422</t>
   </si>
   <si>
     <t xml:space="preserve">21.1338939666748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.523099899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7177028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6398620605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2506542205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5620212554932</t>
+    <t xml:space="preserve">21.5230979919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.717700958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6398601531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2506561279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5620193481445</t>
   </si>
   <si>
     <t xml:space="preserve">21.8344631195068</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">21.678783416748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9901466369629</t>
+    <t xml:space="preserve">21.9901485443115</t>
   </si>
   <si>
     <t xml:space="preserve">22.1458282470703</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">21.3284950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2117309570312</t>
+    <t xml:space="preserve">21.2117328643799</t>
   </si>
   <si>
     <t xml:space="preserve">21.3674144744873</t>
@@ -3696,6 +3696,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.5999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2999992370605</t>
   </si>
 </sst>
 </file>
@@ -69060,7 +69063,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6911111111</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>16254</v>
@@ -69081,6 +69084,32 @@
         <v>1227</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6939699074</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>30218</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>32.9000015258789</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>32.0499992370605</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>32.9000015258789</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>32.2999992370605</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="1229">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,94 +44,94 @@
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9573316574097</t>
+    <t xml:space="preserve">14.0577459335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.957332611084</t>
   </si>
   <si>
     <t xml:space="preserve">13.3883295059204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8896141052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8527965545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9532089233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6185007095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846181869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3842029571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8821420669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7348709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2127265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7307453155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2294597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2194213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2461957931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9148359298706</t>
+    <t xml:space="preserve">12.889612197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8527975082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9532079696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6184988021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.384204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8821401596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7348699569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2127246856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7307462692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2294607162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2194204330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2461948394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9148349761963</t>
   </si>
   <si>
     <t xml:space="preserve">11.1323947906494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6143751144409</t>
+    <t xml:space="preserve">11.6143741607666</t>
   </si>
   <si>
     <t xml:space="preserve">11.6813182830811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474338531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3466091156006</t>
+    <t xml:space="preserve">11.5474328994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3466081619263</t>
   </si>
   <si>
     <t xml:space="preserve">11.3131370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3298740386963</t>
+    <t xml:space="preserve">11.329873085022</t>
   </si>
   <si>
     <t xml:space="preserve">10.8947525024414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8780155181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0453701019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4261617660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094247817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7080955505371</t>
+    <t xml:space="preserve">10.8780174255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.045371055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4261608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094257354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7080936431885</t>
   </si>
   <si>
     <t xml:space="preserve">11.7147884368896</t>
@@ -140,58 +140,58 @@
     <t xml:space="preserve">12.0494947433472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7482566833496</t>
+    <t xml:space="preserve">11.7482595443726</t>
   </si>
   <si>
     <t xml:space="preserve">11.7449131011963</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2135028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168483734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3674688339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7189140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8293657302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0201511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2209739685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3849821090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3347768783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3146924972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569667816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109327316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661823272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306037902832</t>
+    <t xml:space="preserve">12.2135057449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3674697875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7189111709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8293676376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0201501846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2209730148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3849840164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3347749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3146934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569677352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109317779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306056976318</t>
   </si>
   <si>
     <t xml:space="preserve">13.2879161834717</t>
@@ -200,82 +200,82 @@
     <t xml:space="preserve">12.8260192871094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9833326339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.903000831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2377090454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1674194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1138677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5046997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8092832565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8862638473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7055225372314</t>
+    <t xml:space="preserve">12.9833297729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.903003692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2377109527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1674213409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1138696670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971345901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5047006607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8092842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.886266708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7055234909058</t>
   </si>
   <si>
     <t xml:space="preserve">12.7222595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9163904190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0301914215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6318874359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7021789550781</t>
+    <t xml:space="preserve">12.9163885116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0301895141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327159881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6318883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7021770477295</t>
   </si>
   <si>
     <t xml:space="preserve">12.8695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.558253288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5682935714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8360605239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494482040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958946228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5348234176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7791604995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7691173553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.786563873291</t>
+    <t xml:space="preserve">12.5582513809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5682926177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8360595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958955764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5348224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7791595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7691192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7865657806396</t>
   </si>
   <si>
     <t xml:space="preserve">12.502420425415</t>
@@ -284,82 +284,82 @@
     <t xml:space="preserve">12.6512594223022</t>
   </si>
   <si>
-    <t xml:space="preserve">12.752739906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5836038589478</t>
+    <t xml:space="preserve">12.7527379989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5836048126221</t>
   </si>
   <si>
     <t xml:space="preserve">12.4990377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5700750350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159492492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.27916431427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0660524368286</t>
+    <t xml:space="preserve">12.5700731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159521102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2791624069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0660514831543</t>
   </si>
   <si>
     <t xml:space="preserve">12.1776809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1641521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1709175109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1100273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1269426345825</t>
+    <t xml:space="preserve">12.1641502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1709184646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1100292205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1269407272339</t>
   </si>
   <si>
     <t xml:space="preserve">11.9814853668213</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7459726333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580238342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231372833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6973419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.778525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2406778335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8212232589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.061393737793</t>
+    <t xml:space="preserve">12.7459754943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580209732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231382369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.697340965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7785234451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2406759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8212251663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0613956451416</t>
   </si>
   <si>
     <t xml:space="preserve">11.196702003479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4064292907715</t>
+    <t xml:space="preserve">11.4064302444458</t>
   </si>
   <si>
     <t xml:space="preserve">11.5248231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6656198501587</t>
+    <t xml:space="preserve">10.6656188964844</t>
   </si>
   <si>
     <t xml:space="preserve">10.1886606216431</t>
@@ -368,52 +368,52 @@
     <t xml:space="preserve">10.5878171920776</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6825323104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8394136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0199718475342</t>
+    <t xml:space="preserve">10.6825332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8394117355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0199708938599</t>
   </si>
   <si>
     <t xml:space="preserve">13.3616228103638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0233516693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1924877166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4969301223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4698667526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4800157546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2939691543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108816146851</t>
+    <t xml:space="preserve">13.0233545303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1924886703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4969310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4698696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307569503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4800176620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2939682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108825683594</t>
   </si>
   <si>
     <t xml:space="preserve">13.3548564910889</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0740966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.03688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9489345550537</t>
+    <t xml:space="preserve">13.0740976333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368843078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9489336013794</t>
   </si>
   <si>
     <t xml:space="preserve">12.9827613830566</t>
@@ -428,136 +428,136 @@
     <t xml:space="preserve">12.9962911605835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8576021194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113042831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1248369216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1823406219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0605659484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857242584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4123649597168</t>
+    <t xml:space="preserve">12.8576030731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1248359680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1823396682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0605640411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857252120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4123630523682</t>
   </si>
   <si>
     <t xml:space="preserve">13.5679683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4157457351685</t>
+    <t xml:space="preserve">13.4157476425171</t>
   </si>
   <si>
     <t xml:space="preserve">13.5138454437256</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7066583633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8352012634277</t>
+    <t xml:space="preserve">13.706657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8352003097534</t>
   </si>
   <si>
     <t xml:space="preserve">14.2106761932373</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4576148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7552909851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838329315186</t>
+    <t xml:space="preserve">14.4576168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7552928924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838300704956</t>
   </si>
   <si>
     <t xml:space="preserve">15.01575756073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9853162765503</t>
+    <t xml:space="preserve">14.985312461853</t>
   </si>
   <si>
     <t xml:space="preserve">15.3303480148315</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6652364730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2897548675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8297100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842527389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7722015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9514875411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7485284805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7180805206299</t>
+    <t xml:space="preserve">15.6652326583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2897596359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8297090530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6842565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7722043991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.951488494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7485237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7180814743042</t>
   </si>
   <si>
     <t xml:space="preserve">14.8770666122437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992677688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751663208008</t>
+    <t xml:space="preserve">14.7992639541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751634597778</t>
   </si>
   <si>
     <t xml:space="preserve">14.90074634552</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2018060684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939819335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330945968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988431930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9142761230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9278087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7383794784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7248449325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5421800613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4440851211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0529661178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1104755401611</t>
+    <t xml:space="preserve">15.2018051147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939800262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9142770767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.927809715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.738377571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7248468399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5421829223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4440841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0529670715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1442995071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1104736328125</t>
   </si>
   <si>
     <t xml:space="preserve">14.9548692703247</t>
@@ -566,88 +566,88 @@
     <t xml:space="preserve">15.0901775360107</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2187213897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7823524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707220077515</t>
+    <t xml:space="preserve">15.2187204360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7823543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707248687744</t>
   </si>
   <si>
     <t xml:space="preserve">14.6166009902954</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3764305114746</t>
+    <t xml:space="preserve">14.3764314651489</t>
   </si>
   <si>
     <t xml:space="preserve">14.1599388122559</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2546539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.041543006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1125822067261</t>
+    <t xml:space="preserve">14.2546510696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0415420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1125793457031</t>
   </si>
   <si>
     <t xml:space="preserve">14.038161277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1430253982544</t>
+    <t xml:space="preserve">14.1430225372314</t>
   </si>
   <si>
     <t xml:space="preserve">14.1903829574585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3527507781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2072954177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3561325073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373178482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3087787628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2411203384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3392210006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2512702941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464071273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058139801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1193466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.227593421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2715654373169</t>
+    <t xml:space="preserve">14.3527517318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2072973251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3561334609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373197555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730478286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3087768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2411222457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3392190933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2512712478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1464080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058149337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1193437576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2275905609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2715673446655</t>
   </si>
   <si>
     <t xml:space="preserve">14.149790763855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753717422485</t>
+    <t xml:space="preserve">14.0753707885742</t>
   </si>
   <si>
     <t xml:space="preserve">14.0719881057739</t>
@@ -656,31 +656,31 @@
     <t xml:space="preserve">14.2749509811401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1667041778564</t>
+    <t xml:space="preserve">14.1667032241821</t>
   </si>
   <si>
     <t xml:space="preserve">14.4779109954834</t>
   </si>
   <si>
-    <t xml:space="preserve">14.626748085022</t>
+    <t xml:space="preserve">14.6267499923706</t>
   </si>
   <si>
     <t xml:space="preserve">14.7519092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8161792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1037092208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0834102630615</t>
+    <t xml:space="preserve">14.816180229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1037082672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0834121704102</t>
   </si>
   <si>
     <t xml:space="preserve">15.1882762908936</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1172399520874</t>
+    <t xml:space="preserve">15.1172370910645</t>
   </si>
   <si>
     <t xml:space="preserve">15.1544485092163</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">15.4758043289185</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3574132919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3912372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893341064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1713628768921</t>
+    <t xml:space="preserve">15.3574094772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3912391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893350601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1713609695435</t>
   </si>
   <si>
     <t xml:space="preserve">15.1003255844116</t>
@@ -710,103 +710,103 @@
     <t xml:space="preserve">15.3946189880371</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3168172836304</t>
+    <t xml:space="preserve">15.316819190979</t>
   </si>
   <si>
     <t xml:space="preserve">15.3134355545044</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4182996749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4250631332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366926193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6753816604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6449384689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7295055389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6618518829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.651704788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6821479797363</t>
+    <t xml:space="preserve">15.4182987213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4250640869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.536693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6753826141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6449394226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7295074462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6618528366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6517028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.682147026062</t>
   </si>
   <si>
     <t xml:space="preserve">15.5637531280518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.408148765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415576934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7024431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584701538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588890075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5874338150024</t>
+    <t xml:space="preserve">15.4081516265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415557861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7024440765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584711074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.458890914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5874347686768</t>
   </si>
   <si>
     <t xml:space="preserve">15.6550874710083</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7227392196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3350105285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0339488983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4060401916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.402660369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4195766448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6935710906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0994968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9980125427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1671485900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4208507537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5392417907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6407260894775</t>
+    <t xml:space="preserve">15.7227382659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3350067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0339469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4060440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4026622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4195728302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6935729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0994930267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9980144500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1671504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4208488464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5392436981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6407279968262</t>
   </si>
   <si>
     <t xml:space="preserve">17.4039363861084</t>
@@ -821,82 +821,82 @@
     <t xml:space="preserve">17.3870239257812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5223293304443</t>
+    <t xml:space="preserve">17.522331237793</t>
   </si>
   <si>
     <t xml:space="preserve">17.4546775817871</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8775119781494</t>
+    <t xml:space="preserve">17.877513885498</t>
   </si>
   <si>
     <t xml:space="preserve">17.8098602294922</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7083797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7591209411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6745529174805</t>
+    <t xml:space="preserve">17.7083778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7591190338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6745510101318</t>
   </si>
   <si>
     <t xml:space="preserve">17.573070526123</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3362846374512</t>
+    <t xml:space="preserve">17.3362827301025</t>
   </si>
   <si>
     <t xml:space="preserve">17.2009735107422</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2348041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2517147064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2178916931152</t>
+    <t xml:space="preserve">17.2348022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2517166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2178897857666</t>
   </si>
   <si>
     <t xml:space="preserve">17.3701095581055</t>
   </si>
   <si>
-    <t xml:space="preserve">17.456018447876</t>
+    <t xml:space="preserve">17.4560203552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.7147541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5767650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5595169067383</t>
+    <t xml:space="preserve">17.5767612457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.559513092041</t>
   </si>
   <si>
     <t xml:space="preserve">17.6975059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4698219299316</t>
+    <t xml:space="preserve">17.4698181152344</t>
   </si>
   <si>
     <t xml:space="preserve">17.6147117614746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7729568481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0075435638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1662330627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1317405700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9937477111816</t>
+    <t xml:space="preserve">16.7729587554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0075454711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1662349700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1317386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.993745803833</t>
   </si>
   <si>
     <t xml:space="preserve">16.9868469238281</t>
@@ -905,22 +905,22 @@
     <t xml:space="preserve">16.9661483764648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8350524902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.84885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8281536102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7591590881348</t>
+    <t xml:space="preserve">16.835054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8488540649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8281555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7591609954834</t>
   </si>
   <si>
     <t xml:space="preserve">16.8695526123047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9178485870361</t>
+    <t xml:space="preserve">16.9178504943848</t>
   </si>
   <si>
     <t xml:space="preserve">16.9730472564697</t>
@@ -932,19 +932,19 @@
     <t xml:space="preserve">17.152437210083</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6625652313232</t>
+    <t xml:space="preserve">16.6625633239746</t>
   </si>
   <si>
     <t xml:space="preserve">16.5935668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5659694671631</t>
+    <t xml:space="preserve">16.5659675598145</t>
   </si>
   <si>
     <t xml:space="preserve">16.5038738250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626537322998</t>
+    <t xml:space="preserve">16.8626556396484</t>
   </si>
   <si>
     <t xml:space="preserve">16.9040508270264</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">16.80055809021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8971500396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5383701324463</t>
+    <t xml:space="preserve">16.8971538543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5383720397949</t>
   </si>
   <si>
     <t xml:space="preserve">16.5590705871582</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">16.4900741577148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2416877746582</t>
+    <t xml:space="preserve">16.2416896820068</t>
   </si>
   <si>
     <t xml:space="preserve">16.303783416748</t>
@@ -974,34 +974,34 @@
     <t xml:space="preserve">16.2485866546631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.124397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1864910125732</t>
+    <t xml:space="preserve">16.1243934631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1864891052246</t>
   </si>
   <si>
     <t xml:space="preserve">16.1588935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5314712524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2899837493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3175830841064</t>
+    <t xml:space="preserve">16.5314693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2899875640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3175849914551</t>
   </si>
   <si>
     <t xml:space="preserve">16.5452709197998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3658809661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4624786376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3313808441162</t>
+    <t xml:space="preserve">16.3658790588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4624767303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3313827514648</t>
   </si>
   <si>
     <t xml:space="preserve">16.3520832061768</t>
@@ -1010,10 +1010,10 @@
     <t xml:space="preserve">16.6970634460449</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3865776062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4486751556396</t>
+    <t xml:space="preserve">16.3865814208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4486770629883</t>
   </si>
   <si>
     <t xml:space="preserve">16.5107746124268</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">16.4210777282715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4348773956299</t>
+    <t xml:space="preserve">16.4348754882812</t>
   </si>
   <si>
     <t xml:space="preserve">16.3934783935547</t>
@@ -1034,31 +1034,31 @@
     <t xml:space="preserve">16.5245723724365</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4003791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4555778503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3589820861816</t>
+    <t xml:space="preserve">16.4003810882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4555740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.358980178833</t>
   </si>
   <si>
     <t xml:space="preserve">16.2830848693848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5521717071533</t>
+    <t xml:space="preserve">16.5521697998047</t>
   </si>
   <si>
     <t xml:space="preserve">16.1795921325684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2071895599365</t>
+    <t xml:space="preserve">16.2071876525879</t>
   </si>
   <si>
     <t xml:space="preserve">16.1933898925781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1519927978516</t>
+    <t xml:space="preserve">16.1519947052002</t>
   </si>
   <si>
     <t xml:space="preserve">15.9036073684692</t>
@@ -1070,190 +1070,190 @@
     <t xml:space="preserve">15.4965305328369</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9381055831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7794132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7656126022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7863130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9795036315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.931206703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7035188674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6483201980591</t>
+    <t xml:space="preserve">15.9381046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7794170379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7656164169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7863111495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9795055389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9312028884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.703516960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6483211517334</t>
   </si>
   <si>
     <t xml:space="preserve">15.8415098190308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7518157958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691072463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8622074127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0278015136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8967084884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6276216506958</t>
+    <t xml:space="preserve">15.7518148422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691082000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8622064590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0277976989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8967056274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6276206970215</t>
   </si>
   <si>
     <t xml:space="preserve">15.7173175811768</t>
   </si>
   <si>
-    <t xml:space="preserve">15.53102684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.441333770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2481441497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3171377182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.330940246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2826442718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792390823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619428634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.600022315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896306991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9519062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9726028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9864015579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0415992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8553104400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932119369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2895421981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1791467666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2067461013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3999357223511</t>
+    <t xml:space="preserve">15.5310297012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034284591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413290023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2481422424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3171405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3309412002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2826404571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792362213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.261944770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.600025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.489631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9519052505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.972601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.986400604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0416011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8553113937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932138442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.475830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2895412445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1791477203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2067470550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3999347686768</t>
   </si>
   <si>
     <t xml:space="preserve">15.2343454360962</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3033390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137344360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.386137008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.634521484375</t>
+    <t xml:space="preserve">15.3033418655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137334823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3861351013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6345224380493</t>
   </si>
   <si>
     <t xml:space="preserve">16.145092010498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4831733703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6073684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3727798461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6349678039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141807556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0898952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.200288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7315578460693</t>
+    <t xml:space="preserve">16.4831714630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6073665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3727779388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6349658966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141788482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0898971557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.731559753418</t>
   </si>
   <si>
     <t xml:space="preserve">16.6901626586914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4762725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7522602081299</t>
+    <t xml:space="preserve">16.4762744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7522583007812</t>
   </si>
   <si>
     <t xml:space="preserve">16.6487655639648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6280689239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0420455932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0765438079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1110382080078</t>
+    <t xml:space="preserve">16.6280670166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0420417785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0765399932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1110363006592</t>
   </si>
   <si>
     <t xml:space="preserve">17.2145328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1455364227295</t>
+    <t xml:space="preserve">17.1455383300781</t>
   </si>
   <si>
     <t xml:space="preserve">17.1800346374512</t>
@@ -1262,49 +1262,49 @@
     <t xml:space="preserve">16.00710105896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2140922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1105937957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5931234359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621236801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0066585540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.730673789978</t>
+    <t xml:space="preserve">16.21409034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.110595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5931253433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621198654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0066566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7306728363037</t>
   </si>
   <si>
     <t xml:space="preserve">14.9031648635864</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9721603393555</t>
+    <t xml:space="preserve">14.9721612930298</t>
   </si>
   <si>
     <t xml:space="preserve">15.455132484436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1101512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0411577224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0756530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3516359329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4206352233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5241279602051</t>
+    <t xml:space="preserve">15.1101531982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0411539077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0756549835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.351637840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4206342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5241289138794</t>
   </si>
   <si>
     <t xml:space="preserve">15.6966190338135</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">16.0156669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.874249458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5560579299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7328310012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914106369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3439292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7782506942749</t>
+    <t xml:space="preserve">15.8742456436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5560531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7328281402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914087295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3439283370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.379282951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7782516479492</t>
   </si>
   <si>
     <t xml:space="preserve">14.4247064590454</t>
@@ -1340,52 +1340,52 @@
     <t xml:space="preserve">14.5307693481445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4600601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4954166412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8873157501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1135854721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3186435699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6014776229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0257377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0610904693604</t>
+    <t xml:space="preserve">14.4600610733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.495415687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8873147964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1135845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.318642616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6014804840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0257349014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.061089515686</t>
   </si>
   <si>
     <t xml:space="preserve">14.9550275802612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8489637374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8843173980713</t>
+    <t xml:space="preserve">14.8489618301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8843154907227</t>
   </si>
   <si>
     <t xml:space="preserve">14.7075424194336</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1671533584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2025108337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5661249160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.636833190918</t>
+    <t xml:space="preserve">15.1671552658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2025089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.566125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6368360519409</t>
   </si>
   <si>
     <t xml:space="preserve">14.2832889556885</t>
@@ -1397,94 +1397,94 @@
     <t xml:space="preserve">14.81360912323</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3539981842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3893537521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.74289894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1418704986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1772232055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2479314804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2125797271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0711584091187</t>
+    <t xml:space="preserve">14.3539972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3893527984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.742901802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1418676376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1772241592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.247932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2125787734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.071159362793</t>
   </si>
   <si>
     <t xml:space="preserve">13.9438829421997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8731756210327</t>
+    <t xml:space="preserve">13.8731737136841</t>
   </si>
   <si>
     <t xml:space="preserve">13.8166074752808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8590316772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.014591217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9297399520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0004501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0994434356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.97216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.028736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0570182800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1277265548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9196720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6721906661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.434775352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.505485534668</t>
+    <t xml:space="preserve">13.8590326309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0145931243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.929741859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.000449180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0994424819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9721660614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0287322998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.057017326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1277275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9196729660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6721897125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5054845809937</t>
   </si>
   <si>
     <t xml:space="preserve">13.4913425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3782091140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4630613327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5620527267456</t>
+    <t xml:space="preserve">13.3782072067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.463059425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5620517730713</t>
   </si>
   <si>
     <t xml:space="preserve">13.5337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1660814285278</t>
+    <t xml:space="preserve">13.1660804748535</t>
   </si>
   <si>
     <t xml:space="preserve">12.7842502593994</t>
@@ -1493,43 +1493,43 @@
     <t xml:space="preserve">12.6852569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1620073318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6569719314575</t>
+    <t xml:space="preserve">12.1620082855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6569728851318</t>
   </si>
   <si>
     <t xml:space="preserve">13.4064903259277</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5479097366333</t>
+    <t xml:space="preserve">13.5479116439819</t>
   </si>
   <si>
     <t xml:space="preserve">13.7883234024048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7741785049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5903348922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.448917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3074979782104</t>
+    <t xml:space="preserve">13.7741804122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5903339385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4489192962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3074998855591</t>
   </si>
   <si>
     <t xml:space="preserve">13.3923501968384</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0105199813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1519403457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2933549880981</t>
+    <t xml:space="preserve">13.01051902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1519384384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2933559417725</t>
   </si>
   <si>
     <t xml:space="preserve">12.9256687164307</t>
@@ -1538,34 +1538,34 @@
     <t xml:space="preserve">13.0388031005859</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9963788986206</t>
+    <t xml:space="preserve">12.996376991272</t>
   </si>
   <si>
     <t xml:space="preserve">13.2367887496948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0953712463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6469030380249</t>
+    <t xml:space="preserve">13.0953702926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6469039916992</t>
   </si>
   <si>
     <t xml:space="preserve">13.6751880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0670871734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2509288787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2085065841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812301635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3499240875244</t>
+    <t xml:space="preserve">13.0670862197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2509317398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2085056304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812282562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3499231338501</t>
   </si>
   <si>
     <t xml:space="preserve">12.8408174514771</t>
@@ -1574,43 +1574,43 @@
     <t xml:space="preserve">12.5296955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8973836898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6004047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7317552566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5761938095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.519627571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7176132202148</t>
+    <t xml:space="preserve">12.8973846435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6004056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7317543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5761957168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5196285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7176122665405</t>
   </si>
   <si>
     <t xml:space="preserve">13.8307476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7600374221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9155988693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7458963394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0428781509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8448896408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.54176902771</t>
+    <t xml:space="preserve">13.7600355148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.915599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7458982467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0428762435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8448905944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.541766166687</t>
   </si>
   <si>
     <t xml:space="preserve">14.2218475341797</t>
@@ -1622,19 +1622,19 @@
     <t xml:space="preserve">14.1782236099243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9891786575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2073078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4399766921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2654762268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4108905792236</t>
+    <t xml:space="preserve">13.9891805648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2073068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4399757385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2654752731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4108915328979</t>
   </si>
   <si>
     <t xml:space="preserve">14.4981422424316</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">14.4690570831299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3527240753174</t>
+    <t xml:space="preserve">14.3527231216431</t>
   </si>
   <si>
     <t xml:space="preserve">14.3381824493408</t>
@@ -1655,100 +1655,100 @@
     <t xml:space="preserve">14.3963489532471</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6871862411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4254350662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4836006164551</t>
+    <t xml:space="preserve">14.6871871948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4254312515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4835996627808</t>
   </si>
   <si>
     <t xml:space="preserve">14.6144781112671</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8326025009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9780197143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1234359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1961441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4142742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.450629234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3415641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2325029373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3052110671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.268856048584</t>
+    <t xml:space="preserve">14.8326015472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9780206680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1234369277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1961460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4142751693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4506273269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3415660858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2325038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3052091598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2688550949097</t>
   </si>
   <si>
     <t xml:space="preserve">15.6687526702881</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0507278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0870847702026</t>
+    <t xml:space="preserve">15.0507297515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.087082862854</t>
   </si>
   <si>
     <t xml:space="preserve">14.9416646957397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7235403060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0143728256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5781211853027</t>
+    <t xml:space="preserve">14.723539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0143737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5781221389771</t>
   </si>
   <si>
     <t xml:space="preserve">14.7598943710327</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6508293151855</t>
+    <t xml:space="preserve">14.6508283615112</t>
   </si>
   <si>
     <t xml:space="preserve">14.3672666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3236408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5272254943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.454517364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7962503433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9053115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.032299041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.359489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5049076080322</t>
+    <t xml:space="preserve">14.3236417770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5272235870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4545154571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7962484359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9053106307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0322971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3594875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.504903793335</t>
   </si>
   <si>
     <t xml:space="preserve">16.6139698028564</t>
@@ -1757,19 +1757,19 @@
     <t xml:space="preserve">16.5412616729736</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8320941925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6503257751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5776138305664</t>
+    <t xml:space="preserve">16.8320960998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6503219604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.577615737915</t>
   </si>
   <si>
     <t xml:space="preserve">16.8684501647949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7593841552734</t>
+    <t xml:space="preserve">16.7593860626221</t>
   </si>
   <si>
     <t xml:space="preserve">17.0502223968506</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">17.086576461792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4864730834961</t>
+    <t xml:space="preserve">17.4864749908447</t>
   </si>
   <si>
     <t xml:space="preserve">17.4137649536133</t>
@@ -1790,37 +1790,37 @@
     <t xml:space="preserve">17.5228290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8136653900146</t>
+    <t xml:space="preserve">17.813663482666</t>
   </si>
   <si>
     <t xml:space="preserve">17.7409572601318</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7046012878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6682472229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0681476593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9227294921875</t>
+    <t xml:space="preserve">17.6318950653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7046031951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6682453155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0681457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9227256774902</t>
   </si>
   <si>
     <t xml:space="preserve">18.1044998168945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8500194549561</t>
+    <t xml:space="preserve">17.8500175476074</t>
   </si>
   <si>
     <t xml:space="preserve">17.9590816497803</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1772079467773</t>
+    <t xml:space="preserve">18.177209854126</t>
   </si>
   <si>
     <t xml:space="preserve">18.0317897796631</t>
@@ -1829,25 +1829,25 @@
     <t xml:space="preserve">18.2862739562988</t>
   </si>
   <si>
-    <t xml:space="preserve">18.358980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4680461883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5771083831787</t>
+    <t xml:space="preserve">18.3589839935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4680423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5771064758301</t>
   </si>
   <si>
     <t xml:space="preserve">17.9954395294189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5591831207275</t>
+    <t xml:space="preserve">17.5591850280762</t>
   </si>
   <si>
     <t xml:space="preserve">17.5955390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4501190185547</t>
+    <t xml:space="preserve">17.4501209259033</t>
   </si>
   <si>
     <t xml:space="preserve">18.2499179840088</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">18.395336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2135639190674</t>
+    <t xml:space="preserve">18.2135620117188</t>
   </si>
   <si>
     <t xml:space="preserve">18.3226261138916</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6134643554688</t>
+    <t xml:space="preserve">18.6134624481201</t>
   </si>
   <si>
     <t xml:space="preserve">18.6861705780029</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">18.8315868377686</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1951313018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9770050048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0860710144043</t>
+    <t xml:space="preserve">19.1951332092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9770069122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0860691070557</t>
   </si>
   <si>
     <t xml:space="preserve">19.2678413391113</t>
@@ -1886,52 +1886,52 @@
     <t xml:space="preserve">19.1224231719971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3041954040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4132595062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4496116638184</t>
+    <t xml:space="preserve">19.3041973114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4132614135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.449613571167</t>
   </si>
   <si>
     <t xml:space="preserve">16.9048042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7230358123779</t>
+    <t xml:space="preserve">16.7230319976807</t>
   </si>
   <si>
     <t xml:space="preserve">16.4321975708008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7957420349121</t>
+    <t xml:space="preserve">16.7957401275635</t>
   </si>
   <si>
     <t xml:space="preserve">19.2314872741699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9775123596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3047027587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3774147033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7952346801758</t>
+    <t xml:space="preserve">16.9775161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3046989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3774127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7952365875244</t>
   </si>
   <si>
     <t xml:space="preserve">18.5407543182373</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8679428100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9042949676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8495140075684</t>
+    <t xml:space="preserve">18.8679447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9042987823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8495121002197</t>
   </si>
   <si>
     <t xml:space="preserve">19.4213848114014</t>
@@ -1940,25 +1940,25 @@
     <t xml:space="preserve">19.7327499389648</t>
   </si>
   <si>
-    <t xml:space="preserve">20.394401550293</t>
+    <t xml:space="preserve">20.3943996429443</t>
   </si>
   <si>
     <t xml:space="preserve">19.8105926513672</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6549091339111</t>
+    <t xml:space="preserve">19.6549110412598</t>
   </si>
   <si>
     <t xml:space="preserve">20.3554801940918</t>
   </si>
   <si>
-    <t xml:space="preserve">20.121955871582</t>
+    <t xml:space="preserve">20.1219577789307</t>
   </si>
   <si>
     <t xml:space="preserve">19.9273548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4603061676025</t>
+    <t xml:space="preserve">19.4603080749512</t>
   </si>
   <si>
     <t xml:space="preserve">19.3435440063477</t>
@@ -1967,25 +1967,25 @@
     <t xml:space="preserve">19.3046226501465</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9662742614746</t>
+    <t xml:space="preserve">19.966272354126</t>
   </si>
   <si>
     <t xml:space="preserve">19.2657051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">19.771671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7597351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1608753204346</t>
+    <t xml:space="preserve">19.7716693878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7597370147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1608772277832</t>
   </si>
   <si>
     <t xml:space="preserve">20.0441150665283</t>
   </si>
   <si>
-    <t xml:space="preserve">21.172815322876</t>
+    <t xml:space="preserve">21.1728134155273</t>
   </si>
   <si>
     <t xml:space="preserve">21.0560493469238</t>
@@ -1994,37 +1994,37 @@
     <t xml:space="preserve">20.9392890930176</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2895755767822</t>
+    <t xml:space="preserve">21.2895736694336</t>
   </si>
   <si>
     <t xml:space="preserve">21.0171318054199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7836074829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7057647705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0949726104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.445255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7566242218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9512271881104</t>
+    <t xml:space="preserve">20.7836093902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7057666778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.094970703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4452590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7566223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9512252807617</t>
   </si>
   <si>
     <t xml:space="preserve">21.6009387969971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7955436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0290641784668</t>
+    <t xml:space="preserve">21.7955417633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0290660858154</t>
   </si>
   <si>
     <t xml:space="preserve">22.0679874420166</t>
@@ -2033,13 +2033,13 @@
     <t xml:space="preserve">22.5350360870361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5739555358887</t>
+    <t xml:space="preserve">22.57395362854</t>
   </si>
   <si>
     <t xml:space="preserve">22.651798248291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7685565948486</t>
+    <t xml:space="preserve">22.7685604095459</t>
   </si>
   <si>
     <t xml:space="preserve">22.8074779510498</t>
@@ -2048,16 +2048,16 @@
     <t xml:space="preserve">22.7296390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3404331207275</t>
+    <t xml:space="preserve">22.3404312133789</t>
   </si>
   <si>
     <t xml:space="preserve">22.2625904083252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5080509185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.97509765625</t>
+    <t xml:space="preserve">23.5080528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9750957489014</t>
   </si>
   <si>
     <t xml:space="preserve">24.4032249450684</t>
@@ -2069,22 +2069,22 @@
     <t xml:space="preserve">24.7145900726318</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5199871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2983989715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7924308776855</t>
+    <t xml:space="preserve">24.5199851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.298397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7924327850342</t>
   </si>
   <si>
     <t xml:space="preserve">25.1427154541016</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7535095214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6367473602295</t>
+    <t xml:space="preserve">24.7535076141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6367454528809</t>
   </si>
   <si>
     <t xml:space="preserve">24.1697006225586</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">23.0799236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7026519775391</t>
+    <t xml:space="preserve">23.7026538848877</t>
   </si>
   <si>
     <t xml:space="preserve">24.0529384613037</t>
@@ -2111,22 +2111,22 @@
     <t xml:space="preserve">23.1577644348145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8583354949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7415733337402</t>
+    <t xml:space="preserve">23.8583335876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7415752410889</t>
   </si>
   <si>
     <t xml:space="preserve">23.8194160461426</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6637325286865</t>
+    <t xml:space="preserve">23.6637306213379</t>
   </si>
   <si>
     <t xml:space="preserve">23.4302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0918579101562</t>
+    <t xml:space="preserve">24.0918598175049</t>
   </si>
   <si>
     <t xml:space="preserve">23.3912887573242</t>
@@ -2138,28 +2138,28 @@
     <t xml:space="preserve">23.0410022735596</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0020809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1188449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6248111724854</t>
+    <t xml:space="preserve">23.0020790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1188430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.624813079834</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128749847412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1069068908691</t>
+    <t xml:space="preserve">22.1069107055664</t>
   </si>
   <si>
     <t xml:space="preserve">22.1847496032715</t>
   </si>
   <si>
-    <t xml:space="preserve">22.496114730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3015098571777</t>
+    <t xml:space="preserve">22.4961128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3015117645264</t>
   </si>
   <si>
     <t xml:space="preserve">22.6907157897949</t>
@@ -2168,22 +2168,22 @@
     <t xml:space="preserve">22.3793506622314</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9631595611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2356071472168</t>
+    <t xml:space="preserve">22.9631614685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">22.9242401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">22.223669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4182720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9123058319092</t>
+    <t xml:space="preserve">22.2236728668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4182739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9123039245605</t>
   </si>
   <si>
     <t xml:space="preserve">21.4841766357422</t>
@@ -2198,13 +2198,13 @@
     <t xml:space="preserve">21.717700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6398582458496</t>
+    <t xml:space="preserve">21.6398620605469</t>
   </si>
   <si>
     <t xml:space="preserve">21.2506542205811</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5620193481445</t>
+    <t xml:space="preserve">21.5620212554932</t>
   </si>
   <si>
     <t xml:space="preserve">21.8344631195068</t>
@@ -2222,16 +2222,16 @@
     <t xml:space="preserve">22.8464012145996</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8853206634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4571952819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3284950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2117347717285</t>
+    <t xml:space="preserve">22.8853187561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4571914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2117328643799</t>
   </si>
   <si>
     <t xml:space="preserve">21.3674163818359</t>
@@ -2240,19 +2240,19 @@
     <t xml:space="preserve">20.9782104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6279258728027</t>
+    <t xml:space="preserve">20.6279239654541</t>
   </si>
   <si>
     <t xml:space="preserve">21.873384475708</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4407329559326</t>
+    <t xml:space="preserve">23.440731048584</t>
   </si>
   <si>
     <t xml:space="preserve">22.88356590271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7243747711182</t>
+    <t xml:space="preserve">22.7243766784668</t>
   </si>
   <si>
     <t xml:space="preserve">22.8039703369141</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">22.7641754150391</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0427551269531</t>
+    <t xml:space="preserve">23.0427570343018</t>
   </si>
   <si>
     <t xml:space="preserve">23.2417449951172</t>
@@ -2285,25 +2285,25 @@
     <t xml:space="preserve">23.9580993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0774917602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4356689453125</t>
+    <t xml:space="preserve">24.0774898529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4356708526611</t>
   </si>
   <si>
     <t xml:space="preserve">24.3162746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3560733795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7938461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1570854187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6744537353516</t>
+    <t xml:space="preserve">24.3560752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7938442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1570873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6744518280029</t>
   </si>
   <si>
     <t xml:space="preserve">24.913236618042</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">24.555061340332</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7540493011475</t>
+    <t xml:space="preserve">24.7540473937988</t>
   </si>
   <si>
     <t xml:space="preserve">24.2764778137207</t>
@@ -2321,34 +2321,34 @@
     <t xml:space="preserve">24.1172885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5152645111084</t>
+    <t xml:space="preserve">24.5152626037598</t>
   </si>
   <si>
     <t xml:space="preserve">24.4754657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2366790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3958702087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7142505645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6346569061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1968822479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6295928955078</t>
+    <t xml:space="preserve">24.2366828918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3958721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7142486572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6346549987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1968841552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6295948028564</t>
   </si>
   <si>
     <t xml:space="preserve">25.5102005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1520233154297</t>
+    <t xml:space="preserve">25.1520252227783</t>
   </si>
   <si>
     <t xml:space="preserve">25.3510131835938</t>
@@ -2357,40 +2357,40 @@
     <t xml:space="preserve">25.4704036712646</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6693897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3908100128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1918201446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0326309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2714176177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8336448669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9530372619629</t>
+    <t xml:space="preserve">25.6693916320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3908081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.191822052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0326290130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2714157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8336429595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9530353546143</t>
   </si>
   <si>
     <t xml:space="preserve">25.8683795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0724277496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7591114044189</t>
+    <t xml:space="preserve">25.0724296569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7591094970703</t>
   </si>
   <si>
     <t xml:space="preserve">23.4805278778076</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8785037994385</t>
+    <t xml:space="preserve">23.8785057067871</t>
   </si>
   <si>
     <t xml:space="preserve">23.6397190093994</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">25.430606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3112125396729</t>
+    <t xml:space="preserve">25.3112144470215</t>
   </si>
   <si>
     <t xml:space="preserve">25.2316188812256</t>
@@ -2420,25 +2420,25 @@
     <t xml:space="preserve">26.2663536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0275707244873</t>
+    <t xml:space="preserve">26.0275688171387</t>
   </si>
   <si>
     <t xml:space="preserve">25.7887859344482</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5499973297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5897960662842</t>
+    <t xml:space="preserve">25.5499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5897979736328</t>
   </si>
   <si>
     <t xml:space="preserve">25.9479732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1071643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7489833831787</t>
+    <t xml:space="preserve">26.1071624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7489852905273</t>
   </si>
   <si>
     <t xml:space="preserve">24.8734397888184</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">24.0376949310303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3264007568359</t>
+    <t xml:space="preserve">22.3263988494873</t>
   </si>
   <si>
     <t xml:space="preserve">22.3661975860596</t>
@@ -2456,10 +2456,10 @@
     <t xml:space="preserve">23.0825538635254</t>
   </si>
   <si>
-    <t xml:space="preserve">22.923360824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3213386535645</t>
+    <t xml:space="preserve">22.9233646392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3213367462158</t>
   </si>
   <si>
     <t xml:space="preserve">23.5999202728271</t>
@@ -2471,31 +2471,31 @@
     <t xml:space="preserve">23.4009323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5601234436035</t>
+    <t xml:space="preserve">23.5601215362549</t>
   </si>
   <si>
     <t xml:space="preserve">22.4855899810791</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8387069702148</t>
+    <t xml:space="preserve">23.8387050628662</t>
   </si>
   <si>
     <t xml:space="preserve">23.997896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7193126678467</t>
+    <t xml:space="preserve">23.719310760498</t>
   </si>
   <si>
     <t xml:space="preserve">23.8264102935791</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5692920684814</t>
+    <t xml:space="preserve">23.5692901611328</t>
   </si>
   <si>
     <t xml:space="preserve">24.1263828277588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9549713134766</t>
+    <t xml:space="preserve">23.9549694061279</t>
   </si>
   <si>
     <t xml:space="preserve">24.4692077636719</t>
@@ -2504,13 +2504,13 @@
     <t xml:space="preserve">24.4263553619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1692371368408</t>
+    <t xml:space="preserve">24.1692352294922</t>
   </si>
   <si>
     <t xml:space="preserve">24.2120895385742</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7835578918457</t>
+    <t xml:space="preserve">23.7835559844971</t>
   </si>
   <si>
     <t xml:space="preserve">24.340648651123</t>
@@ -2525,13 +2525,13 @@
     <t xml:space="preserve">23.5264377593994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9978218078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9121150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8692626953125</t>
+    <t xml:space="preserve">23.99782371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9121170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8692646026611</t>
   </si>
   <si>
     <t xml:space="preserve">23.7407035827637</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">23.6549968719482</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9693450927734</t>
+    <t xml:space="preserve">22.9693431854248</t>
   </si>
   <si>
     <t xml:space="preserve">22.8836402893066</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">22.5836658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9264907836914</t>
+    <t xml:space="preserve">22.92649269104</t>
   </si>
   <si>
     <t xml:space="preserve">23.1407585144043</t>
@@ -2558,10 +2558,10 @@
     <t xml:space="preserve">22.8407859802246</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7550792694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6693725585938</t>
+    <t xml:space="preserve">22.7550773620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6693744659424</t>
   </si>
   <si>
     <t xml:space="preserve">23.0550518035889</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">23.3550243377686</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0121994018555</t>
+    <t xml:space="preserve">23.0121974945068</t>
   </si>
   <si>
     <t xml:space="preserve">23.3121719360352</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">22.7979316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4551048278809</t>
+    <t xml:space="preserve">22.4551086425781</t>
   </si>
   <si>
     <t xml:space="preserve">22.4979591369629</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">22.6265182495117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6978511810303</t>
+    <t xml:space="preserve">23.6978492736816</t>
   </si>
   <si>
     <t xml:space="preserve">22.5408115386963</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2693157196045</t>
+    <t xml:space="preserve">23.2693176269531</t>
   </si>
   <si>
     <t xml:space="preserve">22.2836933135986</t>
@@ -2633,16 +2633,16 @@
     <t xml:space="preserve">20.826681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9267635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1410312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9980945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1266555786133</t>
+    <t xml:space="preserve">19.9267616271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1410293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9980964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1266536712646</t>
   </si>
   <si>
     <t xml:space="preserve">20.5267105102539</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">20.6552696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3124446868896</t>
+    <t xml:space="preserve">20.312442779541</t>
   </si>
   <si>
     <t xml:space="preserve">20.4410037994385</t>
@@ -2660,19 +2660,19 @@
     <t xml:space="preserve">20.6981220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5980434417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3837738037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5123348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3409214019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.026575088501</t>
+    <t xml:space="preserve">21.5980415344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3837757110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.512336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3409194946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0265731811523</t>
   </si>
   <si>
     <t xml:space="preserve">22.1122798919678</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">22.1551342010498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2408409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6837463378906</t>
+    <t xml:space="preserve">22.2408390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6837482452393</t>
   </si>
   <si>
     <t xml:space="preserve">21.7266006469727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8980121612549</t>
+    <t xml:space="preserve">21.8980140686035</t>
   </si>
   <si>
     <t xml:space="preserve">21.7694530487061</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.0694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9837188720703</t>
+    <t xml:space="preserve">21.9837207794189</t>
   </si>
   <si>
     <t xml:space="preserve">21.8551597595215</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">21.0838012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9408683776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5551872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0409469604492</t>
+    <t xml:space="preserve">21.9408664703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5551853179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0409488677979</t>
   </si>
   <si>
     <t xml:space="preserve">20.912389755249</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">20.7409763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1838836669922</t>
+    <t xml:space="preserve">20.1838817596436</t>
   </si>
   <si>
     <t xml:space="preserve">20.3552951812744</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">22.0611591339111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1051940917969</t>
+    <t xml:space="preserve">22.1051959991455</t>
   </si>
   <si>
     <t xml:space="preserve">22.017126083374</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">21.664852142334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5767822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4887142181396</t>
+    <t xml:space="preserve">21.5767841339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4887161254883</t>
   </si>
   <si>
     <t xml:space="preserve">21.9290561676025</t>
@@ -2792,22 +2792,22 @@
     <t xml:space="preserve">21.8409881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7088871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4006443023682</t>
+    <t xml:space="preserve">21.7088851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4006462097168</t>
   </si>
   <si>
     <t xml:space="preserve">21.7969551086426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9730911254883</t>
+    <t xml:space="preserve">21.9730930328369</t>
   </si>
   <si>
     <t xml:space="preserve">21.7529201507568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.501501083374</t>
+    <t xml:space="preserve">22.5015029907227</t>
   </si>
   <si>
     <t xml:space="preserve">22.2372970581055</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">22.3253650665283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5455379486084</t>
+    <t xml:space="preserve">22.5455360412598</t>
   </si>
   <si>
     <t xml:space="preserve">22.149227142334</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">21.0483722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3566131591797</t>
+    <t xml:space="preserve">21.3566112518311</t>
   </si>
   <si>
     <t xml:space="preserve">21.6208171844482</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">21.4446811676025</t>
   </si>
   <si>
-    <t xml:space="preserve">21.532751083374</t>
+    <t xml:space="preserve">21.5327491760254</t>
   </si>
   <si>
     <t xml:space="preserve">21.0043392181396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8722362518311</t>
+    <t xml:space="preserve">20.8722343444824</t>
   </si>
   <si>
     <t xml:space="preserve">20.6960983276367</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">20.2557563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3878574371338</t>
+    <t xml:space="preserve">20.3878593444824</t>
   </si>
   <si>
     <t xml:space="preserve">20.2997894287109</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">20.7841682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9603042602539</t>
+    <t xml:space="preserve">20.9603023529053</t>
   </si>
   <si>
     <t xml:space="preserve">20.7401313781738</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">21.1804752349854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6336078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4574699401855</t>
+    <t xml:space="preserve">22.6336059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4574680328369</t>
   </si>
   <si>
     <t xml:space="preserve">22.5895709991455</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">24.3949756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">24.30690574646</t>
+    <t xml:space="preserve">24.3069076538086</t>
   </si>
   <si>
     <t xml:space="preserve">24.1307697296143</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">24.3509407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4390106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5711116790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6591796875</t>
+    <t xml:space="preserve">24.4390087127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5711135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6591815948486</t>
   </si>
   <si>
     <t xml:space="preserve">24.7032146453857</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">24.0867366790771</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2188396453857</t>
+    <t xml:space="preserve">24.2188377380371</t>
   </si>
   <si>
     <t xml:space="preserve">24.1748046875</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">23.9546337127686</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7600364685059</t>
+    <t xml:space="preserve">25.7600383758545</t>
   </si>
   <si>
     <t xml:space="preserve">25.4077625274658</t>
@@ -2987,19 +2987,19 @@
     <t xml:space="preserve">26.1123104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1563453674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4645862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5910167694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3708457946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8992595672607</t>
+    <t xml:space="preserve">26.1563472747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4645843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5910148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3708438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8992576599121</t>
   </si>
   <si>
     <t xml:space="preserve">30.0313587188721</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">29.5029487609863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7671546936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2827758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0753974914551</t>
+    <t xml:space="preserve">29.7671527862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2827777862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0753955841064</t>
   </si>
   <si>
     <t xml:space="preserve">29.7231216430664</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">30.471700668335</t>
   </si>
   <si>
-    <t xml:space="preserve">29.811185836792</t>
+    <t xml:space="preserve">29.8111877441406</t>
   </si>
   <si>
     <t xml:space="preserve">29.2387447357178</t>
@@ -3044,28 +3044,28 @@
     <t xml:space="preserve">28.7103309631348</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8424339294434</t>
+    <t xml:space="preserve">28.842435836792</t>
   </si>
   <si>
     <t xml:space="preserve">28.8864688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5469837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2955646514893</t>
+    <t xml:space="preserve">29.5469818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2955665588379</t>
   </si>
   <si>
     <t xml:space="preserve">30.7359104156494</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3836345672607</t>
+    <t xml:space="preserve">30.3836326599121</t>
   </si>
   <si>
     <t xml:space="preserve">29.9873237609863</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4276695251465</t>
+    <t xml:space="preserve">30.4276676177979</t>
   </si>
   <si>
     <t xml:space="preserve">29.4632396697998</t>
@@ -3459,9 +3459,6 @@
   </si>
   <si>
     <t xml:space="preserve">26.0499992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5499992370605</t>
   </si>
   <si>
     <t xml:space="preserve">26.1499996185303</t>
@@ -66120,7 +66117,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G2388" t="s">
-        <v>1149</v>
+        <v>804</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66146,7 +66143,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66172,7 +66169,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66198,7 +66195,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G2391" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66224,7 +66221,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66250,7 +66247,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66276,7 +66273,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66302,7 +66299,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66328,7 +66325,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G2396" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66354,7 +66351,7 @@
         <v>26.75</v>
       </c>
       <c r="G2397" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66380,7 +66377,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2398" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66406,7 +66403,7 @@
         <v>27</v>
       </c>
       <c r="G2399" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66432,7 +66429,7 @@
         <v>27</v>
       </c>
       <c r="G2400" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66458,7 +66455,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66484,7 +66481,7 @@
         <v>26.25</v>
       </c>
       <c r="G2402" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66510,7 +66507,7 @@
         <v>25.5</v>
       </c>
       <c r="G2403" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66536,7 +66533,7 @@
         <v>25.25</v>
       </c>
       <c r="G2404" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66588,7 +66585,7 @@
         <v>25.25</v>
       </c>
       <c r="G2406" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66640,7 +66637,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G2408" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66666,7 +66663,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G2409" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66692,7 +66689,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G2410" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66718,7 +66715,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2411" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66744,7 +66741,7 @@
         <v>25.5</v>
       </c>
       <c r="G2412" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66796,7 +66793,7 @@
         <v>26</v>
       </c>
       <c r="G2414" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66822,7 +66819,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2415" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66848,7 +66845,7 @@
         <v>27</v>
       </c>
       <c r="G2416" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66874,7 +66871,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66900,7 +66897,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G2418" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66926,7 +66923,7 @@
         <v>27.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66952,7 +66949,7 @@
         <v>27.5</v>
       </c>
       <c r="G2420" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66978,7 +66975,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67004,7 +67001,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2422" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67030,7 +67027,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G2423" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67056,7 +67053,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2424" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67082,7 +67079,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G2425" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67108,7 +67105,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2426" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67134,7 +67131,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2427" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67160,7 +67157,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2428" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67186,7 +67183,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2429" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67212,7 +67209,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67238,7 +67235,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67264,7 +67261,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2432" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67290,7 +67287,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67316,7 +67313,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G2434" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67342,7 +67339,7 @@
         <v>29</v>
       </c>
       <c r="G2435" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67368,7 +67365,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G2436" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67394,7 +67391,7 @@
         <v>28.25</v>
       </c>
       <c r="G2437" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67420,7 +67417,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G2438" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67446,7 +67443,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67472,7 +67469,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2440" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67498,7 +67495,7 @@
         <v>27</v>
       </c>
       <c r="G2441" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67524,7 +67521,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2442" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67550,7 +67547,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G2443" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67576,7 +67573,7 @@
         <v>27.25</v>
       </c>
       <c r="G2444" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67602,7 +67599,7 @@
         <v>27.25</v>
       </c>
       <c r="G2445" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67628,7 +67625,7 @@
         <v>27.25</v>
       </c>
       <c r="G2446" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67654,7 +67651,7 @@
         <v>27.25</v>
       </c>
       <c r="G2447" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67680,7 +67677,7 @@
         <v>27.5</v>
       </c>
       <c r="G2448" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67706,7 +67703,7 @@
         <v>27.75</v>
       </c>
       <c r="G2449" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67732,7 +67729,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G2450" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67758,7 +67755,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G2451" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67784,7 +67781,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G2452" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67810,7 +67807,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G2453" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67836,7 +67833,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G2454" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67862,7 +67859,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G2455" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67888,7 +67885,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67914,7 +67911,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67940,7 +67937,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G2458" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67966,7 +67963,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G2459" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67992,7 +67989,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G2460" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68018,7 +68015,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2461" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68044,7 +68041,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68070,7 +68067,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68096,7 +68093,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68122,7 +68119,7 @@
         <v>28.75</v>
       </c>
       <c r="G2465" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68148,7 +68145,7 @@
         <v>29</v>
       </c>
       <c r="G2466" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68174,7 +68171,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68200,7 +68197,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G2468" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68226,7 +68223,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68252,7 +68249,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68278,7 +68275,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68304,7 +68301,7 @@
         <v>29.9500007629395</v>
       </c>
       <c r="G2472" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68330,7 +68327,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68356,7 +68353,7 @@
         <v>30</v>
       </c>
       <c r="G2474" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68382,7 +68379,7 @@
         <v>29.75</v>
       </c>
       <c r="G2475" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68408,7 +68405,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G2476" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68434,7 +68431,7 @@
         <v>30</v>
       </c>
       <c r="G2477" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68460,7 +68457,7 @@
         <v>30.5</v>
       </c>
       <c r="G2478" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68486,7 +68483,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G2479" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68512,7 +68509,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68538,7 +68535,7 @@
         <v>31.25</v>
       </c>
       <c r="G2481" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68564,7 +68561,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G2482" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68590,7 +68587,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68616,7 +68613,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68642,7 +68639,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G2485" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68668,7 +68665,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G2486" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68694,7 +68691,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G2487" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68720,7 +68717,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2488" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68746,7 +68743,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2489" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68772,7 +68769,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G2490" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68798,7 +68795,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G2491" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68824,7 +68821,7 @@
         <v>32.5</v>
       </c>
       <c r="G2492" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68850,7 +68847,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G2493" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68876,7 +68873,7 @@
         <v>33</v>
       </c>
       <c r="G2494" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68902,7 +68899,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G2495" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68928,7 +68925,7 @@
         <v>33</v>
       </c>
       <c r="G2496" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68954,7 +68951,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G2497" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68980,7 +68977,7 @@
         <v>33.5</v>
       </c>
       <c r="G2498" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69006,7 +69003,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G2499" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69032,7 +69029,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G2500" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69058,7 +69055,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G2501" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69084,7 +69081,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G2502" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69110,7 +69107,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G2503" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69136,7 +69133,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2504" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69144,25 +69141,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6937962963</v>
+        <v>45967.6912268518</v>
       </c>
       <c r="B2505" t="n">
-        <v>25887</v>
+        <v>32494</v>
       </c>
       <c r="C2505" t="n">
-        <v>32.3499984741211</v>
+        <v>32.5999984741211</v>
       </c>
       <c r="D2505" t="n">
-        <v>31.75</v>
+        <v>31.8999996185303</v>
       </c>
       <c r="E2505" t="n">
-        <v>32.0999984741211</v>
+        <v>32.2999992370605</v>
       </c>
       <c r="F2505" t="n">
         <v>32.1500015258789</v>
       </c>
       <c r="G2505" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -38,88 +38,88 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8067140579224</t>
+    <t xml:space="preserve">13.806713104248</t>
   </si>
   <si>
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577459335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.957332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3883295059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.889612197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8527975082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9532079696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6184988021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.384204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8821401596069</t>
+    <t xml:space="preserve">14.057746887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9573354721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.388331413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896150588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8527956008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9532070159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6185007095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846162796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3842039108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8821420669556</t>
   </si>
   <si>
     <t xml:space="preserve">11.7348699569702</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2127246856689</t>
+    <t xml:space="preserve">11.2127275466919</t>
   </si>
   <si>
     <t xml:space="preserve">10.7307462692261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2294607162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2194204330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2461948394775</t>
+    <t xml:space="preserve">11.2294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2194194793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2461967468262</t>
   </si>
   <si>
     <t xml:space="preserve">10.9148349761963</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1323947906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6143741607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6813182830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5474328994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3466081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3131370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.329873085022</t>
+    <t xml:space="preserve">11.1323938369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6143751144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6813173294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5474338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3466100692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.313138961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3298721313477</t>
   </si>
   <si>
     <t xml:space="preserve">10.8947525024414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8780174255371</t>
+    <t xml:space="preserve">10.8780183792114</t>
   </si>
   <si>
     <t xml:space="preserve">11.045371055603</t>
@@ -128,127 +128,127 @@
     <t xml:space="preserve">10.4261608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4094257354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7080936431885</t>
+    <t xml:space="preserve">10.4094266891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7080945968628</t>
   </si>
   <si>
     <t xml:space="preserve">11.7147884368896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0494947433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7482595443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7449131011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2135057449341</t>
+    <t xml:space="preserve">12.0494966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7482566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7449102401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2135028839111</t>
   </si>
   <si>
     <t xml:space="preserve">12.2168493270874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3674697875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7189111709595</t>
+    <t xml:space="preserve">12.3674716949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7189130783081</t>
   </si>
   <si>
     <t xml:space="preserve">12.8293676376343</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0201501846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2209730148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3849840164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3347749710083</t>
+    <t xml:space="preserve">13.0201511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2209739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3849830627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870914459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3347759246826</t>
   </si>
   <si>
     <t xml:space="preserve">13.3146934509277</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0569677352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109317779541</t>
+    <t xml:space="preserve">13.0569696426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109336853027</t>
   </si>
   <si>
     <t xml:space="preserve">12.8661842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1306056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2879161834717</t>
+    <t xml:space="preserve">13.1306047439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2879180908203</t>
   </si>
   <si>
     <t xml:space="preserve">12.8260192871094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9833297729492</t>
+    <t xml:space="preserve">12.9833316802979</t>
   </si>
   <si>
     <t xml:space="preserve">12.903003692627</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2377109527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1674213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1138696670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971345901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5047006607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8092842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.886266708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7055234909058</t>
+    <t xml:space="preserve">13.2377090454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1674222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1138677597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971326828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5046997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8092832565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8862657546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7055253982544</t>
   </si>
   <si>
     <t xml:space="preserve">12.7222595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9163885116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0301895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327159881592</t>
+    <t xml:space="preserve">12.916392326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0301923751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327131271362</t>
   </si>
   <si>
     <t xml:space="preserve">12.6318883895874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7021770477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8695316314697</t>
+    <t xml:space="preserve">12.7021760940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8695306777954</t>
   </si>
   <si>
     <t xml:space="preserve">12.5582513809204</t>
@@ -260,109 +260,109 @@
     <t xml:space="preserve">12.8360595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958955764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5348224639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7791595458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7691192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7865657806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.502420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6512594223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7527379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5836048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4990377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5700731277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159521102905</t>
+    <t xml:space="preserve">12.8494482040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958946228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5348234176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7791585922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.769118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.786566734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5024185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6512584686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.752739906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5836067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4990386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5700740814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159511566162</t>
   </si>
   <si>
     <t xml:space="preserve">12.2791624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0660514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776809692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1641502380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1709184646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1100292205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1269407272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9814853668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7459754943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580209732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231382369995</t>
+    <t xml:space="preserve">12.0660524368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776819229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1641511917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.170916557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1100282669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1269426345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9814872741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7459735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231391906738</t>
   </si>
   <si>
     <t xml:space="preserve">11.697340965271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7785234451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2406759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8212251663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554698944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0613956451416</t>
+    <t xml:space="preserve">11.7785243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2406778335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8212242126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554708480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0613946914673</t>
   </si>
   <si>
     <t xml:space="preserve">11.196702003479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4064302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5248231887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6656188964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1886606216431</t>
+    <t xml:space="preserve">11.4064283370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5248222351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6656198501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1886615753174</t>
   </si>
   <si>
     <t xml:space="preserve">10.5878171920776</t>
@@ -371,46 +371,46 @@
     <t xml:space="preserve">10.6825332641602</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8394117355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0199708938599</t>
+    <t xml:space="preserve">11.8394136428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0199728012085</t>
   </si>
   <si>
     <t xml:space="preserve">13.3616228103638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0233545303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1924886703491</t>
+    <t xml:space="preserve">13.0233535766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1924877166748</t>
   </si>
   <si>
     <t xml:space="preserve">13.4969310760498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4698696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307569503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4800176620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2939682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548564910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0740976333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368843078613</t>
+    <t xml:space="preserve">13.4698657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307598114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.480019569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2939691543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108806610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0740957260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368852615356</t>
   </si>
   <si>
     <t xml:space="preserve">12.9489336013794</t>
@@ -419,61 +419,61 @@
     <t xml:space="preserve">12.9827613830566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910091400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0707120895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9962911605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8576030731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1248359680176</t>
+    <t xml:space="preserve">13.0910081863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0707101821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9962892532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8576021194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113052368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1248331069946</t>
   </si>
   <si>
     <t xml:space="preserve">13.1823396682739</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0605640411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857252120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4123630523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5679683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4157476425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5138454437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.706657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8352003097534</t>
+    <t xml:space="preserve">13.060564994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857233047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4123649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5679702758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4157466888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5138463973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7066564559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8352012634277</t>
   </si>
   <si>
     <t xml:space="preserve">14.2106761932373</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4576168060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7552928924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838300704956</t>
+    <t xml:space="preserve">14.4576139450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7552900314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838338851929</t>
   </si>
   <si>
     <t xml:space="preserve">15.01575756073</t>
@@ -485,25 +485,25 @@
     <t xml:space="preserve">15.3303480148315</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6652326583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2897596359253</t>
+    <t xml:space="preserve">15.6652336120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2897567749023</t>
   </si>
   <si>
     <t xml:space="preserve">14.8297090530396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6842565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7722043991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.951488494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7485237121582</t>
+    <t xml:space="preserve">14.6842575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7722024917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9514875411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7485275268555</t>
   </si>
   <si>
     <t xml:space="preserve">14.7180814743042</t>
@@ -512,37 +512,37 @@
     <t xml:space="preserve">14.8770666122437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992639541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751634597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.90074634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2018051147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988460540771</t>
+    <t xml:space="preserve">14.7992658615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9007472991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2018041610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939809799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330936431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988441467285</t>
   </si>
   <si>
     <t xml:space="preserve">14.9142770767212</t>
   </si>
   <si>
-    <t xml:space="preserve">14.927809715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.738377571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7248468399048</t>
+    <t xml:space="preserve">14.9278106689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7383766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7248449325562</t>
   </si>
   <si>
     <t xml:space="preserve">14.5421829223633</t>
@@ -551,70 +551,70 @@
     <t xml:space="preserve">14.4440841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0529670715332</t>
+    <t xml:space="preserve">15.0529680252075</t>
   </si>
   <si>
     <t xml:space="preserve">15.1442995071411</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1104736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9548692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0901775360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2187204360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7823543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6166009902954</t>
+    <t xml:space="preserve">15.1104717254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.954870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0901784896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2187213897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7823514938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707220077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6166000366211</t>
   </si>
   <si>
     <t xml:space="preserve">14.3764314651489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1599388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2546510696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0415420532227</t>
+    <t xml:space="preserve">14.1599378585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2546548843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0415439605713</t>
   </si>
   <si>
     <t xml:space="preserve">14.1125793457031</t>
   </si>
   <si>
-    <t xml:space="preserve">14.038161277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1430225372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527517318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2072973251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3561334609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373197555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730478286743</t>
+    <t xml:space="preserve">14.0381622314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1430253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903848648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527498245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2072954177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3561353683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373178482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730497360229</t>
   </si>
   <si>
     <t xml:space="preserve">14.3087768554688</t>
@@ -623,160 +623,160 @@
     <t xml:space="preserve">14.2411222457886</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3392190933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2512712478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464080810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058149337769</t>
+    <t xml:space="preserve">14.3392210006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2512693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.146409034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058168411255</t>
   </si>
   <si>
     <t xml:space="preserve">14.1193437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2275905609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2715673446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.149790763855</t>
+    <t xml:space="preserve">14.227593421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2715663909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1497898101807</t>
   </si>
   <si>
     <t xml:space="preserve">14.0753707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0719881057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667032241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4779109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267499923706</t>
+    <t xml:space="preserve">14.0719890594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749490737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667013168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4779100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267509460449</t>
   </si>
   <si>
     <t xml:space="preserve">14.7519092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.816180229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1037082672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0834121704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882762908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172370910645</t>
+    <t xml:space="preserve">14.8161792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1037101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0834131240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172399520874</t>
   </si>
   <si>
     <t xml:space="preserve">15.1544485092163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2999048233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758043289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3574094772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3912391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893350601196</t>
+    <t xml:space="preserve">15.2999057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3574123382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3912372589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893360137939</t>
   </si>
   <si>
     <t xml:space="preserve">15.1713609695435</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1003255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.316819190979</t>
+    <t xml:space="preserve">15.100323677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946208953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3168182373047</t>
   </si>
   <si>
     <t xml:space="preserve">15.3134355545044</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4182987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4250640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.536693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6753826141357</t>
+    <t xml:space="preserve">15.4182996749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4250650405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366926193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6753845214844</t>
   </si>
   <si>
     <t xml:space="preserve">15.6449394226074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7295074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6618528366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6517028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.682147026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637531280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081516265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415557861328</t>
+    <t xml:space="preserve">15.7295055389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6618518829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6517057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6821479797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637540817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081506729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415567398071</t>
   </si>
   <si>
     <t xml:space="preserve">15.7024440765381</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5333099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584711074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.458890914917</t>
+    <t xml:space="preserve">15.5333080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584672927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588928222656</t>
   </si>
   <si>
     <t xml:space="preserve">15.5874347686768</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6550874710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227382659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3350067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0339469909668</t>
+    <t xml:space="preserve">15.655086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227411270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3350105285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0339488983154</t>
   </si>
   <si>
     <t xml:space="preserve">16.4060440063477</t>
@@ -785,103 +785,103 @@
     <t xml:space="preserve">16.4026622772217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4195728302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6935729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0994930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9980144500732</t>
+    <t xml:space="preserve">16.4195747375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6935710906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0994968414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9980125427246</t>
   </si>
   <si>
     <t xml:space="preserve">17.1671504974365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4208488464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5392436981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6407279968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4039363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4885025024414</t>
+    <t xml:space="preserve">17.4208526611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5392456054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6407241821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.403938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4885063171387</t>
   </si>
   <si>
     <t xml:space="preserve">17.3531970977783</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3870239257812</t>
+    <t xml:space="preserve">17.3870258331299</t>
   </si>
   <si>
     <t xml:space="preserve">17.522331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4546775817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.877513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8098602294922</t>
+    <t xml:space="preserve">17.4546756744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8775157928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8098621368408</t>
   </si>
   <si>
     <t xml:space="preserve">17.7083778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7591190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6745510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.573070526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3362827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2009735107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2348022460938</t>
+    <t xml:space="preserve">17.7591209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6745529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730743408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3362846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2009754180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2348041534424</t>
   </si>
   <si>
     <t xml:space="preserve">17.2517166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2178897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3701095581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4560203552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7147541046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5767612457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.559513092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975059509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4698181152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6147117614746</t>
+    <t xml:space="preserve">17.2178916931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3701114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.456018447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7147560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5767650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5595149993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.469820022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.614709854126</t>
   </si>
   <si>
     <t xml:space="preserve">16.7729587554932</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">17.1662349700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1317386627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.993745803833</t>
+    <t xml:space="preserve">17.1317367553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9937477111816</t>
   </si>
   <si>
     <t xml:space="preserve">16.9868469238281</t>
@@ -905,28 +905,28 @@
     <t xml:space="preserve">16.9661483764648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.835054397583</t>
+    <t xml:space="preserve">16.8350524902344</t>
   </si>
   <si>
     <t xml:space="preserve">16.8488540649414</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8281555175781</t>
+    <t xml:space="preserve">16.8281536102295</t>
   </si>
   <si>
     <t xml:space="preserve">16.7591609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8695526123047</t>
+    <t xml:space="preserve">16.8695545196533</t>
   </si>
   <si>
     <t xml:space="preserve">16.9178504943848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9730472564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.938549041748</t>
+    <t xml:space="preserve">16.9730491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9385471343994</t>
   </si>
   <si>
     <t xml:space="preserve">17.152437210083</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">16.5935668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5659675598145</t>
+    <t xml:space="preserve">16.5659713745117</t>
   </si>
   <si>
     <t xml:space="preserve">16.5038738250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626556396484</t>
+    <t xml:space="preserve">16.8626537322998</t>
   </si>
   <si>
     <t xml:space="preserve">16.9040508270264</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">16.80055809021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8971538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5383720397949</t>
+    <t xml:space="preserve">16.8971500396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5383701324463</t>
   </si>
   <si>
     <t xml:space="preserve">16.5590705871582</t>
@@ -965,58 +965,58 @@
     <t xml:space="preserve">16.4900741577148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2416896820068</t>
+    <t xml:space="preserve">16.2416877746582</t>
   </si>
   <si>
     <t xml:space="preserve">16.303783416748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2485866546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1243934631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1864891052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1588935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5314693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2899875640869</t>
+    <t xml:space="preserve">16.2485847473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1243953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1864910125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1588916778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5314712524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2899856567383</t>
   </si>
   <si>
     <t xml:space="preserve">16.3175849914551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5452709197998</t>
+    <t xml:space="preserve">16.5452690124512</t>
   </si>
   <si>
     <t xml:space="preserve">16.3658790588379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4624767303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3313827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3520832061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6970634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3865814208984</t>
+    <t xml:space="preserve">16.462474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3313846588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3520812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6970615386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3865795135498</t>
   </si>
   <si>
     <t xml:space="preserve">16.4486770629883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5107746124268</t>
+    <t xml:space="preserve">16.5107727050781</t>
   </si>
   <si>
     <t xml:space="preserve">16.4210777282715</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">16.4969730377197</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5245723724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4003810882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4555740356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.358980178833</t>
+    <t xml:space="preserve">16.5245742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4003791809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4555778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3589782714844</t>
   </si>
   <si>
     <t xml:space="preserve">16.2830848693848</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">16.1795921325684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2071876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1933898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519947052002</t>
+    <t xml:space="preserve">16.2071895599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1933917999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519908905029</t>
   </si>
   <si>
     <t xml:space="preserve">15.9036073684692</t>
@@ -1067,76 +1067,76 @@
     <t xml:space="preserve">15.5586261749268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965305328369</t>
+    <t xml:space="preserve">15.496527671814</t>
   </si>
   <si>
     <t xml:space="preserve">15.9381046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7794170379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7656164169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7863111495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9795055389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9312028884888</t>
+    <t xml:space="preserve">15.7794132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7656135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7863121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9795036315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.931206703186</t>
   </si>
   <si>
     <t xml:space="preserve">15.703516960144</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6483211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8415098190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7518148422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691082000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8622064590454</t>
+    <t xml:space="preserve">15.6483221054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8415117263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7518157958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691091537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8622102737427</t>
   </si>
   <si>
     <t xml:space="preserve">16.0277976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8967056274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6276206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7173175811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310297012329</t>
+    <t xml:space="preserve">15.8967084884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6276216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7173166275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310287475586</t>
   </si>
   <si>
     <t xml:space="preserve">15.5034284591675</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4413290023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2481422424316</t>
+    <t xml:space="preserve">15.4413347244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.248143196106</t>
   </si>
   <si>
     <t xml:space="preserve">15.3171405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3309412002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2826404571533</t>
+    <t xml:space="preserve">15.330940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2826414108276</t>
   </si>
   <si>
     <t xml:space="preserve">15.3792362213135</t>
@@ -1145,73 +1145,73 @@
     <t xml:space="preserve">15.261944770813</t>
   </si>
   <si>
-    <t xml:space="preserve">15.600025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.489631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9519052505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.972601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.986400604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0416011810303</t>
+    <t xml:space="preserve">15.6000213623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896287918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9519062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9726047515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9864044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0415992736816</t>
   </si>
   <si>
     <t xml:space="preserve">15.8553113937378</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7932138442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.475830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2895412445068</t>
+    <t xml:space="preserve">15.793212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2895421981812</t>
   </si>
   <si>
     <t xml:space="preserve">15.1791477203369</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2067470550537</t>
+    <t xml:space="preserve">15.2067461013794</t>
   </si>
   <si>
     <t xml:space="preserve">15.3999347686768</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2343454360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3033418655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137334823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3861351013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6345224380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.145092010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4831714630127</t>
+    <t xml:space="preserve">15.2343435287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033399581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137344360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.386137008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6345205307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1450939178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4831733703613</t>
   </si>
   <si>
     <t xml:space="preserve">16.6073665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3727779388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6349658966064</t>
+    <t xml:space="preserve">16.3727798461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6349697113037</t>
   </si>
   <si>
     <t xml:space="preserve">16.4141788482666</t>
@@ -1223,40 +1223,40 @@
     <t xml:space="preserve">16.2002906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.731559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6901626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4762744903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7522583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6487655639648</t>
+    <t xml:space="preserve">16.7315616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6901607513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4762725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7522621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6487636566162</t>
   </si>
   <si>
     <t xml:space="preserve">16.6280670166016</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0420417785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0765399932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1110363006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2145328521729</t>
+    <t xml:space="preserve">17.0420436859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0765380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1110382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2145347595215</t>
   </si>
   <si>
     <t xml:space="preserve">17.1455383300781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1800346374512</t>
+    <t xml:space="preserve">17.1800365447998</t>
   </si>
   <si>
     <t xml:space="preserve">16.00710105896</t>
@@ -1265,61 +1265,61 @@
     <t xml:space="preserve">16.21409034729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.110595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5931253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621198654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0066566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7306728363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9031648635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9721612930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.455132484436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1101531982422</t>
+    <t xml:space="preserve">16.1105976104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5931215286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0066576004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7306747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9031639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9721603393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551305770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1101493835449</t>
   </si>
   <si>
     <t xml:space="preserve">15.0411539077759</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0756549835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.351637840271</t>
+    <t xml:space="preserve">15.0756540298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.351634979248</t>
   </si>
   <si>
     <t xml:space="preserve">15.4206342697144</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5241289138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6966190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8742456436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5560531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7328281402588</t>
+    <t xml:space="preserve">15.5241279602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6966161727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156650543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8742485046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5560550689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7328290939331</t>
   </si>
   <si>
     <t xml:space="preserve">15.5914087295532</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">15.379282951355</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7782516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4247064590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5307693481445</t>
+    <t xml:space="preserve">14.7782535552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4247074127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5307703018188</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600610733032</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">14.495415687561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8873147964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1135845184326</t>
+    <t xml:space="preserve">13.8873157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1135835647583</t>
   </si>
   <si>
     <t xml:space="preserve">14.318642616272</t>
@@ -1358,127 +1358,127 @@
     <t xml:space="preserve">14.6014804840088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0257349014282</t>
+    <t xml:space="preserve">15.0257358551025</t>
   </si>
   <si>
     <t xml:space="preserve">15.061089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9550275802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8489618301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8843154907227</t>
+    <t xml:space="preserve">14.9550266265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8489646911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.884316444397</t>
   </si>
   <si>
     <t xml:space="preserve">14.7075424194336</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1671552658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2025089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.566125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6368360519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2832889556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0853023529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.81360912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3539972305298</t>
+    <t xml:space="preserve">15.1671562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2025079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5661249160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6368350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2832899093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.085301399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8136072158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3539981842041</t>
   </si>
   <si>
     <t xml:space="preserve">14.3893527984619</t>
   </si>
   <si>
-    <t xml:space="preserve">14.742901802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1418676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1772241592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.247932434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2125787734985</t>
+    <t xml:space="preserve">14.7428998947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1418695449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.177225112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2479333877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2125778198242</t>
   </si>
   <si>
     <t xml:space="preserve">14.071159362793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9438829421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8731737136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8166074752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8590326309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0145931243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.929741859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.000449180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0994424819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9721660614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0287322998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.057017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1277275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9196729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6721897125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4347763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5054845809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4913425445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3782072067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.463059425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5620517730713</t>
+    <t xml:space="preserve">13.9438819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8731746673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8166065216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8590307235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0145921707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9297428131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0004510879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0994434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9721670150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0287351608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570182800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1277256011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9196720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6721887588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.434775352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5054874420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.49134349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3782081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4630603790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5620527267456</t>
   </si>
   <si>
     <t xml:space="preserve">13.5337677001953</t>
@@ -1487,22 +1487,22 @@
     <t xml:space="preserve">13.1660804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7842502593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6852569580078</t>
+    <t xml:space="preserve">12.7842493057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6852550506592</t>
   </si>
   <si>
     <t xml:space="preserve">12.1620082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6569728851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4064903259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5479116439819</t>
+    <t xml:space="preserve">12.6569719314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4064912796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5479106903076</t>
   </si>
   <si>
     <t xml:space="preserve">13.7883234024048</t>
@@ -1511,28 +1511,28 @@
     <t xml:space="preserve">13.7741804122925</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5903339385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4489192962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3074998855591</t>
+    <t xml:space="preserve">13.5903358459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4489183425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3074989318848</t>
   </si>
   <si>
     <t xml:space="preserve">13.3923501968384</t>
   </si>
   <si>
-    <t xml:space="preserve">13.01051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1519384384155</t>
+    <t xml:space="preserve">13.0105199813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1519393920898</t>
   </si>
   <si>
     <t xml:space="preserve">13.2933559417725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9256687164307</t>
+    <t xml:space="preserve">12.925669670105</t>
   </si>
   <si>
     <t xml:space="preserve">13.0388031005859</t>
@@ -1541,88 +1541,88 @@
     <t xml:space="preserve">12.996376991272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2367887496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0953702926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6469039916992</t>
+    <t xml:space="preserve">13.2367877960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0953712463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6469049453735</t>
   </si>
   <si>
     <t xml:space="preserve">13.6751880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0670862197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2509317398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2085056304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812282562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3499231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8408174514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5296955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8973846435547</t>
+    <t xml:space="preserve">13.0670881271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2509326934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2085084915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812301635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3499250411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8408155441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5296964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8973836898804</t>
   </si>
   <si>
     <t xml:space="preserve">12.6004056930542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7317543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5761957168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5196285247803</t>
+    <t xml:space="preserve">13.7317533493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5761947631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.519627571106</t>
   </si>
   <si>
     <t xml:space="preserve">13.7176122665405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8307476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7600355148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.915599822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7458982467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0428762435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8448905944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.541766166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2218475341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9455547332764</t>
+    <t xml:space="preserve">13.8307466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7600364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9155988693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7458992004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0428781509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8448896408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5417680740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.221848487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9455556869507</t>
   </si>
   <si>
     <t xml:space="preserve">14.1782236099243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9891805648804</t>
+    <t xml:space="preserve">13.9891815185547</t>
   </si>
   <si>
     <t xml:space="preserve">14.2073068618774</t>
@@ -1631,112 +1631,112 @@
     <t xml:space="preserve">14.4399757385254</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2654752731323</t>
+    <t xml:space="preserve">14.265474319458</t>
   </si>
   <si>
     <t xml:space="preserve">14.4108915328979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4981422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690570831299</t>
+    <t xml:space="preserve">14.498143196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690580368042</t>
   </si>
   <si>
     <t xml:space="preserve">14.3527231216431</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3381824493408</t>
+    <t xml:space="preserve">14.3381834030151</t>
   </si>
   <si>
     <t xml:space="preserve">14.5126829147339</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3963489532471</t>
+    <t xml:space="preserve">14.3963499069214</t>
   </si>
   <si>
     <t xml:space="preserve">14.6871871948242</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4254312515259</t>
+    <t xml:space="preserve">14.4254341125488</t>
   </si>
   <si>
     <t xml:space="preserve">14.4835996627808</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6144781112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8326015472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9780206680298</t>
+    <t xml:space="preserve">14.6144762039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8326025009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9780197143555</t>
   </si>
   <si>
     <t xml:space="preserve">15.1234369277954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1961460113525</t>
+    <t xml:space="preserve">15.1961469650269</t>
   </si>
   <si>
     <t xml:space="preserve">15.4142751693726</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4506273269653</t>
+    <t xml:space="preserve">15.4506282806396</t>
   </si>
   <si>
     <t xml:space="preserve">15.3415660858154</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2325038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3052091598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2688550949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687526702881</t>
+    <t xml:space="preserve">15.2325010299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3052072525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.268856048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687536239624</t>
   </si>
   <si>
     <t xml:space="preserve">15.0507297515869</t>
   </si>
   <si>
-    <t xml:space="preserve">15.087082862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9416646957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.723539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0143737792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5781221389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7598943710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6508283615112</t>
+    <t xml:space="preserve">15.0870847702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9416666030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7235383987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0143766403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5781211853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7598934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6508302688599</t>
   </si>
   <si>
     <t xml:space="preserve">14.3672666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3236417770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5272235870361</t>
+    <t xml:space="preserve">14.3236408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5272245407104</t>
   </si>
   <si>
     <t xml:space="preserve">14.4545154571533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7962484359741</t>
+    <t xml:space="preserve">14.7962493896484</t>
   </si>
   <si>
     <t xml:space="preserve">14.9053106307983</t>
@@ -1745,25 +1745,25 @@
     <t xml:space="preserve">16.0322971343994</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3594875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.504903793335</t>
+    <t xml:space="preserve">16.359489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5049076080322</t>
   </si>
   <si>
     <t xml:space="preserve">16.6139698028564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5412616729736</t>
+    <t xml:space="preserve">16.541259765625</t>
   </si>
   <si>
     <t xml:space="preserve">16.8320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6503219604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.577615737915</t>
+    <t xml:space="preserve">16.6503238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5776138305664</t>
   </si>
   <si>
     <t xml:space="preserve">16.8684501647949</t>
@@ -1778,10 +1778,10 @@
     <t xml:space="preserve">17.086576461792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4864749908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4137649536133</t>
+    <t xml:space="preserve">17.4864730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4137668609619</t>
   </si>
   <si>
     <t xml:space="preserve">17.2683486938477</t>
@@ -1790,25 +1790,25 @@
     <t xml:space="preserve">17.5228290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">17.813663482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7409572601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6318950653076</t>
+    <t xml:space="preserve">17.8136653900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7409553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6318912506104</t>
   </si>
   <si>
     <t xml:space="preserve">17.7046031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6682453155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0681457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9227256774902</t>
+    <t xml:space="preserve">17.668249130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0681495666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9227275848389</t>
   </si>
   <si>
     <t xml:space="preserve">18.1044998168945</t>
@@ -1817,31 +1817,31 @@
     <t xml:space="preserve">17.8500175476074</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9590816497803</t>
+    <t xml:space="preserve">17.9590835571289</t>
   </si>
   <si>
     <t xml:space="preserve">18.177209854126</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0317897796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2862739562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3589839935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4680423736572</t>
+    <t xml:space="preserve">18.0317916870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2862720489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3589820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4680461883545</t>
   </si>
   <si>
     <t xml:space="preserve">18.5771064758301</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9954395294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5591850280762</t>
+    <t xml:space="preserve">17.9954357147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5591831207275</t>
   </si>
   <si>
     <t xml:space="preserve">17.5955390930176</t>
@@ -1859,16 +1859,16 @@
     <t xml:space="preserve">18.2135620117188</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3226261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6134624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8315868377686</t>
+    <t xml:space="preserve">18.3226299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6134605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6861724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8315887451172</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951332092285</t>
@@ -1883,13 +1883,13 @@
     <t xml:space="preserve">19.2678413391113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1224231719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3041973114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4132614135742</t>
+    <t xml:space="preserve">19.1224250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3041954040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4132595062256</t>
   </si>
   <si>
     <t xml:space="preserve">19.449613571167</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">16.9048042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7230319976807</t>
+    <t xml:space="preserve">16.7230339050293</t>
   </si>
   <si>
     <t xml:space="preserve">16.4321975708008</t>
@@ -1910,43 +1910,43 @@
     <t xml:space="preserve">19.2314872741699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9775161743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3046989440918</t>
+    <t xml:space="preserve">16.9775142669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3047027587891</t>
   </si>
   <si>
     <t xml:space="preserve">17.3774127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7952365875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5407543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8679447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9042987823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8495121002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4213848114014</t>
+    <t xml:space="preserve">18.7952346801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5407524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8679428100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8495101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.42138671875</t>
   </si>
   <si>
     <t xml:space="preserve">19.7327499389648</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3943996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8105926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549110412598</t>
+    <t xml:space="preserve">20.394401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8105907440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549091339111</t>
   </si>
   <si>
     <t xml:space="preserve">20.3554801940918</t>
@@ -1958,22 +1958,22 @@
     <t xml:space="preserve">19.9273548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4603080749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3435440063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3046226501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.966272354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2657051086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7716693878174</t>
+    <t xml:space="preserve">19.4603061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3435459136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3046245574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9662742614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2657032012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7716732025146</t>
   </si>
   <si>
     <t xml:space="preserve">18.7597370147705</t>
@@ -1982,64 +1982,64 @@
     <t xml:space="preserve">20.1608772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0441150665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1728134155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0560493469238</t>
+    <t xml:space="preserve">20.044116973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.172815322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0560512542725</t>
   </si>
   <si>
     <t xml:space="preserve">20.9392890930176</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2895736694336</t>
+    <t xml:space="preserve">21.2895774841309</t>
   </si>
   <si>
     <t xml:space="preserve">21.0171318054199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7836093902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7057666778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.094970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4452590942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7566223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9512252807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6009387969971</t>
+    <t xml:space="preserve">20.7836074829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7057647705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0949726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4452571868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7566242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9512271881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6009407043457</t>
   </si>
   <si>
     <t xml:space="preserve">21.7955417633057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0290660858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0679874420166</t>
+    <t xml:space="preserve">22.0290679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.067985534668</t>
   </si>
   <si>
     <t xml:space="preserve">22.5350360870361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.57395362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.651798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7685604095459</t>
+    <t xml:space="preserve">22.5739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6517963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7685585021973</t>
   </si>
   <si>
     <t xml:space="preserve">22.8074779510498</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">22.7296390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3404312133789</t>
+    <t xml:space="preserve">22.3404293060303</t>
   </si>
   <si>
     <t xml:space="preserve">22.2625904083252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5080528259277</t>
+    <t xml:space="preserve">23.5080509185791</t>
   </si>
   <si>
     <t xml:space="preserve">23.9750957489014</t>
@@ -2063,28 +2063,28 @@
     <t xml:space="preserve">24.4032249450684</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9091911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7145900726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5199851989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.298397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7924327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1427154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7535076141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6367454528809</t>
+    <t xml:space="preserve">24.9091930389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7145881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5199871063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2983989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7924308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1427135467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7535095214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6367473602295</t>
   </si>
   <si>
     <t xml:space="preserve">24.1697006225586</t>
@@ -2102,31 +2102,31 @@
     <t xml:space="preserve">24.0529384613037</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4691295623779</t>
+    <t xml:space="preserve">23.4691257476807</t>
   </si>
   <si>
     <t xml:space="preserve">23.5858898162842</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1577644348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8583335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7415752410889</t>
+    <t xml:space="preserve">23.1577663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8583354949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7415733337402</t>
   </si>
   <si>
     <t xml:space="preserve">23.8194160461426</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6637306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4302082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0918598175049</t>
+    <t xml:space="preserve">23.6637325286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4302101135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0918617248535</t>
   </si>
   <si>
     <t xml:space="preserve">23.3912887573242</t>
@@ -2135,25 +2135,25 @@
     <t xml:space="preserve">23.352367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0410022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0020790100098</t>
+    <t xml:space="preserve">23.0410041809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0020809173584</t>
   </si>
   <si>
     <t xml:space="preserve">23.1188430786133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.624813079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6128749847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1069107055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1847496032715</t>
+    <t xml:space="preserve">23.6248111724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6128768920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1069087982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1847476959229</t>
   </si>
   <si>
     <t xml:space="preserve">22.4961128234863</t>
@@ -2165,19 +2165,19 @@
     <t xml:space="preserve">22.6907157897949</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3793506622314</t>
+    <t xml:space="preserve">22.3793525695801</t>
   </si>
   <si>
     <t xml:space="preserve">22.9631614685059</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2356052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9242401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2236728668213</t>
+    <t xml:space="preserve">23.2356071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9242420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.223669052124</t>
   </si>
   <si>
     <t xml:space="preserve">22.4182739257812</t>
@@ -2189,22 +2189,22 @@
     <t xml:space="preserve">21.4841766357422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1338939666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.523099899292</t>
+    <t xml:space="preserve">21.1338920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5230979919434</t>
   </si>
   <si>
     <t xml:space="preserve">21.717700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6398620605469</t>
+    <t xml:space="preserve">21.6398582458496</t>
   </si>
   <si>
     <t xml:space="preserve">21.2506542205811</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5620212554932</t>
+    <t xml:space="preserve">21.5620193481445</t>
   </si>
   <si>
     <t xml:space="preserve">21.8344631195068</t>
@@ -2213,22 +2213,22 @@
     <t xml:space="preserve">21.6787815093994</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9901466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1458282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8464012145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8853187561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4571914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3284969329834</t>
+    <t xml:space="preserve">21.9901447296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1458301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.846399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8853206634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4571933746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284950256348</t>
   </si>
   <si>
     <t xml:space="preserve">21.2117328643799</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">20.9782104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6279239654541</t>
+    <t xml:space="preserve">20.6279258728027</t>
   </si>
   <si>
     <t xml:space="preserve">21.873384475708</t>
@@ -2249,16 +2249,16 @@
     <t xml:space="preserve">23.440731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.88356590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7243766784668</t>
+    <t xml:space="preserve">22.8835639953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7243747711182</t>
   </si>
   <si>
     <t xml:space="preserve">22.8039703369141</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7641754150391</t>
+    <t xml:space="preserve">22.7641716003418</t>
   </si>
   <si>
     <t xml:space="preserve">23.0427570343018</t>
@@ -2273,46 +2273,46 @@
     <t xml:space="preserve">23.2019462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">23.122350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1621494293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5203247070312</t>
+    <t xml:space="preserve">23.1223487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1621475219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5203266143799</t>
   </si>
   <si>
     <t xml:space="preserve">23.9580993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0774898529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4356708526611</t>
+    <t xml:space="preserve">24.0774917602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4356689453125</t>
   </si>
   <si>
     <t xml:space="preserve">24.3162746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3560752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7938442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1570873260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6744518280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.913236618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.555061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7540473937988</t>
+    <t xml:space="preserve">24.3560733795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7938461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1570854187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6744537353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9132385253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5550594329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7540493011475</t>
   </si>
   <si>
     <t xml:space="preserve">24.2764778137207</t>
@@ -2330,25 +2330,25 @@
     <t xml:space="preserve">24.2366828918457</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3958721160889</t>
+    <t xml:space="preserve">24.3958702087402</t>
   </si>
   <si>
     <t xml:space="preserve">24.7142486572266</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6346549987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1968841552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6295948028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5102005004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1520252227783</t>
+    <t xml:space="preserve">24.6346569061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1968822479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6295928955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5102024078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1520233154297</t>
   </si>
   <si>
     <t xml:space="preserve">25.3510131835938</t>
@@ -2360,46 +2360,46 @@
     <t xml:space="preserve">25.6693916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3908081054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.191822052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0326290130615</t>
+    <t xml:space="preserve">25.3908100128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1918201446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0326328277588</t>
   </si>
   <si>
     <t xml:space="preserve">25.2714157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8336429595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9530353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8683795928955</t>
+    <t xml:space="preserve">24.8336448669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9530372619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8683776855469</t>
   </si>
   <si>
     <t xml:space="preserve">25.0724296569824</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7591094970703</t>
+    <t xml:space="preserve">23.7591114044189</t>
   </si>
   <si>
     <t xml:space="preserve">23.4805278778076</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8785057067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6397190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7989063262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5948581695557</t>
+    <t xml:space="preserve">23.8785037994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.639720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7989101409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.594856262207</t>
   </si>
   <si>
     <t xml:space="preserve">24.9928321838379</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">25.430606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3112144470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2316188812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0673656463623</t>
+    <t xml:space="preserve">25.3112125396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2316207885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0673675537109</t>
   </si>
   <si>
     <t xml:space="preserve">26.2663536071777</t>
@@ -2423,46 +2423,46 @@
     <t xml:space="preserve">26.0275688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7887859344482</t>
+    <t xml:space="preserve">25.7887840270996</t>
   </si>
   <si>
     <t xml:space="preserve">25.5499992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5897979736328</t>
+    <t xml:space="preserve">25.5897960662842</t>
   </si>
   <si>
     <t xml:space="preserve">25.9479732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1071624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7489852905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8734397888184</t>
+    <t xml:space="preserve">26.1071643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7489833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.873441696167</t>
   </si>
   <si>
     <t xml:space="preserve">24.0376949310303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3263988494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3661975860596</t>
+    <t xml:space="preserve">22.3264007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3661994934082</t>
   </si>
   <si>
     <t xml:space="preserve">23.0825538635254</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9233646392822</t>
+    <t xml:space="preserve">22.9233627319336</t>
   </si>
   <si>
     <t xml:space="preserve">23.3213367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5999202728271</t>
+    <t xml:space="preserve">23.5999221801758</t>
   </si>
   <si>
     <t xml:space="preserve">23.3611354827881</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">23.4009323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5601215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4855899810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8387050628662</t>
+    <t xml:space="preserve">23.5601234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4855918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8387069702148</t>
   </si>
   <si>
     <t xml:space="preserve">23.997896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">23.719310760498</t>
+    <t xml:space="preserve">23.7193126678467</t>
   </si>
   <si>
     <t xml:space="preserve">23.8264102935791</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">24.1263828277588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9549694061279</t>
+    <t xml:space="preserve">23.9549713134766</t>
   </si>
   <si>
     <t xml:space="preserve">24.4692077636719</t>
@@ -2504,13 +2504,13 @@
     <t xml:space="preserve">24.4263553619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1692352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2120895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7835559844971</t>
+    <t xml:space="preserve">24.1692371368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2120876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7835578918457</t>
   </si>
   <si>
     <t xml:space="preserve">24.340648651123</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">24.2549419403076</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977981567383</t>
+    <t xml:space="preserve">24.2977962493896</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264377593994</t>
@@ -2549,34 +2549,34 @@
     <t xml:space="preserve">22.5836658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">22.92649269104</t>
+    <t xml:space="preserve">22.9264907836914</t>
   </si>
   <si>
     <t xml:space="preserve">23.1407585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8407859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7550773620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6693744659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0550518035889</t>
+    <t xml:space="preserve">22.840784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7550792694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6693725585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0550498962402</t>
   </si>
   <si>
     <t xml:space="preserve">23.2264652252197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7122249603271</t>
+    <t xml:space="preserve">22.7122268676758</t>
   </si>
   <si>
     <t xml:space="preserve">22.4122524261475</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1836090087891</t>
+    <t xml:space="preserve">23.1836109161377</t>
   </si>
   <si>
     <t xml:space="preserve">23.0979061126709</t>
@@ -2585,34 +2585,34 @@
     <t xml:space="preserve">22.3694000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3550243377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0121974945068</t>
+    <t xml:space="preserve">23.3550262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0121994018555</t>
   </si>
   <si>
     <t xml:space="preserve">23.3121719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">23.397876739502</t>
+    <t xml:space="preserve">23.3978748321533</t>
   </si>
   <si>
     <t xml:space="preserve">22.7979316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4551086425781</t>
+    <t xml:space="preserve">22.4551067352295</t>
   </si>
   <si>
     <t xml:space="preserve">22.4979591369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6265182495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6978492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5408115386963</t>
+    <t xml:space="preserve">22.6265201568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6978511810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5408134460449</t>
   </si>
   <si>
     <t xml:space="preserve">23.2693176269531</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">21.426628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4694805145264</t>
+    <t xml:space="preserve">21.469482421875</t>
   </si>
   <si>
     <t xml:space="preserve">21.2552146911621</t>
@@ -2633,16 +2633,16 @@
     <t xml:space="preserve">20.826681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9267616271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1410293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9980964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1266536712646</t>
+    <t xml:space="preserve">19.9267635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1410312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9980945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1266555786133</t>
   </si>
   <si>
     <t xml:space="preserve">20.5267105102539</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">20.6552696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">20.312442779541</t>
+    <t xml:space="preserve">20.3124446868896</t>
   </si>
   <si>
     <t xml:space="preserve">20.4410037994385</t>
@@ -2666,13 +2666,13 @@
     <t xml:space="preserve">21.3837757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">21.512336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3409194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0265731811523</t>
+    <t xml:space="preserve">21.5123329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3409214019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.026575088501</t>
   </si>
   <si>
     <t xml:space="preserve">22.1122798919678</t>
@@ -2681,19 +2681,19 @@
     <t xml:space="preserve">21.8123073577881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1551342010498</t>
+    <t xml:space="preserve">22.1551322937012</t>
   </si>
   <si>
     <t xml:space="preserve">22.2408390045166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6837482452393</t>
+    <t xml:space="preserve">21.6837463378906</t>
   </si>
   <si>
     <t xml:space="preserve">21.7266006469727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8980140686035</t>
+    <t xml:space="preserve">21.8980121612549</t>
   </si>
   <si>
     <t xml:space="preserve">21.7694530487061</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.0694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9837207794189</t>
+    <t xml:space="preserve">21.9837188720703</t>
   </si>
   <si>
     <t xml:space="preserve">21.8551597595215</t>
@@ -2720,16 +2720,16 @@
     <t xml:space="preserve">21.0838012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9408664703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5551853179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0409488677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.912389755249</t>
+    <t xml:space="preserve">21.9408683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5551872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0409469604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9123878479004</t>
   </si>
   <si>
     <t xml:space="preserve">21.2980690002441</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">20.7409763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1838817596436</t>
+    <t xml:space="preserve">20.1838836669922</t>
   </si>
   <si>
     <t xml:space="preserve">20.3552951812744</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">22.0611591339111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1051959991455</t>
+    <t xml:space="preserve">22.1051940917969</t>
   </si>
   <si>
     <t xml:space="preserve">22.017126083374</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">21.664852142334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5767841339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4887161254883</t>
+    <t xml:space="preserve">21.5767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4887142181396</t>
   </si>
   <si>
     <t xml:space="preserve">21.9290561676025</t>
@@ -2792,22 +2792,22 @@
     <t xml:space="preserve">21.8409881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7088851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4006462097168</t>
+    <t xml:space="preserve">21.7088871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4006443023682</t>
   </si>
   <si>
     <t xml:space="preserve">21.7969551086426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9730930328369</t>
+    <t xml:space="preserve">21.9730911254883</t>
   </si>
   <si>
     <t xml:space="preserve">21.7529201507568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5015029907227</t>
+    <t xml:space="preserve">22.501501083374</t>
   </si>
   <si>
     <t xml:space="preserve">22.2372970581055</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">22.3253650665283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5455360412598</t>
+    <t xml:space="preserve">22.5455379486084</t>
   </si>
   <si>
     <t xml:space="preserve">22.149227142334</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">21.0483722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3566112518311</t>
+    <t xml:space="preserve">21.3566131591797</t>
   </si>
   <si>
     <t xml:space="preserve">21.6208171844482</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">21.4446811676025</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5327491760254</t>
+    <t xml:space="preserve">21.532751083374</t>
   </si>
   <si>
     <t xml:space="preserve">21.0043392181396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8722343444824</t>
+    <t xml:space="preserve">20.8722362518311</t>
   </si>
   <si>
     <t xml:space="preserve">20.6960983276367</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">20.2557563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3878593444824</t>
+    <t xml:space="preserve">20.3878574371338</t>
   </si>
   <si>
     <t xml:space="preserve">20.2997894287109</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">20.7841682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9603023529053</t>
+    <t xml:space="preserve">20.9603042602539</t>
   </si>
   <si>
     <t xml:space="preserve">20.7401313781738</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">21.1804752349854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6336059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4574680328369</t>
+    <t xml:space="preserve">22.6336078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4574699401855</t>
   </si>
   <si>
     <t xml:space="preserve">22.5895709991455</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">24.3949756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3069076538086</t>
+    <t xml:space="preserve">24.30690574646</t>
   </si>
   <si>
     <t xml:space="preserve">24.1307697296143</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">24.3509407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4390087127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5711135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6591815948486</t>
+    <t xml:space="preserve">24.4390106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5711116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6591796875</t>
   </si>
   <si>
     <t xml:space="preserve">24.7032146453857</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">24.0867366790771</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2188377380371</t>
+    <t xml:space="preserve">24.2188396453857</t>
   </si>
   <si>
     <t xml:space="preserve">24.1748046875</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">23.9546337127686</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7600383758545</t>
+    <t xml:space="preserve">25.7600364685059</t>
   </si>
   <si>
     <t xml:space="preserve">25.4077625274658</t>
@@ -2987,19 +2987,19 @@
     <t xml:space="preserve">26.1123104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1563472747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4645843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5910148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3708438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8992576599121</t>
+    <t xml:space="preserve">26.1563453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4645862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5910167694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3708457946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8992595672607</t>
   </si>
   <si>
     <t xml:space="preserve">30.0313587188721</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">29.5029487609863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7671527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2827777862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0753955841064</t>
+    <t xml:space="preserve">29.7671546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2827758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0753974914551</t>
   </si>
   <si>
     <t xml:space="preserve">29.7231216430664</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">30.471700668335</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8111877441406</t>
+    <t xml:space="preserve">29.811185836792</t>
   </si>
   <si>
     <t xml:space="preserve">29.2387447357178</t>
@@ -3044,28 +3044,28 @@
     <t xml:space="preserve">28.7103309631348</t>
   </si>
   <si>
-    <t xml:space="preserve">28.842435836792</t>
+    <t xml:space="preserve">28.8424339294434</t>
   </si>
   <si>
     <t xml:space="preserve">28.8864688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5469818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2955665588379</t>
+    <t xml:space="preserve">29.5469837188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2955646514893</t>
   </si>
   <si>
     <t xml:space="preserve">30.7359104156494</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3836326599121</t>
+    <t xml:space="preserve">30.3836345672607</t>
   </si>
   <si>
     <t xml:space="preserve">29.9873237609863</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4276676177979</t>
+    <t xml:space="preserve">30.4276695251465</t>
   </si>
   <si>
     <t xml:space="preserve">29.4632396697998</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">32.2999992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1500015258789</t>
+    <t xml:space="preserve">31.3999996185303</t>
   </si>
 </sst>
 </file>
@@ -69141,22 +69141,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6912268518</v>
+        <v>45968.6909953704</v>
       </c>
       <c r="B2505" t="n">
-        <v>32494</v>
+        <v>20451</v>
       </c>
       <c r="C2505" t="n">
-        <v>32.5999984741211</v>
+        <v>32.4500007629395</v>
       </c>
       <c r="D2505" t="n">
-        <v>31.8999996185303</v>
+        <v>31.3500003814697</v>
       </c>
       <c r="E2505" t="n">
-        <v>32.2999992370605</v>
+        <v>32.0499992370605</v>
       </c>
       <c r="F2505" t="n">
-        <v>32.1500015258789</v>
+        <v>31.3999996185303</v>
       </c>
       <c r="G2505" t="s">
         <v>1228</v>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="1234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="1236">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,94 +38,94 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8067150115967</t>
+    <t xml:space="preserve">13.8067111968994</t>
   </si>
   <si>
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577440261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.957332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3883295059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8896141052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8527965545654</t>
+    <t xml:space="preserve">14.0577449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9573316574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3883304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896131515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8527975082397</t>
   </si>
   <si>
     <t xml:space="preserve">12.9532079696655</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6184997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846172332764</t>
+    <t xml:space="preserve">12.6184988021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846162796021</t>
   </si>
   <si>
     <t xml:space="preserve">12.3842039108276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8821392059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7348699569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2127265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7307453155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2294597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2194194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2461957931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9148349761963</t>
+    <t xml:space="preserve">11.8821430206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7348709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2127256393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7307462692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2294607162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2194204330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2461967468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.914834022522</t>
   </si>
   <si>
     <t xml:space="preserve">11.1323947906494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6143751144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6813163757324</t>
+    <t xml:space="preserve">11.6143770217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6813173294067</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474338531494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3466100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3131380081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.329873085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8947525024414</t>
+    <t xml:space="preserve">11.3466091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.313136100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3298721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8947534561157</t>
   </si>
   <si>
     <t xml:space="preserve">10.8780174255371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0453701019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4261617660522</t>
+    <t xml:space="preserve">11.0453720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4261608123779</t>
   </si>
   <si>
     <t xml:space="preserve">10.4094257354736</t>
@@ -134,73 +134,73 @@
     <t xml:space="preserve">11.7080936431885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7147884368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0494956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7482557296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.744912147522</t>
+    <t xml:space="preserve">11.7147874832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0494966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7482585906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7449111938477</t>
   </si>
   <si>
     <t xml:space="preserve">12.2135038375854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2168493270874</t>
+    <t xml:space="preserve">12.2168502807617</t>
   </si>
   <si>
     <t xml:space="preserve">12.3674697875977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7189102172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8293657302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0201511383057</t>
+    <t xml:space="preserve">12.7189111709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.82936668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.020149230957</t>
   </si>
   <si>
     <t xml:space="preserve">13.2209758758545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3849830627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536222457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3347759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3146934509277</t>
+    <t xml:space="preserve">13.3849811553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870904922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536203384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.334774017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3146915435791</t>
   </si>
   <si>
     <t xml:space="preserve">13.0569677352905</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2109346389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661851882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306028366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2879180908203</t>
+    <t xml:space="preserve">13.2109336853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661832809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.287917137146</t>
   </si>
   <si>
     <t xml:space="preserve">12.8260192871094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9833307266235</t>
+    <t xml:space="preserve">12.9833316802979</t>
   </si>
   <si>
     <t xml:space="preserve">12.9030017852783</t>
@@ -209,523 +209,523 @@
     <t xml:space="preserve">13.2377090454102</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1674222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1138687133789</t>
+    <t xml:space="preserve">13.1674203872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.113865852356</t>
   </si>
   <si>
     <t xml:space="preserve">13.0971326828003</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5046997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8092823028564</t>
+    <t xml:space="preserve">12.5047006607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8092851638794</t>
   </si>
   <si>
     <t xml:space="preserve">12.8862676620483</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7055234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7222576141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9163913726807</t>
+    <t xml:space="preserve">12.7055244445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7222604751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.916392326355</t>
   </si>
   <si>
     <t xml:space="preserve">13.0301904678345</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8327131271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6318893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7021770477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8695306777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5582523345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5682926177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8360595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494482040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958946228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5348234176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7791604995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.769118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.786566734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.502420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6512584686279</t>
+    <t xml:space="preserve">12.8327121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6318883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7021780014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.869532585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5582513809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5682935714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8360586166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5348224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7791614532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7691202163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7865657806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5024213790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6512594223022</t>
   </si>
   <si>
     <t xml:space="preserve">12.752739906311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5836067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4990377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5700731277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159502029419</t>
+    <t xml:space="preserve">12.5836029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4990367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5700750350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159511566162</t>
   </si>
   <si>
     <t xml:space="preserve">12.2791624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0660543441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776828765869</t>
+    <t xml:space="preserve">12.06605052948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776809692383</t>
   </si>
   <si>
     <t xml:space="preserve">12.1641502380371</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1709175109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1100263595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1269416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9814853668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7459745407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580219268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231382369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.697340965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7785243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2406768798828</t>
+    <t xml:space="preserve">12.170916557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1100282669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1269426345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.981484413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7459735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6973419189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7785234451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2406759262085</t>
   </si>
   <si>
     <t xml:space="preserve">10.8212242126465</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6554708480835</t>
+    <t xml:space="preserve">10.6554718017578</t>
   </si>
   <si>
     <t xml:space="preserve">11.0613946914673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.196702003479</t>
+    <t xml:space="preserve">11.1967010498047</t>
   </si>
   <si>
     <t xml:space="preserve">11.4064283370972</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248222351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6656188964844</t>
+    <t xml:space="preserve">11.5248231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.665620803833</t>
   </si>
   <si>
     <t xml:space="preserve">10.1886606216431</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5878171920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6825332641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.839412689209</t>
+    <t xml:space="preserve">10.587818145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6825323104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8394136428833</t>
   </si>
   <si>
     <t xml:space="preserve">13.0199728012085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3616228103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0233535766602</t>
+    <t xml:space="preserve">13.3616237640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0233554840088</t>
   </si>
   <si>
     <t xml:space="preserve">13.1924896240234</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4969320297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4698686599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307588577271</t>
+    <t xml:space="preserve">13.4969310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4698696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307569503784</t>
   </si>
   <si>
     <t xml:space="preserve">13.4800176620483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2939710617065</t>
+    <t xml:space="preserve">13.2939682006836</t>
   </si>
   <si>
     <t xml:space="preserve">13.3108825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3548583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0740957260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368843078613</t>
+    <t xml:space="preserve">13.3548564910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0740966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368852615356</t>
   </si>
   <si>
     <t xml:space="preserve">12.9489345550537</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9827632904053</t>
+    <t xml:space="preserve">12.982762336731</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910081863403</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0707111358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9962921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8576011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113042831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1248340606689</t>
+    <t xml:space="preserve">13.0707120895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9962930679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8576021194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113052368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1248331069946</t>
   </si>
   <si>
     <t xml:space="preserve">13.1823406219482</t>
   </si>
   <si>
-    <t xml:space="preserve">13.060564994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857233047485</t>
+    <t xml:space="preserve">13.0605621337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857242584229</t>
   </si>
   <si>
     <t xml:space="preserve">13.4123640060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5679683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4157447814941</t>
+    <t xml:space="preserve">13.567967414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4157476425171</t>
   </si>
   <si>
     <t xml:space="preserve">13.5138444900513</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7066555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8351993560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2106781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4576148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7552919387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838338851929</t>
+    <t xml:space="preserve">13.7066593170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8352003097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2106790542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4576168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7552900314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838357925415</t>
   </si>
   <si>
     <t xml:space="preserve">15.01575756073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9853134155273</t>
+    <t xml:space="preserve">14.9853143692017</t>
   </si>
   <si>
     <t xml:space="preserve">15.3303489685059</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6652345657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.289755821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8297080993652</t>
+    <t xml:space="preserve">15.6652374267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2897567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8297090530396</t>
   </si>
   <si>
     <t xml:space="preserve">14.6842555999756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7722034454346</t>
+    <t xml:space="preserve">14.7722063064575</t>
   </si>
   <si>
     <t xml:space="preserve">14.9514875411987</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7485256195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7180805206299</t>
+    <t xml:space="preserve">14.7485237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7180814743042</t>
   </si>
   <si>
     <t xml:space="preserve">14.8770666122437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992668151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9007472991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2018041610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939819335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330945968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988451004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9142780303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.927809715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.738377571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7248449325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.542181968689</t>
+    <t xml:space="preserve">14.7992658615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751653671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.90074634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2018060684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939828872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988470077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9142770767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9278087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7383766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7248468399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5421838760376</t>
   </si>
   <si>
     <t xml:space="preserve">14.4440841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0529670715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1442985534668</t>
+    <t xml:space="preserve">15.0529642105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1443014144897</t>
   </si>
   <si>
     <t xml:space="preserve">15.1104726791382</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9548683166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0901756286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2187194824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7823514938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.616602897644</t>
+    <t xml:space="preserve">14.954870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0901746749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2187204360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7823534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707220077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6165981292725</t>
   </si>
   <si>
     <t xml:space="preserve">14.3764305114746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1599369049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2546529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0415449142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1125812530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0381622314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1430253982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903820037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527479171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2072944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3561334609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373188018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3087778091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2411222457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3392210006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2512722015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464071273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058149337769</t>
+    <t xml:space="preserve">14.1599378585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2546539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0415439605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1125802993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.038158416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1430244445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527488708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2072954177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3561353683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373197555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730497360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3087759017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2411193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3392181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2512693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.146409034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058139801025</t>
   </si>
   <si>
     <t xml:space="preserve">14.119345664978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2275924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2715682983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1497888565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0753707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0719871520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667051315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4779090881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.626748085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7519092559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8161792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1037082672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0834112167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172380447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.154447555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999067306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758043289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3574113845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3912334442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893350601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1713609695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1003255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946199417114</t>
+    <t xml:space="preserve">14.2275905609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2715654373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1497898101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0753688812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0719861984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749490737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667041778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4779109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267490386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7519111633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8161811828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1037101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0834131240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882762908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1544485092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3912372589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893360137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1713619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.100323677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946161270142</t>
   </si>
   <si>
     <t xml:space="preserve">15.3168163299561</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3134355545044</t>
+    <t xml:space="preserve">15.313437461853</t>
   </si>
   <si>
     <t xml:space="preserve">15.4182968139648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4250621795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.536693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6753826141357</t>
+    <t xml:space="preserve">15.4250650405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366926193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6753816604614</t>
   </si>
   <si>
     <t xml:space="preserve">15.6449394226074</t>
@@ -734,22 +734,22 @@
     <t xml:space="preserve">15.7295074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6618509292603</t>
+    <t xml:space="preserve">15.6618518829346</t>
   </si>
   <si>
     <t xml:space="preserve">15.6517028808594</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6821508407593</t>
+    <t xml:space="preserve">15.6821479797363</t>
   </si>
   <si>
     <t xml:space="preserve">15.5637521743774</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4081525802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415576934814</t>
+    <t xml:space="preserve">15.4081506729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415548324585</t>
   </si>
   <si>
     <t xml:space="preserve">15.7024440765381</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">15.5333099365234</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6584711074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588918685913</t>
+    <t xml:space="preserve">15.6584692001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.458890914917</t>
   </si>
   <si>
     <t xml:space="preserve">15.5874347686768</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6550855636597</t>
+    <t xml:space="preserve">15.655086517334</t>
   </si>
   <si>
     <t xml:space="preserve">15.7227420806885</t>
@@ -776,16 +776,16 @@
     <t xml:space="preserve">16.3350067138672</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0339469909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.406042098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4026622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4195728302002</t>
+    <t xml:space="preserve">16.0339488983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4060440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.402660369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4195747375488</t>
   </si>
   <si>
     <t xml:space="preserve">16.6935710906982</t>
@@ -794,67 +794,67 @@
     <t xml:space="preserve">17.099494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9980144500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1671485900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4208545684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5392417907715</t>
+    <t xml:space="preserve">16.9980125427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1671504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4208507537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5392436981201</t>
   </si>
   <si>
     <t xml:space="preserve">17.6407260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4039363861084</t>
+    <t xml:space="preserve">17.403938293457</t>
   </si>
   <si>
     <t xml:space="preserve">17.48850440979</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3531970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3870239257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.522331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4546775817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.877513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8098583221436</t>
+    <t xml:space="preserve">17.353199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3870258331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5223293304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4546794891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8775100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8098602294922</t>
   </si>
   <si>
     <t xml:space="preserve">17.7083797454834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7591190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6745510101318</t>
+    <t xml:space="preserve">17.7591209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6745548248291</t>
   </si>
   <si>
     <t xml:space="preserve">17.5730743408203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3362865447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2009773254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2348003387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2517147064209</t>
+    <t xml:space="preserve">17.3362808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2009754180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2348022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2517166137695</t>
   </si>
   <si>
     <t xml:space="preserve">17.2178897857666</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">17.7147541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5767612457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.559513092041</t>
+    <t xml:space="preserve">17.5767631530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5595149993896</t>
   </si>
   <si>
     <t xml:space="preserve">17.6975059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4698162078857</t>
+    <t xml:space="preserve">17.469820022583</t>
   </si>
   <si>
     <t xml:space="preserve">17.6147117614746</t>
@@ -887,34 +887,34 @@
     <t xml:space="preserve">16.7729587554932</t>
   </si>
   <si>
-    <t xml:space="preserve">17.00754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1662330627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1317367553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.993745803833</t>
+    <t xml:space="preserve">17.0075435638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1662368774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1317386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9937438964844</t>
   </si>
   <si>
     <t xml:space="preserve">16.9868488311768</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9661483764648</t>
+    <t xml:space="preserve">16.9661502838135</t>
   </si>
   <si>
     <t xml:space="preserve">16.835054397583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8488540649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8281555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7591609954834</t>
+    <t xml:space="preserve">16.8488521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8281536102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7591590881348</t>
   </si>
   <si>
     <t xml:space="preserve">16.8695526123047</t>
@@ -935,16 +935,16 @@
     <t xml:space="preserve">16.6625633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5935649871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5659713745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.503870010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8626537322998</t>
+    <t xml:space="preserve">16.5935668945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5659694671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5038738250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8626518249512</t>
   </si>
   <si>
     <t xml:space="preserve">16.9040489196777</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">16.80055809021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8971519470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5383701324463</t>
+    <t xml:space="preserve">16.8971500396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5383720397949</t>
   </si>
   <si>
     <t xml:space="preserve">16.5590705871582</t>
@@ -965,19 +965,19 @@
     <t xml:space="preserve">16.4900741577148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2416896820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3037815093994</t>
+    <t xml:space="preserve">16.2416877746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3037853240967</t>
   </si>
   <si>
     <t xml:space="preserve">16.2485885620117</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1243934631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1864910125732</t>
+    <t xml:space="preserve">16.1243953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1864891052246</t>
   </si>
   <si>
     <t xml:space="preserve">16.1588935852051</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">16.2899856567383</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3175830841064</t>
+    <t xml:space="preserve">16.3175811767578</t>
   </si>
   <si>
     <t xml:space="preserve">16.5452709197998</t>
@@ -1010,28 +1010,28 @@
     <t xml:space="preserve">16.6970634460449</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3865814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4486751556396</t>
+    <t xml:space="preserve">16.3865795135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4486770629883</t>
   </si>
   <si>
     <t xml:space="preserve">16.5107727050781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4210796356201</t>
+    <t xml:space="preserve">16.4210758209229</t>
   </si>
   <si>
     <t xml:space="preserve">16.4348773956299</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3934803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4969711303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5245704650879</t>
+    <t xml:space="preserve">16.393482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4969730377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5245742797852</t>
   </si>
   <si>
     <t xml:space="preserve">16.4003791809082</t>
@@ -1040,103 +1040,103 @@
     <t xml:space="preserve">16.4555759429932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3589782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2830829620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5521697998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1795959472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2071914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1933898925781</t>
+    <t xml:space="preserve">16.3589820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2830848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5521717071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.179594039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2071895599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1933917999268</t>
   </si>
   <si>
     <t xml:space="preserve">16.1519927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9036054611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5586261749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4965295791626</t>
+    <t xml:space="preserve">15.9036073684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5586280822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4965314865112</t>
   </si>
   <si>
     <t xml:space="preserve">15.9381046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7794151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7656164169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7863111495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9795017242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9312028884888</t>
+    <t xml:space="preserve">15.7794132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7656154632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7863140106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9795036315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9312047958374</t>
   </si>
   <si>
     <t xml:space="preserve">15.7035188674927</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6483211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8415098190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7518148422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691101074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.862208366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0277976989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8967094421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6276226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7173156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310277938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034265518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413356781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2481441497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3171396255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3309392929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2826404571533</t>
+    <t xml:space="preserve">15.6483201980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8415117263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7518177032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691091537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8622102737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0277996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8967084884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6276216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7173185348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.53102684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034275054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.441330909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2481451034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3171405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.330940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2826433181763</t>
   </si>
   <si>
     <t xml:space="preserve">15.3792381286621</t>
@@ -1145,34 +1145,34 @@
     <t xml:space="preserve">15.2619428634644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6000232696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9519052505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.972601890564</t>
+    <t xml:space="preserve">15.6000213623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896287918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9519062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9726028442383</t>
   </si>
   <si>
     <t xml:space="preserve">15.9864025115967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0416011810303</t>
+    <t xml:space="preserve">16.041597366333</t>
   </si>
   <si>
     <t xml:space="preserve">15.8553094863892</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7932119369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.475830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2895383834839</t>
+    <t xml:space="preserve">15.793212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758329391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2895402908325</t>
   </si>
   <si>
     <t xml:space="preserve">15.1791477203369</t>
@@ -1181,73 +1181,73 @@
     <t xml:space="preserve">15.2067470550537</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3999357223511</t>
+    <t xml:space="preserve">15.3999366760254</t>
   </si>
   <si>
     <t xml:space="preserve">15.2343454360962</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3033399581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137353897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.386137008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6345224380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.145092010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4831714630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6073703765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3727798461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6349678039551</t>
+    <t xml:space="preserve">15.3033418655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137344360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3861331939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6345205307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1450939178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4831733703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6073665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.37278175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6349658966064</t>
   </si>
   <si>
     <t xml:space="preserve">16.414176940918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0898952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2002925872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7315578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6901626586914</t>
+    <t xml:space="preserve">16.0898971557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7315616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6901607513428</t>
   </si>
   <si>
     <t xml:space="preserve">16.4762725830078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7522621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6487655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6280689239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0420436859131</t>
+    <t xml:space="preserve">16.7522583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6487636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6280651092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0420417785645</t>
   </si>
   <si>
     <t xml:space="preserve">17.0765399932861</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1110363006592</t>
+    <t xml:space="preserve">17.1110382080078</t>
   </si>
   <si>
     <t xml:space="preserve">17.2145347595215</t>
@@ -1256,19 +1256,19 @@
     <t xml:space="preserve">17.1455383300781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1800346374512</t>
+    <t xml:space="preserve">17.1800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">16.00710105896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2140884399414</t>
+    <t xml:space="preserve">16.2140922546387</t>
   </si>
   <si>
     <t xml:space="preserve">16.110595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5931234359741</t>
+    <t xml:space="preserve">15.5931262969971</t>
   </si>
   <si>
     <t xml:space="preserve">15.6621217727661</t>
@@ -1277,49 +1277,49 @@
     <t xml:space="preserve">15.0066576004028</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7306728363037</t>
+    <t xml:space="preserve">14.7306747436523</t>
   </si>
   <si>
     <t xml:space="preserve">14.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9721603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551315307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1101512908936</t>
+    <t xml:space="preserve">14.9721584320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.455132484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1101522445679</t>
   </si>
   <si>
     <t xml:space="preserve">15.0411558151245</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0756521224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3516368865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4206352233887</t>
+    <t xml:space="preserve">15.0756540298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3516387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4206342697144</t>
   </si>
   <si>
     <t xml:space="preserve">15.5241279602051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6966161727905</t>
+    <t xml:space="preserve">15.6966180801392</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156650543213</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8742475509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5560550689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7328281402588</t>
+    <t xml:space="preserve">15.8742485046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5560569763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7328290939331</t>
   </si>
   <si>
     <t xml:space="preserve">15.5914106369019</t>
@@ -1328,55 +1328,55 @@
     <t xml:space="preserve">15.3439264297485</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3792848587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7782526016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4247074127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5307703018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4954166412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8873147964478</t>
+    <t xml:space="preserve">15.379282951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7782535552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4247064590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5307693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600620269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4954175949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8873167037964</t>
   </si>
   <si>
     <t xml:space="preserve">14.1135845184326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3186407089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6014804840088</t>
+    <t xml:space="preserve">14.3186416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6014795303345</t>
   </si>
   <si>
     <t xml:space="preserve">15.0257358551025</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0610904693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9550256729126</t>
+    <t xml:space="preserve">15.0610914230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9550285339355</t>
   </si>
   <si>
     <t xml:space="preserve">14.8489608764648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8843173980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7075433731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671562194824</t>
+    <t xml:space="preserve">14.884316444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7075443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671543121338</t>
   </si>
   <si>
     <t xml:space="preserve">15.2025098800659</t>
@@ -1388,16 +1388,16 @@
     <t xml:space="preserve">14.6368350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2832899093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0853023529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8136081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3539962768555</t>
+    <t xml:space="preserve">14.2832870483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0853004455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.81360912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3539953231812</t>
   </si>
   <si>
     <t xml:space="preserve">14.3893527984619</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">14.1418695449829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.177225112915</t>
+    <t xml:space="preserve">14.1772232055664</t>
   </si>
   <si>
     <t xml:space="preserve">14.2479333877563</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2125797271729</t>
+    <t xml:space="preserve">14.2125778198242</t>
   </si>
   <si>
     <t xml:space="preserve">14.071159362793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9438829421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8731746673584</t>
+    <t xml:space="preserve">13.9438819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8731756210327</t>
   </si>
   <si>
     <t xml:space="preserve">13.8166065216064</t>
@@ -1436,43 +1436,43 @@
     <t xml:space="preserve">14.0145921707153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9297399520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0004501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0994443893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9721660614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.028733253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0570163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1277265548706</t>
+    <t xml:space="preserve">13.9297409057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0004510879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0994434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9721670150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0287342071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.057017326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.127724647522</t>
   </si>
   <si>
     <t xml:space="preserve">14.9196720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6721897125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.434775352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.505485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4913425445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3782081604004</t>
+    <t xml:space="preserve">14.6721868515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5054864883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4913444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3782091140747</t>
   </si>
   <si>
     <t xml:space="preserve">13.463059425354</t>
@@ -1484,28 +1484,28 @@
     <t xml:space="preserve">13.5337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1660814285278</t>
+    <t xml:space="preserve">13.1660804748535</t>
   </si>
   <si>
     <t xml:space="preserve">12.7842493057251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6852569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1620092391968</t>
+    <t xml:space="preserve">12.6852560043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1620073318481</t>
   </si>
   <si>
     <t xml:space="preserve">12.6569719314575</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4064912796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5479106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7883234024048</t>
+    <t xml:space="preserve">13.4064922332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.547908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7883214950562</t>
   </si>
   <si>
     <t xml:space="preserve">13.7741804122925</t>
@@ -1520,67 +1520,67 @@
     <t xml:space="preserve">13.3074989318848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.392352104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0105209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1519393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2933549880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.925669670105</t>
+    <t xml:space="preserve">13.3923501968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0105199813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1519384384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2933540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9256687164307</t>
   </si>
   <si>
     <t xml:space="preserve">13.0388040542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9963760375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2367877960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0953702926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6469039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6751861572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0670862197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2509317398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2085056304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812273025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3499250411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8408174514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5296964645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8973846435547</t>
+    <t xml:space="preserve">12.9963779449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2367897033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0953712463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6469020843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6751871109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0670881271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2509326934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2085065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812292098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3499240875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8408145904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5296945571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8973865509033</t>
   </si>
   <si>
     <t xml:space="preserve">12.6004056930542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7317552566528</t>
+    <t xml:space="preserve">13.7317562103271</t>
   </si>
   <si>
     <t xml:space="preserve">13.5761947631836</t>
@@ -1589,61 +1589,61 @@
     <t xml:space="preserve">13.519627571106</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7176132202148</t>
+    <t xml:space="preserve">13.7176113128662</t>
   </si>
   <si>
     <t xml:space="preserve">13.8307476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7600383758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9155988693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7458982467651</t>
+    <t xml:space="preserve">13.7600393295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.915599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7458972930908</t>
   </si>
   <si>
     <t xml:space="preserve">14.0428762435913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8448905944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5417680740356</t>
+    <t xml:space="preserve">13.8448886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.541766166687</t>
   </si>
   <si>
     <t xml:space="preserve">14.2218475341797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9455547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1782245635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9891815185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2073068618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4399757385254</t>
+    <t xml:space="preserve">13.9455556869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.17822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9891786575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2073087692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4399766921997</t>
   </si>
   <si>
     <t xml:space="preserve">14.265474319458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4108915328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.498143196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527240753174</t>
+    <t xml:space="preserve">14.4108905792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4981412887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690580368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527250289917</t>
   </si>
   <si>
     <t xml:space="preserve">14.3381824493408</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">14.5126829147339</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3963489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871871948242</t>
+    <t xml:space="preserve">14.3963499069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871852874756</t>
   </si>
   <si>
     <t xml:space="preserve">14.4254322052002</t>
@@ -1664,82 +1664,82 @@
     <t xml:space="preserve">14.4836006164551</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6144771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8326034545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9780206680298</t>
+    <t xml:space="preserve">14.6144752502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8326025009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9780216217041</t>
   </si>
   <si>
     <t xml:space="preserve">15.1234369277954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1961460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4142742156982</t>
+    <t xml:space="preserve">15.1961469650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4142732620239</t>
   </si>
   <si>
     <t xml:space="preserve">15.4506282806396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3415651321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2325019836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3052101135254</t>
+    <t xml:space="preserve">15.3415641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2325010299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3052091598511</t>
   </si>
   <si>
     <t xml:space="preserve">15.2688541412354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6687545776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0507297515869</t>
+    <t xml:space="preserve">15.6687536239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0507316589355</t>
   </si>
   <si>
     <t xml:space="preserve">15.0870847702026</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9416656494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7235374450684</t>
+    <t xml:space="preserve">14.9416646957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7235383987427</t>
   </si>
   <si>
     <t xml:space="preserve">15.0143747329712</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5781230926514</t>
+    <t xml:space="preserve">14.5781202316284</t>
   </si>
   <si>
     <t xml:space="preserve">14.7598934173584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6508302688599</t>
+    <t xml:space="preserve">14.6508283615112</t>
   </si>
   <si>
     <t xml:space="preserve">14.3672657012939</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3236398696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5272245407104</t>
+    <t xml:space="preserve">14.3236408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5272254943848</t>
   </si>
   <si>
     <t xml:space="preserve">14.4545154571533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7962484359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9053115844727</t>
+    <t xml:space="preserve">14.7962493896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.905312538147</t>
   </si>
   <si>
     <t xml:space="preserve">16.0322971343994</t>
@@ -1751,22 +1751,22 @@
     <t xml:space="preserve">16.5049076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6139698028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5412578582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8320960998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6503219604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.577615737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8684520721436</t>
+    <t xml:space="preserve">16.6139717102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.541259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8320980072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6503238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5776138305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8684501647949</t>
   </si>
   <si>
     <t xml:space="preserve">16.7593860626221</t>
@@ -1775,25 +1775,25 @@
     <t xml:space="preserve">17.0502223968506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.086576461792</t>
+    <t xml:space="preserve">17.0865783691406</t>
   </si>
   <si>
     <t xml:space="preserve">17.4864749908447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4137649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2683486938477</t>
+    <t xml:space="preserve">17.4137668609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.268346786499</t>
   </si>
   <si>
     <t xml:space="preserve">17.5228290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8136653900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7409572601318</t>
+    <t xml:space="preserve">17.813663482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7409553527832</t>
   </si>
   <si>
     <t xml:space="preserve">17.631893157959</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">17.7046031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6682453155518</t>
+    <t xml:space="preserve">17.6682472229004</t>
   </si>
   <si>
     <t xml:space="preserve">18.0681457519531</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">18.1044998168945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8500175476074</t>
+    <t xml:space="preserve">17.8500194549561</t>
   </si>
   <si>
     <t xml:space="preserve">17.9590835571289</t>
@@ -1832,22 +1832,22 @@
     <t xml:space="preserve">18.3589820861816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4680423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5771083831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9954357147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5591850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5955371856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4501209259033</t>
+    <t xml:space="preserve">18.4680442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5771064758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9954376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5591831207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5955390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4501190185547</t>
   </si>
   <si>
     <t xml:space="preserve">18.2499179840088</t>
@@ -1859,31 +1859,31 @@
     <t xml:space="preserve">18.2135620117188</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3226261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6134624481201</t>
+    <t xml:space="preserve">18.3226280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6134643554688</t>
   </si>
   <si>
     <t xml:space="preserve">18.6861705780029</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8315887451172</t>
+    <t xml:space="preserve">18.8315868377686</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9770069122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.086067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2678413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1224250793457</t>
+    <t xml:space="preserve">18.9770050048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0860691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.26784324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1224231719971</t>
   </si>
   <si>
     <t xml:space="preserve">19.3041954040527</t>
@@ -1892,37 +1892,37 @@
     <t xml:space="preserve">19.4132595062256</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4496154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.904806137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7230319976807</t>
+    <t xml:space="preserve">19.4496116638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9048042297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7230339050293</t>
   </si>
   <si>
     <t xml:space="preserve">16.4321975708008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7957382202148</t>
+    <t xml:space="preserve">16.7957420349121</t>
   </si>
   <si>
     <t xml:space="preserve">19.2314891815186</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9775142669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3047046661377</t>
+    <t xml:space="preserve">16.9775123596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3047027587891</t>
   </si>
   <si>
     <t xml:space="preserve">17.3774127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7952346801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5407524108887</t>
+    <t xml:space="preserve">18.7952327728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5407543182373</t>
   </si>
   <si>
     <t xml:space="preserve">18.8679428100586</t>
@@ -1934,25 +1934,25 @@
     <t xml:space="preserve">19.8495121002197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4213848114014</t>
+    <t xml:space="preserve">19.42138671875</t>
   </si>
   <si>
     <t xml:space="preserve">19.7327518463135</t>
   </si>
   <si>
-    <t xml:space="preserve">20.394401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8105926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549110412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3554821014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1219577789307</t>
+    <t xml:space="preserve">20.3944034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8105907440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3554801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.121955871582</t>
   </si>
   <si>
     <t xml:space="preserve">19.9273548126221</t>
@@ -1961,25 +1961,25 @@
     <t xml:space="preserve">19.4603061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3435459136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3046226501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.966272354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2657032012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7716693878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7597370147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1608772277832</t>
+    <t xml:space="preserve">19.3435440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3046245574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9662742614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2657051086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.771671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7597351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1608753204346</t>
   </si>
   <si>
     <t xml:space="preserve">20.044116973877</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">21.0560512542725</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9392871856689</t>
+    <t xml:space="preserve">20.9392890930176</t>
   </si>
   <si>
     <t xml:space="preserve">21.2895755767822</t>
@@ -2000,22 +2000,22 @@
     <t xml:space="preserve">21.0171318054199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7836093902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7057666778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.094970703125</t>
+    <t xml:space="preserve">20.7836074829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7057647705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0949745178223</t>
   </si>
   <si>
     <t xml:space="preserve">21.4452571868896</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7566223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9512233734131</t>
+    <t xml:space="preserve">21.7566261291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9512252807617</t>
   </si>
   <si>
     <t xml:space="preserve">21.6009407043457</t>
@@ -2024,16 +2024,16 @@
     <t xml:space="preserve">21.7955436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0290679931641</t>
+    <t xml:space="preserve">22.0290660858154</t>
   </si>
   <si>
     <t xml:space="preserve">22.0679874420166</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5350360870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5739555358887</t>
+    <t xml:space="preserve">22.5350341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.57395362854</t>
   </si>
   <si>
     <t xml:space="preserve">22.6517963409424</t>
@@ -2048,16 +2048,16 @@
     <t xml:space="preserve">22.7296390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3404312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2625904083252</t>
+    <t xml:space="preserve">22.3404331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2625923156738</t>
   </si>
   <si>
     <t xml:space="preserve">23.5080509185791</t>
   </si>
   <si>
-    <t xml:space="preserve">23.97509765625</t>
+    <t xml:space="preserve">23.9750957489014</t>
   </si>
   <si>
     <t xml:space="preserve">24.4032249450684</t>
@@ -2069,19 +2069,19 @@
     <t xml:space="preserve">24.7145881652832</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5199851989746</t>
+    <t xml:space="preserve">24.5199871063232</t>
   </si>
   <si>
     <t xml:space="preserve">25.298397064209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7924327850342</t>
+    <t xml:space="preserve">24.7924308776855</t>
   </si>
   <si>
     <t xml:space="preserve">25.1427154541016</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7535076141357</t>
+    <t xml:space="preserve">24.7535095214844</t>
   </si>
   <si>
     <t xml:space="preserve">24.6367454528809</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">23.0799236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7026557922363</t>
+    <t xml:space="preserve">23.7026538848877</t>
   </si>
   <si>
     <t xml:space="preserve">24.0529384613037</t>
@@ -2111,31 +2111,31 @@
     <t xml:space="preserve">23.1577644348145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8583335876465</t>
+    <t xml:space="preserve">23.8583354949951</t>
   </si>
   <si>
     <t xml:space="preserve">23.7415752410889</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8194160461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6637306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4302082061768</t>
+    <t xml:space="preserve">23.8194141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6637325286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4302101135254</t>
   </si>
   <si>
     <t xml:space="preserve">24.0918598175049</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3912868499756</t>
+    <t xml:space="preserve">23.3912887573242</t>
   </si>
   <si>
     <t xml:space="preserve">23.352367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0410022735596</t>
+    <t xml:space="preserve">23.0410041809082</t>
   </si>
   <si>
     <t xml:space="preserve">23.0020809173584</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">23.1188430786133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.624813079834</t>
+    <t xml:space="preserve">23.6248111724854</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128749847412</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">22.1847476959229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.496114730835</t>
+    <t xml:space="preserve">22.4961128234863</t>
   </si>
   <si>
     <t xml:space="preserve">22.3015117645264</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">22.3793525695801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9631633758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2356071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9242401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2236709594727</t>
+    <t xml:space="preserve">22.9631595611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2356052398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9242420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.223669052124</t>
   </si>
   <si>
     <t xml:space="preserve">22.4182739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9123020172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4841747283936</t>
+    <t xml:space="preserve">21.9123039245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4841766357422</t>
   </si>
   <si>
     <t xml:space="preserve">21.1338920593262</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">21.5230979919434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.717700958252</t>
+    <t xml:space="preserve">21.7177028656006</t>
   </si>
   <si>
     <t xml:space="preserve">21.6398601531982</t>
@@ -2204,34 +2204,34 @@
     <t xml:space="preserve">21.2506542205811</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5620212554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8344631195068</t>
+    <t xml:space="preserve">21.5620193481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8344612121582</t>
   </si>
   <si>
     <t xml:space="preserve">21.6787815093994</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9901485443115</t>
+    <t xml:space="preserve">21.9901447296143</t>
   </si>
   <si>
     <t xml:space="preserve">22.1458282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8464012145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8853187561035</t>
+    <t xml:space="preserve">22.846399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8853206634521</t>
   </si>
   <si>
     <t xml:space="preserve">22.4571933746338</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3284969329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2117328643799</t>
+    <t xml:space="preserve">21.3284931182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2117347717285</t>
   </si>
   <si>
     <t xml:space="preserve">21.3674163818359</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">20.9782104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6279239654541</t>
+    <t xml:space="preserve">20.6279258728027</t>
   </si>
   <si>
     <t xml:space="preserve">21.873384475708</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">23.440731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.88356590271</t>
+    <t xml:space="preserve">22.8835639953613</t>
   </si>
   <si>
     <t xml:space="preserve">22.7243747711182</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">22.8039703369141</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7641735076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0427570343018</t>
+    <t xml:space="preserve">22.7641716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0427551269531</t>
   </si>
   <si>
     <t xml:space="preserve">23.2417449951172</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">23.2019462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">23.122350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1621494293213</t>
+    <t xml:space="preserve">23.1223487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1621475219727</t>
   </si>
   <si>
     <t xml:space="preserve">23.5203247070312</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">23.9580993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0774898529053</t>
+    <t xml:space="preserve">24.0774917602539</t>
   </si>
   <si>
     <t xml:space="preserve">24.4356689453125</t>
@@ -2294,13 +2294,13 @@
     <t xml:space="preserve">24.3162746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3560752868652</t>
+    <t xml:space="preserve">24.3560733795166</t>
   </si>
   <si>
     <t xml:space="preserve">24.7938442230225</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1570873260498</t>
+    <t xml:space="preserve">24.1570854187012</t>
   </si>
   <si>
     <t xml:space="preserve">24.6744537353516</t>
@@ -2321,37 +2321,37 @@
     <t xml:space="preserve">24.1172885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5152645111084</t>
+    <t xml:space="preserve">24.5152626037598</t>
   </si>
   <si>
     <t xml:space="preserve">24.4754657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2366828918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3958721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7142486572266</t>
+    <t xml:space="preserve">24.2366809844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3958702087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7142505645752</t>
   </si>
   <si>
     <t xml:space="preserve">24.6346569061279</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1968841552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6295948028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5102005004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1520233154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3510131835938</t>
+    <t xml:space="preserve">24.1968822479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6295928955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5102024078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1520252227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3510112762451</t>
   </si>
   <si>
     <t xml:space="preserve">25.4704036712646</t>
@@ -2360,25 +2360,25 @@
     <t xml:space="preserve">25.6693916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3908100128174</t>
+    <t xml:space="preserve">25.3908081054688</t>
   </si>
   <si>
     <t xml:space="preserve">25.1918201446533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0326309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2714138031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8336429595947</t>
+    <t xml:space="preserve">25.0326328277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2714157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8336448669434</t>
   </si>
   <si>
     <t xml:space="preserve">24.9530372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8683795928955</t>
+    <t xml:space="preserve">25.8683776855469</t>
   </si>
   <si>
     <t xml:space="preserve">25.0724296569824</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">23.6397190093994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7989082336426</t>
+    <t xml:space="preserve">23.7989101409912</t>
   </si>
   <si>
     <t xml:space="preserve">24.5948581695557</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">25.3112125396729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2316188812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0673656463623</t>
+    <t xml:space="preserve">25.2316207885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0673675537109</t>
   </si>
   <si>
     <t xml:space="preserve">26.2663536071777</t>
@@ -2423,1044 +2423,1047 @@
     <t xml:space="preserve">26.0275688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7887878417969</t>
+    <t xml:space="preserve">25.7887840270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5499973297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5897960662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9479713439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1071624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7489852905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.873441696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0376949310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3263988494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3661994934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0825519561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.923360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3213386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5999221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3611354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4009342193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5601234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4855918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8387088775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.997896194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7193126678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8264102935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5692901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1263828277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9549713134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4692077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4263553619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1692371368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2120876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7835578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.340648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2549419403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2977962493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5264377593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.99782371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9121170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8692646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7407035827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6549968719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9693431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8836402893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5836658477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9264907836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1407585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.840784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7550792694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6693725585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0550498962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2264652252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7122268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4122524261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1836109161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0979061126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3694000244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3550262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0121994018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3121719360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3978748321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7979316711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4551067352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4979591369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6265201568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6978511810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5408134460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2693176269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2836933135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.426628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.469482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2552146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.826681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9267635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1410312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9980945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1266555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5267105102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6552696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3124446868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4410037994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6981220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5980415344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3837757110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5123329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3409214019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.026575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1122798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8123073577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1551322937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2408390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6837463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7266006469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8980121612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7694530487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6408939361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1979866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0694274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9837188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8551597595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1695079803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0838012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9408683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5551872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0409469604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9123878479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2980690002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2123622894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4838562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6124153137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7409763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1838836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3552951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.809741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7657089233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7216739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2813320159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0611591339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1051940917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.017126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8850250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.664852142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4887142181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9290561676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8409881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7088871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4006443023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7969551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9730911254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7529201507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.501501083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2372970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1932640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4134349822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3253650665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5455379486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.149227142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3125782012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1364402770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0483722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3566131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6208171844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2685432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4446811676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.532751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0043392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8722362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6960983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3438243865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6080303192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9162693023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8282012939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2557563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3878574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2997894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7841682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9603042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7401313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0924072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1804752349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6336078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4574699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5895709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8537769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0299129486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4702568054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5142917633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8665657043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3949756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.30690574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1307697296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3509407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4390106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5711116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7032146453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.319694519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8353176116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7472496032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8793525695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0867366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2188396453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.52707862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2628726959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9546337127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7600364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4077625274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8481063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1123104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1563453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4645862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5910167694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3708457946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8992595672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0313587188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5029487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7671546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2827758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0753974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7231216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.471700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.811185836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2387447357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4148826599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1506729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9745388031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7103309631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8424339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8864688873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5469837188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2955646514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7359104156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3836345672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9873237609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4276695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4632396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8007907867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8972339630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8490123748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7525691986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0418968200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6079063415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2703552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0292491912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9328060150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2221336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6916999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4023723602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5470352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7399196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0774707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5952568054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5596828460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2094860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7272720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1003952026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1486167907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4861660003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5826091766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4379444122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.052173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9075088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5343856811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9201583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8237152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1612663269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0165996551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7754936218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9683799743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3541488647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1130428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4988136291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6434783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8363628387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8845863342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6790523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.473518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2324123382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3770751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7146244049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6181812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6664028167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0039520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.245059967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8110656738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8592891693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3415031433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1968383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9557323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5699596405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2577075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3897228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2932796478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1841888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.280632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1359691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7501983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0877456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.991304397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8466396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.701976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5090923309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6055335998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7984180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5573120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6537551879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4252967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0395259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3644256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0750980377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6893291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7857723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9786548614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9304351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.219762802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8822135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1715412139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5928859710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3517780303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0268783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4126491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2679843902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1233196258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4608688354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8948612213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9430828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5446643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1462440490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8569183349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5675888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3391304016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8213443756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.255334854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9177856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1106719970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0142288208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8695659637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6766796112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2426872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6640319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6158103942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0371551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1209487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4940719604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2173919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8798408508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9407119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0853748321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.422924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.194465637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2909088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6284580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7731227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0499992370605</t>
   </si>
   <si>
     <t xml:space="preserve">25.5499992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5897979736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9479732513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1071624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7489852905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8734397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0376930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3263988494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3661975860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0825538635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9233646392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3213367462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5999202728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3611354827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4009323120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5601215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4855918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8387050628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9978942871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7193126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8264102935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5692901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1263828277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9549694061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4692077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4263553619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1692352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2120895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7835559844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.340648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2549419403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2977981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5264377593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.99782371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9121170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8692646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7407035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6549968719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9693431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8836402893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5836658477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.92649269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1407585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8407859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7550773620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6693744659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0550518035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2264652252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7122249603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4122524261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1836090087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0979061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3694000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3550243377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0121974945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3121719360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.397876739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7979316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4551086425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4979591369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6265182495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6978492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5408115386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2693176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2836933135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.426628112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4694805145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2552146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.826681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9267616271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1410293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9980964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1266536712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5267105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6552696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.312442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4410037994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6981220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5980415344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3837757110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.512336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3409194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0265731811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1122798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8123073577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1551342010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2408390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6837482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7266006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8980140686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7694530487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6408939361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1979866027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0694274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9837207794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8551597595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1695079803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0838012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9408664703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5551853179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0409488677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.912389755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2980690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2123622894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4838562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6124153137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7409763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1838817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3552951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.809741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7657089233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7216739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2813320159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0611591339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1051959991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.017126083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8850250244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.664852142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5767841339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4887161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9290561676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8409881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7088851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4006462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7969551086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9730930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7529201507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5015029907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2372970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1932640075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4134349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3253650665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5455360412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.149227142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3125782012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1364402770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0483722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3566112518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6208171844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2685432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4446811676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5327491760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0043392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8722343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6960983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3438243865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6080303192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9162693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8282012939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2557563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3878593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2997894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7841682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9603023529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7401313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0924072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1804752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6336059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4574680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5895709991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8537769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0299129486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4702568054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5142917633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8665657043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3949756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3069076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1307697296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3509407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4390087127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5711135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6591815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7032146453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.319694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8353176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7472496032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8793525695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0867366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2188377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.52707862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2628726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9546337127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7600383758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4077625274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8481063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1123104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1563472747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4645843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5910148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3708438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8992576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0313587188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5029487609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7671527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2827777862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0753955841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7231216430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.471700668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8111877441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2387447357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4148826599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1506729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9745388031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7103309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.842435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8864688873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5469818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2955665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7359104156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3836326599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9873237609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4276676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4632396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8007907867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8972339630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8490123748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7525691986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0418968200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6079063415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2703552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0292491912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9328060150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2221336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6916999816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4023723602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5470352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7399196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0774707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5952568054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5596828460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2094860076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7272720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1003952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1486167907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4861660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5826091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4379444122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.052173614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9075088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5343856811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9201583862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8237152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1612663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0165996551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7754936218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9683799743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3541488647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1130428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4988136291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6434783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8363628387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8845863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6790523529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.473518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2324123382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3770751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7146244049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6181812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6664028167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0039520263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.245059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8110656738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8592891693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3415031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1968383789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9557323455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5699596405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2577075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3897228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2932796478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1841888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.280632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1359691619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7501983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0877456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.991304397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8466396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.701976776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5090923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6055335998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7984180450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5573120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6537551879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4252967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0395259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3644256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0750980377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6893291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7857723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9786548614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9304351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.219762802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8822135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1715412139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5928859710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3517780303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0268783569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4126491546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2679843902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1233196258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4608688354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8948612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9430828094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5446643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1462440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8569183349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5675888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3391304016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8213443756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.255334854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3999996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9177856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1106719970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0142288208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8695659637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6766796112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2426872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6640319824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6158103942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0371551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1209487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4940719604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2173919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8798408508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9407119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0853748321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.422924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.194465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2909088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6284580230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7731227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3500003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2000007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8500003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7000007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8999996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2000007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6000003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8500003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7000007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8999996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0499992370605</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.1499996185303</t>
   </si>
   <si>
@@ -3714,6 +3717,9 @@
   </si>
   <si>
     <t xml:space="preserve">28.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
   </si>
 </sst>
 </file>
@@ -66132,7 +66138,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G2388" t="s">
-        <v>804</v>
+        <v>1149</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66158,7 +66164,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66184,7 +66190,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66210,7 +66216,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G2391" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66236,7 +66242,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66262,7 +66268,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66288,7 +66294,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66314,7 +66320,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66340,7 +66346,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G2396" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66366,7 +66372,7 @@
         <v>26.75</v>
       </c>
       <c r="G2397" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66392,7 +66398,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2398" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66418,7 +66424,7 @@
         <v>27</v>
       </c>
       <c r="G2399" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66444,7 +66450,7 @@
         <v>27</v>
       </c>
       <c r="G2400" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66470,7 +66476,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66496,7 +66502,7 @@
         <v>26.25</v>
       </c>
       <c r="G2402" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66522,7 +66528,7 @@
         <v>25.5</v>
       </c>
       <c r="G2403" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66548,7 +66554,7 @@
         <v>25.25</v>
       </c>
       <c r="G2404" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66600,7 +66606,7 @@
         <v>25.25</v>
       </c>
       <c r="G2406" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66652,7 +66658,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G2408" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66678,7 +66684,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G2409" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66704,7 +66710,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G2410" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66730,7 +66736,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2411" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66756,7 +66762,7 @@
         <v>25.5</v>
       </c>
       <c r="G2412" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66808,7 +66814,7 @@
         <v>26</v>
       </c>
       <c r="G2414" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66834,7 +66840,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2415" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66860,7 +66866,7 @@
         <v>27</v>
       </c>
       <c r="G2416" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66886,7 +66892,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66912,7 +66918,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G2418" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66938,7 +66944,7 @@
         <v>27.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66964,7 +66970,7 @@
         <v>27.5</v>
       </c>
       <c r="G2420" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66990,7 +66996,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67016,7 +67022,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2422" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67042,7 +67048,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G2423" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67068,7 +67074,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2424" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67094,7 +67100,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G2425" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67120,7 +67126,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2426" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67146,7 +67152,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2427" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67172,7 +67178,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2428" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67198,7 +67204,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2429" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67224,7 +67230,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67250,7 +67256,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67276,7 +67282,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2432" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67302,7 +67308,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67328,7 +67334,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G2434" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67354,7 +67360,7 @@
         <v>29</v>
       </c>
       <c r="G2435" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67380,7 +67386,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G2436" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67406,7 +67412,7 @@
         <v>28.25</v>
       </c>
       <c r="G2437" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67432,7 +67438,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G2438" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67458,7 +67464,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67484,7 +67490,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2440" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67510,7 +67516,7 @@
         <v>27</v>
       </c>
       <c r="G2441" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67536,7 +67542,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2442" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67562,7 +67568,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G2443" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67588,7 +67594,7 @@
         <v>27.25</v>
       </c>
       <c r="G2444" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67614,7 +67620,7 @@
         <v>27.25</v>
       </c>
       <c r="G2445" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67640,7 +67646,7 @@
         <v>27.25</v>
       </c>
       <c r="G2446" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67666,7 +67672,7 @@
         <v>27.25</v>
       </c>
       <c r="G2447" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67692,7 +67698,7 @@
         <v>27.5</v>
       </c>
       <c r="G2448" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67718,7 +67724,7 @@
         <v>27.75</v>
       </c>
       <c r="G2449" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67744,7 +67750,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G2450" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67770,7 +67776,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G2451" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67796,7 +67802,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G2452" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67822,7 +67828,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G2453" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67848,7 +67854,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G2454" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67874,7 +67880,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G2455" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67900,7 +67906,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67926,7 +67932,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67952,7 +67958,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G2458" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67978,7 +67984,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G2459" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68004,7 +68010,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G2460" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68030,7 +68036,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2461" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68056,7 +68062,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68082,7 +68088,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68108,7 +68114,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68134,7 +68140,7 @@
         <v>28.75</v>
       </c>
       <c r="G2465" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68160,7 +68166,7 @@
         <v>29</v>
       </c>
       <c r="G2466" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68186,7 +68192,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68212,7 +68218,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G2468" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68238,7 +68244,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68264,7 +68270,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68290,7 +68296,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68316,7 +68322,7 @@
         <v>29.9500007629395</v>
       </c>
       <c r="G2472" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68342,7 +68348,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68368,7 +68374,7 @@
         <v>30</v>
       </c>
       <c r="G2474" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68394,7 +68400,7 @@
         <v>29.75</v>
       </c>
       <c r="G2475" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68420,7 +68426,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G2476" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68446,7 +68452,7 @@
         <v>30</v>
       </c>
       <c r="G2477" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68472,7 +68478,7 @@
         <v>30.5</v>
       </c>
       <c r="G2478" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68498,7 +68504,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G2479" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68524,7 +68530,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68550,7 +68556,7 @@
         <v>31.25</v>
       </c>
       <c r="G2481" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68576,7 +68582,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G2482" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68602,7 +68608,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68628,7 +68634,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68654,7 +68660,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G2485" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68680,7 +68686,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G2486" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68706,7 +68712,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G2487" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68732,7 +68738,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2488" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68758,7 +68764,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2489" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68784,7 +68790,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G2490" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68810,7 +68816,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G2491" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68836,7 +68842,7 @@
         <v>32.5</v>
       </c>
       <c r="G2492" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68862,7 +68868,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G2493" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68888,7 +68894,7 @@
         <v>33</v>
       </c>
       <c r="G2494" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68914,7 +68920,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G2495" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68940,7 +68946,7 @@
         <v>33</v>
       </c>
       <c r="G2496" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68966,7 +68972,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G2497" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68992,7 +68998,7 @@
         <v>33.5</v>
       </c>
       <c r="G2498" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69018,7 +69024,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G2499" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69044,7 +69050,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G2500" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69070,7 +69076,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G2501" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69096,7 +69102,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G2502" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69122,7 +69128,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G2503" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69148,7 +69154,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2504" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69174,7 +69180,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G2505" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -69200,7 +69206,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G2506" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -69226,7 +69232,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G2507" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -69252,7 +69258,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G2508" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -69278,7 +69284,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G2509" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -69304,7 +69310,7 @@
         <v>29.25</v>
       </c>
       <c r="G2510" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -69312,7 +69318,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.6913078704</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>47579</v>
@@ -69330,9 +69336,35 @@
         <v>28.5</v>
       </c>
       <c r="G2511" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6910300926</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>31697</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>29.1000003814697</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>29.1000003814697</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>28</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="1238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="1237">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8067150115967</t>
+    <t xml:space="preserve">13.806715965271</t>
   </si>
   <si>
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577440261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9573316574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3883275985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.889612197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8527965545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9532079696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6184988021851</t>
+    <t xml:space="preserve">14.0577449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9573345184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3883285522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896150588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8527956008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9532070159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6184997558594</t>
   </si>
   <si>
     <t xml:space="preserve">12.4846162796021</t>
@@ -77,25 +77,25 @@
     <t xml:space="preserve">11.7348709106445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2127246856689</t>
+    <t xml:space="preserve">11.2127265930176</t>
   </si>
   <si>
     <t xml:space="preserve">10.7307453155518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2294588088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2194194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2461957931519</t>
+    <t xml:space="preserve">11.2294597625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2194204330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2461948394775</t>
   </si>
   <si>
     <t xml:space="preserve">10.9148349761963</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1323938369751</t>
+    <t xml:space="preserve">11.1323957443237</t>
   </si>
   <si>
     <t xml:space="preserve">11.6143741607666</t>
@@ -104,28 +104,28 @@
     <t xml:space="preserve">11.6813173294067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474309921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3466110229492</t>
+    <t xml:space="preserve">11.5474328994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3466091156006</t>
   </si>
   <si>
     <t xml:space="preserve">11.3131380081177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.329873085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8947534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8780164718628</t>
+    <t xml:space="preserve">11.3298711776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8947525024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8780174255371</t>
   </si>
   <si>
     <t xml:space="preserve">11.045371055603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4261608123779</t>
+    <t xml:space="preserve">10.4261617660522</t>
   </si>
   <si>
     <t xml:space="preserve">10.4094257354736</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">11.7080936431885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.714789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0494956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7482585906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7449102401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2135038375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168502807617</t>
+    <t xml:space="preserve">11.7147884368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0494976043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7482576370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7449111938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2135019302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168493270874</t>
   </si>
   <si>
     <t xml:space="preserve">12.3674688339233</t>
@@ -161,67 +161,67 @@
     <t xml:space="preserve">12.8293685913086</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0201501846313</t>
+    <t xml:space="preserve">13.0201511383057</t>
   </si>
   <si>
     <t xml:space="preserve">13.2209749221802</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3849830627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536203384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3347749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3146924972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569658279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109336853027</t>
+    <t xml:space="preserve">13.3849821090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870904922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3347768783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3146915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569667816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109346389771</t>
   </si>
   <si>
     <t xml:space="preserve">12.8661842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1306037902832</t>
+    <t xml:space="preserve">13.1306047439575</t>
   </si>
   <si>
     <t xml:space="preserve">13.2879180908203</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8260202407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9833316802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9030027389526</t>
+    <t xml:space="preserve">12.8260183334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9833326339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.903000831604</t>
   </si>
   <si>
     <t xml:space="preserve">13.2377099990845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.167423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1138668060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.097131729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5047016143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8092842102051</t>
+    <t xml:space="preserve">13.1674213409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1138687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971326828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5046997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8092832565308</t>
   </si>
   <si>
     <t xml:space="preserve">12.886266708374</t>
@@ -230,280 +230,280 @@
     <t xml:space="preserve">12.7055234909058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7222585678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.916392326355</t>
+    <t xml:space="preserve">12.7222576141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9163913726807</t>
   </si>
   <si>
     <t xml:space="preserve">13.0301904678345</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8327121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.631890296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7021770477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8695297241211</t>
+    <t xml:space="preserve">12.8327131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6318893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7021780014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8695306777954</t>
   </si>
   <si>
     <t xml:space="preserve">12.5582523345947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5682945251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8360614776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494482040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958955764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5348224639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7791604995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7691173553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7865676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5024185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6512584686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7527379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5836038589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4990367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5700740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159502029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2791624069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0660524368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776819229126</t>
+    <t xml:space="preserve">12.5682935714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8360595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494501113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958946228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5348215103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7791595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7691192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7865648269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.502420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6512594223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7527389526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5836067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4990377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5700731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159521102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2791614532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0660543441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776828765869</t>
   </si>
   <si>
     <t xml:space="preserve">12.1641511917114</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1709175109863</t>
+    <t xml:space="preserve">12.170916557312</t>
   </si>
   <si>
     <t xml:space="preserve">12.1100273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1269407272339</t>
+    <t xml:space="preserve">12.1269397735596</t>
   </si>
   <si>
     <t xml:space="preserve">11.9814853668213</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7459745407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580247879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231382369995</t>
+    <t xml:space="preserve">12.7459735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580238342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231372833252</t>
   </si>
   <si>
     <t xml:space="preserve">11.697340965271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7785243988037</t>
+    <t xml:space="preserve">11.7785234451294</t>
   </si>
   <si>
     <t xml:space="preserve">11.2406768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8212232589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554727554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0613946914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1967000961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4064283370972</t>
+    <t xml:space="preserve">10.8212251663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554708480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0613956451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.196702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4064292907715</t>
   </si>
   <si>
     <t xml:space="preserve">11.5248222351074</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6656198501587</t>
+    <t xml:space="preserve">10.665620803833</t>
   </si>
   <si>
     <t xml:space="preserve">10.1886606216431</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5878171920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6825332641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8394136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0199718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3616218566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0233564376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1924886703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4969329833984</t>
+    <t xml:space="preserve">10.5878190994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6825342178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.839412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0199728012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3616228103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0233545303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1924896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4969320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.4698686599731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5307559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.480016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2939701080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108806610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0740957260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.036883354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9489326477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827604293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.091007232666</t>
+    <t xml:space="preserve">13.5307579040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4800186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2939682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548564910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0740938186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.03688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9489345550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9827632904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0910062789917</t>
   </si>
   <si>
     <t xml:space="preserve">13.0707120895386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9962921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8576021194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113052368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1248340606689</t>
+    <t xml:space="preserve">12.9962902069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8576011657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113042831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1248359680176</t>
   </si>
   <si>
     <t xml:space="preserve">13.1823406219482</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0605640411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857242584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4123640060425</t>
+    <t xml:space="preserve">13.0605630874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857233047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4123630523682</t>
   </si>
   <si>
     <t xml:space="preserve">13.5679683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4157457351685</t>
+    <t xml:space="preserve">13.4157466888428</t>
   </si>
   <si>
     <t xml:space="preserve">13.513843536377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7066583633423</t>
+    <t xml:space="preserve">13.7066564559937</t>
   </si>
   <si>
     <t xml:space="preserve">13.8352012634277</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2106781005859</t>
+    <t xml:space="preserve">14.2106771469116</t>
   </si>
   <si>
     <t xml:space="preserve">14.457615852356</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7552909851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838329315186</t>
+    <t xml:space="preserve">14.7552890777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838319778442</t>
   </si>
   <si>
     <t xml:space="preserve">15.01575756073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9853134155273</t>
+    <t xml:space="preserve">14.9853143692017</t>
   </si>
   <si>
     <t xml:space="preserve">15.3303489685059</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6652374267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2897548675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8297128677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7722034454346</t>
+    <t xml:space="preserve">15.6652336120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.289755821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8297100067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6842555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7722024917603</t>
   </si>
   <si>
     <t xml:space="preserve">14.951488494873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7485237121582</t>
+    <t xml:space="preserve">14.7485256195068</t>
   </si>
   <si>
     <t xml:space="preserve">14.7180814743042</t>
@@ -512,52 +512,52 @@
     <t xml:space="preserve">14.877067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992639541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751653671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.90074634552</t>
+    <t xml:space="preserve">14.7992658615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9007482528687</t>
   </si>
   <si>
     <t xml:space="preserve">15.2018051147461</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8939819335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330926895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988451004028</t>
+    <t xml:space="preserve">14.8939809799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330936431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988431930542</t>
   </si>
   <si>
     <t xml:space="preserve">14.9142770767212</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9278087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7383785247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7248468399048</t>
+    <t xml:space="preserve">14.927809715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7383794784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7248458862305</t>
   </si>
   <si>
     <t xml:space="preserve">14.5421829223633</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4440832138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0529680252075</t>
+    <t xml:space="preserve">14.4440841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0529699325562</t>
   </si>
   <si>
     <t xml:space="preserve">15.1442995071411</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1104736328125</t>
+    <t xml:space="preserve">15.1104717254639</t>
   </si>
   <si>
     <t xml:space="preserve">14.954870223999</t>
@@ -566,211 +566,211 @@
     <t xml:space="preserve">15.0901775360107</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2187194824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7823524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6166009902954</t>
+    <t xml:space="preserve">15.2187204360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7823505401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6166019439697</t>
   </si>
   <si>
     <t xml:space="preserve">14.3764314651489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1599388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2546529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0415420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1125812530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0381603240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1430234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527517318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.207293510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3561334609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3087749481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2411231994629</t>
+    <t xml:space="preserve">14.1599369049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2546539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0415439605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1125793457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0381631851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1430253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903820037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2072954177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3561315536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373188018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3087768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2411222457886</t>
   </si>
   <si>
     <t xml:space="preserve">14.3392190933228</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2512722015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.146409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058130264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1193466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2275924682617</t>
+    <t xml:space="preserve">14.2512702941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1464080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058168411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1193475723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2275943756104</t>
   </si>
   <si>
     <t xml:space="preserve">14.2715654373169</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1497888565063</t>
+    <t xml:space="preserve">14.149790763855</t>
   </si>
   <si>
     <t xml:space="preserve">14.0753707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0719871520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667022705078</t>
+    <t xml:space="preserve">14.0719861984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667032241821</t>
   </si>
   <si>
     <t xml:space="preserve">14.4779109954834</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6267499923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7519083023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8161783218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1037073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0834131240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882753372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172380447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1544466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999067306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758033752441</t>
+    <t xml:space="preserve">14.6267490386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7519102096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.816180229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.103705406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0834102630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1544485092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758043289185</t>
   </si>
   <si>
     <t xml:space="preserve">15.3574113845825</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3912401199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893341064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1713609695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.100323677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946180343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3168153762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.313437461853</t>
+    <t xml:space="preserve">15.3912363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893350601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1713600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1003246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946199417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3168201446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3134355545044</t>
   </si>
   <si>
     <t xml:space="preserve">15.4182987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4250631332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366945266724</t>
+    <t xml:space="preserve">15.4250650405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366916656494</t>
   </si>
   <si>
     <t xml:space="preserve">15.6753816604614</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6449384689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7295083999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6618490219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6517066955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.682147026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637550354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081525802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415567398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7024440765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584672927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588899612427</t>
+    <t xml:space="preserve">15.6449403762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7295055389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6618528366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6517057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6821479797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637540817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081497192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415576934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7024431228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.65846824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588918685913</t>
   </si>
   <si>
     <t xml:space="preserve">15.5874338150024</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6550874710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227382659912</t>
+    <t xml:space="preserve">15.6550884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227401733398</t>
   </si>
   <si>
     <t xml:space="preserve">16.3350086212158</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">16.4026622772217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4195747375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6935729980469</t>
+    <t xml:space="preserve">16.4195728302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6935710906982</t>
   </si>
   <si>
     <t xml:space="preserve">17.099494934082</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">16.9980144500732</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1671485900879</t>
+    <t xml:space="preserve">17.1671466827393</t>
   </si>
   <si>
     <t xml:space="preserve">17.4208507537842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5392456054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6407260894775</t>
+    <t xml:space="preserve">17.5392436981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6407241821289</t>
   </si>
   <si>
     <t xml:space="preserve">17.4039363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.48850440979</t>
+    <t xml:space="preserve">17.4885063171387</t>
   </si>
   <si>
     <t xml:space="preserve">17.3531951904297</t>
@@ -821,16 +821,16 @@
     <t xml:space="preserve">17.3870239257812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5223293304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4546775817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8775119781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8098602294922</t>
+    <t xml:space="preserve">17.522331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4546794891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.877513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8098583221436</t>
   </si>
   <si>
     <t xml:space="preserve">17.7083797454834</t>
@@ -842,97 +842,97 @@
     <t xml:space="preserve">17.6745529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5730743408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3362827301025</t>
+    <t xml:space="preserve">17.5730724334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3362846374512</t>
   </si>
   <si>
     <t xml:space="preserve">17.2009754180908</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2348041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2517166137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.217887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3701076507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.456018447876</t>
+    <t xml:space="preserve">17.2348022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2517147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2178859710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3701095581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4560203552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.7147541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5767612457275</t>
+    <t xml:space="preserve">17.5767650604248</t>
   </si>
   <si>
     <t xml:space="preserve">17.559513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6975059509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4698219299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.614709854126</t>
+    <t xml:space="preserve">17.6975078582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.469820022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6147117614746</t>
   </si>
   <si>
     <t xml:space="preserve">16.7729568481445</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0075435638428</t>
+    <t xml:space="preserve">17.00754737854</t>
   </si>
   <si>
     <t xml:space="preserve">17.1662349700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1317386627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.993745803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9868450164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9661483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.835054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8488540649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8281536102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.759162902832</t>
+    <t xml:space="preserve">17.1317367553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9937477111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9868469238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9661464691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8350524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.84885597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8281555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7591609954834</t>
   </si>
   <si>
     <t xml:space="preserve">16.8695526123047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9178524017334</t>
+    <t xml:space="preserve">16.9178504943848</t>
   </si>
   <si>
     <t xml:space="preserve">16.9730472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.938549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1524391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6625633239746</t>
+    <t xml:space="preserve">16.9385471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.152437210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6625652313232</t>
   </si>
   <si>
     <t xml:space="preserve">16.5935668945312</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">16.5659694671631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5038719177246</t>
+    <t xml:space="preserve">16.5038738250732</t>
   </si>
   <si>
     <t xml:space="preserve">16.8626537322998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9040489196777</t>
+    <t xml:space="preserve">16.9040508270264</t>
   </si>
   <si>
     <t xml:space="preserve">16.80055809021</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">16.8971519470215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5383720397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5590724945068</t>
+    <t xml:space="preserve">16.5383739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5590705871582</t>
   </si>
   <si>
     <t xml:space="preserve">16.4900741577148</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">16.2416877746582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.303783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2485885620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1243934631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1864910125732</t>
+    <t xml:space="preserve">16.3037815093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2485866546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1243953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1864929199219</t>
   </si>
   <si>
     <t xml:space="preserve">16.1588935852051</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">16.5314712524414</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2899875640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3175830841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5452709197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3658809661865</t>
+    <t xml:space="preserve">16.2899856567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3175849914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5452690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3658790588379</t>
   </si>
   <si>
     <t xml:space="preserve">16.4624767303467</t>
@@ -1007,76 +1007,76 @@
     <t xml:space="preserve">16.3520812988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6970634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3865795135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4486770629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5107727050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4210777282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4348773956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3934803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4969749450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5245723724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4003791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4555759429932</t>
+    <t xml:space="preserve">16.6970615386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3865814208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4486751556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5107746124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4210796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4348754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3934783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4969730377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5245742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4003772735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4555740356445</t>
   </si>
   <si>
     <t xml:space="preserve">16.358980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2830848693848</t>
+    <t xml:space="preserve">16.283088684082</t>
   </si>
   <si>
     <t xml:space="preserve">16.5521697998047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1795921325684</t>
+    <t xml:space="preserve">16.179594039917</t>
   </si>
   <si>
     <t xml:space="preserve">16.2071876525879</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1933879852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.903603553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5586252212524</t>
+    <t xml:space="preserve">16.1933917999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9036083221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5586271286011</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965295791626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9381055831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7794160842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7656145095825</t>
+    <t xml:space="preserve">15.9381065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7794151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7656135559082</t>
   </si>
   <si>
     <t xml:space="preserve">15.7863130569458</t>
@@ -1085,25 +1085,25 @@
     <t xml:space="preserve">15.9795026779175</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9312057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.703516960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6483211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8415079116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7518157958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691082000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8622102737427</t>
+    <t xml:space="preserve">15.9312047958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7035188674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6483192443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8415107727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7518167495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691072463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8622093200684</t>
   </si>
   <si>
     <t xml:space="preserve">16.0277996063232</t>
@@ -1112,64 +1112,64 @@
     <t xml:space="preserve">15.8967065811157</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6276226043701</t>
+    <t xml:space="preserve">15.6276216506958</t>
   </si>
   <si>
     <t xml:space="preserve">15.7173185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">15.53102684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034303665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.441330909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2481441497803</t>
+    <t xml:space="preserve">15.5310297012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034294128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413299560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2481451034546</t>
   </si>
   <si>
     <t xml:space="preserve">15.3171396255493</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3309364318848</t>
+    <t xml:space="preserve">15.3309392929077</t>
   </si>
   <si>
     <t xml:space="preserve">15.2826414108276</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3792371749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619428634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.600022315979</t>
+    <t xml:space="preserve">15.3792400360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.26194190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.600025177002</t>
   </si>
   <si>
     <t xml:space="preserve">15.4896297454834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.951904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9726047515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9864025115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.041597366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8553104400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.793212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758329391479</t>
+    <t xml:space="preserve">15.9519062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9726028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.986400604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0416011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8553085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932109832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758310317993</t>
   </si>
   <si>
     <t xml:space="preserve">15.2895412445068</t>
@@ -1178,31 +1178,31 @@
     <t xml:space="preserve">15.1791486740112</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2067470550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3999357223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2343463897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3033418655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137344360352</t>
+    <t xml:space="preserve">15.2067441940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3999347686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2343435287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137334823608</t>
   </si>
   <si>
     <t xml:space="preserve">15.3861351013184</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6345233917236</t>
+    <t xml:space="preserve">15.634521484375</t>
   </si>
   <si>
     <t xml:space="preserve">16.145092010498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.48317527771</t>
+    <t xml:space="preserve">16.4831733703613</t>
   </si>
   <si>
     <t xml:space="preserve">16.6073684692383</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">16.37278175354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6349639892578</t>
+    <t xml:space="preserve">16.6349678039551</t>
   </si>
   <si>
     <t xml:space="preserve">16.4141788482666</t>
@@ -1220,31 +1220,31 @@
     <t xml:space="preserve">16.0898971557617</t>
   </si>
   <si>
-    <t xml:space="preserve">16.200288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7315616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6901626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4762725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7522583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6487655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6280651092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0420436859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0765419006348</t>
+    <t xml:space="preserve">16.2002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.731559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.69016456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4762744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7522621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6487636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6280670166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0420455932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0765399932861</t>
   </si>
   <si>
     <t xml:space="preserve">17.1110382080078</t>
@@ -1253,82 +1253,82 @@
     <t xml:space="preserve">17.2145347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1455345153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1800365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.00710105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.21409034729</t>
+    <t xml:space="preserve">17.1455364227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1800346374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0071029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2140865325928</t>
   </si>
   <si>
     <t xml:space="preserve">16.110595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5931262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621217727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0066566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7306747436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9031648635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9721603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.455132484436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1101493835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0411558151245</t>
+    <t xml:space="preserve">15.5931234359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0066556930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7306728363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9031629562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9721612930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551334381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1101484298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0411548614502</t>
   </si>
   <si>
     <t xml:space="preserve">15.0756540298462</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3516368865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4206323623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5241289138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6966199874878</t>
+    <t xml:space="preserve">15.351637840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4206342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5241279602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6966190338135</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8742485046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.556056022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7328290939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914106369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3439283370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792839050293</t>
+    <t xml:space="preserve">15.87424659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5560579299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7328300476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914087295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3439292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792819976807</t>
   </si>
   <si>
     <t xml:space="preserve">14.7782526016235</t>
@@ -1337,64 +1337,64 @@
     <t xml:space="preserve">14.4247064590454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5307703018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600629806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.495415687561</t>
+    <t xml:space="preserve">14.5307712554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600620269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4954166412354</t>
   </si>
   <si>
     <t xml:space="preserve">13.8873167037964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1135854721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.318642616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6014795303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0257377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.061089515686</t>
+    <t xml:space="preserve">14.1135845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3186407089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6014804840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0257368087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0610904693604</t>
   </si>
   <si>
     <t xml:space="preserve">14.9550266265869</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8489627838135</t>
+    <t xml:space="preserve">14.8489637374878</t>
   </si>
   <si>
     <t xml:space="preserve">14.8843173980713</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7075443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671552658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.202507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5661249160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6368360519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2832860946655</t>
+    <t xml:space="preserve">14.7075424194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671543121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2025089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.566125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6368350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2832880020142</t>
   </si>
   <si>
     <t xml:space="preserve">14.085301399231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8136081695557</t>
+    <t xml:space="preserve">14.813606262207</t>
   </si>
   <si>
     <t xml:space="preserve">14.3539962768555</t>
@@ -1403,40 +1403,40 @@
     <t xml:space="preserve">14.3893518447876</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7428970336914</t>
+    <t xml:space="preserve">14.7428979873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.1418695449829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1772232055664</t>
+    <t xml:space="preserve">14.1772241592407</t>
   </si>
   <si>
     <t xml:space="preserve">14.2479333877563</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2125806808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0711603164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9438829421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8731746673584</t>
+    <t xml:space="preserve">14.2125797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0711584091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.943883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8731727600098</t>
   </si>
   <si>
     <t xml:space="preserve">13.8166065216064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8590316772461</t>
+    <t xml:space="preserve">13.8590326309204</t>
   </si>
   <si>
     <t xml:space="preserve">14.0145921707153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9297428131104</t>
+    <t xml:space="preserve">13.929741859436</t>
   </si>
   <si>
     <t xml:space="preserve">14.0004501342773</t>
@@ -1445,52 +1445,52 @@
     <t xml:space="preserve">14.0994434356689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9721670150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0287342071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.057017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1277275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9196710586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6721868515015</t>
+    <t xml:space="preserve">13.9721651077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.028733253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570182800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.127724647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9196739196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6721897125244</t>
   </si>
   <si>
     <t xml:space="preserve">13.434775352478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.505485534668</t>
+    <t xml:space="preserve">13.5054864883423</t>
   </si>
   <si>
     <t xml:space="preserve">13.49134349823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3782091140747</t>
+    <t xml:space="preserve">13.3782081604004</t>
   </si>
   <si>
     <t xml:space="preserve">13.4630603790283</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5620527267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.533766746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1660814285278</t>
+    <t xml:space="preserve">13.5620546340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5337677001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1660823822021</t>
   </si>
   <si>
     <t xml:space="preserve">12.7842502593994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6852579116821</t>
+    <t xml:space="preserve">12.6852569580078</t>
   </si>
   <si>
     <t xml:space="preserve">12.1620073318481</t>
@@ -1499,37 +1499,37 @@
     <t xml:space="preserve">12.6569709777832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4064912796021</t>
+    <t xml:space="preserve">13.4064922332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.5479116439819</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7883214950562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7741804122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5903348922729</t>
+    <t xml:space="preserve">13.7883224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7741794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5903367996216</t>
   </si>
   <si>
     <t xml:space="preserve">13.4489183425903</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074979782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.392352104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0105209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1519365310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2933568954468</t>
+    <t xml:space="preserve">13.3074989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3923492431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0105199813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1519393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2933559417725</t>
   </si>
   <si>
     <t xml:space="preserve">12.9256687164307</t>
@@ -1538,85 +1538,85 @@
     <t xml:space="preserve">13.0388021469116</t>
   </si>
   <si>
-    <t xml:space="preserve">12.996376991272</t>
+    <t xml:space="preserve">12.9963760375977</t>
   </si>
   <si>
     <t xml:space="preserve">13.2367887496948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0953712463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6469049453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6751871109009</t>
+    <t xml:space="preserve">13.0953702926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6469030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6751880645752</t>
   </si>
   <si>
     <t xml:space="preserve">13.0670871734619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2509326934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2085075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812282562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3499231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8408164978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5296945571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8973865509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6004047393799</t>
+    <t xml:space="preserve">13.2509317398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2085056304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812292098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3499250411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8408174514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5296964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8973836898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6004037857056</t>
   </si>
   <si>
     <t xml:space="preserve">13.7317552566528</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5761966705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5196256637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7176103591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8307485580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7600374221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9155988693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7458982467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0428771972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8448896408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5417652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2218503952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9455547332764</t>
+    <t xml:space="preserve">13.5761938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5196266174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7176132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8307476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7600383758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9156007766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7458963394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0428791046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8448886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5417680740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.221848487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.945556640625</t>
   </si>
   <si>
     <t xml:space="preserve">14.1782236099243</t>
@@ -1625,43 +1625,43 @@
     <t xml:space="preserve">13.9891805648804</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2073078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4399757385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.265474319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4108915328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4981412887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690599441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527250289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3381834030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5126838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3963489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871862411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4254341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4835996627808</t>
+    <t xml:space="preserve">14.2073087692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4399766921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2654733657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4108924865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4981422424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690570831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527231216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3381824493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5126829147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3963479995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871871948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4254331588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4836015701294</t>
   </si>
   <si>
     <t xml:space="preserve">14.6144752502441</t>
@@ -1670,55 +1670,55 @@
     <t xml:space="preserve">14.8326025009155</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9780216217041</t>
+    <t xml:space="preserve">14.9780197143555</t>
   </si>
   <si>
     <t xml:space="preserve">15.1234369277954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1961469650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4142742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.450629234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3415651321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2325019836426</t>
+    <t xml:space="preserve">15.1961460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4142732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4506282806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3415660858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2325010299683</t>
   </si>
   <si>
     <t xml:space="preserve">15.3052101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2688550949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687526702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0507316589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.087082862854</t>
+    <t xml:space="preserve">15.268856048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687545776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0507297515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0870838165283</t>
   </si>
   <si>
     <t xml:space="preserve">14.9416666030884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7235403060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0143747329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5781192779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7598915100098</t>
+    <t xml:space="preserve">14.7235383987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0143737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5781221389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7598924636841</t>
   </si>
   <si>
     <t xml:space="preserve">14.6508312225342</t>
@@ -1730,13 +1730,13 @@
     <t xml:space="preserve">14.3236408233643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5272254943848</t>
+    <t xml:space="preserve">14.5272245407104</t>
   </si>
   <si>
     <t xml:space="preserve">14.4545164108276</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7962474822998</t>
+    <t xml:space="preserve">14.7962484359741</t>
   </si>
   <si>
     <t xml:space="preserve">14.905312538147</t>
@@ -1745,22 +1745,22 @@
     <t xml:space="preserve">16.032299041748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.359489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5049057006836</t>
+    <t xml:space="preserve">16.3594875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5049076080322</t>
   </si>
   <si>
     <t xml:space="preserve">16.6139698028564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5412616729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8320922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6503238677979</t>
+    <t xml:space="preserve">16.541259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8320960998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6503219604492</t>
   </si>
   <si>
     <t xml:space="preserve">16.5776138305664</t>
@@ -1769,31 +1769,31 @@
     <t xml:space="preserve">16.8684501647949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7593860626221</t>
+    <t xml:space="preserve">16.7593879699707</t>
   </si>
   <si>
     <t xml:space="preserve">17.0502223968506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.086576461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4864768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4137668609619</t>
+    <t xml:space="preserve">17.0865745544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4864749908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4137687683105</t>
   </si>
   <si>
     <t xml:space="preserve">17.2683486938477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5228290557861</t>
+    <t xml:space="preserve">17.5228309631348</t>
   </si>
   <si>
     <t xml:space="preserve">17.8136653900146</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7409572601318</t>
+    <t xml:space="preserve">17.7409553527832</t>
   </si>
   <si>
     <t xml:space="preserve">17.6318950653076</t>
@@ -1802,34 +1802,34 @@
     <t xml:space="preserve">17.7046031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.668249130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0681457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9227294921875</t>
+    <t xml:space="preserve">17.6682472229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0681476593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9227275848389</t>
   </si>
   <si>
     <t xml:space="preserve">18.1044998168945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8500175476074</t>
+    <t xml:space="preserve">17.8500213623047</t>
   </si>
   <si>
     <t xml:space="preserve">17.9590835571289</t>
   </si>
   <si>
-    <t xml:space="preserve">18.177209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0317916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2862720489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.358980178833</t>
+    <t xml:space="preserve">18.1772079467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0317897796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2862739562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3589839935303</t>
   </si>
   <si>
     <t xml:space="preserve">18.4680442810059</t>
@@ -1838,16 +1838,16 @@
     <t xml:space="preserve">18.5771083831787</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9954376220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5591831207275</t>
+    <t xml:space="preserve">17.9954357147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5591850280762</t>
   </si>
   <si>
     <t xml:space="preserve">17.5955390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.450122833252</t>
+    <t xml:space="preserve">17.4501190185547</t>
   </si>
   <si>
     <t xml:space="preserve">18.2499179840088</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">18.3953342437744</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2135639190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3226261138916</t>
+    <t xml:space="preserve">18.2135620117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3226280212402</t>
   </si>
   <si>
     <t xml:space="preserve">18.6134624481201</t>
@@ -1871,10 +1871,10 @@
     <t xml:space="preserve">18.8315868377686</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1951351165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9770069122314</t>
+    <t xml:space="preserve">19.1951332092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9770050048828</t>
   </si>
   <si>
     <t xml:space="preserve">19.0860691070557</t>
@@ -1883,31 +1883,31 @@
     <t xml:space="preserve">19.2678413391113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1224250793457</t>
+    <t xml:space="preserve">19.1224231719971</t>
   </si>
   <si>
     <t xml:space="preserve">19.3041954040527</t>
   </si>
   <si>
-    <t xml:space="preserve">19.413257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.449613571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9048042297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7230339050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321975708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7957401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2314872741699</t>
+    <t xml:space="preserve">19.4132614135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4496154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.904806137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7230319976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321956634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7957420349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2314891815186</t>
   </si>
   <si>
     <t xml:space="preserve">16.9775142669678</t>
@@ -1919,25 +1919,25 @@
     <t xml:space="preserve">17.3774108886719</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7952327728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.54075050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8679447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.904296875</t>
+    <t xml:space="preserve">18.7952346801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5407524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8679428100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9042949676514</t>
   </si>
   <si>
     <t xml:space="preserve">19.8495101928711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4213848114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7327518463135</t>
+    <t xml:space="preserve">19.42138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7327499389648</t>
   </si>
   <si>
     <t xml:space="preserve">20.394401550293</t>
@@ -1946,40 +1946,43 @@
     <t xml:space="preserve">19.8105926513672</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6549072265625</t>
+    <t xml:space="preserve">19.6549110412598</t>
   </si>
   <si>
     <t xml:space="preserve">20.3554821014404</t>
   </si>
   <si>
-    <t xml:space="preserve">20.121955871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9273548126221</t>
+    <t xml:space="preserve">19.8495121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1219577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9273529052734</t>
   </si>
   <si>
     <t xml:space="preserve">19.4603061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3435440063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3046245574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9662742614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2657032012939</t>
+    <t xml:space="preserve">19.3435459136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3046226501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.966272354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2657012939453</t>
   </si>
   <si>
     <t xml:space="preserve">19.771671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7597351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1608753204346</t>
+    <t xml:space="preserve">18.7597370147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1608772277832</t>
   </si>
   <si>
     <t xml:space="preserve">20.044116973877</t>
@@ -1988,25 +1991,25 @@
     <t xml:space="preserve">21.172815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0560493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9392871856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2895755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0171298980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7836055755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7057666778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0949726104736</t>
+    <t xml:space="preserve">21.0560531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9392890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2895774841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0171318054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7836074829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7057647705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.094970703125</t>
   </si>
   <si>
     <t xml:space="preserve">21.4452571868896</t>
@@ -2015,7 +2018,7 @@
     <t xml:space="preserve">21.7566242218018</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9512271881104</t>
+    <t xml:space="preserve">21.9512233734131</t>
   </si>
   <si>
     <t xml:space="preserve">21.6009407043457</t>
@@ -2024,19 +2027,19 @@
     <t xml:space="preserve">21.7955436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0290660858154</t>
+    <t xml:space="preserve">22.0290679931641</t>
   </si>
   <si>
     <t xml:space="preserve">22.0679874420166</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5350341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.57395362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6517963409424</t>
+    <t xml:space="preserve">22.5350360870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5739574432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6517944335938</t>
   </si>
   <si>
     <t xml:space="preserve">22.7685585021973</t>
@@ -2048,16 +2051,16 @@
     <t xml:space="preserve">22.7296390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3404331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2625885009766</t>
+    <t xml:space="preserve">22.3404312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2625904083252</t>
   </si>
   <si>
     <t xml:space="preserve">23.5080509185791</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9750957489014</t>
+    <t xml:space="preserve">23.9750995635986</t>
   </si>
   <si>
     <t xml:space="preserve">24.4032249450684</t>
@@ -2069,13 +2072,13 @@
     <t xml:space="preserve">24.7145881652832</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5199871063232</t>
+    <t xml:space="preserve">24.5199851989746</t>
   </si>
   <si>
     <t xml:space="preserve">25.298397064209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7924308776855</t>
+    <t xml:space="preserve">24.7924327850342</t>
   </si>
   <si>
     <t xml:space="preserve">25.1427154541016</t>
@@ -2084,16 +2087,16 @@
     <t xml:space="preserve">24.7535076141357</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6367473602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1697006225586</t>
+    <t xml:space="preserve">24.6367454528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.16969871521</t>
   </si>
   <si>
     <t xml:space="preserve">24.0140190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0799236297607</t>
+    <t xml:space="preserve">23.0799217224121</t>
   </si>
   <si>
     <t xml:space="preserve">23.7026538848877</t>
@@ -2102,10 +2105,10 @@
     <t xml:space="preserve">24.0529384613037</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4691295623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5858917236328</t>
+    <t xml:space="preserve">23.4691276550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5858898162842</t>
   </si>
   <si>
     <t xml:space="preserve">23.1577644348145</t>
@@ -2120,19 +2123,19 @@
     <t xml:space="preserve">23.8194141387939</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6637306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4302101135254</t>
+    <t xml:space="preserve">23.6637325286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4302082061768</t>
   </si>
   <si>
     <t xml:space="preserve">24.0918598175049</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3912887573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.352367401123</t>
+    <t xml:space="preserve">23.3912868499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3523654937744</t>
   </si>
   <si>
     <t xml:space="preserve">23.0410022735596</t>
@@ -2141,10 +2144,10 @@
     <t xml:space="preserve">23.0020809173584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1188449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6248111724854</t>
+    <t xml:space="preserve">23.1188430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.624813079834</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128730773926</t>
@@ -2153,7 +2156,7 @@
     <t xml:space="preserve">22.1069087982178</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1847496032715</t>
+    <t xml:space="preserve">22.1847476959229</t>
   </si>
   <si>
     <t xml:space="preserve">22.496114730835</t>
@@ -2162,10 +2165,10 @@
     <t xml:space="preserve">22.3015098571777</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6907176971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3793506622314</t>
+    <t xml:space="preserve">22.6907157897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3793525695801</t>
   </si>
   <si>
     <t xml:space="preserve">22.9631614685059</t>
@@ -2174,28 +2177,28 @@
     <t xml:space="preserve">23.2356071472168</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9242401123047</t>
+    <t xml:space="preserve">22.9242420196533</t>
   </si>
   <si>
     <t xml:space="preserve">22.223669052124</t>
   </si>
   <si>
-    <t xml:space="preserve">22.418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9123058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4841785430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1338939666748</t>
+    <t xml:space="preserve">22.4182720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9123020172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4841747283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1338901519775</t>
   </si>
   <si>
     <t xml:space="preserve">21.5230979919434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7177047729492</t>
+    <t xml:space="preserve">21.717700958252</t>
   </si>
   <si>
     <t xml:space="preserve">21.6398601531982</t>
@@ -2204,31 +2207,31 @@
     <t xml:space="preserve">21.2506523132324</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5620212554932</t>
+    <t xml:space="preserve">21.5620193481445</t>
   </si>
   <si>
     <t xml:space="preserve">21.8344612121582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.678783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9901466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1458282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.846399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8853206634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4571914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3284950256348</t>
+    <t xml:space="preserve">21.6787815093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9901485443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1458301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8464012145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8853187561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4571952819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284969329834</t>
   </si>
   <si>
     <t xml:space="preserve">21.2117328643799</t>
@@ -2240,16 +2243,16 @@
     <t xml:space="preserve">20.9782104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6279239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8733863830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.440731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8835639953613</t>
+    <t xml:space="preserve">20.6279258728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.873384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4407329559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.88356590271</t>
   </si>
   <si>
     <t xml:space="preserve">22.7243747711182</t>
@@ -2258,25 +2261,22 @@
     <t xml:space="preserve">22.8039703369141</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7641716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0427551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9631595611572</t>
+    <t xml:space="preserve">22.7641735076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0427570343018</t>
   </si>
   <si>
     <t xml:space="preserve">23.2417449951172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0029582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2019462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1223487854004</t>
+    <t xml:space="preserve">23.0029563903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2019443511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.122350692749</t>
   </si>
   <si>
     <t xml:space="preserve">23.1621475219727</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">23.5203247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9580993652344</t>
+    <t xml:space="preserve">23.9580974578857</t>
   </si>
   <si>
     <t xml:space="preserve">24.0774917602539</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">24.555061340332</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7540473937988</t>
+    <t xml:space="preserve">24.7540493011475</t>
   </si>
   <si>
     <t xml:space="preserve">24.2764778137207</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">24.1172885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5152626037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4754657745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2366809844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3958702087402</t>
+    <t xml:space="preserve">24.5152645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4754638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2366828918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3958721160889</t>
   </si>
   <si>
     <t xml:space="preserve">24.7142505645752</t>
@@ -2342,19 +2342,19 @@
     <t xml:space="preserve">24.6346569061279</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1968822479248</t>
+    <t xml:space="preserve">24.1968841552734</t>
   </si>
   <si>
     <t xml:space="preserve">25.6295928955078</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5102024078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1520252227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3510112762451</t>
+    <t xml:space="preserve">25.5102005004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1520233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3510131835938</t>
   </si>
   <si>
     <t xml:space="preserve">25.4704036712646</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">25.6693916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3908081054688</t>
+    <t xml:space="preserve">25.3908100128174</t>
   </si>
   <si>
     <t xml:space="preserve">25.1918201446533</t>
@@ -2375,19 +2375,19 @@
     <t xml:space="preserve">25.2714157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8336448669434</t>
+    <t xml:space="preserve">24.8336429595947</t>
   </si>
   <si>
     <t xml:space="preserve">24.9530372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8683776855469</t>
+    <t xml:space="preserve">25.8683795928955</t>
   </si>
   <si>
     <t xml:space="preserve">25.0724296569824</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7591114044189</t>
+    <t xml:space="preserve">23.7591133117676</t>
   </si>
   <si>
     <t xml:space="preserve">23.4805278778076</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">23.8785037994385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6397190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7989101409912</t>
+    <t xml:space="preserve">23.6397171020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7989082336426</t>
   </si>
   <si>
     <t xml:space="preserve">24.5948581695557</t>
@@ -2411,13 +2411,13 @@
     <t xml:space="preserve">25.430606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3112125396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2316207885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0673675537109</t>
+    <t xml:space="preserve">25.3112106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2316188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0673656463623</t>
   </si>
   <si>
     <t xml:space="preserve">26.2663536071777</t>
@@ -2426,52 +2426,52 @@
     <t xml:space="preserve">26.0275688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7887840270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5499973297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5897960662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9479713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1071624755859</t>
+    <t xml:space="preserve">25.7887859344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5897979736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9479732513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1071643829346</t>
   </si>
   <si>
     <t xml:space="preserve">25.7489852905273</t>
   </si>
   <si>
-    <t xml:space="preserve">24.873441696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0376949310303</t>
+    <t xml:space="preserve">24.8734397888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0376930236816</t>
   </si>
   <si>
     <t xml:space="preserve">22.3263988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3661994934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0825519561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.923360824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3213386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5999221801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3611354827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4009342193604</t>
+    <t xml:space="preserve">22.3661975860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0825538635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9233646392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3213367462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5999202728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3611373901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4009323120117</t>
   </si>
   <si>
     <t xml:space="preserve">23.5601234436035</t>
@@ -2480,16 +2480,16 @@
     <t xml:space="preserve">22.4855918884277</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8387088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.997896194458</t>
+    <t xml:space="preserve">23.8387050628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9978942871094</t>
   </si>
   <si>
     <t xml:space="preserve">23.7193126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8264102935791</t>
+    <t xml:space="preserve">23.8264083862305</t>
   </si>
   <si>
     <t xml:space="preserve">23.5692901611328</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">24.1263828277588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9549713134766</t>
+    <t xml:space="preserve">23.9549694061279</t>
   </si>
   <si>
     <t xml:space="preserve">24.4692077636719</t>
@@ -2507,13 +2507,13 @@
     <t xml:space="preserve">24.4263553619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1692371368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2120876312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7835578918457</t>
+    <t xml:space="preserve">24.1692352294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2120895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7835559844971</t>
   </si>
   <si>
     <t xml:space="preserve">24.340648651123</t>
@@ -2528,19 +2528,19 @@
     <t xml:space="preserve">23.5264377593994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.99782371521</t>
+    <t xml:space="preserve">23.9978218078613</t>
   </si>
   <si>
     <t xml:space="preserve">23.9121170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8692646026611</t>
+    <t xml:space="preserve">23.8692626953125</t>
   </si>
   <si>
     <t xml:space="preserve">23.7407035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6549968719482</t>
+    <t xml:space="preserve">23.6549987792969</t>
   </si>
   <si>
     <t xml:space="preserve">22.9693431854248</t>
@@ -2558,16 +2558,16 @@
     <t xml:space="preserve">23.1407585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">22.840784072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7550792694092</t>
+    <t xml:space="preserve">22.8407859802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7550773620605</t>
   </si>
   <si>
     <t xml:space="preserve">22.6693725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0550498962402</t>
+    <t xml:space="preserve">23.0550518035889</t>
   </si>
   <si>
     <t xml:space="preserve">23.2264652252197</t>
@@ -2588,16 +2588,16 @@
     <t xml:space="preserve">22.3694000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3550262451172</t>
+    <t xml:space="preserve">23.3550243377686</t>
   </si>
   <si>
     <t xml:space="preserve">23.0121994018555</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3121719360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3978748321533</t>
+    <t xml:space="preserve">23.3121738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.397876739502</t>
   </si>
   <si>
     <t xml:space="preserve">22.7979316711426</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">22.4979591369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6265201568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6978511810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5408134460449</t>
+    <t xml:space="preserve">22.6265182495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6978492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5408115386963</t>
   </si>
   <si>
     <t xml:space="preserve">23.2693176269531</t>
@@ -2636,25 +2636,25 @@
     <t xml:space="preserve">20.826681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9267635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1410312652588</t>
+    <t xml:space="preserve">19.9267616271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1410293579102</t>
   </si>
   <si>
     <t xml:space="preserve">20.9980945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1266555786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5267105102539</t>
+    <t xml:space="preserve">21.1266536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5267086029053</t>
   </si>
   <si>
     <t xml:space="preserve">20.6552696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3124446868896</t>
+    <t xml:space="preserve">20.312442779541</t>
   </si>
   <si>
     <t xml:space="preserve">20.4410037994385</t>
@@ -2669,13 +2669,13 @@
     <t xml:space="preserve">21.3837757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5123329162598</t>
+    <t xml:space="preserve">21.512336730957</t>
   </si>
   <si>
     <t xml:space="preserve">21.3409214019775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.026575088501</t>
+    <t xml:space="preserve">22.0265731811523</t>
   </si>
   <si>
     <t xml:space="preserve">22.1122798919678</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">22.1551322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2408390045166</t>
+    <t xml:space="preserve">22.2408409118652</t>
   </si>
   <si>
     <t xml:space="preserve">21.6837463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7266006469727</t>
+    <t xml:space="preserve">21.726598739624</t>
   </si>
   <si>
     <t xml:space="preserve">21.8980121612549</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">21.6408939361572</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1979866027832</t>
+    <t xml:space="preserve">22.1979846954346</t>
   </si>
   <si>
     <t xml:space="preserve">22.0694274902344</t>
@@ -2717,22 +2717,22 @@
     <t xml:space="preserve">21.8551597595215</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1695079803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0838012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9408683776855</t>
+    <t xml:space="preserve">21.1695098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0838031768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9408664703369</t>
   </si>
   <si>
     <t xml:space="preserve">21.5551872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0409469604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9123878479004</t>
+    <t xml:space="preserve">21.0409488677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.912389755249</t>
   </si>
   <si>
     <t xml:space="preserve">21.2980690002441</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">20.7409763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1838836669922</t>
+    <t xml:space="preserve">20.1838817596436</t>
   </si>
   <si>
     <t xml:space="preserve">20.3552951812744</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">22.0611591339111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1051940917969</t>
+    <t xml:space="preserve">22.1051959991455</t>
   </si>
   <si>
     <t xml:space="preserve">22.017126083374</t>
@@ -2783,10 +2783,10 @@
     <t xml:space="preserve">21.664852142334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5767822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4887142181396</t>
+    <t xml:space="preserve">21.5767841339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4887161254883</t>
   </si>
   <si>
     <t xml:space="preserve">21.9290561676025</t>
@@ -2795,22 +2795,22 @@
     <t xml:space="preserve">21.8409881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7088871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4006443023682</t>
+    <t xml:space="preserve">21.7088851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4006462097168</t>
   </si>
   <si>
     <t xml:space="preserve">21.7969551086426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9730911254883</t>
+    <t xml:space="preserve">21.9730930328369</t>
   </si>
   <si>
     <t xml:space="preserve">21.7529201507568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.501501083374</t>
+    <t xml:space="preserve">22.5015029907227</t>
   </si>
   <si>
     <t xml:space="preserve">22.2372970581055</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">22.3253650665283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5455379486084</t>
+    <t xml:space="preserve">22.5455360412598</t>
   </si>
   <si>
     <t xml:space="preserve">22.149227142334</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">21.0483722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3566131591797</t>
+    <t xml:space="preserve">21.3566112518311</t>
   </si>
   <si>
     <t xml:space="preserve">21.6208171844482</t>
@@ -2852,13 +2852,13 @@
     <t xml:space="preserve">21.4446811676025</t>
   </si>
   <si>
-    <t xml:space="preserve">21.532751083374</t>
+    <t xml:space="preserve">21.5327491760254</t>
   </si>
   <si>
     <t xml:space="preserve">21.0043392181396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8722362518311</t>
+    <t xml:space="preserve">20.8722343444824</t>
   </si>
   <si>
     <t xml:space="preserve">20.6960983276367</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">20.2557563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3878574371338</t>
+    <t xml:space="preserve">20.3878593444824</t>
   </si>
   <si>
     <t xml:space="preserve">20.2997894287109</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">20.7841682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9603042602539</t>
+    <t xml:space="preserve">20.9603023529053</t>
   </si>
   <si>
     <t xml:space="preserve">20.7401313781738</t>
@@ -2900,10 +2900,10 @@
     <t xml:space="preserve">21.1804752349854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6336078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4574699401855</t>
+    <t xml:space="preserve">22.6336059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4574680328369</t>
   </si>
   <si>
     <t xml:space="preserve">22.5895709991455</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">24.3949756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">24.30690574646</t>
+    <t xml:space="preserve">24.3069076538086</t>
   </si>
   <si>
     <t xml:space="preserve">24.1307697296143</t>
@@ -2936,13 +2936,13 @@
     <t xml:space="preserve">24.3509407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4390106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5711116790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6591796875</t>
+    <t xml:space="preserve">24.4390087127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5711135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6591815948486</t>
   </si>
   <si>
     <t xml:space="preserve">24.7032146453857</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">24.0867366790771</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2188396453857</t>
+    <t xml:space="preserve">24.2188377380371</t>
   </si>
   <si>
     <t xml:space="preserve">24.1748046875</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">23.9546337127686</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7600364685059</t>
+    <t xml:space="preserve">25.7600383758545</t>
   </si>
   <si>
     <t xml:space="preserve">25.4077625274658</t>
@@ -2990,19 +2990,19 @@
     <t xml:space="preserve">26.1123104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1563453674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4645862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5910167694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3708457946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8992595672607</t>
+    <t xml:space="preserve">26.1563472747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4645843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5910148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3708438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8992576599121</t>
   </si>
   <si>
     <t xml:space="preserve">30.0313587188721</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">29.5029487609863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7671546936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2827758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0753974914551</t>
+    <t xml:space="preserve">29.7671527862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2827777862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0753955841064</t>
   </si>
   <si>
     <t xml:space="preserve">29.7231216430664</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">30.471700668335</t>
   </si>
   <si>
-    <t xml:space="preserve">29.811185836792</t>
+    <t xml:space="preserve">29.8111877441406</t>
   </si>
   <si>
     <t xml:space="preserve">29.2387447357178</t>
@@ -3047,28 +3047,28 @@
     <t xml:space="preserve">28.7103309631348</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8424339294434</t>
+    <t xml:space="preserve">28.842435836792</t>
   </si>
   <si>
     <t xml:space="preserve">28.8864688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5469837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2955646514893</t>
+    <t xml:space="preserve">29.5469818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2955665588379</t>
   </si>
   <si>
     <t xml:space="preserve">30.7359104156494</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3836345672607</t>
+    <t xml:space="preserve">30.3836326599121</t>
   </si>
   <si>
     <t xml:space="preserve">29.9873237609863</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4276695251465</t>
+    <t xml:space="preserve">30.4276676177979</t>
   </si>
   <si>
     <t xml:space="preserve">29.4632396697998</t>
@@ -3462,9 +3462,6 @@
   </si>
   <si>
     <t xml:space="preserve">26.0499992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5499992370605</t>
   </si>
   <si>
     <t xml:space="preserve">26.1499996185303</t>
@@ -32812,7 +32809,7 @@
         <v>25.5</v>
       </c>
       <c r="G1106" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32864,7 +32861,7 @@
         <v>25.5</v>
       </c>
       <c r="G1108" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32890,7 +32887,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G1109" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32916,7 +32913,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1110" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32942,7 +32939,7 @@
         <v>25</v>
       </c>
       <c r="G1111" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32968,7 +32965,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1112" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32994,7 +32991,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1113" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -33020,7 +33017,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1114" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -33072,7 +33069,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1116" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -33098,7 +33095,7 @@
         <v>24.75</v>
       </c>
       <c r="G1117" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -33124,7 +33121,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1118" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33150,7 +33147,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1119" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33228,7 +33225,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1122" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33254,7 +33251,7 @@
         <v>25.75</v>
       </c>
       <c r="G1123" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33280,7 +33277,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1124" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33306,7 +33303,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1125" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33332,7 +33329,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1126" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33358,7 +33355,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G1127" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33384,7 +33381,7 @@
         <v>27</v>
       </c>
       <c r="G1128" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33410,7 +33407,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1129" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33436,7 +33433,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1130" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33462,7 +33459,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1131" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33488,7 +33485,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1132" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33514,7 +33511,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1133" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33540,7 +33537,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1134" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33566,7 +33563,7 @@
         <v>27.75</v>
       </c>
       <c r="G1135" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33592,7 +33589,7 @@
         <v>28</v>
       </c>
       <c r="G1136" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33618,7 +33615,7 @@
         <v>28</v>
       </c>
       <c r="G1137" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33644,7 +33641,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33670,7 +33667,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1139" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33696,7 +33693,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1140" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33722,7 +33719,7 @@
         <v>29</v>
       </c>
       <c r="G1141" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33748,7 +33745,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33774,7 +33771,7 @@
         <v>29.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33800,7 +33797,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1144" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33826,7 +33823,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1145" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33852,7 +33849,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1146" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33878,7 +33875,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1147" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33904,7 +33901,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1148" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33930,7 +33927,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1149" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33956,7 +33953,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1150" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33982,7 +33979,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1151" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -34008,7 +34005,7 @@
         <v>32</v>
       </c>
       <c r="G1152" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -34034,7 +34031,7 @@
         <v>31.75</v>
       </c>
       <c r="G1153" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -34060,7 +34057,7 @@
         <v>31.5</v>
       </c>
       <c r="G1154" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -34086,7 +34083,7 @@
         <v>32.5</v>
       </c>
       <c r="G1155" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34112,7 +34109,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1156" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34138,7 +34135,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1157" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34164,7 +34161,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1158" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34190,7 +34187,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1159" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34216,7 +34213,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G1160" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34242,7 +34239,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1161" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34268,7 +34265,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G1162" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34294,7 +34291,7 @@
         <v>29.25</v>
       </c>
       <c r="G1163" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34320,7 +34317,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1164" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34346,7 +34343,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G1165" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34372,7 +34369,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34398,7 +34395,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G1167" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34424,7 +34421,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34450,7 +34447,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1169" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34476,7 +34473,7 @@
         <v>29.75</v>
       </c>
       <c r="G1170" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34502,7 +34499,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1171" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34528,7 +34525,7 @@
         <v>30.5</v>
       </c>
       <c r="G1172" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34554,7 +34551,7 @@
         <v>30.5</v>
       </c>
       <c r="G1173" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34580,7 +34577,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1174" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34606,7 +34603,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34632,7 +34629,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34658,7 +34655,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1177" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34684,7 +34681,7 @@
         <v>30.5</v>
       </c>
       <c r="G1178" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34710,7 +34707,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1179" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34736,7 +34733,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1180" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34762,7 +34759,7 @@
         <v>30.5</v>
       </c>
       <c r="G1181" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34788,7 +34785,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1182" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34814,7 +34811,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1183" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34840,7 +34837,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1184" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34866,7 +34863,7 @@
         <v>30.5</v>
       </c>
       <c r="G1185" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34892,7 +34889,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34918,7 +34915,7 @@
         <v>30</v>
       </c>
       <c r="G1187" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34944,7 +34941,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1188" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34970,7 +34967,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1189" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34996,7 +34993,7 @@
         <v>30</v>
       </c>
       <c r="G1190" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -35022,7 +35019,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1191" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -35048,7 +35045,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1192" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -35074,7 +35071,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1193" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -35100,7 +35097,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1194" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -35126,7 +35123,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1195" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35152,7 +35149,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1196" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35178,7 +35175,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1197" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35204,7 +35201,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35230,7 +35227,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35256,7 +35253,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1200" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35282,7 +35279,7 @@
         <v>28.5</v>
       </c>
       <c r="G1201" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35308,7 +35305,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1202" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35334,7 +35331,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1203" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35360,7 +35357,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1204" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35386,7 +35383,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1205" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35412,7 +35409,7 @@
         <v>28.75</v>
       </c>
       <c r="G1206" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35438,7 +35435,7 @@
         <v>29.5</v>
       </c>
       <c r="G1207" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35464,7 +35461,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1208" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35490,7 +35487,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1209" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35516,7 +35513,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1210" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35542,7 +35539,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1211" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35568,7 +35565,7 @@
         <v>29</v>
       </c>
       <c r="G1212" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35594,7 +35591,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35620,7 +35617,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1214" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35646,7 +35643,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1215" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35672,7 +35669,7 @@
         <v>29</v>
       </c>
       <c r="G1216" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35698,7 +35695,7 @@
         <v>29</v>
       </c>
       <c r="G1217" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35724,7 +35721,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1218" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35750,7 +35747,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1219" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35776,7 +35773,7 @@
         <v>29</v>
       </c>
       <c r="G1220" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35802,7 +35799,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1221" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35828,7 +35825,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35854,7 +35851,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1223" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35880,7 +35877,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35906,7 +35903,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1225" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35932,7 +35929,7 @@
         <v>28</v>
       </c>
       <c r="G1226" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35958,7 +35955,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1227" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35984,7 +35981,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1228" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -36010,7 +36007,7 @@
         <v>27.75</v>
       </c>
       <c r="G1229" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -36036,7 +36033,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -36062,7 +36059,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -36088,7 +36085,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -36114,7 +36111,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1233" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -36140,7 +36137,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1234" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36166,7 +36163,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1235" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36192,7 +36189,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1236" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36218,7 +36215,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1237" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36244,7 +36241,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1238" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36270,7 +36267,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36296,7 +36293,7 @@
         <v>27.75</v>
       </c>
       <c r="G1240" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36322,7 +36319,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G1241" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36348,7 +36345,7 @@
         <v>27.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36374,7 +36371,7 @@
         <v>28</v>
       </c>
       <c r="G1243" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36400,7 +36397,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1244" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36426,7 +36423,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36452,7 +36449,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1246" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36478,7 +36475,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1247" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36504,7 +36501,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1248" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36530,7 +36527,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1249" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36556,7 +36553,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36582,7 +36579,7 @@
         <v>28.75</v>
       </c>
       <c r="G1251" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36608,7 +36605,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1252" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36634,7 +36631,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36660,7 +36657,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1254" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36686,7 +36683,7 @@
         <v>28.25</v>
       </c>
       <c r="G1255" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36712,7 +36709,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G1256" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36738,7 +36735,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36764,7 +36761,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1258" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36790,7 +36787,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1259" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36816,7 +36813,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1260" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36842,7 +36839,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1261" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36868,7 +36865,7 @@
         <v>29.25</v>
       </c>
       <c r="G1262" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36894,7 +36891,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1263" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36920,7 +36917,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1264" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36946,7 +36943,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1265" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36972,7 +36969,7 @@
         <v>30</v>
       </c>
       <c r="G1266" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36998,7 +36995,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1267" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -37024,7 +37021,7 @@
         <v>29.25</v>
       </c>
       <c r="G1268" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -37050,7 +37047,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -37076,7 +37073,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1270" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -37102,7 +37099,7 @@
         <v>29.5</v>
       </c>
       <c r="G1271" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -37128,7 +37125,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1272" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37154,7 +37151,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1273" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37180,7 +37177,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1274" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37206,7 +37203,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37232,7 +37229,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1276" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37258,7 +37255,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1277" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37284,7 +37281,7 @@
         <v>29.25</v>
       </c>
       <c r="G1278" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37310,7 +37307,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37336,7 +37333,7 @@
         <v>28.75</v>
       </c>
       <c r="G1280" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37362,7 +37359,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1281" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37388,7 +37385,7 @@
         <v>29.25</v>
       </c>
       <c r="G1282" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37414,7 +37411,7 @@
         <v>29.25</v>
       </c>
       <c r="G1283" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37440,7 +37437,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1284" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37466,7 +37463,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1285" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37492,7 +37489,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1286" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37518,7 +37515,7 @@
         <v>27.75</v>
       </c>
       <c r="G1287" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37544,7 +37541,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1288" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37570,7 +37567,7 @@
         <v>27.25</v>
       </c>
       <c r="G1289" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37596,7 +37593,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1290" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37622,7 +37619,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1291" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37648,7 +37645,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1292" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37674,7 +37671,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1293" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37700,7 +37697,7 @@
         <v>28.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37726,7 +37723,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G1295" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37752,7 +37749,7 @@
         <v>28.75</v>
       </c>
       <c r="G1296" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37778,7 +37775,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37804,7 +37801,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1298" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37830,7 +37827,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1299" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37856,7 +37853,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1300" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37882,7 +37879,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1301" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37908,7 +37905,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1302" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37934,7 +37931,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1303" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37960,7 +37957,7 @@
         <v>27</v>
       </c>
       <c r="G1304" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37986,7 +37983,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1305" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -38012,7 +38009,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1306" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -38038,7 +38035,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1307" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -38064,7 +38061,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1308" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -38090,7 +38087,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -38116,7 +38113,7 @@
         <v>26.5</v>
       </c>
       <c r="G1310" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -38142,7 +38139,7 @@
         <v>27.25</v>
       </c>
       <c r="G1311" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38168,7 +38165,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1312" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38194,7 +38191,7 @@
         <v>27.25</v>
       </c>
       <c r="G1313" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38220,7 +38217,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1314" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38246,7 +38243,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38272,7 +38269,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38298,7 +38295,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1317" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38324,7 +38321,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1318" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38350,7 +38347,7 @@
         <v>29.75</v>
       </c>
       <c r="G1319" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38376,7 +38373,7 @@
         <v>29.5</v>
       </c>
       <c r="G1320" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38402,7 +38399,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38428,7 +38425,7 @@
         <v>29.5</v>
       </c>
       <c r="G1322" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38454,7 +38451,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38480,7 +38477,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38506,7 +38503,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38532,7 +38529,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1326" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38558,7 +38555,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1327" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38584,7 +38581,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1328" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38610,7 +38607,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1329" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38636,7 +38633,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1330" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38662,7 +38659,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1331" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38688,7 +38685,7 @@
         <v>29</v>
       </c>
       <c r="G1332" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38714,7 +38711,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1333" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38740,7 +38737,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1334" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38766,7 +38763,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1335" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38792,7 +38789,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1336" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38818,7 +38815,7 @@
         <v>29</v>
       </c>
       <c r="G1337" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38844,7 +38841,7 @@
         <v>29.25</v>
       </c>
       <c r="G1338" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38870,7 +38867,7 @@
         <v>29</v>
       </c>
       <c r="G1339" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38896,7 +38893,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1340" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38922,7 +38919,7 @@
         <v>29</v>
       </c>
       <c r="G1341" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38948,7 +38945,7 @@
         <v>29</v>
       </c>
       <c r="G1342" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38974,7 +38971,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -39000,7 +38997,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1344" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -39026,7 +39023,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1345" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -39052,7 +39049,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -39078,7 +39075,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -39104,7 +39101,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1348" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39130,7 +39127,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1349" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39156,7 +39153,7 @@
         <v>28.75</v>
       </c>
       <c r="G1350" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39182,7 +39179,7 @@
         <v>29</v>
       </c>
       <c r="G1351" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39208,7 +39205,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1352" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39234,7 +39231,7 @@
         <v>29.5</v>
       </c>
       <c r="G1353" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39260,7 +39257,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1354" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39286,7 +39283,7 @@
         <v>28.75</v>
       </c>
       <c r="G1355" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39312,7 +39309,7 @@
         <v>28.75</v>
       </c>
       <c r="G1356" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39338,7 +39335,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1357" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39364,7 +39361,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39390,7 +39387,7 @@
         <v>28.75</v>
       </c>
       <c r="G1359" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39416,7 +39413,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39442,7 +39439,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1361" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39468,7 +39465,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1362" t="s">
-        <v>750</v>
+        <v>719</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39494,7 +39491,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1363" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39572,7 +39569,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1366" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -39624,7 +39621,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -39728,7 +39725,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1372" t="s">
-        <v>750</v>
+        <v>719</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -44876,7 +44873,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1570" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44902,7 +44899,7 @@
         <v>28.75</v>
       </c>
       <c r="G1571" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45032,7 +45029,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1576" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45474,7 +45471,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1593" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45526,7 +45523,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1595" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45656,7 +45653,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1600" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45682,7 +45679,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1601" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -46020,7 +46017,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1614" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -66144,7 +66141,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G2388" t="s">
-        <v>1150</v>
+        <v>805</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66170,7 +66167,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66196,7 +66193,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66222,7 +66219,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G2391" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66248,7 +66245,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66274,7 +66271,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66300,7 +66297,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66326,7 +66323,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66352,7 +66349,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G2396" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66378,7 +66375,7 @@
         <v>26.75</v>
       </c>
       <c r="G2397" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66404,7 +66401,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2398" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66430,7 +66427,7 @@
         <v>27</v>
       </c>
       <c r="G2399" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66456,7 +66453,7 @@
         <v>27</v>
       </c>
       <c r="G2400" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66482,7 +66479,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66508,7 +66505,7 @@
         <v>26.25</v>
       </c>
       <c r="G2402" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66534,7 +66531,7 @@
         <v>25.5</v>
       </c>
       <c r="G2403" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66560,7 +66557,7 @@
         <v>25.25</v>
       </c>
       <c r="G2404" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66612,7 +66609,7 @@
         <v>25.25</v>
       </c>
       <c r="G2406" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66664,7 +66661,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G2408" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66690,7 +66687,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G2409" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66716,7 +66713,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G2410" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66742,7 +66739,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2411" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66768,7 +66765,7 @@
         <v>25.5</v>
       </c>
       <c r="G2412" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66820,7 +66817,7 @@
         <v>26</v>
       </c>
       <c r="G2414" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66846,7 +66843,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2415" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66872,7 +66869,7 @@
         <v>27</v>
       </c>
       <c r="G2416" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66898,7 +66895,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66924,7 +66921,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G2418" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66950,7 +66947,7 @@
         <v>27.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66976,7 +66973,7 @@
         <v>27.5</v>
       </c>
       <c r="G2420" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67002,7 +66999,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67028,7 +67025,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2422" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67054,7 +67051,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G2423" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67080,7 +67077,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2424" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67106,7 +67103,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G2425" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67132,7 +67129,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2426" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67158,7 +67155,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2427" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67184,7 +67181,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2428" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67210,7 +67207,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2429" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67236,7 +67233,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67262,7 +67259,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67288,7 +67285,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2432" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67314,7 +67311,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67340,7 +67337,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G2434" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67366,7 +67363,7 @@
         <v>29</v>
       </c>
       <c r="G2435" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67392,7 +67389,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G2436" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67418,7 +67415,7 @@
         <v>28.25</v>
       </c>
       <c r="G2437" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67444,7 +67441,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G2438" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67470,7 +67467,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67496,7 +67493,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2440" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67522,7 +67519,7 @@
         <v>27</v>
       </c>
       <c r="G2441" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67548,7 +67545,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2442" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67574,7 +67571,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G2443" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67600,7 +67597,7 @@
         <v>27.25</v>
       </c>
       <c r="G2444" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67626,7 +67623,7 @@
         <v>27.25</v>
       </c>
       <c r="G2445" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67652,7 +67649,7 @@
         <v>27.25</v>
       </c>
       <c r="G2446" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67678,7 +67675,7 @@
         <v>27.25</v>
       </c>
       <c r="G2447" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67704,7 +67701,7 @@
         <v>27.5</v>
       </c>
       <c r="G2448" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67730,7 +67727,7 @@
         <v>27.75</v>
       </c>
       <c r="G2449" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67756,7 +67753,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G2450" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67782,7 +67779,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G2451" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67808,7 +67805,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G2452" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67834,7 +67831,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G2453" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67860,7 +67857,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G2454" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67886,7 +67883,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G2455" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67912,7 +67909,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67938,7 +67935,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67964,7 +67961,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G2458" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67990,7 +67987,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G2459" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68016,7 +68013,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G2460" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68042,7 +68039,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2461" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68068,7 +68065,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68094,7 +68091,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68120,7 +68117,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68146,7 +68143,7 @@
         <v>28.75</v>
       </c>
       <c r="G2465" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68172,7 +68169,7 @@
         <v>29</v>
       </c>
       <c r="G2466" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68198,7 +68195,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68224,7 +68221,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G2468" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68250,7 +68247,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68276,7 +68273,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68302,7 +68299,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68328,7 +68325,7 @@
         <v>29.9500007629395</v>
       </c>
       <c r="G2472" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68354,7 +68351,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68380,7 +68377,7 @@
         <v>30</v>
       </c>
       <c r="G2474" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68406,7 +68403,7 @@
         <v>29.75</v>
       </c>
       <c r="G2475" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68432,7 +68429,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G2476" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68458,7 +68455,7 @@
         <v>30</v>
       </c>
       <c r="G2477" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68484,7 +68481,7 @@
         <v>30.5</v>
       </c>
       <c r="G2478" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68510,7 +68507,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G2479" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68536,7 +68533,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68562,7 +68559,7 @@
         <v>31.25</v>
       </c>
       <c r="G2481" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68588,7 +68585,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G2482" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68614,7 +68611,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68640,7 +68637,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68666,7 +68663,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G2485" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68692,7 +68689,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G2486" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68718,7 +68715,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G2487" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68744,7 +68741,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2488" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68770,7 +68767,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2489" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68796,7 +68793,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G2490" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68822,7 +68819,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G2491" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68848,7 +68845,7 @@
         <v>32.5</v>
       </c>
       <c r="G2492" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68874,7 +68871,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G2493" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68900,7 +68897,7 @@
         <v>33</v>
       </c>
       <c r="G2494" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68926,7 +68923,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G2495" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68952,7 +68949,7 @@
         <v>33</v>
       </c>
       <c r="G2496" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68978,7 +68975,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G2497" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69004,7 +69001,7 @@
         <v>33.5</v>
       </c>
       <c r="G2498" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69030,7 +69027,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G2499" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69056,7 +69053,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G2500" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69082,7 +69079,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G2501" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69108,7 +69105,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G2502" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69134,7 +69131,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G2503" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69160,7 +69157,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2504" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69186,7 +69183,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G2505" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -69212,7 +69209,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G2506" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -69238,7 +69235,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G2507" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -69264,7 +69261,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G2508" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -69290,7 +69287,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G2509" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -69316,7 +69313,7 @@
         <v>29.25</v>
       </c>
       <c r="G2510" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -69342,7 +69339,7 @@
         <v>28.5</v>
       </c>
       <c r="G2511" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -69368,7 +69365,7 @@
         <v>28</v>
       </c>
       <c r="G2512" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -69376,7 +69373,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6911342593</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>26183</v>
@@ -69394,9 +69391,35 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G2513" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6911805556</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>27610</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>27.7999992370605</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>27.1499996185303</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>27.7999992370605</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>27.3999996185303</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="1237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="1238">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.806715965271</t>
+    <t xml:space="preserve">13.8067121505737</t>
   </si>
   <si>
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9573345184326</t>
+    <t xml:space="preserve">14.0577459335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9573335647583</t>
   </si>
   <si>
     <t xml:space="preserve">13.3883285522461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8896150588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8527956008911</t>
+    <t xml:space="preserve">12.8896141052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8527975082397</t>
   </si>
   <si>
     <t xml:space="preserve">12.9532070159912</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6184997558594</t>
+    <t xml:space="preserve">12.6185007095337</t>
   </si>
   <si>
     <t xml:space="preserve">12.4846162796021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.384204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8821430206299</t>
+    <t xml:space="preserve">12.3842039108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8821420669556</t>
   </si>
   <si>
     <t xml:space="preserve">11.7348709106445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2127265930176</t>
+    <t xml:space="preserve">11.2127256393433</t>
   </si>
   <si>
     <t xml:space="preserve">10.7307453155518</t>
@@ -89,43 +89,43 @@
     <t xml:space="preserve">11.2194204330444</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2461948394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9148349761963</t>
+    <t xml:space="preserve">11.2461957931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9148359298706</t>
   </si>
   <si>
     <t xml:space="preserve">11.1323957443237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6143741607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6813173294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5474328994751</t>
+    <t xml:space="preserve">11.6143760681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6813163757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5474338531494</t>
   </si>
   <si>
     <t xml:space="preserve">11.3466091156006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3131380081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3298711776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8947525024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8780174255371</t>
+    <t xml:space="preserve">11.3131370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3298740386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8947515487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8780183792114</t>
   </si>
   <si>
     <t xml:space="preserve">11.045371055603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4261617660522</t>
+    <t xml:space="preserve">10.4261627197266</t>
   </si>
   <si>
     <t xml:space="preserve">10.4094257354736</t>
@@ -134,19 +134,19 @@
     <t xml:space="preserve">11.7080936431885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7147884368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0494976043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7482576370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7449111938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2135019302368</t>
+    <t xml:space="preserve">11.714786529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0494956970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7482566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7449102401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2135038375854</t>
   </si>
   <si>
     <t xml:space="preserve">12.2168493270874</t>
@@ -158,82 +158,82 @@
     <t xml:space="preserve">12.7189121246338</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8293685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0201511383057</t>
+    <t xml:space="preserve">12.82936668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0201501846313</t>
   </si>
   <si>
     <t xml:space="preserve">13.2209749221802</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3849821090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870904922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3347768783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3146915435791</t>
+    <t xml:space="preserve">13.3849840164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870914459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536203384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3347749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3146924972534</t>
   </si>
   <si>
     <t xml:space="preserve">13.0569667816162</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2109346389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306047439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2879180908203</t>
+    <t xml:space="preserve">13.2109317779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661823272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.287917137146</t>
   </si>
   <si>
     <t xml:space="preserve">12.8260183334351</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9833326339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.903000831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2377099990845</t>
+    <t xml:space="preserve">12.9833335876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9029989242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2377090454102</t>
   </si>
   <si>
     <t xml:space="preserve">13.1674213409424</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1138687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971326828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5046997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8092832565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.886266708374</t>
+    <t xml:space="preserve">13.1138668060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5046977996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8092842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8862686157227</t>
   </si>
   <si>
     <t xml:space="preserve">12.7055234909058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7222576141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9163913726807</t>
+    <t xml:space="preserve">12.7222604751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.916389465332</t>
   </si>
   <si>
     <t xml:space="preserve">13.0301904678345</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">12.6318893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7021780014038</t>
+    <t xml:space="preserve">12.7021789550781</t>
   </si>
   <si>
     <t xml:space="preserve">12.8695306777954</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">12.5682935714722</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8360595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494501113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958946228027</t>
+    <t xml:space="preserve">12.8360586166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958936691284</t>
   </si>
   <si>
     <t xml:space="preserve">12.5348215103149</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7791595458984</t>
+    <t xml:space="preserve">12.7791576385498</t>
   </si>
   <si>
     <t xml:space="preserve">12.7691192626953</t>
@@ -278,37 +278,37 @@
     <t xml:space="preserve">12.7865648269653</t>
   </si>
   <si>
-    <t xml:space="preserve">12.502420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6512594223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7527389526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5836067199707</t>
+    <t xml:space="preserve">12.5024185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6512603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.752739906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5836038589478</t>
   </si>
   <si>
     <t xml:space="preserve">12.4990377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5700731277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159521102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2791614532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0660543441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1641511917114</t>
+    <t xml:space="preserve">12.5700740814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2791604995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0660514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776819229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1641502380371</t>
   </si>
   <si>
     <t xml:space="preserve">12.170916557312</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">12.1100273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1269397735596</t>
+    <t xml:space="preserve">12.1269407272339</t>
   </si>
   <si>
     <t xml:space="preserve">11.9814853668213</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7459735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580238342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231372833252</t>
+    <t xml:space="preserve">12.7459745407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580247879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231382369995</t>
   </si>
   <si>
     <t xml:space="preserve">11.697340965271</t>
@@ -341,274 +341,274 @@
     <t xml:space="preserve">11.2406768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8212251663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0613956451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.196702003479</t>
+    <t xml:space="preserve">10.8212232589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0613946914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1967000961304</t>
   </si>
   <si>
     <t xml:space="preserve">11.4064292907715</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248222351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.665620803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1886606216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5878190994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6825342178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.839412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0199728012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3616228103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0233545303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1924896240234</t>
+    <t xml:space="preserve">11.5248241424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6656198501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1886615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5878171920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6825332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8394117355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0199708938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3616237640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0233564376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1924886703491</t>
   </si>
   <si>
     <t xml:space="preserve">13.4969320297241</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4698686599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307579040527</t>
+    <t xml:space="preserve">13.4698696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307569503784</t>
   </si>
   <si>
     <t xml:space="preserve">13.4800186157227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2939682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548564910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0740938186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.03688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9489345550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0910062789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0707120895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9962902069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8576011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113042831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1248359680176</t>
+    <t xml:space="preserve">13.2939701080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108835220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0740947723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368852615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9489336013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9827613830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.091007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0707130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9962930679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8576030731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1248340606689</t>
   </si>
   <si>
     <t xml:space="preserve">13.1823406219482</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0605630874634</t>
+    <t xml:space="preserve">13.0605640411377</t>
   </si>
   <si>
     <t xml:space="preserve">13.1857233047485</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4123630523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5679683685303</t>
+    <t xml:space="preserve">13.4123649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.567967414856</t>
   </si>
   <si>
     <t xml:space="preserve">13.4157466888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.513843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7066564559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8352012634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2106771469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.457615852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7552890777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838319778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.01575756073</t>
+    <t xml:space="preserve">13.5138444900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.706657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8351993560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2106790542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.457612991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7552900314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838329315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0157585144043</t>
   </si>
   <si>
     <t xml:space="preserve">14.9853143692017</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3303489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6652336120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.289755821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8297100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7722024917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.951488494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7485256195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7180814743042</t>
+    <t xml:space="preserve">15.3303480148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6652345657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2897567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8297109603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.684253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7722053527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9514865875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7485246658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7180805206299</t>
   </si>
   <si>
     <t xml:space="preserve">14.877067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992658615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751663208008</t>
+    <t xml:space="preserve">14.7992668151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751644134521</t>
   </si>
   <si>
     <t xml:space="preserve">14.9007482528687</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2018051147461</t>
+    <t xml:space="preserve">15.2018041610718</t>
   </si>
   <si>
     <t xml:space="preserve">14.8939809799194</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8330936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988431930542</t>
+    <t xml:space="preserve">14.8330898284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988451004028</t>
   </si>
   <si>
     <t xml:space="preserve">14.9142770767212</t>
   </si>
   <si>
-    <t xml:space="preserve">14.927809715271</t>
+    <t xml:space="preserve">14.9278087615967</t>
   </si>
   <si>
     <t xml:space="preserve">14.7383794784546</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7248458862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5421829223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4440841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0529699325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1442995071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1104717254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.954870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0901775360107</t>
+    <t xml:space="preserve">14.7248430252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.542181968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4440851211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0529670715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1443004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1104726791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9548711776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0901784896851</t>
   </si>
   <si>
     <t xml:space="preserve">15.2187204360962</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7823505401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6166019439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764314651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1599369049072</t>
+    <t xml:space="preserve">14.7823534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707239151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6166000366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764276504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1599388122559</t>
   </si>
   <si>
     <t xml:space="preserve">14.2546539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0415439605713</t>
+    <t xml:space="preserve">14.041543006897</t>
   </si>
   <si>
     <t xml:space="preserve">14.1125793457031</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0381631851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1430253982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903820037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527526855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2072954177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3561315536499</t>
+    <t xml:space="preserve">14.0381603240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1430234909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903800964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527507781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.20729637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3561344146729</t>
   </si>
   <si>
     <t xml:space="preserve">14.4373188018799</t>
@@ -617,100 +617,100 @@
     <t xml:space="preserve">14.3730487823486</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3087768554688</t>
+    <t xml:space="preserve">14.3087759017944</t>
   </si>
   <si>
     <t xml:space="preserve">14.2411222457886</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3392190933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2512702941895</t>
+    <t xml:space="preserve">14.3392200469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2512722015381</t>
   </si>
   <si>
     <t xml:space="preserve">14.1464080810547</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1058168411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1193475723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2275943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2715654373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.149790763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0753707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0719861984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749500274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667032241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4779109954834</t>
+    <t xml:space="preserve">14.1058158874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.119345664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2275905609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2715625762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1497898101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0753717422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0719871520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667041778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4779100418091</t>
   </si>
   <si>
     <t xml:space="preserve">14.6267490386963</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7519102096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.816180229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.103705406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0834102630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172399520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1544485092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999057769775</t>
+    <t xml:space="preserve">14.7519092559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8161783218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1037092208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0834121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882772445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172409057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1544504165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999029159546</t>
   </si>
   <si>
     <t xml:space="preserve">15.4758043289185</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3574113845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3912363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893350601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1713600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1003246307373</t>
+    <t xml:space="preserve">15.3574094772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3912391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1713619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1003265380859</t>
   </si>
   <si>
     <t xml:space="preserve">15.3946199417114</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3168201446533</t>
+    <t xml:space="preserve">15.3168182373047</t>
   </si>
   <si>
     <t xml:space="preserve">15.3134355545044</t>
@@ -719,79 +719,79 @@
     <t xml:space="preserve">15.4182987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4250650405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366916656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6753816604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6449403762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7295055389404</t>
+    <t xml:space="preserve">15.4250640869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366926193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6753826141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6449384689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7295026779175</t>
   </si>
   <si>
     <t xml:space="preserve">15.6618528366089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6517057418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6821479797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637540817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081497192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415576934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7024431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.65846824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588918685913</t>
+    <t xml:space="preserve">15.6517038345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.682149887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637550354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081516265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415586471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7024440765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333108901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584711074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588890075684</t>
   </si>
   <si>
     <t xml:space="preserve">15.5874338150024</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6550884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227401733398</t>
+    <t xml:space="preserve">15.6550874710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227392196655</t>
   </si>
   <si>
     <t xml:space="preserve">16.3350086212158</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0339488983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4060440063477</t>
+    <t xml:space="preserve">16.0339450836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.406042098999</t>
   </si>
   <si>
     <t xml:space="preserve">16.4026622772217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4195728302002</t>
+    <t xml:space="preserve">16.4195766448975</t>
   </si>
   <si>
     <t xml:space="preserve">16.6935710906982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.099494934082</t>
+    <t xml:space="preserve">17.0994930267334</t>
   </si>
   <si>
     <t xml:space="preserve">16.9980144500732</t>
@@ -803,49 +803,49 @@
     <t xml:space="preserve">17.4208507537842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5392436981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6407241821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4039363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4885063171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3531951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3870239257812</t>
+    <t xml:space="preserve">17.5392456054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6407260894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4039344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4885025024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.353199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3870220184326</t>
   </si>
   <si>
     <t xml:space="preserve">17.522331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4546794891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.877513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8098583221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7083797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7591209411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6745529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5730724334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3362846374512</t>
+    <t xml:space="preserve">17.4546756744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8775157928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8098621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7083778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7591190338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6745510101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730686187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3362808227539</t>
   </si>
   <si>
     <t xml:space="preserve">17.2009754180908</t>
@@ -854,37 +854,37 @@
     <t xml:space="preserve">17.2348022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2517147064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2178859710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3701095581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4560203552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7147541046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5767650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.559513092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.469820022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6147117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7729568481445</t>
+    <t xml:space="preserve">17.2517166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.217887878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3701114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.456018447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7147521972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5767612457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5595149993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975059509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4698181152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.614709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7729587554932</t>
   </si>
   <si>
     <t xml:space="preserve">17.00754737854</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">17.1662349700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1317367553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9937477111816</t>
+    <t xml:space="preserve">17.1317386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.993745803833</t>
   </si>
   <si>
     <t xml:space="preserve">16.9868469238281</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">16.9661464691162</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8350524902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.84885597229</t>
+    <t xml:space="preserve">16.8350563049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8488540649414</t>
   </si>
   <si>
     <t xml:space="preserve">16.8281555175781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7591609954834</t>
+    <t xml:space="preserve">16.7591571807861</t>
   </si>
   <si>
     <t xml:space="preserve">16.8695526123047</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">16.9178504943848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9730472564697</t>
+    <t xml:space="preserve">16.9730491638184</t>
   </si>
   <si>
     <t xml:space="preserve">16.9385471343994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.152437210083</t>
+    <t xml:space="preserve">17.1524353027344</t>
   </si>
   <si>
     <t xml:space="preserve">16.6625652313232</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">16.5659694671631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5038738250732</t>
+    <t xml:space="preserve">16.5038757324219</t>
   </si>
   <si>
     <t xml:space="preserve">16.8626537322998</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">16.80055809021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8971519470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5383739471436</t>
+    <t xml:space="preserve">16.8971500396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5383682250977</t>
   </si>
   <si>
     <t xml:space="preserve">16.5590705871582</t>
@@ -965,19 +965,19 @@
     <t xml:space="preserve">16.4900741577148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2416877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3037815093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2485866546631</t>
+    <t xml:space="preserve">16.2416896820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.303783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2485847473145</t>
   </si>
   <si>
     <t xml:space="preserve">16.1243953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1864929199219</t>
+    <t xml:space="preserve">16.1864891052246</t>
   </si>
   <si>
     <t xml:space="preserve">16.1588935852051</t>
@@ -986,43 +986,43 @@
     <t xml:space="preserve">16.5314712524414</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2899856567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3175849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5452690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3658790588379</t>
+    <t xml:space="preserve">16.2899875640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3175868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5452728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3658771514893</t>
   </si>
   <si>
     <t xml:space="preserve">16.4624767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3313827514648</t>
+    <t xml:space="preserve">16.3313808441162</t>
   </si>
   <si>
     <t xml:space="preserve">16.3520812988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6970615386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3865814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4486751556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5107746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4210796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4348754882812</t>
+    <t xml:space="preserve">16.6970634460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3865795135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4486770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5107727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4210758209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4348773956299</t>
   </si>
   <si>
     <t xml:space="preserve">16.3934783935547</t>
@@ -1031,76 +1031,76 @@
     <t xml:space="preserve">16.4969730377197</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5245742797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4003772735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4555740356445</t>
+    <t xml:space="preserve">16.5245704650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4003810882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4555759429932</t>
   </si>
   <si>
     <t xml:space="preserve">16.358980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.283088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5521697998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.179594039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2071876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1933917999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9036083221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5586271286011</t>
+    <t xml:space="preserve">16.2830848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5521717071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1795921325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2071914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1933879852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9036045074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5586242675781</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965295791626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9381065368652</t>
+    <t xml:space="preserve">15.9381046295166</t>
   </si>
   <si>
     <t xml:space="preserve">15.7794151306152</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7656135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7863130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9795026779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9312047958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7035188674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6483192443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8415107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7518167495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691072463989</t>
+    <t xml:space="preserve">15.7656145095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7863121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9795017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9312057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7035160064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6483201980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8415098190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7518157958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691101074219</t>
   </si>
   <si>
     <t xml:space="preserve">15.8622093200684</t>
@@ -1109,103 +1109,103 @@
     <t xml:space="preserve">16.0277996063232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8967065811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6276216506958</t>
+    <t xml:space="preserve">15.8967094421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6276226043701</t>
   </si>
   <si>
     <t xml:space="preserve">15.7173185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5310297012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413299560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2481451034546</t>
+    <t xml:space="preserve">15.53102684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034265518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413318634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2481422424316</t>
   </si>
   <si>
     <t xml:space="preserve">15.3171396255493</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3309392929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2826414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792400360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.26194190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.600025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9519062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9726028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.986400604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0416011810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8553085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932109832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2895412445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1791486740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2067441940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3999347686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2343435287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3033409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137334823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3861351013184</t>
+    <t xml:space="preserve">15.3309383392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.282642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792371749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619428634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6000242233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.489631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9519052505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9726047515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9864025115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0415992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8553104400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932119369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2895402908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1791477203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2067451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3999366760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2343454360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033399581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137363433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.386137008667</t>
   </si>
   <si>
     <t xml:space="preserve">15.634521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">16.145092010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4831733703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6073684692383</t>
+    <t xml:space="preserve">16.1450939178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4831714630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.607364654541</t>
   </si>
   <si>
     <t xml:space="preserve">16.37278175354</t>
@@ -1214,25 +1214,25 @@
     <t xml:space="preserve">16.6349678039551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4141788482666</t>
+    <t xml:space="preserve">16.414176940918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0898971557617</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2002906799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.731559753418</t>
+    <t xml:space="preserve">16.2002925872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7315616607666</t>
   </si>
   <si>
     <t xml:space="preserve">16.69016456604</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4762744903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7522621154785</t>
+    <t xml:space="preserve">16.4762763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7522602081299</t>
   </si>
   <si>
     <t xml:space="preserve">16.6487636566162</t>
@@ -1241,169 +1241,169 @@
     <t xml:space="preserve">16.6280670166016</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0420455932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0765399932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1110382080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2145347595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1455364227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1800346374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0071029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2140865325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.110595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5931234359741</t>
+    <t xml:space="preserve">17.0420417785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0765419006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1110363006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2145328521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1455383300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1800365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.00710105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2140884399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1105937957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5931253433228</t>
   </si>
   <si>
     <t xml:space="preserve">15.6621208190918</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0066556930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7306728363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9031629562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9721612930298</t>
+    <t xml:space="preserve">15.0066585540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.730673789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9031639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9721584320068</t>
   </si>
   <si>
     <t xml:space="preserve">15.4551334381104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1101484298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0411548614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0756540298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.351637840271</t>
+    <t xml:space="preserve">15.1101522445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0411558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0756530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3516397476196</t>
   </si>
   <si>
     <t xml:space="preserve">15.4206342697144</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5241279602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6966190338135</t>
+    <t xml:space="preserve">15.5241289138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6966218948364</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.87424659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5560579299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7328300476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914087295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3439292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792819976807</t>
+    <t xml:space="preserve">15.874249458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.556056022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7328310012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914125442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3439273834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792839050293</t>
   </si>
   <si>
     <t xml:space="preserve">14.7782526016235</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4247064590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5307712554932</t>
+    <t xml:space="preserve">14.4247074127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5307693481445</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600620269775</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4954166412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8873167037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1135845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3186407089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6014804840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0257368087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0610904693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9550266265869</t>
+    <t xml:space="preserve">14.4954147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8873147964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1135835647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3186416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6014795303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0257358551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0610885620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9550256729126</t>
   </si>
   <si>
     <t xml:space="preserve">14.8489637374878</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8843173980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7075424194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671543121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2025089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.566125869751</t>
+    <t xml:space="preserve">14.8843154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7075443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671533584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2025108337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5661249160767</t>
   </si>
   <si>
     <t xml:space="preserve">14.6368350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2832880020142</t>
+    <t xml:space="preserve">14.2832870483398</t>
   </si>
   <si>
     <t xml:space="preserve">14.085301399231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.813606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3539962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3893518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428979873657</t>
+    <t xml:space="preserve">14.8136072158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3539981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3893527984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.74289894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.1418695449829</t>
@@ -1412,22 +1412,22 @@
     <t xml:space="preserve">14.1772241592407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2479333877563</t>
+    <t xml:space="preserve">14.2479343414307</t>
   </si>
   <si>
     <t xml:space="preserve">14.2125797271729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0711584091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.943883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8731727600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8166065216064</t>
+    <t xml:space="preserve">14.071159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9438819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8731746673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8166074752808</t>
   </si>
   <si>
     <t xml:space="preserve">13.8590326309204</t>
@@ -1436,37 +1436,37 @@
     <t xml:space="preserve">14.0145921707153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.929741859436</t>
+    <t xml:space="preserve">13.9297409057617</t>
   </si>
   <si>
     <t xml:space="preserve">14.0004501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0994434356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9721651077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.028733253479</t>
+    <t xml:space="preserve">14.0994424819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9721660614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0287342071533</t>
   </si>
   <si>
     <t xml:space="preserve">14.0570182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">14.127724647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9196739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6721897125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.434775352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5054864883423</t>
+    <t xml:space="preserve">14.1277265548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9196720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6721868515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5054845809937</t>
   </si>
   <si>
     <t xml:space="preserve">13.49134349823</t>
@@ -1478,40 +1478,40 @@
     <t xml:space="preserve">13.4630603790283</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5620546340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5337677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1660823822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7842502593994</t>
+    <t xml:space="preserve">13.5620527267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.533766746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1660804748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7842493057251</t>
   </si>
   <si>
     <t xml:space="preserve">12.6852569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1620073318481</t>
+    <t xml:space="preserve">12.1620082855225</t>
   </si>
   <si>
     <t xml:space="preserve">12.6569709777832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4064922332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5479116439819</t>
+    <t xml:space="preserve">13.4064912796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5479097366333</t>
   </si>
   <si>
     <t xml:space="preserve">13.7883224487305</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7741794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5903367996216</t>
+    <t xml:space="preserve">13.7741804122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5903348922729</t>
   </si>
   <si>
     <t xml:space="preserve">13.4489183425903</t>
@@ -1520,52 +1520,52 @@
     <t xml:space="preserve">13.3074989318848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3923492431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0105199813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1519393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2933559417725</t>
+    <t xml:space="preserve">13.3923511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0105180740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1519374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2933568954468</t>
   </si>
   <si>
     <t xml:space="preserve">12.9256687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0388021469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9963760375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2367887496948</t>
+    <t xml:space="preserve">13.0388031005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9963779449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2367877960205</t>
   </si>
   <si>
     <t xml:space="preserve">13.0953702926636</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6469030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6751880645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0670871734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2509317398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2085056304932</t>
+    <t xml:space="preserve">13.6469020843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6751861572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0670862197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2509326934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2085046768188</t>
   </si>
   <si>
     <t xml:space="preserve">13.0812292098999</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3499250411987</t>
+    <t xml:space="preserve">13.3499240875244</t>
   </si>
   <si>
     <t xml:space="preserve">12.8408174514771</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">12.5296964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8973836898804</t>
+    <t xml:space="preserve">12.8973846435547</t>
   </si>
   <si>
     <t xml:space="preserve">12.6004037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7317552566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5761938095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5196266174316</t>
+    <t xml:space="preserve">13.7317543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5761957168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.519627571106</t>
   </si>
   <si>
     <t xml:space="preserve">13.7176132202148</t>
@@ -1598,25 +1598,25 @@
     <t xml:space="preserve">13.7600383758545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9156007766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7458963394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0428791046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8448886871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5417680740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.221848487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.945556640625</t>
+    <t xml:space="preserve">13.915599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7458972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0428762435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8448915481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5417671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2218475341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9455547332764</t>
   </si>
   <si>
     <t xml:space="preserve">14.1782236099243</t>
@@ -1625,73 +1625,73 @@
     <t xml:space="preserve">13.9891805648804</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2073087692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4399766921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2654733657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4108924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4981422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690570831299</t>
+    <t xml:space="preserve">14.2073078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4399747848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2654752731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4108915328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4981412887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690580368042</t>
   </si>
   <si>
     <t xml:space="preserve">14.3527231216431</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3381824493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5126829147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3963479995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871871948242</t>
+    <t xml:space="preserve">14.3381814956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5126819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3963499069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871843338013</t>
   </si>
   <si>
     <t xml:space="preserve">14.4254331588745</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4836015701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6144752502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8326025009155</t>
+    <t xml:space="preserve">14.4835996627808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6144781112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8326034545898</t>
   </si>
   <si>
     <t xml:space="preserve">14.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1234369277954</t>
+    <t xml:space="preserve">15.1234378814697</t>
   </si>
   <si>
     <t xml:space="preserve">15.1961460113525</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4142732620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4506282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3415660858154</t>
+    <t xml:space="preserve">15.4142723083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4506273269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3415641784668</t>
   </si>
   <si>
     <t xml:space="preserve">15.2325010299683</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3052101135254</t>
+    <t xml:space="preserve">15.3052091598511</t>
   </si>
   <si>
     <t xml:space="preserve">15.268856048584</t>
@@ -1703,88 +1703,88 @@
     <t xml:space="preserve">15.0507297515869</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0870838165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9416666030884</t>
+    <t xml:space="preserve">15.0870809555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9416646957397</t>
   </si>
   <si>
     <t xml:space="preserve">14.7235383987427</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0143737792969</t>
+    <t xml:space="preserve">15.0143747329712</t>
   </si>
   <si>
     <t xml:space="preserve">14.5781221389771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598924636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6508312225342</t>
+    <t xml:space="preserve">14.759895324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6508321762085</t>
   </si>
   <si>
     <t xml:space="preserve">14.3672647476196</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3236408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5272245407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4545164108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7962484359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.905312538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.032299041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3594875335693</t>
+    <t xml:space="preserve">14.3236417770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5272254943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.454517364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7962493896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.905309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0323009490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.359489440918</t>
   </si>
   <si>
     <t xml:space="preserve">16.5049076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6139698028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.541259765625</t>
+    <t xml:space="preserve">16.6139678955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5412635803223</t>
   </si>
   <si>
     <t xml:space="preserve">16.8320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6503219604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5776138305664</t>
+    <t xml:space="preserve">16.6503238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.577615737915</t>
   </si>
   <si>
     <t xml:space="preserve">16.8684501647949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7593879699707</t>
+    <t xml:space="preserve">16.7593841552734</t>
   </si>
   <si>
     <t xml:space="preserve">17.0502223968506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0865745544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4864749908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4137687683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2683486938477</t>
+    <t xml:space="preserve">17.086576461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4864730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4137649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.268346786499</t>
   </si>
   <si>
     <t xml:space="preserve">17.5228309631348</t>
@@ -1793,34 +1793,34 @@
     <t xml:space="preserve">17.8136653900146</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7409553527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6318950653076</t>
+    <t xml:space="preserve">17.7409572601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.631893157959</t>
   </si>
   <si>
     <t xml:space="preserve">17.7046031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6682472229004</t>
+    <t xml:space="preserve">17.6682453155518</t>
   </si>
   <si>
     <t xml:space="preserve">18.0681476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9227275848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1044998168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8500213623047</t>
+    <t xml:space="preserve">17.9227294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1045017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8500194549561</t>
   </si>
   <si>
     <t xml:space="preserve">17.9590835571289</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1772079467773</t>
+    <t xml:space="preserve">18.177209854126</t>
   </si>
   <si>
     <t xml:space="preserve">18.0317897796631</t>
@@ -1829,58 +1829,58 @@
     <t xml:space="preserve">18.2862739562988</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3589839935303</t>
+    <t xml:space="preserve">18.3589820861816</t>
   </si>
   <si>
     <t xml:space="preserve">18.4680442810059</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5771083831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9954357147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5591850280762</t>
+    <t xml:space="preserve">18.5771064758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9954395294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5591831207275</t>
   </si>
   <si>
     <t xml:space="preserve">17.5955390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4501190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2499179840088</t>
+    <t xml:space="preserve">17.4501209259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2499198913574</t>
   </si>
   <si>
     <t xml:space="preserve">18.3953342437744</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2135620117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3226280212402</t>
+    <t xml:space="preserve">18.213565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3226261138916</t>
   </si>
   <si>
     <t xml:space="preserve">18.6134624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6861724853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8315868377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1951332092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9770050048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0860691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2678413391113</t>
+    <t xml:space="preserve">18.6861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8315849304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1951313018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9770069122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0860710144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.26784324646</t>
   </si>
   <si>
     <t xml:space="preserve">19.1224231719971</t>
@@ -1892,31 +1892,31 @@
     <t xml:space="preserve">19.4132614135742</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4496154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.904806137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7230319976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321956634521</t>
+    <t xml:space="preserve">19.449613571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9048023223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7230339050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321975708008</t>
   </si>
   <si>
     <t xml:space="preserve">16.7957420349121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2314891815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9775142669678</t>
+    <t xml:space="preserve">19.2314872741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9775123596191</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047027587891</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3774108886719</t>
+    <t xml:space="preserve">17.3774127960205</t>
   </si>
   <si>
     <t xml:space="preserve">18.7952346801758</t>
@@ -1925,109 +1925,106 @@
     <t xml:space="preserve">18.5407524108887</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8679428100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9042949676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8495101928711</t>
+    <t xml:space="preserve">18.8679447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9042987823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8495121002197</t>
   </si>
   <si>
     <t xml:space="preserve">19.42138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7327499389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.394401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8105926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549110412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3554821014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8495121002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1219577789307</t>
+    <t xml:space="preserve">19.7327480316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3944034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8105907440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3554801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.121955871582</t>
   </si>
   <si>
     <t xml:space="preserve">19.9273529052734</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4603061676025</t>
+    <t xml:space="preserve">19.4603080749512</t>
   </si>
   <si>
     <t xml:space="preserve">19.3435459136963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3046226501465</t>
+    <t xml:space="preserve">19.3046245574951</t>
   </si>
   <si>
     <t xml:space="preserve">19.966272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2657012939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.771671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7597370147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1608772277832</t>
+    <t xml:space="preserve">19.2657051086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7716693878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7597351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1608753204346</t>
   </si>
   <si>
     <t xml:space="preserve">20.044116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.172815322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0560531616211</t>
+    <t xml:space="preserve">21.1728172302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0560512542725</t>
   </si>
   <si>
     <t xml:space="preserve">20.9392890930176</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2895774841309</t>
+    <t xml:space="preserve">21.2895755767822</t>
   </si>
   <si>
     <t xml:space="preserve">21.0171318054199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7836074829102</t>
+    <t xml:space="preserve">20.7836093902588</t>
   </si>
   <si>
     <t xml:space="preserve">20.7057647705078</t>
   </si>
   <si>
-    <t xml:space="preserve">21.094970703125</t>
+    <t xml:space="preserve">21.0949726104736</t>
   </si>
   <si>
     <t xml:space="preserve">21.4452571868896</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7566242218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9512233734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6009407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7955436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0290679931641</t>
+    <t xml:space="preserve">21.7566223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9512252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6009387969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7955417633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0290660858154</t>
   </si>
   <si>
     <t xml:space="preserve">22.0679874420166</t>
@@ -2036,10 +2033,10 @@
     <t xml:space="preserve">22.5350360870361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5739574432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6517944335938</t>
+    <t xml:space="preserve">22.5739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6517963409424</t>
   </si>
   <si>
     <t xml:space="preserve">22.7685585021973</t>
@@ -2054,13 +2051,13 @@
     <t xml:space="preserve">22.3404312133789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2625904083252</t>
+    <t xml:space="preserve">22.2625923156738</t>
   </si>
   <si>
     <t xml:space="preserve">23.5080509185791</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9750995635986</t>
+    <t xml:space="preserve">23.9750957489014</t>
   </si>
   <si>
     <t xml:space="preserve">24.4032249450684</t>
@@ -2069,34 +2066,34 @@
     <t xml:space="preserve">24.9091930389404</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7145881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5199851989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.298397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7924327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1427154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7535076141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6367454528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.16969871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0140190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0799217224121</t>
+    <t xml:space="preserve">24.7145900726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5199871063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2983989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7924308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1427173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7535095214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6367492675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1697006225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0140171051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0799236297607</t>
   </si>
   <si>
     <t xml:space="preserve">23.7026538848877</t>
@@ -2117,10 +2114,10 @@
     <t xml:space="preserve">23.8583354949951</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7415733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8194141387939</t>
+    <t xml:space="preserve">23.7415714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8194160461426</t>
   </si>
   <si>
     <t xml:space="preserve">23.6637325286865</t>
@@ -2129,13 +2126,13 @@
     <t xml:space="preserve">23.4302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0918598175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3912868499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3523654937744</t>
+    <t xml:space="preserve">24.0918579101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3912887573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.352367401123</t>
   </si>
   <si>
     <t xml:space="preserve">23.0410022735596</t>
@@ -2144,13 +2141,13 @@
     <t xml:space="preserve">23.0020809173584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1188430786133</t>
+    <t xml:space="preserve">23.1188449859619</t>
   </si>
   <si>
     <t xml:space="preserve">23.624813079834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6128730773926</t>
+    <t xml:space="preserve">22.6128749847412</t>
   </si>
   <si>
     <t xml:space="preserve">22.1069087982178</t>
@@ -2159,19 +2156,19 @@
     <t xml:space="preserve">22.1847476959229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.496114730835</t>
+    <t xml:space="preserve">22.4961128234863</t>
   </si>
   <si>
     <t xml:space="preserve">22.3015098571777</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6907157897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3793525695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9631614685059</t>
+    <t xml:space="preserve">22.6907176971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3793506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9631633758545</t>
   </si>
   <si>
     <t xml:space="preserve">23.2356071472168</t>
@@ -2180,67 +2177,67 @@
     <t xml:space="preserve">22.9242420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">22.223669052124</t>
+    <t xml:space="preserve">22.2236671447754</t>
   </si>
   <si>
     <t xml:space="preserve">22.4182720184326</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9123020172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4841747283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1338901519775</t>
+    <t xml:space="preserve">21.9123058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4841785430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1338939666748</t>
   </si>
   <si>
     <t xml:space="preserve">21.5230979919434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.717700958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6398601531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2506523132324</t>
+    <t xml:space="preserve">21.7177028656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6398582458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2506542205811</t>
   </si>
   <si>
     <t xml:space="preserve">21.5620193481445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8344612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6787815093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9901485443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1458301544189</t>
+    <t xml:space="preserve">21.8344631195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6787796020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9901466369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1458282470703</t>
   </si>
   <si>
     <t xml:space="preserve">22.8464012145996</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8853187561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4571952819824</t>
+    <t xml:space="preserve">22.8853206634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4571933746338</t>
   </si>
   <si>
     <t xml:space="preserve">21.3284969329834</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2117328643799</t>
+    <t xml:space="preserve">21.2117347717285</t>
   </si>
   <si>
     <t xml:space="preserve">21.3674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9782104492188</t>
+    <t xml:space="preserve">20.9782123565674</t>
   </si>
   <si>
     <t xml:space="preserve">20.6279258728027</t>
@@ -2249,7 +2246,7 @@
     <t xml:space="preserve">21.873384475708</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4407329559326</t>
+    <t xml:space="preserve">23.440731048584</t>
   </si>
   <si>
     <t xml:space="preserve">22.88356590271</t>
@@ -2261,19 +2258,22 @@
     <t xml:space="preserve">22.8039703369141</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7641735076904</t>
+    <t xml:space="preserve">22.7641754150391</t>
   </si>
   <si>
     <t xml:space="preserve">23.0427570343018</t>
   </si>
   <si>
+    <t xml:space="preserve">22.9631595611572</t>
+  </si>
+  <si>
     <t xml:space="preserve">23.2417449951172</t>
   </si>
   <si>
     <t xml:space="preserve">23.0029563903809</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2019443511963</t>
+    <t xml:space="preserve">23.2019462585449</t>
   </si>
   <si>
     <t xml:space="preserve">23.122350692749</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">23.1621475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5203247070312</t>
+    <t xml:space="preserve">23.5203266143799</t>
   </si>
   <si>
     <t xml:space="preserve">23.9580974578857</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0774917602539</t>
+    <t xml:space="preserve">24.0774898529053</t>
   </si>
   <si>
     <t xml:space="preserve">24.4356689453125</t>
@@ -2300,13 +2300,13 @@
     <t xml:space="preserve">24.3560733795166</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7938442230225</t>
+    <t xml:space="preserve">24.7938461303711</t>
   </si>
   <si>
     <t xml:space="preserve">24.1570854187012</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6744537353516</t>
+    <t xml:space="preserve">24.6744518280029</t>
   </si>
   <si>
     <t xml:space="preserve">24.9132385253906</t>
@@ -2318,40 +2318,40 @@
     <t xml:space="preserve">24.7540493011475</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2764778137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1172885894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5152645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4754638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2366828918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3958721160889</t>
+    <t xml:space="preserve">24.2764759063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1172866821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5152626037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4754657745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2366809844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3958702087402</t>
   </si>
   <si>
     <t xml:space="preserve">24.7142505645752</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6346569061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1968841552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6295928955078</t>
+    <t xml:space="preserve">24.6346549987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1968822479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6295948028564</t>
   </si>
   <si>
     <t xml:space="preserve">25.5102005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1520233154297</t>
+    <t xml:space="preserve">25.1520252227783</t>
   </si>
   <si>
     <t xml:space="preserve">25.3510131835938</t>
@@ -2363,13 +2363,13 @@
     <t xml:space="preserve">25.6693916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3908100128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1918201446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0326328277588</t>
+    <t xml:space="preserve">25.3908081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.191822052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0326309204102</t>
   </si>
   <si>
     <t xml:space="preserve">25.2714157104492</t>
@@ -2384,19 +2384,19 @@
     <t xml:space="preserve">25.8683795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0724296569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7591133117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4805278778076</t>
+    <t xml:space="preserve">25.0724277496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7591114044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4805297851562</t>
   </si>
   <si>
     <t xml:space="preserve">23.8785037994385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6397171020508</t>
+    <t xml:space="preserve">23.639720916748</t>
   </si>
   <si>
     <t xml:space="preserve">23.7989082336426</t>
@@ -2405,13 +2405,13 @@
     <t xml:space="preserve">24.5948581695557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9928321838379</t>
+    <t xml:space="preserve">24.9928340911865</t>
   </si>
   <si>
     <t xml:space="preserve">25.430606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3112106323242</t>
+    <t xml:space="preserve">25.3112144470215</t>
   </si>
   <si>
     <t xml:space="preserve">25.2316188812256</t>
@@ -2420,1048 +2420,1051 @@
     <t xml:space="preserve">26.0673656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2663536071777</t>
+    <t xml:space="preserve">26.2663555145264</t>
   </si>
   <si>
     <t xml:space="preserve">26.0275688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7887859344482</t>
+    <t xml:space="preserve">25.7887840270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5499973297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5897979736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9479713439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1071624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.748987197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.873441696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0376949310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3264007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3661994934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0825538635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9233627319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3213386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5999221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3611354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4009323120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5601234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4855899810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8387069702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9978942871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7193126678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8264083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5692901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1263828277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9549694061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4692077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4263553619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1692352294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2120895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7835559844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.340648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2549419403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2977962493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5264377593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9978218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9121170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8692626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7407035827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6549987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9693431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8836402893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5836658477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9264907836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1407585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8407859802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7550773620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6693725585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0550518035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2264652252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7122268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4122524261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1836109161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0979061126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3694000244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3550243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0121994018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3121738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.397876739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7979316711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4551067352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4979591369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6265182495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6978492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5408115386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2693176269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2836933135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.426628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.469482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2552146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.826681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9267616271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1410293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9980945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1266536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5267086029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6552696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.312442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4410037994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6981220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5980415344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3837757110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.512336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3409214019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0265731811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1122798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8123073577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1551322937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2408409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6837463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.726598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8980121612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7694530487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6408939361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1979846954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0694274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9837188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8551597595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1695098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0838031768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9408664703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5551872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0409488677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.912389755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2980690002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2123622894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4838562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6124153137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7409763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1838817596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3552951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.809741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7657089233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7216739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2813320159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0611591339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1051959991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.017126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8850250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.664852142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5767841339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4887161254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9290561676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8409881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7088851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4006462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7969551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9730930328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7529201507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5015029907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2372970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1932640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4134349822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3253650665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5455360412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.149227142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3125782012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1364402770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0483722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3566112518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6208171844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2685432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4446811676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5327491760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0043392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8722343444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6960983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3438243865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6080303192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9162693023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8282012939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2557563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3878593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2997894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7841682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9603023529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7401313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0924072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1804752349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6336059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4574680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5895709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8537769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0299129486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4702568054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5142917633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8665657043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3949756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3069076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1307697296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3509407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4390087127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5711135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6591815948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7032146453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.319694519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8353176116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7472496032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8793525695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0867366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2188377380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.52707862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2628726959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9546337127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7600383758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4077625274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8481063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1123104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1563472747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4645843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5910148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3708438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8992576599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0313587188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5029487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7671527862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2827777862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0753955841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7231216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.471700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8111877441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2387447357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4148826599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1506729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9745388031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7103309631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.842435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8864688873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5469818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2955665588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7359104156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3836326599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9873237609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4276676177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4632396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8007907867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8972339630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8490123748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7525691986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0418968200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6079063415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2703552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0292491912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9328060150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2221336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6916999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4023723602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5470352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7399196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0774707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5952568054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5596828460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2094860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7272720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1003952026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1486167907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4861660003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5826091766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4379444122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.052173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9075088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5343856811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9201583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8237152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1612663269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0165996551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7754936218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9683799743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3541488647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1130428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4988136291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6434783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8363628387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8845863342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6790523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.473518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2324123382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3770751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7146244049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6181812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6664028167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0039520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.245059967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8110656738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8592891693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3415031433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1968383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9557323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5699596405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2577075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3897228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2932796478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1841888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.280632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1359691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7501983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0877456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.991304397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8466396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.701976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5090923309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6055335998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7984180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5573120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6537551879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4252967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0395259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3644256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0750980377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6893291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7857723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9786548614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9304351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.219762802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8822135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1715412139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5928859710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3517780303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0268783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4126491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2679843902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1233196258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4608688354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8948612213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9430828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5446643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1462440490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8569183349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5675888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3391304016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8213443756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.255334854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9177856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1106719970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0142288208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8695659637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6766796112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2426872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6640319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6158103942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0371551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1209487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4940719604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2173919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8798408508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9407119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0853748321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.422924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.194465637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2909088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6284580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7731227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0499992370605</t>
   </si>
   <si>
     <t xml:space="preserve">25.5499992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5897979736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9479732513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1071643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7489852905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8734397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0376930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3263988494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3661975860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0825538635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9233646392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3213367462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5999202728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3611373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4009323120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5601234436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4855918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8387050628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9978942871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7193126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8264083862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5692901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1263828277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9549694061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4692077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4263553619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1692352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2120895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7835559844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.340648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2549419403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2977962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5264377593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9978218078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9121170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8692626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7407035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6549987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9693431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8836402893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5836658477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9264907836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1407585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8407859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7550773620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6693725585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0550518035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2264652252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7122268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4122524261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1836109161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0979061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3694000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3550243377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0121994018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3121738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.397876739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7979316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4551067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4979591369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6265182495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6978492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5408115386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2693176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2836933135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.426628112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.469482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2552146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.826681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9267616271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1410293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9980945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1266536712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5267086029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6552696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.312442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4410037994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6981220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5980415344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3837757110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.512336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3409214019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0265731811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1122798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8123073577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1551322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2408409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6837463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.726598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8980121612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7694530487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6408939361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1979846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0694274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9837188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8551597595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1695098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0838031768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9408664703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5551872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0409488677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.912389755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2980690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2123622894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4838562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6124153137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7409763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1838817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3552951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.809741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7657089233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7216739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2813320159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0611591339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1051959991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.017126083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8850250244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.664852142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5767841339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4887161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9290561676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8409881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7088851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4006462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7969551086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9730930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7529201507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5015029907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2372970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1932640075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4134349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3253650665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5455360412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.149227142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3125782012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1364402770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0483722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3566112518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6208171844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2685432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4446811676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5327491760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0043392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8722343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6960983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3438243865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6080303192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9162693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8282012939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2557563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3878593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2997894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7841682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9603023529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7401313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0924072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1804752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6336059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4574680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5895709991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8537769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0299129486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4702568054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5142917633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8665657043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3949756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3069076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1307697296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3509407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4390087127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5711135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6591815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7032146453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.319694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8353176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7472496032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8793525695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0867366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2188377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.52707862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2628726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9546337127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7600383758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4077625274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8481063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1123104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1563472747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4645843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5910148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3708438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8992576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0313587188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5029487609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7671527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2827777862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0753955841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7231216430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.471700668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8111877441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2387447357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4148826599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1506729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9745388031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7103309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.842435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8864688873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5469818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2955665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7359104156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3836326599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9873237609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4276676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4632396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8007907867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8972339630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8490123748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7525691986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0418968200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6079063415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2703552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0292491912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9328060150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2221336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6916999816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4023723602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5470352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7399196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0774707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5952568054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5596828460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2094860076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7272720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1003952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1486167907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4861660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5826091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4379444122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.052173614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9075088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5343856811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9201583862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8237152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1612663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0165996551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7754936218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9683799743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3541488647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1130428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4988136291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6434783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8363628387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8845863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6790523529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.473518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2324123382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3770751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7146244049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6181812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6664028167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0039520263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.245059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8110656738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8592891693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3415031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1968383789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9557323455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5699596405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2577075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3897228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2932796478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1841888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.280632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1359691619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7501983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0877456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.991304397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8466396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.701976776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5090923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6055335998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7984180450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5573120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6537551879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4252967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0395259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3644256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0750980377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6893291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7857723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9786548614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9304351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.219762802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8822135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1715412139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5928859710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3517780303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0268783569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4126491546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2679843902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1233196258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4608688354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8948612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9430828094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5446643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1462440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8569183349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5675888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3391304016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8213443756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.255334854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3999996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9177856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1106719970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0142288208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8695659637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6766796112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2426872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6640319824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6158103942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0371551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1209487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4940719604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2173919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8798408508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9407119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0853748321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.422924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.194465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2909088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6284580230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7731227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3500003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2000007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8500003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7000007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8999996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2000007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6000003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8500003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7000007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8999996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0499992370605</t>
   </si>
   <si>
     <t xml:space="preserve">26.1499996185303</t>
@@ -32809,7 +32812,7 @@
         <v>25.5</v>
       </c>
       <c r="G1106" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32861,7 +32864,7 @@
         <v>25.5</v>
       </c>
       <c r="G1108" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32887,7 +32890,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G1109" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32913,7 +32916,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1110" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32939,7 +32942,7 @@
         <v>25</v>
       </c>
       <c r="G1111" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32965,7 +32968,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1112" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32991,7 +32994,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1113" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -33017,7 +33020,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1114" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -33069,7 +33072,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1116" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -33095,7 +33098,7 @@
         <v>24.75</v>
       </c>
       <c r="G1117" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -33121,7 +33124,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1118" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33147,7 +33150,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1119" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33225,7 +33228,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1122" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33251,7 +33254,7 @@
         <v>25.75</v>
       </c>
       <c r="G1123" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33277,7 +33280,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1124" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33303,7 +33306,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1125" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33329,7 +33332,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1126" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33355,7 +33358,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G1127" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33381,7 +33384,7 @@
         <v>27</v>
       </c>
       <c r="G1128" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33407,7 +33410,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1129" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33433,7 +33436,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1130" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33459,7 +33462,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1131" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33485,7 +33488,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1132" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33511,7 +33514,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1133" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33537,7 +33540,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1134" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33563,7 +33566,7 @@
         <v>27.75</v>
       </c>
       <c r="G1135" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33589,7 +33592,7 @@
         <v>28</v>
       </c>
       <c r="G1136" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33615,7 +33618,7 @@
         <v>28</v>
       </c>
       <c r="G1137" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33641,7 +33644,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33667,7 +33670,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1139" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33693,7 +33696,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1140" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33719,7 +33722,7 @@
         <v>29</v>
       </c>
       <c r="G1141" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33745,7 +33748,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33771,7 +33774,7 @@
         <v>29.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33797,7 +33800,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1144" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33823,7 +33826,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1145" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33849,7 +33852,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1146" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33875,7 +33878,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1147" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33901,7 +33904,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1148" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33927,7 +33930,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1149" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33953,7 +33956,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1150" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33979,7 +33982,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1151" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -34005,7 +34008,7 @@
         <v>32</v>
       </c>
       <c r="G1152" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -34031,7 +34034,7 @@
         <v>31.75</v>
       </c>
       <c r="G1153" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -34057,7 +34060,7 @@
         <v>31.5</v>
       </c>
       <c r="G1154" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -34083,7 +34086,7 @@
         <v>32.5</v>
       </c>
       <c r="G1155" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34109,7 +34112,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1156" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34135,7 +34138,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1157" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34161,7 +34164,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1158" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34187,7 +34190,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1159" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34213,7 +34216,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G1160" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34239,7 +34242,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1161" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34265,7 +34268,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G1162" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34291,7 +34294,7 @@
         <v>29.25</v>
       </c>
       <c r="G1163" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34317,7 +34320,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1164" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34343,7 +34346,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G1165" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34369,7 +34372,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34395,7 +34398,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G1167" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34421,7 +34424,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34447,7 +34450,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1169" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34473,7 +34476,7 @@
         <v>29.75</v>
       </c>
       <c r="G1170" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34499,7 +34502,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1171" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34525,7 +34528,7 @@
         <v>30.5</v>
       </c>
       <c r="G1172" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34551,7 +34554,7 @@
         <v>30.5</v>
       </c>
       <c r="G1173" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34577,7 +34580,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1174" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34603,7 +34606,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34629,7 +34632,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34655,7 +34658,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1177" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34681,7 +34684,7 @@
         <v>30.5</v>
       </c>
       <c r="G1178" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34707,7 +34710,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1179" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34733,7 +34736,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1180" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34759,7 +34762,7 @@
         <v>30.5</v>
       </c>
       <c r="G1181" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34785,7 +34788,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1182" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34811,7 +34814,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1183" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34837,7 +34840,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1184" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34863,7 +34866,7 @@
         <v>30.5</v>
       </c>
       <c r="G1185" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34889,7 +34892,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34915,7 +34918,7 @@
         <v>30</v>
       </c>
       <c r="G1187" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34941,7 +34944,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1188" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34967,7 +34970,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1189" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34993,7 +34996,7 @@
         <v>30</v>
       </c>
       <c r="G1190" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -35019,7 +35022,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1191" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -35045,7 +35048,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1192" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -35071,7 +35074,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1193" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -35097,7 +35100,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1194" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -35123,7 +35126,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1195" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35149,7 +35152,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1196" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35175,7 +35178,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1197" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35201,7 +35204,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35227,7 +35230,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35253,7 +35256,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1200" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35279,7 +35282,7 @@
         <v>28.5</v>
       </c>
       <c r="G1201" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35305,7 +35308,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1202" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35331,7 +35334,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1203" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35357,7 +35360,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1204" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35383,7 +35386,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1205" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35409,7 +35412,7 @@
         <v>28.75</v>
       </c>
       <c r="G1206" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35435,7 +35438,7 @@
         <v>29.5</v>
       </c>
       <c r="G1207" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35461,7 +35464,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1208" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35487,7 +35490,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1209" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35513,7 +35516,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1210" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35539,7 +35542,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1211" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35565,7 +35568,7 @@
         <v>29</v>
       </c>
       <c r="G1212" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35591,7 +35594,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35617,7 +35620,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1214" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35643,7 +35646,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1215" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35669,7 +35672,7 @@
         <v>29</v>
       </c>
       <c r="G1216" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35695,7 +35698,7 @@
         <v>29</v>
       </c>
       <c r="G1217" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35721,7 +35724,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1218" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35747,7 +35750,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1219" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35773,7 +35776,7 @@
         <v>29</v>
       </c>
       <c r="G1220" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35799,7 +35802,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1221" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35825,7 +35828,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35851,7 +35854,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1223" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35877,7 +35880,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35903,7 +35906,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1225" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35929,7 +35932,7 @@
         <v>28</v>
       </c>
       <c r="G1226" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35955,7 +35958,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1227" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35981,7 +35984,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1228" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -36007,7 +36010,7 @@
         <v>27.75</v>
       </c>
       <c r="G1229" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -36033,7 +36036,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -36059,7 +36062,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -36085,7 +36088,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -36111,7 +36114,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1233" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -36137,7 +36140,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1234" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36163,7 +36166,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1235" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36189,7 +36192,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1236" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36215,7 +36218,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1237" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36241,7 +36244,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1238" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36267,7 +36270,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36293,7 +36296,7 @@
         <v>27.75</v>
       </c>
       <c r="G1240" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36319,7 +36322,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G1241" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36345,7 +36348,7 @@
         <v>27.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36371,7 +36374,7 @@
         <v>28</v>
       </c>
       <c r="G1243" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36397,7 +36400,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1244" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36423,7 +36426,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36449,7 +36452,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1246" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36475,7 +36478,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1247" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36501,7 +36504,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1248" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36527,7 +36530,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1249" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36553,7 +36556,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36579,7 +36582,7 @@
         <v>28.75</v>
       </c>
       <c r="G1251" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36605,7 +36608,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1252" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36631,7 +36634,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36657,7 +36660,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1254" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36683,7 +36686,7 @@
         <v>28.25</v>
       </c>
       <c r="G1255" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36709,7 +36712,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G1256" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36735,7 +36738,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36761,7 +36764,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1258" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36787,7 +36790,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1259" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36813,7 +36816,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1260" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36839,7 +36842,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1261" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36865,7 +36868,7 @@
         <v>29.25</v>
       </c>
       <c r="G1262" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36891,7 +36894,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1263" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36917,7 +36920,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1264" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36943,7 +36946,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1265" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36969,7 +36972,7 @@
         <v>30</v>
       </c>
       <c r="G1266" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36995,7 +36998,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1267" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -37021,7 +37024,7 @@
         <v>29.25</v>
       </c>
       <c r="G1268" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -37047,7 +37050,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -37073,7 +37076,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1270" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -37099,7 +37102,7 @@
         <v>29.5</v>
       </c>
       <c r="G1271" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -37125,7 +37128,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1272" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37151,7 +37154,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1273" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37177,7 +37180,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1274" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37203,7 +37206,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37229,7 +37232,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1276" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37255,7 +37258,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1277" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37281,7 +37284,7 @@
         <v>29.25</v>
       </c>
       <c r="G1278" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37307,7 +37310,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37333,7 +37336,7 @@
         <v>28.75</v>
       </c>
       <c r="G1280" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37359,7 +37362,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1281" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37385,7 +37388,7 @@
         <v>29.25</v>
       </c>
       <c r="G1282" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37411,7 +37414,7 @@
         <v>29.25</v>
       </c>
       <c r="G1283" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37437,7 +37440,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1284" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37463,7 +37466,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1285" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37489,7 +37492,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1286" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37515,7 +37518,7 @@
         <v>27.75</v>
       </c>
       <c r="G1287" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37541,7 +37544,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1288" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37567,7 +37570,7 @@
         <v>27.25</v>
       </c>
       <c r="G1289" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37593,7 +37596,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1290" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37619,7 +37622,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1291" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37645,7 +37648,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1292" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37671,7 +37674,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1293" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37697,7 +37700,7 @@
         <v>28.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37723,7 +37726,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G1295" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37749,7 +37752,7 @@
         <v>28.75</v>
       </c>
       <c r="G1296" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37775,7 +37778,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37801,7 +37804,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1298" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37827,7 +37830,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1299" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37853,7 +37856,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1300" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37879,7 +37882,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1301" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37905,7 +37908,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1302" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37931,7 +37934,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1303" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37957,7 +37960,7 @@
         <v>27</v>
       </c>
       <c r="G1304" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37983,7 +37986,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1305" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -38009,7 +38012,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1306" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -38035,7 +38038,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1307" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -38061,7 +38064,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1308" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -38087,7 +38090,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -38113,7 +38116,7 @@
         <v>26.5</v>
       </c>
       <c r="G1310" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -38139,7 +38142,7 @@
         <v>27.25</v>
       </c>
       <c r="G1311" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38165,7 +38168,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1312" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38191,7 +38194,7 @@
         <v>27.25</v>
       </c>
       <c r="G1313" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38217,7 +38220,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1314" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38243,7 +38246,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38269,7 +38272,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38295,7 +38298,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1317" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38321,7 +38324,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1318" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38347,7 +38350,7 @@
         <v>29.75</v>
       </c>
       <c r="G1319" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38373,7 +38376,7 @@
         <v>29.5</v>
       </c>
       <c r="G1320" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38399,7 +38402,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38425,7 +38428,7 @@
         <v>29.5</v>
       </c>
       <c r="G1322" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38451,7 +38454,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38477,7 +38480,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38503,7 +38506,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38529,7 +38532,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1326" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38555,7 +38558,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1327" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38581,7 +38584,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1328" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38607,7 +38610,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1329" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38633,7 +38636,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1330" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38659,7 +38662,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1331" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38685,7 +38688,7 @@
         <v>29</v>
       </c>
       <c r="G1332" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38711,7 +38714,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1333" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38737,7 +38740,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1334" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38763,7 +38766,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1335" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38789,7 +38792,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1336" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38815,7 +38818,7 @@
         <v>29</v>
       </c>
       <c r="G1337" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38841,7 +38844,7 @@
         <v>29.25</v>
       </c>
       <c r="G1338" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38867,7 +38870,7 @@
         <v>29</v>
       </c>
       <c r="G1339" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38893,7 +38896,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1340" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38919,7 +38922,7 @@
         <v>29</v>
       </c>
       <c r="G1341" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38945,7 +38948,7 @@
         <v>29</v>
       </c>
       <c r="G1342" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38971,7 +38974,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38997,7 +39000,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1344" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -39023,7 +39026,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1345" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -39049,7 +39052,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -39075,7 +39078,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -39101,7 +39104,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1348" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39127,7 +39130,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1349" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39153,7 +39156,7 @@
         <v>28.75</v>
       </c>
       <c r="G1350" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39179,7 +39182,7 @@
         <v>29</v>
       </c>
       <c r="G1351" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39205,7 +39208,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1352" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39231,7 +39234,7 @@
         <v>29.5</v>
       </c>
       <c r="G1353" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39257,7 +39260,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1354" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39283,7 +39286,7 @@
         <v>28.75</v>
       </c>
       <c r="G1355" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39309,7 +39312,7 @@
         <v>28.75</v>
       </c>
       <c r="G1356" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39335,7 +39338,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1357" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39361,7 +39364,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39387,7 +39390,7 @@
         <v>28.75</v>
       </c>
       <c r="G1359" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39413,7 +39416,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39439,7 +39442,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1361" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39465,7 +39468,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1362" t="s">
-        <v>719</v>
+        <v>750</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39491,7 +39494,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1363" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39569,7 +39572,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1366" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -39621,7 +39624,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -39725,7 +39728,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1372" t="s">
-        <v>719</v>
+        <v>750</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -44873,7 +44876,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1570" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44899,7 +44902,7 @@
         <v>28.75</v>
       </c>
       <c r="G1571" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45029,7 +45032,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1576" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45471,7 +45474,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1593" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45523,7 +45526,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1595" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45653,7 +45656,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1600" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45679,7 +45682,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1601" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -46017,7 +46020,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1614" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -66141,7 +66144,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G2388" t="s">
-        <v>805</v>
+        <v>1150</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66167,7 +66170,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66193,7 +66196,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66219,7 +66222,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G2391" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66245,7 +66248,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66271,7 +66274,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66297,7 +66300,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66323,7 +66326,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66349,7 +66352,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G2396" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66375,7 +66378,7 @@
         <v>26.75</v>
       </c>
       <c r="G2397" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66401,7 +66404,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2398" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66427,7 +66430,7 @@
         <v>27</v>
       </c>
       <c r="G2399" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66453,7 +66456,7 @@
         <v>27</v>
       </c>
       <c r="G2400" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66479,7 +66482,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66505,7 +66508,7 @@
         <v>26.25</v>
       </c>
       <c r="G2402" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66531,7 +66534,7 @@
         <v>25.5</v>
       </c>
       <c r="G2403" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66557,7 +66560,7 @@
         <v>25.25</v>
       </c>
       <c r="G2404" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66609,7 +66612,7 @@
         <v>25.25</v>
       </c>
       <c r="G2406" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66661,7 +66664,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G2408" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66687,7 +66690,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G2409" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66713,7 +66716,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G2410" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66739,7 +66742,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2411" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66765,7 +66768,7 @@
         <v>25.5</v>
       </c>
       <c r="G2412" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66817,7 +66820,7 @@
         <v>26</v>
       </c>
       <c r="G2414" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66843,7 +66846,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2415" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66869,7 +66872,7 @@
         <v>27</v>
       </c>
       <c r="G2416" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66895,7 +66898,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66921,7 +66924,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G2418" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66947,7 +66950,7 @@
         <v>27.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66973,7 +66976,7 @@
         <v>27.5</v>
       </c>
       <c r="G2420" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66999,7 +67002,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67025,7 +67028,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2422" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67051,7 +67054,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G2423" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67077,7 +67080,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2424" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67103,7 +67106,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G2425" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67129,7 +67132,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2426" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67155,7 +67158,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2427" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67181,7 +67184,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2428" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67207,7 +67210,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2429" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67233,7 +67236,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67259,7 +67262,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67285,7 +67288,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2432" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67311,7 +67314,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67337,7 +67340,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G2434" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67363,7 +67366,7 @@
         <v>29</v>
       </c>
       <c r="G2435" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67389,7 +67392,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G2436" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67415,7 +67418,7 @@
         <v>28.25</v>
       </c>
       <c r="G2437" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67441,7 +67444,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G2438" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67467,7 +67470,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67493,7 +67496,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G2440" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67519,7 +67522,7 @@
         <v>27</v>
       </c>
       <c r="G2441" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67545,7 +67548,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2442" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67571,7 +67574,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G2443" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67597,7 +67600,7 @@
         <v>27.25</v>
       </c>
       <c r="G2444" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67623,7 +67626,7 @@
         <v>27.25</v>
       </c>
       <c r="G2445" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67649,7 +67652,7 @@
         <v>27.25</v>
       </c>
       <c r="G2446" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67675,7 +67678,7 @@
         <v>27.25</v>
       </c>
       <c r="G2447" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67701,7 +67704,7 @@
         <v>27.5</v>
       </c>
       <c r="G2448" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67727,7 +67730,7 @@
         <v>27.75</v>
       </c>
       <c r="G2449" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67753,7 +67756,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G2450" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67779,7 +67782,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G2451" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67805,7 +67808,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G2452" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67831,7 +67834,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G2453" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67857,7 +67860,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G2454" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67883,7 +67886,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G2455" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67909,7 +67912,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67935,7 +67938,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67961,7 +67964,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G2458" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67987,7 +67990,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G2459" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68013,7 +68016,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G2460" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68039,7 +68042,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2461" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68065,7 +68068,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68091,7 +68094,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68117,7 +68120,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68143,7 +68146,7 @@
         <v>28.75</v>
       </c>
       <c r="G2465" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68169,7 +68172,7 @@
         <v>29</v>
       </c>
       <c r="G2466" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68195,7 +68198,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68221,7 +68224,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G2468" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68247,7 +68250,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68273,7 +68276,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68299,7 +68302,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68325,7 +68328,7 @@
         <v>29.9500007629395</v>
       </c>
       <c r="G2472" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68351,7 +68354,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68377,7 +68380,7 @@
         <v>30</v>
       </c>
       <c r="G2474" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68403,7 +68406,7 @@
         <v>29.75</v>
       </c>
       <c r="G2475" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68429,7 +68432,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G2476" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68455,7 +68458,7 @@
         <v>30</v>
       </c>
       <c r="G2477" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68481,7 +68484,7 @@
         <v>30.5</v>
       </c>
       <c r="G2478" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68507,7 +68510,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G2479" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68533,7 +68536,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68559,7 +68562,7 @@
         <v>31.25</v>
       </c>
       <c r="G2481" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68585,7 +68588,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G2482" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68611,7 +68614,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68637,7 +68640,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68663,7 +68666,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G2485" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68689,7 +68692,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G2486" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68715,7 +68718,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G2487" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68741,7 +68744,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2488" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68767,7 +68770,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2489" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68793,7 +68796,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G2490" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68819,7 +68822,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G2491" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68845,7 +68848,7 @@
         <v>32.5</v>
       </c>
       <c r="G2492" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68871,7 +68874,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G2493" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68897,7 +68900,7 @@
         <v>33</v>
       </c>
       <c r="G2494" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68923,7 +68926,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G2495" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68949,7 +68952,7 @@
         <v>33</v>
       </c>
       <c r="G2496" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68975,7 +68978,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G2497" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69001,7 +69004,7 @@
         <v>33.5</v>
       </c>
       <c r="G2498" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69027,7 +69030,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G2499" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69053,7 +69056,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G2500" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69079,7 +69082,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G2501" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69105,7 +69108,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G2502" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69131,7 +69134,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G2503" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69157,7 +69160,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G2504" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69183,7 +69186,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G2505" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -69209,7 +69212,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G2506" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -69235,7 +69238,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G2507" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -69261,7 +69264,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G2508" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -69287,7 +69290,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G2509" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -69313,7 +69316,7 @@
         <v>29.25</v>
       </c>
       <c r="G2510" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -69339,7 +69342,7 @@
         <v>28.5</v>
       </c>
       <c r="G2511" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -69365,7 +69368,7 @@
         <v>28</v>
       </c>
       <c r="G2512" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -69391,7 +69394,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G2513" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -69399,7 +69402,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6911805556</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>27610</v>
@@ -69417,9 +69420,35 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2514" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6912268518</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>29951</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>27.3999996185303</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>27.3500003814697</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>27</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="1238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="1239">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8067121505737</t>
+    <t xml:space="preserve">13.8067150115967</t>
   </si>
   <si>
     <t xml:space="preserve">ITM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0577459335327</t>
+    <t xml:space="preserve">14.0577449798584</t>
   </si>
   <si>
     <t xml:space="preserve">13.9573335647583</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3883285522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8896141052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8527975082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9532070159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6185007095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846162796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3842039108276</t>
+    <t xml:space="preserve">13.3883275985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.889612197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8527965545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9532108306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6184988021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846172332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3842058181763</t>
   </si>
   <si>
     <t xml:space="preserve">11.8821420669556</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7348709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2127256393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7307453155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2294597625732</t>
+    <t xml:space="preserve">11.7348699569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2127246856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7307472229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2294616699219</t>
   </si>
   <si>
     <t xml:space="preserve">11.2194204330444</t>
@@ -92,61 +92,61 @@
     <t xml:space="preserve">11.2461957931519</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9148359298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1323957443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6143760681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6813163757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5474338531494</t>
+    <t xml:space="preserve">10.9148349761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1323947906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6143751144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6813182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5474319458008</t>
   </si>
   <si>
     <t xml:space="preserve">11.3466091156006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3131370544434</t>
+    <t xml:space="preserve">11.313138961792</t>
   </si>
   <si>
     <t xml:space="preserve">11.3298740386963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8947515487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8780183792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.045371055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4261627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094257354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7080936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.714786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0494956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7482566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7449102401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2135038375854</t>
+    <t xml:space="preserve">10.8947525024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8780174255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0453720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4261617660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094266891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7080917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7147874832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0494966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7482576370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7449111938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2135028839111</t>
   </si>
   <si>
     <t xml:space="preserve">12.2168493270874</t>
@@ -155,55 +155,55 @@
     <t xml:space="preserve">12.3674688339233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7189121246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.82936668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0201501846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2209749221802</t>
+    <t xml:space="preserve">12.7189130783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8293676376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0201511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2209730148315</t>
   </si>
   <si>
     <t xml:space="preserve">13.3849840164185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0870914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536203384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3347749710083</t>
+    <t xml:space="preserve">13.0870895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.334774017334</t>
   </si>
   <si>
     <t xml:space="preserve">13.3146924972534</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0569667816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109317779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661823272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.287917137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8260183334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9833335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9029989242554</t>
+    <t xml:space="preserve">13.0569658279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109327316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661832809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306047439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2879161834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8260202407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9833326339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.903000831604</t>
   </si>
   <si>
     <t xml:space="preserve">13.2377090454102</t>
@@ -218,76 +218,76 @@
     <t xml:space="preserve">13.0971336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5046977996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8092842102051</t>
+    <t xml:space="preserve">12.5046997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8092832565308</t>
   </si>
   <si>
     <t xml:space="preserve">12.8862686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7055234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7222604751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.916389465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0301904678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327131271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6318893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7021789550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8695306777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5582523345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5682935714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8360586166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7958936691284</t>
+    <t xml:space="preserve">12.7055225372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7222595214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9163904190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0301933288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6318883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7021770477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8695316314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5582513809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5682945251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8360595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494482040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7958946228027</t>
   </si>
   <si>
     <t xml:space="preserve">12.5348215103149</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7791576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7691192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7865648269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5024185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6512603759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.752739906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5836038589478</t>
+    <t xml:space="preserve">12.7791604995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.769118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7865657806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.502420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6512584686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7527389526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5836048126221</t>
   </si>
   <si>
     <t xml:space="preserve">12.4990377426147</t>
@@ -296,97 +296,97 @@
     <t xml:space="preserve">12.5700740814209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5159502029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2791604995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0660514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1641502380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.170916557312</t>
+    <t xml:space="preserve">12.5159511566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2791614532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0660524368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776828765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1641492843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1709146499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.1100273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1269407272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9814853668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7459745407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580247879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231382369995</t>
+    <t xml:space="preserve">12.1269397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9814863204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7459735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580238342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231372833252</t>
   </si>
   <si>
     <t xml:space="preserve">11.697340965271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7785234451294</t>
+    <t xml:space="preserve">11.778525352478</t>
   </si>
   <si>
     <t xml:space="preserve">11.2406768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8212232589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554718017578</t>
+    <t xml:space="preserve">10.8212223052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554727554321</t>
   </si>
   <si>
     <t xml:space="preserve">11.0613946914673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1967000961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4064292907715</t>
+    <t xml:space="preserve">11.196702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4064302444458</t>
   </si>
   <si>
     <t xml:space="preserve">11.5248241424561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6656198501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1886615753174</t>
+    <t xml:space="preserve">10.665620803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1886606216431</t>
   </si>
   <si>
     <t xml:space="preserve">10.5878171920776</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6825332641602</t>
+    <t xml:space="preserve">10.6825323104858</t>
   </si>
   <si>
     <t xml:space="preserve">11.8394117355347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0199708938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3616237640381</t>
+    <t xml:space="preserve">13.0199728012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3616228103638</t>
   </si>
   <si>
     <t xml:space="preserve">13.0233564376831</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1924886703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4969320297241</t>
+    <t xml:space="preserve">13.1924896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4969329833984</t>
   </si>
   <si>
     <t xml:space="preserve">13.4698696136475</t>
@@ -395,43 +395,43 @@
     <t xml:space="preserve">13.5307569503784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4800186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2939701080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108835220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0740947723389</t>
+    <t xml:space="preserve">13.480016708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2939682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548593521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0740957260132</t>
   </si>
   <si>
     <t xml:space="preserve">13.0368852615356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9489336013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827613830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.091007232666</t>
+    <t xml:space="preserve">12.9489326477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9827632904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0910091400146</t>
   </si>
   <si>
     <t xml:space="preserve">13.0707130432129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9962930679321</t>
+    <t xml:space="preserve">12.9962921142578</t>
   </si>
   <si>
     <t xml:space="preserve">12.8576030731201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1113033294678</t>
+    <t xml:space="preserve">13.1113042831421</t>
   </si>
   <si>
     <t xml:space="preserve">13.1248340606689</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">13.1823406219482</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0605640411377</t>
+    <t xml:space="preserve">13.0605630874634</t>
   </si>
   <si>
     <t xml:space="preserve">13.1857233047485</t>
@@ -449,31 +449,31 @@
     <t xml:space="preserve">13.4123649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.567967414856</t>
+    <t xml:space="preserve">13.5679693222046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4157466888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5138444900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.706657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8351993560791</t>
+    <t xml:space="preserve">13.5138425827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7066564559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8352003097534</t>
   </si>
   <si>
     <t xml:space="preserve">14.2106790542603</t>
   </si>
   <si>
-    <t xml:space="preserve">14.457612991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7552900314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838329315186</t>
+    <t xml:space="preserve">14.4576139450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7552909851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838319778442</t>
   </si>
   <si>
     <t xml:space="preserve">15.0157585144043</t>
@@ -482,130 +482,130 @@
     <t xml:space="preserve">14.9853143692017</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3303480148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6652345657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2897567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8297109603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.684253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7722053527832</t>
+    <t xml:space="preserve">15.3303499221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6652326583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2897577285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8297100067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6842555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7722024917603</t>
   </si>
   <si>
     <t xml:space="preserve">14.9514865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7485246658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7180805206299</t>
+    <t xml:space="preserve">14.7485294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7180795669556</t>
   </si>
   <si>
     <t xml:space="preserve">14.877067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992668151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751644134521</t>
+    <t xml:space="preserve">14.7992649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751682281494</t>
   </si>
   <si>
     <t xml:space="preserve">14.9007482528687</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2018041610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939809799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330898284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988451004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9142770767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9278087615967</t>
+    <t xml:space="preserve">15.2018060684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939819335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330936431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988470077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9142761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9278078079224</t>
   </si>
   <si>
     <t xml:space="preserve">14.7383794784546</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7248430252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.542181968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4440851211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0529670715332</t>
+    <t xml:space="preserve">14.7248468399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5421829223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4440841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0529708862305</t>
   </si>
   <si>
     <t xml:space="preserve">15.1443004608154</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1104726791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9548711776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0901784896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2187204360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7823534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6707239151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6166000366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764276504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1599388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2546539306641</t>
+    <t xml:space="preserve">15.1104736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.954870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0901775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2187185287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7823524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6707220077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6166019439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764305114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1599397659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2546529769897</t>
   </si>
   <si>
     <t xml:space="preserve">14.041543006897</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1125793457031</t>
+    <t xml:space="preserve">14.1125802993774</t>
   </si>
   <si>
     <t xml:space="preserve">14.0381603240967</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1430234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1903800964355</t>
+    <t xml:space="preserve">14.1430253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1903839111328</t>
   </si>
   <si>
     <t xml:space="preserve">14.3527507781982</t>
   </si>
   <si>
-    <t xml:space="preserve">14.20729637146</t>
+    <t xml:space="preserve">14.2072944641113</t>
   </si>
   <si>
     <t xml:space="preserve">14.3561344146729</t>
@@ -614,115 +614,115 @@
     <t xml:space="preserve">14.4373188018799</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3730487823486</t>
+    <t xml:space="preserve">14.3730497360229</t>
   </si>
   <si>
     <t xml:space="preserve">14.3087759017944</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2411222457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3392200469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2512722015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464080810547</t>
+    <t xml:space="preserve">14.2411212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3392190933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2512702941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1464061737061</t>
   </si>
   <si>
     <t xml:space="preserve">14.1058158874512</t>
   </si>
   <si>
-    <t xml:space="preserve">14.119345664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2275905609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2715625762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1497898101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0753717422485</t>
+    <t xml:space="preserve">14.1193447113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.227593421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2715654373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1497917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0753707885742</t>
   </si>
   <si>
     <t xml:space="preserve">14.0719871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2749509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667041778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4779100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267490386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7519092559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8161783218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1037092208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0834121704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882772445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1172409057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1544504165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999029159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758043289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3574094772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3912391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893341064453</t>
+    <t xml:space="preserve">14.2749500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667032241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4779090881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267499923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7519073486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8161792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1037101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0834112167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.117241859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.154447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.299901008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758052825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3574113845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3912363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893369674683</t>
   </si>
   <si>
     <t xml:space="preserve">15.1713619232178</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1003265380859</t>
+    <t xml:space="preserve">15.1003255844116</t>
   </si>
   <si>
     <t xml:space="preserve">15.3946199417114</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3168182373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3134355545044</t>
+    <t xml:space="preserve">15.3168172836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3134336471558</t>
   </si>
   <si>
     <t xml:space="preserve">15.4182987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4250640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366926193237</t>
+    <t xml:space="preserve">15.4250621795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366916656494</t>
   </si>
   <si>
     <t xml:space="preserve">15.6753826141357</t>
@@ -731,43 +731,43 @@
     <t xml:space="preserve">15.6449384689331</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7295026779175</t>
+    <t xml:space="preserve">15.7295036315918</t>
   </si>
   <si>
     <t xml:space="preserve">15.6618528366089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6517038345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.682149887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637550354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081516265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6415586471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7024440765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333108901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584711074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588890075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5874338150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6550874710083</t>
+    <t xml:space="preserve">15.651704788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6821451187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637521743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081506729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6415567398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7024431228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.65846824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.458890914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5874357223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.655086517334</t>
   </si>
   <si>
     <t xml:space="preserve">15.7227392196655</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">16.3350086212158</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0339450836182</t>
+    <t xml:space="preserve">16.0339488983154</t>
   </si>
   <si>
     <t xml:space="preserve">16.406042098999</t>
@@ -788,31 +788,31 @@
     <t xml:space="preserve">16.4195766448975</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6935710906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0994930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9980144500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1671466827393</t>
+    <t xml:space="preserve">16.6935729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0994968414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9980125427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1671485900879</t>
   </si>
   <si>
     <t xml:space="preserve">17.4208507537842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5392456054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6407260894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4039344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4885025024414</t>
+    <t xml:space="preserve">17.5392436981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6407241821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.403938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4885063171387</t>
   </si>
   <si>
     <t xml:space="preserve">17.353199005127</t>
@@ -827,25 +827,25 @@
     <t xml:space="preserve">17.4546756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8775157928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8098621368408</t>
+    <t xml:space="preserve">17.877513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8098583221436</t>
   </si>
   <si>
     <t xml:space="preserve">17.7083778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7591190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6745510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5730686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3362808227539</t>
+    <t xml:space="preserve">17.7591209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6745529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.573070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3362846374512</t>
   </si>
   <si>
     <t xml:space="preserve">17.2009754180908</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">17.2348022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2517166137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.217887878418</t>
+    <t xml:space="preserve">17.2517147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2178897857666</t>
   </si>
   <si>
     <t xml:space="preserve">17.3701114654541</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">17.456018447876</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7147521972656</t>
+    <t xml:space="preserve">17.7147560119629</t>
   </si>
   <si>
     <t xml:space="preserve">17.5767612457275</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5595149993896</t>
+    <t xml:space="preserve">17.559513092041</t>
   </si>
   <si>
     <t xml:space="preserve">17.6975059509277</t>
@@ -887,13 +887,13 @@
     <t xml:space="preserve">16.7729587554932</t>
   </si>
   <si>
-    <t xml:space="preserve">17.00754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1662349700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1317386627197</t>
+    <t xml:space="preserve">17.0075416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1662368774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1317367553711</t>
   </si>
   <si>
     <t xml:space="preserve">16.993745803833</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">16.9868469238281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9661464691162</t>
+    <t xml:space="preserve">16.9661483764648</t>
   </si>
   <si>
     <t xml:space="preserve">16.8350563049316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8488540649414</t>
+    <t xml:space="preserve">16.84885597229</t>
   </si>
   <si>
     <t xml:space="preserve">16.8281555175781</t>
@@ -917,22 +917,22 @@
     <t xml:space="preserve">16.7591571807861</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8695526123047</t>
+    <t xml:space="preserve">16.8695507049561</t>
   </si>
   <si>
     <t xml:space="preserve">16.9178504943848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9730491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9385471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1524353027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6625652313232</t>
+    <t xml:space="preserve">16.9730453491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.938549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.152437210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6625633239746</t>
   </si>
   <si>
     <t xml:space="preserve">16.5935668945312</t>
@@ -941,82 +941,82 @@
     <t xml:space="preserve">16.5659694671631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5038757324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8626537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9040508270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.80055809021</t>
+    <t xml:space="preserve">16.5038719177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8626518249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.904052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8005561828613</t>
   </si>
   <si>
     <t xml:space="preserve">16.8971500396729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5383682250977</t>
+    <t xml:space="preserve">16.5383701324463</t>
   </si>
   <si>
     <t xml:space="preserve">16.5590705871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4900741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2416896820068</t>
+    <t xml:space="preserve">16.4900760650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2416877746582</t>
   </si>
   <si>
     <t xml:space="preserve">16.303783416748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2485847473145</t>
+    <t xml:space="preserve">16.2485866546631</t>
   </si>
   <si>
     <t xml:space="preserve">16.1243953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1864891052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1588935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5314712524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2899875640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3175868988037</t>
+    <t xml:space="preserve">16.1864910125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1588897705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5314674377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2899837493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3175830841064</t>
   </si>
   <si>
     <t xml:space="preserve">16.5452728271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3658771514893</t>
+    <t xml:space="preserve">16.3658790588379</t>
   </si>
   <si>
     <t xml:space="preserve">16.4624767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3313808441162</t>
+    <t xml:space="preserve">16.3313827514648</t>
   </si>
   <si>
     <t xml:space="preserve">16.3520812988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6970634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3865795135498</t>
+    <t xml:space="preserve">16.6970615386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3865814208984</t>
   </si>
   <si>
     <t xml:space="preserve">16.4486770629883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5107727050781</t>
+    <t xml:space="preserve">16.5107707977295</t>
   </si>
   <si>
     <t xml:space="preserve">16.4210758209229</t>
@@ -1025,82 +1025,82 @@
     <t xml:space="preserve">16.4348773956299</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3934783935547</t>
+    <t xml:space="preserve">16.393482208252</t>
   </si>
   <si>
     <t xml:space="preserve">16.4969730377197</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5245704650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4003810882568</t>
+    <t xml:space="preserve">16.5245723724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4003791809082</t>
   </si>
   <si>
     <t xml:space="preserve">16.4555759429932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.358980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2830848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5521717071533</t>
+    <t xml:space="preserve">16.3589782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2830867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5521697998047</t>
   </si>
   <si>
     <t xml:space="preserve">16.1795921325684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2071914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1933879852295</t>
+    <t xml:space="preserve">16.2071895599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1933917999268</t>
   </si>
   <si>
     <t xml:space="preserve">16.1519927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9036045074463</t>
+    <t xml:space="preserve">15.9036054611206</t>
   </si>
   <si>
     <t xml:space="preserve">15.5586242675781</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965295791626</t>
+    <t xml:space="preserve">15.4965267181396</t>
   </si>
   <si>
     <t xml:space="preserve">15.9381046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7794151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7656145095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7863121032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9795017242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9312057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7035160064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6483201980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8415098190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7518157958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691101074219</t>
+    <t xml:space="preserve">15.7794132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7656164169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7863111495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9795036315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9312028884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.703516960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6483221054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8415117263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7518138885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691091537476</t>
   </si>
   <si>
     <t xml:space="preserve">15.8622093200684</t>
@@ -1112,55 +1112,55 @@
     <t xml:space="preserve">15.8967094421387</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6276226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7173185348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.53102684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034265518188</t>
+    <t xml:space="preserve">15.6276216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7173175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034275054932</t>
   </si>
   <si>
     <t xml:space="preserve">15.4413318634033</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2481422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3171396255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3309383392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.282642364502</t>
+    <t xml:space="preserve">15.2481441497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3171415328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3309364318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2826404571533</t>
   </si>
   <si>
     <t xml:space="preserve">15.3792371749878</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2619428634644</t>
+    <t xml:space="preserve">15.261944770813</t>
   </si>
   <si>
     <t xml:space="preserve">15.6000242233276</t>
   </si>
   <si>
-    <t xml:space="preserve">15.489631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9519052505493</t>
+    <t xml:space="preserve">15.4896287918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.951904296875</t>
   </si>
   <si>
     <t xml:space="preserve">15.9726047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9864025115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0415992736816</t>
+    <t xml:space="preserve">15.9864015579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.041597366333</t>
   </si>
   <si>
     <t xml:space="preserve">15.8553104400635</t>
@@ -1169,148 +1169,148 @@
     <t xml:space="preserve">15.7932119369507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4758281707764</t>
+    <t xml:space="preserve">15.4758319854736</t>
   </si>
   <si>
     <t xml:space="preserve">15.2895402908325</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1791477203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2067451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3999366760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2343454360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3033399581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137363433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.386137008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.634521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1450939178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4831714630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.607364654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.37278175354</t>
+    <t xml:space="preserve">15.1791467666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2067461013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3999357223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2343435287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137344360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3861351013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6345233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.145092010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.48317527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6073684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3727779388428</t>
   </si>
   <si>
     <t xml:space="preserve">16.6349678039551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.414176940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0898971557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2002925872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7315616607666</t>
+    <t xml:space="preserve">16.4141788482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0898952484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.200288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7315578460693</t>
   </si>
   <si>
     <t xml:space="preserve">16.69016456604</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4762763977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7522602081299</t>
+    <t xml:space="preserve">16.4762744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7522563934326</t>
   </si>
   <si>
     <t xml:space="preserve">16.6487636566162</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6280670166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0420417785645</t>
+    <t xml:space="preserve">16.6280689239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0420436859131</t>
   </si>
   <si>
     <t xml:space="preserve">17.0765419006348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1110363006592</t>
+    <t xml:space="preserve">17.1110401153564</t>
   </si>
   <si>
     <t xml:space="preserve">17.2145328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1455383300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1800365447998</t>
+    <t xml:space="preserve">17.1455402374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1800346374512</t>
   </si>
   <si>
     <t xml:space="preserve">16.00710105896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2140884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1105937957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5931253433228</t>
+    <t xml:space="preserve">16.2140865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1105976104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5931272506714</t>
   </si>
   <si>
     <t xml:space="preserve">15.6621208190918</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0066585540771</t>
+    <t xml:space="preserve">15.0066566467285</t>
   </si>
   <si>
     <t xml:space="preserve">14.730673789978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9031639099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9721584320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551334381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1101522445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0411558151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0756530761719</t>
+    <t xml:space="preserve">14.9031629562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9721622467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.455132484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1101512908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0411577224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0756540298462</t>
   </si>
   <si>
     <t xml:space="preserve">15.3516397476196</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4206342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5241289138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6966218948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156669616699</t>
+    <t xml:space="preserve">15.42063331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5241298675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6966190338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156650543213</t>
   </si>
   <si>
     <t xml:space="preserve">15.874249458313</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">15.3792839050293</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7782526016235</t>
+    <t xml:space="preserve">14.7782535552979</t>
   </si>
   <si>
     <t xml:space="preserve">14.4247074127197</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5307693481445</t>
+    <t xml:space="preserve">14.5307683944702</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600620269775</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">13.8873147964478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1135835647583</t>
+    <t xml:space="preserve">14.1135854721069</t>
   </si>
   <si>
     <t xml:space="preserve">14.3186416625977</t>
@@ -1376,28 +1376,28 @@
     <t xml:space="preserve">14.7075443267822</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1671533584595</t>
+    <t xml:space="preserve">15.1671543121338</t>
   </si>
   <si>
     <t xml:space="preserve">15.2025108337402</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5661249160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6368350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2832870483398</t>
+    <t xml:space="preserve">14.566125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6368370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2832880020142</t>
   </si>
   <si>
     <t xml:space="preserve">14.085301399231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8136072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3539981842041</t>
+    <t xml:space="preserve">14.8136081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3539962768555</t>
   </si>
   <si>
     <t xml:space="preserve">14.3893527984619</t>
@@ -1415,19 +1415,19 @@
     <t xml:space="preserve">14.2479343414307</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2125797271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.071159362793</t>
+    <t xml:space="preserve">14.2125787734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0711603164673</t>
   </si>
   <si>
     <t xml:space="preserve">13.9438819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8731746673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8166074752808</t>
+    <t xml:space="preserve">13.8731756210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8166084289551</t>
   </si>
   <si>
     <t xml:space="preserve">13.8590326309204</t>
@@ -1436,22 +1436,22 @@
     <t xml:space="preserve">14.0145921707153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9297409057617</t>
+    <t xml:space="preserve">13.929741859436</t>
   </si>
   <si>
     <t xml:space="preserve">14.0004501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0994424819946</t>
+    <t xml:space="preserve">14.0994434356689</t>
   </si>
   <si>
     <t xml:space="preserve">13.9721660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0287342071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0570182800293</t>
+    <t xml:space="preserve">14.0287351608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570163726807</t>
   </si>
   <si>
     <t xml:space="preserve">14.1277265548706</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">14.9196720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6721868515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4347763061523</t>
+    <t xml:space="preserve">14.6721878051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4347772598267</t>
   </si>
   <si>
     <t xml:space="preserve">13.5054845809937</t>
@@ -1475,13 +1475,13 @@
     <t xml:space="preserve">13.3782081604004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4630603790283</t>
+    <t xml:space="preserve">13.463059425354</t>
   </si>
   <si>
     <t xml:space="preserve">13.5620527267456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.533766746521</t>
+    <t xml:space="preserve">13.5337677001953</t>
   </si>
   <si>
     <t xml:space="preserve">13.1660804748535</t>
@@ -1496,22 +1496,22 @@
     <t xml:space="preserve">12.1620082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6569709777832</t>
+    <t xml:space="preserve">12.6569728851318</t>
   </si>
   <si>
     <t xml:space="preserve">13.4064912796021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5479097366333</t>
+    <t xml:space="preserve">13.5479106903076</t>
   </si>
   <si>
     <t xml:space="preserve">13.7883224487305</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7741804122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5903348922729</t>
+    <t xml:space="preserve">13.7741813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5903358459473</t>
   </si>
   <si>
     <t xml:space="preserve">13.4489183425903</t>
@@ -1526,10 +1526,10 @@
     <t xml:space="preserve">13.0105180740356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1519374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2933568954468</t>
+    <t xml:space="preserve">13.1519384384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2933578491211</t>
   </si>
   <si>
     <t xml:space="preserve">12.9256687164307</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">12.9963779449463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2367877960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0953702926636</t>
+    <t xml:space="preserve">13.2367868423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0953712463379</t>
   </si>
   <si>
     <t xml:space="preserve">13.6469020843506</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">13.2509326934814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2085046768188</t>
+    <t xml:space="preserve">13.2085065841675</t>
   </si>
   <si>
     <t xml:space="preserve">13.0812292098999</t>
@@ -1574,22 +1574,22 @@
     <t xml:space="preserve">12.5296964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8973846435547</t>
+    <t xml:space="preserve">12.8973836898804</t>
   </si>
   <si>
     <t xml:space="preserve">12.6004037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7317543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5761957168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.519627571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7176132202148</t>
+    <t xml:space="preserve">13.7317562103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5761938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5196285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7176122665405</t>
   </si>
   <si>
     <t xml:space="preserve">13.8307476043701</t>
@@ -1604,10 +1604,10 @@
     <t xml:space="preserve">13.7458972930908</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0428762435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8448915481567</t>
+    <t xml:space="preserve">14.0428781509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8448905944824</t>
   </si>
   <si>
     <t xml:space="preserve">14.5417671203613</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">13.9891805648804</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2073078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4399747848511</t>
+    <t xml:space="preserve">14.2073097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4399757385254</t>
   </si>
   <si>
     <t xml:space="preserve">14.2654752731323</t>
@@ -1640,16 +1640,16 @@
     <t xml:space="preserve">14.4981412887573</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4690580368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3527231216431</t>
+    <t xml:space="preserve">14.4690599441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3527250289917</t>
   </si>
   <si>
     <t xml:space="preserve">14.3381814956665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5126819610596</t>
+    <t xml:space="preserve">14.5126829147339</t>
   </si>
   <si>
     <t xml:space="preserve">14.3963499069214</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">14.6871843338013</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4254331588745</t>
+    <t xml:space="preserve">14.4254350662231</t>
   </si>
   <si>
     <t xml:space="preserve">14.4835996627808</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6144781112671</t>
+    <t xml:space="preserve">14.6144762039185</t>
   </si>
   <si>
     <t xml:space="preserve">14.8326034545898</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">15.1234378814697</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1961460113525</t>
+    <t xml:space="preserve">15.1961479187012</t>
   </si>
   <si>
     <t xml:space="preserve">15.4142723083496</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4506273269653</t>
+    <t xml:space="preserve">15.450629234314</t>
   </si>
   <si>
     <t xml:space="preserve">15.3415641784668</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">15.6687545776367</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0507297515869</t>
+    <t xml:space="preserve">15.0507316589355</t>
   </si>
   <si>
     <t xml:space="preserve">15.0870809555054</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">14.5781221389771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.759895324707</t>
+    <t xml:space="preserve">14.7598934173584</t>
   </si>
   <si>
     <t xml:space="preserve">14.6508321762085</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">14.5272254943848</t>
   </si>
   <si>
-    <t xml:space="preserve">14.454517364502</t>
+    <t xml:space="preserve">14.4545154571533</t>
   </si>
   <si>
     <t xml:space="preserve">14.7962493896484</t>
@@ -1751,25 +1751,25 @@
     <t xml:space="preserve">16.5049076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6139678955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5412635803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8320960998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6503238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.577615737915</t>
+    <t xml:space="preserve">16.6139698028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5412616729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8320980072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6503257751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5776138305664</t>
   </si>
   <si>
     <t xml:space="preserve">16.8684501647949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7593841552734</t>
+    <t xml:space="preserve">16.7593860626221</t>
   </si>
   <si>
     <t xml:space="preserve">17.0502223968506</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">17.4864730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4137649536133</t>
+    <t xml:space="preserve">17.4137668609619</t>
   </si>
   <si>
     <t xml:space="preserve">17.268346786499</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">17.5228309631348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8136653900146</t>
+    <t xml:space="preserve">17.8136672973633</t>
   </si>
   <si>
     <t xml:space="preserve">17.7409572601318</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">17.631893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7046031951904</t>
+    <t xml:space="preserve">17.7046012878418</t>
   </si>
   <si>
     <t xml:space="preserve">17.6682453155518</t>
@@ -1811,13 +1811,13 @@
     <t xml:space="preserve">17.9227294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1045017242432</t>
+    <t xml:space="preserve">18.1044998168945</t>
   </si>
   <si>
     <t xml:space="preserve">17.8500194549561</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9590835571289</t>
+    <t xml:space="preserve">17.9590816497803</t>
   </si>
   <si>
     <t xml:space="preserve">18.177209854126</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">18.0317897796631</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2862739562988</t>
+    <t xml:space="preserve">18.2862720489502</t>
   </si>
   <si>
     <t xml:space="preserve">18.3589820861816</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">18.4680442810059</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5771064758301</t>
+    <t xml:space="preserve">18.5771083831787</t>
   </si>
   <si>
     <t xml:space="preserve">17.9954395294189</t>
@@ -1853,10 +1853,10 @@
     <t xml:space="preserve">18.2499198913574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3953342437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.213565826416</t>
+    <t xml:space="preserve">18.395336151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2135639190674</t>
   </si>
   <si>
     <t xml:space="preserve">18.3226261138916</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">18.6861705780029</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8315849304199</t>
+    <t xml:space="preserve">18.8315868377686</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951313018799</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">19.0860710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.26784324646</t>
+    <t xml:space="preserve">19.2678413391113</t>
   </si>
   <si>
     <t xml:space="preserve">19.1224231719971</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">19.4132614135742</t>
   </si>
   <si>
-    <t xml:space="preserve">19.449613571167</t>
+    <t xml:space="preserve">19.4496154785156</t>
   </si>
   <si>
     <t xml:space="preserve">16.9048023223877</t>
@@ -1907,25 +1907,25 @@
     <t xml:space="preserve">16.7957420349121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2314872741699</t>
+    <t xml:space="preserve">19.2314891815186</t>
   </si>
   <si>
     <t xml:space="preserve">16.9775123596191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3047027587891</t>
+    <t xml:space="preserve">17.3047008514404</t>
   </si>
   <si>
     <t xml:space="preserve">17.3774127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7952346801758</t>
+    <t xml:space="preserve">18.7952365875244</t>
   </si>
   <si>
     <t xml:space="preserve">18.5407524108887</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8679447174072</t>
+    <t xml:space="preserve">18.8679428100586</t>
   </si>
   <si>
     <t xml:space="preserve">18.9042987823486</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">19.42138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7327480316162</t>
+    <t xml:space="preserve">19.7327499389648</t>
   </si>
   <si>
     <t xml:space="preserve">20.3944034576416</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">20.3554801940918</t>
   </si>
   <si>
-    <t xml:space="preserve">20.121955871582</t>
+    <t xml:space="preserve">20.1219577789307</t>
   </si>
   <si>
     <t xml:space="preserve">19.9273529052734</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">19.3046245574951</t>
   </si>
   <si>
-    <t xml:space="preserve">19.966272354126</t>
+    <t xml:space="preserve">19.9662742614746</t>
   </si>
   <si>
     <t xml:space="preserve">19.2657051086426</t>
@@ -1979,22 +1979,22 @@
     <t xml:space="preserve">18.7597351074219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1608753204346</t>
+    <t xml:space="preserve">20.1608772277832</t>
   </si>
   <si>
     <t xml:space="preserve">20.044116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1728172302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0560512542725</t>
+    <t xml:space="preserve">21.172815322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0560493469238</t>
   </si>
   <si>
     <t xml:space="preserve">20.9392890930176</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2895755767822</t>
+    <t xml:space="preserve">21.2895736694336</t>
   </si>
   <si>
     <t xml:space="preserve">21.0171318054199</t>
@@ -2021,19 +2021,19 @@
     <t xml:space="preserve">21.6009387969971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7955417633057</t>
+    <t xml:space="preserve">21.7955436706543</t>
   </si>
   <si>
     <t xml:space="preserve">22.0290660858154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0679874420166</t>
+    <t xml:space="preserve">22.0679893493652</t>
   </si>
   <si>
     <t xml:space="preserve">22.5350360870361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5739555358887</t>
+    <t xml:space="preserve">22.57395362854</t>
   </si>
   <si>
     <t xml:space="preserve">22.6517963409424</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">22.7685585021973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8074798583984</t>
+    <t xml:space="preserve">22.8074779510498</t>
   </si>
   <si>
     <t xml:space="preserve">22.7296390533447</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">24.4032249450684</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9091930389404</t>
+    <t xml:space="preserve">24.9091911315918</t>
   </si>
   <si>
     <t xml:space="preserve">24.7145900726318</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">24.5199871063232</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2983989715576</t>
+    <t xml:space="preserve">25.2984008789062</t>
   </si>
   <si>
     <t xml:space="preserve">24.7924308776855</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1427173614502</t>
+    <t xml:space="preserve">25.1427154541016</t>
   </si>
   <si>
     <t xml:space="preserve">24.7535095214844</t>
@@ -2090,22 +2090,22 @@
     <t xml:space="preserve">24.1697006225586</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0140171051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0799236297607</t>
+    <t xml:space="preserve">24.0140190124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0799217224121</t>
   </si>
   <si>
     <t xml:space="preserve">23.7026538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0529384613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4691276550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5858898162842</t>
+    <t xml:space="preserve">24.0529365539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4691295623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5858917236328</t>
   </si>
   <si>
     <t xml:space="preserve">23.1577644348145</t>
@@ -2114,10 +2114,10 @@
     <t xml:space="preserve">23.8583354949951</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7415714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8194160461426</t>
+    <t xml:space="preserve">23.7415733337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8194179534912</t>
   </si>
   <si>
     <t xml:space="preserve">23.6637325286865</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">23.1188449859619</t>
   </si>
   <si>
-    <t xml:space="preserve">23.624813079834</t>
+    <t xml:space="preserve">23.6248111724854</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128749847412</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">22.1847476959229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4961128234863</t>
+    <t xml:space="preserve">22.496114730835</t>
   </si>
   <si>
     <t xml:space="preserve">22.3015098571777</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">22.9631633758545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2356071472168</t>
+    <t xml:space="preserve">23.2356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">22.9242420196533</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">21.9123058319092</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4841785430908</t>
+    <t xml:space="preserve">21.4841766357422</t>
   </si>
   <si>
     <t xml:space="preserve">21.1338939666748</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">21.7177028656006</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6398582458496</t>
+    <t xml:space="preserve">21.6398601531982</t>
   </si>
   <si>
     <t xml:space="preserve">21.2506542205811</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">21.8344631195068</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6787796020508</t>
+    <t xml:space="preserve">21.6787815093994</t>
   </si>
   <si>
     <t xml:space="preserve">21.9901466369629</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">22.4571933746338</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3284969329834</t>
+    <t xml:space="preserve">21.3284950256348</t>
   </si>
   <si>
     <t xml:space="preserve">21.2117347717285</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">20.9782123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6279258728027</t>
+    <t xml:space="preserve">20.6279239654541</t>
   </si>
   <si>
     <t xml:space="preserve">21.873384475708</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">23.2417449951172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0029563903809</t>
+    <t xml:space="preserve">23.0029582977295</t>
   </si>
   <si>
     <t xml:space="preserve">23.2019462585449</t>
@@ -2282,25 +2282,25 @@
     <t xml:space="preserve">23.1621475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5203266143799</t>
+    <t xml:space="preserve">23.5203247070312</t>
   </si>
   <si>
     <t xml:space="preserve">23.9580974578857</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0774898529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4356689453125</t>
+    <t xml:space="preserve">24.0774917602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4356708526611</t>
   </si>
   <si>
     <t xml:space="preserve">24.3162746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3560733795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7938461303711</t>
+    <t xml:space="preserve">24.3560752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7938480377197</t>
   </si>
   <si>
     <t xml:space="preserve">24.1570854187012</t>
@@ -2312,16 +2312,16 @@
     <t xml:space="preserve">24.9132385253906</t>
   </si>
   <si>
-    <t xml:space="preserve">24.555061340332</t>
+    <t xml:space="preserve">24.5550632476807</t>
   </si>
   <si>
     <t xml:space="preserve">24.7540493011475</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2764759063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1172866821289</t>
+    <t xml:space="preserve">24.2764778137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1172885894775</t>
   </si>
   <si>
     <t xml:space="preserve">24.5152626037598</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">25.3510131835938</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4704036712646</t>
+    <t xml:space="preserve">25.470401763916</t>
   </si>
   <si>
     <t xml:space="preserve">25.6693916320801</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">25.0724277496338</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7591114044189</t>
+    <t xml:space="preserve">23.7591094970703</t>
   </si>
   <si>
     <t xml:space="preserve">23.4805297851562</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">23.639720916748</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7989082336426</t>
+    <t xml:space="preserve">23.7989063262939</t>
   </si>
   <si>
     <t xml:space="preserve">24.5948581695557</t>
@@ -2411,13 +2411,13 @@
     <t xml:space="preserve">25.430606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3112144470215</t>
+    <t xml:space="preserve">25.3112125396729</t>
   </si>
   <si>
     <t xml:space="preserve">25.2316188812256</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0673656463623</t>
+    <t xml:space="preserve">26.0673675537109</t>
   </si>
   <si>
     <t xml:space="preserve">26.2663555145264</t>
@@ -2426,25 +2426,25 @@
     <t xml:space="preserve">26.0275688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7887840270996</t>
+    <t xml:space="preserve">25.7887859344482</t>
   </si>
   <si>
     <t xml:space="preserve">25.5499973297119</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5897979736328</t>
+    <t xml:space="preserve">25.5897960662842</t>
   </si>
   <si>
     <t xml:space="preserve">25.9479713439941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1071624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.748987197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.873441696167</t>
+    <t xml:space="preserve">26.1071643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7489852905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8734397888184</t>
   </si>
   <si>
     <t xml:space="preserve">24.0376949310303</t>
@@ -2456,16 +2456,16 @@
     <t xml:space="preserve">22.3661994934082</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0825538635254</t>
+    <t xml:space="preserve">23.0825519561768</t>
   </si>
   <si>
     <t xml:space="preserve">22.9233627319336</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3213386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5999221801758</t>
+    <t xml:space="preserve">23.3213367462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5999202728271</t>
   </si>
   <si>
     <t xml:space="preserve">23.3611354827881</t>
@@ -2483,13 +2483,13 @@
     <t xml:space="preserve">23.8387069702148</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9978942871094</t>
+    <t xml:space="preserve">23.997896194458</t>
   </si>
   <si>
     <t xml:space="preserve">23.7193126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8264083862305</t>
+    <t xml:space="preserve">23.8264102935791</t>
   </si>
   <si>
     <t xml:space="preserve">23.5692901611328</t>
@@ -2522,25 +2522,25 @@
     <t xml:space="preserve">24.2549419403076</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977962493896</t>
+    <t xml:space="preserve">24.2977981567383</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264377593994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9978218078613</t>
+    <t xml:space="preserve">23.99782371521</t>
   </si>
   <si>
     <t xml:space="preserve">23.9121170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8692626953125</t>
+    <t xml:space="preserve">23.8692646026611</t>
   </si>
   <si>
     <t xml:space="preserve">23.7407035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6549987792969</t>
+    <t xml:space="preserve">23.6549968719482</t>
   </si>
   <si>
     <t xml:space="preserve">22.9693431854248</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">22.5836658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9264907836914</t>
+    <t xml:space="preserve">22.92649269104</t>
   </si>
   <si>
     <t xml:space="preserve">23.1407585144043</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">22.7550773620605</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6693725585938</t>
+    <t xml:space="preserve">22.6693744659424</t>
   </si>
   <si>
     <t xml:space="preserve">23.0550518035889</t>
@@ -2573,13 +2573,13 @@
     <t xml:space="preserve">23.2264652252197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7122268676758</t>
+    <t xml:space="preserve">22.7122249603271</t>
   </si>
   <si>
     <t xml:space="preserve">22.4122524261475</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1836109161377</t>
+    <t xml:space="preserve">23.1836090087891</t>
   </si>
   <si>
     <t xml:space="preserve">23.0979061126709</t>
@@ -2591,10 +2591,10 @@
     <t xml:space="preserve">23.3550243377686</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0121994018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3121738433838</t>
+    <t xml:space="preserve">23.0121974945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3121719360352</t>
   </si>
   <si>
     <t xml:space="preserve">23.397876739502</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">22.7979316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4551067352295</t>
+    <t xml:space="preserve">22.4551086425781</t>
   </si>
   <si>
     <t xml:space="preserve">22.4979591369629</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">21.426628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.469482421875</t>
+    <t xml:space="preserve">21.4694805145264</t>
   </si>
   <si>
     <t xml:space="preserve">21.2552146911621</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">20.1410293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9980945587158</t>
+    <t xml:space="preserve">20.9980964660645</t>
   </si>
   <si>
     <t xml:space="preserve">21.1266536712646</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5267086029053</t>
+    <t xml:space="preserve">20.5267105102539</t>
   </si>
   <si>
     <t xml:space="preserve">20.6552696228027</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">21.512336730957</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3409214019775</t>
+    <t xml:space="preserve">21.3409194946289</t>
   </si>
   <si>
     <t xml:space="preserve">22.0265731811523</t>
@@ -2684,19 +2684,19 @@
     <t xml:space="preserve">21.8123073577881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1551322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2408409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6837463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.726598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8980121612549</t>
+    <t xml:space="preserve">22.1551342010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2408390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6837482452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7266006469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8980140686035</t>
   </si>
   <si>
     <t xml:space="preserve">21.7694530487061</t>
@@ -2705,28 +2705,28 @@
     <t xml:space="preserve">21.6408939361572</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1979846954346</t>
+    <t xml:space="preserve">22.1979866027832</t>
   </si>
   <si>
     <t xml:space="preserve">22.0694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9837188720703</t>
+    <t xml:space="preserve">21.9837207794189</t>
   </si>
   <si>
     <t xml:space="preserve">21.8551597595215</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1695098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0838031768799</t>
+    <t xml:space="preserve">21.1695079803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0838012695312</t>
   </si>
   <si>
     <t xml:space="preserve">21.9408664703369</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5551872253418</t>
+    <t xml:space="preserve">21.5551853179932</t>
   </si>
   <si>
     <t xml:space="preserve">21.0409488677979</t>
@@ -3726,6 +3726,9 @@
   </si>
   <si>
     <t xml:space="preserve">27.8999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8999996185303</t>
   </si>
 </sst>
 </file>
@@ -69428,7 +69431,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6912268518</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>29951</v>
@@ -69449,6 +69452,32 @@
         <v>1159</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6912731481</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>28291</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>27.3999996185303</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>26.8999996185303</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>27.2000007629395</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>26.8999996185303</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8067150115967</t>
+    <t xml:space="preserve">13.806713104248</t>
   </si>
   <si>
     <t xml:space="preserve">ITM.MI</t>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">14.0577449798584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9573335647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3883275985718</t>
+    <t xml:space="preserve">13.9573316574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3883304595947</t>
   </si>
   <si>
     <t xml:space="preserve">12.889612197876</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8527965545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9532108306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6184988021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846172332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3842058181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8821420669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7348699569702</t>
+    <t xml:space="preserve">12.8527956008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9532089233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6184997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.384204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8821411132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7348709106445</t>
   </si>
   <si>
     <t xml:space="preserve">11.2127246856689</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">11.2294616699219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2194204330444</t>
+    <t xml:space="preserve">11.2194213867188</t>
   </si>
   <si>
     <t xml:space="preserve">11.2461957931519</t>
@@ -98,58 +98,58 @@
     <t xml:space="preserve">11.1323947906494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6143751144409</t>
+    <t xml:space="preserve">11.6143760681152</t>
   </si>
   <si>
     <t xml:space="preserve">11.6813182830811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474319458008</t>
+    <t xml:space="preserve">11.5474338531494</t>
   </si>
   <si>
     <t xml:space="preserve">11.3466091156006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.313138961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3298740386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8947525024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8780174255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0453720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4261617660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094266891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7080917358398</t>
+    <t xml:space="preserve">11.313136100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3298721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8947534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8780164718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0453691482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4261608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094247817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7080945968628</t>
   </si>
   <si>
     <t xml:space="preserve">11.7147874832153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0494966506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7482576370239</t>
+    <t xml:space="preserve">12.0494947433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7482585906982</t>
   </si>
   <si>
     <t xml:space="preserve">11.7449111938477</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2135028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168493270874</t>
+    <t xml:space="preserve">12.2135038375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168502807617</t>
   </si>
   <si>
     <t xml:space="preserve">12.3674688339233</t>
@@ -158,34 +158,34 @@
     <t xml:space="preserve">12.7189130783081</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8293676376343</t>
+    <t xml:space="preserve">12.82936668396</t>
   </si>
   <si>
     <t xml:space="preserve">13.0201511383057</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2209730148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3849840164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0536193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.334774017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3146924972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569658279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109327316284</t>
+    <t xml:space="preserve">13.2209749221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3849849700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870904922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0536212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3347749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3146934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569677352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109336853027</t>
   </si>
   <si>
     <t xml:space="preserve">12.8661832809448</t>
@@ -194,85 +194,85 @@
     <t xml:space="preserve">13.1306047439575</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2879161834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8260202407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9833326339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.903000831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2377090454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1674213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1138668060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5046997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8092832565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8862686157227</t>
+    <t xml:space="preserve">13.287917137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8260192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9833316802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9030027389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2377109527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.167423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.113865852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971345901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5047006607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8092842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.886266708374</t>
   </si>
   <si>
     <t xml:space="preserve">12.7055225372314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7222595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9163904190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0301933288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327140808105</t>
+    <t xml:space="preserve">12.7222585678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9163932800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0301914215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327121734619</t>
   </si>
   <si>
     <t xml:space="preserve">12.6318883895874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7021770477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8695316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5582513809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5682945251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8360595703125</t>
+    <t xml:space="preserve">12.7021751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.869532585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5582523345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5682935714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8360605239868</t>
   </si>
   <si>
     <t xml:space="preserve">12.8494482040405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7958946228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5348215103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7791604995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.769118309021</t>
+    <t xml:space="preserve">12.7958955764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5348224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7791595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7691192626953</t>
   </si>
   <si>
     <t xml:space="preserve">12.7865657806396</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">12.502420425415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6512584686279</t>
+    <t xml:space="preserve">12.6512594223022</t>
   </si>
   <si>
     <t xml:space="preserve">12.7527389526367</t>
@@ -299,49 +299,49 @@
     <t xml:space="preserve">12.5159511566162</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2791614532471</t>
+    <t xml:space="preserve">12.2791633605957</t>
   </si>
   <si>
     <t xml:space="preserve">12.0660524368286</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1776828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1641492843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1709146499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1100273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1269397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9814863204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7459735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6580238342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3231372833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.697340965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.778525352478</t>
+    <t xml:space="preserve">12.1776809692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1641511917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1709156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1100282669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1269416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9814853668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7459726333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6580228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3231391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6973400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7785243988037</t>
   </si>
   <si>
     <t xml:space="preserve">11.2406768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8212223052979</t>
+    <t xml:space="preserve">10.8212242126465</t>
   </si>
   <si>
     <t xml:space="preserve">10.6554727554321</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">11.0613946914673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.196702003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4064302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5248241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.665620803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1886606216431</t>
+    <t xml:space="preserve">11.1967010498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4064283370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5248231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6656198501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1886625289917</t>
   </si>
   <si>
     <t xml:space="preserve">10.5878171920776</t>
@@ -371,64 +371,64 @@
     <t xml:space="preserve">10.6825323104858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8394117355347</t>
+    <t xml:space="preserve">11.839412689209</t>
   </si>
   <si>
     <t xml:space="preserve">13.0199728012085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3616228103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0233564376831</t>
+    <t xml:space="preserve">13.3616237640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0233545303345</t>
   </si>
   <si>
     <t xml:space="preserve">13.1924896240234</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4969329833984</t>
+    <t xml:space="preserve">13.4969301223755</t>
   </si>
   <si>
     <t xml:space="preserve">13.4698696136475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5307569503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.480016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2939682006836</t>
+    <t xml:space="preserve">13.5307588577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4800176620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2939691543579</t>
   </si>
   <si>
     <t xml:space="preserve">13.3108825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3548593521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0740957260132</t>
+    <t xml:space="preserve">13.3548564910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0740947723389</t>
   </si>
   <si>
     <t xml:space="preserve">13.0368852615356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9489326477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827632904053</t>
+    <t xml:space="preserve">12.948935508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9827613830566</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910091400146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0707130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9962921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8576030731201</t>
+    <t xml:space="preserve">13.0707111358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9962902069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8576011657715</t>
   </si>
   <si>
     <t xml:space="preserve">13.1113042831421</t>
@@ -437,121 +437,121 @@
     <t xml:space="preserve">13.1248340606689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1823406219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0605630874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857233047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4123649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5679693222046</t>
+    <t xml:space="preserve">13.1823415756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0605640411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4123630523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5679655075073</t>
   </si>
   <si>
     <t xml:space="preserve">13.4157466888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5138425827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7066564559937</t>
+    <t xml:space="preserve">13.5138454437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.706657409668</t>
   </si>
   <si>
     <t xml:space="preserve">13.8352003097534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2106790542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4576139450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7552909851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8838319778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0157585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9853143692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303499221802</t>
+    <t xml:space="preserve">14.210675239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.457612991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7552919387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8838348388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0157613754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9853134155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303489685059</t>
   </si>
   <si>
     <t xml:space="preserve">15.6652326583862</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2897577285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8297100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7722024917603</t>
+    <t xml:space="preserve">15.2897567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8297109603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.684253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7722043991089</t>
   </si>
   <si>
     <t xml:space="preserve">14.9514865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7485294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7180795669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.877067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7992649078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9751682281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9007482528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2018060684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8939819335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8330936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9988470077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9142761230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9278078079224</t>
+    <t xml:space="preserve">14.7485246658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7180805206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8770694732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7992668151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9751653671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9007472991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2018089294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8939809799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9988451004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9142770767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.927806854248</t>
   </si>
   <si>
     <t xml:space="preserve">14.7383794784546</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7248468399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5421829223633</t>
+    <t xml:space="preserve">14.7248458862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.542181968689</t>
   </si>
   <si>
     <t xml:space="preserve">14.4440841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0529708862305</t>
+    <t xml:space="preserve">15.0529689788818</t>
   </si>
   <si>
     <t xml:space="preserve">15.1443004608154</t>
@@ -563,289 +563,289 @@
     <t xml:space="preserve">14.954870223999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0901775360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2187185287476</t>
+    <t xml:space="preserve">15.0901765823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2187175750732</t>
   </si>
   <si>
     <t xml:space="preserve">14.7823524475098</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6707220077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6166019439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764305114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1599397659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2546529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.041543006897</t>
+    <t xml:space="preserve">14.6707210540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6166000366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764295578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1599388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2546548843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0415439605713</t>
   </si>
   <si>
     <t xml:space="preserve">14.1125802993774</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0381603240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1430253982544</t>
+    <t xml:space="preserve">14.0381622314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1430263519287</t>
   </si>
   <si>
     <t xml:space="preserve">14.1903839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3527507781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2072944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3561344146729</t>
+    <t xml:space="preserve">14.3527517318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2072954177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3561334609985</t>
   </si>
   <si>
     <t xml:space="preserve">14.4373188018799</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3730497360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3087759017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2411212921143</t>
+    <t xml:space="preserve">14.3730478286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3087768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2411203384399</t>
   </si>
   <si>
     <t xml:space="preserve">14.3392190933228</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2512702941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1464061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058158874512</t>
+    <t xml:space="preserve">14.2512693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1464080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058149337769</t>
   </si>
   <si>
     <t xml:space="preserve">14.1193447113037</t>
   </si>
   <si>
-    <t xml:space="preserve">14.227593421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2715654373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1497917175293</t>
+    <t xml:space="preserve">14.2275915145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2715663909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.149790763855</t>
   </si>
   <si>
     <t xml:space="preserve">14.0753707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0719871520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2749500274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1667032241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4779090881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267499923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7519073486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8161792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1037101745605</t>
+    <t xml:space="preserve">14.0719881057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2749490737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1667041778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.477912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267518997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7519083023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8161773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1037092208862</t>
   </si>
   <si>
     <t xml:space="preserve">15.0834112167358</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1882743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.117241859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.154447555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.299901008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758052825928</t>
+    <t xml:space="preserve">15.1882753372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1172370910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1544504165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999029159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758033752441</t>
   </si>
   <si>
     <t xml:space="preserve">15.3574113845825</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3912363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893369674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1713619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1003255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946199417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3168172836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3134336471558</t>
+    <t xml:space="preserve">15.3912382125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893360137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1713609695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.100323677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946180343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3168153762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3134355545044</t>
   </si>
   <si>
     <t xml:space="preserve">15.4182987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4250621795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366916656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6753826141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6449384689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7295036315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6618528366089</t>
+    <t xml:space="preserve">15.4250631332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366926193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6753816604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6449403762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7295064926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6618547439575</t>
   </si>
   <si>
     <t xml:space="preserve">15.651704788208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6821451187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637521743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081506729126</t>
+    <t xml:space="preserve">15.682147026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637531280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.408148765564</t>
   </si>
   <si>
     <t xml:space="preserve">15.6415567398071</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7024431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.65846824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.458890914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5874357223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.655086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7227392196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3350086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0339488983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.406042098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4026622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4195766448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6935729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0994968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9980125427246</t>
+    <t xml:space="preserve">15.7024402618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333108901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584692001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588918685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5874338150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6550874710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7227420806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3350067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0339508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4060440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.402660369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4195747375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6935710906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.099494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9980163574219</t>
   </si>
   <si>
     <t xml:space="preserve">17.1671485900879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4208507537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5392436981201</t>
+    <t xml:space="preserve">17.4208488464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5392456054688</t>
   </si>
   <si>
     <t xml:space="preserve">17.6407241821289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.403938293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4885063171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.353199005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3870220184326</t>
+    <t xml:space="preserve">17.4039363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.48850440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3531951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3870258331299</t>
   </si>
   <si>
     <t xml:space="preserve">17.522331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4546756744385</t>
+    <t xml:space="preserve">17.4546775817871</t>
   </si>
   <si>
     <t xml:space="preserve">17.877513885498</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8098583221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7083778381348</t>
+    <t xml:space="preserve">17.8098621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7083759307861</t>
   </si>
   <si>
     <t xml:space="preserve">17.7591209411621</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6745529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.573070526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3362846374512</t>
+    <t xml:space="preserve">17.6745510101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730743408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3362865447998</t>
   </si>
   <si>
     <t xml:space="preserve">17.2009754180908</t>
@@ -854,49 +854,49 @@
     <t xml:space="preserve">17.2348022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2517147064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2178897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3701114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.456018447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7147560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5767612457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.559513092041</t>
+    <t xml:space="preserve">17.2517166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2178916931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3701095581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4560203552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7147541046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5767631530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5595169067383</t>
   </si>
   <si>
     <t xml:space="preserve">17.6975059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4698181152344</t>
+    <t xml:space="preserve">17.4698162078857</t>
   </si>
   <si>
     <t xml:space="preserve">17.614709854126</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7729587554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0075416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1662368774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1317367553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.993745803833</t>
+    <t xml:space="preserve">16.7729606628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0075435638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1662330627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1317386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9937438964844</t>
   </si>
   <si>
     <t xml:space="preserve">16.9868469238281</t>
@@ -905,25 +905,25 @@
     <t xml:space="preserve">16.9661483764648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8350563049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.84885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8281555175781</t>
+    <t xml:space="preserve">16.835054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8488540649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8281536102295</t>
   </si>
   <si>
     <t xml:space="preserve">16.7591571807861</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8695507049561</t>
+    <t xml:space="preserve">16.8695545196533</t>
   </si>
   <si>
     <t xml:space="preserve">16.9178504943848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9730453491211</t>
+    <t xml:space="preserve">16.9730472564697</t>
   </si>
   <si>
     <t xml:space="preserve">16.938549041748</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">16.5935668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5659694671631</t>
+    <t xml:space="preserve">16.5659675598145</t>
   </si>
   <si>
     <t xml:space="preserve">16.5038719177246</t>
@@ -947,85 +947,85 @@
     <t xml:space="preserve">16.8626518249512</t>
   </si>
   <si>
-    <t xml:space="preserve">16.904052734375</t>
+    <t xml:space="preserve">16.9040489196777</t>
   </si>
   <si>
     <t xml:space="preserve">16.8005561828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8971500396729</t>
+    <t xml:space="preserve">16.8971519470215</t>
   </si>
   <si>
     <t xml:space="preserve">16.5383701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5590705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4900760650635</t>
+    <t xml:space="preserve">16.5590724945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4900722503662</t>
   </si>
   <si>
     <t xml:space="preserve">16.2416877746582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.303783416748</t>
+    <t xml:space="preserve">16.3037815093994</t>
   </si>
   <si>
     <t xml:space="preserve">16.2485866546631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1243953704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1864910125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1588897705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5314674377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2899837493896</t>
+    <t xml:space="preserve">16.1243934631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1864929199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1588935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5314693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2899856567383</t>
   </si>
   <si>
     <t xml:space="preserve">16.3175830841064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5452728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3658790588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4624767303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3313827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3520812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6970615386963</t>
+    <t xml:space="preserve">16.5452690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3658809661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.462474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3313846588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3520832061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6970634460449</t>
   </si>
   <si>
     <t xml:space="preserve">16.3865814208984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4486770629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5107707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4210758209229</t>
+    <t xml:space="preserve">16.4486751556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5107727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4210777282715</t>
   </si>
   <si>
     <t xml:space="preserve">16.4348773956299</t>
   </si>
   <si>
-    <t xml:space="preserve">16.393482208252</t>
+    <t xml:space="preserve">16.3934803009033</t>
   </si>
   <si>
     <t xml:space="preserve">16.4969730377197</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">16.5245723724365</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4003791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4555759429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3589782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2830867767334</t>
+    <t xml:space="preserve">16.4003810882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4555740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3589820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2830848693848</t>
   </si>
   <si>
     <t xml:space="preserve">16.5521697998047</t>
@@ -1058,97 +1058,97 @@
     <t xml:space="preserve">16.1933917999268</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1519927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9036054611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5586242675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4965267181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9381046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7794132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7656164169312</t>
+    <t xml:space="preserve">16.1519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9036073684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5586233139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4965286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9381055831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7794141769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7656154632568</t>
   </si>
   <si>
     <t xml:space="preserve">15.7863111495972</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9795036315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9312028884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.703516960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6483221054077</t>
+    <t xml:space="preserve">15.9795026779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9312057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7035188674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.648323059082</t>
   </si>
   <si>
     <t xml:space="preserve">15.8415117263794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7518138885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8691091537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8622093200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0277996063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8967094421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6276216506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7173175811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413318634033</t>
+    <t xml:space="preserve">15.7518157958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8691082000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.862208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0277976989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8967084884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6276206970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7173166275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.53102684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034303665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413347244263</t>
   </si>
   <si>
     <t xml:space="preserve">15.2481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3171415328979</t>
+    <t xml:space="preserve">15.3171396255493</t>
   </si>
   <si>
     <t xml:space="preserve">15.3309364318848</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2826404571533</t>
+    <t xml:space="preserve">15.2826414108276</t>
   </si>
   <si>
     <t xml:space="preserve">15.3792371749878</t>
   </si>
   <si>
-    <t xml:space="preserve">15.261944770813</t>
+    <t xml:space="preserve">15.2619428634644</t>
   </si>
   <si>
     <t xml:space="preserve">15.6000242233276</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4896287918091</t>
+    <t xml:space="preserve">15.4896297454834</t>
   </si>
   <si>
     <t xml:space="preserve">15.951904296875</t>
@@ -1160,40 +1160,40 @@
     <t xml:space="preserve">15.9864015579224</t>
   </si>
   <si>
-    <t xml:space="preserve">16.041597366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8553104400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932119369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4758319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2895402908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1791467666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2067461013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3999357223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2343435287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3033409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4137344360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3861351013184</t>
+    <t xml:space="preserve">16.0415992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8553066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932109832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4758329391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2895431518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1791486740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2067470550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3999338150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2343425750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033418655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4137325286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.386137008667</t>
   </si>
   <si>
     <t xml:space="preserve">15.6345233917236</t>
@@ -1205,10 +1205,10 @@
     <t xml:space="preserve">16.48317527771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6073684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3727779388428</t>
+    <t xml:space="preserve">16.6073665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3727798461914</t>
   </si>
   <si>
     <t xml:space="preserve">16.6349678039551</t>
@@ -1220,40 +1220,40 @@
     <t xml:space="preserve">16.0898952484131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.200288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7315578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.69016456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4762744903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7522563934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6487636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6280689239502</t>
+    <t xml:space="preserve">16.2002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.731559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6901626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4762763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7522583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6487655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6280670166016</t>
   </si>
   <si>
     <t xml:space="preserve">17.0420436859131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0765419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1110401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2145328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1455402374268</t>
+    <t xml:space="preserve">17.0765438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1110382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2145347595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1455364227295</t>
   </si>
   <si>
     <t xml:space="preserve">17.1800346374512</t>
@@ -1262,16 +1262,16 @@
     <t xml:space="preserve">16.00710105896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2140865325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1105976104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5931272506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6621208190918</t>
+    <t xml:space="preserve">16.21409034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.110595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5931262969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6621217727661</t>
   </si>
   <si>
     <t xml:space="preserve">15.0066566467285</t>
@@ -1280,43 +1280,43 @@
     <t xml:space="preserve">14.730673789978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9031629562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9721622467041</t>
+    <t xml:space="preserve">14.9031639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9721584320068</t>
   </si>
   <si>
     <t xml:space="preserve">15.455132484436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1101512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0411577224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0756540298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3516397476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.42063331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5241298675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6966190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.874249458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.556056022644</t>
+    <t xml:space="preserve">15.1101493835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0411539077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0756530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3516387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.420636177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5241250991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6966180801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.87424659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5560550689697</t>
   </si>
   <si>
     <t xml:space="preserve">15.7328310012817</t>
@@ -1325,19 +1325,19 @@
     <t xml:space="preserve">15.5914125442505</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3439273834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7782535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4247074127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5307683944702</t>
+    <t xml:space="preserve">15.3439292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792819976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7782554626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4247064590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5307693481445</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600620269775</t>
@@ -1346,55 +1346,55 @@
     <t xml:space="preserve">14.4954147338867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8873147964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1135854721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3186416625977</t>
+    <t xml:space="preserve">13.8873157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1135864257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3186407089233</t>
   </si>
   <si>
     <t xml:space="preserve">14.6014795303345</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0257358551025</t>
+    <t xml:space="preserve">15.0257377624512</t>
   </si>
   <si>
     <t xml:space="preserve">15.0610885620117</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9550256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8489637374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8843154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7075443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671543121338</t>
+    <t xml:space="preserve">14.9550266265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8489627838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8843173980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7075452804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671552658081</t>
   </si>
   <si>
     <t xml:space="preserve">15.2025108337402</t>
   </si>
   <si>
-    <t xml:space="preserve">14.566125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6368370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2832880020142</t>
+    <t xml:space="preserve">14.5661249160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6368360519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2832870483398</t>
   </si>
   <si>
     <t xml:space="preserve">14.085301399231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8136081695557</t>
+    <t xml:space="preserve">14.8136072158813</t>
   </si>
   <si>
     <t xml:space="preserve">14.3539962768555</t>
@@ -1409,31 +1409,31 @@
     <t xml:space="preserve">14.1418695449829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1772241592407</t>
+    <t xml:space="preserve">14.1772222518921</t>
   </si>
   <si>
     <t xml:space="preserve">14.2479343414307</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2125787734985</t>
+    <t xml:space="preserve">14.2125797271729</t>
   </si>
   <si>
     <t xml:space="preserve">14.0711603164673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9438819885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8731756210327</t>
+    <t xml:space="preserve">13.9438829421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8731746673584</t>
   </si>
   <si>
     <t xml:space="preserve">13.8166084289551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8590326309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0145921707153</t>
+    <t xml:space="preserve">13.8590316772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0145931243896</t>
   </si>
   <si>
     <t xml:space="preserve">13.929741859436</t>
@@ -1445,31 +1445,31 @@
     <t xml:space="preserve">14.0994434356689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9721660614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0287351608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0570163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1277265548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9196720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6721878051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4347772598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5054845809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.49134349823</t>
+    <t xml:space="preserve">13.9721651077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0287342071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570154190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1277256011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9196729660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6721887588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.505485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4913444519043</t>
   </si>
   <si>
     <t xml:space="preserve">13.3782081604004</t>
@@ -1481,61 +1481,61 @@
     <t xml:space="preserve">13.5620527267456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5337677001953</t>
+    <t xml:space="preserve">13.533766746521</t>
   </si>
   <si>
     <t xml:space="preserve">13.1660804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7842493057251</t>
+    <t xml:space="preserve">12.7842502593994</t>
   </si>
   <si>
     <t xml:space="preserve">12.6852569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1620082855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6569728851318</t>
+    <t xml:space="preserve">12.1620073318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6569719314575</t>
   </si>
   <si>
     <t xml:spa